--- a/main/catalog_summary.xlsx
+++ b/main/catalog_summary.xlsx
@@ -1880,12 +1880,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ca-cioos_af65bf72-27af-4747-8911-ab05591762ac</t>
+          <t>ca-cioos_ab901b46-43f6-4044-b0c3-b5fd825622f4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kelp forest communities along an otter gradient</t>
+          <t>World View 2 Imagery - Coverage of three regions of the BC Central Coast - Summer 2014, 2015, &amp; 2016</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1913,12 +1913,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>underDevelopment</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Simon Fraser University</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.770751953125, 51.33404377878941], [-127.74902343749999, 51.33404377878941], [-127.74902343749999, 52.19077237113535], [-128.770751953125, 52.19077237113535], [-128.770751953125, 51.33404377878941]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.61145019531247, 51.61801654877371], [-127.91931152343746, 51.61801654877371], [-127.91931152343746, 52.11325243469631], [-128.61145019531247, 52.11325243469631], [-128.61145019531247, 51.61801654877371]]]}</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>[{'max': '50.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1954,7 +1954,11 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>10.21966/nmds-rx42</t>
+        </is>
+      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>2021-09-23</t>
@@ -1962,24 +1966,32 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="W14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X14" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1987,12 +1999,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ca-cioos_ab901b46-43f6-4044-b0c3-b5fd825622f4</t>
+          <t>ca-cioos_af65bf72-27af-4747-8911-ab05591762ac</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2002,7 +2014,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>World View 2 Imagery - Coverage of three regions of the BC Central Coast - Summer 2014, 2015, &amp; 2016</t>
+          <t>Kelp forest communities along an otter gradient</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2020,12 +2032,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>underDevelopment</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2040,7 +2052,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Simon Fraser University</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -2048,12 +2060,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.61145019531247, 51.61801654877371], [-127.91931152343746, 51.61801654877371], [-127.91931152343746, 52.11325243469631], [-128.61145019531247, 52.11325243469631], [-128.61145019531247, 51.61801654877371]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.770751953125, 51.33404377878941], [-127.74902343749999, 51.33404377878941], [-127.74902343749999, 52.19077237113535], [-128.770751953125, 52.19077237113535], [-128.770751953125, 51.33404377878941]]]}</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '50.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2061,11 +2073,7 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>10.21966/nmds-rx42</t>
-        </is>
-      </c>
+      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>2021-09-23</t>
@@ -2073,32 +2081,24 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr"/>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
       <c r="V15" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X15" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -10445,12 +10445,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ca-cioos_5e4f925a-9cf2-4e33-ae22-75c5b326ce6c</t>
+          <t>ca-cioos_5c13b300-e172-4010-a6d8-7586b68a3a96</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Eelgrass (Z. marina) extent at sites along the Central Coast, British Columbia</t>
+          <t>Kelp extent for the McNaughton Group Islands (2017), Manley Island (2017), and Serpent Group Islands (2016), British Columbia, Canada</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -10478,7 +10478,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Nearshore, Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10502,11 +10502,11 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.65354407, 51.37817421], [-127.69773286, 51.37817421], [-127.69773286, 52.1127963], [-128.65354407, 52.1127963], [-128.65354407, 51.37817421]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.30122253, 51.7689035], [-128.05512885, 51.7689035], [-128.05512885, 51.98187882], [-128.30122253, 51.98187882], [-128.30122253, 51.7689035]]]}</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>10.21966/03pw-2190</t>
+          <t>10.21966/82bd-ks94</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -10534,12 +10534,14 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr"/>
+      <c r="U89" t="n">
+        <v>1</v>
+      </c>
       <c r="V89" t="n">
         <v>2</v>
       </c>
       <c r="W89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X89" t="n">
         <v>5</v>
@@ -10564,12 +10566,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ca-cioos_5c13b300-e172-4010-a6d8-7586b68a3a96</t>
+          <t>ca-cioos_5e4f925a-9cf2-4e33-ae22-75c5b326ce6c</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -10579,7 +10581,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Kelp extent for the McNaughton Group Islands (2017), Manley Island (2017), and Serpent Group Islands (2016), British Columbia, Canada</t>
+          <t>Eelgrass (Z. marina) extent at sites along the Central Coast, British Columbia</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -10597,7 +10599,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Nearshore, Geospatial</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10621,11 +10623,11 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.30122253, 51.7689035], [-128.05512885, 51.7689035], [-128.05512885, 51.98187882], [-128.30122253, 51.98187882], [-128.30122253, 51.7689035]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.65354407, 51.37817421], [-127.69773286, 51.37817421], [-127.69773286, 52.1127963], [-128.65354407, 52.1127963], [-128.65354407, 51.37817421]]]}</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -10635,12 +10637,12 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>other, macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>10.21966/82bd-ks94</t>
+          <t>10.21966/03pw-2190</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -10653,14 +10655,12 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U90" t="n">
-        <v>1</v>
-      </c>
+      <c r="U90" t="inlineStr"/>
       <c r="V90" t="n">
         <v>2</v>
       </c>
       <c r="W90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X90" t="n">
         <v>5</v>
@@ -16337,12 +16337,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>ca-cioos_b694a5c5-6a7e-4206-96aa-5b7754323345</t>
+          <t>ca-cioos_b52d5602-f81d-4565-9574-e448e99bc997</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -16352,7 +16352,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Air temperature and relative humidity time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
+          <t>Bathymetry for Six Lakes on Calvert and Hecate Islands - 2016 - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -16370,12 +16370,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Watersheds, Geospatial</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -16398,12 +16398,12 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.30095161, 50.04299371], [-125.08745063, 50.04299371], [-125.08745063, 51.791595], [-128.30095161, 51.791595], [-128.30095161, 50.04299371]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.09646606445312, 51.5996802644666], [-127.9508972167969, 51.5996802644666], [-127.9508972167969, 51.69171329024539], [-128.09646606445312, 51.69171329024539], [-128.09646606445312, 51.5996802644666]]]}</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>[{'max': '741.0', 'min': '3.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
@@ -16411,7 +16411,11 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R141" t="inlineStr"/>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>10.21966/fcwf-p919</t>
+        </is>
+      </c>
       <c r="S141" t="inlineStr">
         <is>
           <t>2022-03-29</t>
@@ -16419,22 +16423,32 @@
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="U141" t="inlineStr"/>
       <c r="V141" t="n">
+        <v>1</v>
+      </c>
+      <c r="W141" t="n">
         <v>2</v>
       </c>
-      <c r="W141" t="n">
-        <v>8</v>
-      </c>
       <c r="X141" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y141" t="inlineStr"/>
-      <c r="Z141" t="inlineStr"/>
-      <c r="AA141" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>[{'year': '2022', 'total': 1}]</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}]</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16442,12 +16456,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ca-cioos_b52d5602-f81d-4565-9574-e448e99bc997</t>
+          <t>ca-cioos_b694a5c5-6a7e-4206-96aa-5b7754323345</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -16457,7 +16471,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Bathymetry for Six Lakes on Calvert and Hecate Islands - 2016 - British Columbia - Canada</t>
+          <t>Air temperature and relative humidity time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -16475,12 +16489,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Watersheds, Geospatial</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -16503,12 +16517,12 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.09646606445312, 51.5996802644666], [-127.9508972167969, 51.5996802644666], [-127.9508972167969, 51.69171329024539], [-128.09646606445312, 51.69171329024539], [-128.09646606445312, 51.5996802644666]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.30095161, 50.04299371], [-125.08745063, 50.04299371], [-125.08745063, 51.791595], [-128.30095161, 51.791595], [-128.30095161, 50.04299371]]]}</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '741.0', 'min': '3.0'}]</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
@@ -16516,11 +16530,7 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R142" t="inlineStr">
-        <is>
-          <t>10.21966/fcwf-p919</t>
-        </is>
-      </c>
+      <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr">
         <is>
           <t>2022-03-29</t>
@@ -16528,32 +16538,22 @@
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="U142" t="inlineStr"/>
       <c r="V142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W142" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="X142" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y142" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
-        </is>
-      </c>
-      <c r="AA142" t="inlineStr">
-        <is>
-          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}]</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="Y142" t="inlineStr"/>
+      <c r="Z142" t="inlineStr"/>
+      <c r="AA142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">

--- a/main/catalog_summary.xlsx
+++ b/main/catalog_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA260"/>
+  <dimension ref="A1:AA261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ca-cioos_ab901b46-43f6-4044-b0c3-b5fd825622f4</t>
+          <t>ca-cioos_af65bf72-27af-4747-8911-ab05591762ac</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>World View 2 Imagery - Coverage of three regions of the BC Central Coast - Summer 2014, 2015, &amp; 2016</t>
+          <t>Kelp forest communities along an otter gradient</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1913,12 +1913,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>underDevelopment</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Simon Fraser University</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.61145019531247, 51.61801654877371], [-127.91931152343746, 51.61801654877371], [-127.91931152343746, 52.11325243469631], [-128.61145019531247, 52.11325243469631], [-128.61145019531247, 51.61801654877371]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.770751953125, 51.33404377878941], [-127.74902343749999, 51.33404377878941], [-127.74902343749999, 52.19077237113535], [-128.770751953125, 52.19077237113535], [-128.770751953125, 51.33404377878941]]]}</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '50.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1954,11 +1954,7 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>10.21966/nmds-rx42</t>
-        </is>
-      </c>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>2021-09-23</t>
@@ -1966,32 +1962,24 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr"/>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
       <c r="V14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X14" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1999,12 +1987,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ca-cioos_af65bf72-27af-4747-8911-ab05591762ac</t>
+          <t>ca-cioos_ab901b46-43f6-4044-b0c3-b5fd825622f4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2014,7 +2002,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kelp forest communities along an otter gradient</t>
+          <t>World View 2 Imagery - Coverage of three regions of the BC Central Coast - Summer 2014, 2015, &amp; 2016</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2032,12 +2020,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>underDevelopment</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2052,7 +2040,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Simon Fraser University</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -2060,12 +2048,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.770751953125, 51.33404377878941], [-127.74902343749999, 51.33404377878941], [-127.74902343749999, 52.19077237113535], [-128.770751953125, 52.19077237113535], [-128.770751953125, 51.33404377878941]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.61145019531247, 51.61801654877371], [-127.91931152343746, 51.61801654877371], [-127.91931152343746, 52.11325243469631], [-128.61145019531247, 52.11325243469631], [-128.61145019531247, 51.61801654877371]]]}</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>[{'max': '50.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2073,7 +2061,11 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>10.21966/nmds-rx42</t>
+        </is>
+      </c>
       <c r="S15" t="inlineStr">
         <is>
           <t>2021-09-23</t>
@@ -2081,24 +2073,32 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="W15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X15" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -10445,12 +10445,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ca-cioos_5c13b300-e172-4010-a6d8-7586b68a3a96</t>
+          <t>ca-cioos_5e4f925a-9cf2-4e33-ae22-75c5b326ce6c</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Kelp extent for the McNaughton Group Islands (2017), Manley Island (2017), and Serpent Group Islands (2016), British Columbia, Canada</t>
+          <t>Eelgrass (Z. marina) extent at sites along the Central Coast, British Columbia</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -10478,7 +10478,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Nearshore, Geospatial</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10502,11 +10502,11 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.30122253, 51.7689035], [-128.05512885, 51.7689035], [-128.05512885, 51.98187882], [-128.30122253, 51.98187882], [-128.30122253, 51.7689035]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.65354407, 51.37817421], [-127.69773286, 51.37817421], [-127.69773286, 52.1127963], [-128.65354407, 52.1127963], [-128.65354407, 51.37817421]]]}</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>other, macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>10.21966/82bd-ks94</t>
+          <t>10.21966/03pw-2190</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -10534,14 +10534,12 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U89" t="n">
-        <v>1</v>
-      </c>
+      <c r="U89" t="inlineStr"/>
       <c r="V89" t="n">
         <v>2</v>
       </c>
       <c r="W89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X89" t="n">
         <v>5</v>
@@ -10566,12 +10564,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ca-cioos_5e4f925a-9cf2-4e33-ae22-75c5b326ce6c</t>
+          <t>ca-cioos_5c13b300-e172-4010-a6d8-7586b68a3a96</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -10581,7 +10579,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Eelgrass (Z. marina) extent at sites along the Central Coast, British Columbia</t>
+          <t>Kelp extent for the McNaughton Group Islands (2017), Manley Island (2017), and Serpent Group Islands (2016), British Columbia, Canada</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -10599,7 +10597,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Nearshore, Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10623,11 +10621,11 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.65354407, 51.37817421], [-127.69773286, 51.37817421], [-127.69773286, 52.1127963], [-128.65354407, 52.1127963], [-128.65354407, 51.37817421]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.30122253, 51.7689035], [-128.05512885, 51.7689035], [-128.05512885, 51.98187882], [-128.30122253, 51.98187882], [-128.30122253, 51.7689035]]]}</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -10637,12 +10635,12 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>10.21966/03pw-2190</t>
+          <t>10.21966/82bd-ks94</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -10655,12 +10653,14 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr"/>
+      <c r="U90" t="n">
+        <v>1</v>
+      </c>
       <c r="V90" t="n">
         <v>2</v>
       </c>
       <c r="W90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X90" t="n">
         <v>5</v>
@@ -14584,12 +14584,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ca-cioos_184b2f81-d87f-4615-a026-15b87930d15c</t>
+          <t>ca-cioos_23bc8c35-2e4e-4382-9296-a52d5ea49889</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -14599,7 +14599,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Aquatic carbon flux data package for Oliver et al. 2017</t>
+          <t>Discharge Time Series (2013-2017) – Calvert Island - Archived Version 3.0</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -14641,59 +14641,59 @@
         </is>
       </c>
       <c r="N126" t="n">
+        <v>1</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>10.21966/sbyc-d030</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>2022-03-29</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr"/>
+      <c r="V126" t="n">
         <v>3</v>
       </c>
-      <c r="O126" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.15002441406247, 51.614605707797466], [-127.96600341796874, 51.614605707797466], [-127.96600341796874, 51.70405535332591], [-128.15002441406247, 51.70405535332591], [-128.15002441406247, 51.614605707797466]]]}</t>
-        </is>
-      </c>
-      <c r="P126" t="inlineStr">
-        <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q126" t="inlineStr">
-        <is>
-          <t>dissolvedOrganicCarbon, other</t>
-        </is>
-      </c>
-      <c r="R126" t="inlineStr">
-        <is>
-          <t>10.21966/1.321324</t>
-        </is>
-      </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="T126" t="inlineStr">
-        <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="U126" t="n">
-        <v>2</v>
-      </c>
-      <c r="V126" t="n">
+      <c r="W126" t="n">
         <v>5</v>
       </c>
-      <c r="W126" t="inlineStr"/>
       <c r="X126" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}, {'relationship': 'parts', 'id': '10.5194/bg-2017-5', 'type': 'dois', 'status_code': 200, 'url': 'https://bg.copernicus.org/articles/14/3743/2017/bg-14-3743-2017-discussion.html'}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -14703,12 +14703,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ca-cioos_23bc8c35-2e4e-4382-9296-a52d5ea49889</t>
+          <t>ca-cioos_184b2f81-d87f-4615-a026-15b87930d15c</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -14718,7 +14718,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Discharge Time Series (2013-2017) – Calvert Island - Archived Version 3.0</t>
+          <t>Aquatic carbon flux data package for Oliver et al. 2017</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -14760,11 +14760,11 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.15002441406247, 51.614605707797466], [-127.96600341796874, 51.614605707797466], [-127.96600341796874, 51.70405535332591], [-128.15002441406247, 51.70405535332591], [-128.15002441406247, 51.614605707797466]]]}</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -14774,12 +14774,12 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>dissolvedOrganicCarbon, other</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>10.21966/sbyc-d030</t>
+          <t>10.21966/1.321324</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
@@ -14789,30 +14789,30 @@
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="U127" t="inlineStr"/>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="U127" t="n">
+        <v>2</v>
+      </c>
       <c r="V127" t="n">
-        <v>3</v>
-      </c>
-      <c r="W127" t="n">
         <v>5</v>
       </c>
+      <c r="W127" t="inlineStr"/>
       <c r="X127" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}, {'relationship': 'parts', 'id': '10.5194/bg-2017-5', 'type': 'dois', 'status_code': 200, 'url': 'https://bg.copernicus.org/articles/14/3743/2017/bg-14-3743-2017-discussion.html'}]</t>
         </is>
       </c>
     </row>
@@ -14822,12 +14822,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ca-cioos_26443ab2-964f-4031-a53b-f132434573e8</t>
+          <t>ca-cioos_25674e9b-1d49-4270-b917-cfe6cdc30f95</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -14837,7 +14837,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Ecosystem Comparison Plots - Calvert Island</t>
+          <t>Watersheds of the northern Pacific coastal temperate rainforest margin</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -14855,7 +14855,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Geospatial, Watersheds</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -14879,16 +14879,16 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13903808593744, 51.626542529786036], [-127.97355651855466, 51.626542529786036], [-127.97355651855466, 51.67766477883444], [-128.13903808593744, 51.67766477883444], [-128.13903808593744, 51.626542529786036]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-143.16578297, 37.67883738], [-104.45881201, 37.67883738], [-104.45881201, 60.91786918], [-143.16578297, 60.91786918], [-143.16578297, 37.67883738]]]}</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '6000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
@@ -14898,7 +14898,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>10.21966/1.56481</t>
+          <t>10.21966/1.715755</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
@@ -14913,25 +14913,25 @@
       </c>
       <c r="U128" t="inlineStr"/>
       <c r="V128" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W128" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X128" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[{'year': '2022', 'total': 2}, {'year': '2023', 'total': 1}]</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}, {'relationship': 'parts', 'id': '10.5194/bg-2017-5', 'type': 'dois', 'status_code': 200, 'url': 'https://bg.copernicus.org/articles/14/3743/2017/bg-14-3743-2017-discussion.html'}]</t>
+          <t>[{'relationship': 'citations', 'id': '10.5061/dryad.05qfttf2q', 'type': 'dois', 'status_code': 200, 'url': 'https://datadryad.org/dataset/doi:10.5061/dryad.05qfttf2q'}, {'relationship': 'citations', 'id': '10.1002/essoar.10510464.1', 'type': 'dois', 'status_code': 403, 'url': 'https://essopenarchive.org/doi/full/10.1002/essoar.10510464.1'}, {'relationship': 'citations', 'id': '10.1029/2023gl103024', 'type': 'dois', 'status_code': 403, 'url': 'https://agupubs.onlinelibrary.wiley.com/doi/10.1029/2023GL103024'}]</t>
         </is>
       </c>
     </row>
@@ -14941,12 +14941,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ca-cioos_25674e9b-1d49-4270-b917-cfe6cdc30f95</t>
+          <t>ca-cioos_26443ab2-964f-4031-a53b-f132434573e8</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -14956,7 +14956,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Watersheds of the northern Pacific coastal temperate rainforest margin</t>
+          <t>Ecosystem Comparison Plots - Calvert Island</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -14974,7 +14974,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Geospatial, Watersheds</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14998,16 +14998,16 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-143.16578297, 37.67883738], [-104.45881201, 37.67883738], [-104.45881201, 60.91786918], [-143.16578297, 60.91786918], [-143.16578297, 37.67883738]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13903808593744, 51.626542529786036], [-127.97355651855466, 51.626542529786036], [-127.97355651855466, 51.67766477883444], [-128.13903808593744, 51.67766477883444], [-128.13903808593744, 51.626542529786036]]]}</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>[{'max': '6000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
@@ -15017,7 +15017,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>10.21966/1.715755</t>
+          <t>10.21966/1.56481</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
@@ -15032,25 +15032,25 @@
       </c>
       <c r="U129" t="inlineStr"/>
       <c r="V129" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W129" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X129" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 2}, {'year': '2023', 'total': 1}]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.5061/dryad.05qfttf2q', 'type': 'dois', 'status_code': 200, 'url': 'https://datadryad.org/dataset/doi:10.5061/dryad.05qfttf2q'}, {'relationship': 'citations', 'id': '10.1002/essoar.10510464.1', 'type': 'dois', 'status_code': 403, 'url': 'https://essopenarchive.org/doi/full/10.1002/essoar.10510464.1'}, {'relationship': 'citations', 'id': '10.1029/2023gl103024', 'type': 'dois', 'status_code': 403, 'url': 'https://agupubs.onlinelibrary.wiley.com/doi/10.1029/2023GL103024'}]</t>
+          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}, {'relationship': 'parts', 'id': '10.5194/bg-2017-5', 'type': 'dois', 'status_code': 200, 'url': 'https://bg.copernicus.org/articles/14/3743/2017/bg-14-3743-2017-discussion.html'}]</t>
         </is>
       </c>
     </row>
@@ -16337,12 +16337,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>ca-cioos_b52d5602-f81d-4565-9574-e448e99bc997</t>
+          <t>ca-cioos_b694a5c5-6a7e-4206-96aa-5b7754323345</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -16352,7 +16352,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Bathymetry for Six Lakes on Calvert and Hecate Islands - 2016 - British Columbia - Canada</t>
+          <t>Air temperature and relative humidity time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -16370,12 +16370,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Watersheds, Geospatial</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -16398,12 +16398,12 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.09646606445312, 51.5996802644666], [-127.9508972167969, 51.5996802644666], [-127.9508972167969, 51.69171329024539], [-128.09646606445312, 51.69171329024539], [-128.09646606445312, 51.5996802644666]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.30095161, 50.04299371], [-125.08745063, 50.04299371], [-125.08745063, 51.791595], [-128.30095161, 51.791595], [-128.30095161, 50.04299371]]]}</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '741.0', 'min': '3.0'}]</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
@@ -16411,11 +16411,7 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R141" t="inlineStr">
-        <is>
-          <t>10.21966/fcwf-p919</t>
-        </is>
-      </c>
+      <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
           <t>2022-03-29</t>
@@ -16423,32 +16419,22 @@
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="U141" t="inlineStr"/>
       <c r="V141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W141" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="X141" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y141" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
-        </is>
-      </c>
-      <c r="AA141" t="inlineStr">
-        <is>
-          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}]</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="Y141" t="inlineStr"/>
+      <c r="Z141" t="inlineStr"/>
+      <c r="AA141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16456,12 +16442,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ca-cioos_b694a5c5-6a7e-4206-96aa-5b7754323345</t>
+          <t>ca-cioos_b52d5602-f81d-4565-9574-e448e99bc997</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -16471,7 +16457,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Air temperature and relative humidity time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
+          <t>Bathymetry for Six Lakes on Calvert and Hecate Islands - 2016 - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -16489,12 +16475,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Watersheds, Geospatial</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -16517,12 +16503,12 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.30095161, 50.04299371], [-125.08745063, 50.04299371], [-125.08745063, 51.791595], [-128.30095161, 51.791595], [-128.30095161, 50.04299371]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.09646606445312, 51.5996802644666], [-127.9508972167969, 51.5996802644666], [-127.9508972167969, 51.69171329024539], [-128.09646606445312, 51.69171329024539], [-128.09646606445312, 51.5996802644666]]]}</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>[{'max': '741.0', 'min': '3.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
@@ -16530,7 +16516,11 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R142" t="inlineStr"/>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>10.21966/fcwf-p919</t>
+        </is>
+      </c>
       <c r="S142" t="inlineStr">
         <is>
           <t>2022-03-29</t>
@@ -16538,22 +16528,32 @@
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="U142" t="inlineStr"/>
       <c r="V142" t="n">
+        <v>1</v>
+      </c>
+      <c r="W142" t="n">
         <v>2</v>
       </c>
-      <c r="W142" t="n">
-        <v>8</v>
-      </c>
       <c r="X142" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y142" t="inlineStr"/>
-      <c r="Z142" t="inlineStr"/>
-      <c r="AA142" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>[{'year': '2022', 'total': 1}]</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}]</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -21063,12 +21063,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>432b05ce-8904-4094-94bf-b97fb6636e41</t>
+          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>ca-cioos_3e90a567-cdd7-41f3-8157-0e7be76eefb8</t>
+          <t>ca-cioos_6c449900-c726-4e9a-b241-707711e253a7</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21078,7 +21078,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Nuchatlaht Survey - Hakai Airborne Coastal Observatory Imagery and Topography Data - Nootka Island British Columbia - 2023</t>
+          <t>Hakai Institute Juvenile Salmon Program Time Series</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -21096,7 +21096,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Juvenile Salmon Program</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -21124,53 +21124,53 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.1, 49.71], [-126.7, 49.71], [-126.7, 50.01], [-127.1, 50.01], [-127.1, 49.71]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.8232006, 49.89790212], [-124.67574133, 49.89790212], [-124.67574133, 50.73488305], [-126.8232006, 50.73488305], [-126.8232006, 49.89790212]]]}</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>[{'max': '500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '9.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>10.21966/kp87-sf64</t>
+          <t>10.21966/1.566666</t>
         </is>
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>2024-01-08</t>
+          <t>2023-11-03</t>
         </is>
       </c>
       <c r="T181" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="U181" t="inlineStr"/>
       <c r="V181" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W181" t="inlineStr"/>
       <c r="X181" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2024', 'total': 1}]</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'references', 'id': '10.1111/fog.12471', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1111/fog.12471'}, {'relationship': 'references', 'id': '10.26428/1606-9919-2021-201-669-685', 'type': 'dois', 'status_code': 403, 'url': 'https://izvestiya.tinro-center.ru/jour/article/view/662'}, {'relationship': 'references', 'id': '10.5281/zenodo.4005400', 'type': 'dois', 'status_code': 200, 'url': 'https://zenodo.org/records/4005400'}, {'relationship': 'references', 'id': '10.48321/d1cw23', 'type': 'dois', 'status_code': 200, 'url': 'https://dmphub.uc3prd.cdlib.net/dmps/10.48321/D1CW23'}, {'relationship': 'references', 'id': '10.48321/d12k5b', 'type': 'dois', 'status_code': 200, 'url': 'https://dmphub.uc3prd.cdlib.net/dmps/10.48321/D12K5B'}, {'relationship': 'references', 'id': '10.21966/9ktc-qm09', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_6f6560e7-7497-4685-9df2-51c66080b7c9'}, {'relationship': 'references', 'id': '10.5683/sp3/socbjj', 'type': 'dois', 'status_code': 200, 'url': 'https://borealisdata.ca/dataset.xhtml?persistentId=doi:10.5683/SP3/SOCBJJ'}, {'relationship': 'citations', 'id': '10.5061/dryad.x69p8czn0', 'type': 'dois', 'status_code': 200, 'url': 'https://datadryad.org/dataset/doi:10.5061/dryad.x69p8czn0'}, {'relationship': 'partOf', 'id': '10.25607/obis.export.234a34a8', 'type': 'dois', 'status_code': 200, 'url': 'https://obis.org/export/234a34a8'}, {'relationship': 'partOf', 'id': '10.25607/obis.occurrence.b89117cd', 'type': 'dois', 'status_code': 200, 'url': 'https://github.com/iobis/obis-open-data'}, {'relationship': 'versions', 'id': '10.21966/e5c1-c396', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_eb1feb98-b11a-4663-b7ab-2216df8187bd'}, {'relationship': 'versions', 'id': '10.21966/99mg-0s52', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_8853a375-f067-4760-b5d1-98c1fcf40c6d'}, {'relationship': 'versions', 'id': '10.21966/c7na-z171', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_1769a04e-b77b-409b-8e48-bc2098bbad3e'}]</t>
         </is>
       </c>
     </row>
@@ -21180,12 +21180,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>582c6ff0-029e-44ba-8ba1-d3f2f39f2005</t>
+          <t>432b05ce-8904-4094-94bf-b97fb6636e41</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>ca-cioos_6f6560e7-7497-4685-9df2-51c66080b7c9</t>
+          <t>ca-cioos_3e90a567-cdd7-41f3-8157-0e7be76eefb8</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -21195,7 +21195,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Genetic Stock Identification of Juvenile Sockeye Salmon Captured in the Discovery Islands and Johnstone Strait BC, Canada</t>
+          <t>Nuchatlaht Survey - Hakai Airborne Coastal Observatory Imagery and Topography Data - Nootka Island British Columbia - 2023</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -21213,7 +21213,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Juvenile Salmon Program</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -21241,53 +21241,53 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.0, 49.88], [-124.4, 49.88], [-124.4, 50.84], [-127.0, 50.84], [-127.0, 49.88]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.1, 49.71], [-126.7, 49.71], [-126.7, 50.01], [-127.1, 50.01], [-127.1, 49.71]]]}</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>[{'max': '9.0', 'min': '0.0'}]</t>
+          <t>[{'max': '500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>10.21966/9ktc-qm09</t>
+          <t>10.21966/kp87-sf64</t>
         </is>
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-08</t>
         </is>
       </c>
       <c r="T182" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="U182" t="inlineStr"/>
       <c r="V182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W182" t="inlineStr"/>
       <c r="X182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>[{'year': '2024', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.21966/1.566666', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_6c449900-c726-4e9a-b241-707711e253a7'}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -21297,12 +21297,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>11051c56-8d67-43fc-a13c-b706e851a5a4</t>
+          <t>582c6ff0-029e-44ba-8ba1-d3f2f39f2005</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>ca-cioos_2d693456-7e65-46be-95d7-6bb697320017</t>
+          <t>ca-cioos_6f6560e7-7497-4685-9df2-51c66080b7c9</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -21312,7 +21312,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Water Level and Weather Station Time Series, Pruth Bay, Kwakshua Channel, Central Coast, BC, Canada (Provisional)</t>
+          <t>Genetic Stock Identification of Juvenile Sockeye Salmon Captured in the Discovery Islands and Johnstone Strait BC, Canada</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -21330,12 +21330,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Oceanography, Watersheds</t>
+          <t>Juvenile Salmon Program</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -21358,49 +21358,53 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-128.1302805556, 51.6544888889]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.0, 49.88], [-124.4, 49.88], [-124.4, 50.84], [-127.0, 50.84], [-127.0, 49.88]]]}</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '9.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>seaSurfaceHeight, other, seaSurfaceTemperature</t>
+          <t>fishAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>10.21966/8d4w-sr07</t>
+          <t>10.21966/9ktc-qm09</t>
         </is>
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="T183" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="U183" t="inlineStr"/>
-      <c r="V183" t="inlineStr"/>
+      <c r="V183" t="n">
+        <v>2</v>
+      </c>
       <c r="W183" t="inlineStr"/>
-      <c r="X183" t="inlineStr"/>
+      <c r="X183" t="n">
+        <v>2</v>
+      </c>
       <c r="Y183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2024', 'total': 1}]</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'citations', 'id': '10.21966/1.566666', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_6c449900-c726-4e9a-b241-707711e253a7'}]</t>
         </is>
       </c>
     </row>
@@ -21410,12 +21414,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>b0e815da-1b17-404d-8bf6-0bdb4a22d170</t>
+          <t>11051c56-8d67-43fc-a13c-b706e851a5a4</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>ca-cioos_c24f23f0-8d16-4bfd-835a-5475f1ecd8e8</t>
+          <t>ca-cioos_2d693456-7e65-46be-95d7-6bb697320017</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -21425,7 +21429,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Extent of Canopy-Forming Kelps, Derived from World View-2, Central Coast, Central Coast, British Columbia</t>
+          <t>Water Level and Weather Station Time Series, Pruth Bay, Kwakshua Channel, Central Coast, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -21443,12 +21447,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Oceanography, Watersheds</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -21467,26 +21471,26 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6993408203125, 51.31001339554933], [-127.65014648437497, 51.31001339554933], [-127.65014648437497, 52.221069523572794], [-128.6993408203125, 52.221069523572794], [-128.6993408203125, 51.31001339554933]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-128.1302805556, 51.6544888889]}</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>seaSurfaceHeight, other, seaSurfaceTemperature</t>
         </is>
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>10.21966/5fs0-nn02</t>
+          <t>10.21966/8d4w-sr07</t>
         </is>
       </c>
       <c r="S184" t="inlineStr">
@@ -21496,17 +21500,13 @@
       </c>
       <c r="T184" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="U184" t="inlineStr"/>
       <c r="V184" t="inlineStr"/>
-      <c r="W184" t="n">
-        <v>2</v>
-      </c>
-      <c r="X184" t="n">
-        <v>2</v>
-      </c>
+      <c r="W184" t="inlineStr"/>
+      <c r="X184" t="inlineStr"/>
       <c r="Y184" t="n">
         <v>0</v>
       </c>
@@ -21527,12 +21527,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>b0e815da-1b17-404d-8bf6-0bdb4a22d170</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>ca-cioos_d1bef0b7-4d15-4bc1-bf34-faca6352891f</t>
+          <t>ca-cioos_c24f23f0-8d16-4bfd-835a-5475f1ecd8e8</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -21542,7 +21542,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Daily satellite (Sentinel 3A and 3B) chlorophyll and suspended matter concentrations for coastal British Columbia and southeast Alaska</t>
+          <t>Extent of Canopy-Forming Kelps, Derived from World View-2, Central Coast, Central Coast, British Columbia</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -21560,12 +21560,12 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -21584,26 +21584,26 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-139.0, 47.0], [-121.5, 47.0], [-121.5, 59.5], [-139.0, 59.5], [-139.0, 47.0]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6993408203125, 51.31001339554933], [-127.65014648437497, 51.31001339554933], [-127.65014648437497, 52.221069523572794], [-128.6993408203125, 52.221069523572794], [-128.6993408203125, 51.31001339554933]]]}</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>phytoplanktonBiomassAndDiversity, particulateMatter, other</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>10.21966/dveq-bt48</t>
+          <t>10.21966/5fs0-nn02</t>
         </is>
       </c>
       <c r="S185" t="inlineStr">
@@ -21613,13 +21613,17 @@
       </c>
       <c r="T185" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="U185" t="inlineStr"/>
       <c r="V185" t="inlineStr"/>
-      <c r="W185" t="inlineStr"/>
-      <c r="X185" t="inlineStr"/>
+      <c r="W185" t="n">
+        <v>2</v>
+      </c>
+      <c r="X185" t="n">
+        <v>2</v>
+      </c>
       <c r="Y185" t="n">
         <v>0</v>
       </c>
@@ -21640,12 +21644,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>abb0b617-3a3e-43ec-b62e-e2918bfc10aa</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>ca-cioos_b8483c9e-81e6-4e1a-b09f-2d66f8fee9a2</t>
+          <t>ca-cioos_d1bef0b7-4d15-4bc1-bf34-faca6352891f</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -21655,7 +21659,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp (Nereocystis luetkeana) derived from fixed-wing surveys (2023), Denman Island to south Quadra Island, British Columbia, Canada</t>
+          <t>Daily satellite (Sentinel 3A and 3B) chlorophyll and suspended matter concentrations for coastal British Columbia and southeast Alaska</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -21673,12 +21677,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Nearshore, Geospatial</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -21701,42 +21705,38 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.3, 50.02], [-125.1, 50.05], [-125.1, 49.9], [-124.8, 49.71], [-124.7, 49.56], [-124.8, 49.55], [-124.9, 49.64], [-125.2, 49.9], [-125.2, 49.9], [-125.3, 50.02]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-139.0, 47.0], [-121.5, 47.0], [-121.5, 59.5], [-139.0, 59.5], [-139.0, 47.0]]]}</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>phytoplanktonBiomassAndDiversity, particulateMatter, other</t>
         </is>
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>10.21966/fmw1-8w35</t>
+          <t>10.21966/dveq-bt48</t>
         </is>
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="T186" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="U186" t="inlineStr"/>
-      <c r="V186" t="n">
-        <v>1</v>
-      </c>
+      <c r="V186" t="inlineStr"/>
       <c r="W186" t="inlineStr"/>
-      <c r="X186" t="n">
-        <v>1</v>
-      </c>
+      <c r="X186" t="inlineStr"/>
       <c r="Y186" t="n">
         <v>0</v>
       </c>
@@ -21757,12 +21757,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>9df42f88-b8d8-4e2d-97bb-ad5ba49f6f1f</t>
+          <t>abb0b617-3a3e-43ec-b62e-e2918bfc10aa</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>ca-cioos_59b33373-ae4a-4719-a3df-0e36a08187d8</t>
+          <t>ca-cioos_b8483c9e-81e6-4e1a-b09f-2d66f8fee9a2</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -21772,7 +21772,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Seagrass Site-Level Production on BC Central Coast</t>
+          <t>Spatial extent of surface canopy kelp (Nereocystis luetkeana) derived from fixed-wing surveys (2023), Denman Island to south Quadra Island, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -21790,12 +21790,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Airborne Coastal Observatory, Nearshore, Geospatial</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -21818,43 +21818,41 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.98931373, 50.8340959], [-127.03580726, 50.8340959], [-127.03580726, 52.33530479], [-128.98931373, 52.33530479], [-128.98931373, 50.8340959]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.3, 50.02], [-125.1, 50.05], [-125.1, 49.9], [-124.8, 49.71], [-124.7, 49.56], [-124.8, 49.55], [-124.9, 49.64], [-125.2, 49.9], [-125.2, 49.9], [-125.3, 50.02]]]}</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>[{'max': '10.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>other, seagrassCoverAndComposition</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>10.21966/ezev-0v96</t>
+          <t>10.21966/fmw1-8w35</t>
         </is>
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="T187" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="U187" t="inlineStr"/>
       <c r="V187" t="n">
         <v>1</v>
       </c>
-      <c r="W187" t="n">
-        <v>1</v>
-      </c>
+      <c r="W187" t="inlineStr"/>
       <c r="X187" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y187" t="n">
         <v>0</v>
@@ -21876,12 +21874,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>9df42f88-b8d8-4e2d-97bb-ad5ba49f6f1f</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>ca-cioos_91107fce-93a4-4bc9-bce4-e7d9e1cf02a0</t>
+          <t>ca-cioos_59b33373-ae4a-4719-a3df-0e36a08187d8</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -21891,7 +21889,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Sentinel 3A and 3B Chlorophyll and Suspended Matter Concentrations for Coastal British Columbia and Southeast Alaska, 8-Day Average (Research)</t>
+          <t>Seagrass Site-Level Production on BC Central Coast</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -21909,7 +21907,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -21937,41 +21935,43 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-139.0, 47.0], [-121.5, 47.0], [-121.5, 59.5], [-139.0, 59.5], [-139.0, 47.0]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.98931373, 50.8340959], [-127.03580726, 50.8340959], [-127.03580726, 52.33530479], [-128.98931373, 52.33530479], [-128.98931373, 50.8340959]]]}</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
+          <t>[{'max': '10.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>phytoplanktonBiomassAndDiversity, particulateMatter, other</t>
+          <t>other, seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>10.21966/175j-8k96</t>
+          <t>10.21966/ezev-0v96</t>
         </is>
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="T188" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="U188" t="inlineStr"/>
-      <c r="V188" t="inlineStr"/>
+      <c r="V188" t="n">
+        <v>1</v>
+      </c>
       <c r="W188" t="n">
         <v>1</v>
       </c>
       <c r="X188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y188" t="n">
         <v>0</v>
@@ -21993,12 +21993,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>bf7c05e8-510d-4449-9e81-4c358ff3f440</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>ca-cioos_1755dc37-8d33-4158-8041-c22536fd5771</t>
+          <t>ca-cioos_91107fce-93a4-4bc9-bce4-e7d9e1cf02a0</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22008,7 +22008,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Bulk and Size-Fractionated Chlorophyll and Phaeopigment Concentrations Collected by Niskin Bottle, BC, Canada (Provisional)</t>
+          <t>Sentinel 3A and 3B Chlorophyll and Suspended Matter Concentrations for Coastal British Columbia and Southeast Alaska, 8-Day Average (Research)</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -22054,32 +22054,32 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-139.0, 47.0], [-121.5, 47.0], [-121.5, 59.5], [-139.0, 59.5], [-139.0, 47.0]]]}</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>[{'max': '650.0', 'min': '0.0'}]</t>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>particulateMatter</t>
+          <t>phytoplanktonBiomassAndDiversity, particulateMatter, other</t>
         </is>
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>10.21966/90h6-b497</t>
+          <t>10.21966/175j-8k96</t>
         </is>
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="T189" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="U189" t="inlineStr"/>
@@ -22110,12 +22110,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>8882a149-fabd-4ecd-98d3-68a2a88aee38</t>
+          <t>bf7c05e8-510d-4449-9e81-4c358ff3f440</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>ca-cioos_d55021c3-a142-4e14-8208-36c9826c1893</t>
+          <t>ca-cioos_1755dc37-8d33-4158-8041-c22536fd5771</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -22125,7 +22125,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Bulk and Size-Fractionated Chlorophyll and Phaeopigment Concentrations Collected by Niskin Bottle, BC, Canada (Research)</t>
+          <t>Bulk and Size-Fractionated Chlorophyll and Phaeopigment Concentrations Collected by Niskin Bottle, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -22167,7 +22167,7 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O190" t="inlineStr">
         <is>
@@ -22181,12 +22181,12 @@
       </c>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>particulateMatter</t>
         </is>
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>10.21966/q5vm-8797</t>
+          <t>10.21966/90h6-b497</t>
         </is>
       </c>
       <c r="S190" t="inlineStr">
@@ -22196,7 +22196,7 @@
       </c>
       <c r="T190" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="U190" t="inlineStr"/>
@@ -22227,12 +22227,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
+          <t>8882a149-fabd-4ecd-98d3-68a2a88aee38</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>ca-cioos_6143028b-028d-46c7-a67d-f3a513435e63</t>
+          <t>ca-cioos_d55021c3-a142-4e14-8208-36c9826c1893</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -22242,7 +22242,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Water Property Measurements from Conductivity-Temperature-Depth Profiles, BC, Canada (Provisional)</t>
+          <t>Bulk and Size-Fractionated Chlorophyll and Phaeopigment Concentrations Collected by Niskin Bottle, BC, Canada (Research)</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -22260,7 +22260,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Juvenile Salmon Program, Oceanography, Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -22284,7 +22284,7 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O191" t="inlineStr">
         <is>
@@ -22293,34 +22293,34 @@
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>[{'max': '700.0', 'min': '1.0'}]</t>
+          <t>[{'max': '650.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>oxygen, subSurfaceSalinity, subSurfaceTemperature</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>10.21966/rj8w-aa62</t>
+          <t>10.21966/q5vm-8797</t>
         </is>
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="T191" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="U191" t="inlineStr"/>
-      <c r="V191" t="n">
-        <v>1</v>
-      </c>
-      <c r="W191" t="inlineStr"/>
+      <c r="V191" t="inlineStr"/>
+      <c r="W191" t="n">
+        <v>1</v>
+      </c>
       <c r="X191" t="n">
         <v>1</v>
       </c>
@@ -22344,12 +22344,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
+          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>ca-cioos_6652a7a9-d27f-4cbe-ac04-435c238e991d</t>
+          <t>ca-cioos_6143028b-028d-46c7-a67d-f3a513435e63</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -22359,7 +22359,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Water Level Time Series, Choke Pass, Central Coast, BC, Canada (Provisional)</t>
+          <t>Water Property Measurements from Conductivity-Temperature-Depth Profiles, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -22377,12 +22377,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Juvenile Salmon Program, Oceanography, Nearshore</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -22405,32 +22405,32 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-128.12103, 51.670666]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>[{'max': '6.0', 'min': '0.0'}]</t>
+          <t>[{'max': '700.0', 'min': '1.0'}]</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>seaSurfaceHeight</t>
+          <t>oxygen, subSurfaceSalinity, subSurfaceTemperature</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>10.21966/kqd6-1j57</t>
+          <t>10.21966/rj8w-aa62</t>
         </is>
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="T192" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="U192" t="inlineStr"/>
@@ -22461,12 +22461,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2081eb2e-67c5-44b7-b048-aeb2c646f238</t>
+          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>ca-cioos_f67c0c58-3225-4dac-9264-1e76f07c9374</t>
+          <t>ca-cioos_6652a7a9-d27f-4cbe-ac04-435c238e991d</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -22476,7 +22476,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Data for the paper "Phylogenomic position of eupelagonemids, abundant, and diverse deep-ocean heterotrophs"</t>
+          <t>Water Level Time Series, Choke Pass, Central Coast, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -22494,7 +22494,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Genomics</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -22514,7 +22514,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>University of British Columbia</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N193" t="n">
@@ -22522,43 +22522,41 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.9661, 51.65001], [-127.966, 51.65001], [-127.966, 51.65], [-127.9661, 51.65], [-127.9661, 51.65001]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-128.12103, 51.670666]}</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>[{'max': '300.0', 'min': '300.0'}]</t>
+          <t>[{'max': '6.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>seaSurfaceHeight</t>
         </is>
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>10.21966/7t4p-s714</t>
+          <t>10.21966/kqd6-1j57</t>
         </is>
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="T193" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
-        </is>
-      </c>
-      <c r="U193" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr"/>
       <c r="V193" t="n">
         <v>1</v>
       </c>
       <c r="W193" t="inlineStr"/>
       <c r="X193" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y193" t="n">
         <v>0</v>
@@ -22580,12 +22578,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>1dfdbadf-6314-4411-8d18-752f6dd920e9</t>
+          <t>2081eb2e-67c5-44b7-b048-aeb2c646f238</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>ca-cioos_67e89414-a93f-496d-9766-9311f0d3954e</t>
+          <t>ca-cioos_f67c0c58-3225-4dac-9264-1e76f07c9374</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -22595,7 +22593,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Motile Invertebrate Surveys - BC Central Coast</t>
+          <t>Data for the paper "Phylogenomic position of eupelagonemids, abundant, and diverse deep-ocean heterotrophs"</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -22613,12 +22611,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Genomics</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -22633,7 +22631,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="N194" t="n">
@@ -22641,55 +22639,55 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.2, 51.63], [-128.1, 51.63], [-128.1, 51.67], [-128.2, 51.67], [-128.2, 51.63]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.9661, 51.65001], [-127.966, 51.65001], [-127.966, 51.65], [-127.9661, 51.65], [-127.9661, 51.65001]]]}</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '-5.0'}]</t>
+          <t>[{'max': '300.0', 'min': '300.0'}]</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>10.21966/0052-wk15</t>
+          <t>10.21966/7t4p-s714</t>
         </is>
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="T194" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="U194" t="inlineStr"/>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="U194" t="n">
+        <v>1</v>
+      </c>
       <c r="V194" t="n">
-        <v>5</v>
-      </c>
-      <c r="W194" t="n">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="W194" t="inlineStr"/>
       <c r="X194" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.48321/d1ae4278b4', 'type': 'dois', 'status_code': 200, 'url': 'https://dmphub.uc3prd.cdlib.net/dmps/10.48321/D1AE4278B4'}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -22699,12 +22697,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>a8f61379-14f9-4ccc-bc9b-4408ba8340d7</t>
+          <t>1dfdbadf-6314-4411-8d18-752f6dd920e9</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>ca-cioos_52797e17-c0ed-46a4-9dcd-e34f801c6205</t>
+          <t>ca-cioos_67e89414-a93f-496d-9766-9311f0d3954e</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -22714,7 +22712,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Fucus Dynamics - Point Intercept Surveys - BC Central Coast</t>
+          <t>Motile Invertebrate Surveys - BC Central Coast</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -22770,45 +22768,45 @@
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>10.21966/v57r-g944</t>
+          <t>10.21966/0052-wk15</t>
         </is>
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="T195" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="U195" t="inlineStr"/>
       <c r="V195" t="n">
+        <v>5</v>
+      </c>
+      <c r="W195" t="n">
         <v>3</v>
       </c>
-      <c r="W195" t="n">
+      <c r="X195" t="n">
         <v>8</v>
       </c>
-      <c r="X195" t="n">
-        <v>11</v>
-      </c>
       <c r="Y195" t="n">
         <v>1</v>
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>[{'year': '2024', 'total': 1}]</t>
+          <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.21966/hpqq-0k76', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_9201118a-b0c4-470f-a76f-396bacc5e93e'}]</t>
+          <t>[{'relationship': 'citations', 'id': '10.48321/d1ae4278b4', 'type': 'dois', 'status_code': 200, 'url': 'https://dmphub.uc3prd.cdlib.net/dmps/10.48321/D1AE4278B4'}]</t>
         </is>
       </c>
     </row>
@@ -22818,12 +22816,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>c4d3a53a-faa2-4c3e-bcd3-cfdb0aef0078</t>
+          <t>a8f61379-14f9-4ccc-bc9b-4408ba8340d7</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>ca-cioos_355467ad-104d-40a6-b06e-52a67bfe247e</t>
+          <t>ca-cioos_52797e17-c0ed-46a4-9dcd-e34f801c6205</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -22833,7 +22831,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Water column CO2 system measurements from January 2016 to December 2023 from Hakai Institute oceanographic station QU39 in northern Strait of Georgia, British Columbia, Canada</t>
+          <t>Fucus Dynamics - Point Intercept Surveys - BC Central Coast</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -22851,12 +22849,12 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -22879,53 +22877,55 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.1, 50.03]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.2, 51.63], [-128.1, 51.63], [-128.1, 51.67], [-128.2, 51.67], [-128.2, 51.63]]]}</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>[{'max': '262.0', 'min': '1.0'}]</t>
+          <t>[{'max': '5.0', 'min': '-5.0'}]</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>inorganicCarbon, oxygen, subSurfaceSalinity, seaSurfaceTemperature, seaSurfaceSalinity, subSurfaceTemperature</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>10.21966/k1xg-6920</t>
+          <t>10.21966/v57r-g944</t>
         </is>
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="T196" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="U196" t="inlineStr"/>
       <c r="V196" t="n">
-        <v>1</v>
-      </c>
-      <c r="W196" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="W196" t="n">
+        <v>8</v>
+      </c>
       <c r="X196" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2024', 'total': 1}]</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'citations', 'id': '10.21966/hpqq-0k76', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_9201118a-b0c4-470f-a76f-396bacc5e93e'}]</t>
         </is>
       </c>
     </row>
@@ -22935,12 +22935,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>52d607c9-46cd-4be9-a752-1b5446272f32</t>
+          <t>c4d3a53a-faa2-4c3e-bcd3-cfdb0aef0078</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>ca-cioos_0507a738-cd65-4ba4-943e-42b9d022b637</t>
+          <t>ca-cioos_355467ad-104d-40a6-b06e-52a67bfe247e</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -22950,7 +22950,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Fraser River Airborne Surveys - 2021 - Hakai Airborne Coastal Observatory</t>
+          <t>Water column CO2 system measurements from January 2016 to December 2023 from Hakai Institute oceanographic station QU39 in northern Strait of Georgia, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -22968,7 +22968,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -22996,43 +22996,41 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.1, 50.5], [-121.7, 50.5], [-121.7, 51.12], [-122.1, 51.12], [-122.1, 50.5]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.1, 50.03]}</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>[{'max': '1500.0', 'min': '185.0'}]</t>
+          <t>[{'max': '262.0', 'min': '1.0'}]</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>inorganicCarbon, oxygen, subSurfaceSalinity, seaSurfaceTemperature, seaSurfaceSalinity, subSurfaceTemperature</t>
         </is>
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>10.21966/ytgc-6g46</t>
+          <t>10.21966/k1xg-6920</t>
         </is>
       </c>
       <c r="S197" t="inlineStr">
         <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
           <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="T197" t="inlineStr">
-        <is>
-          <t>2025-04-23</t>
         </is>
       </c>
       <c r="U197" t="inlineStr"/>
       <c r="V197" t="n">
         <v>1</v>
       </c>
-      <c r="W197" t="n">
-        <v>2</v>
-      </c>
+      <c r="W197" t="inlineStr"/>
       <c r="X197" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y197" t="n">
         <v>0</v>
@@ -23054,12 +23052,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>551bbe09-f182-478b-8d50-2f9a4dbd93ae</t>
+          <t>52d607c9-46cd-4be9-a752-1b5446272f32</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>ca-cioos_189dd319-d5ef-4f2a-a060-df8d47628b86</t>
+          <t>ca-cioos_0507a738-cd65-4ba4-943e-42b9d022b637</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23069,7 +23067,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Elliot Creek Landslide LiDAR Mapping - 2023 - Airborne Coastal Observatory</t>
+          <t>Fraser River Airborne Surveys - 2021 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -23087,7 +23085,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -23111,42 +23109,44 @@
         </is>
       </c>
       <c r="N198" t="n">
+        <v>1</v>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.1, 50.5], [-121.7, 50.5], [-121.7, 51.12], [-122.1, 51.12], [-122.1, 50.5]]]}</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>[{'max': '1500.0', 'min': '185.0'}]</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>10.21966/ytgc-6g46</t>
+        </is>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr"/>
+      <c r="V198" t="n">
+        <v>1</v>
+      </c>
+      <c r="W198" t="n">
         <v>2</v>
-      </c>
-      <c r="O198" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.8, 50.84], [-124.5, 50.84], [-124.5, 51.0], [-124.8, 51.0], [-124.8, 50.84]]]}</t>
-        </is>
-      </c>
-      <c r="P198" t="inlineStr">
-        <is>
-          <t>[{'max': '2300.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q198" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R198" t="inlineStr">
-        <is>
-          <t>10.21966/szqj-b355</t>
-        </is>
-      </c>
-      <c r="S198" t="inlineStr">
-        <is>
-          <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="T198" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="U198" t="inlineStr"/>
-      <c r="V198" t="inlineStr"/>
-      <c r="W198" t="n">
-        <v>3</v>
       </c>
       <c r="X198" t="n">
         <v>3</v>
@@ -23171,12 +23171,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
+          <t>551bbe09-f182-478b-8d50-2f9a4dbd93ae</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>ca-cioos_33a367c1-2706-4301-af99-4455fbe189a0</t>
+          <t>ca-cioos_189dd319-d5ef-4f2a-a060-df8d47628b86</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -23186,7 +23186,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Cryosphere Snow Surveys Southwest British Columbia - Airborne Coastal Observatory</t>
+          <t>Elliot Creek Landslide LiDAR Mapping - 2023 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -23204,7 +23204,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -23232,7 +23232,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.9, 48.62], [-122.1, 48.62], [-122.1, 50.82], [-126.9, 50.82], [-126.9, 48.62]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.8, 50.84], [-124.5, 50.84], [-124.5, 51.0], [-124.8, 51.0], [-124.8, 50.84]]]}</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
@@ -23247,7 +23247,7 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>10.21966/thq7-0g08</t>
+          <t>10.21966/szqj-b355</t>
         </is>
       </c>
       <c r="S199" t="inlineStr">
@@ -23257,16 +23257,16 @@
       </c>
       <c r="T199" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="U199" t="inlineStr"/>
       <c r="V199" t="inlineStr"/>
       <c r="W199" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X199" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y199" t="n">
         <v>0</v>
@@ -23288,12 +23288,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
+          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a</t>
+          <t>ca-cioos_33a367c1-2706-4301-af99-4455fbe189a0</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -23303,7 +23303,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Bute Inlet Geohazard - Topography Surveys - 2023 - Hakai Airborne Coastal Observatory</t>
+          <t>Cryosphere Snow Surveys Southwest British Columbia - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -23345,16 +23345,16 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.9, 50.53], [-124.2, 50.53], [-124.2, 50.99], [-124.9, 50.99], [-124.9, 50.53]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.9, 48.62], [-122.1, 48.62], [-122.1, 50.82], [-126.9, 50.82], [-126.9, 48.62]]]}</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>[{'max': '2600.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2300.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q200" t="inlineStr">
@@ -23364,7 +23364,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>10.21966/e4b8-vp48</t>
+          <t>10.21966/thq7-0g08</t>
         </is>
       </c>
       <c r="S200" t="inlineStr">
@@ -23374,18 +23374,16 @@
       </c>
       <c r="T200" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="U200" t="inlineStr"/>
-      <c r="V200" t="n">
-        <v>1</v>
-      </c>
+      <c r="V200" t="inlineStr"/>
       <c r="W200" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X200" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y200" t="n">
         <v>0</v>
@@ -23407,12 +23405,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>78efda1b-9688-4bcf-b16e-7167c17c0bcb</t>
+          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>ca-cioos_43422dc8-2573-4f60-bf87-df447d57ab7a</t>
+          <t>ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -23422,7 +23420,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>USGS Glacier Mapping - 2023 - Hakai Airborne Coastal Observatory</t>
+          <t>Bute Inlet Geohazard - Topography Surveys - 2023 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -23464,16 +23462,16 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-121.4, 47.68], [-113.0, 47.68], [-113.0, 49.08], [-121.4, 49.08], [-121.4, 47.68]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.9, 50.53], [-124.2, 50.53], [-124.2, 50.99], [-124.9, 50.99], [-124.9, 50.53]]]}</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>[{'max': '2800.0', 'min': '100.0'}]</t>
+          <t>[{'max': '2600.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q201" t="inlineStr">
@@ -23483,7 +23481,7 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>10.21966/bzr6-er66</t>
+          <t>10.21966/e4b8-vp48</t>
         </is>
       </c>
       <c r="S201" t="inlineStr">
@@ -23493,16 +23491,18 @@
       </c>
       <c r="T201" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="U201" t="inlineStr"/>
-      <c r="V201" t="inlineStr"/>
+      <c r="V201" t="n">
+        <v>1</v>
+      </c>
       <c r="W201" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X201" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y201" t="n">
         <v>0</v>
@@ -23524,12 +23524,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
+          <t>78efda1b-9688-4bcf-b16e-7167c17c0bcb</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>ca-cioos_6756b221-28a0-4848-9761-905cbd558cd7</t>
+          <t>ca-cioos_43422dc8-2573-4f60-bf87-df447d57ab7a</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -23539,7 +23539,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Protistan plankton time series from the northern Salish Sea and Central Coast, British Columbia, Canada</t>
+          <t>USGS Glacier Mapping - 2023 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -23557,12 +23557,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -23581,42 +23581,46 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-121.4, 47.68], [-113.0, 47.68], [-113.0, 49.08], [-121.4, 49.08], [-121.4, 47.68]]]}</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>[{'max': '6.0', 'min': '1.0'}]</t>
+          <t>[{'max': '2800.0', 'min': '100.0'}]</t>
         </is>
       </c>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>phytoplanktonBiomassAndDiversity</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>10.21966/jv5k-3k59</t>
+          <t>10.21966/bzr6-er66</t>
         </is>
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="T202" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="U202" t="inlineStr"/>
       <c r="V202" t="inlineStr"/>
-      <c r="W202" t="inlineStr"/>
-      <c r="X202" t="inlineStr"/>
+      <c r="W202" t="n">
+        <v>3</v>
+      </c>
+      <c r="X202" t="n">
+        <v>3</v>
+      </c>
       <c r="Y202" t="n">
         <v>0</v>
       </c>
@@ -23637,12 +23641,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>9d1749f8-9be2-468c-946e-965f92fcdc67</t>
+          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>ca-cioos_6e947d50-8392-42ce-bff9-24b126c7cab7</t>
+          <t>ca-cioos_6756b221-28a0-4848-9761-905cbd558cd7</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -23652,7 +23656,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Spatial extent of eelgrass (Zostera marina) beds from monitoring sites within the greater park ecosystem of Pacific Rim National Park Reserve (2017, 2018)</t>
+          <t>Protistan plankton time series from the northern Salish Sea and Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -23670,12 +23674,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Nearshore, Geospatial</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -23694,46 +23698,42 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.0511576, 48.72717181], [-124.94565833, 48.72717181], [-124.94565833, 49.24536019], [-126.0511576, 49.24536019], [-126.0511576, 48.72717181]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '6.0', 'min': '1.0'}]</t>
         </is>
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>other, seagrassCoverAndComposition</t>
+          <t>phytoplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>10.21966/8mpe-h081</t>
+          <t>10.21966/jv5k-3k59</t>
         </is>
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="T203" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="U203" t="inlineStr"/>
-      <c r="V203" t="n">
-        <v>2</v>
-      </c>
+      <c r="V203" t="inlineStr"/>
       <c r="W203" t="inlineStr"/>
-      <c r="X203" t="n">
-        <v>2</v>
-      </c>
+      <c r="X203" t="inlineStr"/>
       <c r="Y203" t="n">
         <v>0</v>
       </c>
@@ -23754,12 +23754,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
+          <t>9d1749f8-9be2-468c-946e-965f92fcdc67</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>ca-cioos_f25b00ba-ad63-42b3-8021-3fb6aa99baff</t>
+          <t>ca-cioos_6e947d50-8392-42ce-bff9-24b126c7cab7</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -23769,12 +23769,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Fraser River Landslide Project - Sites of Concern 2024</t>
+          <t>Spatial extent of eelgrass (Zostera marina) beds from monitoring sites within the greater park ecosystem of Pacific Rim National Park Reserve (2017, 2018)</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>document</t>
+          <t>dataset</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -23787,7 +23787,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Nearshore, Geospatial</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -23807,53 +23807,49 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Hakai Geospatial</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.0, 49.0], [-119.5, 49.0], [-119.5, 54.34], [-124.0, 54.34], [-124.0, 49.0]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.0511576, 48.72717181], [-124.94565833, 48.72717181], [-124.94565833, 49.24536019], [-126.0511576, 49.24536019], [-126.0511576, 48.72717181]]]}</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>[{'max': '2500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>10.21966/xp9x-m243</t>
+          <t>10.21966/8mpe-h081</t>
         </is>
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="T204" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
-        </is>
-      </c>
-      <c r="U204" t="n">
-        <v>1</v>
-      </c>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr"/>
       <c r="V204" t="n">
-        <v>4</v>
-      </c>
-      <c r="W204" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="W204" t="inlineStr"/>
       <c r="X204" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y204" t="n">
         <v>0</v>
@@ -23875,12 +23871,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
+          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>ca-cioos_c513de71-ac9d-43fa-b693-8f865de4b137</t>
+          <t>ca-cioos_f25b00ba-ad63-42b3-8021-3fb6aa99baff</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -23890,12 +23886,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Fraser River Landslide Project - 2022-2024 - Drone Data</t>
+          <t>Fraser River Landslide Project - Sites of Concern 2024</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>document</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -23908,7 +23904,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -23936,12 +23932,12 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.8, 49.29], [-121.2, 49.29], [-121.2, 52.28], [-122.8, 52.28], [-122.8, 49.29]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.0, 49.0], [-119.5, 49.0], [-119.5, 54.34], [-124.0, 54.34], [-124.0, 49.0]]]}</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>[{'max': '1500.0', 'min': '50.0'}]</t>
+          <t>[{'max': '2500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q205" t="inlineStr">
@@ -23951,30 +23947,30 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>10.21966/qpe8-ay93</t>
+          <t>10.21966/xp9x-m243</t>
         </is>
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="T205" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="U205" t="n">
         <v>1</v>
       </c>
       <c r="V205" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W205" t="n">
         <v>1</v>
       </c>
       <c r="X205" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y205" t="n">
         <v>0</v>
@@ -23996,12 +23992,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>e8414189-54c9-4311-874e-b97f9b7916ae</t>
+          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>ca-cioos_48acba27-5e01-4b41-9a0e-f3fc8d809a13</t>
+          <t>ca-cioos_c513de71-ac9d-43fa-b693-8f865de4b137</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24011,7 +24007,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>MusselSeg: Semantic Segmentation for Rocky Intertidal Mussel Habitat</t>
+          <t>Fraser River Landslide Project - 2022-2024 - Drone Data</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -24029,12 +24025,12 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -24049,7 +24045,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Hakai Geospatial</t>
         </is>
       </c>
       <c r="N206" t="n">
@@ -24057,41 +24053,45 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-130.1, 51.59], [-120.4, 31.75], [-118.4, 33.38], [-124.3, 44.43], [-122.0, 49.35], [-126.2, 51.59], [-130.1, 51.59]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.8, 49.29], [-121.2, 49.29], [-121.2, 52.28], [-122.8, 52.28], [-122.8, 49.29]]]}</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>[{'max': '75.0', 'min': '15.0'}]</t>
+          <t>[{'max': '1500.0', 'min': '50.0'}]</t>
         </is>
       </c>
       <c r="Q206" t="inlineStr">
         <is>
-          <t>other, invertebrateAbundanceAndDistribution</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>10.21966/fbv4-th96</t>
+          <t>10.21966/qpe8-ay93</t>
         </is>
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="T206" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="U206" t="inlineStr"/>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="U206" t="n">
+        <v>1</v>
+      </c>
       <c r="V206" t="n">
         <v>2</v>
       </c>
-      <c r="W206" t="inlineStr"/>
+      <c r="W206" t="n">
+        <v>1</v>
+      </c>
       <c r="X206" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y206" t="n">
         <v>0</v>
@@ -24113,12 +24113,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
+          <t>e8414189-54c9-4311-874e-b97f9b7916ae</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>ca-cioos_d4942b86-d362-40a3-9399-c124c4c263bd</t>
+          <t>ca-cioos_48acba27-5e01-4b41-9a0e-f3fc8d809a13</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -24128,7 +24128,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Larval Dungeness crab abundance and size time series along the coast of British Columbia</t>
+          <t>MusselSeg: Semantic Segmentation for Rocky Intertidal Mussel Habitat</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -24146,7 +24146,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Sentinels of Change</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -24174,41 +24174,41 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.8, 48.3], [-123.2, 48.37], [-123.2, 48.65], [-123.0, 48.77], [-123.3, 49.01], [-122.9, 49.25], [-122.6, 49.4], [-123.2, 49.45], [-123.7, 49.54], [-124.5, 49.89], [-124.8, 50.09], [-126.5, 50.79], [-128.3, 52.31], [-130.4, 54.75], [-133.8, 54.36], [-132.9, 52.85], [-130.3, 51.48], [-128.1, 50.15], [-125.2, 48.62], [-123.8, 48.3]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-130.1, 51.59], [-120.4, 31.75], [-118.4, 33.38], [-124.3, 44.43], [-122.0, 49.35], [-126.2, 51.59], [-130.1, 51.59]]]}</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>[{'max': '2.0', 'min': '0.0'}]</t>
+          <t>[{'max': '75.0', 'min': '15.0'}]</t>
         </is>
       </c>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution</t>
+          <t>other, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>10.21966/36hp-7f40</t>
+          <t>10.21966/fbv4-th96</t>
         </is>
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="T207" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="U207" t="inlineStr"/>
       <c r="V207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W207" t="inlineStr"/>
       <c r="X207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y207" t="n">
         <v>0</v>
@@ -24230,12 +24230,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>265e0ec8-1d85-4e73-b85d-371845dbd08f</t>
+          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>ca-cioos_f762a307-6dfb-41a8-a56c-ecacfb075a0a</t>
+          <t>ca-cioos_d4942b86-d362-40a3-9399-c124c4c263bd</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -24245,7 +24245,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Denali Fault - 2024 - Airborne LiDAR Survey</t>
+          <t>Larval Dungeness crab abundance and size time series along the coast of British Columbia</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -24263,12 +24263,12 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Sentinels of Change</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -24291,43 +24291,41 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-141.3, 62.08], [-139.8, 61.49], [-137.7, 60.61], [-136.8, 60.1], [-136.4, 60.29], [-138.3, 61.12], [-140.1, 61.86], [-141.2, 62.19], [-141.3, 62.08]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.8, 48.3], [-123.2, 48.37], [-123.2, 48.65], [-123.0, 48.77], [-123.3, 49.01], [-122.9, 49.25], [-122.6, 49.4], [-123.2, 49.45], [-123.7, 49.54], [-124.5, 49.89], [-124.8, 50.09], [-126.5, 50.79], [-128.3, 52.31], [-130.4, 54.75], [-133.8, 54.36], [-132.9, 52.85], [-130.3, 51.48], [-128.1, 50.15], [-125.2, 48.62], [-123.8, 48.3]]]}</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>[{'max': '5000.0', 'min': '100.0'}]</t>
+          <t>[{'max': '2.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q208" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>10.21966/wxph-tz51</t>
+          <t>10.21966/36hp-7f40</t>
         </is>
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="T208" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="U208" t="inlineStr"/>
       <c r="V208" t="n">
-        <v>3</v>
-      </c>
-      <c r="W208" t="n">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="W208" t="inlineStr"/>
       <c r="X208" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y208" t="n">
         <v>0</v>
@@ -24349,12 +24347,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
+          <t>265e0ec8-1d85-4e73-b85d-371845dbd08f</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>ca-cioos_5185ac00-8148-4472-adfd-21741d8a10ce</t>
+          <t>ca-cioos_f762a307-6dfb-41a8-a56c-ecacfb075a0a</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -24364,7 +24362,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Sentinels of Change Sea Surface Temperature Time Series Data Along the British Columbia Coast</t>
+          <t>Denali Fault - 2024 - Airborne LiDAR Survey</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -24382,12 +24380,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Sentinels of Change</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -24410,49 +24408,55 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.6, 48.25], [-123.2, 48.37], [-123.3, 48.71], [-123.0, 48.8], [-123.3, 49.09], [-123.0, 49.1], [-122.4, 49.39], [-122.6, 49.56], [-123.6, 49.55], [-124.8, 50.1], [-125.8, 50.51], [-127.5, 51.15], [-128.6, 52.64], [-130.4, 54.77], [-133.4, 54.37], [-132.8, 52.99], [-130.8, 51.58], [-128.3, 50.21], [-126.5, 49.17], [-125.2, 48.63], [-124.3, 48.43], [-123.6, 48.25]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-141.3, 62.08], [-139.8, 61.49], [-137.7, 60.61], [-136.8, 60.1], [-136.4, 60.29], [-138.3, 61.12], [-140.1, 61.86], [-141.2, 62.19], [-141.3, 62.08]]]}</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>[{'max': '0.5', 'min': '0.5'}]</t>
+          <t>[{'max': '5000.0', 'min': '100.0'}]</t>
         </is>
       </c>
       <c r="Q209" t="inlineStr">
         <is>
-          <t>seaSurfaceTemperature</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>10.21966/4kr2-jc55</t>
+          <t>10.21966/wxph-tz51</t>
         </is>
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="T209" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="U209" t="inlineStr"/>
-      <c r="V209" t="inlineStr"/>
-      <c r="W209" t="inlineStr"/>
-      <c r="X209" t="inlineStr"/>
+      <c r="V209" t="n">
+        <v>3</v>
+      </c>
+      <c r="W209" t="n">
+        <v>3</v>
+      </c>
+      <c r="X209" t="n">
+        <v>6</v>
+      </c>
       <c r="Y209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>[{'year': '2024', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.21966/36hp-7f40', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_d4942b86-d362-40a3-9399-c124c4c263bd'}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -24462,12 +24466,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
+          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>ca-cioos_7fd3ec6c-083a-4942-84b4-215e69492072</t>
+          <t>ca-cioos_5185ac00-8148-4472-adfd-21741d8a10ce</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -24477,7 +24481,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Phytoplankton Pigment Timeseries from High-Performance Liquid Chromatography for the Northern Salish Sea and Central Coast, BC, Canada (Research)</t>
+          <t>Sentinels of Change Sea Surface Temperature Time Series Data Along the British Columbia Coast</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -24495,7 +24499,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Sentinels of Change</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -24523,27 +24527,27 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.6, 48.25], [-123.2, 48.37], [-123.3, 48.71], [-123.0, 48.8], [-123.3, 49.09], [-123.0, 49.1], [-122.4, 49.39], [-122.6, 49.56], [-123.6, 49.55], [-124.8, 50.1], [-125.8, 50.51], [-127.5, 51.15], [-128.6, 52.64], [-130.4, 54.77], [-133.4, 54.37], [-132.8, 52.99], [-130.8, 51.58], [-128.3, 50.21], [-126.5, 49.17], [-125.2, 48.63], [-124.3, 48.43], [-123.6, 48.25]]]}</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.5', 'min': '0.5'}]</t>
         </is>
       </c>
       <c r="Q210" t="inlineStr">
         <is>
-          <t>phytoplanktonBiomassAndDiversity</t>
+          <t>seaSurfaceTemperature</t>
         </is>
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>10.21966/bw2d-tg65</t>
+          <t>10.21966/4kr2-jc55</t>
         </is>
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="T210" t="inlineStr">
@@ -24556,16 +24560,16 @@
       <c r="W210" t="inlineStr"/>
       <c r="X210" t="inlineStr"/>
       <c r="Y210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2024', 'total': 1}]</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'citations', 'id': '10.21966/36hp-7f40', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_d4942b86-d362-40a3-9399-c124c4c263bd'}]</t>
         </is>
       </c>
     </row>
@@ -24575,12 +24579,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>0781c19a-7efb-4680-92fd-8cd5faf0cfe4</t>
+          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>ca-cioos_af344fb9-4901-470c-a441-41f11ee2ccd7</t>
+          <t>ca-cioos_7fd3ec6c-083a-4942-84b4-215e69492072</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -24590,7 +24594,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>iTrack Oysters February 2023 Experiment - Environmental and Oyster Health Data</t>
+          <t>Phytoplankton Pigment Timeseries from High-Performance Liquid Chromatography for the Northern Salish Sea and Central Coast, BC, Canada (Research)</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -24608,12 +24612,12 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Wet Lab</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -24628,7 +24632,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N211" t="n">
@@ -24636,44 +24640,38 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q211" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>phytoplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>10.21966/pvy6-nw38</t>
+          <t>10.21966/bw2d-tg65</t>
         </is>
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="T211" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
-        </is>
-      </c>
-      <c r="U211" t="n">
-        <v>1</v>
-      </c>
-      <c r="V211" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr"/>
+      <c r="V211" t="inlineStr"/>
       <c r="W211" t="inlineStr"/>
-      <c r="X211" t="n">
-        <v>2</v>
-      </c>
+      <c r="X211" t="inlineStr"/>
       <c r="Y211" t="n">
         <v>0</v>
       </c>
@@ -24694,12 +24692,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>0781c19a-7efb-4680-92fd-8cd5faf0cfe4</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>ca-cioos_9fafb4c8-e61f-4372-ac71-c1ddbe57d80c</t>
+          <t>ca-cioos_af344fb9-4901-470c-a441-41f11ee2ccd7</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -24709,7 +24707,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Data record does not exist anymore: Geomorphology - Calvert Island</t>
+          <t>iTrack Oysters February 2023 Experiment - Environmental and Oyster Health Data</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -24725,7 +24723,11 @@
       <c r="H212" t="b">
         <v>0</v>
       </c>
-      <c r="I212" t="inlineStr"/>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Wet Lab</t>
+        </is>
+      </c>
       <c r="J212" t="inlineStr">
         <is>
           <t>completed</t>
@@ -24743,7 +24745,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N212" t="n">
@@ -24751,28 +24753,32 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.2489013671875, 51.40605940499276], [-127.83142089843751, 51.40605940499276], [-127.83142089843751, 51.75934048406748], [-128.2489013671875, 51.75934048406748], [-128.2489013671875, 51.40605940499276]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q212" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R212" t="inlineStr"/>
+          <t>other, inorganicCarbon</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>10.21966/pvy6-nw38</t>
+        </is>
+      </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="T212" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="U212" t="n">
@@ -24781,15 +24787,23 @@
       <c r="V212" t="n">
         <v>1</v>
       </c>
-      <c r="W212" t="n">
+      <c r="W212" t="inlineStr"/>
+      <c r="X212" t="n">
         <v>2</v>
       </c>
-      <c r="X212" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y212" t="inlineStr"/>
-      <c r="Z212" t="inlineStr"/>
-      <c r="AA212" t="inlineStr"/>
+      <c r="Y212" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -24797,12 +24811,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>ca-cioos_d7ffd737-5725-4a56-9134-a9ad91c2734d</t>
+          <t>ca-cioos_9fafb4c8-e61f-4372-ac71-c1ddbe57d80c</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -24812,7 +24826,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Seton and Anderson Lake Multibeam Survey - 2024 - British Columbia</t>
+          <t>Data record does not exist anymore: Geomorphology - Calvert Island</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -24828,11 +24842,7 @@
       <c r="H213" t="b">
         <v>0</v>
       </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>Geospatial</t>
-        </is>
-      </c>
+      <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr">
         <is>
           <t>completed</t>
@@ -24858,12 +24868,12 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.4, 50.62], [-122.0, 50.62], [-122.0, 50.75], [-122.4, 50.75], [-122.4, 50.62]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.2489013671875, 51.40605940499276], [-127.83142089843751, 51.40605940499276], [-127.83142089843751, 51.75934048406748], [-128.2489013671875, 51.75934048406748], [-128.2489013671875, 51.40605940499276]]]}</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>[{'max': '254.0', 'min': '61.0'}]</t>
+          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q213" t="inlineStr">
@@ -24871,22 +24881,20 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R213" t="inlineStr">
-        <is>
-          <t>10.21966/zfxe-rd73</t>
-        </is>
-      </c>
+      <c r="R213" t="inlineStr"/>
       <c r="S213" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="T213" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="U213" t="inlineStr"/>
+          <t>2025-01-03</t>
+        </is>
+      </c>
+      <c r="U213" t="n">
+        <v>1</v>
+      </c>
       <c r="V213" t="n">
         <v>1</v>
       </c>
@@ -24894,21 +24902,11 @@
         <v>2</v>
       </c>
       <c r="X213" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y213" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z213" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AA213" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="Y213" t="inlineStr"/>
+      <c r="Z213" t="inlineStr"/>
+      <c r="AA213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -24916,12 +24914,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>4a949e26-fe94-4f63-a3c6-a62e19301102</t>
+          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>ca-cioos_35beb32e-8dc9-42ab-9630-2ae23e414026</t>
+          <t>ca-cioos_d7ffd737-5725-4a56-9134-a9ad91c2734d</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -24931,7 +24929,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Rocky Subtidal Fish and Invertebrate Community Surveys from the Central Coast of BC</t>
+          <t>Seton and Anderson Lake Multibeam Survey - 2024 - British Columbia</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -24949,12 +24947,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -24977,41 +24975,43 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.7, 51.35], [-127.3, 51.35], [-127.3, 52.27], [-128.7, 52.27], [-128.7, 51.35]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.4, 50.62], [-122.0, 50.62], [-122.0, 50.75], [-122.4, 50.75], [-122.4, 50.62]]]}</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>[{'max': '15.0', 'min': '0.0'}]</t>
+          <t>[{'max': '254.0', 'min': '61.0'}]</t>
         </is>
       </c>
       <c r="Q214" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>10.21966/jj9p-d309</t>
+          <t>10.21966/zfxe-rd73</t>
         </is>
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="T214" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="U214" t="inlineStr"/>
       <c r="V214" t="n">
         <v>1</v>
       </c>
-      <c r="W214" t="inlineStr"/>
+      <c r="W214" t="n">
+        <v>2</v>
+      </c>
       <c r="X214" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y214" t="n">
         <v>0</v>
@@ -25033,12 +25033,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>7fa8cfec-e2e3-4459-9b9d-836335b9fcfa</t>
+          <t>4a949e26-fe94-4f63-a3c6-a62e19301102</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>ca-cioos_00f42725-0a88-4d4f-87a9-4e359d2abff4</t>
+          <t>ca-cioos_35beb32e-8dc9-42ab-9630-2ae23e414026</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25048,7 +25048,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Knight Inlet Remotely Operated Vehicle Marine Habitat Survey</t>
+          <t>Rocky Subtidal Fish and Invertebrate Community Surveys from the Central Coast of BC</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -25066,12 +25066,12 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -25094,43 +25094,41 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.0, 50.65], [-125.9, 50.65], [-125.9, 50.71], [-126.0, 50.71], [-126.0, 50.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.7, 51.35], [-127.3, 51.35], [-127.3, 52.27], [-128.7, 52.27], [-128.7, 51.35]]]}</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>[{'max': '105.0', 'min': '0.0'}]</t>
+          <t>[{'max': '15.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q215" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>10.21966/529y-sh57</t>
+          <t>10.21966/jj9p-d309</t>
         </is>
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="T215" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="U215" t="inlineStr"/>
       <c r="V215" t="n">
         <v>1</v>
       </c>
-      <c r="W215" t="n">
-        <v>2</v>
-      </c>
+      <c r="W215" t="inlineStr"/>
       <c r="X215" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y215" t="n">
         <v>0</v>
@@ -25152,12 +25150,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>5576c279-6d3a-4323-8104-0e1040d9906c</t>
+          <t>7fa8cfec-e2e3-4459-9b9d-836335b9fcfa</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>ca-cioos_314a0846-0fe9-4c2e-81e2-d2b24ac98b6e</t>
+          <t>ca-cioos_00f42725-0a88-4d4f-87a9-4e359d2abff4</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -25167,7 +25165,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Understory kelp biomass data from BC Central Coast</t>
+          <t>Knight Inlet Remotely Operated Vehicle Marine Habitat Survey</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -25185,12 +25183,12 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -25213,41 +25211,43 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.7, 51.33], [-127.4, 51.33], [-127.4, 52.26], [-128.7, 52.26], [-128.7, 51.33]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.0, 50.65], [-125.9, 50.65], [-125.9, 50.71], [-126.0, 50.71], [-126.0, 50.65]]]}</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '105.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q216" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>10.21966/wmsy-5g39</t>
+          <t>10.21966/529y-sh57</t>
         </is>
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="T216" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="U216" t="inlineStr"/>
       <c r="V216" t="n">
+        <v>1</v>
+      </c>
+      <c r="W216" t="n">
         <v>2</v>
       </c>
-      <c r="W216" t="inlineStr"/>
       <c r="X216" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y216" t="n">
         <v>0</v>
@@ -25269,12 +25269,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>cc016896-78d9-46e8-887d-6c1dd106c0e8</t>
+          <t>5576c279-6d3a-4323-8104-0e1040d9906c</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>ca-cioos_52d4f546-dfdf-4bf1-b1ad-f6ec6f2663c0</t>
+          <t>ca-cioos_314a0846-0fe9-4c2e-81e2-d2b24ac98b6e</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Bute Inlet Geo-Hazards &amp; Ramsay West - 2024 - Airborne Coastal Observatory</t>
+          <t>Understory kelp biomass data from BC Central Coast</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -25302,12 +25302,12 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -25330,43 +25330,41 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.5, 50.23], [-124.1, 50.23], [-124.1, 51.73], [-125.5, 51.73], [-125.5, 50.23]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.7, 51.33], [-127.4, 51.33], [-127.4, 52.26], [-128.7, 52.26], [-128.7, 51.33]]]}</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>[{'max': '2500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q217" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>10.21966/8yp1-7m94</t>
+          <t>10.21966/wmsy-5g39</t>
         </is>
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="T217" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="U217" t="inlineStr"/>
       <c r="V217" t="n">
-        <v>1</v>
-      </c>
-      <c r="W217" t="n">
         <v>2</v>
       </c>
+      <c r="W217" t="inlineStr"/>
       <c r="X217" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y217" t="n">
         <v>0</v>
@@ -25388,12 +25386,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>046e5ef5-1480-4868-a65f-23171088bdb8</t>
+          <t>cc016896-78d9-46e8-887d-6c1dd106c0e8</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>ca-cioos_31e15496-e906-43f4-9120-2446ab6125b2</t>
+          <t>ca-cioos_52d4f546-dfdf-4bf1-b1ad-f6ec6f2663c0</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -25403,7 +25401,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Elliot Creek Aerial Photo and LiDAR Survey</t>
+          <t>Bute Inlet Geo-Hazards &amp; Ramsay West - 2024 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -25421,7 +25419,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -25449,12 +25447,12 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.8, 50.84], [-124.5, 50.84], [-124.5, 50.99], [-124.8, 50.99], [-124.8, 50.84]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.5, 50.23], [-124.1, 50.23], [-124.1, 51.73], [-125.5, 51.73], [-125.5, 50.23]]]}</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>[{'max': '2650.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q218" t="inlineStr">
@@ -25464,30 +25462,28 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>10.21966/g64t-ec45</t>
+          <t>10.21966/8yp1-7m94</t>
         </is>
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="T218" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="U218" t="n">
-        <v>1</v>
-      </c>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr"/>
       <c r="V218" t="n">
         <v>1</v>
       </c>
       <c r="W218" t="n">
+        <v>2</v>
+      </c>
+      <c r="X218" t="n">
         <v>3</v>
-      </c>
-      <c r="X218" t="n">
-        <v>5</v>
       </c>
       <c r="Y218" t="n">
         <v>0</v>
@@ -25509,12 +25505,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>8ce79018-75da-42f8-b7cd-195a412ab532</t>
+          <t>046e5ef5-1480-4868-a65f-23171088bdb8</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>ca-cioos_98807d0a-ba68-41e3-a2f5-e3248b459904</t>
+          <t>ca-cioos_31e15496-e906-43f4-9120-2446ab6125b2</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -25524,7 +25520,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Place Glacier Aerial Photo and LiDAR Survey</t>
+          <t>Elliot Creek Aerial Photo and LiDAR Survey</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -25562,7 +25558,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Tula Foundation</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N219" t="n">
@@ -25570,12 +25566,12 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.7, 50.39], [-122.6, 50.39], [-122.6, 50.48], [-122.7, 50.48], [-122.7, 50.39]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.8, 50.84], [-124.5, 50.84], [-124.5, 50.99], [-124.8, 50.99], [-124.8, 50.84]]]}</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>[{'max': '2587.0', 'min': '500.0'}]</t>
+          <t>[{'max': '2650.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q219" t="inlineStr">
@@ -25585,7 +25581,7 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>10.21966/0ydj-0t79</t>
+          <t>10.21966/g64t-ec45</t>
         </is>
       </c>
       <c r="S219" t="inlineStr">
@@ -25599,7 +25595,7 @@
         </is>
       </c>
       <c r="U219" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V219" t="n">
         <v>1</v>
@@ -25608,7 +25604,7 @@
         <v>3</v>
       </c>
       <c r="X219" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y219" t="n">
         <v>0</v>
@@ -25630,12 +25626,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>83f387d2-f77e-4921-af15-e064d87ad01a</t>
+          <t>8ce79018-75da-42f8-b7cd-195a412ab532</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>ca-cioos_53730b70-be6f-4e24-8b9d-4a5e2c491121</t>
+          <t>ca-cioos_98807d0a-ba68-41e3-a2f5-e3248b459904</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -25645,12 +25641,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Cloud-Based LiDAR Application - ELVIZ - Place Glacier, Mt. Robson, and Elliot Creek, BC</t>
+          <t>Place Glacier Aerial Photo and LiDAR Survey</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>dataset</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -25683,7 +25679,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Tula Foundation</t>
         </is>
       </c>
       <c r="N220" t="n">
@@ -25691,12 +25687,12 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.5, 50.34], [-118.7, 50.34], [-118.7, 53.28], [-124.5, 53.28], [-124.5, 50.34]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.7, 50.39], [-122.6, 50.39], [-122.6, 50.48], [-122.7, 50.48], [-122.7, 50.39]]]}</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>[{'max': '3954.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2587.0', 'min': '500.0'}]</t>
         </is>
       </c>
       <c r="Q220" t="inlineStr">
@@ -25706,25 +25702,27 @@
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>10.21966/6x1v-1v62</t>
+          <t>10.21966/0ydj-0t79</t>
         </is>
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="T220" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="U220" t="inlineStr"/>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="U220" t="n">
+        <v>2</v>
+      </c>
       <c r="V220" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W220" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X220" t="n">
         <v>6</v>
@@ -25749,12 +25747,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
+          <t>83f387d2-f77e-4921-af15-e064d87ad01a</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>ca-cioos_78818ed7-ec26-4004-afa1-137741ddda1e</t>
+          <t>ca-cioos_53730b70-be6f-4e24-8b9d-4a5e2c491121</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -25764,12 +25762,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Calliarthron 2023 Experiment - Environmental Data</t>
+          <t>Cloud-Based LiDAR Application - ELVIZ - Place Glacier, Mt. Robson, and Elliot Creek, BC</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>service</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -25782,7 +25780,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Wet Lab</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -25802,7 +25800,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>University of British Columbia</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N221" t="n">
@@ -25810,43 +25808,43 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.5, 50.34], [-118.7, 50.34], [-118.7, 53.28], [-124.5, 53.28], [-124.5, 50.34]]]}</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '3954.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q221" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>10.21966/7nwn-bj60</t>
+          <t>10.21966/6x1v-1v62</t>
         </is>
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="T221" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="U221" t="n">
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr"/>
+      <c r="V221" t="n">
         <v>2</v>
       </c>
-      <c r="V221" t="n">
-        <v>1</v>
-      </c>
-      <c r="W221" t="inlineStr"/>
+      <c r="W221" t="n">
+        <v>4</v>
+      </c>
       <c r="X221" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y221" t="n">
         <v>0</v>
@@ -25868,12 +25866,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
+          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>ca-cioos_87341cb3-f906-4fa5-973c-b6742aa0fbb5</t>
+          <t>ca-cioos_78818ed7-ec26-4004-afa1-137741ddda1e</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -25883,7 +25881,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Glacier and Ice Aerial Surveys in British Columbia - 2023-2024 - Hakai Airborne Coastal Observatory</t>
+          <t>Calliarthron 2023 Experiment - Environmental Data</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -25901,7 +25899,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Wet Lab</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -25921,7 +25919,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="N222" t="n">
@@ -25929,22 +25927,22 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.9, 48.81], [-115.2, 48.81], [-115.2, 54.38], [-128.9, 54.38], [-128.9, 48.81]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
         </is>
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>[{'max': '3954.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q222" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>10.21966/ks82-th39</t>
+          <t>10.21966/7nwn-bj60</t>
         </is>
       </c>
       <c r="S222" t="inlineStr">
@@ -25954,16 +25952,16 @@
       </c>
       <c r="T222" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="U222" t="inlineStr"/>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="U222" t="n">
+        <v>2</v>
+      </c>
       <c r="V222" t="n">
         <v>1</v>
       </c>
-      <c r="W222" t="n">
-        <v>2</v>
-      </c>
+      <c r="W222" t="inlineStr"/>
       <c r="X222" t="n">
         <v>3</v>
       </c>
@@ -25987,12 +25985,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>6c99bd67-3be1-4818-bf01-dfa56e910db3</t>
+          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>ca-cioos_96e3dd9c-7863-44d5-95cd-a3d0a8653d83</t>
+          <t>ca-cioos_87341cb3-f906-4fa5-973c-b6742aa0fbb5</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26002,7 +26000,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Glacier and Ice Aerial Surveys in British Columbia - 2022 - Hakai Airborne Coastal Observatory</t>
+          <t>Glacier and Ice Aerial Surveys in British Columbia - 2023-2024 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -26020,7 +26018,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -26048,12 +26046,12 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.8, 48.1], [-113.1, 48.1], [-113.1, 56.61], [-127.8, 56.61], [-127.8, 48.1]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.9, 48.81], [-115.2, 48.81], [-115.2, 54.38], [-128.9, 54.38], [-128.9, 48.81]]]}</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>[{'max': '4000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '3954.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q223" t="inlineStr">
@@ -26063,7 +26061,7 @@
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>10.21966/n3b4-d226</t>
+          <t>10.21966/ks82-th39</t>
         </is>
       </c>
       <c r="S223" t="inlineStr">
@@ -26073,7 +26071,7 @@
       </c>
       <c r="T223" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="U223" t="inlineStr"/>
@@ -26091,7 +26089,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -26106,12 +26104,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
+          <t>6c99bd67-3be1-4818-bf01-dfa56e910db3</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>ca-cioos_47d8bdd4-c815-4e8d-8d75-53a9db4ae46a</t>
+          <t>ca-cioos_96e3dd9c-7863-44d5-95cd-a3d0a8653d83</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -26121,7 +26119,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Glaciers in Western North America Mass Loss Geospatial Data (2021-2024)</t>
+          <t>Glacier and Ice Aerial Surveys in British Columbia - 2022 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -26167,12 +26165,12 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.3, 54.17], [-119.5, 55.38], [-112.5, 52.06], [-115.3, 47.05], [-125.9, 48.0], [-128.3, 51.41], [-127.3, 54.17]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.8, 48.1], [-113.1, 48.1], [-113.1, 56.61], [-127.8, 56.61], [-127.8, 48.1]]]}</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>[{'max': '2822.0', 'min': '0.0'}]</t>
+          <t>[{'max': '4000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q224" t="inlineStr">
@@ -26182,25 +26180,25 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>10.21966/p6jv-pe95</t>
+          <t>10.21966/n3b4-d226</t>
         </is>
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="T224" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="U224" t="inlineStr"/>
       <c r="V224" t="n">
+        <v>1</v>
+      </c>
+      <c r="W224" t="n">
         <v>2</v>
-      </c>
-      <c r="W224" t="n">
-        <v>1</v>
       </c>
       <c r="X224" t="n">
         <v>3</v>
@@ -26210,7 +26208,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2025', 'total': 1}]</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -26225,12 +26223,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
+          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>ca-cioos_1d142201-cbbe-4c58-b2c2-1feeac112c51</t>
+          <t>ca-cioos_47d8bdd4-c815-4e8d-8d75-53a9db4ae46a</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -26240,7 +26238,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>iTrack Oysters September 2023 Experiment - Environmental and Oyster Health Data</t>
+          <t>Glaciers in Western North America Mass Loss Geospatial Data (2021-2024)</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -26258,7 +26256,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Wet Lab</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -26278,7 +26276,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N225" t="n">
@@ -26286,41 +26284,41 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.3, 54.17], [-119.5, 55.38], [-112.5, 52.06], [-115.3, 47.05], [-125.9, 48.0], [-128.3, 51.41], [-127.3, 54.17]]]}</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '2822.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q225" t="inlineStr">
         <is>
-          <t>inorganicCarbon, other</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>10.21966/q1m4-pz94</t>
+          <t>10.21966/p6jv-pe95</t>
         </is>
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="T225" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="U225" t="n">
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr"/>
+      <c r="V225" t="n">
         <v>2</v>
       </c>
-      <c r="V225" t="n">
-        <v>1</v>
-      </c>
-      <c r="W225" t="inlineStr"/>
+      <c r="W225" t="n">
+        <v>1</v>
+      </c>
       <c r="X225" t="n">
         <v>3</v>
       </c>
@@ -26344,12 +26342,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>da040f55-984d-490d-b917-a67856de4bac</t>
+          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>ca-cioos_31ac855d-bf15-42d8-b20d-754638202c66</t>
+          <t>ca-cioos_1d142201-cbbe-4c58-b2c2-1feeac112c51</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -26359,7 +26357,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Sea Stars 2024 Experiment - Environmental Data</t>
+          <t>iTrack Oysters September 2023 Experiment - Environmental and Oyster Health Data</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -26397,7 +26395,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N226" t="n">
@@ -26420,7 +26418,7 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>10.21966/jkf5-ss08</t>
+          <t>10.21966/q1m4-pz94</t>
         </is>
       </c>
       <c r="S226" t="inlineStr">
@@ -26434,14 +26432,14 @@
         </is>
       </c>
       <c r="U226" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V226" t="n">
         <v>1</v>
       </c>
       <c r="W226" t="inlineStr"/>
       <c r="X226" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y226" t="n">
         <v>0</v>
@@ -26463,12 +26461,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
+          <t>da040f55-984d-490d-b917-a67856de4bac</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>ca-cioos_d959f8f3-6d20-42fe-94da-be49bcd3aeca</t>
+          <t>ca-cioos_31ac855d-bf15-42d8-b20d-754638202c66</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -26478,7 +26476,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Eelgrass (Z. marina) extent at Gulf Islands National Park Reserve eelgrass monitoring sites (2024)</t>
+          <t>Sea Stars 2024 Experiment - Environmental Data</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -26496,7 +26494,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Wet Lab</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -26516,15 +26514,15 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Gulf Islands National Park Reserve</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N227" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.4, 48.61], [-123.0, 48.61], [-123.0, 48.87], [-123.4, 48.87], [-123.4, 48.61]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -26534,33 +26532,33 @@
       </c>
       <c r="Q227" t="inlineStr">
         <is>
-          <t>other, seagrassCoverAndComposition</t>
+          <t>inorganicCarbon, other</t>
         </is>
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>10.21966/x3jm-p494</t>
+          <t>10.21966/jkf5-ss08</t>
         </is>
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="T227" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="U227" t="n">
         <v>1</v>
       </c>
       <c r="V227" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W227" t="inlineStr"/>
       <c r="X227" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y227" t="n">
         <v>0</v>
@@ -26582,12 +26580,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>ca-cioos_39a83551-ab8e-45be-a564-cece4b229371</t>
+          <t>ca-cioos_d959f8f3-6d20-42fe-94da-be49bcd3aeca</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -26597,7 +26595,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Zooplankton taxonomic abundance and biomass along the BC Coast</t>
+          <t>Eelgrass (Z. marina) extent at Gulf Islands National Park Reserve eelgrass monitoring sites (2024)</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -26615,12 +26613,12 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -26635,7 +26633,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Gulf Islands National Park Reserve</t>
         </is>
       </c>
       <c r="N228" t="n">
@@ -26643,55 +26641,55 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.4, 48.61], [-123.0, 48.61], [-123.0, 48.87], [-123.4, 48.87], [-123.4, 48.61]]]}</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>[{'max': '350.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q228" t="inlineStr">
         <is>
-          <t>zooplanktonBiomassAndDiversity</t>
+          <t>other, seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>10.21966/g7zf-1v08</t>
+          <t>10.21966/x3jm-p494</t>
         </is>
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="T228" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="U228" t="n">
         <v>1</v>
       </c>
       <c r="V228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W228" t="inlineStr"/>
       <c r="X228" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y228" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 2}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>[{'relationship': 'references', 'id': '10.21966/g7zf-1v08', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_39a83551-ab8e-45be-a564-cece4b229371'}, {'relationship': 'references', 'id': '10.21966/tcp2-mm86', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_dbb33efe-c207-4d9c-abef-2350595bf47a'}, {'relationship': 'citations', 'id': '10.21966/g7zf-1v08', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_39a83551-ab8e-45be-a564-cece4b229371'}, {'relationship': 'citations', 'id': '10.21966/kace-2d24', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_ba41d935-f293-447f-be3d-7098e569b431'}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -26701,12 +26699,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>ca-cioos_dbb33efe-c207-4d9c-abef-2350595bf47a</t>
+          <t>ca-cioos_39a83551-ab8e-45be-a564-cece4b229371</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -26716,7 +26714,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Size-fractionated zooplankton biomass and isotopes along the BC coast</t>
+          <t>Zooplankton taxonomic abundance and biomass along the BC Coast</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -26758,7 +26756,7 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O229" t="inlineStr">
         <is>
@@ -26777,7 +26775,7 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>10.21966/tcp2-mm86</t>
+          <t>10.21966/g7zf-1v08</t>
         </is>
       </c>
       <c r="S229" t="inlineStr">
@@ -26790,13 +26788,15 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="U229" t="inlineStr"/>
+      <c r="U229" t="n">
+        <v>1</v>
+      </c>
       <c r="V229" t="n">
         <v>1</v>
       </c>
       <c r="W229" t="inlineStr"/>
       <c r="X229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y229" t="n">
         <v>2</v>
@@ -26808,7 +26808,7 @@
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.21966/kace-2d24', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_ba41d935-f293-447f-be3d-7098e569b431'}, {'relationship': 'citations', 'id': '10.21966/g7zf-1v08', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_39a83551-ab8e-45be-a564-cece4b229371'}]</t>
+          <t>[{'relationship': 'references', 'id': '10.21966/g7zf-1v08', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_39a83551-ab8e-45be-a564-cece4b229371'}, {'relationship': 'references', 'id': '10.21966/tcp2-mm86', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_dbb33efe-c207-4d9c-abef-2350595bf47a'}, {'relationship': 'citations', 'id': '10.21966/g7zf-1v08', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_39a83551-ab8e-45be-a564-cece4b229371'}, {'relationship': 'citations', 'id': '10.21966/kace-2d24', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_ba41d935-f293-447f-be3d-7098e569b431'}]</t>
         </is>
       </c>
     </row>
@@ -26818,12 +26818,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>328b062b-3af6-4149-b90f-a85b99dc40eb</t>
+          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>ca-cioos_34a20547-cb60-4ecf-901b-f4ca52eae451</t>
+          <t>ca-cioos_dbb33efe-c207-4d9c-abef-2350595bf47a</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -26833,7 +26833,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), Central Coast, British Columbia, Canada</t>
+          <t>Size-fractionated zooplankton biomass and isotopes along the BC coast</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -26851,12 +26851,12 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
@@ -26879,32 +26879,32 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.4], [-127.9, 51.4], [-127.9, 52.09], [-128.5, 52.09], [-128.5, 51.4]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '350.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q230" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>zooplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>10.21966/w08z-zk15</t>
+          <t>10.21966/tcp2-mm86</t>
         </is>
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="T230" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="U230" t="inlineStr"/>
@@ -26916,16 +26916,16 @@
         <v>1</v>
       </c>
       <c r="Y230" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2025', 'total': 2}]</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'citations', 'id': '10.21966/kace-2d24', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_ba41d935-f293-447f-be3d-7098e569b431'}, {'relationship': 'citations', 'id': '10.21966/g7zf-1v08', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_39a83551-ab8e-45be-a564-cece4b229371'}]</t>
         </is>
       </c>
     </row>
@@ -26935,12 +26935,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>439d703a-2132-4dbd-8d39-a4cacdb8f81d</t>
+          <t>328b062b-3af6-4149-b90f-a85b99dc40eb</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>ca-cioos_e8343aa0-dbea-4267-9f78-662bec08d4bc</t>
+          <t>ca-cioos_34a20547-cb60-4ecf-901b-f4ca52eae451</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -26950,7 +26950,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020-2022), Central Coast, British Columbia, Canada</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -26968,7 +26968,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -26996,7 +26996,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 52.15], [-128.5, 52.23], [-128.2, 52.05], [-128.0, 51.71], [-128.0, 51.63], [-128.2, 51.62], [-128.4, 51.8], [-128.6, 51.89], [-128.6, 51.89], [-128.6, 52.15]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.4], [-127.9, 51.4], [-127.9, 52.09], [-128.5, 52.09], [-128.5, 51.4]]]}</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
@@ -27011,7 +27011,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>10.21966/kqzp-f639</t>
+          <t>10.21966/w08z-zk15</t>
         </is>
       </c>
       <c r="S231" t="inlineStr">
@@ -27021,7 +27021,7 @@
       </c>
       <c r="T231" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="U231" t="inlineStr"/>
@@ -27052,12 +27052,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
+          <t>439d703a-2132-4dbd-8d39-a4cacdb8f81d</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>ca-cioos_f7a867ce-0f18-43f6-8148-775235d800b6</t>
+          <t>ca-cioos_e8343aa0-dbea-4267-9f78-662bec08d4bc</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -27067,7 +27067,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2023), Central Coast, British Columbia, Canada</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020-2022), Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -27085,7 +27085,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
+          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -27113,7 +27113,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.64], [-128.1, 51.64], [-128.1, 52.19], [-128.6, 52.19], [-128.6, 51.64]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 52.15], [-128.5, 52.23], [-128.2, 52.05], [-128.0, 51.71], [-128.0, 51.63], [-128.2, 51.62], [-128.4, 51.8], [-128.6, 51.89], [-128.6, 51.89], [-128.6, 52.15]]]}</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
@@ -27128,7 +27128,7 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>10.21966/qs1b-g693</t>
+          <t>10.21966/kqzp-f639</t>
         </is>
       </c>
       <c r="S232" t="inlineStr">
@@ -27138,7 +27138,7 @@
       </c>
       <c r="T232" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="U232" t="inlineStr"/>
@@ -27169,12 +27169,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
+          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>ca-cioos_291b98a4-d868-462c-852a-d6cf79ecf6ce</t>
+          <t>ca-cioos_f7a867ce-0f18-43f6-8148-775235d800b6</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -27184,7 +27184,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Time series of surface kelp canopy area derived from remotely piloted aerial systems (RPAS, or drone) surveys, Central Coast, British Columbia</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2023), Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -27202,12 +27202,12 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Nearshore, Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -27222,7 +27222,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Tula Foundation</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N233" t="n">
@@ -27230,7 +27230,7 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.65], [-128.1, 51.65], [-128.1, 52.09], [-128.4, 52.09], [-128.4, 51.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.64], [-128.1, 51.64], [-128.1, 52.19], [-128.6, 52.19], [-128.6, 51.64]]]}</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
@@ -27245,30 +27245,26 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>10.21966/9cbv-ra30</t>
+          <t>10.21966/qs1b-g693</t>
         </is>
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="T233" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="U233" t="n">
-        <v>1</v>
-      </c>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr"/>
       <c r="V233" t="n">
         <v>1</v>
       </c>
-      <c r="W233" t="n">
-        <v>1</v>
-      </c>
+      <c r="W233" t="inlineStr"/>
       <c r="X233" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y233" t="n">
         <v>0</v>
@@ -27290,12 +27286,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>44bdc298-1329-400a-bc02-4d35d251865d</t>
+          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>ca-cioos_012164c6-28dd-4078-b702-f0c2ce63d548</t>
+          <t>ca-cioos_291b98a4-d868-462c-852a-d6cf79ecf6ce</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -27305,7 +27301,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Biodiversity and Oceanographic data from the False Creek Bioblitz, 2022</t>
+          <t>Time series of surface kelp canopy area derived from remotely piloted aerial systems (RPAS, or drone) surveys, Central Coast, British Columbia</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -27323,12 +27319,12 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>Genomics, Nearshore, Oceanography</t>
+          <t>Nearshore, Geospatial</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -27343,47 +27339,51 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Tula Foundation</t>
         </is>
       </c>
       <c r="N234" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.2, 49.27], [-123.1, 49.27], [-123.1, 49.28], [-123.2, 49.28], [-123.2, 49.27]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.65], [-128.1, 51.65], [-128.1, 52.09], [-128.4, 52.09], [-128.4, 51.65]]]}</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q234" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution, marineTurtlesBirdsMammalsAbundanceAndDistribution, fishAbundanceAndDistribution, seaSurfaceTemperature, subSurfaceTemperature, other, microbeBiomassAndDiversity</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>10.21966/8sgn-jg38</t>
+          <t>10.21966/9cbv-ra30</t>
         </is>
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="T234" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="U234" t="inlineStr"/>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="U234" t="n">
+        <v>1</v>
+      </c>
       <c r="V234" t="n">
-        <v>3</v>
-      </c>
-      <c r="W234" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W234" t="n">
+        <v>1</v>
+      </c>
       <c r="X234" t="n">
         <v>3</v>
       </c>
@@ -27407,12 +27407,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
+          <t>44bdc298-1329-400a-bc02-4d35d251865d</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>ca-cioos_7e9c97a3-4bf1-4852-81b6-d74cedf2c94c</t>
+          <t>ca-cioos_012164c6-28dd-4078-b702-f0c2ce63d548</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -27422,7 +27422,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Environmental DNA survey of Calvert Island, British Columbia, 2021</t>
+          <t>Biodiversity and Oceanographic data from the False Creek Bioblitz, 2022</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -27440,7 +27440,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Genomics</t>
+          <t>Genomics, Nearshore, Oceanography</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -27464,47 +27464,45 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.31], [-127.3, 51.31], [-127.3, 52.05], [-128.6, 52.05], [-128.6, 51.31]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.2, 49.27], [-123.1, 49.27], [-123.1, 49.28], [-123.2, 49.28], [-123.2, 49.27]]]}</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>[{'max': '60.0', 'min': '0.0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q235" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
+          <t>invertebrateAbundanceAndDistribution, marineTurtlesBirdsMammalsAbundanceAndDistribution, fishAbundanceAndDistribution, seaSurfaceTemperature, subSurfaceTemperature, other, microbeBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>10.21966/vdyq-r660</t>
+          <t>10.21966/8sgn-jg38</t>
         </is>
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="T235" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="U235" t="inlineStr"/>
       <c r="V235" t="n">
-        <v>4</v>
-      </c>
-      <c r="W235" t="n">
         <v>3</v>
       </c>
+      <c r="W235" t="inlineStr"/>
       <c r="X235" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y235" t="n">
         <v>0</v>
@@ -27526,12 +27524,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
+          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>ca-cioos_9a018fe0-8bd1-41d1-af8d-079960b71473</t>
+          <t>ca-cioos_7e9c97a3-4bf1-4852-81b6-d74cedf2c94c</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -27541,7 +27539,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Data from: Prentice et al. 2025. Vibrio pectenicida strain FHCF-3 is a causative agent of sea star wasting disease</t>
+          <t>Environmental DNA survey of Calvert Island, British Columbia, 2021</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -27559,7 +27557,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Genomics, Nearshore</t>
+          <t>Genomics</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -27583,47 +27581,47 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 47.91], [-122.3, 47.91], [-122.3, 51.82], [-128.5, 51.82], [-128.5, 47.91]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.31], [-127.3, 51.31], [-127.3, 52.05], [-128.6, 52.05], [-128.6, 51.31]]]}</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '60.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q236" t="inlineStr">
         <is>
-          <t>microbeBiomassAndDiversity</t>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>10.21966/4dvn-5y90</t>
+          <t>10.21966/vdyq-r660</t>
         </is>
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="T236" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="U236" t="inlineStr"/>
       <c r="V236" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W236" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X236" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Y236" t="n">
         <v>0</v>
@@ -27645,12 +27643,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>0272fd06-6ac8-48cd-80c9-b6e05f15be0f</t>
+          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>ca-cioos_132cecdf-de8a-4b17-b610-0e2b3a343812</t>
+          <t>ca-cioos_9a018fe0-8bd1-41d1-af8d-079960b71473</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -27660,7 +27658,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), North Coast, British Columbia, Canada</t>
+          <t>Data from: Prentice et al. 2025. Vibrio pectenicida strain FHCF-3 is a causative agent of sea star wasting disease</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -27678,7 +27676,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
+          <t>Genomics, Nearshore</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -27702,11 +27700,11 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-131.0, 53.74], [-130.4, 53.74], [-130.4, 54.46], [-131.0, 54.46], [-131.0, 53.74]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 47.91], [-122.3, 47.91], [-122.3, 51.82], [-128.5, 51.82], [-128.5, 47.91]]]}</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
@@ -27716,31 +27714,33 @@
       </c>
       <c r="Q237" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>microbeBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>10.21966/m93t-4181</t>
+          <t>10.21966/4dvn-5y90</t>
         </is>
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="T237" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="U237" t="inlineStr"/>
       <c r="V237" t="n">
-        <v>1</v>
-      </c>
-      <c r="W237" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="W237" t="n">
+        <v>1</v>
+      </c>
       <c r="X237" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y237" t="n">
         <v>0</v>
@@ -27762,12 +27762,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>b01f58f7-1518-4829-aff6-ac4a8f2c0616</t>
+          <t>0272fd06-6ac8-48cd-80c9-b6e05f15be0f</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>ca-cioos_f815a700-c943-4d6f-afeb-a4854ad10cfc</t>
+          <t>ca-cioos_132cecdf-de8a-4b17-b610-0e2b3a343812</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -27777,7 +27777,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), North Vancouver Island, British Columbia, Canada</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), North Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -27823,7 +27823,7 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.6, 50.35], [-124.8, 50.35], [-124.8, 50.7], [-126.6, 50.7], [-126.6, 50.35]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-131.0, 53.74], [-130.4, 53.74], [-130.4, 54.46], [-131.0, 54.46], [-131.0, 53.74]]]}</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
@@ -27838,7 +27838,7 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>10.21966/ntdg-e790</t>
+          <t>10.21966/m93t-4181</t>
         </is>
       </c>
       <c r="S238" t="inlineStr">
@@ -27879,12 +27879,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>b01f58f7-1518-4829-aff6-ac4a8f2c0616</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>ca-cioos_5b4cbe9f-8f2e-414c-80ff-741372891fe9</t>
+          <t>ca-cioos_f815a700-c943-4d6f-afeb-a4854ad10cfc</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -27894,7 +27894,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Gitga'at Territory Coastal Monitoring and Mapping - Airborne Coastal Observatory</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), North Vancouver Island, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -27904,7 +27904,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="H239" t="b">
@@ -27912,7 +27912,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -27940,57 +27940,53 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.8, 52.92], [-129.1, 52.92], [-129.1, 53.67], [-129.8, 53.67], [-129.8, 52.92]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.6, 50.35], [-124.8, 50.35], [-124.8, 50.7], [-126.6, 50.7], [-126.6, 50.35]]]}</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>[{'max': '475.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q239" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>10.21966/0xex-r023</t>
+          <t>10.21966/ntdg-e790</t>
         </is>
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="T239" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="U239" t="n">
-        <v>1</v>
-      </c>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr"/>
       <c r="V239" t="n">
         <v>1</v>
       </c>
-      <c r="W239" t="n">
-        <v>2</v>
-      </c>
+      <c r="W239" t="inlineStr"/>
       <c r="X239" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>[{'relationship': 'references', 'id': '10.21966/2aap-hn61', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_b5f0f854-efe1-4132-808d-074244d813e1'}, {'relationship': 'citations', 'id': '10.21966/2aap-hn61', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_b5f0f854-efe1-4132-808d-074244d813e1'}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -28000,12 +27996,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>0074861a-39f2-42c1-ae71-abef4f78fd78</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>ca-cioos_b5f0f854-efe1-4132-808d-074244d813e1</t>
+          <t>ca-cioos_5b4cbe9f-8f2e-414c-80ff-741372891fe9</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -28015,7 +28011,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Gitga'at Territory Coastal Mapping Project</t>
+          <t>Gitga'at Territory Coastal Monitoring and Mapping - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -28033,12 +28029,12 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -28061,12 +28057,12 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.6, 53.18], [-129.0, 53.18], [-129.0, 53.68], [-129.6, 53.68], [-129.6, 53.18]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.8, 52.92], [-129.1, 52.92], [-129.1, 53.67], [-129.8, 53.67], [-129.8, 52.92]]]}</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>[{'max': '150.0', 'min': '0.0'}]</t>
+          <t>[{'max': '475.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q240" t="inlineStr">
@@ -28076,7 +28072,7 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>10.21966/2aap-hn61</t>
+          <t>10.21966/0xex-r023</t>
         </is>
       </c>
       <c r="S240" t="inlineStr">
@@ -28086,7 +28082,7 @@
       </c>
       <c r="T240" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="U240" t="n">
@@ -28096,22 +28092,22 @@
         <v>1</v>
       </c>
       <c r="W240" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X240" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y240" t="n">
         <v>1</v>
       </c>
       <c r="Z240" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
+          <t>[{'year': '2025', 'total': 1}]</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>[{'relationship': 'references', 'id': '10.21966/0xex-r023', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_5b4cbe9f-8f2e-414c-80ff-741372891fe9'}, {'relationship': 'citations', 'id': '10.21966/0xex-r023', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_5b4cbe9f-8f2e-414c-80ff-741372891fe9'}]</t>
+          <t>[{'relationship': 'references', 'id': '10.21966/2aap-hn61', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_b5f0f854-efe1-4132-808d-074244d813e1'}, {'relationship': 'citations', 'id': '10.21966/2aap-hn61', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_b5f0f854-efe1-4132-808d-074244d813e1'}]</t>
         </is>
       </c>
     </row>
@@ -28121,12 +28117,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>5fc21b4d-2dfa-4908-8aaf-90a82509324a</t>
+          <t>0074861a-39f2-42c1-ae71-abef4f78fd78</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>ca-cioos_35900174-c64a-493e-9a7e-390ac7e997e4</t>
+          <t>ca-cioos_b5f0f854-efe1-4132-808d-074244d813e1</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -28136,7 +28132,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Bowhead Whale Drone Data Collection - Cumberland Sound - Nunavut</t>
+          <t>Gitga'at Territory Coastal Mapping Project</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -28146,7 +28142,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>CC-BY-4.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H241" t="b">
@@ -28159,7 +28155,7 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -28182,12 +28178,12 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-68.21, 64.72], [-64.14, 64.72], [-64.14, 66.48], [-68.21, 66.48], [-68.21, 64.72]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.6, 53.18], [-129.0, 53.18], [-129.0, 53.68], [-129.6, 53.68], [-129.6, 53.18]]]}</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '150.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q241" t="inlineStr">
@@ -28197,22 +28193,24 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>10.21966/fv0q-q364</t>
+          <t>10.21966/2aap-hn61</t>
         </is>
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="T241" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="U241" t="inlineStr"/>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="U241" t="n">
+        <v>1</v>
+      </c>
       <c r="V241" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W241" t="n">
         <v>1</v>
@@ -28230,7 +28228,7 @@
       </c>
       <c r="AA241" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.48321/d16d6f987c', 'type': 'dois', 'status_code': 200, 'url': 'https://dmphub.uc3prd.cdlib.net/dmps/10.48321/D16D6F987C'}]</t>
+          <t>[{'relationship': 'references', 'id': '10.21966/0xex-r023', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_5b4cbe9f-8f2e-414c-80ff-741372891fe9'}, {'relationship': 'citations', 'id': '10.21966/0xex-r023', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_5b4cbe9f-8f2e-414c-80ff-741372891fe9'}]</t>
         </is>
       </c>
     </row>
@@ -28240,12 +28238,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>dbfc5189-f657-4034-af7f-cc358042047d</t>
+          <t>5fc21b4d-2dfa-4908-8aaf-90a82509324a</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>ca-cioos_78686602-1aa9-4246-8a24-915471fe4255</t>
+          <t>ca-cioos_35900174-c64a-493e-9a7e-390ac7e997e4</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -28255,7 +28253,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2025), North Coast, British Columbia, Canada</t>
+          <t>Bowhead Whale Drone Data Collection - Cumberland Sound - Nunavut</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -28273,7 +28271,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -28301,7 +28299,7 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.8, 52.69], [-129.0, 52.69], [-129.0, 53.14], [-129.8, 53.14], [-129.8, 52.69]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-68.21, 64.72], [-64.14, 64.72], [-64.14, 66.48], [-68.21, 66.48], [-68.21, 64.72]]]}</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
@@ -28311,12 +28309,12 @@
       </c>
       <c r="Q242" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>10.21966/nwg7-fe05</t>
+          <t>10.21966/fv0q-q364</t>
         </is>
       </c>
       <c r="S242" t="inlineStr">
@@ -28326,28 +28324,30 @@
       </c>
       <c r="T242" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="U242" t="inlineStr"/>
       <c r="V242" t="n">
-        <v>1</v>
-      </c>
-      <c r="W242" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="W242" t="n">
+        <v>1</v>
+      </c>
       <c r="X242" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'citations', 'id': '10.48321/d16d6f987c', 'type': 'dois', 'status_code': 200, 'url': 'https://dmphub.uc3prd.cdlib.net/dmps/10.48321/D16D6F987C'}]</t>
         </is>
       </c>
     </row>
@@ -28357,12 +28357,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>9eda1bfc-0d13-4e1d-9542-b9a7cce16991</t>
+          <t>dbfc5189-f657-4034-af7f-cc358042047d</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>ca-cioos_c544ef5b-967d-46b2-bbcf-395116b50e7d</t>
+          <t>ca-cioos_78686602-1aa9-4246-8a24-915471fe4255</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -28372,7 +28372,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Mystery Creek Aerial Photo and LiDAR Survey - 2025 - Airborne Coastal Observatory</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2025), North Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -28390,7 +28390,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -28418,27 +28418,27 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.9, 50.21], [-122.8, 50.21], [-122.8, 50.25], [-122.9, 50.25], [-122.9, 50.21]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.8, 52.69], [-129.0, 52.69], [-129.0, 53.14], [-129.8, 53.14], [-129.8, 52.69]]]}</t>
         </is>
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>[{'max': '1690.0', 'min': '378.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q243" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>10.21966/02qp-4945</t>
+          <t>10.21966/nwg7-fe05</t>
         </is>
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="T243" t="inlineStr">
@@ -28450,11 +28450,9 @@
       <c r="V243" t="n">
         <v>1</v>
       </c>
-      <c r="W243" t="n">
-        <v>3</v>
-      </c>
+      <c r="W243" t="inlineStr"/>
       <c r="X243" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y243" t="n">
         <v>0</v>
@@ -28476,12 +28474,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>37440dfd-53f8-462b-a544-b6c8d39c44cd</t>
+          <t>9eda1bfc-0d13-4e1d-9542-b9a7cce16991</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>ca-cioos_43bad5e5-0484-4c11-80a5-c844245f940e</t>
+          <t>ca-cioos_c544ef5b-967d-46b2-bbcf-395116b50e7d</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -28491,7 +28489,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Farwell Canyon Airborne Surveys - 2024 - Airborne Coastal Observatory</t>
+          <t>Mystery Creek Aerial Photo and LiDAR Survey - 2025 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -28537,12 +28535,12 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.6, 51.86], [-122.5, 51.81], [-122.4, 51.74], [-122.4, 51.73], [-122.5, 51.8], [-122.7, 51.83], [-122.6, 51.86]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.9, 50.21], [-122.8, 50.21], [-122.8, 50.25], [-122.9, 50.25], [-122.9, 50.21]]]}</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>[{'max': '1347.62', 'min': '345.9'}]</t>
+          <t>[{'max': '1690.0', 'min': '378.0'}]</t>
         </is>
       </c>
       <c r="Q244" t="inlineStr">
@@ -28552,17 +28550,17 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>10.21966/dtt0-s264</t>
+          <t>10.21966/02qp-4945</t>
         </is>
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="T244" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="U244" t="inlineStr"/>
@@ -28570,10 +28568,10 @@
         <v>1</v>
       </c>
       <c r="W244" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X244" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y244" t="n">
         <v>0</v>
@@ -28595,12 +28593,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
+          <t>37440dfd-53f8-462b-a544-b6c8d39c44cd</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>ca-cioos_7cafde4f-bdd5-4b95-a41d-7939ddcf08c6</t>
+          <t>ca-cioos_43bad5e5-0484-4c11-80a5-c844245f940e</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -28610,7 +28608,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Time series of quarterly kelp canopy extent from Landsat 5, 7, 8, and 9 since 1985</t>
+          <t>Farwell Canyon Airborne Surveys - 2024 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -28628,12 +28626,12 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -28656,41 +28654,43 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-130.5, 54.75], [-133.5, 54.36], [-133.0, 53.09], [-126.0, 48.92], [-123.6, 48.28], [-123.2, 48.8], [-123.8, 49.61], [-127.6, 51.04], [-128.4, 52.4], [-130.4, 54.24], [-130.5, 54.75]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.6, 51.86], [-122.5, 51.81], [-122.4, 51.74], [-122.4, 51.73], [-122.5, 51.8], [-122.7, 51.83], [-122.6, 51.86]]]}</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '1347.62', 'min': '345.9'}]</t>
         </is>
       </c>
       <c r="Q245" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>10.21966/xc7x-9207</t>
+          <t>10.21966/dtt0-s264</t>
         </is>
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="T245" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="U245" t="inlineStr"/>
       <c r="V245" t="n">
+        <v>1</v>
+      </c>
+      <c r="W245" t="n">
         <v>2</v>
       </c>
-      <c r="W245" t="inlineStr"/>
       <c r="X245" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y245" t="n">
         <v>0</v>
@@ -28712,12 +28712,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>3d082072-1ee8-4005-8bba-f9ec795ad5ab</t>
+          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>ca-cioos_cfa4ad65-ee12-47c0-9527-206a0f8d92ae</t>
+          <t>ca-cioos_7cafde4f-bdd5-4b95-a41d-7939ddcf08c6</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Hakai Institute Drone Data Index</t>
+          <t>Time series of quarterly kelp canopy extent from Landsat 5, 7, 8, and 9 since 1985</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -28745,7 +28745,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -28773,43 +28773,41 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-134.1, 42.65], [-59.42, 42.65], [-59.42, 67.53], [-134.1, 67.53], [-134.1, 42.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-130.5, 54.75], [-133.5, 54.36], [-133.0, 53.09], [-126.0, 48.92], [-123.6, 48.28], [-123.2, 48.8], [-123.8, 49.61], [-127.6, 51.04], [-128.4, 52.4], [-130.4, 54.24], [-130.5, 54.75]]]}</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q246" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>10.21966/0r8b-t282</t>
+          <t>10.21966/xc7x-9207</t>
         </is>
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="T246" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="U246" t="inlineStr"/>
       <c r="V246" t="n">
-        <v>1</v>
-      </c>
-      <c r="W246" t="n">
         <v>2</v>
       </c>
+      <c r="W246" t="inlineStr"/>
       <c r="X246" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y246" t="n">
         <v>0</v>
@@ -28831,12 +28829,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>3d082072-1ee8-4005-8bba-f9ec795ad5ab</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>ca-cioos_a924b31b-9882-4abe-8d8e-e875dbbbec82</t>
+          <t>ca-cioos_cfa4ad65-ee12-47c0-9527-206a0f8d92ae</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -28846,7 +28844,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Surface Seawater and Marine Boundary Layer CO2 Time Series from the Bute Inlet Ocean Observing Station (BIOOS) Buoy, Bute Inlet, BC, Canada (Provisional)</t>
+          <t>Hakai Institute Drone Data Index</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -28864,7 +28862,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -28882,51 +28880,67 @@
           <t>dataset</t>
         </is>
       </c>
-      <c r="M247" t="inlineStr"/>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
       <c r="N247" t="n">
         <v>1</v>
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-134.1, 42.65], [-59.42, 42.65], [-59.42, 67.53], [-134.1, 67.53], [-134.1, 42.65]]]}</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q247" t="inlineStr">
         <is>
-          <t>inorganicCarbon, oxygen, seaSurfaceSalinity, seaSurfaceTemperature</t>
-        </is>
-      </c>
-      <c r="R247" t="inlineStr"/>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R247" t="inlineStr">
+        <is>
+          <t>10.21966/0r8b-t282</t>
+        </is>
+      </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="T247" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="U247" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr"/>
       <c r="V247" t="n">
+        <v>1</v>
+      </c>
+      <c r="W247" t="n">
         <v>2</v>
       </c>
-      <c r="W247" t="n">
+      <c r="X247" t="n">
         <v>3</v>
       </c>
-      <c r="X247" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y247" t="inlineStr"/>
-      <c r="Z247" t="inlineStr"/>
-      <c r="AA247" t="inlineStr"/>
+      <c r="Y247" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -28934,12 +28948,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>0894f661-f9cb-48cb-a0b4-8a001eb69420</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>ca-cioos_bfefcdf9-c922-4e4f-a958-aa6da739d3cd</t>
+          <t>ca-cioos_a924b31b-9882-4abe-8d8e-e875dbbbec82</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -28949,7 +28963,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Surface Seawater and Marine Boundary Layer CO2 Time Series from the Bute Inlet Ocean Observing Station (BIOOS) Buoy, Bute Inlet, BC, Canada (Research)</t>
+          <t>Surface Seawater and Marine Boundary Layer CO2 Time Series from the Bute Inlet Ocean Observing Station (BIOOS) Buoy, Bute Inlet, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -28985,11 +28999,7 @@
           <t>dataset</t>
         </is>
       </c>
-      <c r="M248" t="inlineStr">
-        <is>
-          <t>Hakai Institute</t>
-        </is>
-      </c>
+      <c r="M248" t="inlineStr"/>
       <c r="N248" t="n">
         <v>1</v>
       </c>
@@ -29005,14 +29015,10 @@
       </c>
       <c r="Q248" t="inlineStr">
         <is>
-          <t>oxygen, inorganicCarbon, particulateMatter, phytoplanktonBiomassAndDiversity, seaSurfaceSalinity, seaSurfaceTemperature</t>
-        </is>
-      </c>
-      <c r="R248" t="inlineStr">
-        <is>
-          <t>10.21966/4jvz-bv44</t>
-        </is>
-      </c>
+          <t>inorganicCarbon, oxygen, seaSurfaceSalinity, seaSurfaceTemperature</t>
+        </is>
+      </c>
+      <c r="R248" t="inlineStr"/>
       <c r="S248" t="inlineStr">
         <is>
           <t>2026-02-27</t>
@@ -29020,30 +29026,24 @@
       </c>
       <c r="T248" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="U248" t="inlineStr"/>
-      <c r="V248" t="inlineStr"/>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="U248" t="n">
+        <v>1</v>
+      </c>
+      <c r="V248" t="n">
+        <v>2</v>
+      </c>
       <c r="W248" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X248" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y248" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z248" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AA248" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="Y248" t="inlineStr"/>
+      <c r="Z248" t="inlineStr"/>
+      <c r="AA248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -29051,12 +29051,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>e788c2f6-c842-4240-bab4-54a323d62174</t>
+          <t>0894f661-f9cb-48cb-a0b4-8a001eb69420</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>ca-cioos_984e6b72-15d0-4742-bb2d-9ac13b14383a</t>
+          <t>ca-cioos_bfefcdf9-c922-4e4f-a958-aa6da739d3cd</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -29066,7 +29066,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Stream Temperature Observations for Three Streams Near Gold River</t>
+          <t>Surface Seawater and Marine Boundary Layer CO2 Time Series from the Bute Inlet Ocean Observing Station (BIOOS) Buoy, Bute Inlet, BC, Canada (Research)</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -29084,12 +29084,12 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -29112,7 +29112,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.7, 49.96], [-125.9, 49.93], [-126.0, 49.56], [-126.7, 49.73], [-126.7, 49.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976]]]}</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
@@ -29122,29 +29122,29 @@
       </c>
       <c r="Q249" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>oxygen, inorganicCarbon, particulateMatter, phytoplanktonBiomassAndDiversity, seaSurfaceSalinity, seaSurfaceTemperature</t>
         </is>
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>10.21966/cqrt-sk09</t>
+          <t>10.21966/4jvz-bv44</t>
         </is>
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="T249" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="U249" t="inlineStr"/>
-      <c r="V249" t="n">
-        <v>1</v>
-      </c>
-      <c r="W249" t="inlineStr"/>
+      <c r="V249" t="inlineStr"/>
+      <c r="W249" t="n">
+        <v>1</v>
+      </c>
       <c r="X249" t="n">
         <v>1</v>
       </c>
@@ -29168,12 +29168,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
+          <t>e788c2f6-c842-4240-bab4-54a323d62174</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>ca-cioos_84820f31-b6db-479c-a47e-f22f2899b4d2</t>
+          <t>ca-cioos_984e6b72-15d0-4742-bb2d-9ac13b14383a</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -29183,7 +29183,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Biogeochemical Sampling of 28 Streams on Vancouver Island</t>
+          <t>Stream Temperature Observations for Three Streams Near Gold River</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -29229,7 +29229,7 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 50.65], [-127.9, 50.71], [-123.6, 48.43], [-124.0, 48.36], [-127.3, 49.77], [-128.4, 50.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.7, 49.96], [-125.9, 49.93], [-126.0, 49.56], [-126.7, 49.73], [-126.7, 49.96]]]}</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
@@ -29244,40 +29244,38 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>10.21966/chc3-rj93</t>
+          <t>10.21966/cqrt-sk09</t>
         </is>
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="T250" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="U250" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr"/>
       <c r="V250" t="n">
         <v>1</v>
       </c>
       <c r="W250" t="inlineStr"/>
       <c r="X250" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.21966/cqrt-sk09', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_984e6b72-15d0-4742-bb2d-9ac13b14383a'}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -29287,12 +29285,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>63f6c693-7c22-49cc-ad7d-9aa1774a5972</t>
+          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>ca-cioos_d7b34963-67bc-404b-bdd1-b41cc750bdaa</t>
+          <t>ca-cioos_84820f31-b6db-479c-a47e-f22f2899b4d2</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -29302,7 +29300,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Fraser River Airborne Surveys - 2020 - Airborne Coastal Observatory</t>
+          <t>Biogeochemical Sampling of 28 Streams on Vancouver Island</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -29320,7 +29318,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -29348,12 +29346,12 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-121.5, 49.51], [-121.3, 49.53], [-121.4, 49.95], [-121.5, 50.28], [-121.7, 50.52], [-121.8, 50.66], [-121.8, 50.76], [-121.8, 51.01], [-122.1, 51.32], [-122.3, 51.79], [-122.1, 52.11], [-122.3, 52.37], [-122.3, 52.51], [-122.6, 52.49], [-122.4, 51.96], [-122.5, 51.83], [-122.4, 51.49], [-122.3, 51.18], [-121.9, 50.95], [-121.9, 50.62], [-121.8, 50.53], [-121.7, 50.17], [-121.6, 49.89], [-121.5, 49.63], [-121.5, 49.51]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 50.65], [-127.9, 50.71], [-123.6, 48.43], [-124.0, 48.36], [-127.3, 49.77], [-128.4, 50.65]]]}</t>
         </is>
       </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>[{'max': '850.0', 'min': '400.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q251" t="inlineStr">
@@ -29363,38 +29361,40 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>10.21966/f9m6-qg12</t>
+          <t>10.21966/chc3-rj93</t>
         </is>
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="T251" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="U251" t="inlineStr"/>
-      <c r="V251" t="inlineStr"/>
-      <c r="W251" t="n">
-        <v>2</v>
-      </c>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="U251" t="n">
+        <v>1</v>
+      </c>
+      <c r="V251" t="n">
+        <v>1</v>
+      </c>
+      <c r="W251" t="inlineStr"/>
       <c r="X251" t="n">
         <v>2</v>
       </c>
       <c r="Y251" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z251" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'citations', 'id': '10.21966/cqrt-sk09', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_984e6b72-15d0-4742-bb2d-9ac13b14383a'}]</t>
         </is>
       </c>
     </row>
@@ -29404,12 +29404,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
+          <t>63f6c693-7c22-49cc-ad7d-9aa1774a5972</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>ca-cioos_1efbadd2-e735-48cc-9498-e3a5a88e48a6</t>
+          <t>ca-cioos_d7b34963-67bc-404b-bdd1-b41cc750bdaa</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -29419,7 +29419,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Seawater Carbon Dioxide (CO2) Content from the SuperCO2 System in the Pacific Ecosystem Autonomous Research Laboratory, Bamfield Marine Sciences Centre, BC, Canada (Provisional)</t>
+          <t>Fraser River Airborne Surveys - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -29437,12 +29437,12 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
@@ -29461,44 +29461,42 @@
         </is>
       </c>
       <c r="N252" t="n">
+        <v>1</v>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-121.5, 49.51], [-121.3, 49.53], [-121.4, 49.95], [-121.5, 50.28], [-121.7, 50.52], [-121.8, 50.66], [-121.8, 50.76], [-121.8, 51.01], [-122.1, 51.32], [-122.3, 51.79], [-122.1, 52.11], [-122.3, 52.37], [-122.3, 52.51], [-122.6, 52.49], [-122.4, 51.96], [-122.5, 51.83], [-122.4, 51.49], [-122.3, 51.18], [-121.9, 50.95], [-121.9, 50.62], [-121.8, 50.53], [-121.7, 50.17], [-121.6, 49.89], [-121.5, 49.63], [-121.5, 49.51]]]}</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>[{'max': '850.0', 'min': '400.0'}]</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>10.21966/f9m6-qg12</t>
+        </is>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr"/>
+      <c r="V252" t="inlineStr"/>
+      <c r="W252" t="n">
         <v>2</v>
-      </c>
-      <c r="O252" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359]]]}</t>
-        </is>
-      </c>
-      <c r="P252" t="inlineStr">
-        <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
-        </is>
-      </c>
-      <c r="Q252" t="inlineStr">
-        <is>
-          <t>inorganicCarbon, seaSurfaceSalinity, seaSurfaceTemperature</t>
-        </is>
-      </c>
-      <c r="R252" t="inlineStr">
-        <is>
-          <t>10.21966/a0v4-x512</t>
-        </is>
-      </c>
-      <c r="S252" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="T252" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="U252" t="inlineStr"/>
-      <c r="V252" t="n">
-        <v>1</v>
-      </c>
-      <c r="W252" t="n">
-        <v>1</v>
       </c>
       <c r="X252" t="n">
         <v>2</v>
@@ -29523,12 +29521,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>7b1120bc-4a2c-432c-9e54-879d66751a59</t>
+          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>ca-cioos_b2b18171-35b6-4345-b81b-497a90c2e7c5</t>
+          <t>ca-cioos_1efbadd2-e735-48cc-9498-e3a5a88e48a6</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -29538,7 +29536,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Seagrass fish and macroinvertebrate swaths BC Central Coast</t>
+          <t>Seawater Carbon Dioxide (CO2) Content from the SuperCO2 System in the Pacific Ecosystem Autonomous Research Laboratory, Bamfield Marine Sciences Centre, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -29556,7 +29554,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -29580,26 +29578,26 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 52.09], [-128.5, 52.04], [-128.5, 51.97], [-128.5, 51.93], [-128.5, 51.9], [-128.4, 51.88], [-128.3, 51.86], [-128.3, 51.83], [-128.2, 51.63], [-127.9, 51.62], [-127.8, 51.77], [-127.8, 51.83], [-127.9, 51.99], [-128.4, 52.09]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359]]]}</t>
         </is>
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>[{'max': '10.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
+          <t>inorganicCarbon, seaSurfaceSalinity, seaSurfaceTemperature</t>
         </is>
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>10.21966/NMNG-SF35</t>
+          <t>10.21966/a0v4-x512</t>
         </is>
       </c>
       <c r="S253" t="inlineStr">
@@ -29609,16 +29607,18 @@
       </c>
       <c r="T253" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="U253" t="inlineStr"/>
       <c r="V253" t="n">
         <v>1</v>
       </c>
-      <c r="W253" t="inlineStr"/>
+      <c r="W253" t="n">
+        <v>1</v>
+      </c>
       <c r="X253" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y253" t="n">
         <v>0</v>
@@ -29640,12 +29640,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>49374495-400f-4acc-aac6-d7d0b7cae297</t>
+          <t>7b1120bc-4a2c-432c-9e54-879d66751a59</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>ca-cioos_bafcd0eb-8249-471b-b93b-0797cfeea287</t>
+          <t>ca-cioos_b2b18171-35b6-4345-b81b-497a90c2e7c5</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -29655,7 +29655,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020), Central Coast, British Columbia, Canada</t>
+          <t>Seagrass fish and macroinvertebrate swaths BC Central Coast</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -29673,12 +29673,12 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -29701,32 +29701,32 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.64], [-128.1, 51.64], [-128.1, 52.01], [-128.5, 52.01], [-128.5, 51.64]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 52.09], [-128.5, 52.04], [-128.5, 51.97], [-128.5, 51.93], [-128.5, 51.9], [-128.4, 51.88], [-128.3, 51.86], [-128.3, 51.83], [-128.2, 51.63], [-127.9, 51.62], [-127.8, 51.77], [-127.8, 51.83], [-127.9, 51.99], [-128.4, 52.09]]]}</t>
         </is>
       </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '10.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q254" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition, other</t>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>10.21966/20ym-8826</t>
+          <t>10.21966/NMNG-SF35</t>
         </is>
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="T254" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="U254" t="inlineStr"/>
@@ -29757,12 +29757,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>613ba2f9-b21d-445f-8eaa-f42950c9350b</t>
+          <t>49374495-400f-4acc-aac6-d7d0b7cae297</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>ca-cioos_ba41d935-f293-447f-be3d-7098e569b431</t>
+          <t>ca-cioos_bafcd0eb-8249-471b-b93b-0797cfeea287</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -29772,7 +29772,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Water Property Measurements from Conductivity-Temperature-Depth Profiles, BC, Canada (Research)</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020), Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -29790,12 +29790,12 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>Oceanography, Nearshore, Watersheds, Juvenile Salmon Program</t>
+          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -29814,42 +29814,46 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.64], [-128.1, 51.64], [-128.1, 52.01], [-128.5, 52.01], [-128.5, 51.64]]]}</t>
         </is>
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>[{'max': '700.0', 'min': '1.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q255" t="inlineStr">
         <is>
-          <t>oxygen, subSurfaceSalinity, subSurfaceTemperature</t>
+          <t>macroalgalCanopyCoverAndComposition, other</t>
         </is>
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>10.21966/kace-2d24</t>
+          <t>10.21966/20ym-8826</t>
         </is>
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="T255" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="U255" t="inlineStr"/>
-      <c r="V255" t="inlineStr"/>
+      <c r="V255" t="n">
+        <v>1</v>
+      </c>
       <c r="W255" t="inlineStr"/>
-      <c r="X255" t="inlineStr"/>
+      <c r="X255" t="n">
+        <v>1</v>
+      </c>
       <c r="Y255" t="n">
         <v>0</v>
       </c>
@@ -29870,12 +29874,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
+          <t>613ba2f9-b21d-445f-8eaa-f42950c9350b</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>ca-cioos_fb5c9e1e-a911-46b7-8c1d-e34215a105ed</t>
+          <t>ca-cioos_ba41d935-f293-447f-be3d-7098e569b431</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -29885,7 +29889,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 Analyzer located at Bamfield Marine Sciences Centre, Bamfield, BC, Canada (Provisional)</t>
+          <t>Water Property Measurements from Conductivity-Temperature-Depth Profiles, BC, Canada (Research)</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -29903,7 +29907,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Oceanography, Nearshore, Watersheds, Juvenile Salmon Program</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -29927,26 +29931,26 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.13535, 48.83515]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>[{'max': '20.0', 'min': '20.0'}]</t>
+          <t>[{'max': '700.0', 'min': '1.0'}]</t>
         </is>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
-          <t>seaSurfaceTemperature, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
+          <t>oxygen, subSurfaceSalinity, subSurfaceTemperature</t>
         </is>
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>10.21966/65d8-k051</t>
+          <t>10.21966/kace-2d24</t>
         </is>
       </c>
       <c r="S256" t="inlineStr">
@@ -29956,19 +29960,13 @@
       </c>
       <c r="T256" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="U256" t="inlineStr"/>
-      <c r="V256" t="n">
-        <v>1</v>
-      </c>
-      <c r="W256" t="n">
-        <v>2</v>
-      </c>
-      <c r="X256" t="n">
-        <v>3</v>
-      </c>
+      <c r="V256" t="inlineStr"/>
+      <c r="W256" t="inlineStr"/>
+      <c r="X256" t="inlineStr"/>
       <c r="Y256" t="n">
         <v>0</v>
       </c>
@@ -29989,12 +29987,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>b7b923ed-b3fa-48b3-878d-40a3797046bc</t>
+          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>ca-cioos_f7538807-4d49-4ed8-ad36-836c0e71428a</t>
+          <t>ca-cioos_fb5c9e1e-a911-46b7-8c1d-e34215a105ed</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -30004,7 +30002,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>3m Digital Elevation Model - Calvert Island - British Columbia - Canada</t>
+          <t>Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 Analyzer located at Bamfield Marine Sciences Centre, Bamfield, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -30022,12 +30020,12 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -30046,36 +30044,36 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.16482, 51.408116], [-127.868831, 51.408116], [-127.868831, 51.734994], [-128.16482, 51.734994], [-128.16482, 51.408116]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.13535, 48.83515]}</t>
         </is>
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
+          <t>[{'max': '20.0', 'min': '20.0'}]</t>
         </is>
       </c>
       <c r="Q257" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>seaSurfaceTemperature, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
         </is>
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>10.21966/RZVW-4A72</t>
+          <t>10.21966/65d8-k051</t>
         </is>
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="T257" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="U257" t="inlineStr"/>
@@ -30089,16 +30087,16 @@
         <v>3</v>
       </c>
       <c r="Y257" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z257" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -30108,12 +30106,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
+          <t>b7b923ed-b3fa-48b3-878d-40a3797046bc</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>ca-cioos_33c8ce77-0674-4933-a305-01a25d253f70</t>
+          <t>ca-cioos_f7538807-4d49-4ed8-ad36-836c0e71428a</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -30123,7 +30121,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Sea star microbiome data from 16S amplicon sequencing associated with rocky intertidal sites on Calvert and Quadra Islands</t>
+          <t>3m Digital Elevation Model - Calvert Island - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -30141,7 +30139,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Nearshore, Genomics</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -30169,32 +30167,32 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.3, 49.87], [-124.8, 49.87], [-124.8, 51.75], [-128.3, 51.75], [-128.3, 49.87]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.16482, 51.408116], [-127.868831, 51.408116], [-127.868831, 51.734994], [-128.16482, 51.734994], [-128.16482, 51.408116]]]}</t>
         </is>
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q258" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution, microbeBiomassAndDiversity</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>10.21966/0xvh-1318</t>
+          <t>10.21966/RZVW-4A72</t>
         </is>
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="T258" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="U258" t="inlineStr"/>
@@ -30208,16 +30206,16 @@
         <v>3</v>
       </c>
       <c r="Y258" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z258" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}]</t>
         </is>
       </c>
     </row>
@@ -30227,12 +30225,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
+          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>ca-cioos_a8671db6-81cc-4c92-b681-58595fe66182</t>
+          <t>ca-cioos_33c8ce77-0674-4933-a305-01a25d253f70</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -30242,7 +30240,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Water Property Measurements from the Bute Inlet Ocean Observing Station (BIOOS) Wirewalker, Bute Inlet, BC, Canada (Provisional)</t>
+          <t>Sea star microbiome data from 16S amplicon sequencing associated with rocky intertidal sites on Calvert and Quadra Islands</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -30260,12 +30258,12 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore, Genomics</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -30284,36 +30282,36 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-124.9009, 50.5744]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.3, 49.87], [-124.8, 49.87], [-124.8, 51.75], [-128.3, 51.75], [-128.3, 49.87]]]}</t>
         </is>
       </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>[{'max': '250.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q259" t="inlineStr">
         <is>
-          <t>subSurfaceTemperature, subSurfaceSalinity, oxygen, phytoplanktonBiomassAndDiversity</t>
+          <t>invertebrateAbundanceAndDistribution, microbeBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>10.21966/3q5j-n957</t>
+          <t>10.21966/0xvh-1318</t>
         </is>
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="T259" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="U259" t="inlineStr"/>
@@ -30321,10 +30319,10 @@
         <v>1</v>
       </c>
       <c r="W259" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X259" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y259" t="n">
         <v>0</v>
@@ -30346,112 +30344,231 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
+          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>ca-cioos_a8671db6-81cc-4c92-b681-58595fe66182</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Water Property Measurements from the Bute Inlet Ocean Observing Station (BIOOS) Wirewalker, Bute Inlet, BC, Canada (Provisional)</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="H260" t="b">
+        <v>0</v>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Oceanography</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>onGoing</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="N260" t="n">
+        <v>1</v>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>{'type': 'Point', 'coordinates': [-124.9009, 50.5744]}</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>[{'max': '250.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>subSurfaceTemperature, subSurfaceSalinity, oxygen, phytoplanktonBiomassAndDiversity</t>
+        </is>
+      </c>
+      <c r="R260" t="inlineStr">
+        <is>
+          <t>10.21966/3q5j-n957</t>
+        </is>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr"/>
+      <c r="V260" t="n">
+        <v>1</v>
+      </c>
+      <c r="W260" t="n">
+        <v>1</v>
+      </c>
+      <c r="X260" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y260" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z260" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>259</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
           <t>0cef18ab-cea6-4522-baba-1bcd73a30646</t>
         </is>
       </c>
-      <c r="C260" t="inlineStr">
+      <c r="C261" t="inlineStr">
         <is>
           <t>ca-cioos_66fbb7f5-3644-471a-95ee-f8d3758e888b</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>Hakai Institute</t>
-        </is>
-      </c>
-      <c r="E260" t="inlineStr">
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
         <is>
           <t>Mount Robson Aerial Photo and LiDAR Survey</t>
         </is>
       </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>dataset</t>
-        </is>
-      </c>
-      <c r="G260" t="inlineStr">
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
         <is>
           <t>CC-BY-4.0</t>
         </is>
       </c>
-      <c r="H260" t="b">
-        <v>0</v>
-      </c>
-      <c r="I260" t="inlineStr">
+      <c r="H261" t="b">
+        <v>0</v>
+      </c>
+      <c r="I261" t="inlineStr">
         <is>
           <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
-      <c r="J260" t="inlineStr">
+      <c r="J261" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr">
+      <c r="K261" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="L260" t="inlineStr">
-        <is>
-          <t>dataset</t>
-        </is>
-      </c>
-      <c r="M260" t="inlineStr">
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
         <is>
           <t>Tula Foundation</t>
         </is>
       </c>
-      <c r="N260" t="n">
-        <v>1</v>
-      </c>
-      <c r="O260" t="inlineStr">
+      <c r="N261" t="n">
+        <v>1</v>
+      </c>
+      <c r="O261" t="inlineStr">
         <is>
           <t>{'type': 'Polygon', 'coordinates': [[[-119.3, 53.03], [-118.8, 53.03], [-118.8, 53.26], [-119.3, 53.26], [-119.3, 53.03]]]}</t>
         </is>
       </c>
-      <c r="P260" t="inlineStr">
+      <c r="P261" t="inlineStr">
         <is>
           <t>[{'max': '3954.0', 'min': '800.0'}]</t>
         </is>
       </c>
-      <c r="Q260" t="inlineStr">
+      <c r="Q261" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="R260" t="inlineStr">
+      <c r="R261" t="inlineStr">
         <is>
           <t>10.21966/w9n0-kn30</t>
         </is>
       </c>
-      <c r="S260" t="inlineStr"/>
-      <c r="T260" t="inlineStr">
+      <c r="S261" t="inlineStr"/>
+      <c r="T261" t="inlineStr">
         <is>
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="U260" t="n">
-        <v>1</v>
-      </c>
-      <c r="V260" t="n">
-        <v>1</v>
-      </c>
-      <c r="W260" t="n">
+      <c r="U261" t="n">
+        <v>1</v>
+      </c>
+      <c r="V261" t="n">
+        <v>1</v>
+      </c>
+      <c r="W261" t="n">
         <v>3</v>
       </c>
-      <c r="X260" t="n">
+      <c r="X261" t="n">
         <v>5</v>
       </c>
-      <c r="Y260" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z260" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AA260" t="inlineStr">
+      <c r="Y261" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AA261" t="inlineStr">
         <is>
           <t>[]</t>
         </is>

--- a/main/catalog_summary.xlsx
+++ b/main/catalog_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y262"/>
+  <dimension ref="A1:Y261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
@@ -1850,12 +1850,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ca-cioos_af65bf72-27af-4747-8911-ab05591762ac</t>
+          <t>ca-cioos_ab901b46-43f6-4044-b0c3-b5fd825622f4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kelp forest communities along an otter gradient</t>
+          <t>World View 2 Imagery - Coverage of three regions of the BC Central Coast - Summer 2014, 2015, &amp; 2016</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>underDevelopment</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Simon Fraser University</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1911,12 +1911,12 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.770751953125, 51.33404377878941], [-127.74902343749999, 51.33404377878941], [-127.74902343749999, 52.19077237113535], [-128.770751953125, 52.19077237113535], [-128.770751953125, 51.33404377878941]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.61145019531247, 51.61801654877371], [-127.91931152343746, 51.61801654877371], [-127.91931152343746, 52.11325243469631], [-128.61145019531247, 52.11325243469631], [-128.61145019531247, 51.61801654877371]]]}</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>[{'max': '50.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1924,10 +1924,14 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>10.21966/nmds-rx42</t>
+        </is>
+      </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXlMbjJYUlpvZFpITks</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXp1R01BNWFYV0RkUEY</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -1937,15 +1941,25 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>5</v>
-      </c>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1953,12 +1967,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ca-cioos_ab901b46-43f6-4044-b0c3-b5fd825622f4</t>
+          <t>ca-cioos_af65bf72-27af-4747-8911-ab05591762ac</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1968,7 +1982,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>World View 2 Imagery - Coverage of three regions of the BC Central Coast - Summer 2014, 2015, &amp; 2016</t>
+          <t>Kelp forest communities along an otter gradient</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1986,12 +2000,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>underDevelopment</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2006,7 +2020,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Simon Fraser University</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -2014,12 +2028,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.61145019531247, 51.61801654877371], [-127.91931152343746, 51.61801654877371], [-127.91931152343746, 52.11325243469631], [-128.61145019531247, 52.11325243469631], [-128.61145019531247, 51.61801654877371]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.770751953125, 51.33404377878941], [-127.74902343749999, 51.33404377878941], [-127.74902343749999, 52.19077237113535], [-128.770751953125, 52.19077237113535], [-128.770751953125, 51.33404377878941]]]}</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '50.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2027,14 +2041,10 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>10.21966/nmds-rx42</t>
-        </is>
-      </c>
+      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXp1R01BNWFYV0RkUEY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXlMbjJYUlpvZFpITks</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -2044,25 +2054,15 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>3</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -4433,7 +4433,7 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W36" t="n">
         <v>0</v>
@@ -8138,7 +8138,7 @@
         </is>
       </c>
       <c r="V69" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W69" t="n">
         <v>0</v>
@@ -11313,7 +11313,7 @@
         </is>
       </c>
       <c r="V98" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W98" t="inlineStr"/>
       <c r="X98" t="inlineStr"/>
@@ -15525,7 +15525,7 @@
         </is>
       </c>
       <c r="V136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W136" t="n">
         <v>0</v>
@@ -15781,12 +15781,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
+          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -15796,7 +15796,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
+          <t>Stage-Discharge Time Series - Calvert Island - Archived Version 1.0</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -15814,7 +15814,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -15834,20 +15834,20 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Vancouver Island University</t>
         </is>
       </c>
       <c r="N139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
+          <t>[{'max': '250.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
@@ -15855,14 +15855,10 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R139" t="inlineStr">
-        <is>
-          <t>10.21966/1.135248</t>
-        </is>
-      </c>
+      <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFjSmdJMGxrU1pZbXM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
         </is>
       </c>
       <c r="T139" t="inlineStr">
@@ -15872,25 +15868,15 @@
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="V139" t="n">
-        <v>2</v>
-      </c>
-      <c r="W139" t="n">
-        <v>0</v>
-      </c>
-      <c r="X139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="W139" t="inlineStr"/>
+      <c r="X139" t="inlineStr"/>
+      <c r="Y139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15898,12 +15884,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
+          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -15913,7 +15899,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Stage-Discharge Time Series - Calvert Island - Archived Version 1.0</t>
+          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -15931,7 +15917,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -15951,20 +15937,20 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Vancouver Island University</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>[{'max': '250.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
@@ -15972,10 +15958,14 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R140" t="inlineStr"/>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>10.21966/1.135248</t>
+        </is>
+      </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFjSmdJMGxrU1pZbXM</t>
         </is>
       </c>
       <c r="T140" t="inlineStr">
@@ -15985,15 +15975,25 @@
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V140" t="n">
-        <v>5</v>
-      </c>
-      <c r="W140" t="inlineStr"/>
-      <c r="X140" t="inlineStr"/>
-      <c r="Y140" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0</v>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16667,7 +16667,7 @@
         </is>
       </c>
       <c r="V146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W146" t="n">
         <v>0</v>
@@ -20643,12 +20643,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
+          <t>432b05ce-8904-4094-94bf-b97fb6636e41</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>ca-cioos_6c449900-c726-4e9a-b241-707711e253a7</t>
+          <t>ca-cioos_3e90a567-cdd7-41f3-8157-0e7be76eefb8</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -20658,7 +20658,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Hakai Institute Juvenile Salmon Program Time Series</t>
+          <t>Nuchatlaht Survey - Hakai Airborne Coastal Observatory Imagery and Topography Data - Nootka Island British Columbia - 2023</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -20676,7 +20676,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Juvenile Salmon Program</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -20704,53 +20704,51 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.8232006, 49.89790212], [-124.67574133, 49.89790212], [-124.67574133, 50.73488305], [-126.8232006, 50.73488305], [-126.8232006, 49.89790212]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.1, 49.71], [-126.7, 49.71], [-126.7, 50.01], [-127.1, 50.01], [-127.1, 49.71]]]}</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>[{'max': '9.0', 'min': '0.0'}]</t>
+          <t>[{'max': '500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>10.21966/1.566666</t>
+          <t>10.21966/kp87-sf64</t>
         </is>
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXNUQUNpb1hBa0pYWVg</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Nlir_Hi8PQBF_etobGR</t>
         </is>
       </c>
       <c r="T181" t="inlineStr">
         <is>
-          <t>2023-11-03</t>
+          <t>2024-01-08</t>
         </is>
       </c>
       <c r="U181" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
-        </is>
-      </c>
-      <c r="V181" t="n">
-        <v>3</v>
-      </c>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr"/>
       <c r="W181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X181" t="inlineStr">
         <is>
-          <t>[{'year': '2024', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>[{'relationship': 'references', 'id': '10.1111/fog.12471', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1111/fog.12471'}, {'relationship': 'references', 'id': '10.26428/1606-9919-2021-201-669-685', 'type': 'dois', 'status_code': 200, 'url': 'https://izvestiya.tinro-center.ru/jour/article/view/662'}, {'relationship': 'references', 'id': '10.5281/zenodo.4005400', 'type': 'dois', 'status_code': 200, 'url': 'https://zenodo.org/records/4005400'}, {'relationship': 'references', 'id': '10.48321/d1cw23', 'type': 'dois', 'status_code': 200, 'url': 'https://dmphub.uc3prd.cdlib.net/dmps/10.48321/D1CW23'}, {'relationship': 'references', 'id': '10.48321/d12k5b', 'type': 'dois', 'status_code': 200, 'url': 'https://dmphub.uc3prd.cdlib.net/dmps/10.48321/D12K5B'}, {'relationship': 'references', 'id': '10.21966/9ktc-qm09', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_6f6560e7-7497-4685-9df2-51c66080b7c9'}, {'relationship': 'references', 'id': '10.5683/sp3/socbjj', 'type': 'dois', 'status_code': 200, 'url': 'https://borealisdata.ca/dataset.xhtml?persistentId=doi:10.5683/SP3/SOCBJJ'}, {'relationship': 'citations', 'id': '10.5061/dryad.x69p8czn0', 'type': 'dois', 'status_code': 200, 'url': 'https://datadryad.org/dataset/doi:10.5061/dryad.x69p8czn0'}, {'relationship': 'partOf', 'id': '10.25607/obis.export.234a34a8', 'type': 'dois', 'status_code': 200, 'url': 'https://obis.org/export/234a34a8'}, {'relationship': 'partOf', 'id': '10.25607/obis.occurrence.b89117cd', 'type': 'dois', 'status_code': 200, 'url': 'https://github.com/iobis/obis-open-data'}, {'relationship': 'versions', 'id': '10.21966/e5c1-c396', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_eb1feb98-b11a-4663-b7ab-2216df8187bd'}, {'relationship': 'versions', 'id': '10.21966/99mg-0s52', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_8853a375-f067-4760-b5d1-98c1fcf40c6d'}, {'relationship': 'versions', 'id': '10.21966/c7na-z171', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_1769a04e-b77b-409b-8e48-bc2098bbad3e'}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -20760,12 +20758,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>432b05ce-8904-4094-94bf-b97fb6636e41</t>
+          <t>582c6ff0-029e-44ba-8ba1-d3f2f39f2005</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>ca-cioos_3e90a567-cdd7-41f3-8157-0e7be76eefb8</t>
+          <t>ca-cioos_6f6560e7-7497-4685-9df2-51c66080b7c9</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -20775,7 +20773,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Nuchatlaht Survey - Hakai Airborne Coastal Observatory Imagery and Topography Data - Nootka Island British Columbia - 2023</t>
+          <t>Genetic Stock Identification of Juvenile Sockeye Salmon Captured in the Discovery Islands and Johnstone Strait BC, Canada</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -20793,7 +20791,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Juvenile Salmon Program</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -20821,51 +20819,53 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.1, 49.71], [-126.7, 49.71], [-126.7, 50.01], [-127.1, 50.01], [-127.1, 49.71]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.0, 49.88], [-124.4, 49.88], [-124.4, 50.84], [-127.0, 50.84], [-127.0, 49.88]]]}</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>[{'max': '500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '9.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>fishAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>10.21966/kp87-sf64</t>
+          <t>10.21966/9ktc-qm09</t>
         </is>
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Nlir_Hi8PQBF_etobGR</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/UTb9hNU3GJRK302QyaKNIvj2OiJ2/-NM0DF83_HSOwpbGBM8m</t>
         </is>
       </c>
       <c r="T182" t="inlineStr">
         <is>
-          <t>2024-01-08</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="U182" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="V182" t="inlineStr"/>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="V182" t="n">
+        <v>1</v>
+      </c>
       <c r="W182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X182" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2024', 'total': 1}]</t>
         </is>
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'citations', 'id': '10.21966/1.566666', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_6c449900-c726-4e9a-b241-707711e253a7'}]</t>
         </is>
       </c>
     </row>
@@ -20875,12 +20875,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>582c6ff0-029e-44ba-8ba1-d3f2f39f2005</t>
+          <t>11051c56-8d67-43fc-a13c-b706e851a5a4</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>ca-cioos_6f6560e7-7497-4685-9df2-51c66080b7c9</t>
+          <t>ca-cioos_2d693456-7e65-46be-95d7-6bb697320017</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -20890,7 +20890,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Genetic Stock Identification of Juvenile Sockeye Salmon Captured in the Discovery Islands and Johnstone Strait BC, Canada</t>
+          <t>Water Level and Weather Station Time Series, Pruth Bay, Kwakshua Channel, Central Coast, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -20908,12 +20908,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Juvenile Salmon Program</t>
+          <t>Oceanography, Watersheds</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -20936,53 +20936,51 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.0, 49.88], [-124.4, 49.88], [-124.4, 50.84], [-127.0, 50.84], [-127.0, 49.88]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-128.1302805556, 51.6544888889]}</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>[{'max': '9.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution</t>
+          <t>seaSurfaceHeight, other, seaSurfaceTemperature</t>
         </is>
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>10.21966/9ktc-qm09</t>
+          <t>10.21966/8d4w-sr07</t>
         </is>
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/UTb9hNU3GJRK302QyaKNIvj2OiJ2/-NM0DF83_HSOwpbGBM8m</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MkxD-S6TxIvv2e6_OGH</t>
         </is>
       </c>
       <c r="T183" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="U183" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="V183" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr"/>
       <c r="W183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X183" t="inlineStr">
         <is>
-          <t>[{'year': '2024', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.21966/1.566666', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_6c449900-c726-4e9a-b241-707711e253a7'}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -20992,12 +20990,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>11051c56-8d67-43fc-a13c-b706e851a5a4</t>
+          <t>b0e815da-1b17-404d-8bf6-0bdb4a22d170</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>ca-cioos_2d693456-7e65-46be-95d7-6bb697320017</t>
+          <t>ca-cioos_c24f23f0-8d16-4bfd-835a-5475f1ecd8e8</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -21007,7 +21005,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Water Level and Weather Station Time Series, Pruth Bay, Kwakshua Channel, Central Coast, BC, Canada (Provisional)</t>
+          <t>Extent of Canopy-Forming Kelps, Derived from World View-2, Central Coast, Central Coast, British Columbia</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -21025,12 +21023,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Oceanography, Watersheds</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -21049,44 +21047,46 @@
         </is>
       </c>
       <c r="N184" t="n">
+        <v>3</v>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6993408203125, 51.31001339554933], [-127.65014648437497, 51.31001339554933], [-127.65014648437497, 52.221069523572794], [-128.6993408203125, 52.221069523572794], [-128.6993408203125, 51.31001339554933]]]}</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>10.21966/5fs0-nn02</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVE2ZkIxMnhEdmF6Rkw</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>2024-03-14</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="V184" t="n">
         <v>1</v>
       </c>
-      <c r="O184" t="inlineStr">
-        <is>
-          <t>{'type': 'Point', 'coordinates': [-128.1302805556, 51.6544888889]}</t>
-        </is>
-      </c>
-      <c r="P184" t="inlineStr">
-        <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q184" t="inlineStr">
-        <is>
-          <t>seaSurfaceHeight, other, seaSurfaceTemperature</t>
-        </is>
-      </c>
-      <c r="R184" t="inlineStr">
-        <is>
-          <t>10.21966/8d4w-sr07</t>
-        </is>
-      </c>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MkxD-S6TxIvv2e6_OGH</t>
-        </is>
-      </c>
-      <c r="T184" t="inlineStr">
-        <is>
-          <t>2024-03-14</t>
-        </is>
-      </c>
-      <c r="U184" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="V184" t="inlineStr"/>
       <c r="W184" t="n">
         <v>0</v>
       </c>
@@ -21107,12 +21107,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>b0e815da-1b17-404d-8bf6-0bdb4a22d170</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>ca-cioos_c24f23f0-8d16-4bfd-835a-5475f1ecd8e8</t>
+          <t>ca-cioos_d1bef0b7-4d15-4bc1-bf34-faca6352891f</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -21122,7 +21122,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Extent of Canopy-Forming Kelps, Derived from World View-2, Central Coast, Central Coast, British Columbia</t>
+          <t>Daily satellite (Sentinel 3A and 3B) chlorophyll and suspended matter concentrations for coastal British Columbia and southeast Alaska</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -21140,12 +21140,12 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -21164,31 +21164,31 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6993408203125, 51.31001339554933], [-127.65014648437497, 51.31001339554933], [-127.65014648437497, 52.221069523572794], [-128.6993408203125, 52.221069523572794], [-128.6993408203125, 51.31001339554933]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-139.0, 47.0], [-121.5, 47.0], [-121.5, 59.5], [-139.0, 59.5], [-139.0, 47.0]]]}</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>phytoplanktonBiomassAndDiversity, particulateMatter, other</t>
         </is>
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>10.21966/5fs0-nn02</t>
+          <t>10.21966/dveq-bt48</t>
         </is>
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVE2ZkIxMnhEdmF6Rkw</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-NTteirxDjvnABVz_7Dh</t>
         </is>
       </c>
       <c r="T185" t="inlineStr">
@@ -21198,11 +21198,11 @@
       </c>
       <c r="U185" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="V185" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W185" t="n">
         <v>0</v>
@@ -21224,12 +21224,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>abb0b617-3a3e-43ec-b62e-e2918bfc10aa</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>ca-cioos_d1bef0b7-4d15-4bc1-bf34-faca6352891f</t>
+          <t>ca-cioos_b8483c9e-81e6-4e1a-b09f-2d66f8fee9a2</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -21239,7 +21239,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Daily satellite (Sentinel 3A and 3B) chlorophyll and suspended matter concentrations for coastal British Columbia and southeast Alaska</t>
+          <t>Spatial extent of surface canopy kelp (Nereocystis luetkeana) derived from fixed-wing surveys (2023), Denman Island to south Quadra Island, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -21257,12 +21257,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Airborne Coastal Observatory, Nearshore, Geospatial</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -21285,41 +21285,41 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-139.0, 47.0], [-121.5, 47.0], [-121.5, 59.5], [-139.0, 59.5], [-139.0, 47.0]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.3, 50.02], [-125.1, 50.05], [-125.1, 49.9], [-124.8, 49.71], [-124.7, 49.56], [-124.8, 49.55], [-124.9, 49.64], [-125.2, 49.9], [-125.2, 49.9], [-125.3, 50.02]]]}</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>phytoplanktonBiomassAndDiversity, particulateMatter, other</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>10.21966/dveq-bt48</t>
+          <t>10.21966/fmw1-8w35</t>
         </is>
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-NTteirxDjvnABVz_7Dh</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-NpNoCv2XWdhBoo5RBKV</t>
         </is>
       </c>
       <c r="T186" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="U186" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="V186" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W186" t="n">
         <v>0</v>
@@ -21341,12 +21341,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>abb0b617-3a3e-43ec-b62e-e2918bfc10aa</t>
+          <t>9df42f88-b8d8-4e2d-97bb-ad5ba49f6f1f</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>ca-cioos_b8483c9e-81e6-4e1a-b09f-2d66f8fee9a2</t>
+          <t>ca-cioos_59b33373-ae4a-4719-a3df-0e36a08187d8</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -21356,7 +21356,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp (Nereocystis luetkeana) derived from fixed-wing surveys (2023), Denman Island to south Quadra Island, British Columbia, Canada</t>
+          <t>Seagrass Site-Level Production on BC Central Coast</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -21374,12 +21374,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Nearshore, Geospatial</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -21402,37 +21402,37 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.3, 50.02], [-125.1, 50.05], [-125.1, 49.9], [-124.8, 49.71], [-124.7, 49.56], [-124.8, 49.55], [-124.9, 49.64], [-125.2, 49.9], [-125.2, 49.9], [-125.3, 50.02]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.98931373, 50.8340959], [-127.03580726, 50.8340959], [-127.03580726, 52.33530479], [-128.98931373, 52.33530479], [-128.98931373, 50.8340959]]]}</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '10.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>other, seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>10.21966/fmw1-8w35</t>
+          <t>10.21966/ezev-0v96</t>
         </is>
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-NpNoCv2XWdhBoo5RBKV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/lJHlH9nm20QQOPuk217xLlxWbNv1/-NPt7-mgrZEUzma8l5W_</t>
         </is>
       </c>
       <c r="T187" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="U187" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="V187" t="n">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>9df42f88-b8d8-4e2d-97bb-ad5ba49f6f1f</t>
+          <t>bf7c05e8-510d-4449-9e81-4c358ff3f440</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>ca-cioos_59b33373-ae4a-4719-a3df-0e36a08187d8</t>
+          <t>ca-cioos_1755dc37-8d33-4158-8041-c22536fd5771</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -21473,7 +21473,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Seagrass Site-Level Production on BC Central Coast</t>
+          <t>Bulk and Size-Fractionated Chlorophyll and Phaeopigment Concentrations Collected by Niskin Bottle, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -21491,7 +21491,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -21519,37 +21519,37 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.98931373, 50.8340959], [-127.03580726, 50.8340959], [-127.03580726, 52.33530479], [-128.98931373, 52.33530479], [-128.98931373, 50.8340959]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>[{'max': '10.0', 'min': '0.0'}]</t>
+          <t>[{'max': '650.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>other, seagrassCoverAndComposition</t>
+          <t>particulateMatter</t>
         </is>
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>10.21966/ezev-0v96</t>
+          <t>10.21966/90h6-b497</t>
         </is>
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/lJHlH9nm20QQOPuk217xLlxWbNv1/-NPt7-mgrZEUzma8l5W_</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-McQFPAf457LB4-SWmyL</t>
         </is>
       </c>
       <c r="T188" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="U188" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="V188" t="n">
@@ -21575,12 +21575,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>bf7c05e8-510d-4449-9e81-4c358ff3f440</t>
+          <t>8882a149-fabd-4ecd-98d3-68a2a88aee38</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>ca-cioos_1755dc37-8d33-4158-8041-c22536fd5771</t>
+          <t>ca-cioos_d55021c3-a142-4e14-8208-36c9826c1893</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -21590,7 +21590,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Bulk and Size-Fractionated Chlorophyll and Phaeopigment Concentrations Collected by Niskin Bottle, BC, Canada (Provisional)</t>
+          <t>Bulk and Size-Fractionated Chlorophyll and Phaeopigment Concentrations Collected by Niskin Bottle, BC, Canada (Research)</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -21632,7 +21632,7 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O189" t="inlineStr">
         <is>
@@ -21646,17 +21646,17 @@
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>particulateMatter</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>10.21966/90h6-b497</t>
+          <t>10.21966/q5vm-8797</t>
         </is>
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-McQFPAf457LB4-SWmyL</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-MadZvZJ4ZeikpCgRcV8</t>
         </is>
       </c>
       <c r="T189" t="inlineStr">
@@ -21669,9 +21669,7 @@
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="V189" t="n">
-        <v>1</v>
-      </c>
+      <c r="V189" t="inlineStr"/>
       <c r="W189" t="n">
         <v>0</v>
       </c>
@@ -21692,12 +21690,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>8882a149-fabd-4ecd-98d3-68a2a88aee38</t>
+          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>ca-cioos_d55021c3-a142-4e14-8208-36c9826c1893</t>
+          <t>ca-cioos_6143028b-028d-46c7-a67d-f3a513435e63</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -21707,7 +21705,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Bulk and Size-Fractionated Chlorophyll and Phaeopigment Concentrations Collected by Niskin Bottle, BC, Canada (Research)</t>
+          <t>Water Property Measurements from Conductivity-Temperature-Depth Profiles, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -21725,7 +21723,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Juvenile Salmon Program, Oceanography, Nearshore</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -21749,44 +21747,46 @@
         </is>
       </c>
       <c r="N190" t="n">
+        <v>1</v>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>[{'max': '700.0', 'min': '1.0'}]</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>oxygen, subSurfaceSalinity, subSurfaceTemperature</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>10.21966/rj8w-aa62</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MMHJ4k2EEwxkbXkrjxa</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="V190" t="n">
         <v>2</v>
       </c>
-      <c r="O190" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
-        </is>
-      </c>
-      <c r="P190" t="inlineStr">
-        <is>
-          <t>[{'max': '650.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q190" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R190" t="inlineStr">
-        <is>
-          <t>10.21966/q5vm-8797</t>
-        </is>
-      </c>
-      <c r="S190" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-MadZvZJ4ZeikpCgRcV8</t>
-        </is>
-      </c>
-      <c r="T190" t="inlineStr">
-        <is>
-          <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="U190" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="V190" t="inlineStr"/>
       <c r="W190" t="n">
         <v>0</v>
       </c>
@@ -21807,12 +21807,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
+          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>ca-cioos_6143028b-028d-46c7-a67d-f3a513435e63</t>
+          <t>ca-cioos_6652a7a9-d27f-4cbe-ac04-435c238e991d</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -21822,7 +21822,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Water Property Measurements from Conductivity-Temperature-Depth Profiles, BC, Canada (Provisional)</t>
+          <t>Water Level Time Series, Choke Pass, Central Coast, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -21840,12 +21840,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Juvenile Salmon Program, Oceanography, Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -21868,37 +21868,37 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-128.12103, 51.670666]}</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>[{'max': '700.0', 'min': '1.0'}]</t>
+          <t>[{'max': '6.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>oxygen, subSurfaceSalinity, subSurfaceTemperature</t>
+          <t>seaSurfaceHeight</t>
         </is>
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>10.21966/rj8w-aa62</t>
+          <t>10.21966/kqd6-1j57</t>
         </is>
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MMHJ4k2EEwxkbXkrjxa</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-Mknr8pYvIQKw4r-WTFd</t>
         </is>
       </c>
       <c r="T191" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="U191" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="V191" t="n">
@@ -21924,12 +21924,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
+          <t>2081eb2e-67c5-44b7-b048-aeb2c646f238</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>ca-cioos_6652a7a9-d27f-4cbe-ac04-435c238e991d</t>
+          <t>ca-cioos_f67c0c58-3225-4dac-9264-1e76f07c9374</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -21939,7 +21939,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Water Level Time Series, Choke Pass, Central Coast, BC, Canada (Provisional)</t>
+          <t>Data for the paper "Phylogenomic position of eupelagonemids, abundant, and diverse deep-ocean heterotrophs"</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -21957,7 +21957,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Genomics</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -21977,7 +21977,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="N192" t="n">
@@ -21985,42 +21985,40 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-128.12103, 51.670666]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.9661, 51.65001], [-127.966, 51.65001], [-127.966, 51.65], [-127.9661, 51.65], [-127.9661, 51.65001]]]}</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>[{'max': '6.0', 'min': '0.0'}]</t>
+          <t>[{'max': '300.0', 'min': '300.0'}]</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>seaSurfaceHeight</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>10.21966/kqd6-1j57</t>
+          <t>10.21966/7t4p-s714</t>
         </is>
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-Mknr8pYvIQKw4r-WTFd</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/NSo1FkJnvIbQDOlYlwNfWGnAxx33/-O1xBAkNi0P8igzOb4rg</t>
         </is>
       </c>
       <c r="T192" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="U192" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="V192" t="n">
-        <v>2</v>
-      </c>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr"/>
       <c r="W192" t="n">
         <v>0</v>
       </c>
@@ -22041,12 +22039,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2081eb2e-67c5-44b7-b048-aeb2c646f238</t>
+          <t>1dfdbadf-6314-4411-8d18-752f6dd920e9</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>ca-cioos_f67c0c58-3225-4dac-9264-1e76f07c9374</t>
+          <t>ca-cioos_67e89414-a93f-496d-9766-9311f0d3954e</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -22056,7 +22054,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Data for the paper "Phylogenomic position of eupelagonemids, abundant, and diverse deep-ocean heterotrophs"</t>
+          <t>Motile Invertebrate Surveys - BC Central Coast</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -22074,12 +22072,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Genomics</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -22094,7 +22092,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>University of British Columbia</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N193" t="n">
@@ -22102,51 +22100,53 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.9661, 51.65001], [-127.966, 51.65001], [-127.966, 51.65], [-127.9661, 51.65], [-127.9661, 51.65001]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.2, 51.63], [-128.1, 51.63], [-128.1, 51.67], [-128.2, 51.67], [-128.2, 51.63]]]}</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>[{'max': '300.0', 'min': '300.0'}]</t>
+          <t>[{'max': '5.0', 'min': '-5.0'}]</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>10.21966/7t4p-s714</t>
+          <t>10.21966/0052-wk15</t>
         </is>
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/NSo1FkJnvIbQDOlYlwNfWGnAxx33/-O1xBAkNi0P8igzOb4rg</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-MotWzhmBvoGPE8QZ0sf</t>
         </is>
       </c>
       <c r="T193" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="U193" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
-        </is>
-      </c>
-      <c r="V193" t="inlineStr"/>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="V193" t="n">
+        <v>1</v>
+      </c>
       <c r="W193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X193" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'citations', 'id': '10.48321/d1ae4278b4', 'type': 'dois', 'status_code': 200, 'url': 'https://dmphub.uc3prd.cdlib.net/dmps/10.48321/D1AE4278B4'}]</t>
         </is>
       </c>
     </row>
@@ -22156,12 +22156,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>1dfdbadf-6314-4411-8d18-752f6dd920e9</t>
+          <t>a8f61379-14f9-4ccc-bc9b-4408ba8340d7</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>ca-cioos_67e89414-a93f-496d-9766-9311f0d3954e</t>
+          <t>ca-cioos_52797e17-c0ed-46a4-9dcd-e34f801c6205</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -22171,7 +22171,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Motile Invertebrate Surveys - BC Central Coast</t>
+          <t>Fucus Dynamics - Point Intercept Surveys - BC Central Coast</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -22227,27 +22227,27 @@
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>10.21966/0052-wk15</t>
+          <t>10.21966/v57r-g944</t>
         </is>
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-MotWzhmBvoGPE8QZ0sf</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-MopPnOL2o_bshK-cKxr</t>
         </is>
       </c>
       <c r="T194" t="inlineStr">
         <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
           <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="U194" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
         </is>
       </c>
       <c r="V194" t="n">
@@ -22258,12 +22258,12 @@
       </c>
       <c r="X194" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
+          <t>[{'year': '2024', 'total': 1}]</t>
         </is>
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.48321/d1ae4278b4', 'type': 'dois', 'status_code': 200, 'url': 'https://dmphub.uc3prd.cdlib.net/dmps/10.48321/D1AE4278B4'}]</t>
+          <t>[{'relationship': 'citations', 'id': '10.21966/hpqq-0k76', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_9201118a-b0c4-470f-a76f-396bacc5e93e'}]</t>
         </is>
       </c>
     </row>
@@ -22273,12 +22273,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>a8f61379-14f9-4ccc-bc9b-4408ba8340d7</t>
+          <t>c4d3a53a-faa2-4c3e-bcd3-cfdb0aef0078</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>ca-cioos_52797e17-c0ed-46a4-9dcd-e34f801c6205</t>
+          <t>ca-cioos_355467ad-104d-40a6-b06e-52a67bfe247e</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -22288,7 +22288,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Fucus Dynamics - Point Intercept Surveys - BC Central Coast</t>
+          <t>Water column CO2 system measurements from January 2016 to December 2023 from Hakai Institute oceanographic station QU39 in northern Strait of Georgia, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -22306,12 +22306,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -22334,53 +22334,53 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.2, 51.63], [-128.1, 51.63], [-128.1, 51.67], [-128.2, 51.67], [-128.2, 51.63]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.1, 50.03]}</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '-5.0'}]</t>
+          <t>[{'max': '262.0', 'min': '1.0'}]</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>inorganicCarbon, oxygen, subSurfaceSalinity, seaSurfaceTemperature, seaSurfaceSalinity, subSurfaceTemperature</t>
         </is>
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>10.21966/v57r-g944</t>
+          <t>10.21966/k1xg-6920</t>
         </is>
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-MopPnOL2o_bshK-cKxr</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-O6XpUwSfsllQlTBMz53</t>
         </is>
       </c>
       <c r="T195" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="U195" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="V195" t="n">
         <v>1</v>
       </c>
       <c r="W195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X195" t="inlineStr">
         <is>
-          <t>[{'year': '2024', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.21966/hpqq-0k76', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_9201118a-b0c4-470f-a76f-396bacc5e93e'}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -22390,12 +22390,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>c4d3a53a-faa2-4c3e-bcd3-cfdb0aef0078</t>
+          <t>52d607c9-46cd-4be9-a752-1b5446272f32</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>ca-cioos_355467ad-104d-40a6-b06e-52a67bfe247e</t>
+          <t>ca-cioos_0507a738-cd65-4ba4-943e-42b9d022b637</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -22405,7 +22405,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Water column CO2 system measurements from January 2016 to December 2023 from Hakai Institute oceanographic station QU39 in northern Strait of Georgia, British Columbia, Canada</t>
+          <t>Fraser River Airborne Surveys - 2021 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -22451,42 +22451,40 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.1, 50.03]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.1, 50.5], [-121.7, 50.5], [-121.7, 51.12], [-122.1, 51.12], [-122.1, 50.5]]]}</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>[{'max': '262.0', 'min': '1.0'}]</t>
+          <t>[{'max': '1500.0', 'min': '185.0'}]</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>inorganicCarbon, oxygen, subSurfaceSalinity, seaSurfaceTemperature, seaSurfaceSalinity, subSurfaceTemperature</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>10.21966/k1xg-6920</t>
+          <t>10.21966/ytgc-6g46</t>
         </is>
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-O6XpUwSfsllQlTBMz53</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NHfqx-d8tuAroY8BWc7</t>
         </is>
       </c>
       <c r="T196" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="U196" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="V196" t="n">
-        <v>1</v>
-      </c>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr"/>
       <c r="W196" t="n">
         <v>0</v>
       </c>
@@ -22507,12 +22505,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>52d607c9-46cd-4be9-a752-1b5446272f32</t>
+          <t>551bbe09-f182-478b-8d50-2f9a4dbd93ae</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>ca-cioos_0507a738-cd65-4ba4-943e-42b9d022b637</t>
+          <t>ca-cioos_189dd319-d5ef-4f2a-a060-df8d47628b86</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -22522,7 +22520,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Fraser River Airborne Surveys - 2021 - Hakai Airborne Coastal Observatory</t>
+          <t>Elliot Creek Landslide LiDAR Mapping - 2023 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -22540,7 +22538,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -22564,16 +22562,16 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.1, 50.5], [-121.7, 50.5], [-121.7, 51.12], [-122.1, 51.12], [-122.1, 50.5]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.8, 50.84], [-124.5, 50.84], [-124.5, 51.0], [-124.8, 51.0], [-124.8, 50.84]]]}</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>[{'max': '1500.0', 'min': '185.0'}]</t>
+          <t>[{'max': '2300.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr">
@@ -22583,12 +22581,12 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>10.21966/ytgc-6g46</t>
+          <t>10.21966/szqj-b355</t>
         </is>
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NHfqx-d8tuAroY8BWc7</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRZqJivYfce75NOoBD</t>
         </is>
       </c>
       <c r="T197" t="inlineStr">
@@ -22598,7 +22596,7 @@
       </c>
       <c r="U197" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="V197" t="inlineStr"/>
@@ -22622,12 +22620,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>551bbe09-f182-478b-8d50-2f9a4dbd93ae</t>
+          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>ca-cioos_189dd319-d5ef-4f2a-a060-df8d47628b86</t>
+          <t>ca-cioos_33a367c1-2706-4301-af99-4455fbe189a0</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -22637,7 +22635,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Elliot Creek Landslide LiDAR Mapping - 2023 - Airborne Coastal Observatory</t>
+          <t>Cryosphere Snow Surveys Southwest British Columbia - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -22655,7 +22653,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -22683,7 +22681,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.8, 50.84], [-124.5, 50.84], [-124.5, 51.0], [-124.8, 51.0], [-124.8, 50.84]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.9, 48.62], [-122.1, 48.62], [-122.1, 50.82], [-126.9, 50.82], [-126.9, 48.62]]]}</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -22698,12 +22696,12 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>10.21966/szqj-b355</t>
+          <t>10.21966/thq7-0g08</t>
         </is>
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRZqJivYfce75NOoBD</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRfMcU9I8mMcBH6qiv</t>
         </is>
       </c>
       <c r="T198" t="inlineStr">
@@ -22713,10 +22711,12 @@
       </c>
       <c r="U198" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="V198" t="inlineStr"/>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="V198" t="n">
+        <v>3</v>
+      </c>
       <c r="W198" t="n">
         <v>0</v>
       </c>
@@ -22737,12 +22737,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
+          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>ca-cioos_33a367c1-2706-4301-af99-4455fbe189a0</t>
+          <t>ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -22752,7 +22752,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Cryosphere Snow Surveys Southwest British Columbia - Airborne Coastal Observatory</t>
+          <t>Bute Inlet Geohazard - Topography Surveys - 2023 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -22794,16 +22794,16 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.9, 48.62], [-122.1, 48.62], [-122.1, 50.82], [-126.9, 50.82], [-126.9, 48.62]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.9, 50.53], [-124.2, 50.53], [-124.2, 50.99], [-124.9, 50.99], [-124.9, 50.53]]]}</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>[{'max': '2300.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2600.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q199" t="inlineStr">
@@ -22813,12 +22813,12 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>10.21966/thq7-0g08</t>
+          <t>10.21966/e4b8-vp48</t>
         </is>
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRfMcU9I8mMcBH6qiv</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRG7xQ84LQrgS4jhie</t>
         </is>
       </c>
       <c r="T199" t="inlineStr">
@@ -22828,7 +22828,7 @@
       </c>
       <c r="U199" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="V199" t="n">
@@ -22854,12 +22854,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
+          <t>78efda1b-9688-4bcf-b16e-7167c17c0bcb</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a</t>
+          <t>ca-cioos_43422dc8-2573-4f60-bf87-df447d57ab7a</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -22869,7 +22869,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Bute Inlet Geohazard - Topography Surveys - 2023 - Hakai Airborne Coastal Observatory</t>
+          <t>USGS Glacier Mapping - 2023 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -22911,45 +22911,45 @@
         </is>
       </c>
       <c r="N200" t="n">
+        <v>2</v>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-121.4, 47.68], [-113.0, 47.68], [-113.0, 49.08], [-121.4, 49.08], [-121.4, 47.68]]]}</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>[{'max': '2800.0', 'min': '100.0'}]</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>10.21966/bzr6-er66</t>
+        </is>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRKhzLRiCcp6ENuX2r</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="V200" t="n">
         <v>1</v>
-      </c>
-      <c r="O200" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.9, 50.53], [-124.2, 50.53], [-124.2, 50.99], [-124.9, 50.99], [-124.9, 50.53]]]}</t>
-        </is>
-      </c>
-      <c r="P200" t="inlineStr">
-        <is>
-          <t>[{'max': '2600.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q200" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R200" t="inlineStr">
-        <is>
-          <t>10.21966/e4b8-vp48</t>
-        </is>
-      </c>
-      <c r="S200" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRG7xQ84LQrgS4jhie</t>
-        </is>
-      </c>
-      <c r="T200" t="inlineStr">
-        <is>
-          <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="U200" t="inlineStr">
-        <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="V200" t="n">
-        <v>3</v>
       </c>
       <c r="W200" t="n">
         <v>0</v>
@@ -22971,12 +22971,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>78efda1b-9688-4bcf-b16e-7167c17c0bcb</t>
+          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>ca-cioos_43422dc8-2573-4f60-bf87-df447d57ab7a</t>
+          <t>ca-cioos_6756b221-28a0-4848-9761-905cbd558cd7</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -22986,7 +22986,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>USGS Glacier Mapping - 2023 - Hakai Airborne Coastal Observatory</t>
+          <t>Protistan plankton time series from the northern Salish Sea and Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -23004,12 +23004,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -23028,45 +23028,45 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-121.4, 47.68], [-113.0, 47.68], [-113.0, 49.08], [-121.4, 49.08], [-121.4, 47.68]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>[{'max': '2800.0', 'min': '100.0'}]</t>
+          <t>[{'max': '6.0', 'min': '1.0'}]</t>
         </is>
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>phytoplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>10.21966/bzr6-er66</t>
+          <t>10.21966/jv5k-3k59</t>
         </is>
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRKhzLRiCcp6ENuX2r</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-Nh8VlPQ_m681tso87Gd</t>
         </is>
       </c>
       <c r="T201" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="U201" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="V201" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W201" t="n">
         <v>0</v>
@@ -23088,12 +23088,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
+          <t>9d1749f8-9be2-468c-946e-965f92fcdc67</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>ca-cioos_6756b221-28a0-4848-9761-905cbd558cd7</t>
+          <t>ca-cioos_6e947d50-8392-42ce-bff9-24b126c7cab7</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -23103,7 +23103,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Protistan plankton time series from the northern Salish Sea and Central Coast, British Columbia, Canada</t>
+          <t>Spatial extent of eelgrass (Zostera marina) beds from monitoring sites within the greater park ecosystem of Pacific Rim National Park Reserve (2017, 2018)</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -23121,12 +23121,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore, Geospatial</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -23145,46 +23145,44 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.0511576, 48.72717181], [-124.94565833, 48.72717181], [-124.94565833, 49.24536019], [-126.0511576, 49.24536019], [-126.0511576, 48.72717181]]]}</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>[{'max': '6.0', 'min': '1.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>phytoplanktonBiomassAndDiversity</t>
+          <t>other, seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>10.21966/jv5k-3k59</t>
+          <t>10.21966/8mpe-h081</t>
         </is>
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-Nh8VlPQ_m681tso87Gd</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUR4a1V0N1UxYTc2U3Q</t>
         </is>
       </c>
       <c r="T202" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="U202" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="V202" t="n">
-        <v>4</v>
-      </c>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr"/>
       <c r="W202" t="n">
         <v>0</v>
       </c>
@@ -23205,12 +23203,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>9d1749f8-9be2-468c-946e-965f92fcdc67</t>
+          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>ca-cioos_6e947d50-8392-42ce-bff9-24b126c7cab7</t>
+          <t>ca-cioos_f25b00ba-ad63-42b3-8021-3fb6aa99baff</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -23220,12 +23218,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Spatial extent of eelgrass (Zostera marina) beds from monitoring sites within the greater park ecosystem of Pacific Rim National Park Reserve (2017, 2018)</t>
+          <t>Fraser River Landslide Project - Sites of Concern 2024</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>document</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -23238,7 +23236,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Nearshore, Geospatial</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -23258,48 +23256,50 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Hakai Geospatial</t>
         </is>
       </c>
       <c r="N203" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.0511576, 48.72717181], [-124.94565833, 48.72717181], [-124.94565833, 49.24536019], [-126.0511576, 49.24536019], [-126.0511576, 48.72717181]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.0, 49.0], [-119.5, 49.0], [-119.5, 54.34], [-124.0, 54.34], [-124.0, 49.0]]]}</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>other, seagrassCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>10.21966/8mpe-h081</t>
+          <t>10.21966/xp9x-m243</t>
         </is>
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUR4a1V0N1UxYTc2U3Q</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NTLT7n49Ox3SnVoy6nW</t>
         </is>
       </c>
       <c r="T203" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="U203" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="V203" t="inlineStr"/>
+          <t>2024-11-20</t>
+        </is>
+      </c>
+      <c r="V203" t="n">
+        <v>4</v>
+      </c>
       <c r="W203" t="n">
         <v>0</v>
       </c>
@@ -23320,12 +23320,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
+          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>ca-cioos_f25b00ba-ad63-42b3-8021-3fb6aa99baff</t>
+          <t>ca-cioos_c513de71-ac9d-43fa-b693-8f865de4b137</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -23335,12 +23335,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Fraser River Landslide Project - Sites of Concern 2024</t>
+          <t>Fraser River Landslide Project - 2022-2024 - Drone Data</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>document</t>
+          <t>dataset</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -23353,7 +23353,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -23381,12 +23381,12 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.0, 49.0], [-119.5, 49.0], [-119.5, 54.34], [-124.0, 54.34], [-124.0, 49.0]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.8, 49.29], [-121.2, 49.29], [-121.2, 52.28], [-122.8, 52.28], [-122.8, 49.29]]]}</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>[{'max': '2500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1500.0', 'min': '50.0'}]</t>
         </is>
       </c>
       <c r="Q204" t="inlineStr">
@@ -23396,26 +23396,26 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>10.21966/xp9x-m243</t>
+          <t>10.21966/qpe8-ay93</t>
         </is>
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NTLT7n49Ox3SnVoy6nW</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpurN_vwkhOgSJmgBh9</t>
         </is>
       </c>
       <c r="T204" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="U204" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="V204" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W204" t="n">
         <v>0</v>
@@ -23437,12 +23437,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
+          <t>e8414189-54c9-4311-874e-b97f9b7916ae</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>ca-cioos_c513de71-ac9d-43fa-b693-8f865de4b137</t>
+          <t>ca-cioos_48acba27-5e01-4b41-9a0e-f3fc8d809a13</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -23452,7 +23452,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Fraser River Landslide Project - 2022-2024 - Drone Data</t>
+          <t>MusselSeg: Semantic Segmentation for Rocky Intertidal Mussel Habitat</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -23470,12 +23470,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -23490,7 +23490,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Hakai Geospatial</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N205" t="n">
@@ -23498,42 +23498,40 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.8, 49.29], [-121.2, 49.29], [-121.2, 52.28], [-122.8, 52.28], [-122.8, 49.29]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-130.1, 51.59], [-120.4, 31.75], [-118.4, 33.38], [-124.3, 44.43], [-122.0, 49.35], [-126.2, 51.59], [-130.1, 51.59]]]}</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>[{'max': '1500.0', 'min': '50.0'}]</t>
+          <t>[{'max': '75.0', 'min': '15.0'}]</t>
         </is>
       </c>
       <c r="Q205" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>10.21966/qpe8-ay93</t>
+          <t>10.21966/fbv4-th96</t>
         </is>
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpurN_vwkhOgSJmgBh9</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DCH8GzsQKSM8xwJ8WdQFIZrtCaq2/-O26fyGiVXoF__M22UrP</t>
         </is>
       </c>
       <c r="T205" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="U205" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="V205" t="n">
-        <v>2</v>
-      </c>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr"/>
       <c r="W205" t="n">
         <v>0</v>
       </c>
@@ -23554,12 +23552,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>e8414189-54c9-4311-874e-b97f9b7916ae</t>
+          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>ca-cioos_48acba27-5e01-4b41-9a0e-f3fc8d809a13</t>
+          <t>ca-cioos_d4942b86-d362-40a3-9399-c124c4c263bd</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -23569,7 +23567,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>MusselSeg: Semantic Segmentation for Rocky Intertidal Mussel Habitat</t>
+          <t>Larval Dungeness crab abundance and size time series along the coast of British Columbia</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -23587,7 +23585,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Sentinels of Change</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -23615,40 +23613,42 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-130.1, 51.59], [-120.4, 31.75], [-118.4, 33.38], [-124.3, 44.43], [-122.0, 49.35], [-126.2, 51.59], [-130.1, 51.59]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.8, 48.3], [-123.2, 48.37], [-123.2, 48.65], [-123.0, 48.77], [-123.3, 49.01], [-122.9, 49.25], [-122.6, 49.4], [-123.2, 49.45], [-123.7, 49.54], [-124.5, 49.89], [-124.8, 50.09], [-126.5, 50.79], [-128.3, 52.31], [-130.4, 54.75], [-133.8, 54.36], [-132.9, 52.85], [-130.3, 51.48], [-128.1, 50.15], [-125.2, 48.62], [-123.8, 48.3]]]}</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>[{'max': '75.0', 'min': '15.0'}]</t>
+          <t>[{'max': '2.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q206" t="inlineStr">
         <is>
-          <t>other, invertebrateAbundanceAndDistribution</t>
+          <t>invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>10.21966/fbv4-th96</t>
+          <t>10.21966/36hp-7f40</t>
         </is>
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DCH8GzsQKSM8xwJ8WdQFIZrtCaq2/-O26fyGiVXoF__M22UrP</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/57FPdLIBPcb9BOLfIOW44RJVywN2/-N1KAki3SSBEw0aHCoSv</t>
         </is>
       </c>
       <c r="T206" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="U206" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="V206" t="inlineStr"/>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="V206" t="n">
+        <v>2</v>
+      </c>
       <c r="W206" t="n">
         <v>0</v>
       </c>
@@ -23669,12 +23669,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
+          <t>265e0ec8-1d85-4e73-b85d-371845dbd08f</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>ca-cioos_d4942b86-d362-40a3-9399-c124c4c263bd</t>
+          <t>ca-cioos_f762a307-6dfb-41a8-a56c-ecacfb075a0a</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -23684,7 +23684,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Larval Dungeness crab abundance and size time series along the coast of British Columbia</t>
+          <t>Denali Fault - 2024 - Airborne LiDAR Survey</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -23702,12 +23702,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Sentinels of Change</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -23730,42 +23730,40 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.8, 48.3], [-123.2, 48.37], [-123.2, 48.65], [-123.0, 48.77], [-123.3, 49.01], [-122.9, 49.25], [-122.6, 49.4], [-123.2, 49.45], [-123.7, 49.54], [-124.5, 49.89], [-124.8, 50.09], [-126.5, 50.79], [-128.3, 52.31], [-130.4, 54.75], [-133.8, 54.36], [-132.9, 52.85], [-130.3, 51.48], [-128.1, 50.15], [-125.2, 48.62], [-123.8, 48.3]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-141.3, 62.08], [-139.8, 61.49], [-137.7, 60.61], [-136.8, 60.1], [-136.4, 60.29], [-138.3, 61.12], [-140.1, 61.86], [-141.2, 62.19], [-141.3, 62.08]]]}</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>[{'max': '2.0', 'min': '0.0'}]</t>
+          <t>[{'max': '5000.0', 'min': '100.0'}]</t>
         </is>
       </c>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>10.21966/36hp-7f40</t>
+          <t>10.21966/wxph-tz51</t>
         </is>
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/57FPdLIBPcb9BOLfIOW44RJVywN2/-N1KAki3SSBEw0aHCoSv</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCKOQlOxJdTg_BFOoXb</t>
         </is>
       </c>
       <c r="T207" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="U207" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="V207" t="n">
-        <v>2</v>
-      </c>
+          <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr"/>
       <c r="W207" t="n">
         <v>0</v>
       </c>
@@ -23786,12 +23784,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>265e0ec8-1d85-4e73-b85d-371845dbd08f</t>
+          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>ca-cioos_f762a307-6dfb-41a8-a56c-ecacfb075a0a</t>
+          <t>ca-cioos_5185ac00-8148-4472-adfd-21741d8a10ce</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -23801,7 +23799,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Denali Fault - 2024 - Airborne LiDAR Survey</t>
+          <t>Sentinels of Change Sea Surface Temperature Time Series Data Along the British Columbia Coast</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -23819,12 +23817,12 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Sentinels of Change</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -23847,51 +23845,53 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-141.3, 62.08], [-139.8, 61.49], [-137.7, 60.61], [-136.8, 60.1], [-136.4, 60.29], [-138.3, 61.12], [-140.1, 61.86], [-141.2, 62.19], [-141.3, 62.08]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.6, 48.25], [-123.2, 48.37], [-123.3, 48.71], [-123.0, 48.8], [-123.3, 49.09], [-123.0, 49.1], [-122.4, 49.39], [-122.6, 49.56], [-123.6, 49.55], [-124.8, 50.1], [-125.8, 50.51], [-127.5, 51.15], [-128.6, 52.64], [-130.4, 54.77], [-133.4, 54.37], [-132.8, 52.99], [-130.8, 51.58], [-128.3, 50.21], [-126.5, 49.17], [-125.2, 48.63], [-124.3, 48.43], [-123.6, 48.25]]]}</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>[{'max': '5000.0', 'min': '100.0'}]</t>
+          <t>[{'max': '0.5', 'min': '0.5'}]</t>
         </is>
       </c>
       <c r="Q208" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>seaSurfaceTemperature</t>
         </is>
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>10.21966/wxph-tz51</t>
+          <t>10.21966/4kr2-jc55</t>
         </is>
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCKOQlOxJdTg_BFOoXb</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/57FPdLIBPcb9BOLfIOW44RJVywN2/-NH0r8ddHNhVJ5bXkyqR</t>
         </is>
       </c>
       <c r="T208" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="U208" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
-        </is>
-      </c>
-      <c r="V208" t="inlineStr"/>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="V208" t="n">
+        <v>2</v>
+      </c>
       <c r="W208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X208" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2024', 'total': 1}]</t>
         </is>
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'citations', 'id': '10.21966/36hp-7f40', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_d4942b86-d362-40a3-9399-c124c4c263bd'}]</t>
         </is>
       </c>
     </row>
@@ -23901,12 +23901,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
+          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>ca-cioos_5185ac00-8148-4472-adfd-21741d8a10ce</t>
+          <t>ca-cioos_7fd3ec6c-083a-4942-84b4-215e69492072</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -23916,7 +23916,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Sentinels of Change Sea Surface Temperature Time Series Data Along the British Columbia Coast</t>
+          <t>Phytoplankton Pigment Timeseries from High-Performance Liquid Chromatography for the Northern Salish Sea and Central Coast, BC, Canada (Research)</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -23934,7 +23934,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Sentinels of Change</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -23962,32 +23962,32 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.6, 48.25], [-123.2, 48.37], [-123.3, 48.71], [-123.0, 48.8], [-123.3, 49.09], [-123.0, 49.1], [-122.4, 49.39], [-122.6, 49.56], [-123.6, 49.55], [-124.8, 50.1], [-125.8, 50.51], [-127.5, 51.15], [-128.6, 52.64], [-130.4, 54.77], [-133.4, 54.37], [-132.8, 52.99], [-130.8, 51.58], [-128.3, 50.21], [-126.5, 49.17], [-125.2, 48.63], [-124.3, 48.43], [-123.6, 48.25]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>[{'max': '0.5', 'min': '0.5'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q209" t="inlineStr">
         <is>
-          <t>seaSurfaceTemperature</t>
+          <t>phytoplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>10.21966/4kr2-jc55</t>
+          <t>10.21966/bw2d-tg65</t>
         </is>
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/57FPdLIBPcb9BOLfIOW44RJVywN2/-NH0r8ddHNhVJ5bXkyqR</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-O25qzW3OpioeACGpRHl</t>
         </is>
       </c>
       <c r="T209" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="U209" t="inlineStr">
@@ -23999,16 +23999,16 @@
         <v>2</v>
       </c>
       <c r="W209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X209" t="inlineStr">
         <is>
-          <t>[{'year': '2024', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.21966/36hp-7f40', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_d4942b86-d362-40a3-9399-c124c4c263bd'}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -24018,12 +24018,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
+          <t>0781c19a-7efb-4680-92fd-8cd5faf0cfe4</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>ca-cioos_7fd3ec6c-083a-4942-84b4-215e69492072</t>
+          <t>ca-cioos_af344fb9-4901-470c-a441-41f11ee2ccd7</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -24033,7 +24033,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Phytoplankton Pigment Timeseries from High-Performance Liquid Chromatography for the Northern Salish Sea and Central Coast, BC, Canada (Research)</t>
+          <t>iTrack Oysters February 2023 Experiment - Environmental and Oyster Health Data</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -24051,12 +24051,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Wet Lab</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -24071,7 +24071,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N210" t="n">
@@ -24079,42 +24079,40 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q210" t="inlineStr">
         <is>
-          <t>phytoplanktonBiomassAndDiversity</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>10.21966/bw2d-tg65</t>
+          <t>10.21966/pvy6-nw38</t>
         </is>
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-O25qzW3OpioeACGpRHl</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-O0G3gSlISPfB-f0u3Zz</t>
         </is>
       </c>
       <c r="T210" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="U210" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="V210" t="n">
-        <v>2</v>
-      </c>
+          <t>2024-12-19</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr"/>
       <c r="W210" t="n">
         <v>0</v>
       </c>
@@ -24135,12 +24133,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>0781c19a-7efb-4680-92fd-8cd5faf0cfe4</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>ca-cioos_af344fb9-4901-470c-a441-41f11ee2ccd7</t>
+          <t>ca-cioos_9fafb4c8-e61f-4372-ac71-c1ddbe57d80c</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -24150,7 +24148,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>iTrack Oysters February 2023 Experiment - Environmental and Oyster Health Data</t>
+          <t>Data record does not exist anymore: Geomorphology - Calvert Island</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -24166,11 +24164,7 @@
       <c r="H211" t="b">
         <v>0</v>
       </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>Wet Lab</t>
-        </is>
-      </c>
+      <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
           <t>completed</t>
@@ -24188,7 +24182,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N211" t="n">
@@ -24196,53 +24190,41 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.2489013671875, 51.40605940499276], [-127.83142089843751, 51.40605940499276], [-127.83142089843751, 51.75934048406748], [-128.2489013671875, 51.75934048406748], [-128.2489013671875, 51.40605940499276]]]}</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q211" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
-        </is>
-      </c>
-      <c r="R211" t="inlineStr">
-        <is>
-          <t>10.21966/pvy6-nw38</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr"/>
       <c r="S211" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-O0G3gSlISPfB-f0u3Zz</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OFhFpUJDNDF0hlFiGUV</t>
         </is>
       </c>
       <c r="T211" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="U211" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
-        </is>
-      </c>
-      <c r="V211" t="inlineStr"/>
-      <c r="W211" t="n">
-        <v>0</v>
-      </c>
-      <c r="X211" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y211" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>2025-01-03</t>
+        </is>
+      </c>
+      <c r="V211" t="n">
+        <v>4</v>
+      </c>
+      <c r="W211" t="inlineStr"/>
+      <c r="X211" t="inlineStr"/>
+      <c r="Y211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -24250,12 +24232,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>ca-cioos_9fafb4c8-e61f-4372-ac71-c1ddbe57d80c</t>
+          <t>ca-cioos_d7ffd737-5725-4a56-9134-a9ad91c2734d</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -24265,7 +24247,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Data record does not exist anymore: Geomorphology - Calvert Island</t>
+          <t>Seton and Anderson Lake Multibeam Survey - 2024 - British Columbia</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -24281,7 +24263,11 @@
       <c r="H212" t="b">
         <v>0</v>
       </c>
-      <c r="I212" t="inlineStr"/>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Geospatial</t>
+        </is>
+      </c>
       <c r="J212" t="inlineStr">
         <is>
           <t>completed</t>
@@ -24307,12 +24293,12 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.2489013671875, 51.40605940499276], [-127.83142089843751, 51.40605940499276], [-127.83142089843751, 51.75934048406748], [-128.2489013671875, 51.75934048406748], [-128.2489013671875, 51.40605940499276]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.4, 50.62], [-122.0, 50.62], [-122.0, 50.75], [-122.4, 50.75], [-122.4, 50.62]]]}</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
+          <t>[{'max': '254.0', 'min': '61.0'}]</t>
         </is>
       </c>
       <c r="Q212" t="inlineStr">
@@ -24320,28 +24306,42 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R212" t="inlineStr"/>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>10.21966/zfxe-rd73</t>
+        </is>
+      </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OFhFpUJDNDF0hlFiGUV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCe-GBA4i93dk_I9uOR</t>
         </is>
       </c>
       <c r="T212" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="U212" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="V212" t="n">
-        <v>4</v>
-      </c>
-      <c r="W212" t="inlineStr"/>
-      <c r="X212" t="inlineStr"/>
-      <c r="Y212" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="W212" t="n">
+        <v>0</v>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -24349,12 +24349,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
+          <t>4a949e26-fe94-4f63-a3c6-a62e19301102</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>ca-cioos_d7ffd737-5725-4a56-9134-a9ad91c2734d</t>
+          <t>ca-cioos_35beb32e-8dc9-42ab-9630-2ae23e414026</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -24364,7 +24364,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Seton and Anderson Lake Multibeam Survey - 2024 - British Columbia</t>
+          <t>Rocky Subtidal Fish and Invertebrate Community Surveys from the Central Coast of BC</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -24382,12 +24382,12 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -24410,41 +24410,41 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.4, 50.62], [-122.0, 50.62], [-122.0, 50.75], [-122.4, 50.75], [-122.4, 50.62]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.7, 51.35], [-127.3, 51.35], [-127.3, 52.27], [-128.7, 52.27], [-128.7, 51.35]]]}</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>[{'max': '254.0', 'min': '61.0'}]</t>
+          <t>[{'max': '15.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q213" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>10.21966/zfxe-rd73</t>
+          <t>10.21966/jj9p-d309</t>
         </is>
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCe-GBA4i93dk_I9uOR</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtF5vh1GUMdwtJdYjoJ</t>
         </is>
       </c>
       <c r="T213" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="U213" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="V213" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W213" t="n">
         <v>0</v>
@@ -24466,12 +24466,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>4a949e26-fe94-4f63-a3c6-a62e19301102</t>
+          <t>7fa8cfec-e2e3-4459-9b9d-836335b9fcfa</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>ca-cioos_35beb32e-8dc9-42ab-9630-2ae23e414026</t>
+          <t>ca-cioos_00f42725-0a88-4d4f-87a9-4e359d2abff4</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -24481,7 +24481,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Rocky Subtidal Fish and Invertebrate Community Surveys from the Central Coast of BC</t>
+          <t>Knight Inlet Remotely Operated Vehicle Marine Habitat Survey</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -24499,12 +24499,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -24527,42 +24527,40 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.7, 51.35], [-127.3, 51.35], [-127.3, 52.27], [-128.7, 52.27], [-128.7, 51.35]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.0, 50.65], [-125.9, 50.65], [-125.9, 50.71], [-126.0, 50.71], [-126.0, 50.65]]]}</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>[{'max': '15.0', 'min': '0.0'}]</t>
+          <t>[{'max': '105.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q214" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>10.21966/jj9p-d309</t>
+          <t>10.21966/529y-sh57</t>
         </is>
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtF5vh1GUMdwtJdYjoJ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OG736nDr1-1b51V4ZIc</t>
         </is>
       </c>
       <c r="T214" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="U214" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
-        </is>
-      </c>
-      <c r="V214" t="n">
-        <v>1</v>
-      </c>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr"/>
       <c r="W214" t="n">
         <v>0</v>
       </c>
@@ -24583,12 +24581,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>7fa8cfec-e2e3-4459-9b9d-836335b9fcfa</t>
+          <t>5576c279-6d3a-4323-8104-0e1040d9906c</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>ca-cioos_00f42725-0a88-4d4f-87a9-4e359d2abff4</t>
+          <t>ca-cioos_314a0846-0fe9-4c2e-81e2-d2b24ac98b6e</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -24598,7 +24596,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Knight Inlet Remotely Operated Vehicle Marine Habitat Survey</t>
+          <t>Understory kelp biomass data from BC Central Coast</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -24616,12 +24614,12 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -24644,37 +24642,37 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.0, 50.65], [-125.9, 50.65], [-125.9, 50.71], [-126.0, 50.71], [-126.0, 50.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.7, 51.33], [-127.4, 51.33], [-127.4, 52.26], [-128.7, 52.26], [-128.7, 51.33]]]}</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>[{'max': '105.0', 'min': '0.0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q215" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>10.21966/529y-sh57</t>
+          <t>10.21966/wmsy-5g39</t>
         </is>
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OG736nDr1-1b51V4ZIc</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtGQFN6AV5bNminNtYH</t>
         </is>
       </c>
       <c r="T215" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="U215" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="V215" t="inlineStr"/>
@@ -24698,12 +24696,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>5576c279-6d3a-4323-8104-0e1040d9906c</t>
+          <t>cc016896-78d9-46e8-887d-6c1dd106c0e8</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>ca-cioos_314a0846-0fe9-4c2e-81e2-d2b24ac98b6e</t>
+          <t>ca-cioos_52d4f546-dfdf-4bf1-b1ad-f6ec6f2663c0</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -24713,7 +24711,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Understory kelp biomass data from BC Central Coast</t>
+          <t>Bute Inlet Geo-Hazards &amp; Ramsay West - 2024 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -24731,12 +24729,12 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -24759,40 +24757,42 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.7, 51.33], [-127.4, 51.33], [-127.4, 52.26], [-128.7, 52.26], [-128.7, 51.33]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.5, 50.23], [-124.1, 50.23], [-124.1, 51.73], [-125.5, 51.73], [-125.5, 50.23]]]}</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q216" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>10.21966/wmsy-5g39</t>
+          <t>10.21966/8yp1-7m94</t>
         </is>
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtGQFN6AV5bNminNtYH</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCKR1jead4rZb1ooVa6</t>
         </is>
       </c>
       <c r="T216" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="U216" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="V216" t="inlineStr"/>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="V216" t="n">
+        <v>1</v>
+      </c>
       <c r="W216" t="n">
         <v>0</v>
       </c>
@@ -24813,12 +24813,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>cc016896-78d9-46e8-887d-6c1dd106c0e8</t>
+          <t>046e5ef5-1480-4868-a65f-23171088bdb8</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>ca-cioos_52d4f546-dfdf-4bf1-b1ad-f6ec6f2663c0</t>
+          <t>ca-cioos_31e15496-e906-43f4-9120-2446ab6125b2</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -24828,7 +24828,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Bute Inlet Geo-Hazards &amp; Ramsay West - 2024 - Airborne Coastal Observatory</t>
+          <t>Elliot Creek Aerial Photo and LiDAR Survey</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -24846,7 +24846,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -24874,12 +24874,12 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.5, 50.23], [-124.1, 50.23], [-124.1, 51.73], [-125.5, 51.73], [-125.5, 50.23]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.8, 50.84], [-124.5, 50.84], [-124.5, 50.99], [-124.8, 50.99], [-124.8, 50.84]]]}</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>[{'max': '2500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2650.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q217" t="inlineStr">
@@ -24889,27 +24889,25 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>10.21966/8yp1-7m94</t>
+          <t>10.21966/g64t-ec45</t>
         </is>
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCKR1jead4rZb1ooVa6</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICfZ5e-2vhf5NUtDZS</t>
         </is>
       </c>
       <c r="T217" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="U217" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="V217" t="n">
-        <v>1</v>
-      </c>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr"/>
       <c r="W217" t="n">
         <v>0</v>
       </c>
@@ -24930,12 +24928,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>046e5ef5-1480-4868-a65f-23171088bdb8</t>
+          <t>8ce79018-75da-42f8-b7cd-195a412ab532</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>ca-cioos_31e15496-e906-43f4-9120-2446ab6125b2</t>
+          <t>ca-cioos_98807d0a-ba68-41e3-a2f5-e3248b459904</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -24945,7 +24943,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Elliot Creek Aerial Photo and LiDAR Survey</t>
+          <t>Place Glacier Aerial Photo and LiDAR Survey</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -24983,7 +24981,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Tula Foundation</t>
         </is>
       </c>
       <c r="N218" t="n">
@@ -24991,12 +24989,12 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.8, 50.84], [-124.5, 50.84], [-124.5, 50.99], [-124.8, 50.99], [-124.8, 50.84]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.7, 50.39], [-122.6, 50.39], [-122.6, 50.48], [-122.7, 50.48], [-122.7, 50.39]]]}</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>[{'max': '2650.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2587.0', 'min': '500.0'}]</t>
         </is>
       </c>
       <c r="Q218" t="inlineStr">
@@ -25006,12 +25004,12 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>10.21966/g64t-ec45</t>
+          <t>10.21966/0ydj-0t79</t>
         </is>
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICfZ5e-2vhf5NUtDZS</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICMGpnoARQcIltW087</t>
         </is>
       </c>
       <c r="T218" t="inlineStr">
@@ -25045,12 +25043,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>8ce79018-75da-42f8-b7cd-195a412ab532</t>
+          <t>83f387d2-f77e-4921-af15-e064d87ad01a</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>ca-cioos_98807d0a-ba68-41e3-a2f5-e3248b459904</t>
+          <t>ca-cioos_53730b70-be6f-4e24-8b9d-4a5e2c491121</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -25060,12 +25058,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Place Glacier Aerial Photo and LiDAR Survey</t>
+          <t>Cloud-Based LiDAR Application - ELVIZ - Place Glacier, Mt. Robson, and Elliot Creek, BC</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>service</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -25098,7 +25096,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Tula Foundation</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N219" t="n">
@@ -25106,12 +25104,12 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.7, 50.39], [-122.6, 50.39], [-122.6, 50.48], [-122.7, 50.48], [-122.7, 50.39]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.5, 50.34], [-118.7, 50.34], [-118.7, 53.28], [-124.5, 53.28], [-124.5, 50.34]]]}</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>[{'max': '2587.0', 'min': '500.0'}]</t>
+          <t>[{'max': '3954.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q219" t="inlineStr">
@@ -25121,25 +25119,27 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>10.21966/0ydj-0t79</t>
+          <t>10.21966/6x1v-1v62</t>
         </is>
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICMGpnoARQcIltW087</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OIMCEnEEW63IyHyYZOM</t>
         </is>
       </c>
       <c r="T219" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="U219" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="V219" t="inlineStr"/>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="V219" t="n">
+        <v>1</v>
+      </c>
       <c r="W219" t="n">
         <v>0</v>
       </c>
@@ -25160,12 +25160,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>83f387d2-f77e-4921-af15-e064d87ad01a</t>
+          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>ca-cioos_53730b70-be6f-4e24-8b9d-4a5e2c491121</t>
+          <t>ca-cioos_78818ed7-ec26-4004-afa1-137741ddda1e</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -25175,12 +25175,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Cloud-Based LiDAR Application - ELVIZ - Place Glacier, Mt. Robson, and Elliot Creek, BC</t>
+          <t>Calliarthron 2023 Experiment - Environmental Data</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>dataset</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -25193,7 +25193,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Wet Lab</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -25213,7 +25213,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="N220" t="n">
@@ -25221,37 +25221,37 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.5, 50.34], [-118.7, 50.34], [-118.7, 53.28], [-124.5, 53.28], [-124.5, 50.34]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>[{'max': '3954.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q220" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>10.21966/6x1v-1v62</t>
+          <t>10.21966/7nwn-bj60</t>
         </is>
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OIMCEnEEW63IyHyYZOM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-O6XAwxhj0r9Xs-V2QSA</t>
         </is>
       </c>
       <c r="T220" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="U220" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="V220" t="n">
@@ -25277,12 +25277,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
+          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>ca-cioos_78818ed7-ec26-4004-afa1-137741ddda1e</t>
+          <t>ca-cioos_87341cb3-f906-4fa5-973c-b6742aa0fbb5</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -25292,7 +25292,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Calliarthron 2023 Experiment - Environmental Data</t>
+          <t>Glacier and Ice Aerial Surveys in British Columbia - 2023-2024 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -25310,7 +25310,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Wet Lab</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -25330,7 +25330,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>University of British Columbia</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N221" t="n">
@@ -25338,27 +25338,27 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.9, 48.81], [-115.2, 48.81], [-115.2, 54.38], [-128.9, 54.38], [-128.9, 48.81]]]}</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '3954.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q221" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>10.21966/7nwn-bj60</t>
+          <t>10.21966/ks82-th39</t>
         </is>
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-O6XAwxhj0r9Xs-V2QSA</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OP2QaXeKeZ30lz51gEE</t>
         </is>
       </c>
       <c r="T221" t="inlineStr">
@@ -25368,10 +25368,12 @@
       </c>
       <c r="U221" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="V221" t="inlineStr"/>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="V221" t="n">
+        <v>2</v>
+      </c>
       <c r="W221" t="n">
         <v>0</v>
       </c>
@@ -25392,12 +25394,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
+          <t>6c99bd67-3be1-4818-bf01-dfa56e910db3</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>ca-cioos_87341cb3-f906-4fa5-973c-b6742aa0fbb5</t>
+          <t>ca-cioos_96e3dd9c-7863-44d5-95cd-a3d0a8653d83</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -25407,7 +25409,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Glacier and Ice Aerial Surveys in British Columbia - 2023-2024 - Hakai Airborne Coastal Observatory</t>
+          <t>Glacier and Ice Aerial Surveys in British Columbia - 2022 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -25425,7 +25427,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -25453,12 +25455,12 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.9, 48.81], [-115.2, 48.81], [-115.2, 54.38], [-128.9, 54.38], [-128.9, 48.81]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.8, 48.1], [-113.1, 48.1], [-113.1, 56.61], [-127.8, 56.61], [-127.8, 48.1]]]}</t>
         </is>
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>[{'max': '3954.0', 'min': '0.0'}]</t>
+          <t>[{'max': '4000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q222" t="inlineStr">
@@ -25468,12 +25470,12 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>10.21966/ks82-th39</t>
+          <t>10.21966/n3b4-d226</t>
         </is>
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OP2QaXeKeZ30lz51gEE</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NM0zdQjdjAMBZ4cN8ou</t>
         </is>
       </c>
       <c r="T222" t="inlineStr">
@@ -25483,18 +25485,18 @@
       </c>
       <c r="U222" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="V222" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W222" t="n">
         <v>0</v>
       </c>
       <c r="X222" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2025', 'total': 1}]</t>
         </is>
       </c>
       <c r="Y222" t="inlineStr">
@@ -25509,12 +25511,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>6c99bd67-3be1-4818-bf01-dfa56e910db3</t>
+          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>ca-cioos_96e3dd9c-7863-44d5-95cd-a3d0a8653d83</t>
+          <t>ca-cioos_47d8bdd4-c815-4e8d-8d75-53a9db4ae46a</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -25524,7 +25526,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Glacier and Ice Aerial Surveys in British Columbia - 2022 - Hakai Airborne Coastal Observatory</t>
+          <t>Glaciers in Western North America Mass Loss Geospatial Data (2021-2024)</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -25570,12 +25572,12 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.8, 48.1], [-113.1, 48.1], [-113.1, 56.61], [-127.8, 56.61], [-127.8, 48.1]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.3, 54.17], [-119.5, 55.38], [-112.5, 52.06], [-115.3, 47.05], [-125.9, 48.0], [-128.3, 51.41], [-127.3, 54.17]]]}</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>[{'max': '4000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2822.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q223" t="inlineStr">
@@ -25585,33 +25587,33 @@
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>10.21966/n3b4-d226</t>
+          <t>10.21966/p6jv-pe95</t>
         </is>
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NM0zdQjdjAMBZ4cN8ou</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OP86akjVj471Wit4O2y</t>
         </is>
       </c>
       <c r="T223" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="U223" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="V223" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W223" t="n">
         <v>0</v>
       </c>
       <c r="X223" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Y223" t="inlineStr">
@@ -25626,12 +25628,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
+          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>ca-cioos_47d8bdd4-c815-4e8d-8d75-53a9db4ae46a</t>
+          <t>ca-cioos_1d142201-cbbe-4c58-b2c2-1feeac112c51</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -25641,7 +25643,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Glaciers in Western North America Mass Loss Geospatial Data (2021-2024)</t>
+          <t>iTrack Oysters September 2023 Experiment - Environmental and Oyster Health Data</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -25659,7 +25661,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Wet Lab</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -25679,7 +25681,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N224" t="n">
@@ -25687,41 +25689,41 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.3, 54.17], [-119.5, 55.38], [-112.5, 52.06], [-115.3, 47.05], [-125.9, 48.0], [-128.3, 51.41], [-127.3, 54.17]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>[{'max': '2822.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q224" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>inorganicCarbon, other</t>
         </is>
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>10.21966/p6jv-pe95</t>
+          <t>10.21966/q1m4-pz94</t>
         </is>
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OP86akjVj471Wit4O2y</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-OMsFWHXIwEWiFjwQeEo</t>
         </is>
       </c>
       <c r="T224" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="U224" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="V224" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W224" t="n">
         <v>0</v>
@@ -25743,12 +25745,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
+          <t>da040f55-984d-490d-b917-a67856de4bac</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>ca-cioos_1d142201-cbbe-4c58-b2c2-1feeac112c51</t>
+          <t>ca-cioos_31ac855d-bf15-42d8-b20d-754638202c66</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -25758,7 +25760,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>iTrack Oysters September 2023 Experiment - Environmental and Oyster Health Data</t>
+          <t>Sea Stars 2024 Experiment - Environmental Data</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -25796,7 +25798,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N225" t="n">
@@ -25819,12 +25821,12 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>10.21966/q1m4-pz94</t>
+          <t>10.21966/jkf5-ss08</t>
         </is>
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-OMsFWHXIwEWiFjwQeEo</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-OIMW8OO0buhOm_kHuIz</t>
         </is>
       </c>
       <c r="T225" t="inlineStr">
@@ -25837,7 +25839,9 @@
           <t>2025-05-16</t>
         </is>
       </c>
-      <c r="V225" t="inlineStr"/>
+      <c r="V225" t="n">
+        <v>1</v>
+      </c>
       <c r="W225" t="n">
         <v>0</v>
       </c>
@@ -25858,12 +25862,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>da040f55-984d-490d-b917-a67856de4bac</t>
+          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>ca-cioos_31ac855d-bf15-42d8-b20d-754638202c66</t>
+          <t>ca-cioos_d959f8f3-6d20-42fe-94da-be49bcd3aeca</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -25873,7 +25877,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Sea Stars 2024 Experiment - Environmental Data</t>
+          <t>Eelgrass (Z. marina) extent at Gulf Islands National Park Reserve eelgrass monitoring sites (2024)</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -25891,7 +25895,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Wet Lab</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -25911,15 +25915,15 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Gulf Islands National Park Reserve</t>
         </is>
       </c>
       <c r="N226" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.4, 48.61], [-123.0, 48.61], [-123.0, 48.87], [-123.4, 48.87], [-123.4, 48.61]]]}</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -25929,30 +25933,32 @@
       </c>
       <c r="Q226" t="inlineStr">
         <is>
-          <t>inorganicCarbon, other</t>
+          <t>other, seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>10.21966/jkf5-ss08</t>
+          <t>10.21966/x3jm-p494</t>
         </is>
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-OIMW8OO0buhOm_kHuIz</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OUG8anVj4yBJDEHy6Wj</t>
         </is>
       </c>
       <c r="T226" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="U226" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="V226" t="inlineStr"/>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="V226" t="n">
+        <v>2</v>
+      </c>
       <c r="W226" t="n">
         <v>0</v>
       </c>
@@ -25973,12 +25979,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>ca-cioos_d959f8f3-6d20-42fe-94da-be49bcd3aeca</t>
+          <t>ca-cioos_39a83551-ab8e-45be-a564-cece4b229371</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -25988,7 +25994,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Eelgrass (Z. marina) extent at Gulf Islands National Park Reserve eelgrass monitoring sites (2024)</t>
+          <t>Zooplankton taxonomic abundance and biomass along the BC Coast</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -26006,12 +26012,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -26026,7 +26032,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Gulf Islands National Park Reserve</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N227" t="n">
@@ -26034,53 +26040,53 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.4, 48.61], [-123.0, 48.61], [-123.0, 48.87], [-123.4, 48.87], [-123.4, 48.61]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '350.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q227" t="inlineStr">
         <is>
-          <t>other, seagrassCoverAndComposition</t>
+          <t>zooplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>10.21966/x3jm-p494</t>
+          <t>10.21966/g7zf-1v08</t>
         </is>
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OUG8anVj4yBJDEHy6Wj</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-ODO1YbIGbR3Rd8hvLxT</t>
         </is>
       </c>
       <c r="T227" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="U227" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="V227" t="n">
+        <v>4</v>
+      </c>
+      <c r="W227" t="n">
         <v>2</v>
       </c>
-      <c r="W227" t="n">
-        <v>0</v>
-      </c>
       <c r="X227" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2025', 'total': 2}]</t>
         </is>
       </c>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'references', 'id': '10.21966/g7zf-1v08', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_39a83551-ab8e-45be-a564-cece4b229371'}, {'relationship': 'references', 'id': '10.21966/tcp2-mm86', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_dbb33efe-c207-4d9c-abef-2350595bf47a'}, {'relationship': 'citations', 'id': '10.21966/g7zf-1v08', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_39a83551-ab8e-45be-a564-cece4b229371'}, {'relationship': 'citations', 'id': '10.21966/kace-2d24', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_ba41d935-f293-447f-be3d-7098e569b431'}]</t>
         </is>
       </c>
     </row>
@@ -26090,12 +26096,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>ca-cioos_39a83551-ab8e-45be-a564-cece4b229371</t>
+          <t>ca-cioos_dbb33efe-c207-4d9c-abef-2350595bf47a</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -26105,7 +26111,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Zooplankton taxonomic abundance and biomass along the BC Coast</t>
+          <t>Size-fractionated zooplankton biomass and isotopes along the BC coast</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -26147,45 +26153,45 @@
         </is>
       </c>
       <c r="N228" t="n">
+        <v>1</v>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>[{'max': '350.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>zooplanktonBiomassAndDiversity</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>10.21966/tcp2-mm86</t>
+        </is>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/NZb1YZT9Xtbc9Cp9Jc3OtSLRffT2/-OQtxgedRzyaVsL4bWUx</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="V228" t="n">
         <v>2</v>
-      </c>
-      <c r="O228" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
-        </is>
-      </c>
-      <c r="P228" t="inlineStr">
-        <is>
-          <t>[{'max': '350.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q228" t="inlineStr">
-        <is>
-          <t>zooplanktonBiomassAndDiversity</t>
-        </is>
-      </c>
-      <c r="R228" t="inlineStr">
-        <is>
-          <t>10.21966/g7zf-1v08</t>
-        </is>
-      </c>
-      <c r="S228" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-ODO1YbIGbR3Rd8hvLxT</t>
-        </is>
-      </c>
-      <c r="T228" t="inlineStr">
-        <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="U228" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="V228" t="n">
-        <v>3</v>
       </c>
       <c r="W228" t="n">
         <v>2</v>
@@ -26197,7 +26203,7 @@
       </c>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>[{'relationship': 'references', 'id': '10.21966/g7zf-1v08', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_39a83551-ab8e-45be-a564-cece4b229371'}, {'relationship': 'references', 'id': '10.21966/tcp2-mm86', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_dbb33efe-c207-4d9c-abef-2350595bf47a'}, {'relationship': 'citations', 'id': '10.21966/g7zf-1v08', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_39a83551-ab8e-45be-a564-cece4b229371'}, {'relationship': 'citations', 'id': '10.21966/kace-2d24', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_ba41d935-f293-447f-be3d-7098e569b431'}]</t>
+          <t>[{'relationship': 'citations', 'id': '10.21966/kace-2d24', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_ba41d935-f293-447f-be3d-7098e569b431'}, {'relationship': 'citations', 'id': '10.21966/g7zf-1v08', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_39a83551-ab8e-45be-a564-cece4b229371'}]</t>
         </is>
       </c>
     </row>
@@ -26207,12 +26213,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
+          <t>328b062b-3af6-4149-b90f-a85b99dc40eb</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>ca-cioos_dbb33efe-c207-4d9c-abef-2350595bf47a</t>
+          <t>ca-cioos_34a20547-cb60-4ecf-901b-f4ca52eae451</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -26222,7 +26228,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Size-fractionated zooplankton biomass and isotopes along the BC coast</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -26240,12 +26246,12 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -26268,53 +26274,53 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.4], [-127.9, 51.4], [-127.9, 52.09], [-128.5, 52.09], [-128.5, 51.4]]]}</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>[{'max': '350.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q229" t="inlineStr">
         <is>
-          <t>zooplanktonBiomassAndDiversity</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>10.21966/tcp2-mm86</t>
+          <t>10.21966/w08z-zk15</t>
         </is>
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/NZb1YZT9Xtbc9Cp9Jc3OtSLRffT2/-OQtxgedRzyaVsL4bWUx</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8sPFZem68YnizN7L7l</t>
         </is>
       </c>
       <c r="T229" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="U229" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="V229" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W229" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X229" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 2}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.21966/kace-2d24', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_ba41d935-f293-447f-be3d-7098e569b431'}, {'relationship': 'citations', 'id': '10.21966/g7zf-1v08', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_39a83551-ab8e-45be-a564-cece4b229371'}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -26324,12 +26330,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>328b062b-3af6-4149-b90f-a85b99dc40eb</t>
+          <t>439d703a-2132-4dbd-8d39-a4cacdb8f81d</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>ca-cioos_34a20547-cb60-4ecf-901b-f4ca52eae451</t>
+          <t>ca-cioos_e8343aa0-dbea-4267-9f78-662bec08d4bc</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -26339,7 +26345,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), Central Coast, British Columbia, Canada</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020-2022), Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -26357,7 +26363,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
+          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -26385,7 +26391,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.4], [-127.9, 51.4], [-127.9, 52.09], [-128.5, 52.09], [-128.5, 51.4]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 52.15], [-128.5, 52.23], [-128.2, 52.05], [-128.0, 51.71], [-128.0, 51.63], [-128.2, 51.62], [-128.4, 51.8], [-128.6, 51.89], [-128.6, 51.89], [-128.6, 52.15]]]}</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -26400,12 +26406,12 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>10.21966/w08z-zk15</t>
+          <t>10.21966/kqzp-f639</t>
         </is>
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8sPFZem68YnizN7L7l</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-NbzgAmVWcvz-_SOMA0E</t>
         </is>
       </c>
       <c r="T230" t="inlineStr">
@@ -26415,12 +26421,10 @@
       </c>
       <c r="U230" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="V230" t="n">
-        <v>1</v>
-      </c>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr"/>
       <c r="W230" t="n">
         <v>0</v>
       </c>
@@ -26441,12 +26445,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>439d703a-2132-4dbd-8d39-a4cacdb8f81d</t>
+          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>ca-cioos_e8343aa0-dbea-4267-9f78-662bec08d4bc</t>
+          <t>ca-cioos_f7a867ce-0f18-43f6-8148-775235d800b6</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -26456,7 +26460,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020-2022), Central Coast, British Columbia, Canada</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2023), Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -26474,7 +26478,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -26502,7 +26506,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 52.15], [-128.5, 52.23], [-128.2, 52.05], [-128.0, 51.71], [-128.0, 51.63], [-128.2, 51.62], [-128.4, 51.8], [-128.6, 51.89], [-128.6, 51.89], [-128.6, 52.15]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.64], [-128.1, 51.64], [-128.1, 52.19], [-128.6, 52.19], [-128.6, 51.64]]]}</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
@@ -26517,12 +26521,12 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>10.21966/kqzp-f639</t>
+          <t>10.21966/qs1b-g693</t>
         </is>
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-NbzgAmVWcvz-_SOMA0E</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-O8Dvx_fnz1WMY_Wetch</t>
         </is>
       </c>
       <c r="T231" t="inlineStr">
@@ -26532,10 +26536,12 @@
       </c>
       <c r="U231" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="V231" t="inlineStr"/>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="V231" t="n">
+        <v>3</v>
+      </c>
       <c r="W231" t="n">
         <v>0</v>
       </c>
@@ -26556,12 +26562,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
+          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>ca-cioos_f7a867ce-0f18-43f6-8148-775235d800b6</t>
+          <t>ca-cioos_291b98a4-d868-462c-852a-d6cf79ecf6ce</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -26571,7 +26577,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2023), Central Coast, British Columbia, Canada</t>
+          <t>Time series of surface kelp canopy area derived from remotely piloted aerial systems (RPAS, or drone) surveys, Central Coast, British Columbia</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -26589,12 +26595,12 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
+          <t>Nearshore, Geospatial</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -26609,7 +26615,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Tula Foundation</t>
         </is>
       </c>
       <c r="N232" t="n">
@@ -26617,7 +26623,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.64], [-128.1, 51.64], [-128.1, 52.19], [-128.6, 52.19], [-128.6, 51.64]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.65], [-128.1, 51.65], [-128.1, 52.09], [-128.4, 52.09], [-128.4, 51.65]]]}</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
@@ -26632,26 +26638,26 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>10.21966/qs1b-g693</t>
+          <t>10.21966/9cbv-ra30</t>
         </is>
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-O8Dvx_fnz1WMY_Wetch</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OVIwXhdGT9n7FV0wmyz</t>
         </is>
       </c>
       <c r="T232" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="U232" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="V232" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W232" t="n">
         <v>0</v>
@@ -26673,12 +26679,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
+          <t>44bdc298-1329-400a-bc02-4d35d251865d</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>ca-cioos_291b98a4-d868-462c-852a-d6cf79ecf6ce</t>
+          <t>ca-cioos_012164c6-28dd-4078-b702-f0c2ce63d548</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -26688,7 +26694,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Time series of surface kelp canopy area derived from remotely piloted aerial systems (RPAS, or drone) surveys, Central Coast, British Columbia</t>
+          <t>Biodiversity and Oceanographic data from the False Creek Bioblitz, 2022</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -26706,12 +26712,12 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Nearshore, Geospatial</t>
+          <t>Genomics, Nearshore, Oceanography</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -26726,50 +26732,48 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Tula Foundation</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N233" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.65], [-128.1, 51.65], [-128.1, 52.09], [-128.4, 52.09], [-128.4, 51.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.2, 49.27], [-123.1, 49.27], [-123.1, 49.28], [-123.2, 49.28], [-123.2, 49.27]]]}</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q233" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>invertebrateAbundanceAndDistribution, marineTurtlesBirdsMammalsAbundanceAndDistribution, fishAbundanceAndDistribution, seaSurfaceTemperature, subSurfaceTemperature, other, microbeBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>10.21966/9cbv-ra30</t>
+          <t>10.21966/8sgn-jg38</t>
         </is>
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OVIwXhdGT9n7FV0wmyz</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-Nd0YqVrleM4mMLlJDSU</t>
         </is>
       </c>
       <c r="T233" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="U233" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="V233" t="n">
-        <v>2</v>
-      </c>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr"/>
       <c r="W233" t="n">
         <v>0</v>
       </c>
@@ -26790,12 +26794,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>44bdc298-1329-400a-bc02-4d35d251865d</t>
+          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>ca-cioos_012164c6-28dd-4078-b702-f0c2ce63d548</t>
+          <t>ca-cioos_7e9c97a3-4bf1-4852-81b6-d74cedf2c94c</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -26805,7 +26809,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Biodiversity and Oceanographic data from the False Creek Bioblitz, 2022</t>
+          <t>Environmental DNA survey of Calvert Island, British Columbia, 2021</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -26823,7 +26827,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>Genomics, Nearshore, Oceanography</t>
+          <t>Genomics</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -26847,44 +26851,46 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.2, 49.27], [-123.1, 49.27], [-123.1, 49.28], [-123.2, 49.28], [-123.2, 49.27]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.31], [-127.3, 51.31], [-127.3, 52.05], [-128.6, 52.05], [-128.6, 51.31]]]}</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '60.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q234" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution, marineTurtlesBirdsMammalsAbundanceAndDistribution, fishAbundanceAndDistribution, seaSurfaceTemperature, subSurfaceTemperature, other, microbeBiomassAndDiversity</t>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>10.21966/8sgn-jg38</t>
+          <t>10.21966/vdyq-r660</t>
         </is>
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-Nd0YqVrleM4mMLlJDSU</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-ORCQx4QHUuJ1NV1SEig</t>
         </is>
       </c>
       <c r="T234" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="U234" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="V234" t="inlineStr"/>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="V234" t="n">
+        <v>2</v>
+      </c>
       <c r="W234" t="n">
         <v>0</v>
       </c>
@@ -26905,12 +26911,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
+          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>ca-cioos_7e9c97a3-4bf1-4852-81b6-d74cedf2c94c</t>
+          <t>ca-cioos_9a018fe0-8bd1-41d1-af8d-079960b71473</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -26920,7 +26926,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Environmental DNA survey of Calvert Island, British Columbia, 2021</t>
+          <t>Data from: Prentice et al. 2025. Vibrio pectenicida strain FHCF-3 is a causative agent of sea star wasting disease</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -26938,7 +26944,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Genomics</t>
+          <t>Genomics, Nearshore</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -26962,45 +26968,45 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.31], [-127.3, 51.31], [-127.3, 52.05], [-128.6, 52.05], [-128.6, 51.31]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 47.91], [-122.3, 47.91], [-122.3, 51.82], [-128.5, 51.82], [-128.5, 47.91]]]}</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>[{'max': '60.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q235" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
+          <t>microbeBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>10.21966/vdyq-r660</t>
+          <t>10.21966/4dvn-5y90</t>
         </is>
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-ORCQx4QHUuJ1NV1SEig</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/24mf0TP0vkh6bmNOOA3ynoTFPNJ2/-OX0Xm6VoYH22oc68Jfp</t>
         </is>
       </c>
       <c r="T235" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="U235" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="V235" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W235" t="n">
         <v>0</v>
@@ -27022,12 +27028,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
+          <t>0272fd06-6ac8-48cd-80c9-b6e05f15be0f</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>ca-cioos_9a018fe0-8bd1-41d1-af8d-079960b71473</t>
+          <t>ca-cioos_132cecdf-de8a-4b17-b610-0e2b3a343812</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -27037,7 +27043,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Data from: Prentice et al. 2025. Vibrio pectenicida strain FHCF-3 is a causative agent of sea star wasting disease</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), North Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -27055,7 +27061,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Genomics, Nearshore</t>
+          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -27079,11 +27085,11 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 47.91], [-122.3, 47.91], [-122.3, 51.82], [-128.5, 51.82], [-128.5, 47.91]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-131.0, 53.74], [-130.4, 53.74], [-130.4, 54.46], [-131.0, 54.46], [-131.0, 53.74]]]}</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
@@ -27093,27 +27099,27 @@
       </c>
       <c r="Q236" t="inlineStr">
         <is>
-          <t>microbeBiomassAndDiversity</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>10.21966/4dvn-5y90</t>
+          <t>10.21966/m93t-4181</t>
         </is>
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/24mf0TP0vkh6bmNOOA3ynoTFPNJ2/-OX0Xm6VoYH22oc68Jfp</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8sPEiAvbPxw16A-L6I</t>
         </is>
       </c>
       <c r="T236" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="U236" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="V236" t="n">
@@ -27139,12 +27145,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>0272fd06-6ac8-48cd-80c9-b6e05f15be0f</t>
+          <t>b01f58f7-1518-4829-aff6-ac4a8f2c0616</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>ca-cioos_132cecdf-de8a-4b17-b610-0e2b3a343812</t>
+          <t>ca-cioos_f815a700-c943-4d6f-afeb-a4854ad10cfc</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -27154,7 +27160,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), North Coast, British Columbia, Canada</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), North Vancouver Island, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -27200,7 +27206,7 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-131.0, 53.74], [-130.4, 53.74], [-130.4, 54.46], [-131.0, 54.46], [-131.0, 53.74]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.6, 50.35], [-124.8, 50.35], [-124.8, 50.7], [-126.6, 50.7], [-126.6, 50.35]]]}</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
@@ -27215,12 +27221,12 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>10.21966/m93t-4181</t>
+          <t>10.21966/ntdg-e790</t>
         </is>
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8sPEiAvbPxw16A-L6I</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8raBb8T2xZJ-oRzesS</t>
         </is>
       </c>
       <c r="T237" t="inlineStr">
@@ -27256,12 +27262,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>b01f58f7-1518-4829-aff6-ac4a8f2c0616</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>ca-cioos_f815a700-c943-4d6f-afeb-a4854ad10cfc</t>
+          <t>ca-cioos_5b4cbe9f-8f2e-414c-80ff-741372891fe9</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -27271,7 +27277,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), North Vancouver Island, British Columbia, Canada</t>
+          <t>Gitga'at Territory Coastal Monitoring and Mapping - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -27281,7 +27287,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>CC-BY-4.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H238" t="b">
@@ -27289,7 +27295,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -27317,53 +27323,53 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.6, 50.35], [-124.8, 50.35], [-124.8, 50.7], [-126.6, 50.7], [-126.6, 50.35]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.8, 52.92], [-129.1, 52.92], [-129.1, 53.67], [-129.8, 53.67], [-129.8, 52.92]]]}</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '475.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q238" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>10.21966/ntdg-e790</t>
+          <t>10.21966/0xex-r023</t>
         </is>
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8raBb8T2xZJ-oRzesS</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OdPFhWCkXwvqjCqum30</t>
         </is>
       </c>
       <c r="T238" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="U238" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="V238" t="n">
+        <v>3</v>
+      </c>
+      <c r="W238" t="n">
         <v>1</v>
       </c>
-      <c r="W238" t="n">
-        <v>0</v>
-      </c>
       <c r="X238" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2025', 'total': 1}]</t>
         </is>
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'references', 'id': '10.21966/2aap-hn61', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_b5f0f854-efe1-4132-808d-074244d813e1'}, {'relationship': 'citations', 'id': '10.21966/2aap-hn61', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_b5f0f854-efe1-4132-808d-074244d813e1'}]</t>
         </is>
       </c>
     </row>
@@ -27373,12 +27379,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>0074861a-39f2-42c1-ae71-abef4f78fd78</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>ca-cioos_5b4cbe9f-8f2e-414c-80ff-741372891fe9</t>
+          <t>ca-cioos_b5f0f854-efe1-4132-808d-074244d813e1</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -27388,7 +27394,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Gitga'at Territory Coastal Monitoring and Mapping - Airborne Coastal Observatory</t>
+          <t>Gitga'at Territory Coastal Mapping Project</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -27406,12 +27412,12 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -27434,12 +27440,12 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.8, 52.92], [-129.1, 52.92], [-129.1, 53.67], [-129.8, 53.67], [-129.8, 52.92]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.6, 53.18], [-129.0, 53.18], [-129.0, 53.68], [-129.6, 53.68], [-129.6, 53.18]]]}</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>[{'max': '475.0', 'min': '0.0'}]</t>
+          <t>[{'max': '150.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q239" t="inlineStr">
@@ -27449,12 +27455,12 @@
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>10.21966/0xex-r023</t>
+          <t>10.21966/2aap-hn61</t>
         </is>
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OdPFhWCkXwvqjCqum30</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Oa5tvTh2mXFQbI3SkzK</t>
         </is>
       </c>
       <c r="T239" t="inlineStr">
@@ -27464,23 +27470,23 @@
       </c>
       <c r="U239" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="V239" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W239" t="n">
         <v>1</v>
       </c>
       <c r="X239" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 1}]</t>
+          <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>[{'relationship': 'references', 'id': '10.21966/2aap-hn61', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_b5f0f854-efe1-4132-808d-074244d813e1'}, {'relationship': 'citations', 'id': '10.21966/2aap-hn61', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_b5f0f854-efe1-4132-808d-074244d813e1'}]</t>
+          <t>[{'relationship': 'references', 'id': '10.21966/0xex-r023', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_5b4cbe9f-8f2e-414c-80ff-741372891fe9'}, {'relationship': 'citations', 'id': '10.21966/0xex-r023', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_5b4cbe9f-8f2e-414c-80ff-741372891fe9'}]</t>
         </is>
       </c>
     </row>
@@ -27490,12 +27496,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>0074861a-39f2-42c1-ae71-abef4f78fd78</t>
+          <t>5fc21b4d-2dfa-4908-8aaf-90a82509324a</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>ca-cioos_b5f0f854-efe1-4132-808d-074244d813e1</t>
+          <t>ca-cioos_35900174-c64a-493e-9a7e-390ac7e997e4</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -27505,7 +27511,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Gitga'at Territory Coastal Mapping Project</t>
+          <t>Bowhead Whale Drone Data Collection - Cumberland Sound - Nunavut</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -27515,7 +27521,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="H240" t="b">
@@ -27528,7 +27534,7 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -27551,12 +27557,12 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.6, 53.18], [-129.0, 53.18], [-129.0, 53.68], [-129.6, 53.68], [-129.6, 53.18]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-68.21, 64.72], [-64.14, 64.72], [-64.14, 66.48], [-68.21, 66.48], [-68.21, 64.72]]]}</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>[{'max': '150.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q240" t="inlineStr">
@@ -27566,22 +27572,22 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>10.21966/2aap-hn61</t>
+          <t>10.21966/fv0q-q364</t>
         </is>
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Oa5tvTh2mXFQbI3SkzK</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OeY_smu3pJj8TBE9ivK</t>
         </is>
       </c>
       <c r="T240" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="U240" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="V240" t="n">
@@ -27597,7 +27603,7 @@
       </c>
       <c r="Y240" t="inlineStr">
         <is>
-          <t>[{'relationship': 'references', 'id': '10.21966/0xex-r023', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_5b4cbe9f-8f2e-414c-80ff-741372891fe9'}, {'relationship': 'citations', 'id': '10.21966/0xex-r023', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_5b4cbe9f-8f2e-414c-80ff-741372891fe9'}]</t>
+          <t>[{'relationship': 'citations', 'id': '10.48321/d16d6f987c', 'type': 'dois', 'status_code': 200, 'url': 'https://dmphub.uc3prd.cdlib.net/dmps/10.48321/D16D6F987C'}]</t>
         </is>
       </c>
     </row>
@@ -27607,12 +27613,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>5fc21b4d-2dfa-4908-8aaf-90a82509324a</t>
+          <t>dbfc5189-f657-4034-af7f-cc358042047d</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>ca-cioos_35900174-c64a-493e-9a7e-390ac7e997e4</t>
+          <t>ca-cioos_78686602-1aa9-4246-8a24-915471fe4255</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -27622,7 +27628,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Bowhead Whale Drone Data Collection - Cumberland Sound - Nunavut</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2025), North Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -27640,7 +27646,7 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -27668,7 +27674,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-68.21, 64.72], [-64.14, 64.72], [-64.14, 66.48], [-68.21, 66.48], [-68.21, 64.72]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.8, 52.69], [-129.0, 52.69], [-129.0, 53.14], [-129.8, 53.14], [-129.8, 52.69]]]}</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
@@ -27678,17 +27684,17 @@
       </c>
       <c r="Q241" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>10.21966/fv0q-q364</t>
+          <t>10.21966/nwg7-fe05</t>
         </is>
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OeY_smu3pJj8TBE9ivK</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OeItznXpvEFI_t-jsCl</t>
         </is>
       </c>
       <c r="T241" t="inlineStr">
@@ -27698,23 +27704,21 @@
       </c>
       <c r="U241" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="V241" t="n">
-        <v>1</v>
-      </c>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="V241" t="inlineStr"/>
       <c r="W241" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X241" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Y241" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.48321/d16d6f987c', 'type': 'dois', 'status_code': 200, 'url': 'https://dmphub.uc3prd.cdlib.net/dmps/10.48321/D16D6F987C'}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -27724,12 +27728,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>dbfc5189-f657-4034-af7f-cc358042047d</t>
+          <t>9eda1bfc-0d13-4e1d-9542-b9a7cce16991</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>ca-cioos_78686602-1aa9-4246-8a24-915471fe4255</t>
+          <t>ca-cioos_c544ef5b-967d-46b2-bbcf-395116b50e7d</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -27739,7 +27743,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2025), North Coast, British Columbia, Canada</t>
+          <t>Mystery Creek Aerial Photo and LiDAR Survey - 2025 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -27757,7 +27761,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -27785,32 +27789,32 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.8, 52.69], [-129.0, 52.69], [-129.0, 53.14], [-129.8, 53.14], [-129.8, 52.69]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.9, 50.21], [-122.8, 50.21], [-122.8, 50.25], [-122.9, 50.25], [-122.9, 50.21]]]}</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '1690.0', 'min': '378.0'}]</t>
         </is>
       </c>
       <c r="Q242" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>10.21966/nwg7-fe05</t>
+          <t>10.21966/02qp-4945</t>
         </is>
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OeItznXpvEFI_t-jsCl</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/FfIFMI0sx4beFpYCFD9liFIEiMt1/-OeTbb0MbfTCH-YFCNGG</t>
         </is>
       </c>
       <c r="T242" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="U242" t="inlineStr">
@@ -27839,12 +27843,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>9eda1bfc-0d13-4e1d-9542-b9a7cce16991</t>
+          <t>37440dfd-53f8-462b-a544-b6c8d39c44cd</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>ca-cioos_c544ef5b-967d-46b2-bbcf-395116b50e7d</t>
+          <t>ca-cioos_43bad5e5-0484-4c11-80a5-c844245f940e</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -27854,7 +27858,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Mystery Creek Aerial Photo and LiDAR Survey - 2025 - Airborne Coastal Observatory</t>
+          <t>Farwell Canyon Airborne Surveys - 2024 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -27900,12 +27904,12 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.9, 50.21], [-122.8, 50.21], [-122.8, 50.25], [-122.9, 50.25], [-122.9, 50.21]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.6, 51.86], [-122.5, 51.81], [-122.4, 51.74], [-122.4, 51.73], [-122.5, 51.8], [-122.7, 51.83], [-122.6, 51.86]]]}</t>
         </is>
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>[{'max': '1690.0', 'min': '378.0'}]</t>
+          <t>[{'max': '1347.62', 'min': '345.9'}]</t>
         </is>
       </c>
       <c r="Q243" t="inlineStr">
@@ -27915,22 +27919,22 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>10.21966/02qp-4945</t>
+          <t>10.21966/dtt0-s264</t>
         </is>
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/FfIFMI0sx4beFpYCFD9liFIEiMt1/-OeTbb0MbfTCH-YFCNGG</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/FfIFMI0sx4beFpYCFD9liFIEiMt1/-OgDkxI9LmB0KWXvOsZe</t>
         </is>
       </c>
       <c r="T243" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="U243" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="V243" t="inlineStr"/>
@@ -27954,12 +27958,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>37440dfd-53f8-462b-a544-b6c8d39c44cd</t>
+          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>ca-cioos_43bad5e5-0484-4c11-80a5-c844245f940e</t>
+          <t>ca-cioos_7cafde4f-bdd5-4b95-a41d-7939ddcf08c6</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -27969,7 +27973,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Farwell Canyon Airborne Surveys - 2024 - Airborne Coastal Observatory</t>
+          <t>Time series of quarterly kelp canopy extent from Landsat 5, 7, 8, and 9 since 1985</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -27987,12 +27991,12 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -28015,40 +28019,42 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.6, 51.86], [-122.5, 51.81], [-122.4, 51.74], [-122.4, 51.73], [-122.5, 51.8], [-122.7, 51.83], [-122.6, 51.86]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-130.5, 54.75], [-133.5, 54.36], [-133.0, 53.09], [-126.0, 48.92], [-123.6, 48.28], [-123.2, 48.8], [-123.8, 49.61], [-127.6, 51.04], [-128.4, 52.4], [-130.4, 54.24], [-130.5, 54.75]]]}</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>[{'max': '1347.62', 'min': '345.9'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>10.21966/dtt0-s264</t>
+          <t>10.21966/xc7x-9207</t>
         </is>
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/FfIFMI0sx4beFpYCFD9liFIEiMt1/-OgDkxI9LmB0KWXvOsZe</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OZGbDlZ5dgF0dD-ceZ7</t>
         </is>
       </c>
       <c r="T244" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="U244" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
-      <c r="V244" t="inlineStr"/>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="V244" t="n">
+        <v>2</v>
+      </c>
       <c r="W244" t="n">
         <v>0</v>
       </c>
@@ -28069,12 +28075,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
+          <t>3d082072-1ee8-4005-8bba-f9ec795ad5ab</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>ca-cioos_7cafde4f-bdd5-4b95-a41d-7939ddcf08c6</t>
+          <t>ca-cioos_cfa4ad65-ee12-47c0-9527-206a0f8d92ae</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -28084,7 +28090,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Time series of quarterly kelp canopy extent from Landsat 5, 7, 8, and 9 since 1985</t>
+          <t>Hakai Institute Drone Data Index</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -28102,7 +28108,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -28130,42 +28136,40 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-130.5, 54.75], [-133.5, 54.36], [-133.0, 53.09], [-126.0, 48.92], [-123.6, 48.28], [-123.2, 48.8], [-123.8, 49.61], [-127.6, 51.04], [-128.4, 52.4], [-130.4, 54.24], [-130.5, 54.75]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-134.1, 42.65], [-59.42, 42.65], [-59.42, 67.53], [-134.1, 67.53], [-134.1, 42.65]]]}</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q245" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>10.21966/xc7x-9207</t>
+          <t>10.21966/0r8b-t282</t>
         </is>
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OZGbDlZ5dgF0dD-ceZ7</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCdraToZivfj6ZZ8TqZ</t>
         </is>
       </c>
       <c r="T245" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="U245" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="V245" t="n">
-        <v>2</v>
-      </c>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr"/>
       <c r="W245" t="n">
         <v>0</v>
       </c>
@@ -28186,12 +28190,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>3d082072-1ee8-4005-8bba-f9ec795ad5ab</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>ca-cioos_cfa4ad65-ee12-47c0-9527-206a0f8d92ae</t>
+          <t>ca-cioos_a924b31b-9882-4abe-8d8e-e875dbbbec82</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -28201,7 +28205,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Hakai Institute Drone Data Index</t>
+          <t>Surface Seawater and Marine Boundary Layer CO2 Time Series from the Bute Inlet Ocean Observing Station (BIOOS) Buoy, Bute Inlet, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -28219,7 +28223,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -28237,63 +28241,47 @@
           <t>dataset</t>
         </is>
       </c>
-      <c r="M246" t="inlineStr">
-        <is>
-          <t>Hakai Institute</t>
-        </is>
-      </c>
+      <c r="M246" t="inlineStr"/>
       <c r="N246" t="n">
         <v>1</v>
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-134.1, 42.65], [-59.42, 42.65], [-59.42, 67.53], [-134.1, 67.53], [-134.1, 42.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976]]]}</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q246" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R246" t="inlineStr">
-        <is>
-          <t>10.21966/0r8b-t282</t>
-        </is>
-      </c>
+          <t>inorganicCarbon, oxygen, seaSurfaceSalinity, seaSurfaceTemperature</t>
+        </is>
+      </c>
+      <c r="R246" t="inlineStr"/>
       <c r="S246" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCdraToZivfj6ZZ8TqZ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-OlwZ9MM8a9VqCYIJo4W</t>
         </is>
       </c>
       <c r="T246" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="U246" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="V246" t="inlineStr"/>
-      <c r="W246" t="n">
-        <v>0</v>
-      </c>
-      <c r="X246" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y246" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="V246" t="n">
+        <v>4</v>
+      </c>
+      <c r="W246" t="inlineStr"/>
+      <c r="X246" t="inlineStr"/>
+      <c r="Y246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -28301,12 +28289,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>0894f661-f9cb-48cb-a0b4-8a001eb69420</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>ca-cioos_a924b31b-9882-4abe-8d8e-e875dbbbec82</t>
+          <t>ca-cioos_bfefcdf9-c922-4e4f-a958-aa6da739d3cd</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -28316,7 +28304,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Surface Seawater and Marine Boundary Layer CO2 Time Series from the Bute Inlet Ocean Observing Station (BIOOS) Buoy, Bute Inlet, BC, Canada (Provisional)</t>
+          <t>Surface Seawater and Marine Boundary Layer CO2 Time Series from the Bute Inlet Ocean Observing Station (BIOOS) Buoy, Bute Inlet, BC, Canada (Research)</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -28352,7 +28340,11 @@
           <t>dataset</t>
         </is>
       </c>
-      <c r="M247" t="inlineStr"/>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
       <c r="N247" t="n">
         <v>1</v>
       </c>
@@ -28368,13 +28360,17 @@
       </c>
       <c r="Q247" t="inlineStr">
         <is>
-          <t>inorganicCarbon, oxygen, seaSurfaceSalinity, seaSurfaceTemperature</t>
-        </is>
-      </c>
-      <c r="R247" t="inlineStr"/>
+          <t>oxygen, inorganicCarbon, particulateMatter, phytoplanktonBiomassAndDiversity, seaSurfaceSalinity, seaSurfaceTemperature</t>
+        </is>
+      </c>
+      <c r="R247" t="inlineStr">
+        <is>
+          <t>10.21966/4jvz-bv44</t>
+        </is>
+      </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-OlwZ9MM8a9VqCYIJo4W</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-OOYvTmfsWUPdHkDTTFS</t>
         </is>
       </c>
       <c r="T247" t="inlineStr">
@@ -28384,15 +28380,23 @@
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="V247" t="n">
-        <v>4</v>
-      </c>
-      <c r="W247" t="inlineStr"/>
-      <c r="X247" t="inlineStr"/>
-      <c r="Y247" t="inlineStr"/>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr"/>
+      <c r="W247" t="n">
+        <v>0</v>
+      </c>
+      <c r="X247" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -28400,12 +28404,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>0894f661-f9cb-48cb-a0b4-8a001eb69420</t>
+          <t>e788c2f6-c842-4240-bab4-54a323d62174</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>ca-cioos_bfefcdf9-c922-4e4f-a958-aa6da739d3cd</t>
+          <t>ca-cioos_984e6b72-15d0-4742-bb2d-9ac13b14383a</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -28415,7 +28419,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Surface Seawater and Marine Boundary Layer CO2 Time Series from the Bute Inlet Ocean Observing Station (BIOOS) Buoy, Bute Inlet, BC, Canada (Research)</t>
+          <t>Stream Temperature Observations for Three Streams Near Gold River</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -28433,12 +28437,12 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -28461,7 +28465,7 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.7, 49.96], [-125.9, 49.93], [-126.0, 49.56], [-126.7, 49.73], [-126.7, 49.96]]]}</t>
         </is>
       </c>
       <c r="P248" t="inlineStr">
@@ -28471,27 +28475,27 @@
       </c>
       <c r="Q248" t="inlineStr">
         <is>
-          <t>oxygen, inorganicCarbon, particulateMatter, phytoplanktonBiomassAndDiversity, seaSurfaceSalinity, seaSurfaceTemperature</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>10.21966/4jvz-bv44</t>
+          <t>10.21966/cqrt-sk09</t>
         </is>
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-OOYvTmfsWUPdHkDTTFS</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DvuBcQQuVHdxmYEF4yDNBDj30lu1/-Oj8Fegu6V858hz57O8z</t>
         </is>
       </c>
       <c r="T248" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="V248" t="inlineStr"/>
@@ -28515,12 +28519,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>e788c2f6-c842-4240-bab4-54a323d62174</t>
+          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>ca-cioos_984e6b72-15d0-4742-bb2d-9ac13b14383a</t>
+          <t>ca-cioos_84820f31-b6db-479c-a47e-f22f2899b4d2</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -28530,7 +28534,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Stream Temperature Observations for Three Streams Near Gold River</t>
+          <t>Biogeochemical Sampling of 28 Streams on Vancouver Island</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -28576,7 +28580,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.7, 49.96], [-125.9, 49.93], [-126.0, 49.56], [-126.7, 49.73], [-126.7, 49.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 50.65], [-127.9, 50.71], [-123.6, 48.43], [-124.0, 48.36], [-127.3, 49.77], [-128.4, 50.65]]]}</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
@@ -28591,36 +28595,38 @@
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>10.21966/cqrt-sk09</t>
+          <t>10.21966/chc3-rj93</t>
         </is>
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DvuBcQQuVHdxmYEF4yDNBDj30lu1/-Oj8Fegu6V858hz57O8z</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DvuBcQQuVHdxmYEF4yDNBDj30lu1/-OnCm7wniBlFr2gSXQhf</t>
         </is>
       </c>
       <c r="T249" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="U249" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="V249" t="inlineStr"/>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="V249" t="n">
+        <v>3</v>
+      </c>
       <c r="W249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X249" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
       <c r="Y249" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'citations', 'id': '10.21966/cqrt-sk09', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_984e6b72-15d0-4742-bb2d-9ac13b14383a'}]</t>
         </is>
       </c>
     </row>
@@ -28630,12 +28636,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
+          <t>63f6c693-7c22-49cc-ad7d-9aa1774a5972</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>ca-cioos_84820f31-b6db-479c-a47e-f22f2899b4d2</t>
+          <t>ca-cioos_d7b34963-67bc-404b-bdd1-b41cc750bdaa</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -28645,7 +28651,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Biogeochemical Sampling of 28 Streams on Vancouver Island</t>
+          <t>Fraser River Airborne Surveys - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -28663,7 +28669,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -28691,12 +28697,12 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 50.65], [-127.9, 50.71], [-123.6, 48.43], [-124.0, 48.36], [-127.3, 49.77], [-128.4, 50.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-121.5, 49.51], [-121.3, 49.53], [-121.4, 49.95], [-121.5, 50.28], [-121.7, 50.52], [-121.8, 50.66], [-121.8, 50.76], [-121.8, 51.01], [-122.1, 51.32], [-122.3, 51.79], [-122.1, 52.11], [-122.3, 52.37], [-122.3, 52.51], [-122.6, 52.49], [-122.4, 51.96], [-122.5, 51.83], [-122.4, 51.49], [-122.3, 51.18], [-121.9, 50.95], [-121.9, 50.62], [-121.8, 50.53], [-121.7, 50.17], [-121.6, 49.89], [-121.5, 49.63], [-121.5, 49.51]]]}</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '850.0', 'min': '400.0'}]</t>
         </is>
       </c>
       <c r="Q250" t="inlineStr">
@@ -28706,38 +28712,38 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>10.21966/chc3-rj93</t>
+          <t>10.21966/f9m6-qg12</t>
         </is>
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DvuBcQQuVHdxmYEF4yDNBDj30lu1/-OnCm7wniBlFr2gSXQhf</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MibW0TZpoaJ4Ih_2ev7</t>
         </is>
       </c>
       <c r="T250" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="U250" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="V250" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X250" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Y250" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.21966/cqrt-sk09', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_984e6b72-15d0-4742-bb2d-9ac13b14383a'}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -28747,12 +28753,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>63f6c693-7c22-49cc-ad7d-9aa1774a5972</t>
+          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>ca-cioos_d7b34963-67bc-404b-bdd1-b41cc750bdaa</t>
+          <t>ca-cioos_1efbadd2-e735-48cc-9498-e3a5a88e48a6</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -28762,7 +28768,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Fraser River Airborne Surveys - 2020 - Airborne Coastal Observatory</t>
+          <t>Seawater Carbon Dioxide (CO2) Content from the SuperCO2 System in the Pacific Ecosystem Autonomous Research Laboratory, Bamfield Marine Sciences Centre, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -28780,12 +28786,12 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -28804,44 +28810,46 @@
         </is>
       </c>
       <c r="N251" t="n">
+        <v>2</v>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359]]]}</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>[{'max': '0', 'min': '0'}]</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>inorganicCarbon, seaSurfaceSalinity, seaSurfaceTemperature</t>
+        </is>
+      </c>
+      <c r="R251" t="inlineStr">
+        <is>
+          <t>10.21966/a0v4-x512</t>
+        </is>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-Olwvch3kCplJcz3CCeR</t>
+        </is>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="V251" t="n">
         <v>1</v>
       </c>
-      <c r="O251" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-121.5, 49.51], [-121.3, 49.53], [-121.4, 49.95], [-121.5, 50.28], [-121.7, 50.52], [-121.8, 50.66], [-121.8, 50.76], [-121.8, 51.01], [-122.1, 51.32], [-122.3, 51.79], [-122.1, 52.11], [-122.3, 52.37], [-122.3, 52.51], [-122.6, 52.49], [-122.4, 51.96], [-122.5, 51.83], [-122.4, 51.49], [-122.3, 51.18], [-121.9, 50.95], [-121.9, 50.62], [-121.8, 50.53], [-121.7, 50.17], [-121.6, 49.89], [-121.5, 49.63], [-121.5, 49.51]]]}</t>
-        </is>
-      </c>
-      <c r="P251" t="inlineStr">
-        <is>
-          <t>[{'max': '850.0', 'min': '400.0'}]</t>
-        </is>
-      </c>
-      <c r="Q251" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R251" t="inlineStr">
-        <is>
-          <t>10.21966/f9m6-qg12</t>
-        </is>
-      </c>
-      <c r="S251" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MibW0TZpoaJ4Ih_2ev7</t>
-        </is>
-      </c>
-      <c r="T251" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="U251" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="V251" t="inlineStr"/>
       <c r="W251" t="n">
         <v>0</v>
       </c>
@@ -28862,12 +28870,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
+          <t>7b1120bc-4a2c-432c-9e54-879d66751a59</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>ca-cioos_1efbadd2-e735-48cc-9498-e3a5a88e48a6</t>
+          <t>ca-cioos_b2b18171-35b6-4345-b81b-497a90c2e7c5</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -28877,7 +28885,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Seawater Carbon Dioxide (CO2) Content from the SuperCO2 System in the Pacific Ecosystem Autonomous Research Laboratory, Bamfield Marine Sciences Centre, BC, Canada (Provisional)</t>
+          <t>Seagrass fish and macroinvertebrate swaths BC Central Coast</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -28895,7 +28903,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -28919,31 +28927,31 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 52.09], [-128.5, 52.04], [-128.5, 51.97], [-128.5, 51.93], [-128.5, 51.9], [-128.4, 51.88], [-128.3, 51.86], [-128.3, 51.83], [-128.2, 51.63], [-127.9, 51.62], [-127.8, 51.77], [-127.8, 51.83], [-127.9, 51.99], [-128.4, 52.09]]]}</t>
         </is>
       </c>
       <c r="P252" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '10.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q252" t="inlineStr">
         <is>
-          <t>inorganicCarbon, seaSurfaceSalinity, seaSurfaceTemperature</t>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>10.21966/a0v4-x512</t>
+          <t>10.21966/NMNG-SF35</t>
         </is>
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-Olwvch3kCplJcz3CCeR</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/lJHlH9nm20QQOPuk217xLlxWbNv1/-NPt7327bul36pby-Odi</t>
         </is>
       </c>
       <c r="T252" t="inlineStr">
@@ -28953,12 +28961,10 @@
       </c>
       <c r="U252" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="V252" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr"/>
       <c r="W252" t="n">
         <v>0</v>
       </c>
@@ -28979,12 +28985,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>7b1120bc-4a2c-432c-9e54-879d66751a59</t>
+          <t>49374495-400f-4acc-aac6-d7d0b7cae297</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>ca-cioos_b2b18171-35b6-4345-b81b-497a90c2e7c5</t>
+          <t>ca-cioos_bafcd0eb-8249-471b-b93b-0797cfeea287</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -28994,7 +29000,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Seagrass fish and macroinvertebrate swaths BC Central Coast</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020), Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -29012,12 +29018,12 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
@@ -29040,37 +29046,37 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 52.09], [-128.5, 52.04], [-128.5, 51.97], [-128.5, 51.93], [-128.5, 51.9], [-128.4, 51.88], [-128.3, 51.86], [-128.3, 51.83], [-128.2, 51.63], [-127.9, 51.62], [-127.8, 51.77], [-127.8, 51.83], [-127.9, 51.99], [-128.4, 52.09]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.64], [-128.1, 51.64], [-128.1, 52.01], [-128.5, 52.01], [-128.5, 51.64]]]}</t>
         </is>
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>[{'max': '10.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
+          <t>macroalgalCanopyCoverAndComposition, other</t>
         </is>
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>10.21966/NMNG-SF35</t>
+          <t>10.21966/20ym-8826</t>
         </is>
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/lJHlH9nm20QQOPuk217xLlxWbNv1/-NPt7327bul36pby-Odi</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Miha19AtLQ2u1uo0b_q</t>
         </is>
       </c>
       <c r="T253" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="U253" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="V253" t="inlineStr"/>
@@ -29094,12 +29100,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>49374495-400f-4acc-aac6-d7d0b7cae297</t>
+          <t>613ba2f9-b21d-445f-8eaa-f42950c9350b</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>ca-cioos_bafcd0eb-8249-471b-b93b-0797cfeea287</t>
+          <t>ca-cioos_ba41d935-f293-447f-be3d-7098e569b431</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -29109,7 +29115,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020), Central Coast, British Columbia, Canada</t>
+          <t>Water Property Measurements from Conductivity-Temperature-Depth Profiles, BC, Canada (Research)</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -29127,12 +29133,12 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
+          <t>Oceanography, Nearshore, Watersheds, Juvenile Salmon Program</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -29151,41 +29157,41 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.64], [-128.1, 51.64], [-128.1, 52.01], [-128.5, 52.01], [-128.5, 51.64]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '700.0', 'min': '1.0'}]</t>
         </is>
       </c>
       <c r="Q254" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition, other</t>
+          <t>oxygen, subSurfaceSalinity, subSurfaceTemperature</t>
         </is>
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>10.21966/20ym-8826</t>
+          <t>10.21966/kace-2d24</t>
         </is>
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Miha19AtLQ2u1uo0b_q</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MX35qgX-BrwJDdeJKe1</t>
         </is>
       </c>
       <c r="T254" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="U254" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="V254" t="inlineStr"/>
@@ -29209,12 +29215,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>613ba2f9-b21d-445f-8eaa-f42950c9350b</t>
+          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>ca-cioos_ba41d935-f293-447f-be3d-7098e569b431</t>
+          <t>ca-cioos_fb5c9e1e-a911-46b7-8c1d-e34215a105ed</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -29224,7 +29230,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Water Property Measurements from Conductivity-Temperature-Depth Profiles, BC, Canada (Research)</t>
+          <t>Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 Analyzer located at Bamfield Marine Sciences Centre, Bamfield, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -29242,7 +29248,7 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>Oceanography, Nearshore, Watersheds, Juvenile Salmon Program</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -29266,31 +29272,31 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.13535, 48.83515]}</t>
         </is>
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>[{'max': '700.0', 'min': '1.0'}]</t>
+          <t>[{'max': '20.0', 'min': '20.0'}]</t>
         </is>
       </c>
       <c r="Q255" t="inlineStr">
         <is>
-          <t>oxygen, subSurfaceSalinity, subSurfaceTemperature</t>
+          <t>seaSurfaceTemperature, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
         </is>
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>10.21966/kace-2d24</t>
+          <t>10.21966/65d8-k051</t>
         </is>
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MX35qgX-BrwJDdeJKe1</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-NdH-jgHZQzKrYdb2nw_</t>
         </is>
       </c>
       <c r="T255" t="inlineStr">
@@ -29300,10 +29306,12 @@
       </c>
       <c r="U255" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="V255" t="inlineStr"/>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="V255" t="n">
+        <v>1</v>
+      </c>
       <c r="W255" t="n">
         <v>0</v>
       </c>
@@ -29324,12 +29332,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>ca-cioos_fb5c9e1e-a911-46b7-8c1d-e34215a105ed</t>
+          <t>ca-cioos_91107fce-93a4-4bc9-bce4-e7d9e1cf02a0</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -29339,7 +29347,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 Analyzer located at Bamfield Marine Sciences Centre, Bamfield, BC, Canada (Provisional)</t>
+          <t>Sentinel 3A and 3B Chlorophyll and Suspended Matter Concentrations for Coastal British Columbia and Southeast Alaska, 8-Day Average (Research)</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -29385,41 +29393,41 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.13535, 48.83515]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-139.0, 47.0], [-121.5, 47.0], [-121.5, 59.5], [-139.0, 59.5], [-139.0, 47.0]]]}</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>[{'max': '20.0', 'min': '20.0'}]</t>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
-          <t>seaSurfaceTemperature, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
+          <t>phytoplanktonBiomassAndDiversity, particulateMatter, other</t>
         </is>
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>10.21966/65d8-k051</t>
+          <t>10.21966/175j-8k96</t>
         </is>
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-NdH-jgHZQzKrYdb2nw_</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-Nueis-TZEnz_78f8PYf</t>
         </is>
       </c>
       <c r="T256" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="U256" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="V256" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W256" t="n">
         <v>0</v>
@@ -29441,12 +29449,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>b7b923ed-b3fa-48b3-878d-40a3797046bc</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>ca-cioos_91107fce-93a4-4bc9-bce4-e7d9e1cf02a0</t>
+          <t>ca-cioos_f7538807-4d49-4ed8-ad36-836c0e71428a</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -29456,7 +29464,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Sentinel 3A and 3B Chlorophyll and Suspended Matter Concentrations for Coastal British Columbia and Southeast Alaska, 8-Day Average (Research)</t>
+          <t>3m Digital Elevation Model - Calvert Island - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -29474,12 +29482,12 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -29498,57 +29506,55 @@
         </is>
       </c>
       <c r="N257" t="n">
+        <v>2</v>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.16482, 51.408116], [-127.868831, 51.408116], [-127.868831, 51.734994], [-128.16482, 51.734994], [-128.16482, 51.408116]]]}</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R257" t="inlineStr">
+        <is>
+          <t>10.21966/RZVW-4A72</t>
+        </is>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW13R3BBSGRER2ZkYnM</t>
+        </is>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr"/>
+      <c r="W257" t="n">
         <v>1</v>
       </c>
-      <c r="O257" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-139.0, 47.0], [-121.5, 47.0], [-121.5, 59.5], [-139.0, 59.5], [-139.0, 47.0]]]}</t>
-        </is>
-      </c>
-      <c r="P257" t="inlineStr">
-        <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q257" t="inlineStr">
-        <is>
-          <t>phytoplanktonBiomassAndDiversity, particulateMatter, other</t>
-        </is>
-      </c>
-      <c r="R257" t="inlineStr">
-        <is>
-          <t>10.21966/175j-8k96</t>
-        </is>
-      </c>
-      <c r="S257" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-Nueis-TZEnz_78f8PYf</t>
-        </is>
-      </c>
-      <c r="T257" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="U257" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="V257" t="n">
-        <v>4</v>
-      </c>
-      <c r="W257" t="n">
-        <v>0</v>
-      </c>
       <c r="X257" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
       <c r="Y257" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}]</t>
         </is>
       </c>
     </row>
@@ -29558,12 +29564,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>b7b923ed-b3fa-48b3-878d-40a3797046bc</t>
+          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>ca-cioos_f7538807-4d49-4ed8-ad36-836c0e71428a</t>
+          <t>ca-cioos_33c8ce77-0674-4933-a305-01a25d253f70</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -29573,7 +29579,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>3m Digital Elevation Model - Calvert Island - British Columbia - Canada</t>
+          <t>Sea star microbiome data from 16S amplicon sequencing associated with rocky intertidal sites on Calvert and Quadra Islands</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -29591,7 +29597,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Nearshore, Genomics</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -29619,51 +29625,53 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.16482, 51.408116], [-127.868831, 51.408116], [-127.868831, 51.734994], [-128.16482, 51.734994], [-128.16482, 51.408116]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.3, 49.87], [-124.8, 49.87], [-124.8, 51.75], [-128.3, 51.75], [-128.3, 49.87]]]}</t>
         </is>
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q258" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>invertebrateAbundanceAndDistribution, microbeBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>10.21966/RZVW-4A72</t>
+          <t>10.21966/0xvh-1318</t>
         </is>
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW13R3BBSGRER2ZkYnM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/4TvAwNKXC7PkAi0TEZsZbbAzXfi1/-Oo1MBmr8fW1fputdBh6</t>
         </is>
       </c>
       <c r="T258" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="U258" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="V258" t="inlineStr"/>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="V258" t="n">
+        <v>2</v>
+      </c>
       <c r="W258" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X258" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Y258" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -29673,12 +29681,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
+          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>ca-cioos_33c8ce77-0674-4933-a305-01a25d253f70</t>
+          <t>ca-cioos_a8671db6-81cc-4c92-b681-58595fe66182</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -29688,7 +29696,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Sea star microbiome data from 16S amplicon sequencing associated with rocky intertidal sites on Calvert and Quadra Islands</t>
+          <t>Water Property Measurements from the Bute Inlet Ocean Observing Station (BIOOS) Wirewalker, Bute Inlet, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -29706,12 +29714,12 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>Nearshore, Genomics</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -29730,45 +29738,45 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.3, 49.87], [-124.8, 49.87], [-124.8, 51.75], [-128.3, 51.75], [-128.3, 49.87]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-124.9009, 50.5744]}</t>
         </is>
       </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '250.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q259" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution, microbeBiomassAndDiversity</t>
+          <t>subSurfaceTemperature, subSurfaceSalinity, oxygen, phytoplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>10.21966/0xvh-1318</t>
+          <t>10.21966/3q5j-n957</t>
         </is>
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/4TvAwNKXC7PkAi0TEZsZbbAzXfi1/-Oo1MBmr8fW1fputdBh6</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-OqDQ7wqqJtwSgUoAN1g</t>
         </is>
       </c>
       <c r="T259" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="U259" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="V259" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W259" t="n">
         <v>0</v>
@@ -29790,12 +29798,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
+          <t>227eb965-1892-4bad-8ded-dd2e1d68fdf6</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>ca-cioos_a8671db6-81cc-4c92-b681-58595fe66182</t>
+          <t>ca-cioos_08d3e779-2f44-4ce3-82cb-c7b763f72175</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -29805,7 +29813,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Water Property Measurements from the Bute Inlet Ocean Observing Station (BIOOS) Wirewalker, Bute Inlet, BC, Canada (Provisional)</t>
+          <t>DNA metabarcoding data from Autonomous Reef Monitoring Structures (ARMS) deployed around Calvert Island British Columbia</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -29823,12 +29831,12 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore, Genomics</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
@@ -29847,46 +29855,44 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-124.9009, 50.5744]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.61], [-127.8, 51.61], [-127.8, 51.9], [-128.4, 51.9], [-128.4, 51.61]]]}</t>
         </is>
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>[{'max': '250.0', 'min': '0.0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q260" t="inlineStr">
         <is>
-          <t>subSurfaceTemperature, subSurfaceSalinity, oxygen, phytoplanktonBiomassAndDiversity</t>
+          <t>invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>10.21966/3q5j-n957</t>
+          <t>10.21966/kmc2-5r12</t>
         </is>
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-OqDQ7wqqJtwSgUoAN1g</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-ORSLLie2O-FFN8cPV1e</t>
         </is>
       </c>
       <c r="T260" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="U260" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="V260" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="V260" t="inlineStr"/>
       <c r="W260" t="n">
         <v>0</v>
       </c>
@@ -29907,12 +29913,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>227eb965-1892-4bad-8ded-dd2e1d68fdf6</t>
+          <t>0cef18ab-cea6-4522-baba-1bcd73a30646</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>ca-cioos_08d3e779-2f44-4ce3-82cb-c7b763f72175</t>
+          <t>ca-cioos_66fbb7f5-3644-471a-95ee-f8d3758e888b</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -29922,7 +29928,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>DNA metabarcoding data from Autonomous Reef Monitoring Structures (ARMS) deployed around Calvert Island British Columbia</t>
+          <t>Mount Robson Aerial Photo and LiDAR Survey</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -29940,7 +29946,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>Nearshore, Genomics</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -29960,45 +29966,41 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Tula Foundation</t>
         </is>
       </c>
       <c r="N261" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.61], [-127.8, 51.61], [-127.8, 51.9], [-128.4, 51.9], [-128.4, 51.61]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-119.3, 53.03], [-118.8, 53.03], [-118.8, 53.26], [-119.3, 53.26], [-119.3, 53.03]]]}</t>
         </is>
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '3954.0', 'min': '800.0'}]</t>
         </is>
       </c>
       <c r="Q261" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>10.21966/kmc2-5r12</t>
+          <t>10.21966/w9n0-kn30</t>
         </is>
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-ORSLLie2O-FFN8cPV1e</t>
-        </is>
-      </c>
-      <c r="T261" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICbtZXkj6anGvgB3Qi</t>
+        </is>
+      </c>
+      <c r="T261" t="inlineStr"/>
       <c r="U261" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="V261" t="inlineStr"/>
@@ -30011,117 +30013,6 @@
         </is>
       </c>
       <c r="Y261" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="n">
-        <v>260</v>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>0cef18ab-cea6-4522-baba-1bcd73a30646</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>ca-cioos_66fbb7f5-3644-471a-95ee-f8d3758e888b</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>Hakai Institute</t>
-        </is>
-      </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>Mount Robson Aerial Photo and LiDAR Survey</t>
-        </is>
-      </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>dataset</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>CC-BY-4.0</t>
-        </is>
-      </c>
-      <c r="H262" t="b">
-        <v>0</v>
-      </c>
-      <c r="I262" t="inlineStr">
-        <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
-        </is>
-      </c>
-      <c r="J262" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="L262" t="inlineStr">
-        <is>
-          <t>dataset</t>
-        </is>
-      </c>
-      <c r="M262" t="inlineStr">
-        <is>
-          <t>Tula Foundation</t>
-        </is>
-      </c>
-      <c r="N262" t="n">
-        <v>1</v>
-      </c>
-      <c r="O262" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-119.3, 53.03], [-118.8, 53.03], [-118.8, 53.26], [-119.3, 53.26], [-119.3, 53.03]]]}</t>
-        </is>
-      </c>
-      <c r="P262" t="inlineStr">
-        <is>
-          <t>[{'max': '3954.0', 'min': '800.0'}]</t>
-        </is>
-      </c>
-      <c r="Q262" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R262" t="inlineStr">
-        <is>
-          <t>10.21966/w9n0-kn30</t>
-        </is>
-      </c>
-      <c r="S262" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICbtZXkj6anGvgB3Qi</t>
-        </is>
-      </c>
-      <c r="T262" t="inlineStr"/>
-      <c r="U262" t="inlineStr">
-        <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="V262" t="inlineStr"/>
-      <c r="W262" t="n">
-        <v>0</v>
-      </c>
-      <c r="X262" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y262" t="inlineStr">
         <is>
           <t>[]</t>
         </is>

--- a/main/catalog_summary.xlsx
+++ b/main/catalog_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y261"/>
+  <dimension ref="A1:Y262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ca-cioos_ab901b46-43f6-4044-b0c3-b5fd825622f4</t>
+          <t>ca-cioos_af65bf72-27af-4747-8911-ab05591762ac</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>World View 2 Imagery - Coverage of three regions of the BC Central Coast - Summer 2014, 2015, &amp; 2016</t>
+          <t>Kelp forest communities along an otter gradient</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>underDevelopment</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Simon Fraser University</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1911,12 +1911,12 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.61145019531247, 51.61801654877371], [-127.91931152343746, 51.61801654877371], [-127.91931152343746, 52.11325243469631], [-128.61145019531247, 52.11325243469631], [-128.61145019531247, 51.61801654877371]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.770751953125, 51.33404377878941], [-127.74902343749999, 51.33404377878941], [-127.74902343749999, 52.19077237113535], [-128.770751953125, 52.19077237113535], [-128.770751953125, 51.33404377878941]]]}</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '50.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1924,14 +1924,10 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>10.21966/nmds-rx42</t>
-        </is>
-      </c>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXp1R01BNWFYV0RkUEY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXlMbjJYUlpvZFpITks</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -1941,25 +1937,15 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>3</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1967,12 +1953,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ca-cioos_af65bf72-27af-4747-8911-ab05591762ac</t>
+          <t>ca-cioos_ab901b46-43f6-4044-b0c3-b5fd825622f4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1982,7 +1968,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kelp forest communities along an otter gradient</t>
+          <t>World View 2 Imagery - Coverage of three regions of the BC Central Coast - Summer 2014, 2015, &amp; 2016</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2000,12 +1986,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>underDevelopment</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2020,7 +2006,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Simon Fraser University</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -2028,12 +2014,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.770751953125, 51.33404377878941], [-127.74902343749999, 51.33404377878941], [-127.74902343749999, 52.19077237113535], [-128.770751953125, 52.19077237113535], [-128.770751953125, 51.33404377878941]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.61145019531247, 51.61801654877371], [-127.91931152343746, 51.61801654877371], [-127.91931152343746, 52.11325243469631], [-128.61145019531247, 52.11325243469631], [-128.61145019531247, 51.61801654877371]]]}</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>[{'max': '50.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2041,10 +2027,14 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>10.21966/nmds-rx42</t>
+        </is>
+      </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXlMbjJYUlpvZFpITks</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXp1R01BNWFYV0RkUEY</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -2054,15 +2044,25 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>5</v>
-      </c>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
+          <t>ca-cioos_6ebe47c3-6d59-4cb2-a7ba-111698445d8d</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
+          <t>Bald eagles as vectors of marine nutrients – Central Coast Islands (100 Islands study area) – May – July 2017</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>100 Islands</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6627,61 +6627,49 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N56" t="n">
+        <v>2</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.58323147, 51.38160352], [-127.80979387, 51.38160352], [-127.80979387, 52.09997599], [-128.58323147, 52.09997599], [-128.58323147, 51.38160352]]]}</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>other, nutrients</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUxkcndoNFQ4T2xyZWI</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>2022-01-24</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="V56" t="n">
         <v>1</v>
       </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>other, inorganicCarbon</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>10.21966/zxzr-e472</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>2022-01-24</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="n">
-        <v>0</v>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6689,12 +6677,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ca-cioos_6ebe47c3-6d59-4cb2-a7ba-111698445d8d</t>
+          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -6704,7 +6692,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bald eagles as vectors of marine nutrients – Central Coast Islands (100 Islands study area) – May – July 2017</t>
+          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6722,7 +6710,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>100 Islands</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6742,15 +6730,15 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.58323147, 51.38160352], [-127.80979387, 51.38160352], [-127.80979387, 52.09997599], [-128.58323147, 52.09997599], [-128.58323147, 51.38160352]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6760,13 +6748,17 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>other, nutrients</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr"/>
+          <t>other, inorganicCarbon</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>10.21966/zxzr-e472</t>
+        </is>
+      </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUxkcndoNFQ4T2xyZWI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
@@ -6776,15 +6768,23 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="V57" t="n">
-        <v>1</v>
-      </c>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
-      <c r="Y57" t="inlineStr"/>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8138,7 +8138,7 @@
         </is>
       </c>
       <c r="V69" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W69" t="n">
         <v>0</v>
@@ -9577,12 +9577,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ca-cioos_c3958106-fc49-44bd-8227-bfc3e8bcb58c</t>
+          <t>ca-cioos_c3eff62f-bcee-4faa-a7e1-7b9380d94e74</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -9592,7 +9592,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Moore Island Archaeology Survey - 2019 - Airborne Coastal Observatory</t>
+          <t>Ancient Forest Wetlands, BC - Upper Fraser River - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -9610,7 +9610,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.5, 52.65], [-129.4, 52.65], [-129.4, 52.7], [-129.5, 52.7], [-129.5, 52.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-121.3, 53.79], [-121.2, 53.79], [-121.2, 53.84], [-121.3, 53.84], [-121.3, 53.79]]]}</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>[{'max': '150.0', 'min': '0.0'}]</t>
+          <t>[{'max': '500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>10.21966/wfcv-n753</t>
+          <t>10.21966/eysg-7a26</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6MBp3WwVTVbFK-0kv</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6RrLonwFgP-TX9bPv</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
@@ -9694,12 +9694,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ca-cioos_c3eff62f-bcee-4faa-a7e1-7b9380d94e74</t>
+          <t>ca-cioos_c3958106-fc49-44bd-8227-bfc3e8bcb58c</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ancient Forest Wetlands, BC - Upper Fraser River - 2019 - Airborne Coastal Observatory</t>
+          <t>Moore Island Archaeology Survey - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-121.3, 53.79], [-121.2, 53.79], [-121.2, 53.84], [-121.3, 53.84], [-121.3, 53.79]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.5, 52.65], [-129.4, 52.65], [-129.4, 52.7], [-129.5, 52.7], [-129.5, 52.65]]]}</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>[{'max': '500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '150.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>10.21966/eysg-7a26</t>
+          <t>10.21966/wfcv-n753</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6RrLonwFgP-TX9bPv</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6MBp3WwVTVbFK-0kv</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
@@ -10229,12 +10229,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ca-cioos_5e4f925a-9cf2-4e33-ae22-75c5b326ce6c</t>
+          <t>ca-cioos_5c13b300-e172-4010-a6d8-7586b68a3a96</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Eelgrass (Z. marina) extent at sites along the Central Coast, British Columbia</t>
+          <t>Kelp extent for the McNaughton Group Islands (2017), Manley Island (2017), and Serpent Group Islands (2016), British Columbia, Canada</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Nearshore, Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10286,11 +10286,11 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.65354407, 51.37817421], [-127.69773286, 51.37817421], [-127.69773286, 52.1127963], [-128.65354407, 52.1127963], [-128.65354407, 51.37817421]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.30122253, 51.7689035], [-128.05512885, 51.7689035], [-128.05512885, 51.98187882], [-128.30122253, 51.98187882], [-128.30122253, 51.7689035]]]}</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10300,17 +10300,17 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>10.21966/03pw-2190</t>
+          <t>10.21966/82bd-ks94</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTA3NnQ0NnRiemVLSFU</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFIWmZWeEE0RkZrZVc</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
@@ -10346,12 +10346,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ca-cioos_5c13b300-e172-4010-a6d8-7586b68a3a96</t>
+          <t>ca-cioos_5e4f925a-9cf2-4e33-ae22-75c5b326ce6c</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Kelp extent for the McNaughton Group Islands (2017), Manley Island (2017), and Serpent Group Islands (2016), British Columbia, Canada</t>
+          <t>Eelgrass (Z. marina) extent at sites along the Central Coast, British Columbia</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -10379,7 +10379,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Nearshore, Geospatial</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10403,11 +10403,11 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.30122253, 51.7689035], [-128.05512885, 51.7689035], [-128.05512885, 51.98187882], [-128.30122253, 51.98187882], [-128.30122253, 51.7689035]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.65354407, 51.37817421], [-127.69773286, 51.37817421], [-127.69773286, 52.1127963], [-128.65354407, 52.1127963], [-128.65354407, 51.37817421]]]}</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -10417,17 +10417,17 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>other, macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>10.21966/82bd-ks94</t>
+          <t>10.21966/03pw-2190</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFIWmZWeEE0RkZrZVc</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTA3NnQ0NnRiemVLSFU</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
@@ -14284,12 +14284,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ca-cioos_184b2f81-d87f-4615-a026-15b87930d15c</t>
+          <t>ca-cioos_23bc8c35-2e4e-4382-9296-a52d5ea49889</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -14299,7 +14299,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Aquatic carbon flux data package for Oliver et al. 2017</t>
+          <t>Discharge Time Series (2013-2017) – Calvert Island - Archived Version 3.0</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -14341,11 +14341,11 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.15002441406247, 51.614605707797466], [-127.96600341796874, 51.614605707797466], [-127.96600341796874, 51.70405535332591], [-128.15002441406247, 51.70405535332591], [-128.15002441406247, 51.614605707797466]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -14355,17 +14355,17 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>dissolvedOrganicCarbon, other</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>10.21966/1.321324</t>
+          <t>10.21966/sbyc-d030</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW9aOE1zWERKZnFEWm4</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUdGRGRjUW9LRnBVNVI</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
@@ -14375,23 +14375,23 @@
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="V126" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="W126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}, {'relationship': 'parts', 'id': '10.5194/bg-2017-5', 'type': 'dois', 'status_code': 200, 'url': 'https://bg.copernicus.org/articles/14/3743/2017/bg-14-3743-2017-discussion.html'}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -14401,12 +14401,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ca-cioos_23bc8c35-2e4e-4382-9296-a52d5ea49889</t>
+          <t>ca-cioos_184b2f81-d87f-4615-a026-15b87930d15c</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -14416,7 +14416,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Discharge Time Series (2013-2017) – Calvert Island - Archived Version 3.0</t>
+          <t>Aquatic carbon flux data package for Oliver et al. 2017</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -14458,57 +14458,57 @@
         </is>
       </c>
       <c r="N127" t="n">
+        <v>3</v>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.15002441406247, 51.614605707797466], [-127.96600341796874, 51.614605707797466], [-127.96600341796874, 51.70405535332591], [-128.15002441406247, 51.70405535332591], [-128.15002441406247, 51.614605707797466]]]}</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>dissolvedOrganicCarbon, other</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>10.21966/1.321324</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW9aOE1zWERKZnFEWm4</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>2022-03-29</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="V127" t="n">
         <v>1</v>
       </c>
-      <c r="O127" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
-        </is>
-      </c>
-      <c r="P127" t="inlineStr">
-        <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q127" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R127" t="inlineStr">
-        <is>
-          <t>10.21966/sbyc-d030</t>
-        </is>
-      </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUdGRGRjUW9LRnBVNVI</t>
-        </is>
-      </c>
-      <c r="T127" t="inlineStr">
-        <is>
-          <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="V127" t="n">
-        <v>10</v>
-      </c>
       <c r="W127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}, {'relationship': 'parts', 'id': '10.5194/bg-2017-5', 'type': 'dois', 'status_code': 200, 'url': 'https://bg.copernicus.org/articles/14/3743/2017/bg-14-3743-2017-discussion.html'}]</t>
         </is>
       </c>
     </row>
@@ -15525,7 +15525,7 @@
         </is>
       </c>
       <c r="V136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W136" t="n">
         <v>0</v>
@@ -20643,12 +20643,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>432b05ce-8904-4094-94bf-b97fb6636e41</t>
+          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>ca-cioos_3e90a567-cdd7-41f3-8157-0e7be76eefb8</t>
+          <t>ca-cioos_6c449900-c726-4e9a-b241-707711e253a7</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -20658,7 +20658,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Nuchatlaht Survey - Hakai Airborne Coastal Observatory Imagery and Topography Data - Nootka Island British Columbia - 2023</t>
+          <t>Hakai Institute Juvenile Salmon Program Time Series</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -20676,7 +20676,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Juvenile Salmon Program</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -20704,51 +20704,53 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.1, 49.71], [-126.7, 49.71], [-126.7, 50.01], [-127.1, 50.01], [-127.1, 49.71]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.8232006, 49.89790212], [-124.67574133, 49.89790212], [-124.67574133, 50.73488305], [-126.8232006, 50.73488305], [-126.8232006, 49.89790212]]]}</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>[{'max': '500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '9.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>10.21966/kp87-sf64</t>
+          <t>10.21966/1.566666</t>
         </is>
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Nlir_Hi8PQBF_etobGR</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXNUQUNpb1hBa0pYWVg</t>
         </is>
       </c>
       <c r="T181" t="inlineStr">
         <is>
-          <t>2024-01-08</t>
+          <t>2023-11-03</t>
         </is>
       </c>
       <c r="U181" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="V181" t="inlineStr"/>
+          <t>2025-01-18</t>
+        </is>
+      </c>
+      <c r="V181" t="n">
+        <v>3</v>
+      </c>
       <c r="W181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X181" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2024', 'total': 1}]</t>
         </is>
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'references', 'id': '10.1111/fog.12471', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1111/fog.12471'}, {'relationship': 'references', 'id': '10.26428/1606-9919-2021-201-669-685', 'type': 'dois', 'status_code': 200, 'url': 'https://izvestiya.tinro-center.ru/jour/article/view/662'}, {'relationship': 'references', 'id': '10.5281/zenodo.4005400', 'type': 'dois', 'status_code': 200, 'url': 'https://zenodo.org/records/4005400'}, {'relationship': 'references', 'id': '10.48321/d1cw23', 'type': 'dois', 'status_code': 200, 'url': 'https://dmphub.uc3prd.cdlib.net/dmps/10.48321/D1CW23'}, {'relationship': 'references', 'id': '10.48321/d12k5b', 'type': 'dois', 'status_code': 200, 'url': 'https://dmphub.uc3prd.cdlib.net/dmps/10.48321/D12K5B'}, {'relationship': 'references', 'id': '10.21966/9ktc-qm09', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_6f6560e7-7497-4685-9df2-51c66080b7c9'}, {'relationship': 'references', 'id': '10.5683/sp3/socbjj', 'type': 'dois', 'status_code': 200, 'url': 'https://borealisdata.ca/citation?persistentId=doi:10.5683/SP3/SOCBJJ'}, {'relationship': 'citations', 'id': '10.5061/dryad.x69p8czn0', 'type': 'dois', 'status_code': 200, 'url': 'https://datadryad.org/dataset/doi:10.5061/dryad.x69p8czn0'}, {'relationship': 'partOf', 'id': '10.25607/obis.export.234a34a8', 'type': 'dois', 'status_code': 200, 'url': 'https://obis.org/export/234a34a8'}, {'relationship': 'partOf', 'id': '10.25607/obis.occurrence.b89117cd', 'type': 'dois', 'status_code': 200, 'url': 'https://github.com/iobis/obis-open-data'}, {'relationship': 'versions', 'id': '10.21966/e5c1-c396', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_eb1feb98-b11a-4663-b7ab-2216df8187bd'}, {'relationship': 'versions', 'id': '10.21966/99mg-0s52', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_8853a375-f067-4760-b5d1-98c1fcf40c6d'}, {'relationship': 'versions', 'id': '10.21966/c7na-z171', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_1769a04e-b77b-409b-8e48-bc2098bbad3e'}]</t>
         </is>
       </c>
     </row>
@@ -20758,12 +20760,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>582c6ff0-029e-44ba-8ba1-d3f2f39f2005</t>
+          <t>432b05ce-8904-4094-94bf-b97fb6636e41</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>ca-cioos_6f6560e7-7497-4685-9df2-51c66080b7c9</t>
+          <t>ca-cioos_3e90a567-cdd7-41f3-8157-0e7be76eefb8</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -20773,7 +20775,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Genetic Stock Identification of Juvenile Sockeye Salmon Captured in the Discovery Islands and Johnstone Strait BC, Canada</t>
+          <t>Nuchatlaht Survey - Hakai Airborne Coastal Observatory Imagery and Topography Data - Nootka Island British Columbia - 2023</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -20791,7 +20793,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Juvenile Salmon Program</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -20819,53 +20821,51 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.0, 49.88], [-124.4, 49.88], [-124.4, 50.84], [-127.0, 50.84], [-127.0, 49.88]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.1, 49.71], [-126.7, 49.71], [-126.7, 50.01], [-127.1, 50.01], [-127.1, 49.71]]]}</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>[{'max': '9.0', 'min': '0.0'}]</t>
+          <t>[{'max': '500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>10.21966/9ktc-qm09</t>
+          <t>10.21966/kp87-sf64</t>
         </is>
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/UTb9hNU3GJRK302QyaKNIvj2OiJ2/-NM0DF83_HSOwpbGBM8m</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Nlir_Hi8PQBF_etobGR</t>
         </is>
       </c>
       <c r="T182" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-08</t>
         </is>
       </c>
       <c r="U182" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="V182" t="n">
-        <v>1</v>
-      </c>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr"/>
       <c r="W182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X182" t="inlineStr">
         <is>
-          <t>[{'year': '2024', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.21966/1.566666', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_6c449900-c726-4e9a-b241-707711e253a7'}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -20875,12 +20875,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>11051c56-8d67-43fc-a13c-b706e851a5a4</t>
+          <t>582c6ff0-029e-44ba-8ba1-d3f2f39f2005</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>ca-cioos_2d693456-7e65-46be-95d7-6bb697320017</t>
+          <t>ca-cioos_6f6560e7-7497-4685-9df2-51c66080b7c9</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -20890,7 +20890,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Water Level and Weather Station Time Series, Pruth Bay, Kwakshua Channel, Central Coast, BC, Canada (Provisional)</t>
+          <t>Genetic Stock Identification of Juvenile Sockeye Salmon Captured in the Discovery Islands and Johnstone Strait BC, Canada</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -20908,12 +20908,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Oceanography, Watersheds</t>
+          <t>Juvenile Salmon Program</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -20936,51 +20936,53 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-128.1302805556, 51.6544888889]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.0, 49.88], [-124.4, 49.88], [-124.4, 50.84], [-127.0, 50.84], [-127.0, 49.88]]]}</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '9.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>seaSurfaceHeight, other, seaSurfaceTemperature</t>
+          <t>fishAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>10.21966/8d4w-sr07</t>
+          <t>10.21966/9ktc-qm09</t>
         </is>
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MkxD-S6TxIvv2e6_OGH</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/UTb9hNU3GJRK302QyaKNIvj2OiJ2/-NM0DF83_HSOwpbGBM8m</t>
         </is>
       </c>
       <c r="T183" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="U183" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="V183" t="inlineStr"/>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="V183" t="n">
+        <v>1</v>
+      </c>
       <c r="W183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X183" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2024', 'total': 1}]</t>
         </is>
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'citations', 'id': '10.21966/1.566666', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_6c449900-c726-4e9a-b241-707711e253a7'}]</t>
         </is>
       </c>
     </row>
@@ -20990,12 +20992,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>b0e815da-1b17-404d-8bf6-0bdb4a22d170</t>
+          <t>11051c56-8d67-43fc-a13c-b706e851a5a4</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>ca-cioos_c24f23f0-8d16-4bfd-835a-5475f1ecd8e8</t>
+          <t>ca-cioos_2d693456-7e65-46be-95d7-6bb697320017</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -21005,7 +21007,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Extent of Canopy-Forming Kelps, Derived from World View-2, Central Coast, Central Coast, British Columbia</t>
+          <t>Water Level and Weather Station Time Series, Pruth Bay, Kwakshua Channel, Central Coast, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -21023,12 +21025,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Oceanography, Watersheds</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -21047,31 +21049,31 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6993408203125, 51.31001339554933], [-127.65014648437497, 51.31001339554933], [-127.65014648437497, 52.221069523572794], [-128.6993408203125, 52.221069523572794], [-128.6993408203125, 51.31001339554933]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-128.1302805556, 51.6544888889]}</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>seaSurfaceHeight, other, seaSurfaceTemperature</t>
         </is>
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>10.21966/5fs0-nn02</t>
+          <t>10.21966/8d4w-sr07</t>
         </is>
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVE2ZkIxMnhEdmF6Rkw</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MkxD-S6TxIvv2e6_OGH</t>
         </is>
       </c>
       <c r="T184" t="inlineStr">
@@ -21081,12 +21083,10 @@
       </c>
       <c r="U184" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="V184" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr"/>
       <c r="W184" t="n">
         <v>0</v>
       </c>
@@ -21107,12 +21107,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>b0e815da-1b17-404d-8bf6-0bdb4a22d170</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>ca-cioos_d1bef0b7-4d15-4bc1-bf34-faca6352891f</t>
+          <t>ca-cioos_c24f23f0-8d16-4bfd-835a-5475f1ecd8e8</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -21122,7 +21122,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Daily satellite (Sentinel 3A and 3B) chlorophyll and suspended matter concentrations for coastal British Columbia and southeast Alaska</t>
+          <t>Extent of Canopy-Forming Kelps, Derived from World View-2, Central Coast, Central Coast, British Columbia</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -21140,12 +21140,12 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -21164,45 +21164,45 @@
         </is>
       </c>
       <c r="N185" t="n">
+        <v>3</v>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6993408203125, 51.31001339554933], [-127.65014648437497, 51.31001339554933], [-127.65014648437497, 52.221069523572794], [-128.6993408203125, 52.221069523572794], [-128.6993408203125, 51.31001339554933]]]}</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>10.21966/5fs0-nn02</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVE2ZkIxMnhEdmF6Rkw</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>2024-03-14</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="V185" t="n">
         <v>1</v>
-      </c>
-      <c r="O185" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-139.0, 47.0], [-121.5, 47.0], [-121.5, 59.5], [-139.0, 59.5], [-139.0, 47.0]]]}</t>
-        </is>
-      </c>
-      <c r="P185" t="inlineStr">
-        <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q185" t="inlineStr">
-        <is>
-          <t>phytoplanktonBiomassAndDiversity, particulateMatter, other</t>
-        </is>
-      </c>
-      <c r="R185" t="inlineStr">
-        <is>
-          <t>10.21966/dveq-bt48</t>
-        </is>
-      </c>
-      <c r="S185" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-NTteirxDjvnABVz_7Dh</t>
-        </is>
-      </c>
-      <c r="T185" t="inlineStr">
-        <is>
-          <t>2024-03-14</t>
-        </is>
-      </c>
-      <c r="U185" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="V185" t="n">
-        <v>4</v>
       </c>
       <c r="W185" t="n">
         <v>0</v>
@@ -21224,12 +21224,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>abb0b617-3a3e-43ec-b62e-e2918bfc10aa</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>ca-cioos_b8483c9e-81e6-4e1a-b09f-2d66f8fee9a2</t>
+          <t>ca-cioos_d1bef0b7-4d15-4bc1-bf34-faca6352891f</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -21239,7 +21239,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp (Nereocystis luetkeana) derived from fixed-wing surveys (2023), Denman Island to south Quadra Island, British Columbia, Canada</t>
+          <t>Daily satellite (Sentinel 3A and 3B) chlorophyll and suspended matter concentrations for coastal British Columbia and southeast Alaska</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -21257,12 +21257,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Nearshore, Geospatial</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -21285,41 +21285,41 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.3, 50.02], [-125.1, 50.05], [-125.1, 49.9], [-124.8, 49.71], [-124.7, 49.56], [-124.8, 49.55], [-124.9, 49.64], [-125.2, 49.9], [-125.2, 49.9], [-125.3, 50.02]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-139.0, 47.0], [-121.5, 47.0], [-121.5, 59.5], [-139.0, 59.5], [-139.0, 47.0]]]}</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>phytoplanktonBiomassAndDiversity, particulateMatter, other</t>
         </is>
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>10.21966/fmw1-8w35</t>
+          <t>10.21966/dveq-bt48</t>
         </is>
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-NpNoCv2XWdhBoo5RBKV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-NTteirxDjvnABVz_7Dh</t>
         </is>
       </c>
       <c r="T186" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="U186" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="V186" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W186" t="n">
         <v>0</v>
@@ -21341,12 +21341,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>9df42f88-b8d8-4e2d-97bb-ad5ba49f6f1f</t>
+          <t>abb0b617-3a3e-43ec-b62e-e2918bfc10aa</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>ca-cioos_59b33373-ae4a-4719-a3df-0e36a08187d8</t>
+          <t>ca-cioos_b8483c9e-81e6-4e1a-b09f-2d66f8fee9a2</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -21356,7 +21356,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Seagrass Site-Level Production on BC Central Coast</t>
+          <t>Spatial extent of surface canopy kelp (Nereocystis luetkeana) derived from fixed-wing surveys (2023), Denman Island to south Quadra Island, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -21374,12 +21374,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Airborne Coastal Observatory, Nearshore, Geospatial</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -21402,37 +21402,37 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.98931373, 50.8340959], [-127.03580726, 50.8340959], [-127.03580726, 52.33530479], [-128.98931373, 52.33530479], [-128.98931373, 50.8340959]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.3, 50.02], [-125.1, 50.05], [-125.1, 49.9], [-124.8, 49.71], [-124.7, 49.56], [-124.8, 49.55], [-124.9, 49.64], [-125.2, 49.9], [-125.2, 49.9], [-125.3, 50.02]]]}</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>[{'max': '10.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>other, seagrassCoverAndComposition</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>10.21966/ezev-0v96</t>
+          <t>10.21966/fmw1-8w35</t>
         </is>
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/lJHlH9nm20QQOPuk217xLlxWbNv1/-NPt7-mgrZEUzma8l5W_</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-NpNoCv2XWdhBoo5RBKV</t>
         </is>
       </c>
       <c r="T187" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="U187" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="V187" t="n">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>bf7c05e8-510d-4449-9e81-4c358ff3f440</t>
+          <t>9df42f88-b8d8-4e2d-97bb-ad5ba49f6f1f</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>ca-cioos_1755dc37-8d33-4158-8041-c22536fd5771</t>
+          <t>ca-cioos_59b33373-ae4a-4719-a3df-0e36a08187d8</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -21473,7 +21473,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Bulk and Size-Fractionated Chlorophyll and Phaeopigment Concentrations Collected by Niskin Bottle, BC, Canada (Provisional)</t>
+          <t>Seagrass Site-Level Production on BC Central Coast</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -21491,7 +21491,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -21519,37 +21519,37 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.98931373, 50.8340959], [-127.03580726, 50.8340959], [-127.03580726, 52.33530479], [-128.98931373, 52.33530479], [-128.98931373, 50.8340959]]]}</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>[{'max': '650.0', 'min': '0.0'}]</t>
+          <t>[{'max': '10.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>particulateMatter</t>
+          <t>other, seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>10.21966/90h6-b497</t>
+          <t>10.21966/ezev-0v96</t>
         </is>
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-McQFPAf457LB4-SWmyL</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/lJHlH9nm20QQOPuk217xLlxWbNv1/-NPt7-mgrZEUzma8l5W_</t>
         </is>
       </c>
       <c r="T188" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="U188" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="V188" t="n">
@@ -21575,12 +21575,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>8882a149-fabd-4ecd-98d3-68a2a88aee38</t>
+          <t>bf7c05e8-510d-4449-9e81-4c358ff3f440</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>ca-cioos_d55021c3-a142-4e14-8208-36c9826c1893</t>
+          <t>ca-cioos_1755dc37-8d33-4158-8041-c22536fd5771</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -21590,7 +21590,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Bulk and Size-Fractionated Chlorophyll and Phaeopigment Concentrations Collected by Niskin Bottle, BC, Canada (Research)</t>
+          <t>Bulk and Size-Fractionated Chlorophyll and Phaeopigment Concentrations Collected by Niskin Bottle, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -21632,7 +21632,7 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O189" t="inlineStr">
         <is>
@@ -21646,17 +21646,17 @@
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>particulateMatter</t>
         </is>
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>10.21966/q5vm-8797</t>
+          <t>10.21966/90h6-b497</t>
         </is>
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-MadZvZJ4ZeikpCgRcV8</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-McQFPAf457LB4-SWmyL</t>
         </is>
       </c>
       <c r="T189" t="inlineStr">
@@ -21669,7 +21669,9 @@
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="V189" t="inlineStr"/>
+      <c r="V189" t="n">
+        <v>1</v>
+      </c>
       <c r="W189" t="n">
         <v>0</v>
       </c>
@@ -21690,12 +21692,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
+          <t>8882a149-fabd-4ecd-98d3-68a2a88aee38</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>ca-cioos_6143028b-028d-46c7-a67d-f3a513435e63</t>
+          <t>ca-cioos_d55021c3-a142-4e14-8208-36c9826c1893</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -21705,7 +21707,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Water Property Measurements from Conductivity-Temperature-Depth Profiles, BC, Canada (Provisional)</t>
+          <t>Bulk and Size-Fractionated Chlorophyll and Phaeopigment Concentrations Collected by Niskin Bottle, BC, Canada (Research)</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -21723,7 +21725,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Juvenile Salmon Program, Oceanography, Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -21747,7 +21749,7 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O190" t="inlineStr">
         <is>
@@ -21756,37 +21758,35 @@
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>[{'max': '700.0', 'min': '1.0'}]</t>
+          <t>[{'max': '650.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>oxygen, subSurfaceSalinity, subSurfaceTemperature</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>10.21966/rj8w-aa62</t>
+          <t>10.21966/q5vm-8797</t>
         </is>
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MMHJ4k2EEwxkbXkrjxa</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-MadZvZJ4ZeikpCgRcV8</t>
         </is>
       </c>
       <c r="T190" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="U190" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="V190" t="n">
-        <v>2</v>
-      </c>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr"/>
       <c r="W190" t="n">
         <v>0</v>
       </c>
@@ -21807,12 +21807,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
+          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>ca-cioos_6652a7a9-d27f-4cbe-ac04-435c238e991d</t>
+          <t>ca-cioos_6143028b-028d-46c7-a67d-f3a513435e63</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -21822,7 +21822,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Water Level Time Series, Choke Pass, Central Coast, BC, Canada (Provisional)</t>
+          <t>Water Property Measurements from Conductivity-Temperature-Depth Profiles, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -21840,12 +21840,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Juvenile Salmon Program, Oceanography, Nearshore</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -21868,37 +21868,37 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-128.12103, 51.670666]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>[{'max': '6.0', 'min': '0.0'}]</t>
+          <t>[{'max': '700.0', 'min': '1.0'}]</t>
         </is>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>seaSurfaceHeight</t>
+          <t>oxygen, subSurfaceSalinity, subSurfaceTemperature</t>
         </is>
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>10.21966/kqd6-1j57</t>
+          <t>10.21966/rj8w-aa62</t>
         </is>
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-Mknr8pYvIQKw4r-WTFd</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MMHJ4k2EEwxkbXkrjxa</t>
         </is>
       </c>
       <c r="T191" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="U191" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="V191" t="n">
@@ -21924,12 +21924,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2081eb2e-67c5-44b7-b048-aeb2c646f238</t>
+          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>ca-cioos_f67c0c58-3225-4dac-9264-1e76f07c9374</t>
+          <t>ca-cioos_6652a7a9-d27f-4cbe-ac04-435c238e991d</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -21939,7 +21939,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Data for the paper "Phylogenomic position of eupelagonemids, abundant, and diverse deep-ocean heterotrophs"</t>
+          <t>Water Level Time Series, Choke Pass, Central Coast, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -21957,7 +21957,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Genomics</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -21977,7 +21977,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>University of British Columbia</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N192" t="n">
@@ -21985,40 +21985,42 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.9661, 51.65001], [-127.966, 51.65001], [-127.966, 51.65], [-127.9661, 51.65], [-127.9661, 51.65001]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-128.12103, 51.670666]}</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>[{'max': '300.0', 'min': '300.0'}]</t>
+          <t>[{'max': '6.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>seaSurfaceHeight</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>10.21966/7t4p-s714</t>
+          <t>10.21966/kqd6-1j57</t>
         </is>
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/NSo1FkJnvIbQDOlYlwNfWGnAxx33/-O1xBAkNi0P8igzOb4rg</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-Mknr8pYvIQKw4r-WTFd</t>
         </is>
       </c>
       <c r="T192" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="U192" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
-        </is>
-      </c>
-      <c r="V192" t="inlineStr"/>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="V192" t="n">
+        <v>2</v>
+      </c>
       <c r="W192" t="n">
         <v>0</v>
       </c>
@@ -22039,12 +22041,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>1dfdbadf-6314-4411-8d18-752f6dd920e9</t>
+          <t>2081eb2e-67c5-44b7-b048-aeb2c646f238</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>ca-cioos_67e89414-a93f-496d-9766-9311f0d3954e</t>
+          <t>ca-cioos_f67c0c58-3225-4dac-9264-1e76f07c9374</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -22054,7 +22056,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Motile Invertebrate Surveys - BC Central Coast</t>
+          <t>Data for the paper "Phylogenomic position of eupelagonemids, abundant, and diverse deep-ocean heterotrophs"</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -22072,12 +22074,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Genomics</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -22092,7 +22094,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="N193" t="n">
@@ -22100,53 +22102,51 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.2, 51.63], [-128.1, 51.63], [-128.1, 51.67], [-128.2, 51.67], [-128.2, 51.63]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.9661, 51.65001], [-127.966, 51.65001], [-127.966, 51.65], [-127.9661, 51.65], [-127.9661, 51.65001]]]}</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '-5.0'}]</t>
+          <t>[{'max': '300.0', 'min': '300.0'}]</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>10.21966/0052-wk15</t>
+          <t>10.21966/7t4p-s714</t>
         </is>
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-MotWzhmBvoGPE8QZ0sf</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/NSo1FkJnvIbQDOlYlwNfWGnAxx33/-O1xBAkNi0P8igzOb4rg</t>
         </is>
       </c>
       <c r="T193" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="U193" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="V193" t="n">
-        <v>1</v>
-      </c>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr"/>
       <c r="W193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X193" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.48321/d1ae4278b4', 'type': 'dois', 'status_code': 200, 'url': 'https://dmphub.uc3prd.cdlib.net/dmps/10.48321/D1AE4278B4'}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -22156,12 +22156,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>a8f61379-14f9-4ccc-bc9b-4408ba8340d7</t>
+          <t>1dfdbadf-6314-4411-8d18-752f6dd920e9</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>ca-cioos_52797e17-c0ed-46a4-9dcd-e34f801c6205</t>
+          <t>ca-cioos_67e89414-a93f-496d-9766-9311f0d3954e</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -22171,7 +22171,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Fucus Dynamics - Point Intercept Surveys - BC Central Coast</t>
+          <t>Motile Invertebrate Surveys - BC Central Coast</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -22227,27 +22227,27 @@
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>10.21966/v57r-g944</t>
+          <t>10.21966/0052-wk15</t>
         </is>
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-MopPnOL2o_bshK-cKxr</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-MotWzhmBvoGPE8QZ0sf</t>
         </is>
       </c>
       <c r="T194" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="U194" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="V194" t="n">
@@ -22258,12 +22258,12 @@
       </c>
       <c r="X194" t="inlineStr">
         <is>
-          <t>[{'year': '2024', 'total': 1}]</t>
+          <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.21966/hpqq-0k76', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_9201118a-b0c4-470f-a76f-396bacc5e93e'}]</t>
+          <t>[{'relationship': 'citations', 'id': '10.48321/d1ae4278b4', 'type': 'dois', 'status_code': 200, 'url': 'https://dmphub.uc3prd.cdlib.net/dmps/10.48321/D1AE4278B4'}]</t>
         </is>
       </c>
     </row>
@@ -22273,12 +22273,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>c4d3a53a-faa2-4c3e-bcd3-cfdb0aef0078</t>
+          <t>a8f61379-14f9-4ccc-bc9b-4408ba8340d7</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>ca-cioos_355467ad-104d-40a6-b06e-52a67bfe247e</t>
+          <t>ca-cioos_52797e17-c0ed-46a4-9dcd-e34f801c6205</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -22288,7 +22288,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Water column CO2 system measurements from January 2016 to December 2023 from Hakai Institute oceanographic station QU39 in northern Strait of Georgia, British Columbia, Canada</t>
+          <t>Fucus Dynamics - Point Intercept Surveys - BC Central Coast</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -22306,12 +22306,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -22334,53 +22334,53 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.1, 50.03]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.2, 51.63], [-128.1, 51.63], [-128.1, 51.67], [-128.2, 51.67], [-128.2, 51.63]]]}</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>[{'max': '262.0', 'min': '1.0'}]</t>
+          <t>[{'max': '5.0', 'min': '-5.0'}]</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>inorganicCarbon, oxygen, subSurfaceSalinity, seaSurfaceTemperature, seaSurfaceSalinity, subSurfaceTemperature</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>10.21966/k1xg-6920</t>
+          <t>10.21966/v57r-g944</t>
         </is>
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-O6XpUwSfsllQlTBMz53</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-MopPnOL2o_bshK-cKxr</t>
         </is>
       </c>
       <c r="T195" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="U195" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="V195" t="n">
         <v>1</v>
       </c>
       <c r="W195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X195" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2024', 'total': 1}]</t>
         </is>
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'citations', 'id': '10.21966/hpqq-0k76', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_9201118a-b0c4-470f-a76f-396bacc5e93e'}]</t>
         </is>
       </c>
     </row>
@@ -22390,12 +22390,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>52d607c9-46cd-4be9-a752-1b5446272f32</t>
+          <t>c4d3a53a-faa2-4c3e-bcd3-cfdb0aef0078</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>ca-cioos_0507a738-cd65-4ba4-943e-42b9d022b637</t>
+          <t>ca-cioos_355467ad-104d-40a6-b06e-52a67bfe247e</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -22405,7 +22405,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Fraser River Airborne Surveys - 2021 - Hakai Airborne Coastal Observatory</t>
+          <t>Water column CO2 system measurements from January 2016 to December 2023 from Hakai Institute oceanographic station QU39 in northern Strait of Georgia, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -22451,40 +22451,42 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.1, 50.5], [-121.7, 50.5], [-121.7, 51.12], [-122.1, 51.12], [-122.1, 50.5]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.1, 50.03]}</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>[{'max': '1500.0', 'min': '185.0'}]</t>
+          <t>[{'max': '262.0', 'min': '1.0'}]</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>inorganicCarbon, oxygen, subSurfaceSalinity, seaSurfaceTemperature, seaSurfaceSalinity, subSurfaceTemperature</t>
         </is>
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>10.21966/ytgc-6g46</t>
+          <t>10.21966/k1xg-6920</t>
         </is>
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NHfqx-d8tuAroY8BWc7</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-O6XpUwSfsllQlTBMz53</t>
         </is>
       </c>
       <c r="T196" t="inlineStr">
         <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
           <t>2024-10-09</t>
         </is>
       </c>
-      <c r="U196" t="inlineStr">
-        <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="V196" t="inlineStr"/>
+      <c r="V196" t="n">
+        <v>1</v>
+      </c>
       <c r="W196" t="n">
         <v>0</v>
       </c>
@@ -22505,12 +22507,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>551bbe09-f182-478b-8d50-2f9a4dbd93ae</t>
+          <t>52d607c9-46cd-4be9-a752-1b5446272f32</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>ca-cioos_189dd319-d5ef-4f2a-a060-df8d47628b86</t>
+          <t>ca-cioos_0507a738-cd65-4ba4-943e-42b9d022b637</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -22520,7 +22522,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Elliot Creek Landslide LiDAR Mapping - 2023 - Airborne Coastal Observatory</t>
+          <t>Fraser River Airborne Surveys - 2021 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -22538,7 +22540,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -22562,16 +22564,16 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.8, 50.84], [-124.5, 50.84], [-124.5, 51.0], [-124.8, 51.0], [-124.8, 50.84]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.1, 50.5], [-121.7, 50.5], [-121.7, 51.12], [-122.1, 51.12], [-122.1, 50.5]]]}</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>[{'max': '2300.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1500.0', 'min': '185.0'}]</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr">
@@ -22581,12 +22583,12 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>10.21966/szqj-b355</t>
+          <t>10.21966/ytgc-6g46</t>
         </is>
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRZqJivYfce75NOoBD</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NHfqx-d8tuAroY8BWc7</t>
         </is>
       </c>
       <c r="T197" t="inlineStr">
@@ -22596,7 +22598,7 @@
       </c>
       <c r="U197" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="V197" t="inlineStr"/>
@@ -22620,12 +22622,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
+          <t>551bbe09-f182-478b-8d50-2f9a4dbd93ae</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>ca-cioos_33a367c1-2706-4301-af99-4455fbe189a0</t>
+          <t>ca-cioos_189dd319-d5ef-4f2a-a060-df8d47628b86</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -22635,7 +22637,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Cryosphere Snow Surveys Southwest British Columbia - Airborne Coastal Observatory</t>
+          <t>Elliot Creek Landslide LiDAR Mapping - 2023 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -22653,7 +22655,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -22681,7 +22683,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.9, 48.62], [-122.1, 48.62], [-122.1, 50.82], [-126.9, 50.82], [-126.9, 48.62]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.8, 50.84], [-124.5, 50.84], [-124.5, 51.0], [-124.8, 51.0], [-124.8, 50.84]]]}</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -22696,12 +22698,12 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>10.21966/thq7-0g08</t>
+          <t>10.21966/szqj-b355</t>
         </is>
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRfMcU9I8mMcBH6qiv</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRZqJivYfce75NOoBD</t>
         </is>
       </c>
       <c r="T198" t="inlineStr">
@@ -22711,12 +22713,10 @@
       </c>
       <c r="U198" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="V198" t="n">
-        <v>3</v>
-      </c>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr"/>
       <c r="W198" t="n">
         <v>0</v>
       </c>
@@ -22737,12 +22737,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
+          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a</t>
+          <t>ca-cioos_33a367c1-2706-4301-af99-4455fbe189a0</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -22752,7 +22752,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Bute Inlet Geohazard - Topography Surveys - 2023 - Hakai Airborne Coastal Observatory</t>
+          <t>Cryosphere Snow Surveys Southwest British Columbia - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -22794,16 +22794,16 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.9, 50.53], [-124.2, 50.53], [-124.2, 50.99], [-124.9, 50.99], [-124.9, 50.53]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.9, 48.62], [-122.1, 48.62], [-122.1, 50.82], [-126.9, 50.82], [-126.9, 48.62]]]}</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>[{'max': '2600.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2300.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q199" t="inlineStr">
@@ -22813,12 +22813,12 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>10.21966/e4b8-vp48</t>
+          <t>10.21966/thq7-0g08</t>
         </is>
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRG7xQ84LQrgS4jhie</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRfMcU9I8mMcBH6qiv</t>
         </is>
       </c>
       <c r="T199" t="inlineStr">
@@ -22828,7 +22828,7 @@
       </c>
       <c r="U199" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="V199" t="n">
@@ -22854,12 +22854,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>78efda1b-9688-4bcf-b16e-7167c17c0bcb</t>
+          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>ca-cioos_43422dc8-2573-4f60-bf87-df447d57ab7a</t>
+          <t>ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -22869,7 +22869,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>USGS Glacier Mapping - 2023 - Hakai Airborne Coastal Observatory</t>
+          <t>Bute Inlet Geohazard - Topography Surveys - 2023 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -22911,16 +22911,16 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-121.4, 47.68], [-113.0, 47.68], [-113.0, 49.08], [-121.4, 49.08], [-121.4, 47.68]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.9, 50.53], [-124.2, 50.53], [-124.2, 50.99], [-124.9, 50.99], [-124.9, 50.53]]]}</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>[{'max': '2800.0', 'min': '100.0'}]</t>
+          <t>[{'max': '2600.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q200" t="inlineStr">
@@ -22930,12 +22930,12 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>10.21966/bzr6-er66</t>
+          <t>10.21966/e4b8-vp48</t>
         </is>
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRKhzLRiCcp6ENuX2r</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRG7xQ84LQrgS4jhie</t>
         </is>
       </c>
       <c r="T200" t="inlineStr">
@@ -22945,11 +22945,11 @@
       </c>
       <c r="U200" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="V200" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W200" t="n">
         <v>0</v>
@@ -22971,12 +22971,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
+          <t>78efda1b-9688-4bcf-b16e-7167c17c0bcb</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>ca-cioos_6756b221-28a0-4848-9761-905cbd558cd7</t>
+          <t>ca-cioos_43422dc8-2573-4f60-bf87-df447d57ab7a</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -22986,7 +22986,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Protistan plankton time series from the northern Salish Sea and Central Coast, British Columbia, Canada</t>
+          <t>USGS Glacier Mapping - 2023 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -23004,12 +23004,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -23028,45 +23028,45 @@
         </is>
       </c>
       <c r="N201" t="n">
+        <v>2</v>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-121.4, 47.68], [-113.0, 47.68], [-113.0, 49.08], [-121.4, 49.08], [-121.4, 47.68]]]}</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>[{'max': '2800.0', 'min': '100.0'}]</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>10.21966/bzr6-er66</t>
+        </is>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRKhzLRiCcp6ENuX2r</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="V201" t="n">
         <v>1</v>
-      </c>
-      <c r="O201" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
-        </is>
-      </c>
-      <c r="P201" t="inlineStr">
-        <is>
-          <t>[{'max': '6.0', 'min': '1.0'}]</t>
-        </is>
-      </c>
-      <c r="Q201" t="inlineStr">
-        <is>
-          <t>phytoplanktonBiomassAndDiversity</t>
-        </is>
-      </c>
-      <c r="R201" t="inlineStr">
-        <is>
-          <t>10.21966/jv5k-3k59</t>
-        </is>
-      </c>
-      <c r="S201" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-Nh8VlPQ_m681tso87Gd</t>
-        </is>
-      </c>
-      <c r="T201" t="inlineStr">
-        <is>
-          <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="U201" t="inlineStr">
-        <is>
-          <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="V201" t="n">
-        <v>4</v>
       </c>
       <c r="W201" t="n">
         <v>0</v>
@@ -23088,12 +23088,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>9d1749f8-9be2-468c-946e-965f92fcdc67</t>
+          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>ca-cioos_6e947d50-8392-42ce-bff9-24b126c7cab7</t>
+          <t>ca-cioos_6756b221-28a0-4848-9761-905cbd558cd7</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -23103,7 +23103,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Spatial extent of eelgrass (Zostera marina) beds from monitoring sites within the greater park ecosystem of Pacific Rim National Park Reserve (2017, 2018)</t>
+          <t>Protistan plankton time series from the northern Salish Sea and Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -23121,12 +23121,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Nearshore, Geospatial</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -23145,44 +23145,46 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.0511576, 48.72717181], [-124.94565833, 48.72717181], [-124.94565833, 49.24536019], [-126.0511576, 49.24536019], [-126.0511576, 48.72717181]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '6.0', 'min': '1.0'}]</t>
         </is>
       </c>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>other, seagrassCoverAndComposition</t>
+          <t>phytoplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>10.21966/8mpe-h081</t>
+          <t>10.21966/jv5k-3k59</t>
         </is>
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUR4a1V0N1UxYTc2U3Q</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-Nh8VlPQ_m681tso87Gd</t>
         </is>
       </c>
       <c r="T202" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="U202" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="V202" t="inlineStr"/>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="V202" t="n">
+        <v>4</v>
+      </c>
       <c r="W202" t="n">
         <v>0</v>
       </c>
@@ -23203,12 +23205,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
+          <t>9d1749f8-9be2-468c-946e-965f92fcdc67</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>ca-cioos_f25b00ba-ad63-42b3-8021-3fb6aa99baff</t>
+          <t>ca-cioos_6e947d50-8392-42ce-bff9-24b126c7cab7</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -23218,12 +23220,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Fraser River Landslide Project - Sites of Concern 2024</t>
+          <t>Spatial extent of eelgrass (Zostera marina) beds from monitoring sites within the greater park ecosystem of Pacific Rim National Park Reserve (2017, 2018)</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>document</t>
+          <t>dataset</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -23236,7 +23238,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Nearshore, Geospatial</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -23256,50 +23258,48 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Hakai Geospatial</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.0, 49.0], [-119.5, 49.0], [-119.5, 54.34], [-124.0, 54.34], [-124.0, 49.0]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.0511576, 48.72717181], [-124.94565833, 48.72717181], [-124.94565833, 49.24536019], [-126.0511576, 49.24536019], [-126.0511576, 48.72717181]]]}</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>[{'max': '2500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>10.21966/xp9x-m243</t>
+          <t>10.21966/8mpe-h081</t>
         </is>
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NTLT7n49Ox3SnVoy6nW</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUR4a1V0N1UxYTc2U3Q</t>
         </is>
       </c>
       <c r="T203" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="U203" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
-        </is>
-      </c>
-      <c r="V203" t="n">
-        <v>4</v>
-      </c>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr"/>
       <c r="W203" t="n">
         <v>0</v>
       </c>
@@ -23320,12 +23320,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
+          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>ca-cioos_c513de71-ac9d-43fa-b693-8f865de4b137</t>
+          <t>ca-cioos_f25b00ba-ad63-42b3-8021-3fb6aa99baff</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -23335,12 +23335,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Fraser River Landslide Project - 2022-2024 - Drone Data</t>
+          <t>Fraser River Landslide Project - Sites of Concern 2024</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>document</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -23353,7 +23353,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -23381,12 +23381,12 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.8, 49.29], [-121.2, 49.29], [-121.2, 52.28], [-122.8, 52.28], [-122.8, 49.29]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.0, 49.0], [-119.5, 49.0], [-119.5, 54.34], [-124.0, 54.34], [-124.0, 49.0]]]}</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>[{'max': '1500.0', 'min': '50.0'}]</t>
+          <t>[{'max': '2500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q204" t="inlineStr">
@@ -23396,26 +23396,26 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>10.21966/qpe8-ay93</t>
+          <t>10.21966/xp9x-m243</t>
         </is>
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpurN_vwkhOgSJmgBh9</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NTLT7n49Ox3SnVoy6nW</t>
         </is>
       </c>
       <c r="T204" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="U204" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="V204" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W204" t="n">
         <v>0</v>
@@ -23437,12 +23437,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>e8414189-54c9-4311-874e-b97f9b7916ae</t>
+          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>ca-cioos_48acba27-5e01-4b41-9a0e-f3fc8d809a13</t>
+          <t>ca-cioos_c513de71-ac9d-43fa-b693-8f865de4b137</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -23452,7 +23452,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>MusselSeg: Semantic Segmentation for Rocky Intertidal Mussel Habitat</t>
+          <t>Fraser River Landslide Project - 2022-2024 - Drone Data</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -23470,12 +23470,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -23490,7 +23490,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Hakai Geospatial</t>
         </is>
       </c>
       <c r="N205" t="n">
@@ -23498,40 +23498,42 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-130.1, 51.59], [-120.4, 31.75], [-118.4, 33.38], [-124.3, 44.43], [-122.0, 49.35], [-126.2, 51.59], [-130.1, 51.59]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.8, 49.29], [-121.2, 49.29], [-121.2, 52.28], [-122.8, 52.28], [-122.8, 49.29]]]}</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>[{'max': '75.0', 'min': '15.0'}]</t>
+          <t>[{'max': '1500.0', 'min': '50.0'}]</t>
         </is>
       </c>
       <c r="Q205" t="inlineStr">
         <is>
-          <t>other, invertebrateAbundanceAndDistribution</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>10.21966/fbv4-th96</t>
+          <t>10.21966/qpe8-ay93</t>
         </is>
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DCH8GzsQKSM8xwJ8WdQFIZrtCaq2/-O26fyGiVXoF__M22UrP</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpurN_vwkhOgSJmgBh9</t>
         </is>
       </c>
       <c r="T205" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="U205" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="V205" t="inlineStr"/>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="V205" t="n">
+        <v>2</v>
+      </c>
       <c r="W205" t="n">
         <v>0</v>
       </c>
@@ -23552,12 +23554,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
+          <t>e8414189-54c9-4311-874e-b97f9b7916ae</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>ca-cioos_d4942b86-d362-40a3-9399-c124c4c263bd</t>
+          <t>ca-cioos_48acba27-5e01-4b41-9a0e-f3fc8d809a13</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -23567,7 +23569,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Larval Dungeness crab abundance and size time series along the coast of British Columbia</t>
+          <t>MusselSeg: Semantic Segmentation for Rocky Intertidal Mussel Habitat</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -23585,7 +23587,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Sentinels of Change</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -23613,42 +23615,40 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.8, 48.3], [-123.2, 48.37], [-123.2, 48.65], [-123.0, 48.77], [-123.3, 49.01], [-122.9, 49.25], [-122.6, 49.4], [-123.2, 49.45], [-123.7, 49.54], [-124.5, 49.89], [-124.8, 50.09], [-126.5, 50.79], [-128.3, 52.31], [-130.4, 54.75], [-133.8, 54.36], [-132.9, 52.85], [-130.3, 51.48], [-128.1, 50.15], [-125.2, 48.62], [-123.8, 48.3]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-130.1, 51.59], [-120.4, 31.75], [-118.4, 33.38], [-124.3, 44.43], [-122.0, 49.35], [-126.2, 51.59], [-130.1, 51.59]]]}</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>[{'max': '2.0', 'min': '0.0'}]</t>
+          <t>[{'max': '75.0', 'min': '15.0'}]</t>
         </is>
       </c>
       <c r="Q206" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution</t>
+          <t>other, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>10.21966/36hp-7f40</t>
+          <t>10.21966/fbv4-th96</t>
         </is>
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/57FPdLIBPcb9BOLfIOW44RJVywN2/-N1KAki3SSBEw0aHCoSv</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DCH8GzsQKSM8xwJ8WdQFIZrtCaq2/-O26fyGiVXoF__M22UrP</t>
         </is>
       </c>
       <c r="T206" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="U206" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="V206" t="n">
-        <v>2</v>
-      </c>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr"/>
       <c r="W206" t="n">
         <v>0</v>
       </c>
@@ -23669,12 +23669,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>265e0ec8-1d85-4e73-b85d-371845dbd08f</t>
+          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>ca-cioos_f762a307-6dfb-41a8-a56c-ecacfb075a0a</t>
+          <t>ca-cioos_d4942b86-d362-40a3-9399-c124c4c263bd</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -23684,7 +23684,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Denali Fault - 2024 - Airborne LiDAR Survey</t>
+          <t>Larval Dungeness crab abundance and size time series along the coast of British Columbia</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -23702,12 +23702,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Sentinels of Change</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -23730,40 +23730,42 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-141.3, 62.08], [-139.8, 61.49], [-137.7, 60.61], [-136.8, 60.1], [-136.4, 60.29], [-138.3, 61.12], [-140.1, 61.86], [-141.2, 62.19], [-141.3, 62.08]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.8, 48.3], [-123.2, 48.37], [-123.2, 48.65], [-123.0, 48.77], [-123.3, 49.01], [-122.9, 49.25], [-122.6, 49.4], [-123.2, 49.45], [-123.7, 49.54], [-124.5, 49.89], [-124.8, 50.09], [-126.5, 50.79], [-128.3, 52.31], [-130.4, 54.75], [-133.8, 54.36], [-132.9, 52.85], [-130.3, 51.48], [-128.1, 50.15], [-125.2, 48.62], [-123.8, 48.3]]]}</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>[{'max': '5000.0', 'min': '100.0'}]</t>
+          <t>[{'max': '2.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>10.21966/wxph-tz51</t>
+          <t>10.21966/36hp-7f40</t>
         </is>
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCKOQlOxJdTg_BFOoXb</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/57FPdLIBPcb9BOLfIOW44RJVywN2/-N1KAki3SSBEw0aHCoSv</t>
         </is>
       </c>
       <c r="T207" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="U207" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
-        </is>
-      </c>
-      <c r="V207" t="inlineStr"/>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="V207" t="n">
+        <v>2</v>
+      </c>
       <c r="W207" t="n">
         <v>0</v>
       </c>
@@ -23784,12 +23786,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
+          <t>265e0ec8-1d85-4e73-b85d-371845dbd08f</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>ca-cioos_5185ac00-8148-4472-adfd-21741d8a10ce</t>
+          <t>ca-cioos_f762a307-6dfb-41a8-a56c-ecacfb075a0a</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -23799,7 +23801,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Sentinels of Change Sea Surface Temperature Time Series Data Along the British Columbia Coast</t>
+          <t>Denali Fault - 2024 - Airborne LiDAR Survey</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -23817,12 +23819,12 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Sentinels of Change</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -23845,53 +23847,51 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.6, 48.25], [-123.2, 48.37], [-123.3, 48.71], [-123.0, 48.8], [-123.3, 49.09], [-123.0, 49.1], [-122.4, 49.39], [-122.6, 49.56], [-123.6, 49.55], [-124.8, 50.1], [-125.8, 50.51], [-127.5, 51.15], [-128.6, 52.64], [-130.4, 54.77], [-133.4, 54.37], [-132.8, 52.99], [-130.8, 51.58], [-128.3, 50.21], [-126.5, 49.17], [-125.2, 48.63], [-124.3, 48.43], [-123.6, 48.25]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-141.3, 62.08], [-139.8, 61.49], [-137.7, 60.61], [-136.8, 60.1], [-136.4, 60.29], [-138.3, 61.12], [-140.1, 61.86], [-141.2, 62.19], [-141.3, 62.08]]]}</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>[{'max': '0.5', 'min': '0.5'}]</t>
+          <t>[{'max': '5000.0', 'min': '100.0'}]</t>
         </is>
       </c>
       <c r="Q208" t="inlineStr">
         <is>
-          <t>seaSurfaceTemperature</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>10.21966/4kr2-jc55</t>
+          <t>10.21966/wxph-tz51</t>
         </is>
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/57FPdLIBPcb9BOLfIOW44RJVywN2/-NH0r8ddHNhVJ5bXkyqR</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCKOQlOxJdTg_BFOoXb</t>
         </is>
       </c>
       <c r="T208" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="U208" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="V208" t="n">
-        <v>2</v>
-      </c>
+          <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr"/>
       <c r="W208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X208" t="inlineStr">
         <is>
-          <t>[{'year': '2024', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.21966/36hp-7f40', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_d4942b86-d362-40a3-9399-c124c4c263bd'}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -23901,12 +23901,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
+          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>ca-cioos_7fd3ec6c-083a-4942-84b4-215e69492072</t>
+          <t>ca-cioos_5185ac00-8148-4472-adfd-21741d8a10ce</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -23916,7 +23916,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Phytoplankton Pigment Timeseries from High-Performance Liquid Chromatography for the Northern Salish Sea and Central Coast, BC, Canada (Research)</t>
+          <t>Sentinels of Change Sea Surface Temperature Time Series Data Along the British Columbia Coast</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -23934,7 +23934,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Sentinels of Change</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -23962,32 +23962,32 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.6, 48.25], [-123.2, 48.37], [-123.3, 48.71], [-123.0, 48.8], [-123.3, 49.09], [-123.0, 49.1], [-122.4, 49.39], [-122.6, 49.56], [-123.6, 49.55], [-124.8, 50.1], [-125.8, 50.51], [-127.5, 51.15], [-128.6, 52.64], [-130.4, 54.77], [-133.4, 54.37], [-132.8, 52.99], [-130.8, 51.58], [-128.3, 50.21], [-126.5, 49.17], [-125.2, 48.63], [-124.3, 48.43], [-123.6, 48.25]]]}</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.5', 'min': '0.5'}]</t>
         </is>
       </c>
       <c r="Q209" t="inlineStr">
         <is>
-          <t>phytoplanktonBiomassAndDiversity</t>
+          <t>seaSurfaceTemperature</t>
         </is>
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>10.21966/bw2d-tg65</t>
+          <t>10.21966/4kr2-jc55</t>
         </is>
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-O25qzW3OpioeACGpRHl</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/57FPdLIBPcb9BOLfIOW44RJVywN2/-NH0r8ddHNhVJ5bXkyqR</t>
         </is>
       </c>
       <c r="T209" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="U209" t="inlineStr">
@@ -23999,16 +23999,16 @@
         <v>2</v>
       </c>
       <c r="W209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X209" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2024', 'total': 1}]</t>
         </is>
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'citations', 'id': '10.21966/36hp-7f40', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_d4942b86-d362-40a3-9399-c124c4c263bd'}]</t>
         </is>
       </c>
     </row>
@@ -24018,12 +24018,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>0781c19a-7efb-4680-92fd-8cd5faf0cfe4</t>
+          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>ca-cioos_af344fb9-4901-470c-a441-41f11ee2ccd7</t>
+          <t>ca-cioos_7fd3ec6c-083a-4942-84b4-215e69492072</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -24033,7 +24033,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>iTrack Oysters February 2023 Experiment - Environmental and Oyster Health Data</t>
+          <t>Phytoplankton Pigment Timeseries from High-Performance Liquid Chromatography for the Northern Salish Sea and Central Coast, BC, Canada (Research)</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -24051,12 +24051,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Wet Lab</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -24071,7 +24071,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N210" t="n">
@@ -24079,40 +24079,42 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q210" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>phytoplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>10.21966/pvy6-nw38</t>
+          <t>10.21966/bw2d-tg65</t>
         </is>
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-O0G3gSlISPfB-f0u3Zz</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-O25qzW3OpioeACGpRHl</t>
         </is>
       </c>
       <c r="T210" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="U210" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
-        </is>
-      </c>
-      <c r="V210" t="inlineStr"/>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="V210" t="n">
+        <v>2</v>
+      </c>
       <c r="W210" t="n">
         <v>0</v>
       </c>
@@ -24133,12 +24135,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>0781c19a-7efb-4680-92fd-8cd5faf0cfe4</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>ca-cioos_9fafb4c8-e61f-4372-ac71-c1ddbe57d80c</t>
+          <t>ca-cioos_af344fb9-4901-470c-a441-41f11ee2ccd7</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -24148,7 +24150,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Data record does not exist anymore: Geomorphology - Calvert Island</t>
+          <t>iTrack Oysters February 2023 Experiment - Environmental and Oyster Health Data</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -24164,7 +24166,11 @@
       <c r="H211" t="b">
         <v>0</v>
       </c>
-      <c r="I211" t="inlineStr"/>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Wet Lab</t>
+        </is>
+      </c>
       <c r="J211" t="inlineStr">
         <is>
           <t>completed</t>
@@ -24182,7 +24188,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N211" t="n">
@@ -24190,41 +24196,53 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.2489013671875, 51.40605940499276], [-127.83142089843751, 51.40605940499276], [-127.83142089843751, 51.75934048406748], [-128.2489013671875, 51.75934048406748], [-128.2489013671875, 51.40605940499276]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q211" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R211" t="inlineStr"/>
+          <t>other, inorganicCarbon</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>10.21966/pvy6-nw38</t>
+        </is>
+      </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OFhFpUJDNDF0hlFiGUV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-O0G3gSlISPfB-f0u3Zz</t>
         </is>
       </c>
       <c r="T211" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="U211" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
-        </is>
-      </c>
-      <c r="V211" t="n">
-        <v>4</v>
-      </c>
-      <c r="W211" t="inlineStr"/>
-      <c r="X211" t="inlineStr"/>
-      <c r="Y211" t="inlineStr"/>
+          <t>2024-12-19</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr"/>
+      <c r="W211" t="n">
+        <v>0</v>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -24232,12 +24250,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>ca-cioos_d7ffd737-5725-4a56-9134-a9ad91c2734d</t>
+          <t>ca-cioos_9fafb4c8-e61f-4372-ac71-c1ddbe57d80c</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -24247,7 +24265,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Seton and Anderson Lake Multibeam Survey - 2024 - British Columbia</t>
+          <t>Data record does not exist anymore: Geomorphology - Calvert Island</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -24263,11 +24281,7 @@
       <c r="H212" t="b">
         <v>0</v>
       </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>Geospatial</t>
-        </is>
-      </c>
+      <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr">
         <is>
           <t>completed</t>
@@ -24293,12 +24307,12 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.4, 50.62], [-122.0, 50.62], [-122.0, 50.75], [-122.4, 50.75], [-122.4, 50.62]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.2489013671875, 51.40605940499276], [-127.83142089843751, 51.40605940499276], [-127.83142089843751, 51.75934048406748], [-128.2489013671875, 51.75934048406748], [-128.2489013671875, 51.40605940499276]]]}</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>[{'max': '254.0', 'min': '61.0'}]</t>
+          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q212" t="inlineStr">
@@ -24306,42 +24320,28 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R212" t="inlineStr">
-        <is>
-          <t>10.21966/zfxe-rd73</t>
-        </is>
-      </c>
+      <c r="R212" t="inlineStr"/>
       <c r="S212" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCe-GBA4i93dk_I9uOR</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OFhFpUJDNDF0hlFiGUV</t>
         </is>
       </c>
       <c r="T212" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="U212" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="V212" t="n">
-        <v>2</v>
-      </c>
-      <c r="W212" t="n">
-        <v>0</v>
-      </c>
-      <c r="X212" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y212" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="W212" t="inlineStr"/>
+      <c r="X212" t="inlineStr"/>
+      <c r="Y212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -24349,12 +24349,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>4a949e26-fe94-4f63-a3c6-a62e19301102</t>
+          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>ca-cioos_35beb32e-8dc9-42ab-9630-2ae23e414026</t>
+          <t>ca-cioos_d7ffd737-5725-4a56-9134-a9ad91c2734d</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -24364,7 +24364,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Rocky Subtidal Fish and Invertebrate Community Surveys from the Central Coast of BC</t>
+          <t>Seton and Anderson Lake Multibeam Survey - 2024 - British Columbia</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -24382,12 +24382,12 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -24410,41 +24410,41 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.7, 51.35], [-127.3, 51.35], [-127.3, 52.27], [-128.7, 52.27], [-128.7, 51.35]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.4, 50.62], [-122.0, 50.62], [-122.0, 50.75], [-122.4, 50.75], [-122.4, 50.62]]]}</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>[{'max': '15.0', 'min': '0.0'}]</t>
+          <t>[{'max': '254.0', 'min': '61.0'}]</t>
         </is>
       </c>
       <c r="Q213" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>10.21966/jj9p-d309</t>
+          <t>10.21966/zfxe-rd73</t>
         </is>
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtF5vh1GUMdwtJdYjoJ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCe-GBA4i93dk_I9uOR</t>
         </is>
       </c>
       <c r="T213" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="U213" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="V213" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W213" t="n">
         <v>0</v>
@@ -24466,12 +24466,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>7fa8cfec-e2e3-4459-9b9d-836335b9fcfa</t>
+          <t>4a949e26-fe94-4f63-a3c6-a62e19301102</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>ca-cioos_00f42725-0a88-4d4f-87a9-4e359d2abff4</t>
+          <t>ca-cioos_35beb32e-8dc9-42ab-9630-2ae23e414026</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -24481,7 +24481,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Knight Inlet Remotely Operated Vehicle Marine Habitat Survey</t>
+          <t>Rocky Subtidal Fish and Invertebrate Community Surveys from the Central Coast of BC</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -24499,12 +24499,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -24527,40 +24527,42 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.0, 50.65], [-125.9, 50.65], [-125.9, 50.71], [-126.0, 50.71], [-126.0, 50.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.7, 51.35], [-127.3, 51.35], [-127.3, 52.27], [-128.7, 52.27], [-128.7, 51.35]]]}</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>[{'max': '105.0', 'min': '0.0'}]</t>
+          <t>[{'max': '15.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q214" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>10.21966/529y-sh57</t>
+          <t>10.21966/jj9p-d309</t>
         </is>
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OG736nDr1-1b51V4ZIc</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtF5vh1GUMdwtJdYjoJ</t>
         </is>
       </c>
       <c r="T214" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="U214" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="V214" t="inlineStr"/>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="V214" t="n">
+        <v>1</v>
+      </c>
       <c r="W214" t="n">
         <v>0</v>
       </c>
@@ -24581,12 +24583,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>5576c279-6d3a-4323-8104-0e1040d9906c</t>
+          <t>7fa8cfec-e2e3-4459-9b9d-836335b9fcfa</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>ca-cioos_314a0846-0fe9-4c2e-81e2-d2b24ac98b6e</t>
+          <t>ca-cioos_00f42725-0a88-4d4f-87a9-4e359d2abff4</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -24596,7 +24598,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Understory kelp biomass data from BC Central Coast</t>
+          <t>Knight Inlet Remotely Operated Vehicle Marine Habitat Survey</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -24614,12 +24616,12 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -24642,37 +24644,37 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.7, 51.33], [-127.4, 51.33], [-127.4, 52.26], [-128.7, 52.26], [-128.7, 51.33]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.0, 50.65], [-125.9, 50.65], [-125.9, 50.71], [-126.0, 50.71], [-126.0, 50.65]]]}</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '105.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q215" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>10.21966/wmsy-5g39</t>
+          <t>10.21966/529y-sh57</t>
         </is>
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtGQFN6AV5bNminNtYH</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OG736nDr1-1b51V4ZIc</t>
         </is>
       </c>
       <c r="T215" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="U215" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="V215" t="inlineStr"/>
@@ -24696,12 +24698,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>cc016896-78d9-46e8-887d-6c1dd106c0e8</t>
+          <t>5576c279-6d3a-4323-8104-0e1040d9906c</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>ca-cioos_52d4f546-dfdf-4bf1-b1ad-f6ec6f2663c0</t>
+          <t>ca-cioos_314a0846-0fe9-4c2e-81e2-d2b24ac98b6e</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -24711,7 +24713,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Bute Inlet Geo-Hazards &amp; Ramsay West - 2024 - Airborne Coastal Observatory</t>
+          <t>Understory kelp biomass data from BC Central Coast</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -24729,12 +24731,12 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -24757,42 +24759,40 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.5, 50.23], [-124.1, 50.23], [-124.1, 51.73], [-125.5, 51.73], [-125.5, 50.23]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.7, 51.33], [-127.4, 51.33], [-127.4, 52.26], [-128.7, 52.26], [-128.7, 51.33]]]}</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>[{'max': '2500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q216" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>10.21966/8yp1-7m94</t>
+          <t>10.21966/wmsy-5g39</t>
         </is>
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCKR1jead4rZb1ooVa6</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtGQFN6AV5bNminNtYH</t>
         </is>
       </c>
       <c r="T216" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="U216" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="V216" t="n">
-        <v>1</v>
-      </c>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr"/>
       <c r="W216" t="n">
         <v>0</v>
       </c>
@@ -24813,12 +24813,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>046e5ef5-1480-4868-a65f-23171088bdb8</t>
+          <t>cc016896-78d9-46e8-887d-6c1dd106c0e8</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>ca-cioos_31e15496-e906-43f4-9120-2446ab6125b2</t>
+          <t>ca-cioos_52d4f546-dfdf-4bf1-b1ad-f6ec6f2663c0</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -24828,7 +24828,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Elliot Creek Aerial Photo and LiDAR Survey</t>
+          <t>Bute Inlet Geo-Hazards &amp; Ramsay West - 2024 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -24846,7 +24846,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -24874,12 +24874,12 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.8, 50.84], [-124.5, 50.84], [-124.5, 50.99], [-124.8, 50.99], [-124.8, 50.84]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.5, 50.23], [-124.1, 50.23], [-124.1, 51.73], [-125.5, 51.73], [-125.5, 50.23]]]}</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>[{'max': '2650.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q217" t="inlineStr">
@@ -24889,25 +24889,27 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>10.21966/g64t-ec45</t>
+          <t>10.21966/8yp1-7m94</t>
         </is>
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICfZ5e-2vhf5NUtDZS</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCKR1jead4rZb1ooVa6</t>
         </is>
       </c>
       <c r="T217" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="U217" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="V217" t="inlineStr"/>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="V217" t="n">
+        <v>1</v>
+      </c>
       <c r="W217" t="n">
         <v>0</v>
       </c>
@@ -24928,12 +24930,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>8ce79018-75da-42f8-b7cd-195a412ab532</t>
+          <t>046e5ef5-1480-4868-a65f-23171088bdb8</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>ca-cioos_98807d0a-ba68-41e3-a2f5-e3248b459904</t>
+          <t>ca-cioos_31e15496-e906-43f4-9120-2446ab6125b2</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -24943,7 +24945,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Place Glacier Aerial Photo and LiDAR Survey</t>
+          <t>Elliot Creek Aerial Photo and LiDAR Survey</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -24981,7 +24983,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Tula Foundation</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N218" t="n">
@@ -24989,12 +24991,12 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.7, 50.39], [-122.6, 50.39], [-122.6, 50.48], [-122.7, 50.48], [-122.7, 50.39]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.8, 50.84], [-124.5, 50.84], [-124.5, 50.99], [-124.8, 50.99], [-124.8, 50.84]]]}</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>[{'max': '2587.0', 'min': '500.0'}]</t>
+          <t>[{'max': '2650.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q218" t="inlineStr">
@@ -25004,12 +25006,12 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>10.21966/0ydj-0t79</t>
+          <t>10.21966/g64t-ec45</t>
         </is>
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICMGpnoARQcIltW087</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICfZ5e-2vhf5NUtDZS</t>
         </is>
       </c>
       <c r="T218" t="inlineStr">
@@ -25043,12 +25045,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>83f387d2-f77e-4921-af15-e064d87ad01a</t>
+          <t>8ce79018-75da-42f8-b7cd-195a412ab532</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>ca-cioos_53730b70-be6f-4e24-8b9d-4a5e2c491121</t>
+          <t>ca-cioos_98807d0a-ba68-41e3-a2f5-e3248b459904</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -25058,12 +25060,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Cloud-Based LiDAR Application - ELVIZ - Place Glacier, Mt. Robson, and Elliot Creek, BC</t>
+          <t>Place Glacier Aerial Photo and LiDAR Survey</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>dataset</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -25096,7 +25098,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Tula Foundation</t>
         </is>
       </c>
       <c r="N219" t="n">
@@ -25104,12 +25106,12 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.5, 50.34], [-118.7, 50.34], [-118.7, 53.28], [-124.5, 53.28], [-124.5, 50.34]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.7, 50.39], [-122.6, 50.39], [-122.6, 50.48], [-122.7, 50.48], [-122.7, 50.39]]]}</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>[{'max': '3954.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2587.0', 'min': '500.0'}]</t>
         </is>
       </c>
       <c r="Q219" t="inlineStr">
@@ -25119,27 +25121,25 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>10.21966/6x1v-1v62</t>
+          <t>10.21966/0ydj-0t79</t>
         </is>
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OIMCEnEEW63IyHyYZOM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICMGpnoARQcIltW087</t>
         </is>
       </c>
       <c r="T219" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="U219" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="V219" t="n">
-        <v>1</v>
-      </c>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr"/>
       <c r="W219" t="n">
         <v>0</v>
       </c>
@@ -25160,12 +25160,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
+          <t>83f387d2-f77e-4921-af15-e064d87ad01a</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>ca-cioos_78818ed7-ec26-4004-afa1-137741ddda1e</t>
+          <t>ca-cioos_53730b70-be6f-4e24-8b9d-4a5e2c491121</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -25175,12 +25175,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Calliarthron 2023 Experiment - Environmental Data</t>
+          <t>Cloud-Based LiDAR Application - ELVIZ - Place Glacier, Mt. Robson, and Elliot Creek, BC</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>service</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -25193,7 +25193,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Wet Lab</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -25213,7 +25213,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>University of British Columbia</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N220" t="n">
@@ -25221,37 +25221,37 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.5, 50.34], [-118.7, 50.34], [-118.7, 53.28], [-124.5, 53.28], [-124.5, 50.34]]]}</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '3954.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q220" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>10.21966/7nwn-bj60</t>
+          <t>10.21966/6x1v-1v62</t>
         </is>
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-O6XAwxhj0r9Xs-V2QSA</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OIMCEnEEW63IyHyYZOM</t>
         </is>
       </c>
       <c r="T220" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="U220" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="V220" t="n">
@@ -25277,12 +25277,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
+          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>ca-cioos_87341cb3-f906-4fa5-973c-b6742aa0fbb5</t>
+          <t>ca-cioos_78818ed7-ec26-4004-afa1-137741ddda1e</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -25292,7 +25292,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Glacier and Ice Aerial Surveys in British Columbia - 2023-2024 - Hakai Airborne Coastal Observatory</t>
+          <t>Calliarthron 2023 Experiment - Environmental Data</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -25310,7 +25310,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Wet Lab</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -25330,7 +25330,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="N221" t="n">
@@ -25338,27 +25338,27 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.9, 48.81], [-115.2, 48.81], [-115.2, 54.38], [-128.9, 54.38], [-128.9, 48.81]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>[{'max': '3954.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q221" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>10.21966/ks82-th39</t>
+          <t>10.21966/7nwn-bj60</t>
         </is>
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OP2QaXeKeZ30lz51gEE</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-O6XAwxhj0r9Xs-V2QSA</t>
         </is>
       </c>
       <c r="T221" t="inlineStr">
@@ -25368,11 +25368,11 @@
       </c>
       <c r="U221" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="V221" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W221" t="n">
         <v>0</v>
@@ -25394,12 +25394,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>6c99bd67-3be1-4818-bf01-dfa56e910db3</t>
+          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>ca-cioos_96e3dd9c-7863-44d5-95cd-a3d0a8653d83</t>
+          <t>ca-cioos_87341cb3-f906-4fa5-973c-b6742aa0fbb5</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -25409,7 +25409,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Glacier and Ice Aerial Surveys in British Columbia - 2022 - Hakai Airborne Coastal Observatory</t>
+          <t>Glacier and Ice Aerial Surveys in British Columbia - 2023-2024 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -25427,7 +25427,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -25455,12 +25455,12 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.8, 48.1], [-113.1, 48.1], [-113.1, 56.61], [-127.8, 56.61], [-127.8, 48.1]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.9, 48.81], [-115.2, 48.81], [-115.2, 54.38], [-128.9, 54.38], [-128.9, 48.81]]]}</t>
         </is>
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>[{'max': '4000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '3954.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q222" t="inlineStr">
@@ -25470,12 +25470,12 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>10.21966/n3b4-d226</t>
+          <t>10.21966/ks82-th39</t>
         </is>
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NM0zdQjdjAMBZ4cN8ou</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OP2QaXeKeZ30lz51gEE</t>
         </is>
       </c>
       <c r="T222" t="inlineStr">
@@ -25485,18 +25485,18 @@
       </c>
       <c r="U222" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="V222" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W222" t="n">
         <v>0</v>
       </c>
       <c r="X222" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Y222" t="inlineStr">
@@ -25511,12 +25511,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
+          <t>6c99bd67-3be1-4818-bf01-dfa56e910db3</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>ca-cioos_47d8bdd4-c815-4e8d-8d75-53a9db4ae46a</t>
+          <t>ca-cioos_96e3dd9c-7863-44d5-95cd-a3d0a8653d83</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -25526,7 +25526,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Glaciers in Western North America Mass Loss Geospatial Data (2021-2024)</t>
+          <t>Glacier and Ice Aerial Surveys in British Columbia - 2022 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -25572,12 +25572,12 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.3, 54.17], [-119.5, 55.38], [-112.5, 52.06], [-115.3, 47.05], [-125.9, 48.0], [-128.3, 51.41], [-127.3, 54.17]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.8, 48.1], [-113.1, 48.1], [-113.1, 56.61], [-127.8, 56.61], [-127.8, 48.1]]]}</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>[{'max': '2822.0', 'min': '0.0'}]</t>
+          <t>[{'max': '4000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q223" t="inlineStr">
@@ -25587,33 +25587,33 @@
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>10.21966/p6jv-pe95</t>
+          <t>10.21966/n3b4-d226</t>
         </is>
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OP86akjVj471Wit4O2y</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NM0zdQjdjAMBZ4cN8ou</t>
         </is>
       </c>
       <c r="T223" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="U223" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="V223" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W223" t="n">
         <v>0</v>
       </c>
       <c r="X223" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2025', 'total': 1}]</t>
         </is>
       </c>
       <c r="Y223" t="inlineStr">
@@ -25628,12 +25628,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
+          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>ca-cioos_1d142201-cbbe-4c58-b2c2-1feeac112c51</t>
+          <t>ca-cioos_47d8bdd4-c815-4e8d-8d75-53a9db4ae46a</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -25643,7 +25643,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>iTrack Oysters September 2023 Experiment - Environmental and Oyster Health Data</t>
+          <t>Glaciers in Western North America Mass Loss Geospatial Data (2021-2024)</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -25661,7 +25661,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Wet Lab</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -25681,7 +25681,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N224" t="n">
@@ -25689,41 +25689,41 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.3, 54.17], [-119.5, 55.38], [-112.5, 52.06], [-115.3, 47.05], [-125.9, 48.0], [-128.3, 51.41], [-127.3, 54.17]]]}</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '2822.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q224" t="inlineStr">
         <is>
-          <t>inorganicCarbon, other</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>10.21966/q1m4-pz94</t>
+          <t>10.21966/p6jv-pe95</t>
         </is>
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-OMsFWHXIwEWiFjwQeEo</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OP86akjVj471Wit4O2y</t>
         </is>
       </c>
       <c r="T224" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="U224" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="V224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W224" t="n">
         <v>0</v>
@@ -25745,12 +25745,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>da040f55-984d-490d-b917-a67856de4bac</t>
+          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>ca-cioos_31ac855d-bf15-42d8-b20d-754638202c66</t>
+          <t>ca-cioos_1d142201-cbbe-4c58-b2c2-1feeac112c51</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -25760,7 +25760,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Sea Stars 2024 Experiment - Environmental Data</t>
+          <t>iTrack Oysters September 2023 Experiment - Environmental and Oyster Health Data</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -25798,7 +25798,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N225" t="n">
@@ -25821,12 +25821,12 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>10.21966/jkf5-ss08</t>
+          <t>10.21966/q1m4-pz94</t>
         </is>
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-OIMW8OO0buhOm_kHuIz</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-OMsFWHXIwEWiFjwQeEo</t>
         </is>
       </c>
       <c r="T225" t="inlineStr">
@@ -25862,12 +25862,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
+          <t>da040f55-984d-490d-b917-a67856de4bac</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>ca-cioos_d959f8f3-6d20-42fe-94da-be49bcd3aeca</t>
+          <t>ca-cioos_31ac855d-bf15-42d8-b20d-754638202c66</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -25877,7 +25877,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Eelgrass (Z. marina) extent at Gulf Islands National Park Reserve eelgrass monitoring sites (2024)</t>
+          <t>Sea Stars 2024 Experiment - Environmental Data</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -25895,7 +25895,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Wet Lab</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -25915,15 +25915,15 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Gulf Islands National Park Reserve</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N226" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.4, 48.61], [-123.0, 48.61], [-123.0, 48.87], [-123.4, 48.87], [-123.4, 48.61]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -25933,31 +25933,31 @@
       </c>
       <c r="Q226" t="inlineStr">
         <is>
-          <t>other, seagrassCoverAndComposition</t>
+          <t>inorganicCarbon, other</t>
         </is>
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>10.21966/x3jm-p494</t>
+          <t>10.21966/jkf5-ss08</t>
         </is>
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OUG8anVj4yBJDEHy6Wj</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-OIMW8OO0buhOm_kHuIz</t>
         </is>
       </c>
       <c r="T226" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="U226" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="V226" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W226" t="n">
         <v>0</v>
@@ -25979,12 +25979,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>ca-cioos_39a83551-ab8e-45be-a564-cece4b229371</t>
+          <t>ca-cioos_d959f8f3-6d20-42fe-94da-be49bcd3aeca</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -25994,7 +25994,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Zooplankton taxonomic abundance and biomass along the BC Coast</t>
+          <t>Eelgrass (Z. marina) extent at Gulf Islands National Park Reserve eelgrass monitoring sites (2024)</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -26012,12 +26012,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -26032,7 +26032,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Gulf Islands National Park Reserve</t>
         </is>
       </c>
       <c r="N227" t="n">
@@ -26040,53 +26040,53 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.4, 48.61], [-123.0, 48.61], [-123.0, 48.87], [-123.4, 48.87], [-123.4, 48.61]]]}</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>[{'max': '350.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q227" t="inlineStr">
         <is>
-          <t>zooplanktonBiomassAndDiversity</t>
+          <t>other, seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>10.21966/g7zf-1v08</t>
+          <t>10.21966/x3jm-p494</t>
         </is>
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-ODO1YbIGbR3Rd8hvLxT</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OUG8anVj4yBJDEHy6Wj</t>
         </is>
       </c>
       <c r="T227" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="U227" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="V227" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W227" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X227" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 2}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>[{'relationship': 'references', 'id': '10.21966/g7zf-1v08', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_39a83551-ab8e-45be-a564-cece4b229371'}, {'relationship': 'references', 'id': '10.21966/tcp2-mm86', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_dbb33efe-c207-4d9c-abef-2350595bf47a'}, {'relationship': 'citations', 'id': '10.21966/g7zf-1v08', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_39a83551-ab8e-45be-a564-cece4b229371'}, {'relationship': 'citations', 'id': '10.21966/kace-2d24', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_ba41d935-f293-447f-be3d-7098e569b431'}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -26096,12 +26096,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>ca-cioos_dbb33efe-c207-4d9c-abef-2350595bf47a</t>
+          <t>ca-cioos_39a83551-ab8e-45be-a564-cece4b229371</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -26111,7 +26111,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Size-fractionated zooplankton biomass and isotopes along the BC coast</t>
+          <t>Zooplankton taxonomic abundance and biomass along the BC Coast</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -26153,7 +26153,7 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O228" t="inlineStr">
         <is>
@@ -26172,12 +26172,12 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>10.21966/tcp2-mm86</t>
+          <t>10.21966/g7zf-1v08</t>
         </is>
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/NZb1YZT9Xtbc9Cp9Jc3OtSLRffT2/-OQtxgedRzyaVsL4bWUx</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-ODO1YbIGbR3Rd8hvLxT</t>
         </is>
       </c>
       <c r="T228" t="inlineStr">
@@ -26191,7 +26191,7 @@
         </is>
       </c>
       <c r="V228" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W228" t="n">
         <v>2</v>
@@ -26203,7 +26203,7 @@
       </c>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.21966/kace-2d24', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_ba41d935-f293-447f-be3d-7098e569b431'}, {'relationship': 'citations', 'id': '10.21966/g7zf-1v08', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_39a83551-ab8e-45be-a564-cece4b229371'}]</t>
+          <t>[{'relationship': 'references', 'id': '10.21966/g7zf-1v08', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_39a83551-ab8e-45be-a564-cece4b229371'}, {'relationship': 'references', 'id': '10.21966/tcp2-mm86', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_dbb33efe-c207-4d9c-abef-2350595bf47a'}, {'relationship': 'citations', 'id': '10.21966/g7zf-1v08', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_39a83551-ab8e-45be-a564-cece4b229371'}, {'relationship': 'citations', 'id': '10.21966/kace-2d24', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_ba41d935-f293-447f-be3d-7098e569b431'}]</t>
         </is>
       </c>
     </row>
@@ -26213,12 +26213,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>328b062b-3af6-4149-b90f-a85b99dc40eb</t>
+          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>ca-cioos_34a20547-cb60-4ecf-901b-f4ca52eae451</t>
+          <t>ca-cioos_dbb33efe-c207-4d9c-abef-2350595bf47a</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -26228,7 +26228,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), Central Coast, British Columbia, Canada</t>
+          <t>Size-fractionated zooplankton biomass and isotopes along the BC coast</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -26246,12 +26246,12 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -26274,53 +26274,53 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.4], [-127.9, 51.4], [-127.9, 52.09], [-128.5, 52.09], [-128.5, 51.4]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '350.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q229" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>zooplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>10.21966/w08z-zk15</t>
+          <t>10.21966/tcp2-mm86</t>
         </is>
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8sPFZem68YnizN7L7l</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/NZb1YZT9Xtbc9Cp9Jc3OtSLRffT2/-OQtxgedRzyaVsL4bWUx</t>
         </is>
       </c>
       <c r="T229" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="U229" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="V229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W229" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X229" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2025', 'total': 2}]</t>
         </is>
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'citations', 'id': '10.21966/kace-2d24', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_ba41d935-f293-447f-be3d-7098e569b431'}, {'relationship': 'citations', 'id': '10.21966/g7zf-1v08', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_39a83551-ab8e-45be-a564-cece4b229371'}]</t>
         </is>
       </c>
     </row>
@@ -26330,12 +26330,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>439d703a-2132-4dbd-8d39-a4cacdb8f81d</t>
+          <t>328b062b-3af6-4149-b90f-a85b99dc40eb</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>ca-cioos_e8343aa0-dbea-4267-9f78-662bec08d4bc</t>
+          <t>ca-cioos_34a20547-cb60-4ecf-901b-f4ca52eae451</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -26345,7 +26345,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020-2022), Central Coast, British Columbia, Canada</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -26391,7 +26391,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 52.15], [-128.5, 52.23], [-128.2, 52.05], [-128.0, 51.71], [-128.0, 51.63], [-128.2, 51.62], [-128.4, 51.8], [-128.6, 51.89], [-128.6, 51.89], [-128.6, 52.15]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.4], [-127.9, 51.4], [-127.9, 52.09], [-128.5, 52.09], [-128.5, 51.4]]]}</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -26406,12 +26406,12 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>10.21966/kqzp-f639</t>
+          <t>10.21966/w08z-zk15</t>
         </is>
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-NbzgAmVWcvz-_SOMA0E</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8sPFZem68YnizN7L7l</t>
         </is>
       </c>
       <c r="T230" t="inlineStr">
@@ -26421,10 +26421,12 @@
       </c>
       <c r="U230" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="V230" t="inlineStr"/>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="V230" t="n">
+        <v>1</v>
+      </c>
       <c r="W230" t="n">
         <v>0</v>
       </c>
@@ -26445,12 +26447,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
+          <t>439d703a-2132-4dbd-8d39-a4cacdb8f81d</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>ca-cioos_f7a867ce-0f18-43f6-8148-775235d800b6</t>
+          <t>ca-cioos_e8343aa0-dbea-4267-9f78-662bec08d4bc</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -26460,7 +26462,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2023), Central Coast, British Columbia, Canada</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020-2022), Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -26478,7 +26480,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
+          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -26506,7 +26508,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.64], [-128.1, 51.64], [-128.1, 52.19], [-128.6, 52.19], [-128.6, 51.64]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 52.15], [-128.5, 52.23], [-128.2, 52.05], [-128.0, 51.71], [-128.0, 51.63], [-128.2, 51.62], [-128.4, 51.8], [-128.6, 51.89], [-128.6, 51.89], [-128.6, 52.15]]]}</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
@@ -26521,12 +26523,12 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>10.21966/qs1b-g693</t>
+          <t>10.21966/kqzp-f639</t>
         </is>
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-O8Dvx_fnz1WMY_Wetch</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-NbzgAmVWcvz-_SOMA0E</t>
         </is>
       </c>
       <c r="T231" t="inlineStr">
@@ -26536,12 +26538,10 @@
       </c>
       <c r="U231" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="V231" t="n">
-        <v>3</v>
-      </c>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr"/>
       <c r="W231" t="n">
         <v>0</v>
       </c>
@@ -26562,12 +26562,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
+          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>ca-cioos_291b98a4-d868-462c-852a-d6cf79ecf6ce</t>
+          <t>ca-cioos_f7a867ce-0f18-43f6-8148-775235d800b6</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -26577,7 +26577,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Time series of surface kelp canopy area derived from remotely piloted aerial systems (RPAS, or drone) surveys, Central Coast, British Columbia</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2023), Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -26595,12 +26595,12 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Nearshore, Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -26615,7 +26615,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Tula Foundation</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N232" t="n">
@@ -26623,7 +26623,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.65], [-128.1, 51.65], [-128.1, 52.09], [-128.4, 52.09], [-128.4, 51.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.64], [-128.1, 51.64], [-128.1, 52.19], [-128.6, 52.19], [-128.6, 51.64]]]}</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
@@ -26638,26 +26638,26 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>10.21966/9cbv-ra30</t>
+          <t>10.21966/qs1b-g693</t>
         </is>
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OVIwXhdGT9n7FV0wmyz</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-O8Dvx_fnz1WMY_Wetch</t>
         </is>
       </c>
       <c r="T232" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="U232" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="V232" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W232" t="n">
         <v>0</v>
@@ -26679,12 +26679,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>44bdc298-1329-400a-bc02-4d35d251865d</t>
+          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>ca-cioos_012164c6-28dd-4078-b702-f0c2ce63d548</t>
+          <t>ca-cioos_291b98a4-d868-462c-852a-d6cf79ecf6ce</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -26694,7 +26694,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Biodiversity and Oceanographic data from the False Creek Bioblitz, 2022</t>
+          <t>Time series of surface kelp canopy area derived from remotely piloted aerial systems (RPAS, or drone) surveys, Central Coast, British Columbia</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -26712,12 +26712,12 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Genomics, Nearshore, Oceanography</t>
+          <t>Nearshore, Geospatial</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -26732,48 +26732,50 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Tula Foundation</t>
         </is>
       </c>
       <c r="N233" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.2, 49.27], [-123.1, 49.27], [-123.1, 49.28], [-123.2, 49.28], [-123.2, 49.27]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.65], [-128.1, 51.65], [-128.1, 52.09], [-128.4, 52.09], [-128.4, 51.65]]]}</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q233" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution, marineTurtlesBirdsMammalsAbundanceAndDistribution, fishAbundanceAndDistribution, seaSurfaceTemperature, subSurfaceTemperature, other, microbeBiomassAndDiversity</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>10.21966/8sgn-jg38</t>
+          <t>10.21966/9cbv-ra30</t>
         </is>
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-Nd0YqVrleM4mMLlJDSU</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OVIwXhdGT9n7FV0wmyz</t>
         </is>
       </c>
       <c r="T233" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="U233" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="V233" t="inlineStr"/>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="V233" t="n">
+        <v>2</v>
+      </c>
       <c r="W233" t="n">
         <v>0</v>
       </c>
@@ -26794,12 +26796,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
+          <t>44bdc298-1329-400a-bc02-4d35d251865d</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>ca-cioos_7e9c97a3-4bf1-4852-81b6-d74cedf2c94c</t>
+          <t>ca-cioos_012164c6-28dd-4078-b702-f0c2ce63d548</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -26809,7 +26811,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Environmental DNA survey of Calvert Island, British Columbia, 2021</t>
+          <t>Biodiversity and Oceanographic data from the False Creek Bioblitz, 2022</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -26827,7 +26829,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>Genomics</t>
+          <t>Genomics, Nearshore, Oceanography</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -26851,46 +26853,44 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.31], [-127.3, 51.31], [-127.3, 52.05], [-128.6, 52.05], [-128.6, 51.31]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.2, 49.27], [-123.1, 49.27], [-123.1, 49.28], [-123.2, 49.28], [-123.2, 49.27]]]}</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>[{'max': '60.0', 'min': '0.0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q234" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
+          <t>invertebrateAbundanceAndDistribution, marineTurtlesBirdsMammalsAbundanceAndDistribution, fishAbundanceAndDistribution, seaSurfaceTemperature, subSurfaceTemperature, other, microbeBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>10.21966/vdyq-r660</t>
+          <t>10.21966/8sgn-jg38</t>
         </is>
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-ORCQx4QHUuJ1NV1SEig</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-Nd0YqVrleM4mMLlJDSU</t>
         </is>
       </c>
       <c r="T234" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="U234" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="V234" t="n">
-        <v>2</v>
-      </c>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr"/>
       <c r="W234" t="n">
         <v>0</v>
       </c>
@@ -26911,12 +26911,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
+          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>ca-cioos_9a018fe0-8bd1-41d1-af8d-079960b71473</t>
+          <t>ca-cioos_7e9c97a3-4bf1-4852-81b6-d74cedf2c94c</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -26926,7 +26926,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Data from: Prentice et al. 2025. Vibrio pectenicida strain FHCF-3 is a causative agent of sea star wasting disease</t>
+          <t>Environmental DNA survey of Calvert Island, British Columbia, 2021</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -26944,7 +26944,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Genomics, Nearshore</t>
+          <t>Genomics</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -26968,45 +26968,45 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 47.91], [-122.3, 47.91], [-122.3, 51.82], [-128.5, 51.82], [-128.5, 47.91]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.31], [-127.3, 51.31], [-127.3, 52.05], [-128.6, 52.05], [-128.6, 51.31]]]}</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '60.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q235" t="inlineStr">
         <is>
-          <t>microbeBiomassAndDiversity</t>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>10.21966/4dvn-5y90</t>
+          <t>10.21966/vdyq-r660</t>
         </is>
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/24mf0TP0vkh6bmNOOA3ynoTFPNJ2/-OX0Xm6VoYH22oc68Jfp</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-ORCQx4QHUuJ1NV1SEig</t>
         </is>
       </c>
       <c r="T235" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="U235" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="V235" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W235" t="n">
         <v>0</v>
@@ -27028,12 +27028,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>0272fd06-6ac8-48cd-80c9-b6e05f15be0f</t>
+          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>ca-cioos_132cecdf-de8a-4b17-b610-0e2b3a343812</t>
+          <t>ca-cioos_9a018fe0-8bd1-41d1-af8d-079960b71473</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -27043,7 +27043,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), North Coast, British Columbia, Canada</t>
+          <t>Data from: Prentice et al. 2025. Vibrio pectenicida strain FHCF-3 is a causative agent of sea star wasting disease</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -27061,7 +27061,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
+          <t>Genomics, Nearshore</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -27085,11 +27085,11 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-131.0, 53.74], [-130.4, 53.74], [-130.4, 54.46], [-131.0, 54.46], [-131.0, 53.74]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 47.91], [-122.3, 47.91], [-122.3, 51.82], [-128.5, 51.82], [-128.5, 47.91]]]}</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
@@ -27099,27 +27099,27 @@
       </c>
       <c r="Q236" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>microbeBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>10.21966/m93t-4181</t>
+          <t>10.21966/4dvn-5y90</t>
         </is>
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8sPEiAvbPxw16A-L6I</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/24mf0TP0vkh6bmNOOA3ynoTFPNJ2/-OX0Xm6VoYH22oc68Jfp</t>
         </is>
       </c>
       <c r="T236" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="U236" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="V236" t="n">
@@ -27145,12 +27145,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>b01f58f7-1518-4829-aff6-ac4a8f2c0616</t>
+          <t>0272fd06-6ac8-48cd-80c9-b6e05f15be0f</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>ca-cioos_f815a700-c943-4d6f-afeb-a4854ad10cfc</t>
+          <t>ca-cioos_132cecdf-de8a-4b17-b610-0e2b3a343812</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -27160,7 +27160,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), North Vancouver Island, British Columbia, Canada</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), North Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -27206,7 +27206,7 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.6, 50.35], [-124.8, 50.35], [-124.8, 50.7], [-126.6, 50.7], [-126.6, 50.35]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-131.0, 53.74], [-130.4, 53.74], [-130.4, 54.46], [-131.0, 54.46], [-131.0, 53.74]]]}</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
@@ -27221,12 +27221,12 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>10.21966/ntdg-e790</t>
+          <t>10.21966/m93t-4181</t>
         </is>
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8raBb8T2xZJ-oRzesS</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8sPEiAvbPxw16A-L6I</t>
         </is>
       </c>
       <c r="T237" t="inlineStr">
@@ -27262,12 +27262,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>b01f58f7-1518-4829-aff6-ac4a8f2c0616</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>ca-cioos_5b4cbe9f-8f2e-414c-80ff-741372891fe9</t>
+          <t>ca-cioos_f815a700-c943-4d6f-afeb-a4854ad10cfc</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -27277,7 +27277,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Gitga'at Territory Coastal Monitoring and Mapping - Airborne Coastal Observatory</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), North Vancouver Island, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -27287,7 +27287,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="H238" t="b">
@@ -27295,7 +27295,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -27323,53 +27323,53 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.8, 52.92], [-129.1, 52.92], [-129.1, 53.67], [-129.8, 53.67], [-129.8, 52.92]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.6, 50.35], [-124.8, 50.35], [-124.8, 50.7], [-126.6, 50.7], [-126.6, 50.35]]]}</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>[{'max': '475.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q238" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>10.21966/0xex-r023</t>
+          <t>10.21966/ntdg-e790</t>
         </is>
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OdPFhWCkXwvqjCqum30</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8raBb8T2xZJ-oRzesS</t>
         </is>
       </c>
       <c r="T238" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="U238" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="V238" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X238" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>[{'relationship': 'references', 'id': '10.21966/2aap-hn61', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_b5f0f854-efe1-4132-808d-074244d813e1'}, {'relationship': 'citations', 'id': '10.21966/2aap-hn61', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_b5f0f854-efe1-4132-808d-074244d813e1'}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -27379,12 +27379,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>0074861a-39f2-42c1-ae71-abef4f78fd78</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>ca-cioos_b5f0f854-efe1-4132-808d-074244d813e1</t>
+          <t>ca-cioos_5b4cbe9f-8f2e-414c-80ff-741372891fe9</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -27394,7 +27394,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Gitga'at Territory Coastal Mapping Project</t>
+          <t>Gitga'at Territory Coastal Monitoring and Mapping - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -27412,12 +27412,12 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -27440,12 +27440,12 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.6, 53.18], [-129.0, 53.18], [-129.0, 53.68], [-129.6, 53.68], [-129.6, 53.18]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.8, 52.92], [-129.1, 52.92], [-129.1, 53.67], [-129.8, 53.67], [-129.8, 52.92]]]}</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>[{'max': '150.0', 'min': '0.0'}]</t>
+          <t>[{'max': '475.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q239" t="inlineStr">
@@ -27455,12 +27455,12 @@
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>10.21966/2aap-hn61</t>
+          <t>10.21966/0xex-r023</t>
         </is>
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Oa5tvTh2mXFQbI3SkzK</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OdPFhWCkXwvqjCqum30</t>
         </is>
       </c>
       <c r="T239" t="inlineStr">
@@ -27470,23 +27470,23 @@
       </c>
       <c r="U239" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="V239" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W239" t="n">
         <v>1</v>
       </c>
       <c r="X239" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
+          <t>[{'year': '2025', 'total': 1}]</t>
         </is>
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>[{'relationship': 'references', 'id': '10.21966/0xex-r023', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_5b4cbe9f-8f2e-414c-80ff-741372891fe9'}, {'relationship': 'citations', 'id': '10.21966/0xex-r023', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_5b4cbe9f-8f2e-414c-80ff-741372891fe9'}]</t>
+          <t>[{'relationship': 'references', 'id': '10.21966/2aap-hn61', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_b5f0f854-efe1-4132-808d-074244d813e1'}, {'relationship': 'citations', 'id': '10.21966/2aap-hn61', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_b5f0f854-efe1-4132-808d-074244d813e1'}]</t>
         </is>
       </c>
     </row>
@@ -27496,12 +27496,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>5fc21b4d-2dfa-4908-8aaf-90a82509324a</t>
+          <t>0074861a-39f2-42c1-ae71-abef4f78fd78</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>ca-cioos_35900174-c64a-493e-9a7e-390ac7e997e4</t>
+          <t>ca-cioos_b5f0f854-efe1-4132-808d-074244d813e1</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -27511,7 +27511,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Bowhead Whale Drone Data Collection - Cumberland Sound - Nunavut</t>
+          <t>Gitga'at Territory Coastal Mapping Project</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -27521,7 +27521,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>CC-BY-4.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H240" t="b">
@@ -27534,7 +27534,7 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -27557,12 +27557,12 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-68.21, 64.72], [-64.14, 64.72], [-64.14, 66.48], [-68.21, 66.48], [-68.21, 64.72]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.6, 53.18], [-129.0, 53.18], [-129.0, 53.68], [-129.6, 53.68], [-129.6, 53.18]]]}</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '150.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q240" t="inlineStr">
@@ -27572,22 +27572,22 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>10.21966/fv0q-q364</t>
+          <t>10.21966/2aap-hn61</t>
         </is>
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OeY_smu3pJj8TBE9ivK</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Oa5tvTh2mXFQbI3SkzK</t>
         </is>
       </c>
       <c r="T240" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="U240" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="V240" t="n">
@@ -27603,7 +27603,7 @@
       </c>
       <c r="Y240" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.48321/d16d6f987c', 'type': 'dois', 'status_code': 200, 'url': 'https://dmphub.uc3prd.cdlib.net/dmps/10.48321/D16D6F987C'}]</t>
+          <t>[{'relationship': 'references', 'id': '10.21966/0xex-r023', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_5b4cbe9f-8f2e-414c-80ff-741372891fe9'}, {'relationship': 'citations', 'id': '10.21966/0xex-r023', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_5b4cbe9f-8f2e-414c-80ff-741372891fe9'}]</t>
         </is>
       </c>
     </row>
@@ -27613,12 +27613,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>dbfc5189-f657-4034-af7f-cc358042047d</t>
+          <t>5fc21b4d-2dfa-4908-8aaf-90a82509324a</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>ca-cioos_78686602-1aa9-4246-8a24-915471fe4255</t>
+          <t>ca-cioos_35900174-c64a-493e-9a7e-390ac7e997e4</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -27628,7 +27628,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2025), North Coast, British Columbia, Canada</t>
+          <t>Bowhead Whale Drone Data Collection - Cumberland Sound - Nunavut</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -27646,7 +27646,7 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -27674,7 +27674,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.8, 52.69], [-129.0, 52.69], [-129.0, 53.14], [-129.8, 53.14], [-129.8, 52.69]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-68.21, 64.72], [-64.14, 64.72], [-64.14, 66.48], [-68.21, 66.48], [-68.21, 64.72]]]}</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
@@ -27684,17 +27684,17 @@
       </c>
       <c r="Q241" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>10.21966/nwg7-fe05</t>
+          <t>10.21966/fv0q-q364</t>
         </is>
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OeItznXpvEFI_t-jsCl</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OeY_smu3pJj8TBE9ivK</t>
         </is>
       </c>
       <c r="T241" t="inlineStr">
@@ -27704,21 +27704,23 @@
       </c>
       <c r="U241" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="V241" t="inlineStr"/>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="V241" t="n">
+        <v>1</v>
+      </c>
       <c r="W241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X241" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
       <c r="Y241" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'citations', 'id': '10.48321/d16d6f987c', 'type': 'dois', 'status_code': 200, 'url': 'https://dmphub.uc3prd.cdlib.net/dmps/10.48321/D16D6F987C'}]</t>
         </is>
       </c>
     </row>
@@ -27728,12 +27730,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>9eda1bfc-0d13-4e1d-9542-b9a7cce16991</t>
+          <t>dbfc5189-f657-4034-af7f-cc358042047d</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>ca-cioos_c544ef5b-967d-46b2-bbcf-395116b50e7d</t>
+          <t>ca-cioos_78686602-1aa9-4246-8a24-915471fe4255</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -27743,7 +27745,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Mystery Creek Aerial Photo and LiDAR Survey - 2025 - Airborne Coastal Observatory</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2025), North Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -27761,7 +27763,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -27789,32 +27791,32 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.9, 50.21], [-122.8, 50.21], [-122.8, 50.25], [-122.9, 50.25], [-122.9, 50.21]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.8, 52.69], [-129.0, 52.69], [-129.0, 53.14], [-129.8, 53.14], [-129.8, 52.69]]]}</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>[{'max': '1690.0', 'min': '378.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q242" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>10.21966/02qp-4945</t>
+          <t>10.21966/nwg7-fe05</t>
         </is>
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/FfIFMI0sx4beFpYCFD9liFIEiMt1/-OeTbb0MbfTCH-YFCNGG</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OeItznXpvEFI_t-jsCl</t>
         </is>
       </c>
       <c r="T242" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="U242" t="inlineStr">
@@ -27843,12 +27845,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>37440dfd-53f8-462b-a544-b6c8d39c44cd</t>
+          <t>9eda1bfc-0d13-4e1d-9542-b9a7cce16991</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>ca-cioos_43bad5e5-0484-4c11-80a5-c844245f940e</t>
+          <t>ca-cioos_c544ef5b-967d-46b2-bbcf-395116b50e7d</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -27858,7 +27860,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Farwell Canyon Airborne Surveys - 2024 - Airborne Coastal Observatory</t>
+          <t>Mystery Creek Aerial Photo and LiDAR Survey - 2025 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -27904,12 +27906,12 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.6, 51.86], [-122.5, 51.81], [-122.4, 51.74], [-122.4, 51.73], [-122.5, 51.8], [-122.7, 51.83], [-122.6, 51.86]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.9, 50.21], [-122.8, 50.21], [-122.8, 50.25], [-122.9, 50.25], [-122.9, 50.21]]]}</t>
         </is>
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>[{'max': '1347.62', 'min': '345.9'}]</t>
+          <t>[{'max': '1690.0', 'min': '378.0'}]</t>
         </is>
       </c>
       <c r="Q243" t="inlineStr">
@@ -27919,22 +27921,22 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>10.21966/dtt0-s264</t>
+          <t>10.21966/02qp-4945</t>
         </is>
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/FfIFMI0sx4beFpYCFD9liFIEiMt1/-OgDkxI9LmB0KWXvOsZe</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/FfIFMI0sx4beFpYCFD9liFIEiMt1/-OeTbb0MbfTCH-YFCNGG</t>
         </is>
       </c>
       <c r="T243" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="U243" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="V243" t="inlineStr"/>
@@ -27958,12 +27960,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
+          <t>37440dfd-53f8-462b-a544-b6c8d39c44cd</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>ca-cioos_7cafde4f-bdd5-4b95-a41d-7939ddcf08c6</t>
+          <t>ca-cioos_43bad5e5-0484-4c11-80a5-c844245f940e</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -27973,7 +27975,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Time series of quarterly kelp canopy extent from Landsat 5, 7, 8, and 9 since 1985</t>
+          <t>Farwell Canyon Airborne Surveys - 2024 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -27991,12 +27993,12 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -28019,42 +28021,40 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-130.5, 54.75], [-133.5, 54.36], [-133.0, 53.09], [-126.0, 48.92], [-123.6, 48.28], [-123.2, 48.8], [-123.8, 49.61], [-127.6, 51.04], [-128.4, 52.4], [-130.4, 54.24], [-130.5, 54.75]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.6, 51.86], [-122.5, 51.81], [-122.4, 51.74], [-122.4, 51.73], [-122.5, 51.8], [-122.7, 51.83], [-122.6, 51.86]]]}</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '1347.62', 'min': '345.9'}]</t>
         </is>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>10.21966/xc7x-9207</t>
+          <t>10.21966/dtt0-s264</t>
         </is>
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OZGbDlZ5dgF0dD-ceZ7</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/FfIFMI0sx4beFpYCFD9liFIEiMt1/-OgDkxI9LmB0KWXvOsZe</t>
         </is>
       </c>
       <c r="T244" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="U244" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="V244" t="n">
-        <v>2</v>
-      </c>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr"/>
       <c r="W244" t="n">
         <v>0</v>
       </c>
@@ -28075,12 +28075,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>3d082072-1ee8-4005-8bba-f9ec795ad5ab</t>
+          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>ca-cioos_cfa4ad65-ee12-47c0-9527-206a0f8d92ae</t>
+          <t>ca-cioos_7cafde4f-bdd5-4b95-a41d-7939ddcf08c6</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -28090,7 +28090,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Hakai Institute Drone Data Index</t>
+          <t>Time series of quarterly kelp canopy extent from Landsat 5, 7, 8, and 9 since 1985</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -28108,7 +28108,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -28136,40 +28136,42 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-134.1, 42.65], [-59.42, 42.65], [-59.42, 67.53], [-134.1, 67.53], [-134.1, 42.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-130.5, 54.75], [-133.5, 54.36], [-133.0, 53.09], [-126.0, 48.92], [-123.6, 48.28], [-123.2, 48.8], [-123.8, 49.61], [-127.6, 51.04], [-128.4, 52.4], [-130.4, 54.24], [-130.5, 54.75]]]}</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q245" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>10.21966/0r8b-t282</t>
+          <t>10.21966/xc7x-9207</t>
         </is>
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCdraToZivfj6ZZ8TqZ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OZGbDlZ5dgF0dD-ceZ7</t>
         </is>
       </c>
       <c r="T245" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="U245" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="V245" t="inlineStr"/>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="V245" t="n">
+        <v>2</v>
+      </c>
       <c r="W245" t="n">
         <v>0</v>
       </c>
@@ -28190,12 +28192,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>3d082072-1ee8-4005-8bba-f9ec795ad5ab</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>ca-cioos_a924b31b-9882-4abe-8d8e-e875dbbbec82</t>
+          <t>ca-cioos_cfa4ad65-ee12-47c0-9527-206a0f8d92ae</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -28205,7 +28207,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Surface Seawater and Marine Boundary Layer CO2 Time Series from the Bute Inlet Ocean Observing Station (BIOOS) Buoy, Bute Inlet, BC, Canada (Provisional)</t>
+          <t>Hakai Institute Drone Data Index</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -28223,7 +28225,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -28241,47 +28243,63 @@
           <t>dataset</t>
         </is>
       </c>
-      <c r="M246" t="inlineStr"/>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
       <c r="N246" t="n">
         <v>1</v>
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-134.1, 42.65], [-59.42, 42.65], [-59.42, 67.53], [-134.1, 67.53], [-134.1, 42.65]]]}</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q246" t="inlineStr">
         <is>
-          <t>inorganicCarbon, oxygen, seaSurfaceSalinity, seaSurfaceTemperature</t>
-        </is>
-      </c>
-      <c r="R246" t="inlineStr"/>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>10.21966/0r8b-t282</t>
+        </is>
+      </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-OlwZ9MM8a9VqCYIJo4W</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCdraToZivfj6ZZ8TqZ</t>
         </is>
       </c>
       <c r="T246" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="U246" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="V246" t="n">
-        <v>4</v>
-      </c>
-      <c r="W246" t="inlineStr"/>
-      <c r="X246" t="inlineStr"/>
-      <c r="Y246" t="inlineStr"/>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr"/>
+      <c r="W246" t="n">
+        <v>0</v>
+      </c>
+      <c r="X246" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -28289,12 +28307,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>0894f661-f9cb-48cb-a0b4-8a001eb69420</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>ca-cioos_bfefcdf9-c922-4e4f-a958-aa6da739d3cd</t>
+          <t>ca-cioos_a924b31b-9882-4abe-8d8e-e875dbbbec82</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -28304,7 +28322,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Surface Seawater and Marine Boundary Layer CO2 Time Series from the Bute Inlet Ocean Observing Station (BIOOS) Buoy, Bute Inlet, BC, Canada (Research)</t>
+          <t>Surface Seawater and Marine Boundary Layer CO2 Time Series from the Bute Inlet Ocean Observing Station (BIOOS) Buoy, Bute Inlet, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -28340,11 +28358,7 @@
           <t>dataset</t>
         </is>
       </c>
-      <c r="M247" t="inlineStr">
-        <is>
-          <t>Hakai Institute</t>
-        </is>
-      </c>
+      <c r="M247" t="inlineStr"/>
       <c r="N247" t="n">
         <v>1</v>
       </c>
@@ -28360,17 +28374,13 @@
       </c>
       <c r="Q247" t="inlineStr">
         <is>
-          <t>oxygen, inorganicCarbon, particulateMatter, phytoplanktonBiomassAndDiversity, seaSurfaceSalinity, seaSurfaceTemperature</t>
-        </is>
-      </c>
-      <c r="R247" t="inlineStr">
-        <is>
-          <t>10.21966/4jvz-bv44</t>
-        </is>
-      </c>
+          <t>inorganicCarbon, oxygen, seaSurfaceSalinity, seaSurfaceTemperature</t>
+        </is>
+      </c>
+      <c r="R247" t="inlineStr"/>
       <c r="S247" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-OOYvTmfsWUPdHkDTTFS</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-OlwZ9MM8a9VqCYIJo4W</t>
         </is>
       </c>
       <c r="T247" t="inlineStr">
@@ -28380,23 +28390,15 @@
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="V247" t="inlineStr"/>
-      <c r="W247" t="n">
-        <v>0</v>
-      </c>
-      <c r="X247" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y247" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="V247" t="n">
+        <v>4</v>
+      </c>
+      <c r="W247" t="inlineStr"/>
+      <c r="X247" t="inlineStr"/>
+      <c r="Y247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -28404,12 +28406,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>e788c2f6-c842-4240-bab4-54a323d62174</t>
+          <t>0894f661-f9cb-48cb-a0b4-8a001eb69420</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>ca-cioos_984e6b72-15d0-4742-bb2d-9ac13b14383a</t>
+          <t>ca-cioos_bfefcdf9-c922-4e4f-a958-aa6da739d3cd</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -28419,7 +28421,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Stream Temperature Observations for Three Streams Near Gold River</t>
+          <t>Surface Seawater and Marine Boundary Layer CO2 Time Series from the Bute Inlet Ocean Observing Station (BIOOS) Buoy, Bute Inlet, BC, Canada (Research)</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -28437,12 +28439,12 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -28465,7 +28467,7 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.7, 49.96], [-125.9, 49.93], [-126.0, 49.56], [-126.7, 49.73], [-126.7, 49.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976]]]}</t>
         </is>
       </c>
       <c r="P248" t="inlineStr">
@@ -28475,27 +28477,27 @@
       </c>
       <c r="Q248" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>oxygen, inorganicCarbon, particulateMatter, phytoplanktonBiomassAndDiversity, seaSurfaceSalinity, seaSurfaceTemperature</t>
         </is>
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>10.21966/cqrt-sk09</t>
+          <t>10.21966/4jvz-bv44</t>
         </is>
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DvuBcQQuVHdxmYEF4yDNBDj30lu1/-Oj8Fegu6V858hz57O8z</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-OOYvTmfsWUPdHkDTTFS</t>
         </is>
       </c>
       <c r="T248" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="V248" t="inlineStr"/>
@@ -28519,12 +28521,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
+          <t>e788c2f6-c842-4240-bab4-54a323d62174</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>ca-cioos_84820f31-b6db-479c-a47e-f22f2899b4d2</t>
+          <t>ca-cioos_984e6b72-15d0-4742-bb2d-9ac13b14383a</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -28534,7 +28536,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Biogeochemical Sampling of 28 Streams on Vancouver Island</t>
+          <t>Stream Temperature Observations for Three Streams Near Gold River</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -28580,7 +28582,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 50.65], [-127.9, 50.71], [-123.6, 48.43], [-124.0, 48.36], [-127.3, 49.77], [-128.4, 50.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.7, 49.96], [-125.9, 49.93], [-126.0, 49.56], [-126.7, 49.73], [-126.7, 49.96]]]}</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
@@ -28595,38 +28597,36 @@
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>10.21966/chc3-rj93</t>
+          <t>10.21966/cqrt-sk09</t>
         </is>
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DvuBcQQuVHdxmYEF4yDNBDj30lu1/-OnCm7wniBlFr2gSXQhf</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DvuBcQQuVHdxmYEF4yDNBDj30lu1/-Oj8Fegu6V858hz57O8z</t>
         </is>
       </c>
       <c r="T249" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="U249" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="V249" t="n">
-        <v>3</v>
-      </c>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr"/>
       <c r="W249" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X249" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Y249" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.21966/cqrt-sk09', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_984e6b72-15d0-4742-bb2d-9ac13b14383a'}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -28636,12 +28636,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>63f6c693-7c22-49cc-ad7d-9aa1774a5972</t>
+          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>ca-cioos_d7b34963-67bc-404b-bdd1-b41cc750bdaa</t>
+          <t>ca-cioos_84820f31-b6db-479c-a47e-f22f2899b4d2</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -28651,7 +28651,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Fraser River Airborne Surveys - 2020 - Airborne Coastal Observatory</t>
+          <t>Biogeochemical Sampling of 28 Streams on Vancouver Island</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -28669,7 +28669,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -28697,12 +28697,12 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-121.5, 49.51], [-121.3, 49.53], [-121.4, 49.95], [-121.5, 50.28], [-121.7, 50.52], [-121.8, 50.66], [-121.8, 50.76], [-121.8, 51.01], [-122.1, 51.32], [-122.3, 51.79], [-122.1, 52.11], [-122.3, 52.37], [-122.3, 52.51], [-122.6, 52.49], [-122.4, 51.96], [-122.5, 51.83], [-122.4, 51.49], [-122.3, 51.18], [-121.9, 50.95], [-121.9, 50.62], [-121.8, 50.53], [-121.7, 50.17], [-121.6, 49.89], [-121.5, 49.63], [-121.5, 49.51]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 50.65], [-127.9, 50.71], [-123.6, 48.43], [-124.0, 48.36], [-127.3, 49.77], [-128.4, 50.65]]]}</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>[{'max': '850.0', 'min': '400.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q250" t="inlineStr">
@@ -28712,38 +28712,38 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>10.21966/f9m6-qg12</t>
+          <t>10.21966/chc3-rj93</t>
         </is>
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MibW0TZpoaJ4Ih_2ev7</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DvuBcQQuVHdxmYEF4yDNBDj30lu1/-OnCm7wniBlFr2gSXQhf</t>
         </is>
       </c>
       <c r="T250" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="U250" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="V250" t="n">
+        <v>3</v>
+      </c>
+      <c r="W250" t="n">
         <v>1</v>
       </c>
-      <c r="W250" t="n">
-        <v>0</v>
-      </c>
       <c r="X250" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
       <c r="Y250" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'citations', 'id': '10.21966/cqrt-sk09', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_984e6b72-15d0-4742-bb2d-9ac13b14383a'}]</t>
         </is>
       </c>
     </row>
@@ -28753,12 +28753,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
+          <t>63f6c693-7c22-49cc-ad7d-9aa1774a5972</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>ca-cioos_1efbadd2-e735-48cc-9498-e3a5a88e48a6</t>
+          <t>ca-cioos_d7b34963-67bc-404b-bdd1-b41cc750bdaa</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -28768,7 +28768,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Seawater Carbon Dioxide (CO2) Content from the SuperCO2 System in the Pacific Ecosystem Autonomous Research Laboratory, Bamfield Marine Sciences Centre, BC, Canada (Provisional)</t>
+          <t>Fraser River Airborne Surveys - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -28786,12 +28786,12 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -28810,46 +28810,44 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-121.5, 49.51], [-121.3, 49.53], [-121.4, 49.95], [-121.5, 50.28], [-121.7, 50.52], [-121.8, 50.66], [-121.8, 50.76], [-121.8, 51.01], [-122.1, 51.32], [-122.3, 51.79], [-122.1, 52.11], [-122.3, 52.37], [-122.3, 52.51], [-122.6, 52.49], [-122.4, 51.96], [-122.5, 51.83], [-122.4, 51.49], [-122.3, 51.18], [-121.9, 50.95], [-121.9, 50.62], [-121.8, 50.53], [-121.7, 50.17], [-121.6, 49.89], [-121.5, 49.63], [-121.5, 49.51]]]}</t>
         </is>
       </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '850.0', 'min': '400.0'}]</t>
         </is>
       </c>
       <c r="Q251" t="inlineStr">
         <is>
-          <t>inorganicCarbon, seaSurfaceSalinity, seaSurfaceTemperature</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>10.21966/a0v4-x512</t>
+          <t>10.21966/f9m6-qg12</t>
         </is>
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-Olwvch3kCplJcz3CCeR</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MibW0TZpoaJ4Ih_2ev7</t>
         </is>
       </c>
       <c r="T251" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="U251" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="V251" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr"/>
       <c r="W251" t="n">
         <v>0</v>
       </c>
@@ -28870,12 +28868,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>7b1120bc-4a2c-432c-9e54-879d66751a59</t>
+          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>ca-cioos_b2b18171-35b6-4345-b81b-497a90c2e7c5</t>
+          <t>ca-cioos_1efbadd2-e735-48cc-9498-e3a5a88e48a6</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -28885,7 +28883,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Seagrass fish and macroinvertebrate swaths BC Central Coast</t>
+          <t>Seawater Carbon Dioxide (CO2) Content from the SuperCO2 System in the Pacific Ecosystem Autonomous Research Laboratory, Bamfield Marine Sciences Centre, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -28903,7 +28901,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -28927,44 +28925,46 @@
         </is>
       </c>
       <c r="N252" t="n">
+        <v>2</v>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359]]]}</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>[{'max': '0', 'min': '0'}]</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>inorganicCarbon, seaSurfaceSalinity, seaSurfaceTemperature</t>
+        </is>
+      </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>10.21966/a0v4-x512</t>
+        </is>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-Olwvch3kCplJcz3CCeR</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="V252" t="n">
         <v>1</v>
       </c>
-      <c r="O252" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 52.09], [-128.5, 52.04], [-128.5, 51.97], [-128.5, 51.93], [-128.5, 51.9], [-128.4, 51.88], [-128.3, 51.86], [-128.3, 51.83], [-128.2, 51.63], [-127.9, 51.62], [-127.8, 51.77], [-127.8, 51.83], [-127.9, 51.99], [-128.4, 52.09]]]}</t>
-        </is>
-      </c>
-      <c r="P252" t="inlineStr">
-        <is>
-          <t>[{'max': '10.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q252" t="inlineStr">
-        <is>
-          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
-        </is>
-      </c>
-      <c r="R252" t="inlineStr">
-        <is>
-          <t>10.21966/NMNG-SF35</t>
-        </is>
-      </c>
-      <c r="S252" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/lJHlH9nm20QQOPuk217xLlxWbNv1/-NPt7327bul36pby-Odi</t>
-        </is>
-      </c>
-      <c r="T252" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="U252" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="V252" t="inlineStr"/>
       <c r="W252" t="n">
         <v>0</v>
       </c>
@@ -28985,12 +28985,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>49374495-400f-4acc-aac6-d7d0b7cae297</t>
+          <t>7b1120bc-4a2c-432c-9e54-879d66751a59</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>ca-cioos_bafcd0eb-8249-471b-b93b-0797cfeea287</t>
+          <t>ca-cioos_b2b18171-35b6-4345-b81b-497a90c2e7c5</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -29000,7 +29000,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020), Central Coast, British Columbia, Canada</t>
+          <t>Seagrass fish and macroinvertebrate swaths BC Central Coast</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -29018,12 +29018,12 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
@@ -29046,37 +29046,37 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.64], [-128.1, 51.64], [-128.1, 52.01], [-128.5, 52.01], [-128.5, 51.64]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 52.09], [-128.5, 52.04], [-128.5, 51.97], [-128.5, 51.93], [-128.5, 51.9], [-128.4, 51.88], [-128.3, 51.86], [-128.3, 51.83], [-128.2, 51.63], [-127.9, 51.62], [-127.8, 51.77], [-127.8, 51.83], [-127.9, 51.99], [-128.4, 52.09]]]}</t>
         </is>
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '10.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition, other</t>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>10.21966/20ym-8826</t>
+          <t>10.21966/NMNG-SF35</t>
         </is>
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Miha19AtLQ2u1uo0b_q</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/lJHlH9nm20QQOPuk217xLlxWbNv1/-NPt7327bul36pby-Odi</t>
         </is>
       </c>
       <c r="T253" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="U253" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="V253" t="inlineStr"/>
@@ -29100,12 +29100,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>613ba2f9-b21d-445f-8eaa-f42950c9350b</t>
+          <t>49374495-400f-4acc-aac6-d7d0b7cae297</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>ca-cioos_ba41d935-f293-447f-be3d-7098e569b431</t>
+          <t>ca-cioos_bafcd0eb-8249-471b-b93b-0797cfeea287</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -29115,7 +29115,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Water Property Measurements from Conductivity-Temperature-Depth Profiles, BC, Canada (Research)</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020), Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -29133,12 +29133,12 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>Oceanography, Nearshore, Watersheds, Juvenile Salmon Program</t>
+          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -29157,41 +29157,41 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.64], [-128.1, 51.64], [-128.1, 52.01], [-128.5, 52.01], [-128.5, 51.64]]]}</t>
         </is>
       </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>[{'max': '700.0', 'min': '1.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q254" t="inlineStr">
         <is>
-          <t>oxygen, subSurfaceSalinity, subSurfaceTemperature</t>
+          <t>macroalgalCanopyCoverAndComposition, other</t>
         </is>
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>10.21966/kace-2d24</t>
+          <t>10.21966/20ym-8826</t>
         </is>
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MX35qgX-BrwJDdeJKe1</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Miha19AtLQ2u1uo0b_q</t>
         </is>
       </c>
       <c r="T254" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="U254" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="V254" t="inlineStr"/>
@@ -29215,12 +29215,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
+          <t>613ba2f9-b21d-445f-8eaa-f42950c9350b</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>ca-cioos_fb5c9e1e-a911-46b7-8c1d-e34215a105ed</t>
+          <t>ca-cioos_ba41d935-f293-447f-be3d-7098e569b431</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -29230,7 +29230,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 Analyzer located at Bamfield Marine Sciences Centre, Bamfield, BC, Canada (Provisional)</t>
+          <t>Water Property Measurements from Conductivity-Temperature-Depth Profiles, BC, Canada (Research)</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -29248,7 +29248,7 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Oceanography, Nearshore, Watersheds, Juvenile Salmon Program</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -29272,31 +29272,31 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.13535, 48.83515]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>[{'max': '20.0', 'min': '20.0'}]</t>
+          <t>[{'max': '700.0', 'min': '1.0'}]</t>
         </is>
       </c>
       <c r="Q255" t="inlineStr">
         <is>
-          <t>seaSurfaceTemperature, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
+          <t>oxygen, subSurfaceSalinity, subSurfaceTemperature</t>
         </is>
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>10.21966/65d8-k051</t>
+          <t>10.21966/kace-2d24</t>
         </is>
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-NdH-jgHZQzKrYdb2nw_</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MX35qgX-BrwJDdeJKe1</t>
         </is>
       </c>
       <c r="T255" t="inlineStr">
@@ -29306,12 +29306,10 @@
       </c>
       <c r="U255" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="V255" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr"/>
       <c r="W255" t="n">
         <v>0</v>
       </c>
@@ -29332,12 +29330,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>ca-cioos_91107fce-93a4-4bc9-bce4-e7d9e1cf02a0</t>
+          <t>ca-cioos_fb5c9e1e-a911-46b7-8c1d-e34215a105ed</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -29347,7 +29345,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Sentinel 3A and 3B Chlorophyll and Suspended Matter Concentrations for Coastal British Columbia and Southeast Alaska, 8-Day Average (Research)</t>
+          <t>Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 Analyzer located at Bamfield Marine Sciences Centre, Bamfield, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -29393,41 +29391,41 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-139.0, 47.0], [-121.5, 47.0], [-121.5, 59.5], [-139.0, 59.5], [-139.0, 47.0]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.13535, 48.83515]}</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
+          <t>[{'max': '20.0', 'min': '20.0'}]</t>
         </is>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
-          <t>phytoplanktonBiomassAndDiversity, particulateMatter, other</t>
+          <t>seaSurfaceTemperature, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
         </is>
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>10.21966/175j-8k96</t>
+          <t>10.21966/65d8-k051</t>
         </is>
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-Nueis-TZEnz_78f8PYf</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-NdH-jgHZQzKrYdb2nw_</t>
         </is>
       </c>
       <c r="T256" t="inlineStr">
         <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="U256" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
       <c r="V256" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W256" t="n">
         <v>0</v>
@@ -29449,12 +29447,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>b7b923ed-b3fa-48b3-878d-40a3797046bc</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>ca-cioos_f7538807-4d49-4ed8-ad36-836c0e71428a</t>
+          <t>ca-cioos_91107fce-93a4-4bc9-bce4-e7d9e1cf02a0</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -29464,7 +29462,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>3m Digital Elevation Model - Calvert Island - British Columbia - Canada</t>
+          <t>Sentinel 3A and 3B Chlorophyll and Suspended Matter Concentrations for Coastal British Columbia and Southeast Alaska, 8-Day Average (Research)</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -29482,12 +29480,12 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -29506,55 +29504,57 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.16482, 51.408116], [-127.868831, 51.408116], [-127.868831, 51.734994], [-128.16482, 51.734994], [-128.16482, 51.408116]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-139.0, 47.0], [-121.5, 47.0], [-121.5, 59.5], [-139.0, 59.5], [-139.0, 47.0]]]}</t>
         </is>
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q257" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>phytoplanktonBiomassAndDiversity, particulateMatter, other</t>
         </is>
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>10.21966/RZVW-4A72</t>
+          <t>10.21966/175j-8k96</t>
         </is>
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW13R3BBSGRER2ZkYnM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-Nueis-TZEnz_78f8PYf</t>
         </is>
       </c>
       <c r="T257" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="U257" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="V257" t="inlineStr"/>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="V257" t="n">
+        <v>4</v>
+      </c>
       <c r="W257" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X257" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Y257" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -29564,12 +29564,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
+          <t>b7b923ed-b3fa-48b3-878d-40a3797046bc</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>ca-cioos_33c8ce77-0674-4933-a305-01a25d253f70</t>
+          <t>ca-cioos_f7538807-4d49-4ed8-ad36-836c0e71428a</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -29579,7 +29579,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Sea star microbiome data from 16S amplicon sequencing associated with rocky intertidal sites on Calvert and Quadra Islands</t>
+          <t>3m Digital Elevation Model - Calvert Island - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -29597,7 +29597,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Nearshore, Genomics</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -29625,53 +29625,51 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.3, 49.87], [-124.8, 49.87], [-124.8, 51.75], [-128.3, 51.75], [-128.3, 49.87]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.16482, 51.408116], [-127.868831, 51.408116], [-127.868831, 51.734994], [-128.16482, 51.734994], [-128.16482, 51.408116]]]}</t>
         </is>
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q258" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution, microbeBiomassAndDiversity</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>10.21966/0xvh-1318</t>
+          <t>10.21966/RZVW-4A72</t>
         </is>
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/4TvAwNKXC7PkAi0TEZsZbbAzXfi1/-Oo1MBmr8fW1fputdBh6</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW13R3BBSGRER2ZkYnM</t>
         </is>
       </c>
       <c r="T258" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="U258" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="V258" t="n">
-        <v>2</v>
-      </c>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr"/>
       <c r="W258" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X258" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
       <c r="Y258" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}]</t>
         </is>
       </c>
     </row>
@@ -29681,12 +29679,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
+          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>ca-cioos_a8671db6-81cc-4c92-b681-58595fe66182</t>
+          <t>ca-cioos_33c8ce77-0674-4933-a305-01a25d253f70</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -29696,7 +29694,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Water Property Measurements from the Bute Inlet Ocean Observing Station (BIOOS) Wirewalker, Bute Inlet, BC, Canada (Provisional)</t>
+          <t>Sea star microbiome data from 16S amplicon sequencing associated with rocky intertidal sites on Calvert and Quadra Islands</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -29714,12 +29712,12 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore, Genomics</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -29738,45 +29736,45 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-124.9009, 50.5744]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.3, 49.87], [-124.8, 49.87], [-124.8, 51.75], [-128.3, 51.75], [-128.3, 49.87]]]}</t>
         </is>
       </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>[{'max': '250.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q259" t="inlineStr">
         <is>
-          <t>subSurfaceTemperature, subSurfaceSalinity, oxygen, phytoplanktonBiomassAndDiversity</t>
+          <t>invertebrateAbundanceAndDistribution, microbeBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>10.21966/3q5j-n957</t>
+          <t>10.21966/0xvh-1318</t>
         </is>
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-OqDQ7wqqJtwSgUoAN1g</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/4TvAwNKXC7PkAi0TEZsZbbAzXfi1/-Oo1MBmr8fW1fputdBh6</t>
         </is>
       </c>
       <c r="T259" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="U259" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="V259" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W259" t="n">
         <v>0</v>
@@ -29798,12 +29796,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>227eb965-1892-4bad-8ded-dd2e1d68fdf6</t>
+          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>ca-cioos_08d3e779-2f44-4ce3-82cb-c7b763f72175</t>
+          <t>ca-cioos_a8671db6-81cc-4c92-b681-58595fe66182</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -29813,7 +29811,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>DNA metabarcoding data from Autonomous Reef Monitoring Structures (ARMS) deployed around Calvert Island British Columbia</t>
+          <t>Water Property Measurements from the Bute Inlet Ocean Observing Station (BIOOS) Wirewalker, Bute Inlet, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -29831,12 +29829,12 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>Nearshore, Genomics</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
@@ -29855,44 +29853,46 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.61], [-127.8, 51.61], [-127.8, 51.9], [-128.4, 51.9], [-128.4, 51.61]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-124.9009, 50.5744]}</t>
         </is>
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '250.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q260" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution</t>
+          <t>subSurfaceTemperature, subSurfaceSalinity, oxygen, phytoplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>10.21966/kmc2-5r12</t>
+          <t>10.21966/3q5j-n957</t>
         </is>
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-ORSLLie2O-FFN8cPV1e</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-OqDQ7wqqJtwSgUoAN1g</t>
         </is>
       </c>
       <c r="T260" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="U260" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="V260" t="inlineStr"/>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="V260" t="n">
+        <v>1</v>
+      </c>
       <c r="W260" t="n">
         <v>0</v>
       </c>
@@ -29913,12 +29913,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>0cef18ab-cea6-4522-baba-1bcd73a30646</t>
+          <t>227eb965-1892-4bad-8ded-dd2e1d68fdf6</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>ca-cioos_66fbb7f5-3644-471a-95ee-f8d3758e888b</t>
+          <t>ca-cioos_08d3e779-2f44-4ce3-82cb-c7b763f72175</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -29928,7 +29928,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Mount Robson Aerial Photo and LiDAR Survey</t>
+          <t>DNA metabarcoding data from Autonomous Reef Monitoring Structures (ARMS) deployed around Calvert Island British Columbia</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -29946,7 +29946,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Nearshore, Genomics</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -29966,41 +29966,45 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Tula Foundation</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N261" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-119.3, 53.03], [-118.8, 53.03], [-118.8, 53.26], [-119.3, 53.26], [-119.3, 53.03]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.61], [-127.8, 51.61], [-127.8, 51.9], [-128.4, 51.9], [-128.4, 51.61]]]}</t>
         </is>
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>[{'max': '3954.0', 'min': '800.0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q261" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>10.21966/w9n0-kn30</t>
+          <t>10.21966/kmc2-5r12</t>
         </is>
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICbtZXkj6anGvgB3Qi</t>
-        </is>
-      </c>
-      <c r="T261" t="inlineStr"/>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-ORSLLie2O-FFN8cPV1e</t>
+        </is>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
       <c r="U261" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="V261" t="inlineStr"/>
@@ -30013,6 +30017,117 @@
         </is>
       </c>
       <c r="Y261" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>260</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>0cef18ab-cea6-4522-baba-1bcd73a30646</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>ca-cioos_66fbb7f5-3644-471a-95ee-f8d3758e888b</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Mount Robson Aerial Photo and LiDAR Survey</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="H262" t="b">
+        <v>0</v>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Airborne Coastal Observatory, Geospatial</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>Tula Foundation</t>
+        </is>
+      </c>
+      <c r="N262" t="n">
+        <v>1</v>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-119.3, 53.03], [-118.8, 53.03], [-118.8, 53.26], [-119.3, 53.26], [-119.3, 53.03]]]}</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>[{'max': '3954.0', 'min': '800.0'}]</t>
+        </is>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R262" t="inlineStr">
+        <is>
+          <t>10.21966/w9n0-kn30</t>
+        </is>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICbtZXkj6anGvgB3Qi</t>
+        </is>
+      </c>
+      <c r="T262" t="inlineStr"/>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr"/>
+      <c r="W262" t="n">
+        <v>0</v>
+      </c>
+      <c r="X262" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y262" t="inlineStr">
         <is>
           <t>[]</t>
         </is>

--- a/main/catalog_summary.xlsx
+++ b/main/catalog_summary.xlsx
@@ -6574,12 +6574,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ca-cioos_6ebe47c3-6d59-4cb2-a7ba-111698445d8d</t>
+          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bald eagles as vectors of marine nutrients – Central Coast Islands (100 Islands study area) – May – July 2017</t>
+          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>100 Islands</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6627,15 +6627,15 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.58323147, 51.38160352], [-127.80979387, 51.38160352], [-127.80979387, 52.09997599], [-128.58323147, 52.09997599], [-128.58323147, 51.38160352]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6645,13 +6645,17 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>other, nutrients</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr"/>
+          <t>other, inorganicCarbon</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>10.21966/zxzr-e472</t>
+        </is>
+      </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUxkcndoNFQ4T2xyZWI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
@@ -6661,15 +6665,23 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="V56" t="n">
-        <v>1</v>
-      </c>
-      <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
-      <c r="Y56" t="inlineStr"/>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6677,12 +6689,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
+          <t>ca-cioos_6ebe47c3-6d59-4cb2-a7ba-111698445d8d</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -6692,7 +6704,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
+          <t>Bald eagles as vectors of marine nutrients – Central Coast Islands (100 Islands study area) – May – July 2017</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6710,7 +6722,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>100 Islands</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6730,61 +6742,49 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N57" t="n">
+        <v>2</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.58323147, 51.38160352], [-127.80979387, 51.38160352], [-127.80979387, 52.09997599], [-128.58323147, 52.09997599], [-128.58323147, 51.38160352]]]}</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>other, nutrients</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUxkcndoNFQ4T2xyZWI</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>2022-01-24</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="V57" t="n">
         <v>1</v>
       </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>other, inorganicCarbon</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>10.21966/zxzr-e472</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>2022-01-24</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="n">
-        <v>0</v>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
+          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
+          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -9006,7 +9006,11 @@
       <c r="H77" t="b">
         <v>0</v>
       </c>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Airborne Coastal Observatory</t>
+        </is>
+      </c>
       <c r="J77" t="inlineStr">
         <is>
           <t>completed</t>
@@ -9032,12 +9036,12 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -9048,7 +9052,7 @@
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -9062,7 +9066,7 @@
         </is>
       </c>
       <c r="V77" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
@@ -9074,12 +9078,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
+          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9089,7 +9093,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
+          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -9105,11 +9109,7 @@
       <c r="H78" t="b">
         <v>0</v>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Airborne Coastal Observatory</t>
-        </is>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>completed</t>
@@ -9135,12 +9135,12 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -9151,7 +9151,7 @@
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -9165,7 +9165,7 @@
         </is>
       </c>
       <c r="V78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
@@ -9577,12 +9577,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ca-cioos_c3eff62f-bcee-4faa-a7e1-7b9380d94e74</t>
+          <t>ca-cioos_c3958106-fc49-44bd-8227-bfc3e8bcb58c</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -9592,7 +9592,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ancient Forest Wetlands, BC - Upper Fraser River - 2019 - Airborne Coastal Observatory</t>
+          <t>Moore Island Archaeology Survey - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -9610,7 +9610,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-121.3, 53.79], [-121.2, 53.79], [-121.2, 53.84], [-121.3, 53.84], [-121.3, 53.79]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.5, 52.65], [-129.4, 52.65], [-129.4, 52.7], [-129.5, 52.7], [-129.5, 52.65]]]}</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>[{'max': '500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '150.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>10.21966/eysg-7a26</t>
+          <t>10.21966/wfcv-n753</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6RrLonwFgP-TX9bPv</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6MBp3WwVTVbFK-0kv</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
@@ -9694,12 +9694,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ca-cioos_c3958106-fc49-44bd-8227-bfc3e8bcb58c</t>
+          <t>ca-cioos_c3eff62f-bcee-4faa-a7e1-7b9380d94e74</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Moore Island Archaeology Survey - 2019 - Airborne Coastal Observatory</t>
+          <t>Ancient Forest Wetlands, BC - Upper Fraser River - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.5, 52.65], [-129.4, 52.65], [-129.4, 52.7], [-129.5, 52.7], [-129.5, 52.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-121.3, 53.79], [-121.2, 53.79], [-121.2, 53.84], [-121.3, 53.84], [-121.3, 53.79]]]}</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>[{'max': '150.0', 'min': '0.0'}]</t>
+          <t>[{'max': '500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>10.21966/wfcv-n753</t>
+          <t>10.21966/eysg-7a26</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6MBp3WwVTVbFK-0kv</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6RrLonwFgP-TX9bPv</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
@@ -10229,12 +10229,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ca-cioos_5c13b300-e172-4010-a6d8-7586b68a3a96</t>
+          <t>ca-cioos_5e4f925a-9cf2-4e33-ae22-75c5b326ce6c</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Kelp extent for the McNaughton Group Islands (2017), Manley Island (2017), and Serpent Group Islands (2016), British Columbia, Canada</t>
+          <t>Eelgrass (Z. marina) extent at sites along the Central Coast, British Columbia</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Nearshore, Geospatial</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10286,11 +10286,11 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.30122253, 51.7689035], [-128.05512885, 51.7689035], [-128.05512885, 51.98187882], [-128.30122253, 51.98187882], [-128.30122253, 51.7689035]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.65354407, 51.37817421], [-127.69773286, 51.37817421], [-127.69773286, 52.1127963], [-128.65354407, 52.1127963], [-128.65354407, 51.37817421]]]}</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10300,17 +10300,17 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>other, macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>10.21966/82bd-ks94</t>
+          <t>10.21966/03pw-2190</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFIWmZWeEE0RkZrZVc</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTA3NnQ0NnRiemVLSFU</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
@@ -10346,12 +10346,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ca-cioos_5e4f925a-9cf2-4e33-ae22-75c5b326ce6c</t>
+          <t>ca-cioos_5c13b300-e172-4010-a6d8-7586b68a3a96</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Eelgrass (Z. marina) extent at sites along the Central Coast, British Columbia</t>
+          <t>Kelp extent for the McNaughton Group Islands (2017), Manley Island (2017), and Serpent Group Islands (2016), British Columbia, Canada</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -10379,7 +10379,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Nearshore, Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10403,11 +10403,11 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.65354407, 51.37817421], [-127.69773286, 51.37817421], [-127.69773286, 52.1127963], [-128.65354407, 52.1127963], [-128.65354407, 51.37817421]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.30122253, 51.7689035], [-128.05512885, 51.7689035], [-128.05512885, 51.98187882], [-128.30122253, 51.98187882], [-128.30122253, 51.7689035]]]}</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -10417,17 +10417,17 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>10.21966/03pw-2190</t>
+          <t>10.21966/82bd-ks94</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTA3NnQ0NnRiemVLSFU</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFIWmZWeEE0RkZrZVc</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ca-cioos_51171738-7556-48f1-8757-658d99fa25dd</t>
+          <t>ca-cioos_4fac74c8-f58c-46b0-87dc-ab70ce756880</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12010,7 +12010,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Eelgrass Extent 2014 - Central Coast</t>
+          <t>Discovery Islands LiDAR Dataset  - 2014 - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -12026,10 +12026,14 @@
       <c r="H105" t="b">
         <v>0</v>
       </c>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Geospatial</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>underDevelopment</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -12048,16 +12052,16 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4878540039062, 51.653814904471545], [-128.0978393554687, 51.653814904471545], [-128.0978393554687, 52.07950600379698], [-128.4878540039062, 52.07950600379698], [-128.4878540039062, 51.653814904471545]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.3704833984375, 49.9229354544957], [-124.75524902343749, 49.9229354544957], [-124.75524902343749, 50.291094042311386], [-125.3704833984375, 50.291094042311386], [-125.3704833984375, 49.9229354544957]]]}</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>[{'max': '50.0', 'min': '0.0'}]</t>
+          <t>[{'max': '500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -12068,7 +12072,7 @@
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUZuOThkU2QzakpPNEQ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXR6SWM4aTRoYk9MeU0</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
@@ -12078,11 +12082,11 @@
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="V105" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W105" t="inlineStr"/>
       <c r="X105" t="inlineStr"/>
@@ -12094,12 +12098,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ca-cioos_4fac74c8-f58c-46b0-87dc-ab70ce756880</t>
+          <t>ca-cioos_51171738-7556-48f1-8757-658d99fa25dd</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -12109,7 +12113,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Discovery Islands LiDAR Dataset  - 2014 - British Columbia - Canada</t>
+          <t>Eelgrass Extent 2014 - Central Coast</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -12125,14 +12129,10 @@
       <c r="H106" t="b">
         <v>0</v>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>Geospatial</t>
-        </is>
-      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
-          <t>underDevelopment</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -12151,16 +12151,16 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.3704833984375, 49.9229354544957], [-124.75524902343749, 49.9229354544957], [-124.75524902343749, 50.291094042311386], [-125.3704833984375, 50.291094042311386], [-125.3704833984375, 49.9229354544957]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4878540039062, 51.653814904471545], [-128.0978393554687, 51.653814904471545], [-128.0978393554687, 52.07950600379698], [-128.4878540039062, 52.07950600379698], [-128.4878540039062, 51.653814904471545]]]}</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>[{'max': '500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '50.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
@@ -12171,7 +12171,7 @@
       <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXR6SWM4aTRoYk9MeU0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUZuOThkU2QzakpPNEQ</t>
         </is>
       </c>
       <c r="T106" t="inlineStr">
@@ -12181,11 +12181,11 @@
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V106" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W106" t="inlineStr"/>
       <c r="X106" t="inlineStr"/>
@@ -14284,12 +14284,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ca-cioos_23bc8c35-2e4e-4382-9296-a52d5ea49889</t>
+          <t>ca-cioos_184b2f81-d87f-4615-a026-15b87930d15c</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -14299,7 +14299,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Discharge Time Series (2013-2017) – Calvert Island - Archived Version 3.0</t>
+          <t>Aquatic carbon flux data package for Oliver et al. 2017</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -14341,57 +14341,57 @@
         </is>
       </c>
       <c r="N126" t="n">
+        <v>3</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.15002441406247, 51.614605707797466], [-127.96600341796874, 51.614605707797466], [-127.96600341796874, 51.70405535332591], [-128.15002441406247, 51.70405535332591], [-128.15002441406247, 51.614605707797466]]]}</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>dissolvedOrganicCarbon, other</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>10.21966/1.321324</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW9aOE1zWERKZnFEWm4</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>2022-03-29</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="V126" t="n">
         <v>1</v>
       </c>
-      <c r="O126" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
-        </is>
-      </c>
-      <c r="P126" t="inlineStr">
-        <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q126" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R126" t="inlineStr">
-        <is>
-          <t>10.21966/sbyc-d030</t>
-        </is>
-      </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUdGRGRjUW9LRnBVNVI</t>
-        </is>
-      </c>
-      <c r="T126" t="inlineStr">
-        <is>
-          <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="V126" t="n">
-        <v>10</v>
-      </c>
       <c r="W126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}, {'relationship': 'parts', 'id': '10.5194/bg-2017-5', 'type': 'dois', 'status_code': 200, 'url': 'https://bg.copernicus.org/articles/14/3743/2017/bg-14-3743-2017-discussion.html'}]</t>
         </is>
       </c>
     </row>
@@ -14401,12 +14401,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ca-cioos_184b2f81-d87f-4615-a026-15b87930d15c</t>
+          <t>ca-cioos_23bc8c35-2e4e-4382-9296-a52d5ea49889</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -14416,7 +14416,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Aquatic carbon flux data package for Oliver et al. 2017</t>
+          <t>Discharge Time Series (2013-2017) – Calvert Island - Archived Version 3.0</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -14458,11 +14458,11 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.15002441406247, 51.614605707797466], [-127.96600341796874, 51.614605707797466], [-127.96600341796874, 51.70405535332591], [-128.15002441406247, 51.70405535332591], [-128.15002441406247, 51.614605707797466]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -14472,17 +14472,17 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>dissolvedOrganicCarbon, other</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>10.21966/1.321324</t>
+          <t>10.21966/sbyc-d030</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW9aOE1zWERKZnFEWm4</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUdGRGRjUW9LRnBVNVI</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
@@ -14492,23 +14492,23 @@
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="V127" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="W127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}, {'relationship': 'parts', 'id': '10.5194/bg-2017-5', 'type': 'dois', 'status_code': 200, 'url': 'https://bg.copernicus.org/articles/14/3743/2017/bg-14-3743-2017-discussion.html'}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -14518,12 +14518,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ca-cioos_26443ab2-964f-4031-a53b-f132434573e8</t>
+          <t>ca-cioos_25674e9b-1d49-4270-b917-cfe6cdc30f95</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -14533,7 +14533,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Ecosystem Comparison Plots - Calvert Island</t>
+          <t>Watersheds of the northern Pacific coastal temperate rainforest margin</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -14551,7 +14551,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Geospatial, Watersheds</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -14575,16 +14575,16 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13903808593744, 51.626542529786036], [-127.97355651855466, 51.626542529786036], [-127.97355651855466, 51.67766477883444], [-128.13903808593744, 51.67766477883444], [-128.13903808593744, 51.626542529786036]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-143.16578297, 37.67883738], [-104.45881201, 37.67883738], [-104.45881201, 60.91786918], [-143.16578297, 60.91786918], [-143.16578297, 37.67883738]]]}</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '6000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
@@ -14594,12 +14594,12 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>10.21966/1.56481</t>
+          <t>10.21966/1.715755</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWc4TU94c2lwT0tYa2U</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWJSa2xESlBIbk1rSXA</t>
         </is>
       </c>
       <c r="T128" t="inlineStr">
@@ -14613,19 +14613,19 @@
         </is>
       </c>
       <c r="V128" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="W128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[{'year': '2022', 'total': 2}, {'year': '2023', 'total': 1}]</t>
         </is>
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}, {'relationship': 'parts', 'id': '10.5194/bg-2017-5', 'type': 'dois', 'status_code': 200, 'url': 'https://bg.copernicus.org/articles/14/3743/2017/bg-14-3743-2017-discussion.html'}]</t>
+          <t>[{'relationship': 'citations', 'id': '10.5061/dryad.05qfttf2q', 'type': 'dois', 'status_code': 200, 'url': 'https://datadryad.org/dataset/doi:10.5061/dryad.05qfttf2q'}, {'relationship': 'citations', 'id': '10.1002/essoar.10510464.1', 'type': 'dois', 'status_code': 403, 'url': 'https://essopenarchive.org/doi/full/10.1002/essoar.10510464.1'}, {'relationship': 'citations', 'id': '10.1029/2023gl103024', 'type': 'dois', 'status_code': 403, 'url': 'https://agupubs.onlinelibrary.wiley.com/doi/10.1029/2023GL103024'}]</t>
         </is>
       </c>
     </row>
@@ -14635,12 +14635,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ca-cioos_25674e9b-1d49-4270-b917-cfe6cdc30f95</t>
+          <t>ca-cioos_26443ab2-964f-4031-a53b-f132434573e8</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -14650,7 +14650,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Watersheds of the northern Pacific coastal temperate rainforest margin</t>
+          <t>Ecosystem Comparison Plots - Calvert Island</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -14668,7 +14668,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Geospatial, Watersheds</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14692,57 +14692,57 @@
         </is>
       </c>
       <c r="N129" t="n">
+        <v>1</v>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13903808593744, 51.626542529786036], [-127.97355651855466, 51.626542529786036], [-127.97355651855466, 51.67766477883444], [-128.13903808593744, 51.67766477883444], [-128.13903808593744, 51.626542529786036]]]}</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>10.21966/1.56481</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWc4TU94c2lwT0tYa2U</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>2022-03-29</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="V129" t="n">
         <v>2</v>
       </c>
-      <c r="O129" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-143.16578297, 37.67883738], [-104.45881201, 37.67883738], [-104.45881201, 60.91786918], [-143.16578297, 60.91786918], [-143.16578297, 37.67883738]]]}</t>
-        </is>
-      </c>
-      <c r="P129" t="inlineStr">
-        <is>
-          <t>[{'max': '6000.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q129" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R129" t="inlineStr">
-        <is>
-          <t>10.21966/1.715755</t>
-        </is>
-      </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWJSa2xESlBIbk1rSXA</t>
-        </is>
-      </c>
-      <c r="T129" t="inlineStr">
-        <is>
-          <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="U129" t="inlineStr">
-        <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="V129" t="n">
-        <v>9</v>
-      </c>
       <c r="W129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 2}, {'year': '2023', 'total': 1}]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.5061/dryad.05qfttf2q', 'type': 'dois', 'status_code': 200, 'url': 'https://datadryad.org/dataset/doi:10.5061/dryad.05qfttf2q'}, {'relationship': 'citations', 'id': '10.1002/essoar.10510464.1', 'type': 'dois', 'status_code': 403, 'url': 'https://essopenarchive.org/doi/full/10.1002/essoar.10510464.1'}, {'relationship': 'citations', 'id': '10.1029/2023gl103024', 'type': 'dois', 'status_code': 403, 'url': 'https://agupubs.onlinelibrary.wiley.com/doi/10.1029/2023GL103024'}]</t>
+          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}, {'relationship': 'parts', 'id': '10.5194/bg-2017-5', 'type': 'dois', 'status_code': 200, 'url': 'https://bg.copernicus.org/articles/14/3743/2017/bg-14-3743-2017-discussion.html'}]</t>
         </is>
       </c>
     </row>
@@ -16001,12 +16001,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>ca-cioos_b694a5c5-6a7e-4206-96aa-5b7754323345</t>
+          <t>ca-cioos_b52d5602-f81d-4565-9574-e448e99bc997</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -16016,7 +16016,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Air temperature and relative humidity time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
+          <t>Bathymetry for Six Lakes on Calvert and Hecate Islands - 2016 - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -16034,12 +16034,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Watersheds, Geospatial</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -16062,12 +16062,12 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.30095161, 50.04299371], [-125.08745063, 50.04299371], [-125.08745063, 51.791595], [-128.30095161, 51.791595], [-128.30095161, 50.04299371]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.09646606445312, 51.5996802644666], [-127.9508972167969, 51.5996802644666], [-127.9508972167969, 51.69171329024539], [-128.09646606445312, 51.69171329024539], [-128.09646606445312, 51.5996802644666]]]}</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>[{'max': '741.0', 'min': '3.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
@@ -16075,10 +16075,14 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R141" t="inlineStr"/>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>10.21966/fcwf-p919</t>
+        </is>
+      </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWRmQkdrNXg2bFpvUTE</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWxuNHhkYXVuNlFDSVY</t>
         </is>
       </c>
       <c r="T141" t="inlineStr">
@@ -16088,15 +16092,25 @@
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V141" t="n">
-        <v>8</v>
-      </c>
-      <c r="W141" t="inlineStr"/>
-      <c r="X141" t="inlineStr"/>
-      <c r="Y141" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W141" t="n">
+        <v>1</v>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>[{'year': '2022', 'total': 1}]</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}]</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16104,12 +16118,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ca-cioos_b52d5602-f81d-4565-9574-e448e99bc997</t>
+          <t>ca-cioos_b694a5c5-6a7e-4206-96aa-5b7754323345</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -16119,7 +16133,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Bathymetry for Six Lakes on Calvert and Hecate Islands - 2016 - British Columbia - Canada</t>
+          <t>Air temperature and relative humidity time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -16137,12 +16151,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Watersheds, Geospatial</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -16165,12 +16179,12 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.09646606445312, 51.5996802644666], [-127.9508972167969, 51.5996802644666], [-127.9508972167969, 51.69171329024539], [-128.09646606445312, 51.69171329024539], [-128.09646606445312, 51.5996802644666]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.30095161, 50.04299371], [-125.08745063, 50.04299371], [-125.08745063, 51.791595], [-128.30095161, 51.791595], [-128.30095161, 50.04299371]]]}</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '741.0', 'min': '3.0'}]</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
@@ -16178,14 +16192,10 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R142" t="inlineStr">
-        <is>
-          <t>10.21966/fcwf-p919</t>
-        </is>
-      </c>
+      <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWxuNHhkYXVuNlFDSVY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWRmQkdrNXg2bFpvUTE</t>
         </is>
       </c>
       <c r="T142" t="inlineStr">
@@ -16195,25 +16205,15 @@
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="V142" t="n">
-        <v>1</v>
-      </c>
-      <c r="W142" t="n">
-        <v>1</v>
-      </c>
-      <c r="X142" t="inlineStr">
-        <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
-        </is>
-      </c>
-      <c r="Y142" t="inlineStr">
-        <is>
-          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}]</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="W142" t="inlineStr"/>
+      <c r="X142" t="inlineStr"/>
+      <c r="Y142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">

--- a/main/catalog_summary.xlsx
+++ b/main/catalog_summary.xlsx
@@ -8975,12 +8975,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
+          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
+          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -9006,11 +9006,7 @@
       <c r="H77" t="b">
         <v>0</v>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Airborne Coastal Observatory</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>completed</t>
@@ -9036,12 +9032,12 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -9052,7 +9048,7 @@
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -9066,7 +9062,7 @@
         </is>
       </c>
       <c r="V77" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
@@ -9078,12 +9074,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
+          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9093,7 +9089,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
+          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -9109,7 +9105,11 @@
       <c r="H78" t="b">
         <v>0</v>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Airborne Coastal Observatory</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr">
         <is>
           <t>completed</t>
@@ -9135,12 +9135,12 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -9151,7 +9151,7 @@
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -9165,7 +9165,7 @@
         </is>
       </c>
       <c r="V78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
@@ -10229,12 +10229,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ca-cioos_5e4f925a-9cf2-4e33-ae22-75c5b326ce6c</t>
+          <t>ca-cioos_5c13b300-e172-4010-a6d8-7586b68a3a96</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Eelgrass (Z. marina) extent at sites along the Central Coast, British Columbia</t>
+          <t>Kelp extent for the McNaughton Group Islands (2017), Manley Island (2017), and Serpent Group Islands (2016), British Columbia, Canada</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Nearshore, Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10286,11 +10286,11 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.65354407, 51.37817421], [-127.69773286, 51.37817421], [-127.69773286, 52.1127963], [-128.65354407, 52.1127963], [-128.65354407, 51.37817421]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.30122253, 51.7689035], [-128.05512885, 51.7689035], [-128.05512885, 51.98187882], [-128.30122253, 51.98187882], [-128.30122253, 51.7689035]]]}</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10300,17 +10300,17 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>10.21966/03pw-2190</t>
+          <t>10.21966/82bd-ks94</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTA3NnQ0NnRiemVLSFU</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFIWmZWeEE0RkZrZVc</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
@@ -10346,12 +10346,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ca-cioos_5c13b300-e172-4010-a6d8-7586b68a3a96</t>
+          <t>ca-cioos_5e4f925a-9cf2-4e33-ae22-75c5b326ce6c</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Kelp extent for the McNaughton Group Islands (2017), Manley Island (2017), and Serpent Group Islands (2016), British Columbia, Canada</t>
+          <t>Eelgrass (Z. marina) extent at sites along the Central Coast, British Columbia</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -10379,7 +10379,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Nearshore, Geospatial</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10403,11 +10403,11 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.30122253, 51.7689035], [-128.05512885, 51.7689035], [-128.05512885, 51.98187882], [-128.30122253, 51.98187882], [-128.30122253, 51.7689035]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.65354407, 51.37817421], [-127.69773286, 51.37817421], [-127.69773286, 52.1127963], [-128.65354407, 52.1127963], [-128.65354407, 51.37817421]]]}</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -10417,17 +10417,17 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>other, macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>10.21966/82bd-ks94</t>
+          <t>10.21966/03pw-2190</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFIWmZWeEE0RkZrZVc</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTA3NnQ0NnRiemVLSFU</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
@@ -14518,12 +14518,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ca-cioos_25674e9b-1d49-4270-b917-cfe6cdc30f95</t>
+          <t>ca-cioos_26443ab2-964f-4031-a53b-f132434573e8</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -14533,7 +14533,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Watersheds of the northern Pacific coastal temperate rainforest margin</t>
+          <t>Ecosystem Comparison Plots - Calvert Island</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -14551,7 +14551,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Geospatial, Watersheds</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -14575,57 +14575,57 @@
         </is>
       </c>
       <c r="N128" t="n">
+        <v>1</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13903808593744, 51.626542529786036], [-127.97355651855466, 51.626542529786036], [-127.97355651855466, 51.67766477883444], [-128.13903808593744, 51.67766477883444], [-128.13903808593744, 51.626542529786036]]]}</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>10.21966/1.56481</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWc4TU94c2lwT0tYa2U</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>2022-03-29</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="V128" t="n">
         <v>2</v>
       </c>
-      <c r="O128" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-143.16578297, 37.67883738], [-104.45881201, 37.67883738], [-104.45881201, 60.91786918], [-143.16578297, 60.91786918], [-143.16578297, 37.67883738]]]}</t>
-        </is>
-      </c>
-      <c r="P128" t="inlineStr">
-        <is>
-          <t>[{'max': '6000.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q128" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R128" t="inlineStr">
-        <is>
-          <t>10.21966/1.715755</t>
-        </is>
-      </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWJSa2xESlBIbk1rSXA</t>
-        </is>
-      </c>
-      <c r="T128" t="inlineStr">
-        <is>
-          <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="U128" t="inlineStr">
-        <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="V128" t="n">
-        <v>9</v>
-      </c>
       <c r="W128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 2}, {'year': '2023', 'total': 1}]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.5061/dryad.05qfttf2q', 'type': 'dois', 'status_code': 200, 'url': 'https://datadryad.org/dataset/doi:10.5061/dryad.05qfttf2q'}, {'relationship': 'citations', 'id': '10.1002/essoar.10510464.1', 'type': 'dois', 'status_code': 403, 'url': 'https://essopenarchive.org/doi/full/10.1002/essoar.10510464.1'}, {'relationship': 'citations', 'id': '10.1029/2023gl103024', 'type': 'dois', 'status_code': 403, 'url': 'https://agupubs.onlinelibrary.wiley.com/doi/10.1029/2023GL103024'}]</t>
+          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}, {'relationship': 'parts', 'id': '10.5194/bg-2017-5', 'type': 'dois', 'status_code': 200, 'url': 'https://bg.copernicus.org/articles/14/3743/2017/bg-14-3743-2017-discussion.html'}]</t>
         </is>
       </c>
     </row>
@@ -14635,12 +14635,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ca-cioos_26443ab2-964f-4031-a53b-f132434573e8</t>
+          <t>ca-cioos_25674e9b-1d49-4270-b917-cfe6cdc30f95</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -14650,7 +14650,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Ecosystem Comparison Plots - Calvert Island</t>
+          <t>Watersheds of the northern Pacific coastal temperate rainforest margin</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -14668,7 +14668,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Geospatial, Watersheds</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -14692,16 +14692,16 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13903808593744, 51.626542529786036], [-127.97355651855466, 51.626542529786036], [-127.97355651855466, 51.67766477883444], [-128.13903808593744, 51.67766477883444], [-128.13903808593744, 51.626542529786036]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-143.16578297, 37.67883738], [-104.45881201, 37.67883738], [-104.45881201, 60.91786918], [-143.16578297, 60.91786918], [-143.16578297, 37.67883738]]]}</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '6000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
@@ -14711,12 +14711,12 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>10.21966/1.56481</t>
+          <t>10.21966/1.715755</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWc4TU94c2lwT0tYa2U</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWJSa2xESlBIbk1rSXA</t>
         </is>
       </c>
       <c r="T129" t="inlineStr">
@@ -14730,19 +14730,19 @@
         </is>
       </c>
       <c r="V129" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="W129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[{'year': '2022', 'total': 2}, {'year': '2023', 'total': 1}]</t>
         </is>
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}, {'relationship': 'parts', 'id': '10.5194/bg-2017-5', 'type': 'dois', 'status_code': 200, 'url': 'https://bg.copernicus.org/articles/14/3743/2017/bg-14-3743-2017-discussion.html'}]</t>
+          <t>[{'relationship': 'citations', 'id': '10.5061/dryad.05qfttf2q', 'type': 'dois', 'status_code': 200, 'url': 'https://datadryad.org/dataset/doi:10.5061/dryad.05qfttf2q'}, {'relationship': 'citations', 'id': '10.1002/essoar.10510464.1', 'type': 'dois', 'status_code': 403, 'url': 'https://essopenarchive.org/doi/full/10.1002/essoar.10510464.1'}, {'relationship': 'citations', 'id': '10.1029/2023gl103024', 'type': 'dois', 'status_code': 403, 'url': 'https://agupubs.onlinelibrary.wiley.com/doi/10.1029/2023GL103024'}]</t>
         </is>
       </c>
     </row>
@@ -15781,12 +15781,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
+          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -15796,7 +15796,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Stage-Discharge Time Series - Calvert Island - Archived Version 1.0</t>
+          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -15814,7 +15814,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -15834,20 +15834,20 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Vancouver Island University</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>[{'max': '250.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
@@ -15855,10 +15855,14 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R139" t="inlineStr"/>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>10.21966/1.135248</t>
+        </is>
+      </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFjSmdJMGxrU1pZbXM</t>
         </is>
       </c>
       <c r="T139" t="inlineStr">
@@ -15868,15 +15872,25 @@
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V139" t="n">
-        <v>5</v>
-      </c>
-      <c r="W139" t="inlineStr"/>
-      <c r="X139" t="inlineStr"/>
-      <c r="Y139" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0</v>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15884,12 +15898,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
+          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -15899,7 +15913,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
+          <t>Stage-Discharge Time Series - Calvert Island - Archived Version 1.0</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -15917,7 +15931,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -15937,20 +15951,20 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Vancouver Island University</t>
         </is>
       </c>
       <c r="N140" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
+          <t>[{'max': '250.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
@@ -15958,14 +15972,10 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R140" t="inlineStr">
-        <is>
-          <t>10.21966/1.135248</t>
-        </is>
-      </c>
+      <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFjSmdJMGxrU1pZbXM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
         </is>
       </c>
       <c r="T140" t="inlineStr">
@@ -15975,25 +15985,15 @@
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="V140" t="n">
-        <v>2</v>
-      </c>
-      <c r="W140" t="n">
-        <v>0</v>
-      </c>
-      <c r="X140" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y140" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="W140" t="inlineStr"/>
+      <c r="X140" t="inlineStr"/>
+      <c r="Y140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16001,12 +16001,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>ca-cioos_b52d5602-f81d-4565-9574-e448e99bc997</t>
+          <t>ca-cioos_b694a5c5-6a7e-4206-96aa-5b7754323345</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -16016,7 +16016,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Bathymetry for Six Lakes on Calvert and Hecate Islands - 2016 - British Columbia - Canada</t>
+          <t>Air temperature and relative humidity time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -16034,12 +16034,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Watersheds, Geospatial</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -16062,12 +16062,12 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.09646606445312, 51.5996802644666], [-127.9508972167969, 51.5996802644666], [-127.9508972167969, 51.69171329024539], [-128.09646606445312, 51.69171329024539], [-128.09646606445312, 51.5996802644666]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.30095161, 50.04299371], [-125.08745063, 50.04299371], [-125.08745063, 51.791595], [-128.30095161, 51.791595], [-128.30095161, 50.04299371]]]}</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '741.0', 'min': '3.0'}]</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
@@ -16075,14 +16075,10 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R141" t="inlineStr">
-        <is>
-          <t>10.21966/fcwf-p919</t>
-        </is>
-      </c>
+      <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWxuNHhkYXVuNlFDSVY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWRmQkdrNXg2bFpvUTE</t>
         </is>
       </c>
       <c r="T141" t="inlineStr">
@@ -16092,25 +16088,15 @@
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="V141" t="n">
-        <v>1</v>
-      </c>
-      <c r="W141" t="n">
-        <v>1</v>
-      </c>
-      <c r="X141" t="inlineStr">
-        <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
-        </is>
-      </c>
-      <c r="Y141" t="inlineStr">
-        <is>
-          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}]</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="W141" t="inlineStr"/>
+      <c r="X141" t="inlineStr"/>
+      <c r="Y141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16118,12 +16104,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ca-cioos_b694a5c5-6a7e-4206-96aa-5b7754323345</t>
+          <t>ca-cioos_b52d5602-f81d-4565-9574-e448e99bc997</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -16133,7 +16119,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Air temperature and relative humidity time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
+          <t>Bathymetry for Six Lakes on Calvert and Hecate Islands - 2016 - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -16151,12 +16137,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Watersheds, Geospatial</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -16179,12 +16165,12 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.30095161, 50.04299371], [-125.08745063, 50.04299371], [-125.08745063, 51.791595], [-128.30095161, 51.791595], [-128.30095161, 50.04299371]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.09646606445312, 51.5996802644666], [-127.9508972167969, 51.5996802644666], [-127.9508972167969, 51.69171329024539], [-128.09646606445312, 51.69171329024539], [-128.09646606445312, 51.5996802644666]]]}</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>[{'max': '741.0', 'min': '3.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
@@ -16192,10 +16178,14 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R142" t="inlineStr"/>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>10.21966/fcwf-p919</t>
+        </is>
+      </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWRmQkdrNXg2bFpvUTE</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWxuNHhkYXVuNlFDSVY</t>
         </is>
       </c>
       <c r="T142" t="inlineStr">
@@ -16205,15 +16195,25 @@
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V142" t="n">
-        <v>8</v>
-      </c>
-      <c r="W142" t="inlineStr"/>
-      <c r="X142" t="inlineStr"/>
-      <c r="Y142" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W142" t="n">
+        <v>1</v>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>[{'year': '2022', 'total': 1}]</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}]</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">

--- a/main/catalog_summary.xlsx
+++ b/main/catalog_summary.xlsx
@@ -1614,11 +1614,11 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Nereocystis kelp canopy productivity data from BC Central Coast, v1.2.0</t>
+          <t>Nereocystis kelp canopy productivity data from BC Central Coast</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -5089,12 +5089,10 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="V42" t="n">
-        <v>7</v>
-      </c>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr"/>
       <c r="W42" t="n">
         <v>1</v>
       </c>
@@ -6574,12 +6572,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ca-cioos_6ebe47c3-6d59-4cb2-a7ba-111698445d8d</t>
+          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6589,7 +6587,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bald eagles as vectors of marine nutrients – Central Coast Islands (100 Islands study area) – May – July 2017</t>
+          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6607,7 +6605,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>100 Islands</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6627,15 +6625,15 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.58323147, 51.38160352], [-127.80979387, 51.38160352], [-127.80979387, 52.09997599], [-128.58323147, 52.09997599], [-128.58323147, 51.38160352]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6645,13 +6643,17 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>other, nutrients</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr"/>
+          <t>other, inorganicCarbon</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>10.21966/zxzr-e472</t>
+        </is>
+      </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUxkcndoNFQ4T2xyZWI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
@@ -6661,15 +6663,23 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="V56" t="n">
-        <v>1</v>
-      </c>
-      <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
-      <c r="Y56" t="inlineStr"/>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6677,12 +6687,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
+          <t>ca-cioos_6ebe47c3-6d59-4cb2-a7ba-111698445d8d</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -6692,7 +6702,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
+          <t>Bald eagles as vectors of marine nutrients – Central Coast Islands (100 Islands study area) – May – July 2017</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6710,7 +6720,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>100 Islands</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6730,61 +6740,49 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N57" t="n">
+        <v>2</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.58323147, 51.38160352], [-127.80979387, 51.38160352], [-127.80979387, 52.09997599], [-128.58323147, 52.09997599], [-128.58323147, 51.38160352]]]}</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>other, nutrients</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUxkcndoNFQ4T2xyZWI</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>2022-01-24</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="V57" t="n">
         <v>1</v>
       </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>other, inorganicCarbon</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>10.21966/zxzr-e472</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>2022-01-24</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="n">
-        <v>0</v>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6909,12 +6907,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>9e4a38d6-eb29-44a8-b495-c56ce74a227c</t>
+          <t>dd5c8784-c292-4f68-bc3d-a460adb8cdbf</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ca-cioos_c113d7a8-6a46-46fc-b49c-a4e69afedfbc</t>
+          <t>ca-cioos_b4cac70e-a6fa-4d77-8fdb-1d3612006bc4</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -6924,7 +6922,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hakai Institute’s Burke-o-Lator TCO2/pCO2 Analyzer Discrete Sample Analysis Protocols</t>
+          <t>Pacific Northwest Eelgrass Sediment Carbon Data</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6942,7 +6940,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6966,31 +6964,31 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-121.200851030026, 47.5931373865871], [-133.329762644444, 58.3685518859093], [-138.778981394444, 57.2923559868765], [-128.407887644444, 50.1363698995369], [-122.519210405026, 46.8770323398551], [-121.200851030026, 47.5931373865871]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-143.1666738, 39.75452039], [-118.41060343, 39.75452039], [-118.41060343, 59.04838928], [-143.1666738, 59.04838928], [-143.1666738, 39.75452039]]]}</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>[{'max': '50.15267028510888', 'min': '50.15091039641325'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>10.21966/1.521066</t>
+          <t>10.21966/20SJ-J017</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUQyQ3F1WFBEZ2FkTnI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVlYNnVCWW5yQ3RrUkM</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
@@ -7000,21 +6998,23 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr"/>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="V59" t="n">
+        <v>8</v>
+      </c>
       <c r="W59" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>[{'year': '2024', 'total': 1}, {'year': '2025', 'total': 2}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.21966/k1xg-6920', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_355467ad-104d-40a6-b06e-52a67bfe247e'}, {'relationship': 'citations', 'id': '10.1002/eap.70058', 'type': 'dois', 'status_code': 403, 'url': 'https://esajournals.onlinelibrary.wiley.com/doi/10.1002/eap.70058'}, {'relationship': 'citations', 'id': '10.1002/edn3.70158', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/edn3.70158'}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -7024,12 +7024,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1f798a06-9c01-4025-93c6-b1a9f8ce6832</t>
+          <t>9e4a38d6-eb29-44a8-b495-c56ce74a227c</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ca-cioos_d200376b-7dd8-4778-b3f5-379243bf93b8</t>
+          <t>ca-cioos_c113d7a8-6a46-46fc-b49c-a4e69afedfbc</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>High-resolution record of surface water pH at Sentry Shoal in the Northern Strait of Georgia</t>
+          <t>Hakai Institute’s Burke-o-Lator TCO2/pCO2 Analyzer Discrete Sample Analysis Protocols</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -7081,31 +7081,31 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.9855, 49.9066], [-124.9854, 49.9066], [-124.9854, 49.9067], [-124.9855, 49.9067], [-124.9855, 49.9066]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-121.200851030026, 47.5931373865871], [-133.329762644444, 58.3685518859093], [-138.778981394444, 57.2923559868765], [-128.407887644444, 50.1363698995369], [-122.519210405026, 46.8770323398551], [-121.200851030026, 47.5931373865871]]]}</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '50.15267028510888', 'min': '50.15091039641325'}]</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>10.21966/1.715693</t>
+          <t>10.21966/1.521066</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUlpdWJIYjdIVDZJWTk</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUQyQ3F1WFBEZ2FkTnI</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
@@ -7118,20 +7118,18 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="V60" t="n">
-        <v>1</v>
-      </c>
+      <c r="V60" t="inlineStr"/>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2024', 'total': 1}, {'year': '2025', 'total': 2}]</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'citations', 'id': '10.21966/k1xg-6920', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_355467ad-104d-40a6-b06e-52a67bfe247e'}, {'relationship': 'citations', 'id': '10.1002/eap.70058', 'type': 'dois', 'status_code': 403, 'url': 'https://esajournals.onlinelibrary.wiley.com/doi/10.1002/eap.70058'}, {'relationship': 'citations', 'id': '10.1002/edn3.70158', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/edn3.70158'}]</t>
         </is>
       </c>
     </row>
@@ -7141,12 +7139,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>24c3b914-33d7-4267-a1aa-8ce7523b296d</t>
+          <t>1f798a06-9c01-4025-93c6-b1a9f8ce6832</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ca-cioos_dc50a22a-44c0-478c-aa19-a46343bc764a</t>
+          <t>ca-cioos_d200376b-7dd8-4778-b3f5-379243bf93b8</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7156,7 +7154,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Barnacle Dynamics: Point Intercept Surveys - BC Central Coast - 2019</t>
+          <t>High-resolution record of surface water pH at Sentry Shoal in the Northern Strait of Georgia</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -7174,7 +7172,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7202,7 +7200,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.1518199, 51.64582999], [-128.12195082, 51.64582999], [-128.12195082, 51.66861942], [-128.1518199, 51.66861942], [-128.1518199, 51.64582999]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.9855, 49.9066], [-124.9854, 49.9066], [-124.9854, 49.9067], [-124.9855, 49.9067], [-124.9855, 49.9066]]]}</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7217,12 +7215,12 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>10.21966/m8kp-gy81</t>
+          <t>10.21966/1.715693</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUFaZGRYOURGWVg5UzA</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUlpdWJIYjdIVDZJWTk</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
@@ -7232,10 +7230,12 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr"/>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="V61" t="n">
+        <v>1</v>
+      </c>
       <c r="W61" t="n">
         <v>0</v>
       </c>
@@ -7256,12 +7256,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
+          <t>24c3b914-33d7-4267-a1aa-8ce7523b296d</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ca-cioos_f00b9c87-190e-4b89-a864-7c012b989e49</t>
+          <t>ca-cioos_dc50a22a-44c0-478c-aa19-a46343bc764a</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>High-resolution record of surface seawater CO2 content from December 2014 to April 2016 collected in Hyacinthe Bay, British Columbia, Canada. Version 1.0.</t>
+          <t>Barnacle Dynamics: Point Intercept Surveys - BC Central Coast - 2019</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7313,31 +7313,31 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.2229619026184, 50.116395452024676], [-125.22092342376709, 50.116395452024676], [-125.22092342376709, 50.11764753238538], [-125.2229619026184, 50.11764753238538], [-125.2229619026184, 50.116395452024676]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.1518199, 51.64582999], [-128.12195082, 51.64582999], [-128.12195082, 51.66861942], [-128.1518199, 51.66861942], [-128.1518199, 51.64582999]]]}</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>[{'max': '1.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>10.21966/1.437736</t>
+          <t>10.21966/m8kp-gy81</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXg3Yk10WFU2UGRwYkY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUFaZGRYOURGWVg5UzA</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
@@ -7347,12 +7347,10 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="V62" t="n">
-        <v>3</v>
-      </c>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr"/>
       <c r="W62" t="n">
         <v>0</v>
       </c>
@@ -7373,12 +7371,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
+          <t>d8d3f510-8d7c-4b51-ba80-f7a77244eb4e</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ca-cioos_fcb4dfb6-606b-4b4b-bdcb-90f3f480fc33</t>
+          <t>ca-cioos_f00b9c87-190e-4b89-a864-7c012b989e49</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7388,7 +7386,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Data on invasion of Calvert Island by Orthione griffenis</t>
+          <t>High-resolution record of surface seawater CO2 content from December 2014 to April 2016 collected in Hyacinthe Bay, British Columbia, Canada. Version 1.0.</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7404,7 +7402,11 @@
       <c r="H63" t="b">
         <v>0</v>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Oceanography</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr">
         <is>
           <t>completed</t>
@@ -7426,31 +7428,31 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.17334953, 51.61670267], [-127.92753044, 51.61670267], [-127.92753044, 51.73677458], [-128.17334953, 51.73677458], [-128.17334953, 51.61670267]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.2229619026184, 50.116395452024676], [-125.22092342376709, 50.116395452024676], [-125.22092342376709, 50.11764753238538], [-125.2229619026184, 50.11764753238538], [-125.2229619026184, 50.116395452024676]]]}</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>other, invertebrateAbundanceAndDistribution</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>10.21966/kddh-gj22</t>
+          <t>10.21966/1.437736</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWpwT0Z6RlAySHp6cU0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXg3Yk10WFU2UGRwYkY</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
@@ -7464,7 +7466,7 @@
         </is>
       </c>
       <c r="V63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W63" t="n">
         <v>0</v>
@@ -7486,12 +7488,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
+          <t>ad032cd1-86cc-47cc-ac01-fce09e4cf8d9</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ca-cioos_41b0137d-6ac0-407d-a550-dd375475b2b0</t>
+          <t>ca-cioos_fcb4dfb6-606b-4b4b-bdcb-90f3f480fc33</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -7501,7 +7503,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Seafloor Observatory in Hyacinthe Bay, Quadra Island, British Columbia, Canada (Provisional)</t>
+          <t>Data on invasion of Calvert Island by Orthione griffenis</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7517,14 +7519,10 @@
       <c r="H64" t="b">
         <v>0</v>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Oceanography</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -7547,41 +7545,55 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.22003, 50.11736]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.17334953, 51.61670267], [-127.92753044, 51.61670267], [-127.92753044, 51.73677458], [-128.17334953, 51.73677458], [-128.17334953, 51.61670267]]]}</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>[{'max': '20.0', 'min': '10.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>oxygen, dissolvedOrganicCarbon, subSurfaceSalinity, subSurfaceTemperature, seaSurfaceHeight</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr"/>
+          <t>other, invertebrateAbundanceAndDistribution</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>10.21966/kddh-gj22</t>
+        </is>
+      </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MW5xCIKrrtNHbrGqNTx</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWpwT0Z6RlAySHp6cU0</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>2022-02-01</t>
+          <t>2022-01-24</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V64" t="n">
-        <v>2</v>
-      </c>
-      <c r="W64" t="inlineStr"/>
-      <c r="X64" t="inlineStr"/>
-      <c r="Y64" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7589,12 +7601,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
+          <t>0c864dea-998e-4a5e-94d3-c5fbda339eee</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ca-cioos_87a845e3-e71a-43cc-a75f-ec6a3b812a0e</t>
+          <t>ca-cioos_41b0137d-6ac0-407d-a550-dd375475b2b0</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -7604,7 +7616,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Acoustic Doppler Current Profiler Time Series from Fixed Platform on the British Columbia Central Coast (Provisional)</t>
+          <t>Seafloor Observatory in Hyacinthe Bay, Quadra Island, British Columbia, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7650,23 +7662,23 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.2, 51.61], [-128.6, 51.95], [-128.2, 52.04], [-127.8, 51.61], [-125.0, 50.12], [-125.2, 50.04], [-125.2, 50.04], [-125.2, 50.04], [-128.2, 51.61]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.22003, 50.11736]}</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>[{'max': '90.0', 'min': '0.0'}]</t>
+          <t>[{'max': '20.0', 'min': '10.0'}]</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>subSurfaceCurrents, subSurfaceTemperature, seaSurfaceHeight</t>
+          <t>oxygen, dissolvedOrganicCarbon, subSurfaceSalinity, subSurfaceTemperature, seaSurfaceHeight</t>
         </is>
       </c>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MsbCMOYj2L_7dgICnzw</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MW5xCIKrrtNHbrGqNTx</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
@@ -7676,11 +7688,11 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="V65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W65" t="inlineStr"/>
       <c r="X65" t="inlineStr"/>
@@ -7692,12 +7704,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
+          <t>9c581481-f2ee-4353-b1ab-c5bf242945fe</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ca-cioos_e09522d7-24f7-4c0e-afac-6cafd22a54f6</t>
+          <t>ca-cioos_87a845e3-e71a-43cc-a75f-ec6a3b812a0e</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -7707,7 +7719,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>High-resolution record of CO2 content from October 2013 to December 2018 measured in seawater entering the Alutiiq Pride Shellfish Hatchery in Seward, Alaska, USA</t>
+          <t>Acoustic Doppler Current Profiler Time Series from Fixed Platform on the British Columbia Central Coast (Provisional)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7730,7 +7742,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -7753,27 +7765,23 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-150.14476634, 59.68961051], [-148.42177964, 59.68961051], [-148.42177964, 60.2984757], [-150.14476634, 60.2984757], [-150.14476634, 59.68961051]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.2, 51.61], [-128.6, 51.95], [-128.2, 52.04], [-127.8, 51.61], [-125.0, 50.12], [-125.2, 50.04], [-125.2, 50.04], [-125.2, 50.04], [-128.2, 51.61]]]}</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '90.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>10.21966/nkcy-8c07</t>
-        </is>
-      </c>
+          <t>subSurfaceCurrents, subSurfaceTemperature, seaSurfaceHeight</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVZUYVNsZXAyTXh5bnQ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MsbCMOYj2L_7dgICnzw</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
@@ -7783,25 +7791,15 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="V66" t="n">
-        <v>6</v>
-      </c>
-      <c r="W66" t="n">
-        <v>0</v>
-      </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7809,12 +7807,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1a9a5aae-41ee-4272-a52e-6c37abedfbff</t>
+          <t>15f1d4a2-c82a-450c-a8f7-badb34b9c0dc</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ca-cioos_4b5c0c20-2115-4986-bf56-237e360240bd</t>
+          <t>ca-cioos_e09522d7-24f7-4c0e-afac-6cafd22a54f6</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -7824,7 +7822,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Freshwater and marine water quality (nutrients and carbon) - Calvert Island - 2014 to 2018</t>
+          <t>High-resolution record of CO2 content from October 2013 to December 2018 measured in seawater entering the Alutiiq Pride Shellfish Hatchery in Seward, Alaska, USA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7842,7 +7840,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Oceanography, Watersheds</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7870,7 +7868,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.2, 51.64], [-127.9, 51.64], [-127.9, 51.74], [-128.2, 51.74], [-128.2, 51.64]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-150.14476634, 59.68961051], [-148.42177964, 59.68961051], [-148.42177964, 60.2984757], [-150.14476634, 60.2984757], [-150.14476634, 59.68961051]]]}</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7880,43 +7878,43 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>nutrients, dissolvedOrganicCarbon</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>10.21966/n0h9-cq15</t>
+          <t>10.21966/nkcy-8c07</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MuwHJS-RtHVqJmki_OG</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVZUYVNsZXAyTXh5bnQ</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>2022-02-02</t>
+          <t>2022-02-01</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="V67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.5194/bg-18-3029-2021', 'type': 'dois', 'status_code': 200, 'url': 'https://bg.copernicus.org/articles/18/3029/2021/'}, {'relationship': 'parts', 'id': '10.5194/bg-2020-350', 'type': 'dois', 'status_code': 200, 'url': 'https://bg.copernicus.org/articles/18/3029/2021/bg-18-3029-2021-discussion.html'}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -7926,12 +7924,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
+          <t>1a9a5aae-41ee-4272-a52e-6c37abedfbff</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ca-cioos_a0ca5d26-b457-4726-97d4-ed0c8dd6cd99</t>
+          <t>ca-cioos_4b5c0c20-2115-4986-bf56-237e360240bd</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -7941,7 +7939,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Seascape connectivity data from a sub-tidal Zostera marina meadow, Choked Passage, Calvert Island, 2015</t>
+          <t>Freshwater and marine water quality (nutrients and carbon) - Calvert Island - 2014 to 2018</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7959,7 +7957,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Oceanography, Watersheds</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -7987,7 +7985,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.24596616, 51.41449798], [-127.75115224, 51.41449798], [-127.75115224, 51.74287494], [-128.24596616, 51.74287494], [-128.24596616, 51.41449798]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.2, 51.64], [-127.9, 51.64], [-127.9, 51.74], [-128.2, 51.74], [-128.2, 51.64]]]}</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7997,17 +7995,17 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>other, seagrassCoverAndComposition</t>
+          <t>nutrients, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>10.21966/exy6-1k58</t>
+          <t>10.21966/n0h9-cq15</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUoydUo4NEl3VEtGdU0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MuwHJS-RtHVqJmki_OG</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
@@ -8017,23 +8015,23 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="V68" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'citations', 'id': '10.5194/bg-18-3029-2021', 'type': 'dois', 'status_code': 200, 'url': 'https://bg.copernicus.org/articles/18/3029/2021/'}, {'relationship': 'parts', 'id': '10.5194/bg-2020-350', 'type': 'dois', 'status_code': 200, 'url': 'https://bg.copernicus.org/articles/18/3029/2021/bg-18-3029-2021-discussion.html'}]</t>
         </is>
       </c>
     </row>
@@ -8043,12 +8041,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>4becb6c2-ebdb-43f2-8f15-dee50aaa19d8</t>
+          <t>dd30b32a-2099-4909-838d-6ade9804381a</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ca-cioos_fd5ada9a-5719-4ca1-89d2-17adb48d1493</t>
+          <t>ca-cioos_a0ca5d26-b457-4726-97d4-ed0c8dd6cd99</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8058,7 +8056,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Eelgrass (Z. marina) extent at Gulf Islands National Park Reserve eelgrass monitoring sites (2017, 2018) v1.0.0</t>
+          <t>Seascape connectivity data from a sub-tidal Zostera marina meadow, Choked Passage, Calvert Island, 2015</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -8076,7 +8074,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Nearshore, Geospatial</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8104,27 +8102,27 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.81789453, 48.48393505], [-122.96096027, 48.48393505], [-122.96096027, 49.05595865], [-123.81789453, 49.05595865], [-123.81789453, 48.48393505]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.24596616, 51.41449798], [-127.75115224, 51.41449798], [-127.75115224, 51.74287494], [-128.24596616, 51.74287494], [-128.24596616, 51.41449798]]]}</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>[{'max': '100.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>10.21966/t8hm-ge90</t>
+          <t>10.21966/exy6-1k58</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXBNZnZGekFJcFFDcm8</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUoydUo4NEl3VEtGdU0</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
@@ -8134,10 +8132,12 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr"/>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="V69" t="n">
+        <v>9</v>
+      </c>
       <c r="W69" t="n">
         <v>0</v>
       </c>
@@ -8158,12 +8158,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>26186b9d-a292-43c4-aec6-e928aa52b002</t>
+          <t>4becb6c2-ebdb-43f2-8f15-dee50aaa19d8</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ca-cioos_63765cc6-5730-4a28-9d96-3de38066312f</t>
+          <t>ca-cioos_fd5ada9a-5719-4ca1-89d2-17adb48d1493</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>High-resolution record of surface seawater CO2 content from April 2016 to November 2017 collected in Hyacinthe Bay, British Columbia, Canada</t>
+          <t>Eelgrass (Z. marina) extent at Gulf Islands National Park Reserve eelgrass monitoring sites (2017, 2018) v1.0.0</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore, Geospatial</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8215,41 +8215,41 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.22364854812619, 50.116106505752896], [-125.22126674652097, 50.116106505752896], [-125.22126674652097, 50.11770256813347], [-125.22364854812619, 50.11770256813347], [-125.22364854812619, 50.116106505752896]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.81789453, 48.48393505], [-122.96096027, 48.48393505], [-122.96096027, 49.05595865], [-123.81789453, 49.05595865], [-123.81789453, 48.48393505]]]}</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '100.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>10.21966/1.614670</t>
+          <t>10.21966/t8hm-ge90</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVpjRzlIZEFLbE9tSnA</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXBNZnZGekFJcFFDcm8</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>2022-02-03</t>
+          <t>2022-02-02</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="V70" t="inlineStr"/>
@@ -8273,12 +8273,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>f31f38bf-16bc-4136-8982-a2df5fefb3a0</t>
+          <t>26186b9d-a292-43c4-aec6-e928aa52b002</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ca-cioos_7c47472a-b16c-446c-89d5-eefa23e07922</t>
+          <t>ca-cioos_63765cc6-5730-4a28-9d96-3de38066312f</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>High-resolution record of surface seawater CO2 content from November 2017 to June 2018 collected in Hyacinthe Bay, British Columbia, Canada</t>
+          <t>High-resolution record of surface seawater CO2 content from April 2016 to November 2017 collected in Hyacinthe Bay, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -8330,7 +8330,7 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -8349,12 +8349,12 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>10.21966/1.715729</t>
+          <t>10.21966/1.614670</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUhwbUdDUUlVTWtHYzE</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVpjRzlIZEFLbE9tSnA</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
@@ -8364,12 +8364,10 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="V71" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr"/>
       <c r="W71" t="n">
         <v>0</v>
       </c>
@@ -8390,12 +8388,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>45983472-7627-4227-b312-079c2aeda7ef</t>
+          <t>f31f38bf-16bc-4136-8982-a2df5fefb3a0</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ca-cioos_a72c43e2-5b4d-4d56-89d4-464b4c513710</t>
+          <t>ca-cioos_7c47472a-b16c-446c-89d5-eefa23e07922</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8405,7 +8403,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Surface water CO2 parameters collected by shellfish growers and partners in the northern Salish Sea from 2016 to 2018</t>
+          <t>High-resolution record of surface seawater CO2 content from November 2017 to June 2018 collected in Hyacinthe Bay, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -8451,7 +8449,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.57747949, 49.70969514], [-124.52984083, 49.70969514], [-124.52984083, 50.11496976], [-125.57747949, 50.11496976], [-125.57747949, 49.70969514]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.22364854812619, 50.116106505752896], [-125.22126674652097, 50.116106505752896], [-125.22126674652097, 50.11770256813347], [-125.22364854812619, 50.11770256813347], [-125.22364854812619, 50.116106505752896]]]}</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8466,12 +8464,12 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>10.21966/1.715756</t>
+          <t>10.21966/1.715729</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWYwNjRsV2piMFJOR08</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUhwbUdDUUlVTWtHYzE</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
@@ -8481,7 +8479,7 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V72" t="n">
@@ -8507,12 +8505,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
+          <t>45983472-7627-4227-b312-079c2aeda7ef</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ca-cioos_77a256cd-baf7-434e-9f62-53ba809e48cb</t>
+          <t>ca-cioos_a72c43e2-5b4d-4d56-89d4-464b4c513710</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -8522,7 +8520,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>High-resolution record of 8-m seawater CO2 content entering Fanny Bay Oysters in Baynes Sound, British Columbia, Canada from March 2017 to November 2017</t>
+          <t>Surface water CO2 parameters collected by shellfish growers and partners in the northern Salish Sea from 2016 to 2018</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -8564,11 +8562,11 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.88983154296876, 49.44759314103575], [-124.70993041992188, 49.44759314103575], [-124.70993041992188, 49.56975910961884], [-124.88983154296876, 49.56975910961884], [-124.88983154296876, 49.44759314103575]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.57747949, 49.70969514], [-124.52984083, 49.70969514], [-124.52984083, 50.11496976], [-125.57747949, 50.11496976], [-125.57747949, 49.70969514]]]}</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8583,22 +8581,22 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>10.21966/1.622315</t>
+          <t>10.21966/1.715756</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTV4aEZoVWsyRXpHWno</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWYwNjRsV2piMFJOR08</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>2022-02-04</t>
+          <t>2022-02-03</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="V73" t="n">
@@ -8624,12 +8622,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>6338c2fa-3d4d-42dc-9c91-31761365e11e</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ca-cioos_804b5b42-5550-4620-b789-7c2fe9572c03</t>
+          <t>ca-cioos_77a256cd-baf7-434e-9f62-53ba809e48cb</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -8639,7 +8637,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Zooplankton - Taxonomy – Northern Strait of Georgia, Discovery Islands, Johnstone Strait, and Queen Charlotte Strait – April to July 2015 and 2016</t>
+          <t>High-resolution record of 8-m seawater CO2 content entering Fanny Bay Oysters in Baynes Sound, British Columbia, Canada from March 2017 to November 2017</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -8662,7 +8660,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>underDevelopment</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -8681,45 +8679,45 @@
         </is>
       </c>
       <c r="N74" t="n">
+        <v>3</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.88983154296876, 49.44759314103575], [-124.70993041992188, 49.44759314103575], [-124.70993041992188, 49.56975910961884], [-124.88983154296876, 49.56975910961884], [-124.88983154296876, 49.44759314103575]]]}</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>other, inorganicCarbon</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>10.21966/1.622315</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTV4aEZoVWsyRXpHWno</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>2022-02-04</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="V74" t="n">
         <v>1</v>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.93452704, 49.56730131], [-124.18481219, 49.56730131], [-124.18481219, 50.90762515], [-126.93452704, 50.90762515], [-126.93452704, 49.56730131]]]}</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>other, zooplanktonBiomassAndDiversity</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr">
-        <is>
-          <t>10.21966/bhqd-9361</t>
-        </is>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTZhamNPb0U3cThnR0o</t>
-        </is>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>2022-02-04</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="V74" t="n">
-        <v>5</v>
       </c>
       <c r="W74" t="n">
         <v>0</v>
@@ -8741,12 +8739,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ca-cioos_a0263680-f0d5-46d5-85ea-483fa58c74b6</t>
+          <t>ca-cioos_804b5b42-5550-4620-b789-7c2fe9572c03</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -8756,7 +8754,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>High-resolution record of sea surface nitrate at Sentry Shoal in the Northern Strait of Georgia, British Columbia, Canada from 2015 to 2017.</t>
+          <t>Zooplankton - Taxonomy – Northern Strait of Georgia, Discovery Islands, Johnstone Strait, and Queen Charlotte Strait – April to July 2015 and 2016</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8798,11 +8796,11 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.2942704, 49.83702595], [-124.90571487, 49.83702595], [-124.90571487, 50.05976151], [-125.2942704, 50.05976151], [-125.2942704, 49.83702595]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.93452704, 49.56730131], [-124.18481219, 49.56730131], [-124.18481219, 50.90762515], [-126.93452704, 50.90762515], [-126.93452704, 49.56730131]]]}</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8812,17 +8810,17 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>nutrients</t>
+          <t>other, zooplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>10.21966/yk87-4x24</t>
+          <t>10.21966/bhqd-9361</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTZ1QmZ1a3ZiZWEwM24</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTZhamNPb0U3cThnR0o</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
@@ -8832,12 +8830,10 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="V75" t="n">
-        <v>4</v>
-      </c>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr"/>
       <c r="W75" t="n">
         <v>0</v>
       </c>
@@ -8858,12 +8854,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>7f23d45b-b777-491c-b602-def5402d3d83</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
+          <t>ca-cioos_a0263680-f0d5-46d5-85ea-483fa58c74b6</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -8873,7 +8869,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
+          <t>High-resolution record of sea surface nitrate at Sentry Shoal in the Northern Strait of Georgia, British Columbia, Canada from 2015 to 2017.</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -8889,10 +8885,14 @@
       <c r="H76" t="b">
         <v>0</v>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Oceanography</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>underDevelopment</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -8915,28 +8915,32 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.2942704, 49.83702595], [-124.90571487, 49.83702595], [-124.90571487, 50.05976151], [-125.2942704, 50.05976151], [-125.2942704, 49.83702595]]]}</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr"/>
+          <t>nutrients</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>10.21966/yk87-4x24</t>
+        </is>
+      </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTZ1QmZ1a3ZiZWEwM24</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2022-02-04</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8947,9 +8951,19 @@
       <c r="V76" t="n">
         <v>4</v>
       </c>
-      <c r="W76" t="inlineStr"/>
-      <c r="X76" t="inlineStr"/>
-      <c r="Y76" t="inlineStr"/>
+      <c r="W76" t="n">
+        <v>0</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9060,12 +9074,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>e3205958-52b4-4c42-a02d-34d713a20a53</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ca-cioos_62de21ed-90fb-422a-9c55-29c513a00f95</t>
+          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9075,7 +9089,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Kilbella River Estuary LiDAR Survey - 2019 - Airborne Coastal Observatory</t>
+          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -9091,11 +9105,7 @@
       <c r="H78" t="b">
         <v>0</v>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Airborne Coastal Observatory</t>
-        </is>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>completed</t>
@@ -9121,12 +9131,12 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 51.72], [-127.3, 51.72], [-127.3, 51.74], [-127.4, 51.74], [-127.4, 51.72]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>[{'max': '50.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -9137,7 +9147,7 @@
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6CPeL2BfoPN85rGFk</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -9151,7 +9161,7 @@
         </is>
       </c>
       <c r="V78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
@@ -9163,12 +9173,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
+          <t>e3205958-52b4-4c42-a02d-34d713a20a53</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ca-cioos_95bee6a0-ae38-4427-b5b2-5cc5835df70d</t>
+          <t>ca-cioos_62de21ed-90fb-422a-9c55-29c513a00f95</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9178,7 +9188,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>North Vancouver Island Survey - 2019 - Airborne Coastal Observatory</t>
+          <t>Kilbella River Estuary LiDAR Survey - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -9194,7 +9204,11 @@
       <c r="H79" t="b">
         <v>0</v>
       </c>
-      <c r="I79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Airborne Coastal Observatory</t>
+        </is>
+      </c>
       <c r="J79" t="inlineStr">
         <is>
           <t>completed</t>
@@ -9220,12 +9234,12 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.3, 50.33], [-127.6, 50.33], [-127.6, 50.63], [-128.3, 50.63], [-128.3, 50.33]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 51.72], [-127.3, 51.72], [-127.3, 51.74], [-127.4, 51.74], [-127.4, 51.72]]]}</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>[{'max': '500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '50.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -9236,7 +9250,7 @@
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6hTZuLZ6h5NLfVXzz</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6CPeL2BfoPN85rGFk</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
@@ -9250,7 +9264,7 @@
         </is>
       </c>
       <c r="V79" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W79" t="inlineStr"/>
       <c r="X79" t="inlineStr"/>
@@ -9262,12 +9276,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
+          <t>b5ee0615-c04d-462e-8199-f611bc6370ce</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ca-cioos_a60a0468-3f56-4f22-abd4-5268fcfb9744</t>
+          <t>ca-cioos_95bee6a0-ae38-4427-b5b2-5cc5835df70d</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9277,7 +9291,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Owikeno Basin LiDAR Survey - 2019 - Airborne Coastal Observatory</t>
+          <t>North Vancouver Island Survey - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -9319,12 +9333,12 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.3, 51.46], [-125.9, 51.46], [-125.9, 51.92], [-127.3, 51.92], [-127.3, 51.46]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.3, 50.33], [-127.6, 50.33], [-127.6, 50.63], [-128.3, 50.63], [-128.3, 50.33]]]}</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>[{'max': '2500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -9335,7 +9349,7 @@
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MjBOaZ2eyXo9wQ38kdy</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6hTZuLZ6h5NLfVXzz</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
@@ -9361,12 +9375,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>727b8863-91cc-4765-b0c0-80cb74b11182</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ca-cioos_bb59cb9e-887a-40a3-b41a-f4a5b2263ce6</t>
+          <t>ca-cioos_a60a0468-3f56-4f22-abd4-5268fcfb9744</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -9376,7 +9390,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Fountain Valley LiDAR Data - 2019 &amp; 2020 - Hakai Airborne Coastal Observatory - British Columbia - Canada</t>
+          <t>Owikeno Basin LiDAR Survey - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -9418,12 +9432,12 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.0, 50.56], [-121.7, 50.56], [-121.7, 50.8], [-122.0, 50.8], [-122.0, 50.56]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.3, 51.46], [-125.9, 51.46], [-125.9, 51.92], [-127.3, 51.92], [-127.3, 51.46]]]}</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>[{'max': '1500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -9434,7 +9448,7 @@
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MmUnbGWVNvtiQAsYVPj</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MjBOaZ2eyXo9wQ38kdy</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
@@ -9460,12 +9474,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ca-cioos_c3958106-fc49-44bd-8227-bfc3e8bcb58c</t>
+          <t>ca-cioos_bb59cb9e-887a-40a3-b41a-f4a5b2263ce6</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -9475,7 +9489,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Moore Island Archaeology Survey - 2019 - Airborne Coastal Observatory</t>
+          <t>Fountain Valley LiDAR Data - 2019 &amp; 2020 - Hakai Airborne Coastal Observatory - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -9491,11 +9505,7 @@
       <c r="H82" t="b">
         <v>0</v>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>Airborne Coastal Observatory</t>
-        </is>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>completed</t>
@@ -9521,12 +9531,12 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.5, 52.65], [-129.4, 52.65], [-129.4, 52.7], [-129.5, 52.7], [-129.5, 52.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.0, 50.56], [-121.7, 50.56], [-121.7, 50.8], [-122.0, 50.8], [-122.0, 50.56]]]}</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>[{'max': '150.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
@@ -9534,14 +9544,10 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>10.21966/wfcv-n753</t>
-        </is>
-      </c>
+      <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6MBp3WwVTVbFK-0kv</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MmUnbGWVNvtiQAsYVPj</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
@@ -9555,21 +9561,11 @@
         </is>
       </c>
       <c r="V82" t="n">
-        <v>3</v>
-      </c>
-      <c r="W82" t="n">
-        <v>0</v>
-      </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="inlineStr"/>
+      <c r="Y82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9577,12 +9573,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ca-cioos_c3eff62f-bcee-4faa-a7e1-7b9380d94e74</t>
+          <t>ca-cioos_c3958106-fc49-44bd-8227-bfc3e8bcb58c</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -9592,7 +9588,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ancient Forest Wetlands, BC - Upper Fraser River - 2019 - Airborne Coastal Observatory</t>
+          <t>Moore Island Archaeology Survey - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -9610,7 +9606,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -9638,12 +9634,12 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-121.3, 53.79], [-121.2, 53.79], [-121.2, 53.84], [-121.3, 53.84], [-121.3, 53.79]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.5, 52.65], [-129.4, 52.65], [-129.4, 52.7], [-129.5, 52.7], [-129.5, 52.65]]]}</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>[{'max': '500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '150.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -9653,12 +9649,12 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>10.21966/eysg-7a26</t>
+          <t>10.21966/wfcv-n753</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6RrLonwFgP-TX9bPv</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6MBp3WwVTVbFK-0kv</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
@@ -9694,12 +9690,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
+          <t>a8d40002-d393-40da-882c-73c0ad8ca7e6</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ca-cioos_d2e83e40-9e95-4a47-a899-b37c744be3ab</t>
+          <t>ca-cioos_c3eff62f-bcee-4faa-a7e1-7b9380d94e74</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -9709,7 +9705,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Fin Island &amp; K'yel - 2020 - Airborne Coastal Observatory Data</t>
+          <t>Ancient Forest Wetlands, BC - Upper Fraser River - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -9725,7 +9721,11 @@
       <c r="H84" t="b">
         <v>0</v>
       </c>
-      <c r="I84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Geospatial, Airborne Coastal Observatory</t>
+        </is>
+      </c>
       <c r="J84" t="inlineStr">
         <is>
           <t>completed</t>
@@ -9751,7 +9751,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.4, 53.03], [-129.1, 53.03], [-129.1, 53.29], [-129.4, 53.29], [-129.4, 53.03]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-121.3, 53.79], [-121.2, 53.79], [-121.2, 53.84], [-121.3, 53.84], [-121.3, 53.79]]]}</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9764,10 +9764,14 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr"/>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>10.21966/eysg-7a26</t>
+        </is>
+      </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNm5cwomXVNI6vWU-R</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6RrLonwFgP-TX9bPv</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
@@ -9781,11 +9785,21 @@
         </is>
       </c>
       <c r="V84" t="n">
-        <v>4</v>
-      </c>
-      <c r="W84" t="inlineStr"/>
-      <c r="X84" t="inlineStr"/>
-      <c r="Y84" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="W84" t="n">
+        <v>0</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9793,12 +9807,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>826d8228-baab-4191-82de-44701cd93806</t>
+          <t>8d3f619f-e3e5-44a7-8b35-7e4ed1e6af31</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ca-cioos_e0c768fc-5c37-455f-b2a3-604f766f4148</t>
+          <t>ca-cioos_d2e83e40-9e95-4a47-a899-b37c744be3ab</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -9808,7 +9822,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Nanwakolas Watershed Surveys - Knight Inlet - 2019 - Hakai Airborne Coastal Observatory</t>
+          <t>Fin Island &amp; K'yel - 2020 - Airborne Coastal Observatory Data</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -9850,12 +9864,12 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.1, 50.54], [-125.3, 50.54], [-125.3, 51.02], [-126.1, 51.02], [-126.1, 50.54]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.4, 53.03], [-129.1, 53.03], [-129.1, 53.29], [-129.4, 53.29], [-129.4, 53.03]]]}</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>[{'max': '1500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -9866,7 +9880,7 @@
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkEoax-I-IalULFPmu9</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNm5cwomXVNI6vWU-R</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
@@ -9892,12 +9906,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>826d8228-baab-4191-82de-44701cd93806</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ca-cioos_2a92ca16-f5c6-4362-acea-6bb5117b8d65</t>
+          <t>ca-cioos_e0c768fc-5c37-455f-b2a3-604f766f4148</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -9907,7 +9921,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Google Earth Engine Kelp Tool - Central Coast Output - Version 1.0.0</t>
+          <t>Nanwakolas Watershed Surveys - Knight Inlet - 2019 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -9923,11 +9937,7 @@
       <c r="H86" t="b">
         <v>0</v>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>Geospatial</t>
-        </is>
-      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>completed</t>
@@ -9953,12 +9963,12 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-130.35642493, 50.22213452], [-126.18162025, 50.22213452], [-126.18162025, 52.9911972], [-130.35642493, 52.9911972], [-130.35642493, 50.22213452]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.1, 50.54], [-125.3, 50.54], [-125.3, 51.02], [-126.1, 51.02], [-126.1, 50.54]]]}</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
@@ -9969,12 +9979,12 @@
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFUcWNIVGxwZEVLNTE</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkEoax-I-IalULFPmu9</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>2022-03-02</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9995,12 +10005,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2fe3bd2a-973e-48db-a599-6d44ca1ef0ad</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ca-cioos_27ba6c11-2421-4e85-bc11-1c1083514ed9</t>
+          <t>ca-cioos_2a92ca16-f5c6-4362-acea-6bb5117b8d65</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10010,7 +10020,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Owikeno Lake Bathymetric Survey</t>
+          <t>Google Earth Engine Kelp Tool - Central Coast Output - Version 1.0.0</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -10048,7 +10058,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Hakai Geospatial</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N87" t="n">
@@ -10056,7 +10066,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.22312137, 51.63113942], [-126.67792484, 51.63113942], [-126.67792484, 51.7324654], [-127.22312137, 51.7324654], [-127.22312137, 51.63113942]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-130.35642493, 50.22213452], [-126.18162025, 50.22213452], [-126.18162025, 52.9911972], [-130.35642493, 52.9911972], [-130.35642493, 50.22213452]]]}</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -10069,14 +10079,10 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr">
-        <is>
-          <t>10.21966/31db-5090</t>
-        </is>
-      </c>
+      <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFqOFB5dmFHWXM5am0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFUcWNIVGxwZEVLNTE</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
@@ -10086,25 +10092,15 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>2025-01-08</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="V87" t="n">
-        <v>1</v>
-      </c>
-      <c r="W87" t="n">
-        <v>0</v>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="W87" t="inlineStr"/>
+      <c r="X87" t="inlineStr"/>
+      <c r="Y87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10112,12 +10108,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
+          <t>2fe3bd2a-973e-48db-a599-6d44ca1ef0ad</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ca-cioos_5c13b300-e172-4010-a6d8-7586b68a3a96</t>
+          <t>ca-cioos_27ba6c11-2421-4e85-bc11-1c1083514ed9</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10127,7 +10123,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kelp extent for the McNaughton Group Islands (2017), Manley Island (2017), and Serpent Group Islands (2016), British Columbia, Canada</t>
+          <t>Owikeno Lake Bathymetric Survey</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -10145,7 +10141,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10165,15 +10161,15 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Hakai Geospatial</t>
         </is>
       </c>
       <c r="N88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.30122253, 51.7689035], [-128.05512885, 51.7689035], [-128.05512885, 51.98187882], [-128.30122253, 51.98187882], [-128.30122253, 51.7689035]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.22312137, 51.63113942], [-126.67792484, 51.63113942], [-126.67792484, 51.7324654], [-127.22312137, 51.7324654], [-127.22312137, 51.63113942]]]}</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -10183,17 +10179,17 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>other, macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>10.21966/82bd-ks94</t>
+          <t>10.21966/31db-5090</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFIWmZWeEE0RkZrZVc</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFqOFB5dmFHWXM5am0</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
@@ -10203,11 +10199,11 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="V88" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W88" t="n">
         <v>0</v>
@@ -10229,12 +10225,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1ad9809b-16a0-44f4-abc8-a1474b728c15</t>
+          <t>c8f6fd7c-7c63-440b-b69a-bd0df3abfd26</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ca-cioos_5e4f925a-9cf2-4e33-ae22-75c5b326ce6c</t>
+          <t>ca-cioos_5c13b300-e172-4010-a6d8-7586b68a3a96</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10244,7 +10240,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Eelgrass (Z. marina) extent at sites along the Central Coast, British Columbia</t>
+          <t>Kelp extent for the McNaughton Group Islands (2017), Manley Island (2017), and Serpent Group Islands (2016), British Columbia, Canada</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -10262,7 +10258,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Nearshore, Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10286,11 +10282,11 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.65354407, 51.37817421], [-127.69773286, 51.37817421], [-127.69773286, 52.1127963], [-128.65354407, 52.1127963], [-128.65354407, 51.37817421]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.30122253, 51.7689035], [-128.05512885, 51.7689035], [-128.05512885, 51.98187882], [-128.30122253, 51.98187882], [-128.30122253, 51.7689035]]]}</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10300,17 +10296,17 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>10.21966/03pw-2190</t>
+          <t>10.21966/82bd-ks94</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTA3NnQ0NnRiemVLSFU</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFIWmZWeEE0RkZrZVc</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
@@ -11916,7 +11912,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>underDevelopment</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -11965,11 +11961,11 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="V104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W104" t="inlineStr"/>
       <c r="X104" t="inlineStr"/>
@@ -14970,12 +14966,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>ca-cioos_6844547c-708e-437b-aef7-157b4d9d9bcb</t>
+          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -14985,7 +14981,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Nutrient and dissolved organic carbon in fresh and marine waters of Kwakshua Channel, British Columbia, Canada. Version 1.0.</t>
+          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada. Version 1.0.</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -15021,17 +15017,13 @@
           <t>dataset</t>
         </is>
       </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>Hakai Institute</t>
-        </is>
-      </c>
+      <c r="M132" t="inlineStr"/>
       <c r="N132" t="n">
         <v>1</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.15445681, 51.61731613], [-127.95404703, 51.61731613], [-127.95404703, 51.71899959], [-128.15445681, 51.71899959], [-128.15445681, 51.61731613]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -15041,17 +15033,17 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>nutrients, dissolvedOrganicCarbon, other</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>10.21966/n0h9-cq15</t>
+          <t>10.21966/66x5-a210</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW9FaWlnNDM5TVFnV0I</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
         </is>
       </c>
       <c r="T132" t="inlineStr">
@@ -15065,19 +15057,19 @@
         </is>
       </c>
       <c r="V132" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="W132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.5194/bg-18-3029-2021', 'type': 'dois', 'status_code': 200, 'url': 'https://bg.copernicus.org/articles/18/3029/2021/'}, {'relationship': 'parts', 'id': '10.5194/bg-2020-350', 'type': 'dois', 'status_code': 200, 'url': 'https://bg.copernicus.org/articles/18/3029/2021/bg-18-3029-2021-discussion.html'}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -15204,12 +15196,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
+          <t>ca-cioos_6844547c-708e-437b-aef7-157b4d9d9bcb</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -15219,7 +15211,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada. Version 1.0.</t>
+          <t>Nutrient and dissolved organic carbon in fresh and marine waters of Kwakshua Channel, British Columbia, Canada. Version 1.0.</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -15255,13 +15247,17 @@
           <t>dataset</t>
         </is>
       </c>
-      <c r="M134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
       <c r="N134" t="n">
         <v>1</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.15445681, 51.61731613], [-127.95404703, 51.61731613], [-127.95404703, 51.71899959], [-128.15445681, 51.71899959], [-128.15445681, 51.61731613]]]}</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -15271,17 +15267,17 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>nutrients, dissolvedOrganicCarbon, other</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>10.21966/66x5-a210</t>
+          <t>10.21966/n0h9-cq15</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW9FaWlnNDM5TVFnV0I</t>
         </is>
       </c>
       <c r="T134" t="inlineStr">
@@ -15295,19 +15291,19 @@
         </is>
       </c>
       <c r="V134" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="W134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'citations', 'id': '10.5194/bg-18-3029-2021', 'type': 'dois', 'status_code': 200, 'url': 'https://bg.copernicus.org/articles/18/3029/2021/'}, {'relationship': 'parts', 'id': '10.5194/bg-2020-350', 'type': 'dois', 'status_code': 200, 'url': 'https://bg.copernicus.org/articles/18/3029/2021/bg-18-3029-2021-discussion.html'}]</t>
         </is>
       </c>
     </row>
@@ -21552,7 +21548,9 @@
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="V188" t="inlineStr"/>
+      <c r="V188" t="n">
+        <v>1</v>
+      </c>
       <c r="W188" t="n">
         <v>0</v>
       </c>

--- a/main/catalog_summary.xlsx
+++ b/main/catalog_summary.xlsx
@@ -1850,12 +1850,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ca-cioos_ab901b46-43f6-4044-b0c3-b5fd825622f4</t>
+          <t>ca-cioos_af65bf72-27af-4747-8911-ab05591762ac</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>World View 2 Imagery - Coverage of three regions of the BC Central Coast - Summer 2014, 2015, &amp; 2016</t>
+          <t>Kelp forest communities along an otter gradient</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>underDevelopment</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Simon Fraser University</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1911,12 +1911,12 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.61145019531247, 51.61801654877371], [-127.91931152343746, 51.61801654877371], [-127.91931152343746, 52.11325243469631], [-128.61145019531247, 52.11325243469631], [-128.61145019531247, 51.61801654877371]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.770751953125, 51.33404377878941], [-127.74902343749999, 51.33404377878941], [-127.74902343749999, 52.19077237113535], [-128.770751953125, 52.19077237113535], [-128.770751953125, 51.33404377878941]]]}</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '50.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1924,14 +1924,10 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>10.21966/nmds-rx42</t>
-        </is>
-      </c>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXp1R01BNWFYV0RkUEY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXlMbjJYUlpvZFpITks</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -1941,25 +1937,15 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>3</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1967,12 +1953,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ca-cioos_af65bf72-27af-4747-8911-ab05591762ac</t>
+          <t>ca-cioos_ab901b46-43f6-4044-b0c3-b5fd825622f4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1982,7 +1968,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kelp forest communities along an otter gradient</t>
+          <t>World View 2 Imagery - Coverage of three regions of the BC Central Coast - Summer 2014, 2015, &amp; 2016</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2000,12 +1986,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>underDevelopment</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2020,7 +2006,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Simon Fraser University</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -2028,12 +2014,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.770751953125, 51.33404377878941], [-127.74902343749999, 51.33404377878941], [-127.74902343749999, 52.19077237113535], [-128.770751953125, 52.19077237113535], [-128.770751953125, 51.33404377878941]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.61145019531247, 51.61801654877371], [-127.91931152343746, 51.61801654877371], [-127.91931152343746, 52.11325243469631], [-128.61145019531247, 52.11325243469631], [-128.61145019531247, 51.61801654877371]]]}</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>[{'max': '50.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2041,10 +2027,14 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>10.21966/nmds-rx42</t>
+        </is>
+      </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXlMbjJYUlpvZFpITks</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXp1R01BNWFYV0RkUEY</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -2054,15 +2044,25 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>5</v>
-      </c>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -10005,12 +10005,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>2fe3bd2a-973e-48db-a599-6d44ca1ef0ad</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ca-cioos_2a92ca16-f5c6-4362-acea-6bb5117b8d65</t>
+          <t>ca-cioos_27ba6c11-2421-4e85-bc11-1c1083514ed9</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10020,7 +10020,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Google Earth Engine Kelp Tool - Central Coast Output - Version 1.0.0</t>
+          <t>Owikeno Lake Bathymetric Survey</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Hakai Geospatial</t>
         </is>
       </c>
       <c r="N87" t="n">
@@ -10066,7 +10066,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-130.35642493, 50.22213452], [-126.18162025, 50.22213452], [-126.18162025, 52.9911972], [-130.35642493, 52.9911972], [-130.35642493, 50.22213452]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.22312137, 51.63113942], [-126.67792484, 51.63113942], [-126.67792484, 51.7324654], [-127.22312137, 51.7324654], [-127.22312137, 51.63113942]]]}</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -10079,10 +10079,14 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr"/>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>10.21966/31db-5090</t>
+        </is>
+      </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFUcWNIVGxwZEVLNTE</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFqOFB5dmFHWXM5am0</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
@@ -10092,15 +10096,25 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="V87" t="n">
-        <v>4</v>
-      </c>
-      <c r="W87" t="inlineStr"/>
-      <c r="X87" t="inlineStr"/>
-      <c r="Y87" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W87" t="n">
+        <v>0</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10108,12 +10122,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2fe3bd2a-973e-48db-a599-6d44ca1ef0ad</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ca-cioos_27ba6c11-2421-4e85-bc11-1c1083514ed9</t>
+          <t>ca-cioos_2a92ca16-f5c6-4362-acea-6bb5117b8d65</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10123,7 +10137,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Owikeno Lake Bathymetric Survey</t>
+          <t>Google Earth Engine Kelp Tool - Central Coast Output - Version 1.0.0</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -10161,7 +10175,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Hakai Geospatial</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N88" t="n">
@@ -10169,7 +10183,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.22312137, 51.63113942], [-126.67792484, 51.63113942], [-126.67792484, 51.7324654], [-127.22312137, 51.7324654], [-127.22312137, 51.63113942]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-130.35642493, 50.22213452], [-126.18162025, 50.22213452], [-126.18162025, 52.9911972], [-130.35642493, 52.9911972], [-130.35642493, 50.22213452]]]}</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -10182,14 +10196,10 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr">
-        <is>
-          <t>10.21966/31db-5090</t>
-        </is>
-      </c>
+      <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFqOFB5dmFHWXM5am0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFUcWNIVGxwZEVLNTE</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
@@ -10199,25 +10209,15 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>2025-01-08</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="V88" t="n">
-        <v>1</v>
-      </c>
-      <c r="W88" t="n">
-        <v>0</v>
-      </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="W88" t="inlineStr"/>
+      <c r="X88" t="inlineStr"/>
+      <c r="Y88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -14966,12 +14966,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
+          <t>ca-cioos_6844547c-708e-437b-aef7-157b4d9d9bcb</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -14981,7 +14981,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada. Version 1.0.</t>
+          <t>Nutrient and dissolved organic carbon in fresh and marine waters of Kwakshua Channel, British Columbia, Canada. Version 1.0.</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -15017,13 +15017,17 @@
           <t>dataset</t>
         </is>
       </c>
-      <c r="M132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
       <c r="N132" t="n">
         <v>1</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.15445681, 51.61731613], [-127.95404703, 51.61731613], [-127.95404703, 51.71899959], [-128.15445681, 51.71899959], [-128.15445681, 51.61731613]]]}</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -15033,17 +15037,17 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>nutrients, dissolvedOrganicCarbon, other</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>10.21966/66x5-a210</t>
+          <t>10.21966/n0h9-cq15</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW9FaWlnNDM5TVFnV0I</t>
         </is>
       </c>
       <c r="T132" t="inlineStr">
@@ -15057,19 +15061,19 @@
         </is>
       </c>
       <c r="V132" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="W132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'citations', 'id': '10.5194/bg-18-3029-2021', 'type': 'dois', 'status_code': 200, 'url': 'https://bg.copernicus.org/articles/18/3029/2021/'}, {'relationship': 'parts', 'id': '10.5194/bg-2020-350', 'type': 'dois', 'status_code': 200, 'url': 'https://bg.copernicus.org/articles/18/3029/2021/bg-18-3029-2021-discussion.html'}]</t>
         </is>
       </c>
     </row>
@@ -15079,12 +15083,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ca-cioos_765d00bb-beec-486c-bd00-e27f972b7324</t>
+          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -15094,7 +15098,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Microbial activity and carbon fluxes in rainforest soil – Tsunami Hill, Calvert Island – June 2015 - April 2016</t>
+          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada. Version 1.0.</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -15112,7 +15116,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Genomics, Watersheds</t>
+          <t>Watersheds, Oceanography</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -15130,37 +15134,33 @@
           <t>dataset</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>University of British Columbia</t>
-        </is>
-      </c>
+      <c r="M133" t="inlineStr"/>
       <c r="N133" t="n">
         <v>1</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13650264, 51.64966999], [-128.12495841, 51.64966999], [-128.12495841, 51.65523482], [-128.13650264, 51.65523482], [-128.13650264, 51.64966999]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>10.21966/1.715630</t>
+          <t>10.21966/66x5-a210</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUE0SHdBOUNiWjU5bFY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
         </is>
       </c>
       <c r="T133" t="inlineStr">
@@ -15174,7 +15174,7 @@
         </is>
       </c>
       <c r="V133" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W133" t="n">
         <v>0</v>
@@ -15196,12 +15196,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>3c4cc294-1e9a-410e-81b0-0d9461e4b1c9</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ca-cioos_6844547c-708e-437b-aef7-157b4d9d9bcb</t>
+          <t>ca-cioos_765d00bb-beec-486c-bd00-e27f972b7324</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -15211,7 +15211,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Nutrient and dissolved organic carbon in fresh and marine waters of Kwakshua Channel, British Columbia, Canada. Version 1.0.</t>
+          <t>Microbial activity and carbon fluxes in rainforest soil – Tsunami Hill, Calvert Island – June 2015 - April 2016</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -15229,7 +15229,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Watersheds, Oceanography</t>
+          <t>Genomics, Watersheds</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15249,7 +15249,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="N134" t="n">
@@ -15257,27 +15257,27 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.15445681, 51.61731613], [-127.95404703, 51.61731613], [-127.95404703, 51.71899959], [-128.15445681, 51.71899959], [-128.15445681, 51.61731613]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13650264, 51.64966999], [-128.12495841, 51.64966999], [-128.12495841, 51.65523482], [-128.13650264, 51.65523482], [-128.13650264, 51.64966999]]]}</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>nutrients, dissolvedOrganicCarbon, other</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>10.21966/n0h9-cq15</t>
+          <t>10.21966/1.715630</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW9FaWlnNDM5TVFnV0I</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUE0SHdBOUNiWjU5bFY</t>
         </is>
       </c>
       <c r="T134" t="inlineStr">
@@ -15291,19 +15291,19 @@
         </is>
       </c>
       <c r="V134" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="W134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.5194/bg-18-3029-2021', 'type': 'dois', 'status_code': 200, 'url': 'https://bg.copernicus.org/articles/18/3029/2021/'}, {'relationship': 'parts', 'id': '10.5194/bg-2020-350', 'type': 'dois', 'status_code': 200, 'url': 'https://bg.copernicus.org/articles/18/3029/2021/bg-18-3029-2021-discussion.html'}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>

--- a/main/catalog_summary.xlsx
+++ b/main/catalog_summary.xlsx
@@ -1527,12 +1527,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
+          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ca-cioos_55daf524-146e-4b06-8c6c-3255c7e3c77a</t>
+          <t>ca-cioos_4bf1e341-637c-4884-b373-033e033b3cba</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vegetated Islands Polygons - 100 Islands Research</t>
+          <t>Northwest Calvert Substrate Mapping</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>100 Islands</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1584,16 +1584,16 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6993408203125, 51.368351060511344], [-127.4908447265625, 51.368351060511344], [-127.4908447265625, 52.197506856993925], [-128.6993408203125, 52.197506856993925], [-128.6993408203125, 51.368351060511344]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.18309295, 51.63973703], [-128.06292998, 51.63973703], [-128.06292998, 51.71531293], [-128.18309295, 51.71531293], [-128.18309295, 51.63973703]]]}</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>[{'max': '500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '600.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1601,10 +1601,14 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>10.21966/35tn-w772</t>
+        </is>
+      </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW90czhQM1A2WXJWTVg</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWJlU2MzU0psd2EzM0w</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1614,15 +1618,25 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V11" t="n">
         <v>2</v>
       </c>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1630,12 +1644,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
+          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ca-cioos_4bf1e341-637c-4884-b373-033e033b3cba</t>
+          <t>ca-cioos_55daf524-146e-4b06-8c6c-3255c7e3c77a</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1645,7 +1659,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Northwest Calvert Substrate Mapping</t>
+          <t>Vegetated Islands Polygons - 100 Islands Research</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1663,7 +1677,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>100 Islands</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1687,16 +1701,16 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.18309295, 51.63973703], [-128.06292998, 51.63973703], [-128.06292998, 51.71531293], [-128.18309295, 51.71531293], [-128.18309295, 51.63973703]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6993408203125, 51.368351060511344], [-127.4908447265625, 51.368351060511344], [-127.4908447265625, 52.197506856993925], [-128.6993408203125, 52.197506856993925], [-128.6993408203125, 51.368351060511344]]]}</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>[{'max': '600.0', 'min': '0.0'}]</t>
+          <t>[{'max': '500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1704,14 +1718,10 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>10.21966/35tn-w772</t>
-        </is>
-      </c>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWJlU2MzU0psd2EzM0w</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW90czhQM1A2WXJWTVg</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -1721,25 +1731,15 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>3</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
@@ -8971,12 +8971,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
+          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
+          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -9002,11 +9002,7 @@
       <c r="H77" t="b">
         <v>0</v>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Airborne Coastal Observatory</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>completed</t>
@@ -9032,12 +9028,12 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -9048,7 +9044,7 @@
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -9062,7 +9058,7 @@
         </is>
       </c>
       <c r="V77" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
@@ -9074,12 +9070,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
+          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9089,7 +9085,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
+          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -9105,7 +9101,11 @@
       <c r="H78" t="b">
         <v>0</v>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Airborne Coastal Observatory</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr">
         <is>
           <t>completed</t>
@@ -9131,12 +9131,12 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -9147,7 +9147,7 @@
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="V78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
@@ -10005,12 +10005,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2fe3bd2a-973e-48db-a599-6d44ca1ef0ad</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ca-cioos_27ba6c11-2421-4e85-bc11-1c1083514ed9</t>
+          <t>ca-cioos_2a92ca16-f5c6-4362-acea-6bb5117b8d65</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10020,7 +10020,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Owikeno Lake Bathymetric Survey</t>
+          <t>Google Earth Engine Kelp Tool - Central Coast Output - Version 1.0.0</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Hakai Geospatial</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N87" t="n">
@@ -10066,7 +10066,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.22312137, 51.63113942], [-126.67792484, 51.63113942], [-126.67792484, 51.7324654], [-127.22312137, 51.7324654], [-127.22312137, 51.63113942]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-130.35642493, 50.22213452], [-126.18162025, 50.22213452], [-126.18162025, 52.9911972], [-130.35642493, 52.9911972], [-130.35642493, 50.22213452]]]}</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -10079,14 +10079,10 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr">
-        <is>
-          <t>10.21966/31db-5090</t>
-        </is>
-      </c>
+      <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFqOFB5dmFHWXM5am0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFUcWNIVGxwZEVLNTE</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
@@ -10096,25 +10092,15 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>2025-01-08</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="V87" t="n">
-        <v>1</v>
-      </c>
-      <c r="W87" t="n">
-        <v>0</v>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="W87" t="inlineStr"/>
+      <c r="X87" t="inlineStr"/>
+      <c r="Y87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10122,12 +10108,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>2fe3bd2a-973e-48db-a599-6d44ca1ef0ad</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ca-cioos_2a92ca16-f5c6-4362-acea-6bb5117b8d65</t>
+          <t>ca-cioos_27ba6c11-2421-4e85-bc11-1c1083514ed9</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10137,7 +10123,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Google Earth Engine Kelp Tool - Central Coast Output - Version 1.0.0</t>
+          <t>Owikeno Lake Bathymetric Survey</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -10175,7 +10161,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Hakai Geospatial</t>
         </is>
       </c>
       <c r="N88" t="n">
@@ -10183,7 +10169,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-130.35642493, 50.22213452], [-126.18162025, 50.22213452], [-126.18162025, 52.9911972], [-130.35642493, 52.9911972], [-130.35642493, 50.22213452]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.22312137, 51.63113942], [-126.67792484, 51.63113942], [-126.67792484, 51.7324654], [-127.22312137, 51.7324654], [-127.22312137, 51.63113942]]]}</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -10196,10 +10182,14 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr"/>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>10.21966/31db-5090</t>
+        </is>
+      </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFUcWNIVGxwZEVLNTE</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFqOFB5dmFHWXM5am0</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
@@ -10209,15 +10199,25 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="V88" t="n">
-        <v>4</v>
-      </c>
-      <c r="W88" t="inlineStr"/>
-      <c r="X88" t="inlineStr"/>
-      <c r="Y88" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W88" t="n">
+        <v>0</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10437,7 +10437,7 @@
         </is>
       </c>
       <c r="V90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W90" t="n">
         <v>0</v>
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="V91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W91" t="n">
         <v>0</v>
@@ -10671,7 +10671,7 @@
         </is>
       </c>
       <c r="V92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W92" t="n">
         <v>0</v>
@@ -11299,7 +11299,7 @@
         </is>
       </c>
       <c r="V98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W98" t="n">
         <v>0</v>
@@ -11874,12 +11874,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ca-cioos_4fac74c8-f58c-46b0-87dc-ab70ce756880</t>
+          <t>ca-cioos_51171738-7556-48f1-8757-658d99fa25dd</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -11889,7 +11889,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Discovery Islands LiDAR Dataset  - 2014 - British Columbia - Canada</t>
+          <t>Eelgrass Extent 2014 - Central Coast</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -11905,11 +11905,7 @@
       <c r="H104" t="b">
         <v>0</v>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>Geospatial</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>completed</t>
@@ -11931,16 +11927,16 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.3704833984375, 49.9229354544957], [-124.75524902343749, 49.9229354544957], [-124.75524902343749, 50.291094042311386], [-125.3704833984375, 50.291094042311386], [-125.3704833984375, 49.9229354544957]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4878540039062, 51.653814904471545], [-128.0978393554687, 51.653814904471545], [-128.0978393554687, 52.07950600379698], [-128.4878540039062, 52.07950600379698], [-128.4878540039062, 51.653814904471545]]]}</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>[{'max': '500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '50.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -11951,7 +11947,7 @@
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXR6SWM4aTRoYk9MeU0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUZuOThkU2QzakpPNEQ</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
@@ -11961,11 +11957,11 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V104" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W104" t="inlineStr"/>
       <c r="X104" t="inlineStr"/>
@@ -11977,12 +11973,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ca-cioos_51171738-7556-48f1-8757-658d99fa25dd</t>
+          <t>ca-cioos_4fac74c8-f58c-46b0-87dc-ab70ce756880</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -11992,7 +11988,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Eelgrass Extent 2014 - Central Coast</t>
+          <t>Discovery Islands LiDAR Dataset  - 2014 - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -12008,7 +12004,11 @@
       <c r="H105" t="b">
         <v>0</v>
       </c>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Geospatial</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr">
         <is>
           <t>completed</t>
@@ -12030,16 +12030,16 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4878540039062, 51.653814904471545], [-128.0978393554687, 51.653814904471545], [-128.0978393554687, 52.07950600379698], [-128.4878540039062, 52.07950600379698], [-128.4878540039062, 51.653814904471545]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.3704833984375, 49.9229354544957], [-124.75524902343749, 49.9229354544957], [-124.75524902343749, 50.291094042311386], [-125.3704833984375, 50.291094042311386], [-125.3704833984375, 49.9229354544957]]]}</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>[{'max': '50.0', 'min': '0.0'}]</t>
+          <t>[{'max': '500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -12050,7 +12050,7 @@
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUZuOThkU2QzakpPNEQ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXR6SWM4aTRoYk9MeU0</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
@@ -12060,11 +12060,11 @@
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="V105" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W105" t="inlineStr"/>
       <c r="X105" t="inlineStr"/>
@@ -14163,12 +14163,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ca-cioos_184b2f81-d87f-4615-a026-15b87930d15c</t>
+          <t>ca-cioos_23bc8c35-2e4e-4382-9296-a52d5ea49889</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Aquatic carbon flux data package for Oliver et al. 2017</t>
+          <t>Discharge Time Series (2013-2017) – Calvert Island - Archived Version 3.0</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -14220,11 +14220,11 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.15002441406247, 51.614605707797466], [-127.96600341796874, 51.614605707797466], [-127.96600341796874, 51.70405535332591], [-128.15002441406247, 51.70405535332591], [-128.15002441406247, 51.614605707797466]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -14234,17 +14234,17 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>dissolvedOrganicCarbon, other</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>10.21966/1.321324</t>
+          <t>10.21966/sbyc-d030</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW9aOE1zWERKZnFEWm4</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUdGRGRjUW9LRnBVNVI</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
@@ -14254,23 +14254,23 @@
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="V125" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="W125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}, {'relationship': 'parts', 'id': '10.5194/bg-2017-5', 'type': 'dois', 'status_code': 200, 'url': 'https://bg.copernicus.org/articles/14/3743/2017/bg-14-3743-2017-discussion.html'}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -14280,12 +14280,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>1be9154a-1497-42eb-8821-b0d63000814c</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ca-cioos_23bc8c35-2e4e-4382-9296-a52d5ea49889</t>
+          <t>ca-cioos_184b2f81-d87f-4615-a026-15b87930d15c</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Discharge Time Series (2013-2017) – Calvert Island - Archived Version 3.0</t>
+          <t>Aquatic carbon flux data package for Oliver et al. 2017</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -14337,57 +14337,57 @@
         </is>
       </c>
       <c r="N126" t="n">
+        <v>3</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.15002441406247, 51.614605707797466], [-127.96600341796874, 51.614605707797466], [-127.96600341796874, 51.70405535332591], [-128.15002441406247, 51.70405535332591], [-128.15002441406247, 51.614605707797466]]]}</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>dissolvedOrganicCarbon, other</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>10.21966/1.321324</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW9aOE1zWERKZnFEWm4</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>2022-03-29</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="V126" t="n">
         <v>1</v>
       </c>
-      <c r="O126" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
-        </is>
-      </c>
-      <c r="P126" t="inlineStr">
-        <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q126" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R126" t="inlineStr">
-        <is>
-          <t>10.21966/sbyc-d030</t>
-        </is>
-      </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUdGRGRjUW9LRnBVNVI</t>
-        </is>
-      </c>
-      <c r="T126" t="inlineStr">
-        <is>
-          <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="V126" t="n">
-        <v>10</v>
-      </c>
       <c r="W126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}, {'relationship': 'parts', 'id': '10.5194/bg-2017-5', 'type': 'dois', 'status_code': 200, 'url': 'https://bg.copernicus.org/articles/14/3743/2017/bg-14-3743-2017-discussion.html'}]</t>
         </is>
       </c>
     </row>
@@ -15083,12 +15083,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
+          <t>ca-cioos_765d00bb-beec-486c-bd00-e27f972b7324</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -15098,7 +15098,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada. Version 1.0.</t>
+          <t>Microbial activity and carbon fluxes in rainforest soil – Tsunami Hill, Calvert Island – June 2015 - April 2016</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Watersheds, Oceanography</t>
+          <t>Genomics, Watersheds</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -15134,33 +15134,37 @@
           <t>dataset</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>University of British Columbia</t>
+        </is>
+      </c>
       <c r="N133" t="n">
         <v>1</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13650264, 51.64966999], [-128.12495841, 51.64966999], [-128.12495841, 51.65523482], [-128.13650264, 51.65523482], [-128.13650264, 51.64966999]]]}</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>10.21966/66x5-a210</t>
+          <t>10.21966/1.715630</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUE0SHdBOUNiWjU5bFY</t>
         </is>
       </c>
       <c r="T133" t="inlineStr">
@@ -15174,7 +15178,7 @@
         </is>
       </c>
       <c r="V133" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="W133" t="n">
         <v>0</v>
@@ -15196,12 +15200,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ca-cioos_765d00bb-beec-486c-bd00-e27f972b7324</t>
+          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -15211,7 +15215,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Microbial activity and carbon fluxes in rainforest soil – Tsunami Hill, Calvert Island – June 2015 - April 2016</t>
+          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada. Version 1.0.</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -15229,7 +15233,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Genomics, Watersheds</t>
+          <t>Watersheds, Oceanography</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15247,37 +15251,33 @@
           <t>dataset</t>
         </is>
       </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>University of British Columbia</t>
-        </is>
-      </c>
+      <c r="M134" t="inlineStr"/>
       <c r="N134" t="n">
         <v>1</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13650264, 51.64966999], [-128.12495841, 51.64966999], [-128.12495841, 51.65523482], [-128.13650264, 51.65523482], [-128.13650264, 51.64966999]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>10.21966/1.715630</t>
+          <t>10.21966/66x5-a210</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUE0SHdBOUNiWjU5bFY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
         </is>
       </c>
       <c r="T134" t="inlineStr">
@@ -15291,7 +15291,7 @@
         </is>
       </c>
       <c r="V134" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W134" t="n">
         <v>0</v>
@@ -15880,12 +15880,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ca-cioos_b694a5c5-6a7e-4206-96aa-5b7754323345</t>
+          <t>ca-cioos_b52d5602-f81d-4565-9574-e448e99bc997</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -15895,7 +15895,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Air temperature and relative humidity time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
+          <t>Bathymetry for Six Lakes on Calvert and Hecate Islands - 2016 - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -15913,12 +15913,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Watersheds, Geospatial</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -15941,12 +15941,12 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.30095161, 50.04299371], [-125.08745063, 50.04299371], [-125.08745063, 51.791595], [-128.30095161, 51.791595], [-128.30095161, 50.04299371]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.09646606445312, 51.5996802644666], [-127.9508972167969, 51.5996802644666], [-127.9508972167969, 51.69171329024539], [-128.09646606445312, 51.69171329024539], [-128.09646606445312, 51.5996802644666]]]}</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>[{'max': '741.0', 'min': '3.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
@@ -15954,10 +15954,14 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R140" t="inlineStr"/>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>10.21966/fcwf-p919</t>
+        </is>
+      </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWRmQkdrNXg2bFpvUTE</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWxuNHhkYXVuNlFDSVY</t>
         </is>
       </c>
       <c r="T140" t="inlineStr">
@@ -15967,15 +15971,25 @@
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V140" t="n">
-        <v>8</v>
-      </c>
-      <c r="W140" t="inlineStr"/>
-      <c r="X140" t="inlineStr"/>
-      <c r="Y140" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W140" t="n">
+        <v>1</v>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>[{'year': '2022', 'total': 1}]</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}]</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15983,12 +15997,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>ca-cioos_b52d5602-f81d-4565-9574-e448e99bc997</t>
+          <t>ca-cioos_b694a5c5-6a7e-4206-96aa-5b7754323345</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -15998,7 +16012,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Bathymetry for Six Lakes on Calvert and Hecate Islands - 2016 - British Columbia - Canada</t>
+          <t>Air temperature and relative humidity time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -16016,12 +16030,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Watersheds, Geospatial</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -16044,12 +16058,12 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.09646606445312, 51.5996802644666], [-127.9508972167969, 51.5996802644666], [-127.9508972167969, 51.69171329024539], [-128.09646606445312, 51.69171329024539], [-128.09646606445312, 51.5996802644666]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.30095161, 50.04299371], [-125.08745063, 50.04299371], [-125.08745063, 51.791595], [-128.30095161, 51.791595], [-128.30095161, 50.04299371]]]}</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '741.0', 'min': '3.0'}]</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
@@ -16057,14 +16071,10 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R141" t="inlineStr">
-        <is>
-          <t>10.21966/fcwf-p919</t>
-        </is>
-      </c>
+      <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWxuNHhkYXVuNlFDSVY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWRmQkdrNXg2bFpvUTE</t>
         </is>
       </c>
       <c r="T141" t="inlineStr">
@@ -16074,25 +16084,15 @@
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="V141" t="n">
-        <v>1</v>
-      </c>
-      <c r="W141" t="n">
-        <v>1</v>
-      </c>
-      <c r="X141" t="inlineStr">
-        <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
-        </is>
-      </c>
-      <c r="Y141" t="inlineStr">
-        <is>
-          <t>[{'relationship': 'citations', 'id': '10.1002/hyp.14198', 'type': 'dois', 'status_code': 403, 'url': 'https://onlinelibrary.wiley.com/doi/10.1002/hyp.14198'}]</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="W141" t="inlineStr"/>
+      <c r="X141" t="inlineStr"/>
+      <c r="Y141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -21548,9 +21548,7 @@
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="V188" t="n">
-        <v>1</v>
-      </c>
+      <c r="V188" t="inlineStr"/>
       <c r="W188" t="n">
         <v>0</v>
       </c>
@@ -22716,16 +22714,16 @@
         <v>3</v>
       </c>
       <c r="W198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X198" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'relationship': 'citations', 'id': '10.21966/8yp1-7m94', 'type': 'dois', 'status_code': 200, 'url': 'https://catalogue.hakai.org/dataset/ca-cioos_52d4f546-dfdf-4bf1-b1ad-f6ec6f2663c0'}]</t>
         </is>
       </c>
     </row>
@@ -24208,7 +24206,7 @@
         </is>
       </c>
       <c r="V211" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W211" t="n">
         <v>0</v>

--- a/main/catalog_summary.xlsx
+++ b/main/catalog_summary.xlsx
@@ -6263,12 +6263,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
+          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
+          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6334,17 +6334,17 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>10.21966/zxzr-e472</t>
+          <t>10.21966/1.715793</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="V55" t="inlineStr"/>
@@ -6475,12 +6475,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
+          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -6490,7 +6490,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
+          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6546,17 +6546,17 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>10.21966/1.715793</t>
+          <t>10.21966/zxzr-e472</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="V57" t="inlineStr"/>
@@ -8679,12 +8679,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
+          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
+          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -8710,11 +8710,7 @@
       <c r="H77" t="b">
         <v>0</v>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Airborne Coastal Observatory</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>completed</t>
@@ -8740,12 +8736,12 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -8756,7 +8752,7 @@
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -8770,7 +8766,7 @@
         </is>
       </c>
       <c r="V77" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
@@ -8781,12 +8777,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
+          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -8796,7 +8792,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
+          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8812,7 +8808,11 @@
       <c r="H78" t="b">
         <v>0</v>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Airborne Coastal Observatory</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr">
         <is>
           <t>completed</t>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -8854,7 +8854,7 @@
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -8868,7 +8868,7 @@
         </is>
       </c>
       <c r="V78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
@@ -14623,12 +14623,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
+          <t>ca-cioos_765d00bb-beec-486c-bd00-e27f972b7324</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -14638,7 +14638,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada. Version 1.0.</t>
+          <t>Microbial activity and carbon fluxes in rainforest soil – Tsunami Hill, Calvert Island – June 2015 - April 2016</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -14656,7 +14656,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Watersheds, Oceanography</t>
+          <t>Genomics, Watersheds</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -14674,33 +14674,37 @@
           <t>dataset</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>University of British Columbia</t>
+        </is>
+      </c>
       <c r="N133" t="n">
         <v>1</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13650264, 51.64966999], [-128.12495841, 51.64966999], [-128.12495841, 51.65523482], [-128.13650264, 51.65523482], [-128.13650264, 51.64966999]]]}</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>10.21966/66x5-a210</t>
+          <t>10.21966/1.715630</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUE0SHdBOUNiWjU5bFY</t>
         </is>
       </c>
       <c r="T133" t="inlineStr">
@@ -14714,7 +14718,7 @@
         </is>
       </c>
       <c r="V133" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="W133" t="n">
         <v>0</v>
@@ -14731,12 +14735,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ca-cioos_765d00bb-beec-486c-bd00-e27f972b7324</t>
+          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -14746,7 +14750,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Microbial activity and carbon fluxes in rainforest soil – Tsunami Hill, Calvert Island – June 2015 - April 2016</t>
+          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada. Version 1.0.</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -14764,7 +14768,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Genomics, Watersheds</t>
+          <t>Watersheds, Oceanography</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -14782,37 +14786,33 @@
           <t>dataset</t>
         </is>
       </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>University of British Columbia</t>
-        </is>
-      </c>
+      <c r="M134" t="inlineStr"/>
       <c r="N134" t="n">
         <v>1</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13650264, 51.64966999], [-128.12495841, 51.64966999], [-128.12495841, 51.65523482], [-128.13650264, 51.65523482], [-128.13650264, 51.64966999]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>10.21966/1.715630</t>
+          <t>10.21966/66x5-a210</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUE0SHdBOUNiWjU5bFY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
         </is>
       </c>
       <c r="T134" t="inlineStr">
@@ -14826,7 +14826,7 @@
         </is>
       </c>
       <c r="V134" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W134" t="n">
         <v>0</v>

--- a/main/catalog_summary.xlsx
+++ b/main/catalog_summary.xlsx
@@ -1331,7 +1331,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1367,7 +1367,11 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>10.21966/4wyf-1p04</t>
+        </is>
+      </c>
       <c r="S9" t="inlineStr">
         <is>
           <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXpLZ1BkS1R3cXBNenY</t>
@@ -1380,14 +1384,18 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="V9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1690,12 +1698,10 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="V12" t="n">
-        <v>2</v>
-      </c>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="n">
         <v>0</v>
       </c>
@@ -2006,12 +2012,10 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="V15" t="n">
-        <v>3</v>
-      </c>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="n">
         <v>0</v>
       </c>
@@ -2118,7 +2122,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="V16" t="n">
@@ -3874,7 +3878,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="V32" t="n">
@@ -4825,7 +4829,11 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>10.21966/ebd6-yd93</t>
+        </is>
+      </c>
       <c r="S41" t="inlineStr">
         <is>
           <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXN1MUhmRE9GRndsSko</t>
@@ -4838,14 +4846,18 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="V41" t="n">
-        <v>5</v>
-      </c>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6263,12 +6275,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
+          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
+          <t>ca-cioos_6ebe47c3-6d59-4cb2-a7ba-111698445d8d</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6278,7 +6290,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
+          <t>Bald eagles as vectors of marine nutrients – Central Coast Islands (100 Islands study area) – May – July 2017</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6296,7 +6308,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>100 Islands</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6316,56 +6328,48 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N55" t="n">
+        <v>2</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.58323147, 51.38160352], [-127.80979387, 51.38160352], [-127.80979387, 52.09997599], [-128.58323147, 52.09997599], [-128.58323147, 51.38160352]]]}</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>other, nutrients</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUxkcndoNFQ4T2xyZWI</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>2022-01-24</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="V55" t="n">
         <v>1</v>
       </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>other, dissolvedOrganicCarbon</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>10.21966/1.715793</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>2022-01-24</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6373,12 +6377,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ca-cioos_6ebe47c3-6d59-4cb2-a7ba-111698445d8d</t>
+          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6388,7 +6392,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bald eagles as vectors of marine nutrients – Central Coast Islands (100 Islands study area) – May – July 2017</t>
+          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6406,7 +6410,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>100 Islands</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6426,15 +6430,15 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.58323147, 51.38160352], [-127.80979387, 51.38160352], [-127.80979387, 52.09997599], [-128.58323147, 52.09997599], [-128.58323147, 51.38160352]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6444,13 +6448,17 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>other, nutrients</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr"/>
+          <t>other, dissolvedOrganicCarbon</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>10.21966/1.715793</t>
+        </is>
+      </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUxkcndoNFQ4T2xyZWI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
@@ -6460,14 +6468,18 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="V56" t="n">
-        <v>1</v>
-      </c>
-      <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7916,7 +7928,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Eelgrass (Z. marina) extent at Gulf Islands National Park Reserve eelgrass monitoring sites (2017, 2018) v1.0.0</t>
+          <t>Eelgrass (Z. marina) extent at Gulf Islands National Park Reserve eelgrass monitoring sites (2017, 2018)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7992,7 +8004,7 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="V70" t="inlineStr"/>
@@ -8402,7 +8414,7 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -8436,12 +8448,10 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="V74" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr"/>
       <c r="W74" t="n">
         <v>0</v>
       </c>
@@ -8679,12 +8689,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
+          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -8694,7 +8704,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
+          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -8710,7 +8720,11 @@
       <c r="H77" t="b">
         <v>0</v>
       </c>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Airborne Coastal Observatory</t>
+        </is>
+      </c>
       <c r="J77" t="inlineStr">
         <is>
           <t>completed</t>
@@ -8736,12 +8750,12 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -8752,7 +8766,7 @@
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -8766,7 +8780,7 @@
         </is>
       </c>
       <c r="V77" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
@@ -8777,12 +8791,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
+          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -8792,7 +8806,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
+          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8808,11 +8822,7 @@
       <c r="H78" t="b">
         <v>0</v>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Airborne Coastal Observatory</t>
-        </is>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>completed</t>
@@ -8838,12 +8848,12 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -8854,7 +8864,7 @@
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -8868,7 +8878,7 @@
         </is>
       </c>
       <c r="V78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
@@ -9695,12 +9705,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>2fe3bd2a-973e-48db-a599-6d44ca1ef0ad</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ca-cioos_2a92ca16-f5c6-4362-acea-6bb5117b8d65</t>
+          <t>ca-cioos_27ba6c11-2421-4e85-bc11-1c1083514ed9</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -9710,7 +9720,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Google Earth Engine Kelp Tool - Central Coast Output - Version 1.0.0</t>
+          <t>Owikeno Lake Bathymetric Survey</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -9748,7 +9758,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Hakai Geospatial</t>
         </is>
       </c>
       <c r="N87" t="n">
@@ -9756,7 +9766,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-130.35642493, 50.22213452], [-126.18162025, 50.22213452], [-126.18162025, 52.9911972], [-130.35642493, 52.9911972], [-130.35642493, 50.22213452]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.22312137, 51.63113942], [-126.67792484, 51.63113942], [-126.67792484, 51.7324654], [-127.22312137, 51.7324654], [-127.22312137, 51.63113942]]]}</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -9769,10 +9779,14 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr"/>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>10.21966/31db-5090</t>
+        </is>
+      </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFUcWNIVGxwZEVLNTE</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFqOFB5dmFHWXM5am0</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
@@ -9782,14 +9796,18 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="V87" t="n">
-        <v>4</v>
-      </c>
-      <c r="W87" t="inlineStr"/>
-      <c r="X87" t="inlineStr"/>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="n">
+        <v>0</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9797,12 +9815,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2fe3bd2a-973e-48db-a599-6d44ca1ef0ad</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ca-cioos_27ba6c11-2421-4e85-bc11-1c1083514ed9</t>
+          <t>ca-cioos_2a92ca16-f5c6-4362-acea-6bb5117b8d65</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -9812,12 +9830,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Owikeno Lake Bathymetric Survey</t>
+          <t>Google Earth Engine Kelp Tool - Central Coast Output</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>software</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -9850,7 +9868,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Hakai Geospatial</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N88" t="n">
@@ -9858,7 +9876,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.22312137, 51.63113942], [-126.67792484, 51.63113942], [-126.67792484, 51.7324654], [-127.22312137, 51.7324654], [-127.22312137, 51.63113942]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-130.35642493, 50.22213452], [-126.18162025, 50.22213452], [-126.18162025, 52.9911972], [-130.35642493, 52.9911972], [-130.35642493, 50.22213452]]]}</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -9873,12 +9891,12 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>10.21966/31db-5090</t>
+          <t>10.21966/yff8-2w22</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFqOFB5dmFHWXM5am0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFUcWNIVGxwZEVLNTE</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
@@ -9888,12 +9906,10 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>2025-01-08</t>
-        </is>
-      </c>
-      <c r="V88" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr"/>
       <c r="W88" t="n">
         <v>0</v>
       </c>
@@ -10000,11 +10016,11 @@
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="V89" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W89" t="n">
         <v>0</v>
@@ -10112,12 +10128,10 @@
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="V90" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr"/>
       <c r="W90" t="n">
         <v>0</v>
       </c>
@@ -10224,7 +10238,7 @@
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="V91" t="n">
@@ -10336,7 +10350,7 @@
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="V92" t="n">
@@ -10577,7 +10591,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>service</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -10595,7 +10609,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -10631,7 +10645,11 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr"/>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>10.21966/r0nk-cz60</t>
+        </is>
+      </c>
       <c r="S95" t="inlineStr">
         <is>
           <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTRPT3Q4SUJwZDBDazY</t>
@@ -10644,14 +10662,18 @@
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="V95" t="n">
-        <v>3</v>
-      </c>
-      <c r="W95" t="inlineStr"/>
-      <c r="X95" t="inlineStr"/>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr"/>
+      <c r="W95" t="n">
+        <v>0</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10954,11 +10976,11 @@
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="V98" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W98" t="n">
         <v>0</v>
@@ -11511,12 +11533,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ca-cioos_4fac74c8-f58c-46b0-87dc-ab70ce756880</t>
+          <t>ca-cioos_51171738-7556-48f1-8757-658d99fa25dd</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -11526,7 +11548,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Discovery Islands LiDAR Dataset  - 2014 - British Columbia - Canada</t>
+          <t>Eelgrass Extent 2014 - Central Coast</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -11542,11 +11564,7 @@
       <c r="H104" t="b">
         <v>0</v>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>Geospatial</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>completed</t>
@@ -11568,16 +11586,16 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.3704833984375, 49.9229354544957], [-124.75524902343749, 49.9229354544957], [-124.75524902343749, 50.291094042311386], [-125.3704833984375, 50.291094042311386], [-125.3704833984375, 49.9229354544957]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4878540039062, 51.653814904471545], [-128.0978393554687, 51.653814904471545], [-128.0978393554687, 52.07950600379698], [-128.4878540039062, 52.07950600379698], [-128.4878540039062, 51.653814904471545]]]}</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>[{'max': '500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '50.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -11588,7 +11606,7 @@
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXR6SWM4aTRoYk9MeU0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUZuOThkU2QzakpPNEQ</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
@@ -11598,11 +11616,11 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V104" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W104" t="inlineStr"/>
       <c r="X104" t="inlineStr"/>
@@ -11613,12 +11631,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ca-cioos_51171738-7556-48f1-8757-658d99fa25dd</t>
+          <t>ca-cioos_4fac74c8-f58c-46b0-87dc-ab70ce756880</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -11628,7 +11646,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Eelgrass Extent 2014 - Central Coast</t>
+          <t>Discovery Islands LiDAR Dataset  - 2014 - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -11644,7 +11662,11 @@
       <c r="H105" t="b">
         <v>0</v>
       </c>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Geospatial</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr">
         <is>
           <t>completed</t>
@@ -11666,16 +11688,16 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4878540039062, 51.653814904471545], [-128.0978393554687, 51.653814904471545], [-128.0978393554687, 52.07950600379698], [-128.4878540039062, 52.07950600379698], [-128.4878540039062, 51.653814904471545]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.3704833984375, 49.9229354544957], [-124.75524902343749, 49.9229354544957], [-124.75524902343749, 50.291094042311386], [-125.3704833984375, 50.291094042311386], [-125.3704833984375, 49.9229354544957]]]}</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>[{'max': '50.0', 'min': '0.0'}]</t>
+          <t>[{'max': '500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -11686,7 +11708,7 @@
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUZuOThkU2QzakpPNEQ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXR6SWM4aTRoYk9MeU0</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
@@ -11696,11 +11718,11 @@
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="V105" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W105" t="inlineStr"/>
       <c r="X105" t="inlineStr"/>
@@ -12529,7 +12551,11 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R113" t="inlineStr"/>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>10.21966/hq5n-5g06</t>
+        </is>
+      </c>
       <c r="S113" t="inlineStr">
         <is>
           <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTRhNE0wUGxJZktQTHE</t>
@@ -12542,14 +12568,18 @@
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="V113" t="n">
-        <v>4</v>
-      </c>
-      <c r="W113" t="inlineStr"/>
-      <c r="X113" t="inlineStr"/>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr"/>
+      <c r="W113" t="n">
+        <v>0</v>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12729,7 +12759,11 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R115" t="inlineStr"/>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>10.21966/74y7-v484</t>
+        </is>
+      </c>
       <c r="S115" t="inlineStr">
         <is>
           <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTVjN1laU01nM3dsWnY</t>
@@ -12742,14 +12776,18 @@
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="V115" t="n">
-        <v>2</v>
-      </c>
-      <c r="W115" t="inlineStr"/>
-      <c r="X115" t="inlineStr"/>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr"/>
+      <c r="W115" t="n">
+        <v>0</v>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13191,12 +13229,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
+          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -13206,7 +13244,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
+          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019 Version 4.1</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -13229,7 +13267,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -13248,11 +13286,11 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -13267,12 +13305,12 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>10.21966/XNH1-TP28</t>
+          <t>10.21966/zvwf-qn04</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
@@ -13282,16 +13320,18 @@
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="V120" t="inlineStr"/>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="V120" t="n">
+        <v>5</v>
+      </c>
       <c r="W120" t="n">
         <v>1</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[{'year': '2025', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -13301,12 +13341,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
+          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -13316,7 +13356,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019 Version 4.1</t>
+          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -13339,7 +13379,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -13358,11 +13398,11 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -13377,12 +13417,12 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>10.21966/zvwf-qn04</t>
+          <t>10.21966/XNH1-TP28</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
         </is>
       </c>
       <c r="T121" t="inlineStr">
@@ -13392,18 +13432,16 @@
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="V121" t="n">
-        <v>5</v>
-      </c>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr"/>
       <c r="W121" t="n">
         <v>1</v>
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 1}]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -13504,7 +13542,7 @@
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="V122" t="n">
@@ -14623,12 +14661,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ca-cioos_765d00bb-beec-486c-bd00-e27f972b7324</t>
+          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -14638,7 +14676,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Microbial activity and carbon fluxes in rainforest soil – Tsunami Hill, Calvert Island – June 2015 - April 2016</t>
+          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada. Version 1.0.</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -14656,7 +14694,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Genomics, Watersheds</t>
+          <t>Watersheds, Oceanography</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -14674,37 +14712,33 @@
           <t>dataset</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>University of British Columbia</t>
-        </is>
-      </c>
+      <c r="M133" t="inlineStr"/>
       <c r="N133" t="n">
         <v>1</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13650264, 51.64966999], [-128.12495841, 51.64966999], [-128.12495841, 51.65523482], [-128.13650264, 51.65523482], [-128.13650264, 51.64966999]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>10.21966/1.715630</t>
+          <t>10.21966/66x5-a210</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUE0SHdBOUNiWjU5bFY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
         </is>
       </c>
       <c r="T133" t="inlineStr">
@@ -14718,7 +14752,7 @@
         </is>
       </c>
       <c r="V133" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W133" t="n">
         <v>0</v>
@@ -14735,12 +14769,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
+          <t>ca-cioos_765d00bb-beec-486c-bd00-e27f972b7324</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -14750,7 +14784,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada. Version 1.0.</t>
+          <t>Microbial activity and carbon fluxes in rainforest soil – Tsunami Hill, Calvert Island – June 2015 - April 2016</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -14768,7 +14802,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Watersheds, Oceanography</t>
+          <t>Genomics, Watersheds</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -14786,33 +14820,37 @@
           <t>dataset</t>
         </is>
       </c>
-      <c r="M134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>University of British Columbia</t>
+        </is>
+      </c>
       <c r="N134" t="n">
         <v>1</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13650264, 51.64966999], [-128.12495841, 51.64966999], [-128.12495841, 51.65523482], [-128.13650264, 51.65523482], [-128.13650264, 51.64966999]]]}</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>10.21966/66x5-a210</t>
+          <t>10.21966/1.715630</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUE0SHdBOUNiWjU5bFY</t>
         </is>
       </c>
       <c r="T134" t="inlineStr">
@@ -14826,7 +14864,7 @@
         </is>
       </c>
       <c r="V134" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="W134" t="n">
         <v>0</v>
@@ -14874,7 +14912,11 @@
       <c r="H135" t="b">
         <v>0</v>
       </c>
-      <c r="I135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Watersheds</t>
+        </is>
+      </c>
       <c r="J135" t="inlineStr">
         <is>
           <t>completed</t>
@@ -14930,12 +14972,10 @@
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="V135" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr"/>
       <c r="W135" t="n">
         <v>0</v>
       </c>
@@ -15175,12 +15215,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
+          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -15190,7 +15230,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Stage-Discharge Time Series - Calvert Island - Archived Version 1.0</t>
+          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -15208,7 +15248,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15228,20 +15268,20 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Vancouver Island University</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>[{'max': '250.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
@@ -15249,10 +15289,14 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R138" t="inlineStr"/>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>10.21966/1.135248</t>
+        </is>
+      </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFjSmdJMGxrU1pZbXM</t>
         </is>
       </c>
       <c r="T138" t="inlineStr">
@@ -15262,14 +15306,20 @@
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V138" t="n">
-        <v>5</v>
-      </c>
-      <c r="W138" t="inlineStr"/>
-      <c r="X138" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0</v>
+      </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15277,12 +15327,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
+          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -15292,7 +15342,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
+          <t>Stage-Discharge Time Series - Calvert Island - Archived Version 1.0</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -15310,7 +15360,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -15330,20 +15380,20 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Vancouver Island University</t>
         </is>
       </c>
       <c r="N139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
+          <t>[{'max': '250.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
@@ -15351,14 +15401,10 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R139" t="inlineStr">
-        <is>
-          <t>10.21966/1.135248</t>
-        </is>
-      </c>
+      <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFjSmdJMGxrU1pZbXM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
         </is>
       </c>
       <c r="T139" t="inlineStr">
@@ -15368,20 +15414,14 @@
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="V139" t="n">
-        <v>2</v>
-      </c>
-      <c r="W139" t="n">
-        <v>0</v>
-      </c>
-      <c r="X139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="W139" t="inlineStr"/>
+      <c r="X139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16030,7 +16070,7 @@
       </c>
       <c r="U145" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="V145" t="n">
@@ -21824,7 +21864,7 @@
       </c>
       <c r="U197" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="V197" t="inlineStr"/>
@@ -21934,7 +21974,7 @@
       </c>
       <c r="U198" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="V198" t="n">
@@ -22382,7 +22422,7 @@
       </c>
       <c r="U202" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="V202" t="inlineStr"/>
@@ -22566,7 +22606,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Hakai Geospatial</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N204" t="n">
@@ -22604,7 +22644,7 @@
       </c>
       <c r="U204" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="V204" t="n">
@@ -22938,7 +22978,7 @@
       </c>
       <c r="U207" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="V207" t="inlineStr"/>
@@ -23480,7 +23520,7 @@
       </c>
       <c r="U212" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="V212" t="n">
@@ -23704,7 +23744,7 @@
       </c>
       <c r="U214" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="V214" t="inlineStr"/>
@@ -23924,7 +23964,7 @@
       </c>
       <c r="U216" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="V216" t="n">
@@ -25825,7 +25865,9 @@
           <t>2026-03-19</t>
         </is>
       </c>
-      <c r="V233" t="inlineStr"/>
+      <c r="V233" t="n">
+        <v>1</v>
+      </c>
       <c r="W233" t="n">
         <v>0</v>
       </c>

--- a/main/catalog_summary.xlsx
+++ b/main/catalog_summary.xlsx
@@ -6275,12 +6275,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
+          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ca-cioos_6ebe47c3-6d59-4cb2-a7ba-111698445d8d</t>
+          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bald eagles as vectors of marine nutrients – Central Coast Islands (100 Islands study area) – May – July 2017</t>
+          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>100 Islands</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6328,15 +6328,15 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.58323147, 51.38160352], [-127.80979387, 51.38160352], [-127.80979387, 52.09997599], [-128.58323147, 52.09997599], [-128.58323147, 51.38160352]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6346,13 +6346,17 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>other, nutrients</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr"/>
+          <t>other, dissolvedOrganicCarbon</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>10.21966/1.715793</t>
+        </is>
+      </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUxkcndoNFQ4T2xyZWI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
@@ -6362,14 +6366,18 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="V55" t="n">
-        <v>1</v>
-      </c>
-      <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr"/>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6377,12 +6385,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>6083b388-4d24-4ac3-9464-dfea94468203</t>
+          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ca-cioos_6c0697e9-7776-4d36-8219-b21ce72fbcc9</t>
+          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6392,7 +6400,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Surface water CO2 parameters collected by Alaskan citizens around the northern Gulf of Alaska from April 2015 to August 2017. Version 1.0.</t>
+          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6438,7 +6446,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-153.45020164, 58.42955383], [-145.36907065, 58.42955383], [-145.36907065, 61.89059635], [-153.45020164, 61.89059635], [-153.45020164, 58.42955383]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6448,17 +6456,17 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>10.21966/1.715793</t>
+          <t>10.21966/zxzr-e472</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXhoOWQwcFE2aUY3Q1M</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
@@ -6468,7 +6476,7 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="V56" t="inlineStr"/>
@@ -6487,12 +6495,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2abe9ff4-76de-4221-9ca6-ec3403a56efa</t>
+          <t>9b7adebb-5027-486a-8ed1-f97b5353a480</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ca-cioos_6d779012-e236-4a03-b11a-a5915f0f4342</t>
+          <t>ca-cioos_6ebe47c3-6d59-4cb2-a7ba-111698445d8d</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -6502,7 +6510,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Underway surface seawater and marine boundary layer observations made from the Alaska Marine Highway System M/V Columbia from October 2017 to October 2018</t>
+          <t>Bald eagles as vectors of marine nutrients – Central Coast Islands (100 Islands study area) – May – July 2017</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6520,7 +6528,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>100 Islands</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6540,56 +6548,48 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N57" t="n">
+        <v>2</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.58323147, 51.38160352], [-127.80979387, 51.38160352], [-127.80979387, 52.09997599], [-128.58323147, 52.09997599], [-128.58323147, 51.38160352]]]}</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>other, nutrients</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUxkcndoNFQ4T2xyZWI</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>2022-01-24</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="V57" t="n">
         <v>1</v>
       </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-140.68082679, 46.98536693], [-119.96438849, 46.98536693], [-119.96438849, 59.31669647], [-140.68082679, 59.31669647], [-140.68082679, 46.98536693]]]}</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>other, inorganicCarbon</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>10.21966/zxzr-e472</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWdoaWlmcWF6VWhJWTk</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>2022-01-24</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="n">
-        <v>0</v>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8689,12 +8689,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
+          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -8704,7 +8704,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
+          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -8720,11 +8720,7 @@
       <c r="H77" t="b">
         <v>0</v>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Airborne Coastal Observatory</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>completed</t>
@@ -8750,12 +8746,12 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -8766,7 +8762,7 @@
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -8780,7 +8776,7 @@
         </is>
       </c>
       <c r="V77" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
@@ -8791,12 +8787,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
+          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -8806,7 +8802,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
+          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8822,7 +8818,11 @@
       <c r="H78" t="b">
         <v>0</v>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Airborne Coastal Observatory</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr">
         <is>
           <t>completed</t>
@@ -8848,12 +8848,12 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -8864,7 +8864,7 @@
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -8878,7 +8878,7 @@
         </is>
       </c>
       <c r="V78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
@@ -13229,12 +13229,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
+          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019 Version 4.1</t>
+          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -13267,7 +13267,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -13286,11 +13286,11 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -13305,12 +13305,12 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>10.21966/zvwf-qn04</t>
+          <t>10.21966/XNH1-TP28</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
@@ -13320,18 +13320,16 @@
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="V120" t="n">
-        <v>5</v>
-      </c>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr"/>
       <c r="W120" t="n">
         <v>1</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 1}]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -13341,12 +13339,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
+          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -13356,7 +13354,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
+          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019 Version 4.1</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -13379,7 +13377,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -13398,11 +13396,11 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -13417,12 +13415,12 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>10.21966/XNH1-TP28</t>
+          <t>10.21966/zvwf-qn04</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
         </is>
       </c>
       <c r="T121" t="inlineStr">
@@ -13432,16 +13430,18 @@
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="V121" t="inlineStr"/>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="V121" t="n">
+        <v>5</v>
+      </c>
       <c r="W121" t="n">
         <v>1</v>
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[{'year': '2025', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -14661,12 +14661,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
+          <t>ca-cioos_765d00bb-beec-486c-bd00-e27f972b7324</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada. Version 1.0.</t>
+          <t>Microbial activity and carbon fluxes in rainforest soil – Tsunami Hill, Calvert Island – June 2015 - April 2016</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Watersheds, Oceanography</t>
+          <t>Genomics, Watersheds</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -14712,33 +14712,37 @@
           <t>dataset</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>University of British Columbia</t>
+        </is>
+      </c>
       <c r="N133" t="n">
         <v>1</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13650264, 51.64966999], [-128.12495841, 51.64966999], [-128.12495841, 51.65523482], [-128.13650264, 51.65523482], [-128.13650264, 51.64966999]]]}</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>10.21966/66x5-a210</t>
+          <t>10.21966/1.715630</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUE0SHdBOUNiWjU5bFY</t>
         </is>
       </c>
       <c r="T133" t="inlineStr">
@@ -14752,7 +14756,7 @@
         </is>
       </c>
       <c r="V133" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="W133" t="n">
         <v>0</v>
@@ -14769,12 +14773,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ca-cioos_765d00bb-beec-486c-bd00-e27f972b7324</t>
+          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -14784,7 +14788,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Microbial activity and carbon fluxes in rainforest soil – Tsunami Hill, Calvert Island – June 2015 - April 2016</t>
+          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada. Version 1.0.</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -14802,7 +14806,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Genomics, Watersheds</t>
+          <t>Watersheds, Oceanography</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -14820,37 +14824,33 @@
           <t>dataset</t>
         </is>
       </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>University of British Columbia</t>
-        </is>
-      </c>
+      <c r="M134" t="inlineStr"/>
       <c r="N134" t="n">
         <v>1</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13650264, 51.64966999], [-128.12495841, 51.64966999], [-128.12495841, 51.65523482], [-128.13650264, 51.65523482], [-128.13650264, 51.64966999]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>10.21966/1.715630</t>
+          <t>10.21966/66x5-a210</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUE0SHdBOUNiWjU5bFY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
         </is>
       </c>
       <c r="T134" t="inlineStr">
@@ -14864,7 +14864,7 @@
         </is>
       </c>
       <c r="V134" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W134" t="n">
         <v>0</v>
@@ -15215,12 +15215,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
+          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -15230,7 +15230,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
+          <t>Stage-Discharge Time Series - Calvert Island - Archived Version 1.0</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -15248,7 +15248,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15268,20 +15268,20 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Vancouver Island University</t>
         </is>
       </c>
       <c r="N138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
+          <t>[{'max': '250.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
@@ -15289,14 +15289,10 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R138" t="inlineStr">
-        <is>
-          <t>10.21966/1.135248</t>
-        </is>
-      </c>
+      <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFjSmdJMGxrU1pZbXM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
         </is>
       </c>
       <c r="T138" t="inlineStr">
@@ -15306,20 +15302,14 @@
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="V138" t="n">
-        <v>2</v>
-      </c>
-      <c r="W138" t="n">
-        <v>0</v>
-      </c>
-      <c r="X138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="W138" t="inlineStr"/>
+      <c r="X138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15327,12 +15317,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
+          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -15342,7 +15332,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Stage-Discharge Time Series - Calvert Island - Archived Version 1.0</t>
+          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -15360,7 +15350,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -15380,20 +15370,20 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Vancouver Island University</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>[{'max': '250.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
@@ -15401,10 +15391,14 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R139" t="inlineStr"/>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>10.21966/1.135248</t>
+        </is>
+      </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFjSmdJMGxrU1pZbXM</t>
         </is>
       </c>
       <c r="T139" t="inlineStr">
@@ -15414,14 +15408,20 @@
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V139" t="n">
-        <v>5</v>
-      </c>
-      <c r="W139" t="inlineStr"/>
-      <c r="X139" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0</v>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15429,12 +15429,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ca-cioos_b694a5c5-6a7e-4206-96aa-5b7754323345</t>
+          <t>ca-cioos_b52d5602-f81d-4565-9574-e448e99bc997</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -15444,7 +15444,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Air temperature and relative humidity time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
+          <t>Bathymetry for Six Lakes on Calvert and Hecate Islands - 2016 - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -15462,12 +15462,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Watersheds, Geospatial</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -15490,12 +15490,12 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.30095161, 50.04299371], [-125.08745063, 50.04299371], [-125.08745063, 51.791595], [-128.30095161, 51.791595], [-128.30095161, 50.04299371]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.09646606445312, 51.5996802644666], [-127.9508972167969, 51.5996802644666], [-127.9508972167969, 51.69171329024539], [-128.09646606445312, 51.69171329024539], [-128.09646606445312, 51.5996802644666]]]}</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>[{'max': '741.0', 'min': '3.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
@@ -15503,10 +15503,14 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R140" t="inlineStr"/>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>10.21966/fcwf-p919</t>
+        </is>
+      </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWRmQkdrNXg2bFpvUTE</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWxuNHhkYXVuNlFDSVY</t>
         </is>
       </c>
       <c r="T140" t="inlineStr">
@@ -15516,14 +15520,20 @@
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V140" t="n">
-        <v>8</v>
-      </c>
-      <c r="W140" t="inlineStr"/>
-      <c r="X140" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W140" t="n">
+        <v>1</v>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>[{'year': '2022', 'total': 1}]</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15531,12 +15541,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>ca-cioos_b52d5602-f81d-4565-9574-e448e99bc997</t>
+          <t>ca-cioos_b694a5c5-6a7e-4206-96aa-5b7754323345</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -15546,7 +15556,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Bathymetry for Six Lakes on Calvert and Hecate Islands - 2016 - British Columbia - Canada</t>
+          <t>Air temperature and relative humidity time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -15564,12 +15574,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Watersheds, Geospatial</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -15592,12 +15602,12 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.09646606445312, 51.5996802644666], [-127.9508972167969, 51.5996802644666], [-127.9508972167969, 51.69171329024539], [-128.09646606445312, 51.69171329024539], [-128.09646606445312, 51.5996802644666]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.30095161, 50.04299371], [-125.08745063, 50.04299371], [-125.08745063, 51.791595], [-128.30095161, 51.791595], [-128.30095161, 50.04299371]]]}</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '741.0', 'min': '3.0'}]</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
@@ -15605,14 +15615,10 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R141" t="inlineStr">
-        <is>
-          <t>10.21966/fcwf-p919</t>
-        </is>
-      </c>
+      <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWxuNHhkYXVuNlFDSVY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWRmQkdrNXg2bFpvUTE</t>
         </is>
       </c>
       <c r="T141" t="inlineStr">
@@ -15622,20 +15628,14 @@
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="V141" t="n">
-        <v>1</v>
-      </c>
-      <c r="W141" t="n">
-        <v>1</v>
-      </c>
-      <c r="X141" t="inlineStr">
-        <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="W141" t="inlineStr"/>
+      <c r="X141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -25865,9 +25865,7 @@
           <t>2026-03-19</t>
         </is>
       </c>
-      <c r="V233" t="n">
-        <v>1</v>
-      </c>
+      <c r="V233" t="inlineStr"/>
       <c r="W233" t="n">
         <v>0</v>
       </c>

--- a/main/catalog_summary.xlsx
+++ b/main/catalog_summary.xlsx
@@ -1819,12 +1819,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ca-cioos_af65bf72-27af-4747-8911-ab05591762ac</t>
+          <t>ca-cioos_ab901b46-43f6-4044-b0c3-b5fd825622f4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kelp forest communities along an otter gradient</t>
+          <t>World View 2 Imagery - Coverage of three regions of the BC Central Coast - Summer 2014, 2015, &amp; 2016</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1852,12 +1852,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>underDevelopment</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Simon Fraser University</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.770751953125, 51.33404377878941], [-127.74902343749999, 51.33404377878941], [-127.74902343749999, 52.19077237113535], [-128.770751953125, 52.19077237113535], [-128.770751953125, 51.33404377878941]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.61145019531247, 51.61801654877371], [-127.91931152343746, 51.61801654877371], [-127.91931152343746, 52.11325243469631], [-128.61145019531247, 52.11325243469631], [-128.61145019531247, 51.61801654877371]]]}</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>[{'max': '50.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1893,10 +1893,14 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>10.21966/nmds-rx42</t>
+        </is>
+      </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXlMbjJYUlpvZFpITks</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXp1R01BNWFYV0RkUEY</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -1906,14 +1910,18 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="V14" t="n">
-        <v>5</v>
-      </c>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1921,12 +1929,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ca-cioos_ab901b46-43f6-4044-b0c3-b5fd825622f4</t>
+          <t>ca-cioos_af65bf72-27af-4747-8911-ab05591762ac</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1936,7 +1944,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>World View 2 Imagery - Coverage of three regions of the BC Central Coast - Summer 2014, 2015, &amp; 2016</t>
+          <t>Kelp forest communities along an otter gradient</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1954,12 +1962,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>underDevelopment</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1974,7 +1982,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Simon Fraser University</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1982,12 +1990,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.61145019531247, 51.61801654877371], [-127.91931152343746, 51.61801654877371], [-127.91931152343746, 52.11325243469631], [-128.61145019531247, 52.11325243469631], [-128.61145019531247, 51.61801654877371]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.770751953125, 51.33404377878941], [-127.74902343749999, 51.33404377878941], [-127.74902343749999, 52.19077237113535], [-128.770751953125, 52.19077237113535], [-128.770751953125, 51.33404377878941]]]}</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '50.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1995,14 +2003,10 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>10.21966/nmds-rx42</t>
-        </is>
-      </c>
+      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXp1R01BNWFYV0RkUEY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXlMbjJYUlpvZFpITks</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -2012,18 +2016,14 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>5</v>
+      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -8689,12 +8689,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
+          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -8704,7 +8704,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
+          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -8720,7 +8720,11 @@
       <c r="H77" t="b">
         <v>0</v>
       </c>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Airborne Coastal Observatory</t>
+        </is>
+      </c>
       <c r="J77" t="inlineStr">
         <is>
           <t>completed</t>
@@ -8746,12 +8750,12 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -8762,7 +8766,7 @@
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -8776,7 +8780,7 @@
         </is>
       </c>
       <c r="V77" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
@@ -8787,12 +8791,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
+          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -8802,7 +8806,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
+          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8818,11 +8822,7 @@
       <c r="H78" t="b">
         <v>0</v>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Airborne Coastal Observatory</t>
-        </is>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>completed</t>
@@ -8848,12 +8848,12 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -8864,7 +8864,7 @@
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -8878,7 +8878,7 @@
         </is>
       </c>
       <c r="V78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
@@ -13229,12 +13229,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
+          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
+          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019 Version 4.1</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -13267,7 +13267,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -13286,11 +13286,11 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -13305,12 +13305,12 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>10.21966/XNH1-TP28</t>
+          <t>10.21966/zvwf-qn04</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
@@ -13320,16 +13320,18 @@
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="V120" t="inlineStr"/>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="V120" t="n">
+        <v>5</v>
+      </c>
       <c r="W120" t="n">
         <v>1</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[{'year': '2025', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -13339,12 +13341,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
+          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -13354,7 +13356,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019 Version 4.1</t>
+          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -13377,7 +13379,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -13396,11 +13398,11 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -13415,12 +13417,12 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>10.21966/zvwf-qn04</t>
+          <t>10.21966/XNH1-TP28</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
         </is>
       </c>
       <c r="T121" t="inlineStr">
@@ -13430,18 +13432,16 @@
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="V121" t="n">
-        <v>5</v>
-      </c>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr"/>
       <c r="W121" t="n">
         <v>1</v>
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 1}]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -14661,12 +14661,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ca-cioos_765d00bb-beec-486c-bd00-e27f972b7324</t>
+          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Microbial activity and carbon fluxes in rainforest soil – Tsunami Hill, Calvert Island – June 2015 - April 2016</t>
+          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada. Version 1.0.</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Genomics, Watersheds</t>
+          <t>Watersheds, Oceanography</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -14712,37 +14712,33 @@
           <t>dataset</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>University of British Columbia</t>
-        </is>
-      </c>
+      <c r="M133" t="inlineStr"/>
       <c r="N133" t="n">
         <v>1</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13650264, 51.64966999], [-128.12495841, 51.64966999], [-128.12495841, 51.65523482], [-128.13650264, 51.65523482], [-128.13650264, 51.64966999]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>10.21966/1.715630</t>
+          <t>10.21966/66x5-a210</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUE0SHdBOUNiWjU5bFY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
         </is>
       </c>
       <c r="T133" t="inlineStr">
@@ -14756,7 +14752,7 @@
         </is>
       </c>
       <c r="V133" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W133" t="n">
         <v>0</v>
@@ -14773,12 +14769,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
+          <t>ca-cioos_765d00bb-beec-486c-bd00-e27f972b7324</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -14788,7 +14784,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada. Version 1.0.</t>
+          <t>Microbial activity and carbon fluxes in rainforest soil – Tsunami Hill, Calvert Island – June 2015 - April 2016</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -14806,7 +14802,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Watersheds, Oceanography</t>
+          <t>Genomics, Watersheds</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -14824,33 +14820,37 @@
           <t>dataset</t>
         </is>
       </c>
-      <c r="M134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>University of British Columbia</t>
+        </is>
+      </c>
       <c r="N134" t="n">
         <v>1</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13650264, 51.64966999], [-128.12495841, 51.64966999], [-128.12495841, 51.65523482], [-128.13650264, 51.65523482], [-128.13650264, 51.64966999]]]}</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>10.21966/66x5-a210</t>
+          <t>10.21966/1.715630</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUE0SHdBOUNiWjU5bFY</t>
         </is>
       </c>
       <c r="T134" t="inlineStr">
@@ -14864,7 +14864,7 @@
         </is>
       </c>
       <c r="V134" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="W134" t="n">
         <v>0</v>
@@ -15103,12 +15103,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>ca-cioos_97684a5c-9b70-4d8c-854b-9de895d3d71e</t>
+          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -15118,7 +15118,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Baseline Limnology of Lakes in the Kwakshua Watersheds of Calvert and Hecate Islands, BC. 2016-2019 v2.0</t>
+          <t>Stage-Discharge Time Series - Calvert Island - Archived Version 1.0</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -15156,7 +15156,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Vancouver Island University</t>
         </is>
       </c>
       <c r="N137" t="n">
@@ -15164,12 +15164,12 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.15445681, 51.61731613], [-127.95404703, 51.61731613], [-127.95404703, 51.71899959], [-128.15445681, 51.71899959], [-128.15445681, 51.61731613]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '250.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
@@ -15177,14 +15177,10 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R137" t="inlineStr">
-        <is>
-          <t>10.21966/q2tr-2n80</t>
-        </is>
-      </c>
+      <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUxNZXRzVG5oaUFvN1M</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
         </is>
       </c>
       <c r="T137" t="inlineStr">
@@ -15194,20 +15190,14 @@
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="V137" t="n">
-        <v>2</v>
-      </c>
-      <c r="W137" t="n">
-        <v>0</v>
-      </c>
-      <c r="X137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="W137" t="inlineStr"/>
+      <c r="X137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15215,12 +15205,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
+          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -15230,7 +15220,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Stage-Discharge Time Series - Calvert Island - Archived Version 1.0</t>
+          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -15248,7 +15238,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15268,20 +15258,20 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Vancouver Island University</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>[{'max': '250.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
@@ -15289,10 +15279,14 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R138" t="inlineStr"/>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>10.21966/1.135248</t>
+        </is>
+      </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFjSmdJMGxrU1pZbXM</t>
         </is>
       </c>
       <c r="T138" t="inlineStr">
@@ -15302,14 +15296,20 @@
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V138" t="n">
-        <v>5</v>
-      </c>
-      <c r="W138" t="inlineStr"/>
-      <c r="X138" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0</v>
+      </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15317,12 +15317,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
+          <t>ca-cioos_97684a5c-9b70-4d8c-854b-9de895d3d71e</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -15332,7 +15332,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
+          <t>Baseline Limnology of Lakes in the Kwakshua Watersheds of Calvert and Hecate Islands, BC. 2016-2019 v2.0</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -15370,20 +15370,20 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.15445681, 51.61731613], [-127.95404703, 51.61731613], [-127.95404703, 51.71899959], [-128.15445681, 51.71899959], [-128.15445681, 51.61731613]]]}</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
@@ -15393,12 +15393,12 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>10.21966/1.135248</t>
+          <t>10.21966/q2tr-2n80</t>
         </is>
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFjSmdJMGxrU1pZbXM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUxNZXRzVG5oaUFvN1M</t>
         </is>
       </c>
       <c r="T139" t="inlineStr">
@@ -15429,12 +15429,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ca-cioos_b52d5602-f81d-4565-9574-e448e99bc997</t>
+          <t>ca-cioos_b694a5c5-6a7e-4206-96aa-5b7754323345</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -15444,7 +15444,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Bathymetry for Six Lakes on Calvert and Hecate Islands - 2016 - British Columbia - Canada</t>
+          <t>Air temperature and relative humidity time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -15462,12 +15462,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Watersheds, Geospatial</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -15490,12 +15490,12 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.09646606445312, 51.5996802644666], [-127.9508972167969, 51.5996802644666], [-127.9508972167969, 51.69171329024539], [-128.09646606445312, 51.69171329024539], [-128.09646606445312, 51.5996802644666]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.30095161, 50.04299371], [-125.08745063, 50.04299371], [-125.08745063, 51.791595], [-128.30095161, 51.791595], [-128.30095161, 50.04299371]]]}</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '741.0', 'min': '3.0'}]</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
@@ -15503,14 +15503,10 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R140" t="inlineStr">
-        <is>
-          <t>10.21966/fcwf-p919</t>
-        </is>
-      </c>
+      <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWxuNHhkYXVuNlFDSVY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWRmQkdrNXg2bFpvUTE</t>
         </is>
       </c>
       <c r="T140" t="inlineStr">
@@ -15520,20 +15516,14 @@
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="V140" t="n">
-        <v>1</v>
-      </c>
-      <c r="W140" t="n">
-        <v>1</v>
-      </c>
-      <c r="X140" t="inlineStr">
-        <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="W140" t="inlineStr"/>
+      <c r="X140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15541,12 +15531,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>ca-cioos_b694a5c5-6a7e-4206-96aa-5b7754323345</t>
+          <t>ca-cioos_b52d5602-f81d-4565-9574-e448e99bc997</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -15556,7 +15546,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Air temperature and relative humidity time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
+          <t>Bathymetry for Six Lakes on Calvert and Hecate Islands - 2016 - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -15574,12 +15564,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Watersheds, Geospatial</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -15602,12 +15592,12 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.30095161, 50.04299371], [-125.08745063, 50.04299371], [-125.08745063, 51.791595], [-128.30095161, 51.791595], [-128.30095161, 50.04299371]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.09646606445312, 51.5996802644666], [-127.9508972167969, 51.5996802644666], [-127.9508972167969, 51.69171329024539], [-128.09646606445312, 51.69171329024539], [-128.09646606445312, 51.5996802644666]]]}</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>[{'max': '741.0', 'min': '3.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
@@ -15615,10 +15605,14 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R141" t="inlineStr"/>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>10.21966/fcwf-p919</t>
+        </is>
+      </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWRmQkdrNXg2bFpvUTE</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWxuNHhkYXVuNlFDSVY</t>
         </is>
       </c>
       <c r="T141" t="inlineStr">
@@ -15628,14 +15622,20 @@
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V141" t="n">
-        <v>8</v>
-      </c>
-      <c r="W141" t="inlineStr"/>
-      <c r="X141" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W141" t="n">
+        <v>1</v>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>[{'year': '2022', 'total': 1}]</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -20530,7 +20530,7 @@
         </is>
       </c>
       <c r="V185" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W185" t="n">
         <v>0</v>

--- a/main/catalog_summary.xlsx
+++ b/main/catalog_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X261"/>
+  <dimension ref="A1:X260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1265,7 +1265,11 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>10.21966/k6t6-bp93</t>
+        </is>
+      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXlVaXo3ZUV1VXBVeHI</t>
@@ -1278,14 +1282,18 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="V8" t="n">
-        <v>5</v>
-      </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1477,7 +1485,11 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>10.21966/dtf5-j890</t>
+        </is>
+      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVZnUmI5R3pHdHJYVXQ</t>
@@ -1490,14 +1502,20 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="V10" t="n">
         <v>2</v>
       </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1505,12 +1523,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
+          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ca-cioos_55daf524-146e-4b06-8c6c-3255c7e3c77a</t>
+          <t>ca-cioos_4bf1e341-637c-4884-b373-033e033b3cba</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1520,7 +1538,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vegetated Islands Polygons - 100 Islands Research</t>
+          <t>Northwest Calvert Substrate Mapping</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1538,7 +1556,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>100 Islands</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1562,16 +1580,16 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6993408203125, 51.368351060511344], [-127.4908447265625, 51.368351060511344], [-127.4908447265625, 52.197506856993925], [-128.6993408203125, 52.197506856993925], [-128.6993408203125, 51.368351060511344]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.18309295, 51.63973703], [-128.06292998, 51.63973703], [-128.06292998, 51.71531293], [-128.18309295, 51.71531293], [-128.18309295, 51.63973703]]]}</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>[{'max': '500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '600.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1579,10 +1597,14 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>10.21966/35tn-w772</t>
+        </is>
+      </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW90czhQM1A2WXJWTVg</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWJlU2MzU0psd2EzM0w</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1592,14 +1614,18 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="V11" t="n">
-        <v>2</v>
-      </c>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1607,12 +1633,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6a1254e5-3815-4289-ba1c-984fb84dc1fe</t>
+          <t>0c08a4f0-b28c-40fe-aaa8-a03113a7c735</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ca-cioos_4bf1e341-637c-4884-b373-033e033b3cba</t>
+          <t>ca-cioos_55daf524-146e-4b06-8c6c-3255c7e3c77a</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1622,7 +1648,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Northwest Calvert Substrate Mapping</t>
+          <t>Vegetated Islands Polygons - 100 Islands Research</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1640,7 +1666,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>100 Islands</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1664,16 +1690,16 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.18309295, 51.63973703], [-128.06292998, 51.63973703], [-128.06292998, 51.71531293], [-128.18309295, 51.71531293], [-128.18309295, 51.63973703]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6993408203125, 51.368351060511344], [-127.4908447265625, 51.368351060511344], [-127.4908447265625, 52.197506856993925], [-128.6993408203125, 52.197506856993925], [-128.6993408203125, 51.368351060511344]]]}</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>[{'max': '600.0', 'min': '0.0'}]</t>
+          <t>[{'max': '500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1683,12 +1709,12 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>10.21966/35tn-w772</t>
+          <t>10.21966/smwx-qp54</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWJlU2MzU0psd2EzM0w</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW90czhQM1A2WXJWTVg</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -1698,10 +1724,12 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr"/>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
@@ -1819,12 +1847,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ca-cioos_ab901b46-43f6-4044-b0c3-b5fd825622f4</t>
+          <t>ca-cioos_af65bf72-27af-4747-8911-ab05591762ac</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1834,7 +1862,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>World View 2 Imagery - Coverage of three regions of the BC Central Coast - Summer 2014, 2015, &amp; 2016</t>
+          <t>Kelp forest communities along an otter gradient</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1852,12 +1880,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>underDevelopment</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1872,7 +1900,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Simon Fraser University</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1880,12 +1908,12 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.61145019531247, 51.61801654877371], [-127.91931152343746, 51.61801654877371], [-127.91931152343746, 52.11325243469631], [-128.61145019531247, 52.11325243469631], [-128.61145019531247, 51.61801654877371]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.770751953125, 51.33404377878941], [-127.74902343749999, 51.33404377878941], [-127.74902343749999, 52.19077237113535], [-128.770751953125, 52.19077237113535], [-128.770751953125, 51.33404377878941]]]}</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '50.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1893,14 +1921,10 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>10.21966/nmds-rx42</t>
-        </is>
-      </c>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXp1R01BNWFYV0RkUEY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXlMbjJYUlpvZFpITks</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -1910,18 +1934,14 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>5</v>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1929,12 +1949,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ca-cioos_af65bf72-27af-4747-8911-ab05591762ac</t>
+          <t>ca-cioos_ab901b46-43f6-4044-b0c3-b5fd825622f4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1944,7 +1964,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kelp forest communities along an otter gradient</t>
+          <t>World View 2 Imagery - Coverage of three regions of the BC Central Coast - Summer 2014, 2015, &amp; 2016</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1962,12 +1982,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>underDevelopment</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1982,7 +2002,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Simon Fraser University</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1990,12 +2010,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.770751953125, 51.33404377878941], [-127.74902343749999, 51.33404377878941], [-127.74902343749999, 52.19077237113535], [-128.770751953125, 52.19077237113535], [-128.770751953125, 51.33404377878941]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.61145019531247, 51.61801654877371], [-127.91931152343746, 51.61801654877371], [-127.91931152343746, 52.11325243469631], [-128.61145019531247, 52.11325243469631], [-128.61145019531247, 51.61801654877371]]]}</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>[{'max': '50.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2003,10 +2023,14 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>10.21966/nmds-rx42</t>
+        </is>
+      </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXlMbjJYUlpvZFpITks</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXp1R01BNWFYV0RkUEY</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -2016,14 +2040,18 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="V15" t="n">
-        <v>5</v>
-      </c>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -6569,7 +6597,11 @@
           <t>other, nutrients</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>10.21966/2svf-e642</t>
+        </is>
+      </c>
       <c r="S57" t="inlineStr">
         <is>
           <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUxkcndoNFQ4T2xyZWI</t>
@@ -6582,14 +6614,18 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="V57" t="n">
-        <v>1</v>
-      </c>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8689,12 +8725,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
+          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -8704,7 +8740,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
+          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -8720,11 +8756,7 @@
       <c r="H77" t="b">
         <v>0</v>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Airborne Coastal Observatory</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>completed</t>
@@ -8750,12 +8782,12 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -8766,7 +8798,7 @@
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -8780,7 +8812,7 @@
         </is>
       </c>
       <c r="V77" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
@@ -8791,12 +8823,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
+          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -8806,7 +8838,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
+          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8822,7 +8854,11 @@
       <c r="H78" t="b">
         <v>0</v>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Airborne Coastal Observatory</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr">
         <is>
           <t>completed</t>
@@ -8848,12 +8884,12 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -8864,7 +8900,7 @@
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -8878,7 +8914,7 @@
         </is>
       </c>
       <c r="V78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
@@ -10428,7 +10464,7 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -10445,7 +10481,11 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr"/>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>10.21966/64tt-jh34</t>
+        </is>
+      </c>
       <c r="S93" t="inlineStr">
         <is>
           <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1SSXd3cG5UbzVYVW8</t>
@@ -10458,14 +10498,18 @@
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="V93" t="n">
-        <v>2</v>
-      </c>
-      <c r="W93" t="inlineStr"/>
-      <c r="X93" t="inlineStr"/>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr"/>
+      <c r="W93" t="n">
+        <v>0</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10526,7 +10570,7 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -10543,7 +10587,11 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr"/>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>10.21966/rwwv-na68</t>
+        </is>
+      </c>
       <c r="S94" t="inlineStr">
         <is>
           <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1BMXVHcFJ0d1ZVbjg</t>
@@ -10556,14 +10604,20 @@
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="V94" t="n">
-        <v>4</v>
-      </c>
-      <c r="W94" t="inlineStr"/>
-      <c r="X94" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="W94" t="n">
+        <v>0</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10755,7 +10809,11 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R96" t="inlineStr"/>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>10.21966/3aa8-3347</t>
+        </is>
+      </c>
       <c r="S96" t="inlineStr">
         <is>
           <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTdQU1J3ejBLVmp5MGY</t>
@@ -10768,14 +10826,18 @@
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="V96" t="n">
-        <v>5</v>
-      </c>
-      <c r="W96" t="inlineStr"/>
-      <c r="X96" t="inlineStr"/>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr"/>
+      <c r="W96" t="n">
+        <v>0</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10857,7 +10919,11 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr"/>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>10.21966/36b8-hq30</t>
+        </is>
+      </c>
       <c r="S97" t="inlineStr">
         <is>
           <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTNoNHEyQ0g1c3VIbGE</t>
@@ -10870,14 +10936,20 @@
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="V97" t="n">
-        <v>7</v>
-      </c>
-      <c r="W97" t="inlineStr"/>
-      <c r="X97" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W97" t="n">
+        <v>0</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11067,7 +11139,11 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr"/>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>10.21966/zk1j-y602</t>
+        </is>
+      </c>
       <c r="S99" t="inlineStr">
         <is>
           <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTJRNjNXMTFqUE5Semc</t>
@@ -11080,14 +11156,20 @@
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="V99" t="n">
-        <v>5</v>
-      </c>
-      <c r="W99" t="inlineStr"/>
-      <c r="X99" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W99" t="n">
+        <v>0</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11505,7 +11587,11 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R103" t="inlineStr"/>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>10.21966/dzhe-t816</t>
+        </is>
+      </c>
       <c r="S103" t="inlineStr">
         <is>
           <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVpRZnZ2Y0d4cWhKcHk</t>
@@ -11518,14 +11604,18 @@
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="V103" t="n">
-        <v>4</v>
-      </c>
-      <c r="W103" t="inlineStr"/>
-      <c r="X103" t="inlineStr"/>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr"/>
+      <c r="W103" t="n">
+        <v>0</v>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12607,7 +12697,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>document</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -12618,7 +12708,11 @@
       <c r="H114" t="b">
         <v>0</v>
       </c>
-      <c r="I114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Geospatial</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr">
         <is>
           <t>completed</t>
@@ -12657,7 +12751,11 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R114" t="inlineStr"/>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>10.21966/da7n-d283</t>
+        </is>
+      </c>
       <c r="S114" t="inlineStr">
         <is>
           <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTRJWUxCNm94ZkpxNkk</t>
@@ -12670,14 +12768,18 @@
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="V114" t="n">
-        <v>6</v>
-      </c>
-      <c r="W114" t="inlineStr"/>
-      <c r="X114" t="inlineStr"/>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr"/>
+      <c r="W114" t="n">
+        <v>0</v>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13212,7 +13314,7 @@
         </is>
       </c>
       <c r="V119" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W119" t="n">
         <v>0</v>
@@ -13229,12 +13331,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
+          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -13244,7 +13346,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019 Version 4.1</t>
+          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -13267,7 +13369,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -13286,11 +13388,11 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -13305,12 +13407,12 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>10.21966/zvwf-qn04</t>
+          <t>10.21966/XNH1-TP28</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
@@ -13320,18 +13422,16 @@
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="V120" t="n">
-        <v>5</v>
-      </c>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr"/>
       <c r="W120" t="n">
         <v>1</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 1}]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -13341,12 +13441,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
+          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -13356,7 +13456,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
+          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019 Version 4.1</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -13379,7 +13479,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -13398,11 +13498,11 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -13417,12 +13517,12 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>10.21966/XNH1-TP28</t>
+          <t>10.21966/zvwf-qn04</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
         </is>
       </c>
       <c r="T121" t="inlineStr">
@@ -13432,16 +13532,18 @@
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="V121" t="inlineStr"/>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="V121" t="n">
+        <v>5</v>
+      </c>
       <c r="W121" t="n">
         <v>1</v>
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[{'year': '2025', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -13889,12 +13991,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ca-cioos_23bc8c35-2e4e-4382-9296-a52d5ea49889</t>
+          <t>ca-cioos_26443ab2-964f-4031-a53b-f132434573e8</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -13904,7 +14006,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Discharge Time Series (2013-2017) – Calvert Island - Archived Version 3.0</t>
+          <t>Ecosystem Comparison Plots - Calvert Island</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -13922,7 +14024,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Geospatial, Watersheds</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -13950,7 +14052,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13903808593744, 51.626542529786036], [-127.97355651855466, 51.626542529786036], [-127.97355651855466, 51.67766477883444], [-128.13903808593744, 51.67766477883444], [-128.13903808593744, 51.626542529786036]]]}</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -13965,12 +14067,12 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>10.21966/sbyc-d030</t>
+          <t>10.21966/1.56481</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUdGRGRjUW9LRnBVNVI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWc4TU94c2lwT0tYa2U</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
@@ -13980,18 +14082,18 @@
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V126" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="W126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -14001,12 +14103,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ca-cioos_26443ab2-964f-4031-a53b-f132434573e8</t>
+          <t>ca-cioos_23bc8c35-2e4e-4382-9296-a52d5ea49889</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -14016,7 +14118,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Ecosystem Comparison Plots - Calvert Island</t>
+          <t>Discharge Time Series (2013-2017) – Calvert Island - Archived Version 3.0</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -14034,7 +14136,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Geospatial, Watersheds</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -14062,7 +14164,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13903808593744, 51.626542529786036], [-127.97355651855466, 51.626542529786036], [-127.97355651855466, 51.67766477883444], [-128.13903808593744, 51.67766477883444], [-128.13903808593744, 51.626542529786036]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -14077,12 +14179,12 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>10.21966/1.56481</t>
+          <t>10.21966/sbyc-d030</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWc4TU94c2lwT0tYa2U</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUdGRGRjUW9LRnBVNVI</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
@@ -14092,18 +14194,18 @@
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="V127" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="W127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -14752,7 +14854,7 @@
         </is>
       </c>
       <c r="V133" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="W133" t="n">
         <v>0</v>
@@ -15103,12 +15205,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
+          <t>ca-cioos_97684a5c-9b70-4d8c-854b-9de895d3d71e</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -15118,7 +15220,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Stage-Discharge Time Series - Calvert Island - Archived Version 1.0</t>
+          <t>Baseline Limnology of Lakes in the Kwakshua Watersheds of Calvert and Hecate Islands, BC. 2016-2019 v2.0</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -15156,7 +15258,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Vancouver Island University</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N137" t="n">
@@ -15164,12 +15266,12 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.15445681, 51.61731613], [-127.95404703, 51.61731613], [-127.95404703, 51.71899959], [-128.15445681, 51.71899959], [-128.15445681, 51.61731613]]]}</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>[{'max': '250.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
@@ -15177,10 +15279,14 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R137" t="inlineStr"/>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>10.21966/q2tr-2n80</t>
+        </is>
+      </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUxNZXRzVG5oaUFvN1M</t>
         </is>
       </c>
       <c r="T137" t="inlineStr">
@@ -15190,14 +15296,20 @@
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V137" t="n">
-        <v>5</v>
-      </c>
-      <c r="W137" t="inlineStr"/>
-      <c r="X137" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0</v>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15317,12 +15429,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>49ec67e4-f7be-4658-b2b6-e4b57d9901df</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ca-cioos_97684a5c-9b70-4d8c-854b-9de895d3d71e</t>
+          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -15332,7 +15444,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Baseline Limnology of Lakes in the Kwakshua Watersheds of Calvert and Hecate Islands, BC. 2016-2019 v2.0</t>
+          <t>Stage-Discharge Time Series - Calvert Island - Archived Version 1.0</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -15370,7 +15482,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Vancouver Island University</t>
         </is>
       </c>
       <c r="N139" t="n">
@@ -15378,12 +15490,12 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.15445681, 51.61731613], [-127.95404703, 51.61731613], [-127.95404703, 51.71899959], [-128.15445681, 51.71899959], [-128.15445681, 51.61731613]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '250.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
@@ -15391,14 +15503,10 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R139" t="inlineStr">
-        <is>
-          <t>10.21966/q2tr-2n80</t>
-        </is>
-      </c>
+      <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUxNZXRzVG5oaUFvN1M</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
         </is>
       </c>
       <c r="T139" t="inlineStr">
@@ -15408,20 +15516,14 @@
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="V139" t="n">
-        <v>2</v>
-      </c>
-      <c r="W139" t="n">
-        <v>0</v>
-      </c>
-      <c r="X139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="W139" t="inlineStr"/>
+      <c r="X139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -20530,7 +20632,7 @@
         </is>
       </c>
       <c r="V185" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W185" t="n">
         <v>0</v>
@@ -20547,12 +20649,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>abb0b617-3a3e-43ec-b62e-e2918bfc10aa</t>
+          <t>9df42f88-b8d8-4e2d-97bb-ad5ba49f6f1f</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>ca-cioos_b8483c9e-81e6-4e1a-b09f-2d66f8fee9a2</t>
+          <t>ca-cioos_59b33373-ae4a-4719-a3df-0e36a08187d8</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -20562,7 +20664,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp (Nereocystis luetkeana) derived from fixed-wing surveys (2023), Denman Island to south Quadra Island, British Columbia, Canada</t>
+          <t>Seagrass Site-Level Production on BC Central Coast</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -20580,12 +20682,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Nearshore, Geospatial</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -20608,37 +20710,37 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.3, 50.02], [-125.1, 50.05], [-125.1, 49.9], [-124.8, 49.71], [-124.7, 49.56], [-124.8, 49.55], [-124.9, 49.64], [-125.2, 49.9], [-125.2, 49.9], [-125.3, 50.02]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.98931373, 50.8340959], [-127.03580726, 50.8340959], [-127.03580726, 52.33530479], [-128.98931373, 52.33530479], [-128.98931373, 50.8340959]]]}</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '10.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>other, seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>10.21966/fmw1-8w35</t>
+          <t>10.21966/ezev-0v96</t>
         </is>
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-NpNoCv2XWdhBoo5RBKV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/lJHlH9nm20QQOPuk217xLlxWbNv1/-NPt7-mgrZEUzma8l5W_</t>
         </is>
       </c>
       <c r="T186" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="U186" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="V186" t="n">
@@ -20659,12 +20761,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>9df42f88-b8d8-4e2d-97bb-ad5ba49f6f1f</t>
+          <t>bf7c05e8-510d-4449-9e81-4c358ff3f440</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>ca-cioos_59b33373-ae4a-4719-a3df-0e36a08187d8</t>
+          <t>ca-cioos_1755dc37-8d33-4158-8041-c22536fd5771</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -20674,7 +20776,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Seagrass Site-Level Production on BC Central Coast</t>
+          <t>Bulk and Size-Fractionated Chlorophyll and Phaeopigment Concentrations Collected by Niskin Bottle, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -20692,7 +20794,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -20720,37 +20822,37 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.98931373, 50.8340959], [-127.03580726, 50.8340959], [-127.03580726, 52.33530479], [-128.98931373, 52.33530479], [-128.98931373, 50.8340959]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>[{'max': '10.0', 'min': '0.0'}]</t>
+          <t>[{'max': '650.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>other, seagrassCoverAndComposition</t>
+          <t>particulateMatter</t>
         </is>
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>10.21966/ezev-0v96</t>
+          <t>10.21966/90h6-b497</t>
         </is>
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/lJHlH9nm20QQOPuk217xLlxWbNv1/-NPt7-mgrZEUzma8l5W_</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-McQFPAf457LB4-SWmyL</t>
         </is>
       </c>
       <c r="T187" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="U187" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="V187" t="n">
@@ -20771,12 +20873,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>bf7c05e8-510d-4449-9e81-4c358ff3f440</t>
+          <t>8882a149-fabd-4ecd-98d3-68a2a88aee38</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>ca-cioos_1755dc37-8d33-4158-8041-c22536fd5771</t>
+          <t>ca-cioos_d55021c3-a142-4e14-8208-36c9826c1893</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -20786,7 +20888,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Bulk and Size-Fractionated Chlorophyll and Phaeopigment Concentrations Collected by Niskin Bottle, BC, Canada (Provisional)</t>
+          <t>Bulk and Size-Fractionated Chlorophyll and Phaeopigment Concentrations Collected by Niskin Bottle, BC, Canada (Research)</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -20828,7 +20930,7 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O188" t="inlineStr">
         <is>
@@ -20842,17 +20944,17 @@
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>particulateMatter</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>10.21966/90h6-b497</t>
+          <t>10.21966/q5vm-8797</t>
         </is>
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-McQFPAf457LB4-SWmyL</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-MadZvZJ4ZeikpCgRcV8</t>
         </is>
       </c>
       <c r="T188" t="inlineStr">
@@ -20865,9 +20967,7 @@
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="V188" t="n">
-        <v>1</v>
-      </c>
+      <c r="V188" t="inlineStr"/>
       <c r="W188" t="n">
         <v>0</v>
       </c>
@@ -20883,12 +20983,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>8882a149-fabd-4ecd-98d3-68a2a88aee38</t>
+          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>ca-cioos_d55021c3-a142-4e14-8208-36c9826c1893</t>
+          <t>ca-cioos_6143028b-028d-46c7-a67d-f3a513435e63</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -20898,7 +20998,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Bulk and Size-Fractionated Chlorophyll and Phaeopigment Concentrations Collected by Niskin Bottle, BC, Canada (Research)</t>
+          <t>Water Property Measurements from Conductivity-Temperature-Depth Profiles, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -20916,7 +21016,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Juvenile Salmon Program, Oceanography, Nearshore</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -20940,44 +21040,46 @@
         </is>
       </c>
       <c r="N189" t="n">
+        <v>1</v>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>[{'max': '700.0', 'min': '1.0'}]</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>oxygen, subSurfaceSalinity, subSurfaceTemperature</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>10.21966/rj8w-aa62</t>
+        </is>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MMHJ4k2EEwxkbXkrjxa</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="V189" t="n">
         <v>2</v>
       </c>
-      <c r="O189" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
-        </is>
-      </c>
-      <c r="P189" t="inlineStr">
-        <is>
-          <t>[{'max': '650.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q189" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R189" t="inlineStr">
-        <is>
-          <t>10.21966/q5vm-8797</t>
-        </is>
-      </c>
-      <c r="S189" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-MadZvZJ4ZeikpCgRcV8</t>
-        </is>
-      </c>
-      <c r="T189" t="inlineStr">
-        <is>
-          <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="U189" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="V189" t="inlineStr"/>
       <c r="W189" t="n">
         <v>0</v>
       </c>
@@ -20993,12 +21095,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
+          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>ca-cioos_6143028b-028d-46c7-a67d-f3a513435e63</t>
+          <t>ca-cioos_6652a7a9-d27f-4cbe-ac04-435c238e991d</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -21008,7 +21110,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Water Property Measurements from Conductivity-Temperature-Depth Profiles, BC, Canada (Provisional)</t>
+          <t>Water Level Time Series, Choke Pass, Central Coast, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -21026,12 +21128,12 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Juvenile Salmon Program, Oceanography, Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -21054,37 +21156,37 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-128.12103, 51.670666]}</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>[{'max': '700.0', 'min': '1.0'}]</t>
+          <t>[{'max': '6.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>oxygen, subSurfaceSalinity, subSurfaceTemperature</t>
+          <t>seaSurfaceHeight</t>
         </is>
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>10.21966/rj8w-aa62</t>
+          <t>10.21966/kqd6-1j57</t>
         </is>
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MMHJ4k2EEwxkbXkrjxa</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-Mknr8pYvIQKw4r-WTFd</t>
         </is>
       </c>
       <c r="T190" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="U190" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="V190" t="n">
@@ -21105,12 +21207,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
+          <t>2081eb2e-67c5-44b7-b048-aeb2c646f238</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>ca-cioos_6652a7a9-d27f-4cbe-ac04-435c238e991d</t>
+          <t>ca-cioos_f67c0c58-3225-4dac-9264-1e76f07c9374</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -21120,7 +21222,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Water Level Time Series, Choke Pass, Central Coast, BC, Canada (Provisional)</t>
+          <t>Data for the paper "Phylogenomic position of eupelagonemids, abundant, and diverse deep-ocean heterotrophs"</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -21138,7 +21240,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Genomics</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -21158,7 +21260,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="N191" t="n">
@@ -21166,42 +21268,40 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-128.12103, 51.670666]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.9661, 51.65001], [-127.966, 51.65001], [-127.966, 51.65], [-127.9661, 51.65], [-127.9661, 51.65001]]]}</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>[{'max': '6.0', 'min': '0.0'}]</t>
+          <t>[{'max': '300.0', 'min': '300.0'}]</t>
         </is>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>seaSurfaceHeight</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>10.21966/kqd6-1j57</t>
+          <t>10.21966/7t4p-s714</t>
         </is>
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-Mknr8pYvIQKw4r-WTFd</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/NSo1FkJnvIbQDOlYlwNfWGnAxx33/-O1xBAkNi0P8igzOb4rg</t>
         </is>
       </c>
       <c r="T191" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="U191" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="V191" t="n">
-        <v>2</v>
-      </c>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr"/>
       <c r="W191" t="n">
         <v>0</v>
       </c>
@@ -21217,12 +21317,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2081eb2e-67c5-44b7-b048-aeb2c646f238</t>
+          <t>1dfdbadf-6314-4411-8d18-752f6dd920e9</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>ca-cioos_f67c0c58-3225-4dac-9264-1e76f07c9374</t>
+          <t>ca-cioos_67e89414-a93f-496d-9766-9311f0d3954e</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -21232,7 +21332,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Data for the paper "Phylogenomic position of eupelagonemids, abundant, and diverse deep-ocean heterotrophs"</t>
+          <t>Motile Invertebrate Surveys - BC Central Coast</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -21250,12 +21350,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Genomics</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -21270,7 +21370,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>University of British Columbia</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N192" t="n">
@@ -21278,46 +21378,48 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.9661, 51.65001], [-127.966, 51.65001], [-127.966, 51.65], [-127.9661, 51.65], [-127.9661, 51.65001]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.2, 51.63], [-128.1, 51.63], [-128.1, 51.67], [-128.2, 51.67], [-128.2, 51.63]]]}</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>[{'max': '300.0', 'min': '300.0'}]</t>
+          <t>[{'max': '5.0', 'min': '-5.0'}]</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>10.21966/7t4p-s714</t>
+          <t>10.21966/0052-wk15</t>
         </is>
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/NSo1FkJnvIbQDOlYlwNfWGnAxx33/-O1xBAkNi0P8igzOb4rg</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-MotWzhmBvoGPE8QZ0sf</t>
         </is>
       </c>
       <c r="T192" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="U192" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
-        </is>
-      </c>
-      <c r="V192" t="inlineStr"/>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="V192" t="n">
+        <v>1</v>
+      </c>
       <c r="W192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X192" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -21327,12 +21429,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>1dfdbadf-6314-4411-8d18-752f6dd920e9</t>
+          <t>a8f61379-14f9-4ccc-bc9b-4408ba8340d7</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>ca-cioos_67e89414-a93f-496d-9766-9311f0d3954e</t>
+          <t>ca-cioos_52797e17-c0ed-46a4-9dcd-e34f801c6205</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -21342,7 +21444,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Motile Invertebrate Surveys - BC Central Coast</t>
+          <t>Fucus Dynamics - Point Intercept Surveys - BC Central Coast</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -21398,27 +21500,27 @@
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>10.21966/0052-wk15</t>
+          <t>10.21966/v57r-g944</t>
         </is>
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-MotWzhmBvoGPE8QZ0sf</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-MopPnOL2o_bshK-cKxr</t>
         </is>
       </c>
       <c r="T193" t="inlineStr">
         <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
           <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="U193" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
         </is>
       </c>
       <c r="V193" t="n">
@@ -21429,7 +21531,7 @@
       </c>
       <c r="X193" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
+          <t>[{'year': '2024', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -21439,12 +21541,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>a8f61379-14f9-4ccc-bc9b-4408ba8340d7</t>
+          <t>c4d3a53a-faa2-4c3e-bcd3-cfdb0aef0078</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>ca-cioos_52797e17-c0ed-46a4-9dcd-e34f801c6205</t>
+          <t>ca-cioos_355467ad-104d-40a6-b06e-52a67bfe247e</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -21454,7 +21556,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Fucus Dynamics - Point Intercept Surveys - BC Central Coast</t>
+          <t>Water column CO2 system measurements from January 2016 to December 2023 from Hakai Institute oceanographic station QU39 in northern Strait of Georgia, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -21472,12 +21574,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -21500,48 +21602,48 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.2, 51.63], [-128.1, 51.63], [-128.1, 51.67], [-128.2, 51.67], [-128.2, 51.63]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.1, 50.03]}</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '-5.0'}]</t>
+          <t>[{'max': '262.0', 'min': '1.0'}]</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>inorganicCarbon, oxygen, subSurfaceSalinity, seaSurfaceTemperature, seaSurfaceSalinity, subSurfaceTemperature</t>
         </is>
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>10.21966/v57r-g944</t>
+          <t>10.21966/k1xg-6920</t>
         </is>
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-MopPnOL2o_bshK-cKxr</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-O6XpUwSfsllQlTBMz53</t>
         </is>
       </c>
       <c r="T194" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="U194" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="V194" t="n">
         <v>1</v>
       </c>
       <c r="W194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X194" t="inlineStr">
         <is>
-          <t>[{'year': '2024', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -21551,12 +21653,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>c4d3a53a-faa2-4c3e-bcd3-cfdb0aef0078</t>
+          <t>52d607c9-46cd-4be9-a752-1b5446272f32</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>ca-cioos_355467ad-104d-40a6-b06e-52a67bfe247e</t>
+          <t>ca-cioos_0507a738-cd65-4ba4-943e-42b9d022b637</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -21566,7 +21668,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Water column CO2 system measurements from January 2016 to December 2023 from Hakai Institute oceanographic station QU39 in northern Strait of Georgia, British Columbia, Canada</t>
+          <t>Fraser River Airborne Surveys - 2021 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -21584,7 +21686,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -21612,42 +21714,40 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.1, 50.03]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.1, 50.5], [-121.7, 50.5], [-121.7, 51.12], [-122.1, 51.12], [-122.1, 50.5]]]}</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>[{'max': '262.0', 'min': '1.0'}]</t>
+          <t>[{'max': '1500.0', 'min': '185.0'}]</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>inorganicCarbon, oxygen, subSurfaceSalinity, seaSurfaceTemperature, seaSurfaceSalinity, subSurfaceTemperature</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>10.21966/k1xg-6920</t>
+          <t>10.21966/ytgc-6g46</t>
         </is>
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-O6XpUwSfsllQlTBMz53</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NHfqx-d8tuAroY8BWc7</t>
         </is>
       </c>
       <c r="T195" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="U195" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="V195" t="n">
-        <v>1</v>
-      </c>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr"/>
       <c r="W195" t="n">
         <v>0</v>
       </c>
@@ -21663,12 +21763,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>52d607c9-46cd-4be9-a752-1b5446272f32</t>
+          <t>551bbe09-f182-478b-8d50-2f9a4dbd93ae</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>ca-cioos_0507a738-cd65-4ba4-943e-42b9d022b637</t>
+          <t>ca-cioos_189dd319-d5ef-4f2a-a060-df8d47628b86</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -21678,7 +21778,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Fraser River Airborne Surveys - 2021 - Hakai Airborne Coastal Observatory</t>
+          <t>Elliot Creek Landslide LiDAR Mapping - 2023 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -21696,7 +21796,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -21720,16 +21820,16 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.1, 50.5], [-121.7, 50.5], [-121.7, 51.12], [-122.1, 51.12], [-122.1, 50.5]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.8, 50.84], [-124.5, 50.84], [-124.5, 51.0], [-124.8, 51.0], [-124.8, 50.84]]]}</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>[{'max': '1500.0', 'min': '185.0'}]</t>
+          <t>[{'max': '2300.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
@@ -21739,12 +21839,12 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>10.21966/ytgc-6g46</t>
+          <t>10.21966/szqj-b355</t>
         </is>
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NHfqx-d8tuAroY8BWc7</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRZqJivYfce75NOoBD</t>
         </is>
       </c>
       <c r="T196" t="inlineStr">
@@ -21754,7 +21854,7 @@
       </c>
       <c r="U196" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="V196" t="inlineStr"/>
@@ -21773,12 +21873,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>551bbe09-f182-478b-8d50-2f9a4dbd93ae</t>
+          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>ca-cioos_189dd319-d5ef-4f2a-a060-df8d47628b86</t>
+          <t>ca-cioos_33a367c1-2706-4301-af99-4455fbe189a0</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -21788,7 +21888,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Elliot Creek Landslide LiDAR Mapping - 2023 - Airborne Coastal Observatory</t>
+          <t>Cryosphere Snow Surveys Southwest British Columbia - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -21806,7 +21906,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -21834,7 +21934,7 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.8, 50.84], [-124.5, 50.84], [-124.5, 51.0], [-124.8, 51.0], [-124.8, 50.84]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.9, 48.62], [-122.1, 48.62], [-122.1, 50.82], [-126.9, 50.82], [-126.9, 48.62]]]}</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
@@ -21849,12 +21949,12 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>10.21966/szqj-b355</t>
+          <t>10.21966/thq7-0g08</t>
         </is>
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRZqJivYfce75NOoBD</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRfMcU9I8mMcBH6qiv</t>
         </is>
       </c>
       <c r="T197" t="inlineStr">
@@ -21867,7 +21967,9 @@
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="V197" t="inlineStr"/>
+      <c r="V197" t="n">
+        <v>3</v>
+      </c>
       <c r="W197" t="n">
         <v>0</v>
       </c>
@@ -21883,12 +21985,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
+          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>ca-cioos_33a367c1-2706-4301-af99-4455fbe189a0</t>
+          <t>ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -21898,7 +22000,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Cryosphere Snow Surveys Southwest British Columbia - Airborne Coastal Observatory</t>
+          <t>Bute Inlet Geohazard - Topography Surveys - 2023 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -21940,16 +22042,16 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.9, 48.62], [-122.1, 48.62], [-122.1, 50.82], [-126.9, 50.82], [-126.9, 48.62]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.9, 50.53], [-124.2, 50.53], [-124.2, 50.99], [-124.9, 50.99], [-124.9, 50.53]]]}</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>[{'max': '2300.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2600.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q198" t="inlineStr">
@@ -21959,12 +22061,12 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>10.21966/thq7-0g08</t>
+          <t>10.21966/e4b8-vp48</t>
         </is>
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRfMcU9I8mMcBH6qiv</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRG7xQ84LQrgS4jhie</t>
         </is>
       </c>
       <c r="T198" t="inlineStr">
@@ -21974,18 +22076,18 @@
       </c>
       <c r="U198" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="V198" t="n">
         <v>3</v>
       </c>
       <c r="W198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X198" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -21995,12 +22097,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
+          <t>78efda1b-9688-4bcf-b16e-7167c17c0bcb</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a</t>
+          <t>ca-cioos_43422dc8-2573-4f60-bf87-df447d57ab7a</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -22010,7 +22112,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Bute Inlet Geohazard - Topography Surveys - 2023 - Hakai Airborne Coastal Observatory</t>
+          <t>USGS Glacier Mapping - 2023 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -22052,52 +22154,52 @@
         </is>
       </c>
       <c r="N199" t="n">
+        <v>2</v>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-121.4, 47.68], [-113.0, 47.68], [-113.0, 49.08], [-121.4, 49.08], [-121.4, 47.68]]]}</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>[{'max': '2800.0', 'min': '100.0'}]</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>10.21966/bzr6-er66</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRKhzLRiCcp6ENuX2r</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="V199" t="n">
         <v>1</v>
       </c>
-      <c r="O199" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.9, 50.53], [-124.2, 50.53], [-124.2, 50.99], [-124.9, 50.99], [-124.9, 50.53]]]}</t>
-        </is>
-      </c>
-      <c r="P199" t="inlineStr">
-        <is>
-          <t>[{'max': '2600.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q199" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R199" t="inlineStr">
-        <is>
-          <t>10.21966/e4b8-vp48</t>
-        </is>
-      </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRG7xQ84LQrgS4jhie</t>
-        </is>
-      </c>
-      <c r="T199" t="inlineStr">
-        <is>
-          <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="U199" t="inlineStr">
-        <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="V199" t="n">
-        <v>3</v>
-      </c>
       <c r="W199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X199" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -22107,12 +22209,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>78efda1b-9688-4bcf-b16e-7167c17c0bcb</t>
+          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>ca-cioos_43422dc8-2573-4f60-bf87-df447d57ab7a</t>
+          <t>ca-cioos_6756b221-28a0-4848-9761-905cbd558cd7</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -22122,7 +22224,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>USGS Glacier Mapping - 2023 - Hakai Airborne Coastal Observatory</t>
+          <t>Protistan plankton time series from the northern Salish Sea and Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -22140,12 +22242,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -22164,45 +22266,45 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-121.4, 47.68], [-113.0, 47.68], [-113.0, 49.08], [-121.4, 49.08], [-121.4, 47.68]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>[{'max': '2800.0', 'min': '100.0'}]</t>
+          <t>[{'max': '6.0', 'min': '1.0'}]</t>
         </is>
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>phytoplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>10.21966/bzr6-er66</t>
+          <t>10.21966/jv5k-3k59</t>
         </is>
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRKhzLRiCcp6ENuX2r</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-Nh8VlPQ_m681tso87Gd</t>
         </is>
       </c>
       <c r="T200" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="U200" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="V200" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W200" t="n">
         <v>0</v>
@@ -22219,12 +22321,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
+          <t>9d1749f8-9be2-468c-946e-965f92fcdc67</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>ca-cioos_6756b221-28a0-4848-9761-905cbd558cd7</t>
+          <t>ca-cioos_6e947d50-8392-42ce-bff9-24b126c7cab7</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -22234,7 +22336,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Protistan plankton time series from the northern Salish Sea and Central Coast, British Columbia, Canada</t>
+          <t>Spatial extent of eelgrass (Zostera marina) beds from monitoring sites within the greater park ecosystem of Pacific Rim National Park Reserve (2017, 2018)</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -22252,12 +22354,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore, Geospatial</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -22276,46 +22378,44 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.0511576, 48.72717181], [-124.94565833, 48.72717181], [-124.94565833, 49.24536019], [-126.0511576, 49.24536019], [-126.0511576, 48.72717181]]]}</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>[{'max': '6.0', 'min': '1.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>phytoplanktonBiomassAndDiversity</t>
+          <t>other, seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>10.21966/jv5k-3k59</t>
+          <t>10.21966/8mpe-h081</t>
         </is>
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-Nh8VlPQ_m681tso87Gd</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUR4a1V0N1UxYTc2U3Q</t>
         </is>
       </c>
       <c r="T201" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="U201" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="V201" t="n">
-        <v>4</v>
-      </c>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr"/>
       <c r="W201" t="n">
         <v>0</v>
       </c>
@@ -22331,12 +22431,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>9d1749f8-9be2-468c-946e-965f92fcdc67</t>
+          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>ca-cioos_6e947d50-8392-42ce-bff9-24b126c7cab7</t>
+          <t>ca-cioos_f25b00ba-ad63-42b3-8021-3fb6aa99baff</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -22346,12 +22446,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Spatial extent of eelgrass (Zostera marina) beds from monitoring sites within the greater park ecosystem of Pacific Rim National Park Reserve (2017, 2018)</t>
+          <t>Fraser River Landslide Project - Sites of Concern 2024</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>document</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -22364,7 +22464,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Nearshore, Geospatial</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -22384,48 +22484,50 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Hakai Geospatial</t>
         </is>
       </c>
       <c r="N202" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.0511576, 48.72717181], [-124.94565833, 48.72717181], [-124.94565833, 49.24536019], [-126.0511576, 49.24536019], [-126.0511576, 48.72717181]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.0, 49.0], [-119.5, 49.0], [-119.5, 54.34], [-124.0, 54.34], [-124.0, 49.0]]]}</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>other, seagrassCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>10.21966/8mpe-h081</t>
+          <t>10.21966/xp9x-m243</t>
         </is>
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUR4a1V0N1UxYTc2U3Q</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NTLT7n49Ox3SnVoy6nW</t>
         </is>
       </c>
       <c r="T202" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="U202" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="V202" t="inlineStr"/>
+          <t>2024-11-20</t>
+        </is>
+      </c>
+      <c r="V202" t="n">
+        <v>4</v>
+      </c>
       <c r="W202" t="n">
         <v>0</v>
       </c>
@@ -22441,12 +22543,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
+          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>ca-cioos_f25b00ba-ad63-42b3-8021-3fb6aa99baff</t>
+          <t>ca-cioos_c513de71-ac9d-43fa-b693-8f865de4b137</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -22456,12 +22558,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Fraser River Landslide Project - Sites of Concern 2024</t>
+          <t>Fraser River Landslide Project - 2022-2024 - Drone Data</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>document</t>
+          <t>dataset</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -22474,7 +22576,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -22494,7 +22596,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Hakai Geospatial</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N203" t="n">
@@ -22502,12 +22604,12 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.0, 49.0], [-119.5, 49.0], [-119.5, 54.34], [-124.0, 54.34], [-124.0, 49.0]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.8, 49.29], [-121.2, 49.29], [-121.2, 52.28], [-122.8, 52.28], [-122.8, 49.29]]]}</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>[{'max': '2500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1500.0', 'min': '50.0'}]</t>
         </is>
       </c>
       <c r="Q203" t="inlineStr">
@@ -22517,26 +22619,26 @@
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>10.21966/xp9x-m243</t>
+          <t>10.21966/qpe8-ay93</t>
         </is>
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NTLT7n49Ox3SnVoy6nW</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpurN_vwkhOgSJmgBh9</t>
         </is>
       </c>
       <c r="T203" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="U203" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="V203" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W203" t="n">
         <v>0</v>
@@ -22553,12 +22655,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
+          <t>e8414189-54c9-4311-874e-b97f9b7916ae</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>ca-cioos_c513de71-ac9d-43fa-b693-8f865de4b137</t>
+          <t>ca-cioos_48acba27-5e01-4b41-9a0e-f3fc8d809a13</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -22568,7 +22670,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Fraser River Landslide Project - 2022-2024 - Drone Data</t>
+          <t>MusselSeg: Semantic Segmentation for Rocky Intertidal Mussel Habitat</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -22586,12 +22688,12 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -22614,42 +22716,40 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.8, 49.29], [-121.2, 49.29], [-121.2, 52.28], [-122.8, 52.28], [-122.8, 49.29]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-130.1, 51.59], [-120.4, 31.75], [-118.4, 33.38], [-124.3, 44.43], [-122.0, 49.35], [-126.2, 51.59], [-130.1, 51.59]]]}</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>[{'max': '1500.0', 'min': '50.0'}]</t>
+          <t>[{'max': '75.0', 'min': '15.0'}]</t>
         </is>
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>10.21966/qpe8-ay93</t>
+          <t>10.21966/fbv4-th96</t>
         </is>
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpurN_vwkhOgSJmgBh9</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DCH8GzsQKSM8xwJ8WdQFIZrtCaq2/-O26fyGiVXoF__M22UrP</t>
         </is>
       </c>
       <c r="T204" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="U204" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="V204" t="n">
-        <v>2</v>
-      </c>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr"/>
       <c r="W204" t="n">
         <v>0</v>
       </c>
@@ -22665,12 +22765,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>e8414189-54c9-4311-874e-b97f9b7916ae</t>
+          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>ca-cioos_48acba27-5e01-4b41-9a0e-f3fc8d809a13</t>
+          <t>ca-cioos_d4942b86-d362-40a3-9399-c124c4c263bd</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -22680,7 +22780,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>MusselSeg: Semantic Segmentation for Rocky Intertidal Mussel Habitat</t>
+          <t>Larval Dungeness crab abundance and size time series along the coast of British Columbia</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -22698,7 +22798,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Sentinels of Change</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -22726,40 +22826,42 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-130.1, 51.59], [-120.4, 31.75], [-118.4, 33.38], [-124.3, 44.43], [-122.0, 49.35], [-126.2, 51.59], [-130.1, 51.59]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.8, 48.3], [-123.2, 48.37], [-123.2, 48.65], [-123.0, 48.77], [-123.3, 49.01], [-122.9, 49.25], [-122.6, 49.4], [-123.2, 49.45], [-123.7, 49.54], [-124.5, 49.89], [-124.8, 50.09], [-126.5, 50.79], [-128.3, 52.31], [-130.4, 54.75], [-133.8, 54.36], [-132.9, 52.85], [-130.3, 51.48], [-128.1, 50.15], [-125.2, 48.62], [-123.8, 48.3]]]}</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>[{'max': '75.0', 'min': '15.0'}]</t>
+          <t>[{'max': '2.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q205" t="inlineStr">
         <is>
-          <t>other, invertebrateAbundanceAndDistribution</t>
+          <t>invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>10.21966/fbv4-th96</t>
+          <t>10.21966/36hp-7f40</t>
         </is>
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DCH8GzsQKSM8xwJ8WdQFIZrtCaq2/-O26fyGiVXoF__M22UrP</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/57FPdLIBPcb9BOLfIOW44RJVywN2/-N1KAki3SSBEw0aHCoSv</t>
         </is>
       </c>
       <c r="T205" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="U205" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="V205" t="inlineStr"/>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="V205" t="n">
+        <v>2</v>
+      </c>
       <c r="W205" t="n">
         <v>0</v>
       </c>
@@ -22775,12 +22877,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
+          <t>265e0ec8-1d85-4e73-b85d-371845dbd08f</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>ca-cioos_d4942b86-d362-40a3-9399-c124c4c263bd</t>
+          <t>ca-cioos_f762a307-6dfb-41a8-a56c-ecacfb075a0a</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -22790,7 +22892,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Larval Dungeness crab abundance and size time series along the coast of British Columbia</t>
+          <t>Denali Fault - 2024 - Airborne LiDAR Survey</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -22808,12 +22910,12 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Sentinels of Change</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -22836,42 +22938,40 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.8, 48.3], [-123.2, 48.37], [-123.2, 48.65], [-123.0, 48.77], [-123.3, 49.01], [-122.9, 49.25], [-122.6, 49.4], [-123.2, 49.45], [-123.7, 49.54], [-124.5, 49.89], [-124.8, 50.09], [-126.5, 50.79], [-128.3, 52.31], [-130.4, 54.75], [-133.8, 54.36], [-132.9, 52.85], [-130.3, 51.48], [-128.1, 50.15], [-125.2, 48.62], [-123.8, 48.3]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-141.3, 62.08], [-139.8, 61.49], [-137.7, 60.61], [-136.8, 60.1], [-136.4, 60.29], [-138.3, 61.12], [-140.1, 61.86], [-141.2, 62.19], [-141.3, 62.08]]]}</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>[{'max': '2.0', 'min': '0.0'}]</t>
+          <t>[{'max': '5000.0', 'min': '100.0'}]</t>
         </is>
       </c>
       <c r="Q206" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>10.21966/36hp-7f40</t>
+          <t>10.21966/wxph-tz51</t>
         </is>
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/57FPdLIBPcb9BOLfIOW44RJVywN2/-N1KAki3SSBEw0aHCoSv</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCKOQlOxJdTg_BFOoXb</t>
         </is>
       </c>
       <c r="T206" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="U206" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="V206" t="n">
-        <v>2</v>
-      </c>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr"/>
       <c r="W206" t="n">
         <v>0</v>
       </c>
@@ -22887,12 +22987,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>265e0ec8-1d85-4e73-b85d-371845dbd08f</t>
+          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>ca-cioos_f762a307-6dfb-41a8-a56c-ecacfb075a0a</t>
+          <t>ca-cioos_5185ac00-8148-4472-adfd-21741d8a10ce</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -22902,7 +23002,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Denali Fault - 2024 - Airborne LiDAR Survey</t>
+          <t>Sentinels of Change Sea Surface Temperature Time Series Data Along the British Columbia Coast</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -22920,12 +23020,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Sentinels of Change</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -22948,46 +23048,48 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-141.3, 62.08], [-139.8, 61.49], [-137.7, 60.61], [-136.8, 60.1], [-136.4, 60.29], [-138.3, 61.12], [-140.1, 61.86], [-141.2, 62.19], [-141.3, 62.08]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.6, 48.25], [-123.2, 48.37], [-123.3, 48.71], [-123.0, 48.8], [-123.3, 49.09], [-123.0, 49.1], [-122.4, 49.39], [-122.6, 49.56], [-123.6, 49.55], [-124.8, 50.1], [-125.8, 50.51], [-127.5, 51.15], [-128.6, 52.64], [-130.4, 54.77], [-133.4, 54.37], [-132.8, 52.99], [-130.8, 51.58], [-128.3, 50.21], [-126.5, 49.17], [-125.2, 48.63], [-124.3, 48.43], [-123.6, 48.25]]]}</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>[{'max': '5000.0', 'min': '100.0'}]</t>
+          <t>[{'max': '0.5', 'min': '0.5'}]</t>
         </is>
       </c>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>seaSurfaceTemperature</t>
         </is>
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>10.21966/wxph-tz51</t>
+          <t>10.21966/4kr2-jc55</t>
         </is>
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCKOQlOxJdTg_BFOoXb</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/57FPdLIBPcb9BOLfIOW44RJVywN2/-NH0r8ddHNhVJ5bXkyqR</t>
         </is>
       </c>
       <c r="T207" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="U207" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="V207" t="inlineStr"/>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="V207" t="n">
+        <v>2</v>
+      </c>
       <c r="W207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X207" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2024', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -22997,12 +23099,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
+          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>ca-cioos_5185ac00-8148-4472-adfd-21741d8a10ce</t>
+          <t>ca-cioos_7fd3ec6c-083a-4942-84b4-215e69492072</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -23012,7 +23114,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Sentinels of Change Sea Surface Temperature Time Series Data Along the British Columbia Coast</t>
+          <t>Phytoplankton Pigment Timeseries from High-Performance Liquid Chromatography for the Northern Salish Sea and Central Coast, BC, Canada (Research)</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -23030,7 +23132,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Sentinels of Change</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -23058,32 +23160,32 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.6, 48.25], [-123.2, 48.37], [-123.3, 48.71], [-123.0, 48.8], [-123.3, 49.09], [-123.0, 49.1], [-122.4, 49.39], [-122.6, 49.56], [-123.6, 49.55], [-124.8, 50.1], [-125.8, 50.51], [-127.5, 51.15], [-128.6, 52.64], [-130.4, 54.77], [-133.4, 54.37], [-132.8, 52.99], [-130.8, 51.58], [-128.3, 50.21], [-126.5, 49.17], [-125.2, 48.63], [-124.3, 48.43], [-123.6, 48.25]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>[{'max': '0.5', 'min': '0.5'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q208" t="inlineStr">
         <is>
-          <t>seaSurfaceTemperature</t>
+          <t>phytoplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>10.21966/4kr2-jc55</t>
+          <t>10.21966/bw2d-tg65</t>
         </is>
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/57FPdLIBPcb9BOLfIOW44RJVywN2/-NH0r8ddHNhVJ5bXkyqR</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-O25qzW3OpioeACGpRHl</t>
         </is>
       </c>
       <c r="T208" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="U208" t="inlineStr">
@@ -23095,11 +23197,11 @@
         <v>2</v>
       </c>
       <c r="W208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X208" t="inlineStr">
         <is>
-          <t>[{'year': '2024', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -23109,12 +23211,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
+          <t>0781c19a-7efb-4680-92fd-8cd5faf0cfe4</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>ca-cioos_7fd3ec6c-083a-4942-84b4-215e69492072</t>
+          <t>ca-cioos_af344fb9-4901-470c-a441-41f11ee2ccd7</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -23124,7 +23226,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Phytoplankton Pigment Timeseries from High-Performance Liquid Chromatography for the Northern Salish Sea and Central Coast, BC, Canada (Research)</t>
+          <t>iTrack Oysters February 2023 Experiment - Environmental and Oyster Health Data</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -23142,12 +23244,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Wet Lab</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -23162,7 +23264,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N209" t="n">
@@ -23170,42 +23272,40 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q209" t="inlineStr">
         <is>
-          <t>phytoplanktonBiomassAndDiversity</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>10.21966/bw2d-tg65</t>
+          <t>10.21966/pvy6-nw38</t>
         </is>
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-O25qzW3OpioeACGpRHl</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-O0G3gSlISPfB-f0u3Zz</t>
         </is>
       </c>
       <c r="T209" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="U209" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="V209" t="n">
-        <v>2</v>
-      </c>
+          <t>2024-12-19</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr"/>
       <c r="W209" t="n">
         <v>0</v>
       </c>
@@ -23221,12 +23321,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>0781c19a-7efb-4680-92fd-8cd5faf0cfe4</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>ca-cioos_af344fb9-4901-470c-a441-41f11ee2ccd7</t>
+          <t>ca-cioos_9fafb4c8-e61f-4372-ac71-c1ddbe57d80c</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -23236,7 +23336,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>iTrack Oysters February 2023 Experiment - Environmental and Oyster Health Data</t>
+          <t>Data record does not exist anymore: Geomorphology - Calvert Island</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -23252,11 +23352,7 @@
       <c r="H210" t="b">
         <v>0</v>
       </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>Wet Lab</t>
-        </is>
-      </c>
+      <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr">
         <is>
           <t>completed</t>
@@ -23274,7 +23370,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N210" t="n">
@@ -23282,48 +23378,40 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.2489013671875, 51.40605940499276], [-127.83142089843751, 51.40605940499276], [-127.83142089843751, 51.75934048406748], [-128.2489013671875, 51.75934048406748], [-128.2489013671875, 51.40605940499276]]]}</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q210" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
-        </is>
-      </c>
-      <c r="R210" t="inlineStr">
-        <is>
-          <t>10.21966/pvy6-nw38</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr"/>
       <c r="S210" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-O0G3gSlISPfB-f0u3Zz</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OFhFpUJDNDF0hlFiGUV</t>
         </is>
       </c>
       <c r="T210" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="U210" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
-        </is>
-      </c>
-      <c r="V210" t="inlineStr"/>
-      <c r="W210" t="n">
-        <v>0</v>
-      </c>
-      <c r="X210" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>2025-01-03</t>
+        </is>
+      </c>
+      <c r="V210" t="n">
+        <v>4</v>
+      </c>
+      <c r="W210" t="inlineStr"/>
+      <c r="X210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -23331,12 +23419,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>ca-cioos_9fafb4c8-e61f-4372-ac71-c1ddbe57d80c</t>
+          <t>ca-cioos_d7ffd737-5725-4a56-9134-a9ad91c2734d</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -23346,7 +23434,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Data record does not exist anymore: Geomorphology - Calvert Island</t>
+          <t>Seton and Anderson Lake Multibeam Survey - 2024 - British Columbia</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -23362,7 +23450,11 @@
       <c r="H211" t="b">
         <v>0</v>
       </c>
-      <c r="I211" t="inlineStr"/>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Geospatial</t>
+        </is>
+      </c>
       <c r="J211" t="inlineStr">
         <is>
           <t>completed</t>
@@ -23388,12 +23480,12 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.2489013671875, 51.40605940499276], [-127.83142089843751, 51.40605940499276], [-127.83142089843751, 51.75934048406748], [-128.2489013671875, 51.75934048406748], [-128.2489013671875, 51.40605940499276]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.4, 50.62], [-122.0, 50.62], [-122.0, 50.75], [-122.4, 50.75], [-122.4, 50.62]]]}</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
+          <t>[{'max': '254.0', 'min': '61.0'}]</t>
         </is>
       </c>
       <c r="Q211" t="inlineStr">
@@ -23401,27 +23493,37 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R211" t="inlineStr"/>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>10.21966/zfxe-rd73</t>
+        </is>
+      </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OFhFpUJDNDF0hlFiGUV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCe-GBA4i93dk_I9uOR</t>
         </is>
       </c>
       <c r="T211" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="U211" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="V211" t="n">
-        <v>4</v>
-      </c>
-      <c r="W211" t="inlineStr"/>
-      <c r="X211" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W211" t="n">
+        <v>0</v>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -23429,12 +23531,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
+          <t>4a949e26-fe94-4f63-a3c6-a62e19301102</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>ca-cioos_d7ffd737-5725-4a56-9134-a9ad91c2734d</t>
+          <t>ca-cioos_35beb32e-8dc9-42ab-9630-2ae23e414026</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -23444,7 +23546,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Seton and Anderson Lake Multibeam Survey - 2024 - British Columbia</t>
+          <t>Rocky Subtidal Fish and Invertebrate Community Surveys from the Central Coast of BC</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -23462,12 +23564,12 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -23490,37 +23592,37 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.4, 50.62], [-122.0, 50.62], [-122.0, 50.75], [-122.4, 50.75], [-122.4, 50.62]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.7, 51.35], [-127.3, 51.35], [-127.3, 52.27], [-128.7, 52.27], [-128.7, 51.35]]]}</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>[{'max': '254.0', 'min': '61.0'}]</t>
+          <t>[{'max': '15.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q212" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>10.21966/zfxe-rd73</t>
+          <t>10.21966/jj9p-d309</t>
         </is>
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCe-GBA4i93dk_I9uOR</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtF5vh1GUMdwtJdYjoJ</t>
         </is>
       </c>
       <c r="T212" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="U212" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="V212" t="n">
@@ -23541,12 +23643,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>4a949e26-fe94-4f63-a3c6-a62e19301102</t>
+          <t>7fa8cfec-e2e3-4459-9b9d-836335b9fcfa</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>ca-cioos_35beb32e-8dc9-42ab-9630-2ae23e414026</t>
+          <t>ca-cioos_00f42725-0a88-4d4f-87a9-4e359d2abff4</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -23556,7 +23658,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Rocky Subtidal Fish and Invertebrate Community Surveys from the Central Coast of BC</t>
+          <t>Knight Inlet Remotely Operated Vehicle Marine Habitat Survey</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -23574,12 +23676,12 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -23602,42 +23704,40 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.7, 51.35], [-127.3, 51.35], [-127.3, 52.27], [-128.7, 52.27], [-128.7, 51.35]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.0, 50.65], [-125.9, 50.65], [-125.9, 50.71], [-126.0, 50.71], [-126.0, 50.65]]]}</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>[{'max': '15.0', 'min': '0.0'}]</t>
+          <t>[{'max': '105.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q213" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>10.21966/jj9p-d309</t>
+          <t>10.21966/529y-sh57</t>
         </is>
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtF5vh1GUMdwtJdYjoJ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OG736nDr1-1b51V4ZIc</t>
         </is>
       </c>
       <c r="T213" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="U213" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
-        </is>
-      </c>
-      <c r="V213" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr"/>
       <c r="W213" t="n">
         <v>0</v>
       </c>
@@ -23653,12 +23753,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>7fa8cfec-e2e3-4459-9b9d-836335b9fcfa</t>
+          <t>5576c279-6d3a-4323-8104-0e1040d9906c</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>ca-cioos_00f42725-0a88-4d4f-87a9-4e359d2abff4</t>
+          <t>ca-cioos_314a0846-0fe9-4c2e-81e2-d2b24ac98b6e</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -23668,7 +23768,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Knight Inlet Remotely Operated Vehicle Marine Habitat Survey</t>
+          <t>Understory kelp biomass data from BC Central Coast</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -23686,12 +23786,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -23714,37 +23814,37 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.0, 50.65], [-125.9, 50.65], [-125.9, 50.71], [-126.0, 50.71], [-126.0, 50.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.7, 51.33], [-127.4, 51.33], [-127.4, 52.26], [-128.7, 52.26], [-128.7, 51.33]]]}</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>[{'max': '105.0', 'min': '0.0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q214" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>10.21966/529y-sh57</t>
+          <t>10.21966/wmsy-5g39</t>
         </is>
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OG736nDr1-1b51V4ZIc</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtGQFN6AV5bNminNtYH</t>
         </is>
       </c>
       <c r="T214" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="U214" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="V214" t="inlineStr"/>
@@ -23763,12 +23863,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>5576c279-6d3a-4323-8104-0e1040d9906c</t>
+          <t>cc016896-78d9-46e8-887d-6c1dd106c0e8</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>ca-cioos_314a0846-0fe9-4c2e-81e2-d2b24ac98b6e</t>
+          <t>ca-cioos_52d4f546-dfdf-4bf1-b1ad-f6ec6f2663c0</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -23778,7 +23878,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Understory kelp biomass data from BC Central Coast</t>
+          <t>Bute Inlet Geo-Hazards &amp; Ramsay West - 2024 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -23796,12 +23896,12 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -23824,40 +23924,42 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.7, 51.33], [-127.4, 51.33], [-127.4, 52.26], [-128.7, 52.26], [-128.7, 51.33]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.5, 50.23], [-124.1, 50.23], [-124.1, 51.73], [-125.5, 51.73], [-125.5, 50.23]]]}</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q215" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>10.21966/wmsy-5g39</t>
+          <t>10.21966/8yp1-7m94</t>
         </is>
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtGQFN6AV5bNminNtYH</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCKR1jead4rZb1ooVa6</t>
         </is>
       </c>
       <c r="T215" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="U215" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="V215" t="inlineStr"/>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="V215" t="n">
+        <v>1</v>
+      </c>
       <c r="W215" t="n">
         <v>0</v>
       </c>
@@ -23873,12 +23975,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>cc016896-78d9-46e8-887d-6c1dd106c0e8</t>
+          <t>046e5ef5-1480-4868-a65f-23171088bdb8</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>ca-cioos_52d4f546-dfdf-4bf1-b1ad-f6ec6f2663c0</t>
+          <t>ca-cioos_31e15496-e906-43f4-9120-2446ab6125b2</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -23888,7 +23990,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Bute Inlet Geo-Hazards &amp; Ramsay West - 2024 - Airborne Coastal Observatory</t>
+          <t>Elliot Creek Aerial Photo and LiDAR Survey</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -23906,7 +24008,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -23934,12 +24036,12 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.5, 50.23], [-124.1, 50.23], [-124.1, 51.73], [-125.5, 51.73], [-125.5, 50.23]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.8, 50.84], [-124.5, 50.84], [-124.5, 50.99], [-124.8, 50.99], [-124.8, 50.84]]]}</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>[{'max': '2500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2650.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q216" t="inlineStr">
@@ -23949,27 +24051,25 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>10.21966/8yp1-7m94</t>
+          <t>10.21966/g64t-ec45</t>
         </is>
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCKR1jead4rZb1ooVa6</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICfZ5e-2vhf5NUtDZS</t>
         </is>
       </c>
       <c r="T216" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="U216" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="V216" t="n">
-        <v>1</v>
-      </c>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr"/>
       <c r="W216" t="n">
         <v>0</v>
       </c>
@@ -23985,12 +24085,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>046e5ef5-1480-4868-a65f-23171088bdb8</t>
+          <t>8ce79018-75da-42f8-b7cd-195a412ab532</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>ca-cioos_31e15496-e906-43f4-9120-2446ab6125b2</t>
+          <t>ca-cioos_98807d0a-ba68-41e3-a2f5-e3248b459904</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -24000,7 +24100,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Elliot Creek Aerial Photo and LiDAR Survey</t>
+          <t>Place Glacier Aerial Photo and LiDAR Survey</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -24038,7 +24138,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Tula Foundation</t>
         </is>
       </c>
       <c r="N217" t="n">
@@ -24046,12 +24146,12 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.8, 50.84], [-124.5, 50.84], [-124.5, 50.99], [-124.8, 50.99], [-124.8, 50.84]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.7, 50.39], [-122.6, 50.39], [-122.6, 50.48], [-122.7, 50.48], [-122.7, 50.39]]]}</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>[{'max': '2650.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2587.0', 'min': '500.0'}]</t>
         </is>
       </c>
       <c r="Q217" t="inlineStr">
@@ -24061,12 +24161,12 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>10.21966/g64t-ec45</t>
+          <t>10.21966/0ydj-0t79</t>
         </is>
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICfZ5e-2vhf5NUtDZS</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICMGpnoARQcIltW087</t>
         </is>
       </c>
       <c r="T217" t="inlineStr">
@@ -24095,12 +24195,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>8ce79018-75da-42f8-b7cd-195a412ab532</t>
+          <t>83f387d2-f77e-4921-af15-e064d87ad01a</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>ca-cioos_98807d0a-ba68-41e3-a2f5-e3248b459904</t>
+          <t>ca-cioos_53730b70-be6f-4e24-8b9d-4a5e2c491121</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -24110,12 +24210,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Place Glacier Aerial Photo and LiDAR Survey</t>
+          <t>Cloud-Based LiDAR Application - ELVIZ - Place Glacier, Mt. Robson, and Elliot Creek, BC</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>service</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -24148,7 +24248,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Tula Foundation</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N218" t="n">
@@ -24156,12 +24256,12 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.7, 50.39], [-122.6, 50.39], [-122.6, 50.48], [-122.7, 50.48], [-122.7, 50.39]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.5, 50.34], [-118.7, 50.34], [-118.7, 53.28], [-124.5, 53.28], [-124.5, 50.34]]]}</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>[{'max': '2587.0', 'min': '500.0'}]</t>
+          <t>[{'max': '3954.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q218" t="inlineStr">
@@ -24171,25 +24271,27 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>10.21966/0ydj-0t79</t>
+          <t>10.21966/6x1v-1v62</t>
         </is>
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICMGpnoARQcIltW087</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OIMCEnEEW63IyHyYZOM</t>
         </is>
       </c>
       <c r="T218" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="U218" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="V218" t="inlineStr"/>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="V218" t="n">
+        <v>2</v>
+      </c>
       <c r="W218" t="n">
         <v>0</v>
       </c>
@@ -24205,12 +24307,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>83f387d2-f77e-4921-af15-e064d87ad01a</t>
+          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>ca-cioos_53730b70-be6f-4e24-8b9d-4a5e2c491121</t>
+          <t>ca-cioos_78818ed7-ec26-4004-afa1-137741ddda1e</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -24220,12 +24322,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Cloud-Based LiDAR Application - ELVIZ - Place Glacier, Mt. Robson, and Elliot Creek, BC</t>
+          <t>Calliarthron 2023 Experiment - Environmental Data</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>dataset</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -24238,7 +24340,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Wet Lab</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -24258,7 +24360,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="N219" t="n">
@@ -24266,37 +24368,37 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.5, 50.34], [-118.7, 50.34], [-118.7, 53.28], [-124.5, 53.28], [-124.5, 50.34]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>[{'max': '3954.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q219" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>10.21966/6x1v-1v62</t>
+          <t>10.21966/7nwn-bj60</t>
         </is>
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OIMCEnEEW63IyHyYZOM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-O6XAwxhj0r9Xs-V2QSA</t>
         </is>
       </c>
       <c r="T219" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="U219" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="V219" t="n">
@@ -24317,12 +24419,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
+          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>ca-cioos_78818ed7-ec26-4004-afa1-137741ddda1e</t>
+          <t>ca-cioos_87341cb3-f906-4fa5-973c-b6742aa0fbb5</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -24332,7 +24434,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Calliarthron 2023 Experiment - Environmental Data</t>
+          <t>Glacier and Ice Aerial Surveys in British Columbia - 2023-2024 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -24350,7 +24452,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Wet Lab</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -24370,7 +24472,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>University of British Columbia</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N220" t="n">
@@ -24378,27 +24480,27 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.9, 48.81], [-115.2, 48.81], [-115.2, 54.38], [-128.9, 54.38], [-128.9, 48.81]]]}</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '3954.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q220" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>10.21966/7nwn-bj60</t>
+          <t>10.21966/ks82-th39</t>
         </is>
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-O6XAwxhj0r9Xs-V2QSA</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OP2QaXeKeZ30lz51gEE</t>
         </is>
       </c>
       <c r="T220" t="inlineStr">
@@ -24408,11 +24510,11 @@
       </c>
       <c r="U220" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="V220" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W220" t="n">
         <v>0</v>
@@ -24429,12 +24531,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
+          <t>6c99bd67-3be1-4818-bf01-dfa56e910db3</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>ca-cioos_87341cb3-f906-4fa5-973c-b6742aa0fbb5</t>
+          <t>ca-cioos_96e3dd9c-7863-44d5-95cd-a3d0a8653d83</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -24444,7 +24546,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Glacier and Ice Aerial Surveys in British Columbia - 2023-2024 - Hakai Airborne Coastal Observatory</t>
+          <t>Glacier and Ice Aerial Surveys in British Columbia - 2022 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -24462,7 +24564,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -24490,12 +24592,12 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.9, 48.81], [-115.2, 48.81], [-115.2, 54.38], [-128.9, 54.38], [-128.9, 48.81]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.8, 48.1], [-113.1, 48.1], [-113.1, 56.61], [-127.8, 56.61], [-127.8, 48.1]]]}</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>[{'max': '3954.0', 'min': '0.0'}]</t>
+          <t>[{'max': '4000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q221" t="inlineStr">
@@ -24505,12 +24607,12 @@
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>10.21966/ks82-th39</t>
+          <t>10.21966/n3b4-d226</t>
         </is>
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OP2QaXeKeZ30lz51gEE</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NM0zdQjdjAMBZ4cN8ou</t>
         </is>
       </c>
       <c r="T221" t="inlineStr">
@@ -24520,18 +24622,18 @@
       </c>
       <c r="U221" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="V221" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W221" t="n">
         <v>0</v>
       </c>
       <c r="X221" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2025', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -24541,12 +24643,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>6c99bd67-3be1-4818-bf01-dfa56e910db3</t>
+          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>ca-cioos_96e3dd9c-7863-44d5-95cd-a3d0a8653d83</t>
+          <t>ca-cioos_47d8bdd4-c815-4e8d-8d75-53a9db4ae46a</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -24556,7 +24658,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Glacier and Ice Aerial Surveys in British Columbia - 2022 - Hakai Airborne Coastal Observatory</t>
+          <t>Glaciers in Western North America Mass Loss Geospatial Data (2021-2024)</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -24602,12 +24704,12 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.8, 48.1], [-113.1, 48.1], [-113.1, 56.61], [-127.8, 56.61], [-127.8, 48.1]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.3, 54.17], [-119.5, 55.38], [-112.5, 52.06], [-115.3, 47.05], [-125.9, 48.0], [-128.3, 51.41], [-127.3, 54.17]]]}</t>
         </is>
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>[{'max': '4000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2822.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q222" t="inlineStr">
@@ -24617,33 +24719,33 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>10.21966/n3b4-d226</t>
+          <t>10.21966/p6jv-pe95</t>
         </is>
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NM0zdQjdjAMBZ4cN8ou</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OP86akjVj471Wit4O2y</t>
         </is>
       </c>
       <c r="T222" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="U222" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="V222" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W222" t="n">
         <v>0</v>
       </c>
       <c r="X222" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -24653,12 +24755,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
+          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>ca-cioos_47d8bdd4-c815-4e8d-8d75-53a9db4ae46a</t>
+          <t>ca-cioos_1d142201-cbbe-4c58-b2c2-1feeac112c51</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -24668,7 +24770,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Glaciers in Western North America Mass Loss Geospatial Data (2021-2024)</t>
+          <t>iTrack Oysters September 2023 Experiment - Environmental and Oyster Health Data</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -24686,7 +24788,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Wet Lab</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -24706,7 +24808,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N223" t="n">
@@ -24714,41 +24816,41 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.3, 54.17], [-119.5, 55.38], [-112.5, 52.06], [-115.3, 47.05], [-125.9, 48.0], [-128.3, 51.41], [-127.3, 54.17]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>[{'max': '2822.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q223" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>inorganicCarbon, other</t>
         </is>
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>10.21966/p6jv-pe95</t>
+          <t>10.21966/q1m4-pz94</t>
         </is>
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OP86akjVj471Wit4O2y</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-OMsFWHXIwEWiFjwQeEo</t>
         </is>
       </c>
       <c r="T223" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="U223" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="V223" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W223" t="n">
         <v>0</v>
@@ -24765,12 +24867,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
+          <t>da040f55-984d-490d-b917-a67856de4bac</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>ca-cioos_1d142201-cbbe-4c58-b2c2-1feeac112c51</t>
+          <t>ca-cioos_31ac855d-bf15-42d8-b20d-754638202c66</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -24780,7 +24882,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>iTrack Oysters September 2023 Experiment - Environmental and Oyster Health Data</t>
+          <t>Sea Stars 2024 Experiment - Environmental Data</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -24818,7 +24920,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N224" t="n">
@@ -24841,12 +24943,12 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>10.21966/q1m4-pz94</t>
+          <t>10.21966/jkf5-ss08</t>
         </is>
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-OMsFWHXIwEWiFjwQeEo</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-OIMW8OO0buhOm_kHuIz</t>
         </is>
       </c>
       <c r="T224" t="inlineStr">
@@ -24877,12 +24979,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>da040f55-984d-490d-b917-a67856de4bac</t>
+          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>ca-cioos_31ac855d-bf15-42d8-b20d-754638202c66</t>
+          <t>ca-cioos_d959f8f3-6d20-42fe-94da-be49bcd3aeca</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -24892,7 +24994,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Sea Stars 2024 Experiment - Environmental Data</t>
+          <t>Eelgrass (Z. marina) extent at Gulf Islands National Park Reserve eelgrass monitoring sites (2024)</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -24910,7 +25012,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Wet Lab</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -24930,15 +25032,15 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Gulf Islands National Park Reserve</t>
         </is>
       </c>
       <c r="N225" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.4, 48.61], [-123.0, 48.61], [-123.0, 48.87], [-123.4, 48.87], [-123.4, 48.61]]]}</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
@@ -24948,31 +25050,31 @@
       </c>
       <c r="Q225" t="inlineStr">
         <is>
-          <t>inorganicCarbon, other</t>
+          <t>other, seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>10.21966/jkf5-ss08</t>
+          <t>10.21966/x3jm-p494</t>
         </is>
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-OIMW8OO0buhOm_kHuIz</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OUG8anVj4yBJDEHy6Wj</t>
         </is>
       </c>
       <c r="T225" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="U225" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="V225" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W225" t="n">
         <v>0</v>
@@ -24989,12 +25091,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>ca-cioos_d959f8f3-6d20-42fe-94da-be49bcd3aeca</t>
+          <t>ca-cioos_39a83551-ab8e-45be-a564-cece4b229371</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -25004,7 +25106,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Eelgrass (Z. marina) extent at Gulf Islands National Park Reserve eelgrass monitoring sites (2024)</t>
+          <t>Zooplankton taxonomic abundance and biomass along the BC Coast</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -25022,12 +25124,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -25042,7 +25144,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Gulf Islands National Park Reserve</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N226" t="n">
@@ -25050,48 +25152,48 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.4, 48.61], [-123.0, 48.61], [-123.0, 48.87], [-123.4, 48.87], [-123.4, 48.61]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '350.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q226" t="inlineStr">
         <is>
-          <t>other, seagrassCoverAndComposition</t>
+          <t>zooplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>10.21966/x3jm-p494</t>
+          <t>10.21966/g7zf-1v08</t>
         </is>
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OUG8anVj4yBJDEHy6Wj</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-ODO1YbIGbR3Rd8hvLxT</t>
         </is>
       </c>
       <c r="T226" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="U226" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="V226" t="n">
+        <v>4</v>
+      </c>
+      <c r="W226" t="n">
         <v>2</v>
       </c>
-      <c r="W226" t="n">
-        <v>0</v>
-      </c>
       <c r="X226" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2025', 'total': 2}]</t>
         </is>
       </c>
     </row>
@@ -25101,12 +25203,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>ca-cioos_39a83551-ab8e-45be-a564-cece4b229371</t>
+          <t>ca-cioos_dbb33efe-c207-4d9c-abef-2350595bf47a</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -25116,7 +25218,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Zooplankton taxonomic abundance and biomass along the BC Coast</t>
+          <t>Size-fractionated zooplankton biomass and isotopes along the BC coast</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -25158,45 +25260,45 @@
         </is>
       </c>
       <c r="N227" t="n">
+        <v>1</v>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>[{'max': '350.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>zooplanktonBiomassAndDiversity</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>10.21966/tcp2-mm86</t>
+        </is>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/NZb1YZT9Xtbc9Cp9Jc3OtSLRffT2/-OQtxgedRzyaVsL4bWUx</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="V227" t="n">
         <v>2</v>
-      </c>
-      <c r="O227" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
-        </is>
-      </c>
-      <c r="P227" t="inlineStr">
-        <is>
-          <t>[{'max': '350.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q227" t="inlineStr">
-        <is>
-          <t>zooplanktonBiomassAndDiversity</t>
-        </is>
-      </c>
-      <c r="R227" t="inlineStr">
-        <is>
-          <t>10.21966/g7zf-1v08</t>
-        </is>
-      </c>
-      <c r="S227" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-ODO1YbIGbR3Rd8hvLxT</t>
-        </is>
-      </c>
-      <c r="T227" t="inlineStr">
-        <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="U227" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="V227" t="n">
-        <v>4</v>
       </c>
       <c r="W227" t="n">
         <v>2</v>
@@ -25213,12 +25315,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
+          <t>328b062b-3af6-4149-b90f-a85b99dc40eb</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>ca-cioos_dbb33efe-c207-4d9c-abef-2350595bf47a</t>
+          <t>ca-cioos_34a20547-cb60-4ecf-901b-f4ca52eae451</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -25228,7 +25330,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Size-fractionated zooplankton biomass and isotopes along the BC coast</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -25246,12 +25348,12 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -25274,48 +25376,48 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.4], [-127.9, 51.4], [-127.9, 52.09], [-128.5, 52.09], [-128.5, 51.4]]]}</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>[{'max': '350.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q228" t="inlineStr">
         <is>
-          <t>zooplanktonBiomassAndDiversity</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>10.21966/tcp2-mm86</t>
+          <t>10.21966/w08z-zk15</t>
         </is>
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/NZb1YZT9Xtbc9Cp9Jc3OtSLRffT2/-OQtxgedRzyaVsL4bWUx</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8sPFZem68YnizN7L7l</t>
         </is>
       </c>
       <c r="T228" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="U228" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="V228" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W228" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X228" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 2}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -25325,12 +25427,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>328b062b-3af6-4149-b90f-a85b99dc40eb</t>
+          <t>439d703a-2132-4dbd-8d39-a4cacdb8f81d</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>ca-cioos_34a20547-cb60-4ecf-901b-f4ca52eae451</t>
+          <t>ca-cioos_e8343aa0-dbea-4267-9f78-662bec08d4bc</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -25340,7 +25442,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), Central Coast, British Columbia, Canada</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020-2022), Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -25358,7 +25460,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
+          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -25386,7 +25488,7 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.4], [-127.9, 51.4], [-127.9, 52.09], [-128.5, 52.09], [-128.5, 51.4]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 52.15], [-128.5, 52.23], [-128.2, 52.05], [-128.0, 51.71], [-128.0, 51.63], [-128.2, 51.62], [-128.4, 51.8], [-128.6, 51.89], [-128.6, 51.89], [-128.6, 52.15]]]}</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -25401,12 +25503,12 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>10.21966/w08z-zk15</t>
+          <t>10.21966/kqzp-f639</t>
         </is>
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8sPFZem68YnizN7L7l</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-NbzgAmVWcvz-_SOMA0E</t>
         </is>
       </c>
       <c r="T229" t="inlineStr">
@@ -25416,12 +25518,10 @@
       </c>
       <c r="U229" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="V229" t="n">
-        <v>1</v>
-      </c>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr"/>
       <c r="W229" t="n">
         <v>0</v>
       </c>
@@ -25437,12 +25537,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>439d703a-2132-4dbd-8d39-a4cacdb8f81d</t>
+          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>ca-cioos_e8343aa0-dbea-4267-9f78-662bec08d4bc</t>
+          <t>ca-cioos_f7a867ce-0f18-43f6-8148-775235d800b6</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -25452,7 +25552,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020-2022), Central Coast, British Columbia, Canada</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2023), Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -25470,7 +25570,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -25498,7 +25598,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 52.15], [-128.5, 52.23], [-128.2, 52.05], [-128.0, 51.71], [-128.0, 51.63], [-128.2, 51.62], [-128.4, 51.8], [-128.6, 51.89], [-128.6, 51.89], [-128.6, 52.15]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.64], [-128.1, 51.64], [-128.1, 52.19], [-128.6, 52.19], [-128.6, 51.64]]]}</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -25513,12 +25613,12 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>10.21966/kqzp-f639</t>
+          <t>10.21966/qs1b-g693</t>
         </is>
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-NbzgAmVWcvz-_SOMA0E</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-O8Dvx_fnz1WMY_Wetch</t>
         </is>
       </c>
       <c r="T230" t="inlineStr">
@@ -25528,10 +25628,12 @@
       </c>
       <c r="U230" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="V230" t="inlineStr"/>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="V230" t="n">
+        <v>3</v>
+      </c>
       <c r="W230" t="n">
         <v>0</v>
       </c>
@@ -25547,12 +25649,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
+          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>ca-cioos_f7a867ce-0f18-43f6-8148-775235d800b6</t>
+          <t>ca-cioos_291b98a4-d868-462c-852a-d6cf79ecf6ce</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -25562,7 +25664,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2023), Central Coast, British Columbia, Canada</t>
+          <t>Time series of surface kelp canopy area derived from remotely piloted aerial systems (RPAS, or drone) surveys, Central Coast, British Columbia</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -25580,12 +25682,12 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
+          <t>Nearshore, Geospatial</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -25600,7 +25702,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Tula Foundation</t>
         </is>
       </c>
       <c r="N231" t="n">
@@ -25608,7 +25710,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.64], [-128.1, 51.64], [-128.1, 52.19], [-128.6, 52.19], [-128.6, 51.64]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.65], [-128.1, 51.65], [-128.1, 52.09], [-128.4, 52.09], [-128.4, 51.65]]]}</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
@@ -25623,26 +25725,26 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>10.21966/qs1b-g693</t>
+          <t>10.21966/9cbv-ra30</t>
         </is>
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-O8Dvx_fnz1WMY_Wetch</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OVIwXhdGT9n7FV0wmyz</t>
         </is>
       </c>
       <c r="T231" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="U231" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="V231" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W231" t="n">
         <v>0</v>
@@ -25659,12 +25761,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
+          <t>44bdc298-1329-400a-bc02-4d35d251865d</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>ca-cioos_291b98a4-d868-462c-852a-d6cf79ecf6ce</t>
+          <t>ca-cioos_012164c6-28dd-4078-b702-f0c2ce63d548</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -25674,7 +25776,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Time series of surface kelp canopy area derived from remotely piloted aerial systems (RPAS, or drone) surveys, Central Coast, British Columbia</t>
+          <t>Biodiversity and Oceanographic data from the False Creek Bioblitz, 2022</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -25692,12 +25794,12 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Nearshore, Geospatial</t>
+          <t>Genomics, Nearshore, Oceanography</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -25712,50 +25814,48 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Tula Foundation</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N232" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.65], [-128.1, 51.65], [-128.1, 52.09], [-128.4, 52.09], [-128.4, 51.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.2, 49.27], [-123.1, 49.27], [-123.1, 49.28], [-123.2, 49.28], [-123.2, 49.27]]]}</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q232" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>invertebrateAbundanceAndDistribution, marineTurtlesBirdsMammalsAbundanceAndDistribution, fishAbundanceAndDistribution, seaSurfaceTemperature, subSurfaceTemperature, other, microbeBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>10.21966/9cbv-ra30</t>
+          <t>10.21966/8sgn-jg38</t>
         </is>
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OVIwXhdGT9n7FV0wmyz</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-Nd0YqVrleM4mMLlJDSU</t>
         </is>
       </c>
       <c r="T232" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="U232" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="V232" t="n">
-        <v>2</v>
-      </c>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr"/>
       <c r="W232" t="n">
         <v>0</v>
       </c>
@@ -25771,12 +25871,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>44bdc298-1329-400a-bc02-4d35d251865d</t>
+          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>ca-cioos_012164c6-28dd-4078-b702-f0c2ce63d548</t>
+          <t>ca-cioos_7e9c97a3-4bf1-4852-81b6-d74cedf2c94c</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -25786,7 +25886,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Biodiversity and Oceanographic data from the False Creek Bioblitz, 2022</t>
+          <t>Environmental DNA survey of Calvert Island, British Columbia, 2021</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -25804,7 +25904,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Genomics, Nearshore, Oceanography</t>
+          <t>Genomics</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -25828,44 +25928,46 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.2, 49.27], [-123.1, 49.27], [-123.1, 49.28], [-123.2, 49.28], [-123.2, 49.27]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.31], [-127.3, 51.31], [-127.3, 52.05], [-128.6, 52.05], [-128.6, 51.31]]]}</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '60.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q233" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution, marineTurtlesBirdsMammalsAbundanceAndDistribution, fishAbundanceAndDistribution, seaSurfaceTemperature, subSurfaceTemperature, other, microbeBiomassAndDiversity</t>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>10.21966/8sgn-jg38</t>
+          <t>10.21966/vdyq-r660</t>
         </is>
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-Nd0YqVrleM4mMLlJDSU</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-ORCQx4QHUuJ1NV1SEig</t>
         </is>
       </c>
       <c r="T233" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="U233" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="V233" t="inlineStr"/>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="V233" t="n">
+        <v>2</v>
+      </c>
       <c r="W233" t="n">
         <v>0</v>
       </c>
@@ -25881,12 +25983,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
+          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>ca-cioos_7e9c97a3-4bf1-4852-81b6-d74cedf2c94c</t>
+          <t>ca-cioos_9a018fe0-8bd1-41d1-af8d-079960b71473</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -25896,7 +25998,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Environmental DNA survey of Calvert Island, British Columbia, 2021</t>
+          <t>Data from: Prentice et al. 2025. Vibrio pectenicida strain FHCF-3 is a causative agent of sea star wasting disease</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -25914,7 +26016,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>Genomics</t>
+          <t>Genomics, Nearshore</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -25938,45 +26040,45 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.31], [-127.3, 51.31], [-127.3, 52.05], [-128.6, 52.05], [-128.6, 51.31]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 47.91], [-122.3, 47.91], [-122.3, 51.82], [-128.5, 51.82], [-128.5, 47.91]]]}</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>[{'max': '60.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q234" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
+          <t>microbeBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>10.21966/vdyq-r660</t>
+          <t>10.21966/4dvn-5y90</t>
         </is>
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-ORCQx4QHUuJ1NV1SEig</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/24mf0TP0vkh6bmNOOA3ynoTFPNJ2/-OX0Xm6VoYH22oc68Jfp</t>
         </is>
       </c>
       <c r="T234" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="U234" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="V234" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W234" t="n">
         <v>0</v>
@@ -25993,12 +26095,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
+          <t>0272fd06-6ac8-48cd-80c9-b6e05f15be0f</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>ca-cioos_9a018fe0-8bd1-41d1-af8d-079960b71473</t>
+          <t>ca-cioos_132cecdf-de8a-4b17-b610-0e2b3a343812</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -26008,7 +26110,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Data from: Prentice et al. 2025. Vibrio pectenicida strain FHCF-3 is a causative agent of sea star wasting disease</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), North Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -26026,7 +26128,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Genomics, Nearshore</t>
+          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -26050,11 +26152,11 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 47.91], [-122.3, 47.91], [-122.3, 51.82], [-128.5, 51.82], [-128.5, 47.91]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-131.0, 53.74], [-130.4, 53.74], [-130.4, 54.46], [-131.0, 54.46], [-131.0, 53.74]]]}</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
@@ -26064,27 +26166,27 @@
       </c>
       <c r="Q235" t="inlineStr">
         <is>
-          <t>microbeBiomassAndDiversity</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>10.21966/4dvn-5y90</t>
+          <t>10.21966/m93t-4181</t>
         </is>
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/24mf0TP0vkh6bmNOOA3ynoTFPNJ2/-OX0Xm6VoYH22oc68Jfp</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8sPEiAvbPxw16A-L6I</t>
         </is>
       </c>
       <c r="T235" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="U235" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="V235" t="n">
@@ -26105,12 +26207,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>0272fd06-6ac8-48cd-80c9-b6e05f15be0f</t>
+          <t>b01f58f7-1518-4829-aff6-ac4a8f2c0616</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>ca-cioos_132cecdf-de8a-4b17-b610-0e2b3a343812</t>
+          <t>ca-cioos_f815a700-c943-4d6f-afeb-a4854ad10cfc</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -26120,7 +26222,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), North Coast, British Columbia, Canada</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), North Vancouver Island, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -26166,7 +26268,7 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-131.0, 53.74], [-130.4, 53.74], [-130.4, 54.46], [-131.0, 54.46], [-131.0, 53.74]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.6, 50.35], [-124.8, 50.35], [-124.8, 50.7], [-126.6, 50.7], [-126.6, 50.35]]]}</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
@@ -26181,12 +26283,12 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>10.21966/m93t-4181</t>
+          <t>10.21966/ntdg-e790</t>
         </is>
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8sPEiAvbPxw16A-L6I</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8raBb8T2xZJ-oRzesS</t>
         </is>
       </c>
       <c r="T236" t="inlineStr">
@@ -26217,12 +26319,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>b01f58f7-1518-4829-aff6-ac4a8f2c0616</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>ca-cioos_f815a700-c943-4d6f-afeb-a4854ad10cfc</t>
+          <t>ca-cioos_5b4cbe9f-8f2e-414c-80ff-741372891fe9</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -26232,7 +26334,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), North Vancouver Island, British Columbia, Canada</t>
+          <t>Gitga'at Territory Coastal Monitoring and Mapping - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -26242,7 +26344,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>CC-BY-4.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H237" t="b">
@@ -26250,7 +26352,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -26278,48 +26380,48 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.6, 50.35], [-124.8, 50.35], [-124.8, 50.7], [-126.6, 50.7], [-126.6, 50.35]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.8, 52.92], [-129.1, 52.92], [-129.1, 53.67], [-129.8, 53.67], [-129.8, 52.92]]]}</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '475.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q237" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>10.21966/ntdg-e790</t>
+          <t>10.21966/0xex-r023</t>
         </is>
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8raBb8T2xZJ-oRzesS</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OdPFhWCkXwvqjCqum30</t>
         </is>
       </c>
       <c r="T237" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="U237" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="V237" t="n">
+        <v>3</v>
+      </c>
+      <c r="W237" t="n">
         <v>1</v>
       </c>
-      <c r="W237" t="n">
-        <v>0</v>
-      </c>
       <c r="X237" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2025', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -26329,12 +26431,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>0074861a-39f2-42c1-ae71-abef4f78fd78</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>ca-cioos_5b4cbe9f-8f2e-414c-80ff-741372891fe9</t>
+          <t>ca-cioos_b5f0f854-efe1-4132-808d-074244d813e1</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -26344,7 +26446,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Gitga'at Territory Coastal Monitoring and Mapping - Airborne Coastal Observatory</t>
+          <t>Gitga'at Territory Coastal Mapping Project</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -26362,12 +26464,12 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -26390,12 +26492,12 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.8, 52.92], [-129.1, 52.92], [-129.1, 53.67], [-129.8, 53.67], [-129.8, 52.92]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.6, 53.18], [-129.0, 53.18], [-129.0, 53.68], [-129.6, 53.68], [-129.6, 53.18]]]}</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>[{'max': '475.0', 'min': '0.0'}]</t>
+          <t>[{'max': '150.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q238" t="inlineStr">
@@ -26405,12 +26507,12 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>10.21966/0xex-r023</t>
+          <t>10.21966/2aap-hn61</t>
         </is>
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OdPFhWCkXwvqjCqum30</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Oa5tvTh2mXFQbI3SkzK</t>
         </is>
       </c>
       <c r="T238" t="inlineStr">
@@ -26420,18 +26522,18 @@
       </c>
       <c r="U238" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="V238" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W238" t="n">
         <v>1</v>
       </c>
       <c r="X238" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 1}]</t>
+          <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -26441,12 +26543,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>0074861a-39f2-42c1-ae71-abef4f78fd78</t>
+          <t>5fc21b4d-2dfa-4908-8aaf-90a82509324a</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>ca-cioos_b5f0f854-efe1-4132-808d-074244d813e1</t>
+          <t>ca-cioos_35900174-c64a-493e-9a7e-390ac7e997e4</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -26456,7 +26558,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Gitga'at Territory Coastal Mapping Project</t>
+          <t>Bowhead Whale Drone Data Collection - Cumberland Sound - Nunavut</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -26466,7 +26568,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="H239" t="b">
@@ -26479,7 +26581,7 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -26502,12 +26604,12 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.6, 53.18], [-129.0, 53.18], [-129.0, 53.68], [-129.6, 53.68], [-129.6, 53.18]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-68.21, 64.72], [-64.14, 64.72], [-64.14, 66.48], [-68.21, 66.48], [-68.21, 64.72]]]}</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>[{'max': '150.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q239" t="inlineStr">
@@ -26517,22 +26619,22 @@
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>10.21966/2aap-hn61</t>
+          <t>10.21966/fv0q-q364</t>
         </is>
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Oa5tvTh2mXFQbI3SkzK</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OeY_smu3pJj8TBE9ivK</t>
         </is>
       </c>
       <c r="T239" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="U239" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="V239" t="n">
@@ -26553,12 +26655,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>5fc21b4d-2dfa-4908-8aaf-90a82509324a</t>
+          <t>dbfc5189-f657-4034-af7f-cc358042047d</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>ca-cioos_35900174-c64a-493e-9a7e-390ac7e997e4</t>
+          <t>ca-cioos_78686602-1aa9-4246-8a24-915471fe4255</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -26568,7 +26670,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Bowhead Whale Drone Data Collection - Cumberland Sound - Nunavut</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2025), North Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -26586,7 +26688,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -26614,7 +26716,7 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-68.21, 64.72], [-64.14, 64.72], [-64.14, 66.48], [-68.21, 66.48], [-68.21, 64.72]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.8, 52.69], [-129.0, 52.69], [-129.0, 53.14], [-129.8, 53.14], [-129.8, 52.69]]]}</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
@@ -26624,17 +26726,17 @@
       </c>
       <c r="Q240" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>10.21966/fv0q-q364</t>
+          <t>10.21966/nwg7-fe05</t>
         </is>
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OeY_smu3pJj8TBE9ivK</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OeItznXpvEFI_t-jsCl</t>
         </is>
       </c>
       <c r="T240" t="inlineStr">
@@ -26644,18 +26746,16 @@
       </c>
       <c r="U240" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="V240" t="n">
-        <v>1</v>
-      </c>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="V240" t="inlineStr"/>
       <c r="W240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X240" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -26665,12 +26765,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>dbfc5189-f657-4034-af7f-cc358042047d</t>
+          <t>9eda1bfc-0d13-4e1d-9542-b9a7cce16991</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>ca-cioos_78686602-1aa9-4246-8a24-915471fe4255</t>
+          <t>ca-cioos_c544ef5b-967d-46b2-bbcf-395116b50e7d</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -26680,7 +26780,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2025), North Coast, British Columbia, Canada</t>
+          <t>Mystery Creek Aerial Photo and LiDAR Survey - 2025 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -26698,7 +26798,7 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -26726,32 +26826,32 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.8, 52.69], [-129.0, 52.69], [-129.0, 53.14], [-129.8, 53.14], [-129.8, 52.69]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.9, 50.21], [-122.8, 50.21], [-122.8, 50.25], [-122.9, 50.25], [-122.9, 50.21]]]}</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '1690.0', 'min': '378.0'}]</t>
         </is>
       </c>
       <c r="Q241" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>10.21966/nwg7-fe05</t>
+          <t>10.21966/02qp-4945</t>
         </is>
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OeItznXpvEFI_t-jsCl</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/FfIFMI0sx4beFpYCFD9liFIEiMt1/-OeTbb0MbfTCH-YFCNGG</t>
         </is>
       </c>
       <c r="T241" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="U241" t="inlineStr">
@@ -26775,12 +26875,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>9eda1bfc-0d13-4e1d-9542-b9a7cce16991</t>
+          <t>37440dfd-53f8-462b-a544-b6c8d39c44cd</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>ca-cioos_c544ef5b-967d-46b2-bbcf-395116b50e7d</t>
+          <t>ca-cioos_43bad5e5-0484-4c11-80a5-c844245f940e</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -26790,7 +26890,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Mystery Creek Aerial Photo and LiDAR Survey - 2025 - Airborne Coastal Observatory</t>
+          <t>Farwell Canyon Airborne Surveys - 2024 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -26836,12 +26936,12 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.9, 50.21], [-122.8, 50.21], [-122.8, 50.25], [-122.9, 50.25], [-122.9, 50.21]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.6, 51.86], [-122.5, 51.81], [-122.4, 51.74], [-122.4, 51.73], [-122.5, 51.8], [-122.7, 51.83], [-122.6, 51.86]]]}</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>[{'max': '1690.0', 'min': '378.0'}]</t>
+          <t>[{'max': '1347.62', 'min': '345.9'}]</t>
         </is>
       </c>
       <c r="Q242" t="inlineStr">
@@ -26851,22 +26951,22 @@
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>10.21966/02qp-4945</t>
+          <t>10.21966/dtt0-s264</t>
         </is>
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/FfIFMI0sx4beFpYCFD9liFIEiMt1/-OeTbb0MbfTCH-YFCNGG</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/FfIFMI0sx4beFpYCFD9liFIEiMt1/-OgDkxI9LmB0KWXvOsZe</t>
         </is>
       </c>
       <c r="T242" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="U242" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="V242" t="inlineStr"/>
@@ -26885,12 +26985,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>37440dfd-53f8-462b-a544-b6c8d39c44cd</t>
+          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>ca-cioos_43bad5e5-0484-4c11-80a5-c844245f940e</t>
+          <t>ca-cioos_7cafde4f-bdd5-4b95-a41d-7939ddcf08c6</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -26900,7 +27000,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Farwell Canyon Airborne Surveys - 2024 - Airborne Coastal Observatory</t>
+          <t>Time series of quarterly kelp canopy extent from Landsat 5, 7, 8, and 9 since 1985</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -26918,12 +27018,12 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -26946,40 +27046,42 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.6, 51.86], [-122.5, 51.81], [-122.4, 51.74], [-122.4, 51.73], [-122.5, 51.8], [-122.7, 51.83], [-122.6, 51.86]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-130.5, 54.75], [-133.5, 54.36], [-133.0, 53.09], [-126.0, 48.92], [-123.6, 48.28], [-123.2, 48.8], [-123.8, 49.61], [-127.6, 51.04], [-128.4, 52.4], [-130.4, 54.24], [-130.5, 54.75]]]}</t>
         </is>
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>[{'max': '1347.62', 'min': '345.9'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q243" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>10.21966/dtt0-s264</t>
+          <t>10.21966/xc7x-9207</t>
         </is>
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/FfIFMI0sx4beFpYCFD9liFIEiMt1/-OgDkxI9LmB0KWXvOsZe</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OZGbDlZ5dgF0dD-ceZ7</t>
         </is>
       </c>
       <c r="T243" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="U243" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
-      <c r="V243" t="inlineStr"/>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="V243" t="n">
+        <v>2</v>
+      </c>
       <c r="W243" t="n">
         <v>0</v>
       </c>
@@ -26995,12 +27097,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
+          <t>3d082072-1ee8-4005-8bba-f9ec795ad5ab</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>ca-cioos_7cafde4f-bdd5-4b95-a41d-7939ddcf08c6</t>
+          <t>ca-cioos_cfa4ad65-ee12-47c0-9527-206a0f8d92ae</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -27010,7 +27112,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Time series of quarterly kelp canopy extent from Landsat 5, 7, 8, and 9 since 1985</t>
+          <t>Hakai Institute Drone Data Index</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -27028,7 +27130,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -27056,42 +27158,40 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-130.5, 54.75], [-133.5, 54.36], [-133.0, 53.09], [-126.0, 48.92], [-123.6, 48.28], [-123.2, 48.8], [-123.8, 49.61], [-127.6, 51.04], [-128.4, 52.4], [-130.4, 54.24], [-130.5, 54.75]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-134.1, 42.65], [-59.42, 42.65], [-59.42, 67.53], [-134.1, 67.53], [-134.1, 42.65]]]}</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>10.21966/xc7x-9207</t>
+          <t>10.21966/0r8b-t282</t>
         </is>
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OZGbDlZ5dgF0dD-ceZ7</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCdraToZivfj6ZZ8TqZ</t>
         </is>
       </c>
       <c r="T244" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="U244" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="V244" t="n">
-        <v>2</v>
-      </c>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr"/>
       <c r="W244" t="n">
         <v>0</v>
       </c>
@@ -27107,12 +27207,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>3d082072-1ee8-4005-8bba-f9ec795ad5ab</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>ca-cioos_cfa4ad65-ee12-47c0-9527-206a0f8d92ae</t>
+          <t>ca-cioos_a924b31b-9882-4abe-8d8e-e875dbbbec82</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -27122,7 +27222,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Hakai Institute Drone Data Index</t>
+          <t>Surface Seawater and Marine Boundary Layer CO2 Time Series from the Bute Inlet Ocean Observing Station (BIOOS) Buoy, Bute Inlet, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -27140,7 +27240,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -27158,58 +27258,46 @@
           <t>dataset</t>
         </is>
       </c>
-      <c r="M245" t="inlineStr">
-        <is>
-          <t>Hakai Institute</t>
-        </is>
-      </c>
+      <c r="M245" t="inlineStr"/>
       <c r="N245" t="n">
         <v>1</v>
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-134.1, 42.65], [-59.42, 42.65], [-59.42, 67.53], [-134.1, 67.53], [-134.1, 42.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976]]]}</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q245" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R245" t="inlineStr">
-        <is>
-          <t>10.21966/0r8b-t282</t>
-        </is>
-      </c>
+          <t>inorganicCarbon, oxygen, seaSurfaceSalinity, seaSurfaceTemperature</t>
+        </is>
+      </c>
+      <c r="R245" t="inlineStr"/>
       <c r="S245" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCdraToZivfj6ZZ8TqZ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-OlwZ9MM8a9VqCYIJo4W</t>
         </is>
       </c>
       <c r="T245" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="U245" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="V245" t="inlineStr"/>
-      <c r="W245" t="n">
-        <v>0</v>
-      </c>
-      <c r="X245" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="V245" t="n">
+        <v>4</v>
+      </c>
+      <c r="W245" t="inlineStr"/>
+      <c r="X245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -27217,12 +27305,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>0894f661-f9cb-48cb-a0b4-8a001eb69420</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>ca-cioos_a924b31b-9882-4abe-8d8e-e875dbbbec82</t>
+          <t>ca-cioos_bfefcdf9-c922-4e4f-a958-aa6da739d3cd</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -27232,7 +27320,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Surface Seawater and Marine Boundary Layer CO2 Time Series from the Bute Inlet Ocean Observing Station (BIOOS) Buoy, Bute Inlet, BC, Canada (Provisional)</t>
+          <t>Surface Seawater and Marine Boundary Layer CO2 Time Series from the Bute Inlet Ocean Observing Station (BIOOS) Buoy, Bute Inlet, BC, Canada (Research)</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -27268,7 +27356,11 @@
           <t>dataset</t>
         </is>
       </c>
-      <c r="M246" t="inlineStr"/>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
       <c r="N246" t="n">
         <v>1</v>
       </c>
@@ -27284,13 +27376,17 @@
       </c>
       <c r="Q246" t="inlineStr">
         <is>
-          <t>inorganicCarbon, oxygen, seaSurfaceSalinity, seaSurfaceTemperature</t>
-        </is>
-      </c>
-      <c r="R246" t="inlineStr"/>
+          <t>oxygen, inorganicCarbon, particulateMatter, phytoplanktonBiomassAndDiversity, seaSurfaceSalinity, seaSurfaceTemperature</t>
+        </is>
+      </c>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>10.21966/4jvz-bv44</t>
+        </is>
+      </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-OlwZ9MM8a9VqCYIJo4W</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-OOYvTmfsWUPdHkDTTFS</t>
         </is>
       </c>
       <c r="T246" t="inlineStr">
@@ -27300,14 +27396,18 @@
       </c>
       <c r="U246" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="V246" t="n">
-        <v>4</v>
-      </c>
-      <c r="W246" t="inlineStr"/>
-      <c r="X246" t="inlineStr"/>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr"/>
+      <c r="W246" t="n">
+        <v>0</v>
+      </c>
+      <c r="X246" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -27315,12 +27415,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>0894f661-f9cb-48cb-a0b4-8a001eb69420</t>
+          <t>e788c2f6-c842-4240-bab4-54a323d62174</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>ca-cioos_bfefcdf9-c922-4e4f-a958-aa6da739d3cd</t>
+          <t>ca-cioos_984e6b72-15d0-4742-bb2d-9ac13b14383a</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -27330,7 +27430,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Surface Seawater and Marine Boundary Layer CO2 Time Series from the Bute Inlet Ocean Observing Station (BIOOS) Buoy, Bute Inlet, BC, Canada (Research)</t>
+          <t>Stream Temperature Observations for Three Streams Near Gold River</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -27348,12 +27448,12 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -27376,7 +27476,7 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.7, 49.96], [-125.9, 49.93], [-126.0, 49.56], [-126.7, 49.73], [-126.7, 49.96]]]}</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
@@ -27386,27 +27486,27 @@
       </c>
       <c r="Q247" t="inlineStr">
         <is>
-          <t>oxygen, inorganicCarbon, particulateMatter, phytoplanktonBiomassAndDiversity, seaSurfaceSalinity, seaSurfaceTemperature</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>10.21966/4jvz-bv44</t>
+          <t>10.21966/cqrt-sk09</t>
         </is>
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-OOYvTmfsWUPdHkDTTFS</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DvuBcQQuVHdxmYEF4yDNBDj30lu1/-Oj8Fegu6V858hz57O8z</t>
         </is>
       </c>
       <c r="T247" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="V247" t="inlineStr"/>
@@ -27425,12 +27525,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>e788c2f6-c842-4240-bab4-54a323d62174</t>
+          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>ca-cioos_984e6b72-15d0-4742-bb2d-9ac13b14383a</t>
+          <t>ca-cioos_84820f31-b6db-479c-a47e-f22f2899b4d2</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -27440,7 +27540,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Stream Temperature Observations for Three Streams Near Gold River</t>
+          <t>Biogeochemical Sampling of 28 Streams on Vancouver Island</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -27486,7 +27586,7 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.7, 49.96], [-125.9, 49.93], [-126.0, 49.56], [-126.7, 49.73], [-126.7, 49.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 50.65], [-127.9, 50.71], [-123.6, 48.43], [-124.0, 48.36], [-127.3, 49.77], [-128.4, 50.65]]]}</t>
         </is>
       </c>
       <c r="P248" t="inlineStr">
@@ -27501,31 +27601,33 @@
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>10.21966/cqrt-sk09</t>
+          <t>10.21966/chc3-rj93</t>
         </is>
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DvuBcQQuVHdxmYEF4yDNBDj30lu1/-Oj8Fegu6V858hz57O8z</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DvuBcQQuVHdxmYEF4yDNBDj30lu1/-OnCm7wniBlFr2gSXQhf</t>
         </is>
       </c>
       <c r="T248" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="V248" t="inlineStr"/>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="V248" t="n">
+        <v>3</v>
+      </c>
       <c r="W248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X248" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -27535,12 +27637,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
+          <t>63f6c693-7c22-49cc-ad7d-9aa1774a5972</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>ca-cioos_84820f31-b6db-479c-a47e-f22f2899b4d2</t>
+          <t>ca-cioos_d7b34963-67bc-404b-bdd1-b41cc750bdaa</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -27550,7 +27652,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Biogeochemical Sampling of 28 Streams on Vancouver Island</t>
+          <t>Fraser River Airborne Surveys - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -27568,7 +27670,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -27596,12 +27698,12 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 50.65], [-127.9, 50.71], [-123.6, 48.43], [-124.0, 48.36], [-127.3, 49.77], [-128.4, 50.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-121.5, 49.51], [-121.3, 49.53], [-121.4, 49.95], [-121.5, 50.28], [-121.7, 50.52], [-121.8, 50.66], [-121.8, 50.76], [-121.8, 51.01], [-122.1, 51.32], [-122.3, 51.79], [-122.1, 52.11], [-122.3, 52.37], [-122.3, 52.51], [-122.6, 52.49], [-122.4, 51.96], [-122.5, 51.83], [-122.4, 51.49], [-122.3, 51.18], [-121.9, 50.95], [-121.9, 50.62], [-121.8, 50.53], [-121.7, 50.17], [-121.6, 49.89], [-121.5, 49.63], [-121.5, 49.51]]]}</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '850.0', 'min': '400.0'}]</t>
         </is>
       </c>
       <c r="Q249" t="inlineStr">
@@ -27611,33 +27713,31 @@
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>10.21966/chc3-rj93</t>
+          <t>10.21966/f9m6-qg12</t>
         </is>
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DvuBcQQuVHdxmYEF4yDNBDj30lu1/-OnCm7wniBlFr2gSXQhf</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MibW0TZpoaJ4Ih_2ev7</t>
         </is>
       </c>
       <c r="T249" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="U249" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="V249" t="n">
-        <v>3</v>
-      </c>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr"/>
       <c r="W249" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X249" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -27647,12 +27747,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>63f6c693-7c22-49cc-ad7d-9aa1774a5972</t>
+          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>ca-cioos_d7b34963-67bc-404b-bdd1-b41cc750bdaa</t>
+          <t>ca-cioos_1efbadd2-e735-48cc-9498-e3a5a88e48a6</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -27662,7 +27762,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Fraser River Airborne Surveys - 2020 - Airborne Coastal Observatory</t>
+          <t>Seawater Carbon Dioxide (CO2) Content from the SuperCO2 System in the Pacific Ecosystem Autonomous Research Laboratory, Bamfield Marine Sciences Centre, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -27680,12 +27780,12 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -27704,44 +27804,46 @@
         </is>
       </c>
       <c r="N250" t="n">
+        <v>2</v>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359]]]}</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>[{'max': '0', 'min': '0'}]</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>inorganicCarbon, seaSurfaceSalinity, seaSurfaceTemperature</t>
+        </is>
+      </c>
+      <c r="R250" t="inlineStr">
+        <is>
+          <t>10.21966/a0v4-x512</t>
+        </is>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-Olwvch3kCplJcz3CCeR</t>
+        </is>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="V250" t="n">
         <v>1</v>
       </c>
-      <c r="O250" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-121.5, 49.51], [-121.3, 49.53], [-121.4, 49.95], [-121.5, 50.28], [-121.7, 50.52], [-121.8, 50.66], [-121.8, 50.76], [-121.8, 51.01], [-122.1, 51.32], [-122.3, 51.79], [-122.1, 52.11], [-122.3, 52.37], [-122.3, 52.51], [-122.6, 52.49], [-122.4, 51.96], [-122.5, 51.83], [-122.4, 51.49], [-122.3, 51.18], [-121.9, 50.95], [-121.9, 50.62], [-121.8, 50.53], [-121.7, 50.17], [-121.6, 49.89], [-121.5, 49.63], [-121.5, 49.51]]]}</t>
-        </is>
-      </c>
-      <c r="P250" t="inlineStr">
-        <is>
-          <t>[{'max': '850.0', 'min': '400.0'}]</t>
-        </is>
-      </c>
-      <c r="Q250" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R250" t="inlineStr">
-        <is>
-          <t>10.21966/f9m6-qg12</t>
-        </is>
-      </c>
-      <c r="S250" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MibW0TZpoaJ4Ih_2ev7</t>
-        </is>
-      </c>
-      <c r="T250" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="U250" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="V250" t="inlineStr"/>
       <c r="W250" t="n">
         <v>0</v>
       </c>
@@ -27757,12 +27859,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
+          <t>7b1120bc-4a2c-432c-9e54-879d66751a59</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>ca-cioos_1efbadd2-e735-48cc-9498-e3a5a88e48a6</t>
+          <t>ca-cioos_b2b18171-35b6-4345-b81b-497a90c2e7c5</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -27772,7 +27874,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Seawater Carbon Dioxide (CO2) Content from the SuperCO2 System in the Pacific Ecosystem Autonomous Research Laboratory, Bamfield Marine Sciences Centre, BC, Canada (Provisional)</t>
+          <t>Seagrass fish and macroinvertebrate swaths BC Central Coast</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -27790,7 +27892,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -27814,31 +27916,31 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 52.09], [-128.5, 52.04], [-128.5, 51.97], [-128.5, 51.93], [-128.5, 51.9], [-128.4, 51.88], [-128.3, 51.86], [-128.3, 51.83], [-128.2, 51.63], [-127.9, 51.62], [-127.8, 51.77], [-127.8, 51.83], [-127.9, 51.99], [-128.4, 52.09]]]}</t>
         </is>
       </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '10.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q251" t="inlineStr">
         <is>
-          <t>inorganicCarbon, seaSurfaceSalinity, seaSurfaceTemperature</t>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>10.21966/a0v4-x512</t>
+          <t>10.21966/NMNG-SF35</t>
         </is>
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-Olwvch3kCplJcz3CCeR</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/lJHlH9nm20QQOPuk217xLlxWbNv1/-NPt7327bul36pby-Odi</t>
         </is>
       </c>
       <c r="T251" t="inlineStr">
@@ -27848,12 +27950,10 @@
       </c>
       <c r="U251" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="V251" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr"/>
       <c r="W251" t="n">
         <v>0</v>
       </c>
@@ -27869,12 +27969,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>7b1120bc-4a2c-432c-9e54-879d66751a59</t>
+          <t>49374495-400f-4acc-aac6-d7d0b7cae297</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>ca-cioos_b2b18171-35b6-4345-b81b-497a90c2e7c5</t>
+          <t>ca-cioos_bafcd0eb-8249-471b-b93b-0797cfeea287</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -27884,7 +27984,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Seagrass fish and macroinvertebrate swaths BC Central Coast</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020), Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -27902,12 +28002,12 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
@@ -27930,37 +28030,37 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 52.09], [-128.5, 52.04], [-128.5, 51.97], [-128.5, 51.93], [-128.5, 51.9], [-128.4, 51.88], [-128.3, 51.86], [-128.3, 51.83], [-128.2, 51.63], [-127.9, 51.62], [-127.8, 51.77], [-127.8, 51.83], [-127.9, 51.99], [-128.4, 52.09]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.64], [-128.1, 51.64], [-128.1, 52.01], [-128.5, 52.01], [-128.5, 51.64]]]}</t>
         </is>
       </c>
       <c r="P252" t="inlineStr">
         <is>
-          <t>[{'max': '10.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q252" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
+          <t>macroalgalCanopyCoverAndComposition, other</t>
         </is>
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>10.21966/NMNG-SF35</t>
+          <t>10.21966/20ym-8826</t>
         </is>
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/lJHlH9nm20QQOPuk217xLlxWbNv1/-NPt7327bul36pby-Odi</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Miha19AtLQ2u1uo0b_q</t>
         </is>
       </c>
       <c r="T252" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="U252" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="V252" t="inlineStr"/>
@@ -27979,12 +28079,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>49374495-400f-4acc-aac6-d7d0b7cae297</t>
+          <t>613ba2f9-b21d-445f-8eaa-f42950c9350b</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>ca-cioos_bafcd0eb-8249-471b-b93b-0797cfeea287</t>
+          <t>ca-cioos_ba41d935-f293-447f-be3d-7098e569b431</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -27994,7 +28094,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020), Central Coast, British Columbia, Canada</t>
+          <t>Water Property Measurements from Conductivity-Temperature-Depth Profiles, BC, Canada (Research)</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -28012,12 +28112,12 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
+          <t>Oceanography, Nearshore, Watersheds, Juvenile Salmon Program</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
@@ -28036,41 +28136,41 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.64], [-128.1, 51.64], [-128.1, 52.01], [-128.5, 52.01], [-128.5, 51.64]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '700.0', 'min': '1.0'}]</t>
         </is>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition, other</t>
+          <t>oxygen, subSurfaceSalinity, subSurfaceTemperature</t>
         </is>
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>10.21966/20ym-8826</t>
+          <t>10.21966/kace-2d24</t>
         </is>
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Miha19AtLQ2u1uo0b_q</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MX35qgX-BrwJDdeJKe1</t>
         </is>
       </c>
       <c r="T253" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="U253" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="V253" t="inlineStr"/>
@@ -28089,12 +28189,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>613ba2f9-b21d-445f-8eaa-f42950c9350b</t>
+          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>ca-cioos_ba41d935-f293-447f-be3d-7098e569b431</t>
+          <t>ca-cioos_fb5c9e1e-a911-46b7-8c1d-e34215a105ed</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -28104,7 +28204,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Water Property Measurements from Conductivity-Temperature-Depth Profiles, BC, Canada (Research)</t>
+          <t>Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 Analyzer located at Bamfield Marine Sciences Centre, Bamfield, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -28122,7 +28222,7 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>Oceanography, Nearshore, Watersheds, Juvenile Salmon Program</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -28146,31 +28246,31 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.13535, 48.83515]}</t>
         </is>
       </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>[{'max': '700.0', 'min': '1.0'}]</t>
+          <t>[{'max': '20.0', 'min': '20.0'}]</t>
         </is>
       </c>
       <c r="Q254" t="inlineStr">
         <is>
-          <t>oxygen, subSurfaceSalinity, subSurfaceTemperature</t>
+          <t>seaSurfaceTemperature, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
         </is>
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>10.21966/kace-2d24</t>
+          <t>10.21966/65d8-k051</t>
         </is>
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MX35qgX-BrwJDdeJKe1</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-NdH-jgHZQzKrYdb2nw_</t>
         </is>
       </c>
       <c r="T254" t="inlineStr">
@@ -28180,10 +28280,12 @@
       </c>
       <c r="U254" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="V254" t="inlineStr"/>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="V254" t="n">
+        <v>1</v>
+      </c>
       <c r="W254" t="n">
         <v>0</v>
       </c>
@@ -28199,12 +28301,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>ca-cioos_fb5c9e1e-a911-46b7-8c1d-e34215a105ed</t>
+          <t>ca-cioos_91107fce-93a4-4bc9-bce4-e7d9e1cf02a0</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -28214,7 +28316,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 Analyzer located at Bamfield Marine Sciences Centre, Bamfield, BC, Canada (Provisional)</t>
+          <t>Sentinel 3A and 3B Chlorophyll and Suspended Matter Concentrations for Coastal British Columbia and Southeast Alaska, 8-Day Average (Research)</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -28260,41 +28362,41 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.13535, 48.83515]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-139.0, 47.0], [-121.5, 47.0], [-121.5, 59.5], [-139.0, 59.5], [-139.0, 47.0]]]}</t>
         </is>
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>[{'max': '20.0', 'min': '20.0'}]</t>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q255" t="inlineStr">
         <is>
-          <t>seaSurfaceTemperature, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
+          <t>phytoplanktonBiomassAndDiversity, particulateMatter, other</t>
         </is>
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>10.21966/65d8-k051</t>
+          <t>10.21966/175j-8k96</t>
         </is>
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-NdH-jgHZQzKrYdb2nw_</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-Nueis-TZEnz_78f8PYf</t>
         </is>
       </c>
       <c r="T255" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="U255" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="V255" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W255" t="n">
         <v>0</v>
@@ -28311,12 +28413,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>b7b923ed-b3fa-48b3-878d-40a3797046bc</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>ca-cioos_91107fce-93a4-4bc9-bce4-e7d9e1cf02a0</t>
+          <t>ca-cioos_f7538807-4d49-4ed8-ad36-836c0e71428a</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -28326,7 +28428,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Sentinel 3A and 3B Chlorophyll and Suspended Matter Concentrations for Coastal British Columbia and Southeast Alaska, 8-Day Average (Research)</t>
+          <t>3m Digital Elevation Model - Calvert Island - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -28344,12 +28446,12 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -28368,52 +28470,50 @@
         </is>
       </c>
       <c r="N256" t="n">
+        <v>2</v>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.16482, 51.408116], [-127.868831, 51.408116], [-127.868831, 51.734994], [-128.16482, 51.734994], [-128.16482, 51.408116]]]}</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t>10.21966/RZVW-4A72</t>
+        </is>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW13R3BBSGRER2ZkYnM</t>
+        </is>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr"/>
+      <c r="W256" t="n">
         <v>1</v>
       </c>
-      <c r="O256" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-139.0, 47.0], [-121.5, 47.0], [-121.5, 59.5], [-139.0, 59.5], [-139.0, 47.0]]]}</t>
-        </is>
-      </c>
-      <c r="P256" t="inlineStr">
-        <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q256" t="inlineStr">
-        <is>
-          <t>phytoplanktonBiomassAndDiversity, particulateMatter, other</t>
-        </is>
-      </c>
-      <c r="R256" t="inlineStr">
-        <is>
-          <t>10.21966/175j-8k96</t>
-        </is>
-      </c>
-      <c r="S256" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-Nueis-TZEnz_78f8PYf</t>
-        </is>
-      </c>
-      <c r="T256" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="U256" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="V256" t="n">
-        <v>4</v>
-      </c>
-      <c r="W256" t="n">
-        <v>0</v>
-      </c>
       <c r="X256" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -28423,12 +28523,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>b7b923ed-b3fa-48b3-878d-40a3797046bc</t>
+          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>ca-cioos_f7538807-4d49-4ed8-ad36-836c0e71428a</t>
+          <t>ca-cioos_33c8ce77-0674-4933-a305-01a25d253f70</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -28438,7 +28538,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>3m Digital Elevation Model - Calvert Island - British Columbia - Canada</t>
+          <t>Sea star microbiome data from 16S amplicon sequencing associated with rocky intertidal sites on Calvert and Quadra Islands</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -28456,7 +28556,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Nearshore, Genomics</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -28484,46 +28584,48 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.16482, 51.408116], [-127.868831, 51.408116], [-127.868831, 51.734994], [-128.16482, 51.734994], [-128.16482, 51.408116]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.3, 49.87], [-124.8, 49.87], [-124.8, 51.75], [-128.3, 51.75], [-128.3, 49.87]]]}</t>
         </is>
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q257" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>invertebrateAbundanceAndDistribution, microbeBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>10.21966/RZVW-4A72</t>
+          <t>10.21966/0xvh-1318</t>
         </is>
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW13R3BBSGRER2ZkYnM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/4TvAwNKXC7PkAi0TEZsZbbAzXfi1/-Oo1MBmr8fW1fputdBh6</t>
         </is>
       </c>
       <c r="T257" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="U257" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="V257" t="inlineStr"/>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="V257" t="n">
+        <v>2</v>
+      </c>
       <c r="W257" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X257" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -28533,12 +28635,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
+          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>ca-cioos_33c8ce77-0674-4933-a305-01a25d253f70</t>
+          <t>ca-cioos_a8671db6-81cc-4c92-b681-58595fe66182</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -28548,7 +28650,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Sea star microbiome data from 16S amplicon sequencing associated with rocky intertidal sites on Calvert and Quadra Islands</t>
+          <t>Water Property Measurements from the Bute Inlet Ocean Observing Station (BIOOS) Wirewalker, Bute Inlet, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -28566,12 +28668,12 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Nearshore, Genomics</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -28590,45 +28692,45 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.3, 49.87], [-124.8, 49.87], [-124.8, 51.75], [-128.3, 51.75], [-128.3, 49.87]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-124.9009, 50.5744]}</t>
         </is>
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '250.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q258" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution, microbeBiomassAndDiversity</t>
+          <t>subSurfaceTemperature, subSurfaceSalinity, oxygen, phytoplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>10.21966/0xvh-1318</t>
+          <t>10.21966/3q5j-n957</t>
         </is>
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/4TvAwNKXC7PkAi0TEZsZbbAzXfi1/-Oo1MBmr8fW1fputdBh6</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-OqDQ7wqqJtwSgUoAN1g</t>
         </is>
       </c>
       <c r="T258" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="U258" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="V258" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W258" t="n">
         <v>0</v>
@@ -28645,12 +28747,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
+          <t>227eb965-1892-4bad-8ded-dd2e1d68fdf6</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>ca-cioos_a8671db6-81cc-4c92-b681-58595fe66182</t>
+          <t>ca-cioos_08d3e779-2f44-4ce3-82cb-c7b763f72175</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -28660,7 +28762,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Water Property Measurements from the Bute Inlet Ocean Observing Station (BIOOS) Wirewalker, Bute Inlet, BC, Canada (Provisional)</t>
+          <t>DNA metabarcoding data from Autonomous Reef Monitoring Structures (ARMS) deployed around Calvert Island British Columbia</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -28678,12 +28780,12 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore, Genomics</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -28702,46 +28804,44 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-124.9009, 50.5744]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.61], [-127.8, 51.61], [-127.8, 51.9], [-128.4, 51.9], [-128.4, 51.61]]]}</t>
         </is>
       </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>[{'max': '250.0', 'min': '0.0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q259" t="inlineStr">
         <is>
-          <t>subSurfaceTemperature, subSurfaceSalinity, oxygen, phytoplanktonBiomassAndDiversity</t>
+          <t>invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>10.21966/3q5j-n957</t>
+          <t>10.21966/kmc2-5r12</t>
         </is>
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-OqDQ7wqqJtwSgUoAN1g</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-ORSLLie2O-FFN8cPV1e</t>
         </is>
       </c>
       <c r="T259" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="U259" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="V259" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr"/>
       <c r="W259" t="n">
         <v>0</v>
       </c>
@@ -28757,12 +28857,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>227eb965-1892-4bad-8ded-dd2e1d68fdf6</t>
+          <t>0cef18ab-cea6-4522-baba-1bcd73a30646</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>ca-cioos_08d3e779-2f44-4ce3-82cb-c7b763f72175</t>
+          <t>ca-cioos_66fbb7f5-3644-471a-95ee-f8d3758e888b</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -28772,7 +28872,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>DNA metabarcoding data from Autonomous Reef Monitoring Structures (ARMS) deployed around Calvert Island British Columbia</t>
+          <t>Mount Robson Aerial Photo and LiDAR Survey</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -28790,7 +28890,7 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>Nearshore, Genomics</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
@@ -28810,45 +28910,41 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Tula Foundation</t>
         </is>
       </c>
       <c r="N260" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.61], [-127.8, 51.61], [-127.8, 51.9], [-128.4, 51.9], [-128.4, 51.61]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-119.3, 53.03], [-118.8, 53.03], [-118.8, 53.26], [-119.3, 53.26], [-119.3, 53.03]]]}</t>
         </is>
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '3954.0', 'min': '800.0'}]</t>
         </is>
       </c>
       <c r="Q260" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>10.21966/kmc2-5r12</t>
+          <t>10.21966/w9n0-kn30</t>
         </is>
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-ORSLLie2O-FFN8cPV1e</t>
-        </is>
-      </c>
-      <c r="T260" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICbtZXkj6anGvgB3Qi</t>
+        </is>
+      </c>
+      <c r="T260" t="inlineStr"/>
       <c r="U260" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="V260" t="inlineStr"/>
@@ -28856,112 +28952,6 @@
         <v>0</v>
       </c>
       <c r="X260" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="n">
-        <v>259</v>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>0cef18ab-cea6-4522-baba-1bcd73a30646</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>ca-cioos_66fbb7f5-3644-471a-95ee-f8d3758e888b</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>Hakai Institute</t>
-        </is>
-      </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>Mount Robson Aerial Photo and LiDAR Survey</t>
-        </is>
-      </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>dataset</t>
-        </is>
-      </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>CC-BY-4.0</t>
-        </is>
-      </c>
-      <c r="H261" t="b">
-        <v>0</v>
-      </c>
-      <c r="I261" t="inlineStr">
-        <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
-        </is>
-      </c>
-      <c r="J261" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="L261" t="inlineStr">
-        <is>
-          <t>dataset</t>
-        </is>
-      </c>
-      <c r="M261" t="inlineStr">
-        <is>
-          <t>Tula Foundation</t>
-        </is>
-      </c>
-      <c r="N261" t="n">
-        <v>1</v>
-      </c>
-      <c r="O261" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-119.3, 53.03], [-118.8, 53.03], [-118.8, 53.26], [-119.3, 53.26], [-119.3, 53.03]]]}</t>
-        </is>
-      </c>
-      <c r="P261" t="inlineStr">
-        <is>
-          <t>[{'max': '3954.0', 'min': '800.0'}]</t>
-        </is>
-      </c>
-      <c r="Q261" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R261" t="inlineStr">
-        <is>
-          <t>10.21966/w9n0-kn30</t>
-        </is>
-      </c>
-      <c r="S261" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICbtZXkj6anGvgB3Qi</t>
-        </is>
-      </c>
-      <c r="T261" t="inlineStr"/>
-      <c r="U261" t="inlineStr">
-        <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="V261" t="inlineStr"/>
-      <c r="W261" t="n">
-        <v>0</v>
-      </c>
-      <c r="X261" t="inlineStr">
         <is>
           <t>[]</t>
         </is>

--- a/main/catalog_summary.xlsx
+++ b/main/catalog_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X260"/>
+  <dimension ref="A1:X261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
+          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
+          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -8756,7 +8756,11 @@
       <c r="H77" t="b">
         <v>0</v>
       </c>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Airborne Coastal Observatory</t>
+        </is>
+      </c>
       <c r="J77" t="inlineStr">
         <is>
           <t>completed</t>
@@ -8782,12 +8786,12 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -8798,7 +8802,7 @@
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -8812,7 +8816,7 @@
         </is>
       </c>
       <c r="V77" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
@@ -8823,12 +8827,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
+          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -8838,7 +8842,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
+          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8854,11 +8858,7 @@
       <c r="H78" t="b">
         <v>0</v>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Airborne Coastal Observatory</t>
-        </is>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>completed</t>
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -8900,7 +8900,7 @@
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -8914,7 +8914,7 @@
         </is>
       </c>
       <c r="V78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
@@ -10052,11 +10052,11 @@
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="V89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W89" t="n">
         <v>0</v>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="V97" t="n">
@@ -13991,12 +13991,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ca-cioos_26443ab2-964f-4031-a53b-f132434573e8</t>
+          <t>ca-cioos_23bc8c35-2e4e-4382-9296-a52d5ea49889</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -14006,7 +14006,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Ecosystem Comparison Plots - Calvert Island</t>
+          <t>Discharge Time Series (2013-2017) – Calvert Island - Archived Version 3.0</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Geospatial, Watersheds</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -14052,7 +14052,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13903808593744, 51.626542529786036], [-127.97355651855466, 51.626542529786036], [-127.97355651855466, 51.67766477883444], [-128.13903808593744, 51.67766477883444], [-128.13903808593744, 51.626542529786036]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -14067,12 +14067,12 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>10.21966/1.56481</t>
+          <t>10.21966/sbyc-d030</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWc4TU94c2lwT0tYa2U</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUdGRGRjUW9LRnBVNVI</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
@@ -14082,18 +14082,18 @@
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="V126" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="W126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -14103,12 +14103,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ca-cioos_23bc8c35-2e4e-4382-9296-a52d5ea49889</t>
+          <t>ca-cioos_26443ab2-964f-4031-a53b-f132434573e8</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -14118,7 +14118,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Discharge Time Series (2013-2017) – Calvert Island - Archived Version 3.0</t>
+          <t>Ecosystem Comparison Plots - Calvert Island</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -14136,7 +14136,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Geospatial, Watersheds</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -14164,7 +14164,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13903808593744, 51.626542529786036], [-127.97355651855466, 51.626542529786036], [-127.97355651855466, 51.67766477883444], [-128.13903808593744, 51.67766477883444], [-128.13903808593744, 51.626542529786036]]]}</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -14179,12 +14179,12 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>10.21966/sbyc-d030</t>
+          <t>10.21966/1.56481</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUdGRGRjUW9LRnBVNVI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWc4TU94c2lwT0tYa2U</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
@@ -14194,18 +14194,18 @@
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V127" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="W127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -14778,7 +14778,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada. Version 1.0.</t>
+          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -14850,11 +14850,11 @@
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="V133" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="W133" t="n">
         <v>0</v>
@@ -14962,11 +14962,11 @@
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="V134" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W134" t="n">
         <v>0</v>
@@ -15317,12 +15317,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
+          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -15332,7 +15332,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
+          <t>Stage-Discharge Time Series - Calvert Island - Archived Version 1.0</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15370,20 +15370,20 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Vancouver Island University</t>
         </is>
       </c>
       <c r="N138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
+          <t>[{'max': '250.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
@@ -15391,14 +15391,10 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R138" t="inlineStr">
-        <is>
-          <t>10.21966/1.135248</t>
-        </is>
-      </c>
+      <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFjSmdJMGxrU1pZbXM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
         </is>
       </c>
       <c r="T138" t="inlineStr">
@@ -15408,20 +15404,14 @@
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="V138" t="n">
-        <v>2</v>
-      </c>
-      <c r="W138" t="n">
-        <v>0</v>
-      </c>
-      <c r="X138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="W138" t="inlineStr"/>
+      <c r="X138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15429,12 +15419,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>6f261f49-dd1b-4250-ac59-e88c3d1b2470</t>
+          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ca-cioos_a242acd4-e3c7-46e0-8f43-f428fb824018</t>
+          <t>ca-cioos_9e61819e-8385-41d2-a5c5-0e2f37c522ef</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -15444,7 +15434,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Stage-Discharge Time Series - Calvert Island - Archived Version 1.0</t>
+          <t>LiDAR-based Ecosystem Classification for Calvert Island</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -15462,7 +15452,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -15482,20 +15472,20 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Vancouver Island University</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13217163085935, 51.59626804559349], [-127.97149658203124, 51.59626804559349], [-127.97149658203124, 51.6857538480987], [-128.13217163085935, 51.6857538480987], [-128.13217163085935, 51.59626804559349]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.22692871093747, 51.40948589555509], [-127.80944824218746, 51.40948589555509], [-127.80944824218746, 51.74233687689102], [-128.22692871093747, 51.74233687689102], [-128.22692871093747, 51.40948589555509]]]}</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>[{'max': '250.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
@@ -15503,10 +15493,14 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R139" t="inlineStr"/>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>10.21966/1.135248</t>
+        </is>
+      </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUpNR0VhOVRlU210cDI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVFjSmdJMGxrU1pZbXM</t>
         </is>
       </c>
       <c r="T139" t="inlineStr">
@@ -15516,14 +15510,20 @@
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V139" t="n">
-        <v>5</v>
-      </c>
-      <c r="W139" t="inlineStr"/>
-      <c r="X139" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0</v>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -19630,7 +19630,7 @@
         </is>
       </c>
       <c r="V176" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W176" t="n">
         <v>0</v>
@@ -20537,12 +20537,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>abb0b617-3a3e-43ec-b62e-e2918bfc10aa</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>ca-cioos_d1bef0b7-4d15-4bc1-bf34-faca6352891f</t>
+          <t>ca-cioos_b8483c9e-81e6-4e1a-b09f-2d66f8fee9a2</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -20552,7 +20552,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Daily satellite (Sentinel 3A and 3B) chlorophyll and suspended matter concentrations for coastal British Columbia and southeast Alaska</t>
+          <t>Spatial extent of surface canopy kelp (Nereocystis luetkeana) derived from fixed-wing surveys (2023), Denman Island to south Quadra Island, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -20570,12 +20570,12 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Airborne Coastal Observatory, Nearshore, Geospatial</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -20598,41 +20598,41 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-139.0, 47.0], [-121.5, 47.0], [-121.5, 59.5], [-139.0, 59.5], [-139.0, 47.0]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.3, 50.02], [-125.1, 50.05], [-125.1, 49.9], [-124.8, 49.71], [-124.7, 49.56], [-124.8, 49.55], [-124.9, 49.64], [-125.2, 49.9], [-125.2, 49.9], [-125.3, 50.02]]]}</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>phytoplanktonBiomassAndDiversity, particulateMatter, other</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>10.21966/dveq-bt48</t>
+          <t>10.21966/fmw1-8w35</t>
         </is>
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-NTteirxDjvnABVz_7Dh</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-NpNoCv2XWdhBoo5RBKV</t>
         </is>
       </c>
       <c r="T185" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="U185" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="V185" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W185" t="n">
         <v>0</v>
@@ -24290,7 +24290,7 @@
         </is>
       </c>
       <c r="V218" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W218" t="n">
         <v>0</v>
@@ -25962,11 +25962,11 @@
       </c>
       <c r="U233" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="V233" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W233" t="n">
         <v>0</v>
@@ -27258,7 +27258,11 @@
           <t>dataset</t>
         </is>
       </c>
-      <c r="M245" t="inlineStr"/>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
       <c r="N245" t="n">
         <v>1</v>
       </c>
@@ -27290,11 +27294,11 @@
       </c>
       <c r="U245" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="V245" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W245" t="inlineStr"/>
       <c r="X245" t="inlineStr"/>
@@ -28413,12 +28417,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>b7b923ed-b3fa-48b3-878d-40a3797046bc</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>ca-cioos_f7538807-4d49-4ed8-ad36-836c0e71428a</t>
+          <t>ca-cioos_d1bef0b7-4d15-4bc1-bf34-faca6352891f</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -28428,7 +28432,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>3m Digital Elevation Model - Calvert Island - British Columbia - Canada</t>
+          <t>Daily satellite (Sentinel 3A and 3B) chlorophyll and suspended matter concentrations for coastal British Columbia and southeast Alaska</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -28446,12 +28450,12 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -28470,50 +28474,52 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.16482, 51.408116], [-127.868831, 51.408116], [-127.868831, 51.734994], [-128.16482, 51.734994], [-128.16482, 51.408116]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-139.0, 47.0], [-121.5, 47.0], [-121.5, 59.5], [-139.0, 59.5], [-139.0, 47.0]]]}</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>phytoplanktonBiomassAndDiversity, particulateMatter, other</t>
         </is>
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>10.21966/RZVW-4A72</t>
+          <t>10.21966/dveq-bt48</t>
         </is>
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW13R3BBSGRER2ZkYnM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-NTteirxDjvnABVz_7Dh</t>
         </is>
       </c>
       <c r="T256" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="U256" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="V256" t="inlineStr"/>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="V256" t="n">
+        <v>4</v>
+      </c>
       <c r="W256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X256" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -28523,12 +28529,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
+          <t>b7b923ed-b3fa-48b3-878d-40a3797046bc</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>ca-cioos_33c8ce77-0674-4933-a305-01a25d253f70</t>
+          <t>ca-cioos_f7538807-4d49-4ed8-ad36-836c0e71428a</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -28538,7 +28544,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Sea star microbiome data from 16S amplicon sequencing associated with rocky intertidal sites on Calvert and Quadra Islands</t>
+          <t>3m Digital Elevation Model - Calvert Island - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -28556,7 +28562,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Nearshore, Genomics</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -28584,48 +28590,46 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.3, 49.87], [-124.8, 49.87], [-124.8, 51.75], [-128.3, 51.75], [-128.3, 49.87]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.16482, 51.408116], [-127.868831, 51.408116], [-127.868831, 51.734994], [-128.16482, 51.734994], [-128.16482, 51.408116]]]}</t>
         </is>
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q257" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution, microbeBiomassAndDiversity</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>10.21966/0xvh-1318</t>
+          <t>10.21966/RZVW-4A72</t>
         </is>
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/4TvAwNKXC7PkAi0TEZsZbbAzXfi1/-Oo1MBmr8fW1fputdBh6</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW13R3BBSGRER2ZkYnM</t>
         </is>
       </c>
       <c r="T257" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="U257" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="V257" t="n">
-        <v>2</v>
-      </c>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr"/>
       <c r="W257" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X257" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -28635,12 +28639,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
+          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>ca-cioos_a8671db6-81cc-4c92-b681-58595fe66182</t>
+          <t>ca-cioos_33c8ce77-0674-4933-a305-01a25d253f70</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -28650,7 +28654,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Water Property Measurements from the Bute Inlet Ocean Observing Station (BIOOS) Wirewalker, Bute Inlet, BC, Canada (Provisional)</t>
+          <t>Sea star microbiome data from 16S amplicon sequencing associated with rocky intertidal sites on Calvert and Quadra Islands</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -28668,12 +28672,12 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore, Genomics</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -28692,45 +28696,45 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-124.9009, 50.5744]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.3, 49.87], [-124.8, 49.87], [-124.8, 51.75], [-128.3, 51.75], [-128.3, 49.87]]]}</t>
         </is>
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>[{'max': '250.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q258" t="inlineStr">
         <is>
-          <t>subSurfaceTemperature, subSurfaceSalinity, oxygen, phytoplanktonBiomassAndDiversity</t>
+          <t>invertebrateAbundanceAndDistribution, microbeBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>10.21966/3q5j-n957</t>
+          <t>10.21966/0xvh-1318</t>
         </is>
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-OqDQ7wqqJtwSgUoAN1g</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/4TvAwNKXC7PkAi0TEZsZbbAzXfi1/-Oo1MBmr8fW1fputdBh6</t>
         </is>
       </c>
       <c r="T258" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="U258" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="V258" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W258" t="n">
         <v>0</v>
@@ -28747,12 +28751,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>227eb965-1892-4bad-8ded-dd2e1d68fdf6</t>
+          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>ca-cioos_08d3e779-2f44-4ce3-82cb-c7b763f72175</t>
+          <t>ca-cioos_a8671db6-81cc-4c92-b681-58595fe66182</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -28762,7 +28766,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>DNA metabarcoding data from Autonomous Reef Monitoring Structures (ARMS) deployed around Calvert Island British Columbia</t>
+          <t>Water Property Measurements from the Bute Inlet Ocean Observing Station (BIOOS) Wirewalker, Bute Inlet, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -28780,12 +28784,12 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>Nearshore, Genomics</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -28804,44 +28808,46 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.61], [-127.8, 51.61], [-127.8, 51.9], [-128.4, 51.9], [-128.4, 51.61]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-124.9009, 50.5744]}</t>
         </is>
       </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '250.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q259" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution</t>
+          <t>subSurfaceTemperature, subSurfaceSalinity, oxygen, phytoplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>10.21966/kmc2-5r12</t>
+          <t>10.21966/3q5j-n957</t>
         </is>
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-ORSLLie2O-FFN8cPV1e</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-OqDQ7wqqJtwSgUoAN1g</t>
         </is>
       </c>
       <c r="T259" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="U259" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="V259" t="inlineStr"/>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="V259" t="n">
+        <v>1</v>
+      </c>
       <c r="W259" t="n">
         <v>0</v>
       </c>
@@ -28857,12 +28863,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>0cef18ab-cea6-4522-baba-1bcd73a30646</t>
+          <t>227eb965-1892-4bad-8ded-dd2e1d68fdf6</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>ca-cioos_66fbb7f5-3644-471a-95ee-f8d3758e888b</t>
+          <t>ca-cioos_08d3e779-2f44-4ce3-82cb-c7b763f72175</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -28872,7 +28878,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Mount Robson Aerial Photo and LiDAR Survey</t>
+          <t>DNA metabarcoding data from Autonomous Reef Monitoring Structures (ARMS) deployed around Calvert Island British Columbia</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -28890,7 +28896,7 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Nearshore, Genomics</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
@@ -28910,41 +28916,45 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Tula Foundation</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N260" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-119.3, 53.03], [-118.8, 53.03], [-118.8, 53.26], [-119.3, 53.26], [-119.3, 53.03]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.61], [-127.8, 51.61], [-127.8, 51.9], [-128.4, 51.9], [-128.4, 51.61]]]}</t>
         </is>
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>[{'max': '3954.0', 'min': '800.0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q260" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>10.21966/w9n0-kn30</t>
+          <t>10.21966/kmc2-5r12</t>
         </is>
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICbtZXkj6anGvgB3Qi</t>
-        </is>
-      </c>
-      <c r="T260" t="inlineStr"/>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-ORSLLie2O-FFN8cPV1e</t>
+        </is>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
       <c r="U260" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="V260" t="inlineStr"/>
@@ -28952,6 +28962,112 @@
         <v>0</v>
       </c>
       <c r="X260" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>259</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>0cef18ab-cea6-4522-baba-1bcd73a30646</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>ca-cioos_66fbb7f5-3644-471a-95ee-f8d3758e888b</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Mount Robson Aerial Photo and LiDAR Survey</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="H261" t="b">
+        <v>0</v>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Airborne Coastal Observatory, Geospatial</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>Tula Foundation</t>
+        </is>
+      </c>
+      <c r="N261" t="n">
+        <v>1</v>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-119.3, 53.03], [-118.8, 53.03], [-118.8, 53.26], [-119.3, 53.26], [-119.3, 53.03]]]}</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>[{'max': '3954.0', 'min': '800.0'}]</t>
+        </is>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R261" t="inlineStr">
+        <is>
+          <t>10.21966/w9n0-kn30</t>
+        </is>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICbtZXkj6anGvgB3Qi</t>
+        </is>
+      </c>
+      <c r="T261" t="inlineStr"/>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr"/>
+      <c r="W261" t="n">
+        <v>0</v>
+      </c>
+      <c r="X261" t="inlineStr">
         <is>
           <t>[]</t>
         </is>

--- a/main/catalog_summary.xlsx
+++ b/main/catalog_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X262"/>
+  <dimension ref="A1:X264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, invertebrateAbundanceAndDistribution, fishAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1934,11 +1934,11 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
@@ -11623,12 +11623,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ca-cioos_4fac74c8-f58c-46b0-87dc-ab70ce756880</t>
+          <t>ca-cioos_51171738-7556-48f1-8757-658d99fa25dd</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -11638,7 +11638,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Discovery Islands LiDAR Dataset  - 2014 - British Columbia - Canada</t>
+          <t>Eelgrass Extent 2014 - Central Coast</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -11654,11 +11654,7 @@
       <c r="H104" t="b">
         <v>0</v>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>Geospatial</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>completed</t>
@@ -11680,16 +11676,16 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.3704833984375, 49.9229354544957], [-124.75524902343749, 49.9229354544957], [-124.75524902343749, 50.291094042311386], [-125.3704833984375, 50.291094042311386], [-125.3704833984375, 49.9229354544957]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4878540039062, 51.653814904471545], [-128.0978393554687, 51.653814904471545], [-128.0978393554687, 52.07950600379698], [-128.4878540039062, 52.07950600379698], [-128.4878540039062, 51.653814904471545]]]}</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>[{'max': '500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '50.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -11700,7 +11696,7 @@
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXR6SWM4aTRoYk9MeU0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUZuOThkU2QzakpPNEQ</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
@@ -11710,11 +11706,11 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V104" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W104" t="inlineStr"/>
       <c r="X104" t="inlineStr"/>
@@ -11725,12 +11721,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ca-cioos_51171738-7556-48f1-8757-658d99fa25dd</t>
+          <t>ca-cioos_4fac74c8-f58c-46b0-87dc-ab70ce756880</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -11740,7 +11736,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Eelgrass Extent 2014 - Central Coast</t>
+          <t>Discovery Islands LiDAR Dataset  - 2014 - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -11756,7 +11752,11 @@
       <c r="H105" t="b">
         <v>0</v>
       </c>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Geospatial</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr">
         <is>
           <t>completed</t>
@@ -11778,16 +11778,16 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4878540039062, 51.653814904471545], [-128.0978393554687, 51.653814904471545], [-128.0978393554687, 52.07950600379698], [-128.4878540039062, 52.07950600379698], [-128.4878540039062, 51.653814904471545]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.3704833984375, 49.9229354544957], [-124.75524902343749, 49.9229354544957], [-124.75524902343749, 50.291094042311386], [-125.3704833984375, 50.291094042311386], [-125.3704833984375, 49.9229354544957]]]}</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>[{'max': '50.0', 'min': '0.0'}]</t>
+          <t>[{'max': '500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -11798,7 +11798,7 @@
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUZuOThkU2QzakpPNEQ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXR6SWM4aTRoYk9MeU0</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
@@ -11808,11 +11808,11 @@
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="V105" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W105" t="inlineStr"/>
       <c r="X105" t="inlineStr"/>
@@ -13995,12 +13995,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ca-cioos_26443ab2-964f-4031-a53b-f132434573e8</t>
+          <t>ca-cioos_25674e9b-1d49-4270-b917-cfe6cdc30f95</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Ecosystem Comparison Plots - Calvert Island</t>
+          <t>Watersheds of the northern Pacific coastal temperate rainforest margin</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -14028,7 +14028,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Geospatial, Watersheds</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -14052,16 +14052,16 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13903808593744, 51.626542529786036], [-127.97355651855466, 51.626542529786036], [-127.97355651855466, 51.67766477883444], [-128.13903808593744, 51.67766477883444], [-128.13903808593744, 51.626542529786036]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-143.16578297, 37.67883738], [-104.45881201, 37.67883738], [-104.45881201, 60.91786918], [-143.16578297, 60.91786918], [-143.16578297, 37.67883738]]]}</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '6000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
@@ -14071,12 +14071,12 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>10.21966/1.56481</t>
+          <t>10.21966/1.715755</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWc4TU94c2lwT0tYa2U</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWJSa2xESlBIbk1rSXA</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
@@ -14090,14 +14090,14 @@
         </is>
       </c>
       <c r="V126" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="W126" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[{'year': '2022', 'total': 2}, {'year': '2023', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -14107,12 +14107,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ca-cioos_25674e9b-1d49-4270-b917-cfe6cdc30f95</t>
+          <t>ca-cioos_26443ab2-964f-4031-a53b-f132434573e8</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Watersheds of the northern Pacific coastal temperate rainforest margin</t>
+          <t>Ecosystem Comparison Plots - Calvert Island</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -14140,7 +14140,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Geospatial, Watersheds</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -14164,52 +14164,52 @@
         </is>
       </c>
       <c r="N127" t="n">
+        <v>1</v>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13903808593744, 51.626542529786036], [-127.97355651855466, 51.626542529786036], [-127.97355651855466, 51.67766477883444], [-128.13903808593744, 51.67766477883444], [-128.13903808593744, 51.626542529786036]]]}</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>10.21966/1.56481</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWc4TU94c2lwT0tYa2U</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>2022-03-29</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="V127" t="n">
         <v>2</v>
       </c>
-      <c r="O127" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-143.16578297, 37.67883738], [-104.45881201, 37.67883738], [-104.45881201, 60.91786918], [-143.16578297, 60.91786918], [-143.16578297, 37.67883738]]]}</t>
-        </is>
-      </c>
-      <c r="P127" t="inlineStr">
-        <is>
-          <t>[{'max': '6000.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q127" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R127" t="inlineStr">
-        <is>
-          <t>10.21966/1.715755</t>
-        </is>
-      </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWJSa2xESlBIbk1rSXA</t>
-        </is>
-      </c>
-      <c r="T127" t="inlineStr">
-        <is>
-          <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="V127" t="n">
-        <v>9</v>
-      </c>
       <c r="W127" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 2}, {'year': '2023', 'total': 1}]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -14655,12 +14655,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
+          <t>ca-cioos_765d00bb-beec-486c-bd00-e27f972b7324</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -14670,7 +14670,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada</t>
+          <t>Microbial activity and carbon fluxes in rainforest soil – Tsunami Hill, Calvert Island – June 2015 - April 2016</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -14688,7 +14688,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Watersheds, Oceanography</t>
+          <t>Genomics, Watersheds</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -14706,33 +14706,37 @@
           <t>dataset</t>
         </is>
       </c>
-      <c r="M132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>University of British Columbia</t>
+        </is>
+      </c>
       <c r="N132" t="n">
         <v>1</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13650264, 51.64966999], [-128.12495841, 51.64966999], [-128.12495841, 51.65523482], [-128.13650264, 51.65523482], [-128.13650264, 51.64966999]]]}</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>10.21966/66x5-a210</t>
+          <t>10.21966/1.715630</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUE0SHdBOUNiWjU5bFY</t>
         </is>
       </c>
       <c r="T132" t="inlineStr">
@@ -14742,11 +14746,11 @@
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="V132" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W132" t="n">
         <v>0</v>
@@ -14763,12 +14767,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ca-cioos_765d00bb-beec-486c-bd00-e27f972b7324</t>
+          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -14778,7 +14782,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Microbial activity and carbon fluxes in rainforest soil – Tsunami Hill, Calvert Island – June 2015 - April 2016</t>
+          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -14796,7 +14800,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Genomics, Watersheds</t>
+          <t>Watersheds, Oceanography</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -14814,37 +14818,33 @@
           <t>dataset</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>University of British Columbia</t>
-        </is>
-      </c>
+      <c r="M133" t="inlineStr"/>
       <c r="N133" t="n">
         <v>1</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13650264, 51.64966999], [-128.12495841, 51.64966999], [-128.12495841, 51.65523482], [-128.13650264, 51.65523482], [-128.13650264, 51.64966999]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>10.21966/1.715630</t>
+          <t>10.21966/66x5-a210</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUE0SHdBOUNiWjU5bFY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
         </is>
       </c>
       <c r="T133" t="inlineStr">
@@ -14854,11 +14854,11 @@
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="V133" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W133" t="n">
         <v>0</v>
@@ -15423,12 +15423,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
+          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ca-cioos_b52d5602-f81d-4565-9574-e448e99bc997</t>
+          <t>ca-cioos_b694a5c5-6a7e-4206-96aa-5b7754323345</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -15438,7 +15438,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Bathymetry for Six Lakes on Calvert and Hecate Islands - 2016 - British Columbia - Canada</t>
+          <t>Air temperature and relative humidity time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -15456,12 +15456,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Watersheds, Geospatial</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -15484,12 +15484,12 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.09646606445312, 51.5996802644666], [-127.9508972167969, 51.5996802644666], [-127.9508972167969, 51.69171329024539], [-128.09646606445312, 51.69171329024539], [-128.09646606445312, 51.5996802644666]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.30095161, 50.04299371], [-125.08745063, 50.04299371], [-125.08745063, 51.791595], [-128.30095161, 51.791595], [-128.30095161, 50.04299371]]]}</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '741.0', 'min': '3.0'}]</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
@@ -15497,14 +15497,10 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R139" t="inlineStr">
-        <is>
-          <t>10.21966/fcwf-p919</t>
-        </is>
-      </c>
+      <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWxuNHhkYXVuNlFDSVY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWRmQkdrNXg2bFpvUTE</t>
         </is>
       </c>
       <c r="T139" t="inlineStr">
@@ -15514,20 +15510,14 @@
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="V139" t="n">
-        <v>1</v>
-      </c>
-      <c r="W139" t="n">
-        <v>1</v>
-      </c>
-      <c r="X139" t="inlineStr">
-        <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="W139" t="inlineStr"/>
+      <c r="X139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15535,12 +15525,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
+          <t>f0cae885-2124-41c1-8523-2c6725c40dd6</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ca-cioos_cb13f042-bf47-4874-86e6-4728aa9380d4</t>
+          <t>ca-cioos_b52d5602-f81d-4565-9574-e448e99bc997</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -15550,7 +15540,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Groundwater sampling in the Kwakshua Watersheds of Calvert and Hecate Islands, BC (2016-2019) - Version 1.0</t>
+          <t>Bathymetry for Six Lakes on Calvert and Hecate Islands - 2016 - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -15568,7 +15558,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Watersheds, Geospatial</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -15592,45 +15582,45 @@
         </is>
       </c>
       <c r="N140" t="n">
+        <v>2</v>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.09646606445312, 51.5996802644666], [-127.9508972167969, 51.5996802644666], [-127.9508972167969, 51.69171329024539], [-128.09646606445312, 51.69171329024539], [-128.09646606445312, 51.5996802644666]]]}</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>10.21966/fcwf-p919</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWxuNHhkYXVuNlFDSVY</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>2022-03-29</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="V140" t="n">
         <v>1</v>
-      </c>
-      <c r="O140" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.98931373, 50.8340959], [-127.03580726, 50.8340959], [-127.03580726, 52.33530479], [-128.98931373, 52.33530479], [-128.98931373, 50.8340959]]]}</t>
-        </is>
-      </c>
-      <c r="P140" t="inlineStr">
-        <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q140" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R140" t="inlineStr">
-        <is>
-          <t>10.21966/mnwn-gw16</t>
-        </is>
-      </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWVHTU93c2dHU3lmSzU</t>
-        </is>
-      </c>
-      <c r="T140" t="inlineStr">
-        <is>
-          <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="U140" t="inlineStr">
-        <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="V140" t="n">
-        <v>9</v>
       </c>
       <c r="W140" t="n">
         <v>1</v>
@@ -15647,12 +15637,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
+          <t>39f8b771-eb65-420f-b64e-742d94bbebf0</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>ca-cioos_d05df775-4295-4b9f-b3b3-29fe891d9ed9</t>
+          <t>ca-cioos_cb13f042-bf47-4874-86e6-4728aa9380d4</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -15662,7 +15652,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>LIDAR Derived Forest Metrics - Calvert Island - British Columbia - Canada</t>
+          <t>Groundwater sampling in the Kwakshua Watersheds of Calvert and Hecate Islands, BC (2016-2019) - Version 1.0</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -15680,7 +15670,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -15708,12 +15698,12 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.21777349337933, 51.412912129355306], [-127.82775884494184, 51.412912129355306], [-127.82775884494184, 51.74403752566786], [-128.21777349337933, 51.74403752566786], [-128.21777349337933, 51.412912129355306]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.98931373, 50.8340959], [-127.03580726, 50.8340959], [-127.03580726, 52.33530479], [-128.98931373, 52.33530479], [-128.98931373, 50.8340959]]]}</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
@@ -15723,12 +15713,12 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>10.21966/MQ9T-BW79</t>
+          <t>10.21966/mnwn-gw16</t>
         </is>
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWZyU1hnTHowV2poZUk</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWVHTU93c2dHU3lmSzU</t>
         </is>
       </c>
       <c r="T141" t="inlineStr">
@@ -15742,7 +15732,7 @@
         </is>
       </c>
       <c r="V141" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W141" t="n">
         <v>1</v>
@@ -15759,12 +15749,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
+          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ca-cioos_d94882f8-c069-454d-a0ea-96c2b17d789d</t>
+          <t>ca-cioos_d05df775-4295-4b9f-b3b3-29fe891d9ed9</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -15774,7 +15764,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>LiDAR Derived Watersheds with Metrics - Calvert Island</t>
+          <t>LIDAR Derived Forest Metrics - Calvert Island - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -15816,16 +15806,16 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.159953, 51.411975], [-127.869461, 51.411975], [-127.869461, 51.734199], [-128.159953, 51.734199], [-128.159953, 51.411975]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.21777349337933, 51.412912129355306], [-127.82775884494184, 51.412912129355306], [-127.82775884494184, 51.74403752566786], [-128.21777349337933, 51.74403752566786], [-128.21777349337933, 51.412912129355306]]]}</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1014.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
@@ -15835,12 +15825,12 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>10.21966/1.15311</t>
+          <t>10.21966/MQ9T-BW79</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWlXa3RKM3k5Q29aTWQ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWZyU1hnTHowV2poZUk</t>
         </is>
       </c>
       <c r="T142" t="inlineStr">
@@ -15854,14 +15844,14 @@
         </is>
       </c>
       <c r="V142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 2}]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -15871,12 +15861,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>17680b42-fb77-4ab5-8645-23bb2f28c3e0</t>
+          <t>79e98468-af9a-4b52-aa9c-71129fa9cb03</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>ca-cioos_b694a5c5-6a7e-4206-96aa-5b7754323345</t>
+          <t>ca-cioos_d94882f8-c069-454d-a0ea-96c2b17d789d</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -15886,7 +15876,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Air temperature and relative humidity time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
+          <t>LiDAR Derived Watersheds with Metrics - Calvert Island</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -15904,12 +15894,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -15932,12 +15922,12 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.30095161, 50.04299371], [-125.08745063, 50.04299371], [-125.08745063, 51.791595], [-128.30095161, 51.791595], [-128.30095161, 50.04299371]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.159953, 51.411975], [-127.869461, 51.411975], [-127.869461, 51.734199], [-128.159953, 51.734199], [-128.159953, 51.411975]]]}</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>[{'max': '741.0', 'min': '3.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
@@ -15945,10 +15935,14 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R143" t="inlineStr"/>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>10.21966/1.15311</t>
+        </is>
+      </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWRmQkdrNXg2bFpvUTE</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWlXa3RKM3k5Q29aTWQ</t>
         </is>
       </c>
       <c r="T143" t="inlineStr">
@@ -15958,14 +15952,20 @@
       </c>
       <c r="U143" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V143" t="n">
-        <v>9</v>
-      </c>
-      <c r="W143" t="inlineStr"/>
-      <c r="X143" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="W143" t="n">
+        <v>2</v>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>[{'year': '2022', 'total': 2}]</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -17956,7 +17956,7 @@
         </is>
       </c>
       <c r="V161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W161" t="n">
         <v>0</v>
@@ -19634,7 +19634,7 @@
         </is>
       </c>
       <c r="V176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W176" t="n">
         <v>0</v>
@@ -20859,7 +20859,9 @@
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="V187" t="inlineStr"/>
+      <c r="V187" t="n">
+        <v>1</v>
+      </c>
       <c r="W187" t="n">
         <v>0</v>
       </c>
@@ -26306,7 +26308,7 @@
         </is>
       </c>
       <c r="V236" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W236" t="n">
         <v>1</v>
@@ -27643,12 +27645,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>7b1120bc-4a2c-432c-9e54-879d66751a59</t>
+          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>ca-cioos_b2b18171-35b6-4345-b81b-497a90c2e7c5</t>
+          <t>ca-cioos_1efbadd2-e735-48cc-9498-e3a5a88e48a6</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -27658,7 +27660,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Seagrass fish and macroinvertebrate swaths BC Central Coast</t>
+          <t>Seawater Carbon Dioxide (CO2) Content from the SuperCO2 System in the Pacific Ecosystem Autonomous Research Laboratory, Bamfield Marine Sciences Centre, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -27676,7 +27678,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -27700,44 +27702,46 @@
         </is>
       </c>
       <c r="N249" t="n">
+        <v>2</v>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359]]]}</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>[{'max': '0', 'min': '0'}]</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>inorganicCarbon, seaSurfaceSalinity, seaSurfaceTemperature</t>
+        </is>
+      </c>
+      <c r="R249" t="inlineStr">
+        <is>
+          <t>10.21966/a0v4-x512</t>
+        </is>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-Olwvch3kCplJcz3CCeR</t>
+        </is>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="V249" t="n">
         <v>1</v>
       </c>
-      <c r="O249" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 52.09], [-128.5, 52.04], [-128.5, 51.97], [-128.5, 51.93], [-128.5, 51.9], [-128.4, 51.88], [-128.3, 51.86], [-128.3, 51.83], [-128.2, 51.63], [-127.9, 51.62], [-127.8, 51.77], [-127.8, 51.83], [-127.9, 51.99], [-128.4, 52.09]]]}</t>
-        </is>
-      </c>
-      <c r="P249" t="inlineStr">
-        <is>
-          <t>[{'max': '10.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q249" t="inlineStr">
-        <is>
-          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
-        </is>
-      </c>
-      <c r="R249" t="inlineStr">
-        <is>
-          <t>10.21966/NMNG-SF35</t>
-        </is>
-      </c>
-      <c r="S249" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/lJHlH9nm20QQOPuk217xLlxWbNv1/-NPt7327bul36pby-Odi</t>
-        </is>
-      </c>
-      <c r="T249" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="U249" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="V249" t="inlineStr"/>
       <c r="W249" t="n">
         <v>0</v>
       </c>
@@ -27753,12 +27757,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
+          <t>7b1120bc-4a2c-432c-9e54-879d66751a59</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>ca-cioos_1efbadd2-e735-48cc-9498-e3a5a88e48a6</t>
+          <t>ca-cioos_b2b18171-35b6-4345-b81b-497a90c2e7c5</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -27768,7 +27772,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Seawater Carbon Dioxide (CO2) Content from the SuperCO2 System in the Pacific Ecosystem Autonomous Research Laboratory, Bamfield Marine Sciences Centre, BC, Canada (Provisional)</t>
+          <t>Seagrass fish and macroinvertebrate swaths BC Central Coast</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -27786,7 +27790,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -27810,31 +27814,31 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 52.09], [-128.5, 52.04], [-128.5, 51.97], [-128.5, 51.93], [-128.5, 51.9], [-128.4, 51.88], [-128.3, 51.86], [-128.3, 51.83], [-128.2, 51.63], [-127.9, 51.62], [-127.8, 51.77], [-127.8, 51.83], [-127.9, 51.99], [-128.4, 52.09]]]}</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '10.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q250" t="inlineStr">
         <is>
-          <t>inorganicCarbon, seaSurfaceSalinity, seaSurfaceTemperature</t>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>10.21966/a0v4-x512</t>
+          <t>10.21966/NMNG-SF35</t>
         </is>
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-Olwvch3kCplJcz3CCeR</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/lJHlH9nm20QQOPuk217xLlxWbNv1/-NPt7327bul36pby-Odi</t>
         </is>
       </c>
       <c r="T250" t="inlineStr">
@@ -27844,12 +27848,10 @@
       </c>
       <c r="U250" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="V250" t="n">
-        <v>2</v>
-      </c>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr"/>
       <c r="W250" t="n">
         <v>0</v>
       </c>
@@ -28069,7 +28071,9 @@
           <t>2026-04-13</t>
         </is>
       </c>
-      <c r="V252" t="inlineStr"/>
+      <c r="V252" t="n">
+        <v>1</v>
+      </c>
       <c r="W252" t="n">
         <v>0</v>
       </c>
@@ -28960,10 +28964,16 @@
         </is>
       </c>
       <c r="V260" t="n">
-        <v>2</v>
-      </c>
-      <c r="W260" t="inlineStr"/>
-      <c r="X260" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="W260" t="n">
+        <v>0</v>
+      </c>
+      <c r="X260" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -28996,7 +29006,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>CC-BY-NC-4.0</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="H261" t="b">
@@ -29047,7 +29057,7 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>10.21966/0xex-r023</t>
+          <t>10.21966/k0z0-3z50</t>
         </is>
       </c>
       <c r="S261" t="inlineStr">
@@ -29062,18 +29072,16 @@
       </c>
       <c r="U261" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="V261" t="n">
-        <v>4</v>
-      </c>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr"/>
       <c r="W261" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X261" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -29083,12 +29091,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>0cef18ab-cea6-4522-baba-1bcd73a30646</t>
+          <t>6c4803cc-d1c6-4327-806a-7f6796606175</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>ca-cioos_66fbb7f5-3644-471a-95ee-f8d3758e888b</t>
+          <t>ca-cioos_6c34ed6e-5a17-41f2-b83a-cd59d1ce07bd</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -29098,7 +29106,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Mount Robson Aerial Photo and LiDAR Survey</t>
+          <t>Knight Inlet Multibeam Bathymetry Survey</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -29116,7 +29124,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -29136,7 +29144,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Tula Foundation</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N262" t="n">
@@ -29144,40 +29152,262 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.0537, 50.6529], [-125.9229, 50.6529], [-125.9229, 50.7077], [-126.0537, 50.7077], [-126.0537, 50.6529]]]}</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>[{'max': '288.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R262" t="inlineStr">
+        <is>
+          <t>10.21966/8dgz-1z27</t>
+        </is>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OG7EOynnzSIOU7LPWgs</t>
+        </is>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="V262" t="n">
+        <v>1</v>
+      </c>
+      <c r="W262" t="n">
+        <v>0</v>
+      </c>
+      <c r="X262" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>261</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>ce6f3f8c-6b57-4f18-be46-8c0b5a4baeb9</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>ca-cioos_8755f475-2133-4205-baff-5e2937824f45</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Poole Creek Aerial Surveys - Airborne Coastal Observatory</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="H263" t="b">
+        <v>0</v>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Airborne Coastal Observatory, Geospatial</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="N263" t="n">
+        <v>1</v>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.9075, 50.2436], [-122.8124, 50.2436], [-122.8124, 50.3016], [-122.9075, 50.3016], [-122.9075, 50.2436]]]}</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>[{'max': '450.0', 'min': '200.0'}]</t>
+        </is>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R263" t="inlineStr">
+        <is>
+          <t>10.21966/g8f2-jw82</t>
+        </is>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OtfdtO43um_1J_LdCpn</t>
+        </is>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="V263" t="inlineStr"/>
+      <c r="W263" t="n">
+        <v>0</v>
+      </c>
+      <c r="X263" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>262</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>0cef18ab-cea6-4522-baba-1bcd73a30646</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>ca-cioos_66fbb7f5-3644-471a-95ee-f8d3758e888b</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Mount Robson Aerial Photo and LiDAR Survey</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="H264" t="b">
+        <v>0</v>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Airborne Coastal Observatory, Geospatial</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>Tula Foundation</t>
+        </is>
+      </c>
+      <c r="N264" t="n">
+        <v>1</v>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
           <t>{'type': 'Polygon', 'coordinates': [[[-119.3, 53.03], [-118.8, 53.03], [-118.8, 53.26], [-119.3, 53.26], [-119.3, 53.03]]]}</t>
         </is>
       </c>
-      <c r="P262" t="inlineStr">
+      <c r="P264" t="inlineStr">
         <is>
           <t>[{'max': '3954.0', 'min': '800.0'}]</t>
         </is>
       </c>
-      <c r="Q262" t="inlineStr">
+      <c r="Q264" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="R262" t="inlineStr">
+      <c r="R264" t="inlineStr">
         <is>
           <t>10.21966/w9n0-kn30</t>
         </is>
       </c>
-      <c r="S262" t="inlineStr">
+      <c r="S264" t="inlineStr">
         <is>
           <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICbtZXkj6anGvgB3Qi</t>
         </is>
       </c>
-      <c r="T262" t="inlineStr"/>
-      <c r="U262" t="inlineStr">
+      <c r="T264" t="inlineStr"/>
+      <c r="U264" t="inlineStr">
         <is>
           <t>2025-04-02</t>
         </is>
       </c>
-      <c r="V262" t="inlineStr"/>
-      <c r="W262" t="n">
-        <v>0</v>
-      </c>
-      <c r="X262" t="inlineStr">
+      <c r="V264" t="inlineStr"/>
+      <c r="W264" t="n">
+        <v>0</v>
+      </c>
+      <c r="X264" t="inlineStr">
         <is>
           <t>[]</t>
         </is>

--- a/main/catalog_summary.xlsx
+++ b/main/catalog_summary.xlsx
@@ -13223,12 +13223,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
+          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -13238,7 +13238,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
+          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019 Version 4.1</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -13261,7 +13261,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -13280,11 +13280,11 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>10.21966/XNH1-TP28</t>
+          <t>10.21966/zvwf-qn04</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
         </is>
       </c>
       <c r="T119" t="inlineStr">
@@ -13314,16 +13314,18 @@
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="V119" t="inlineStr"/>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="V119" t="n">
+        <v>5</v>
+      </c>
       <c r="W119" t="n">
         <v>1</v>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[{'year': '2025', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -13333,12 +13335,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
+          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -13348,7 +13350,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019 Version 4.1</t>
+          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -13371,7 +13373,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -13390,11 +13392,11 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -13409,12 +13411,12 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>10.21966/zvwf-qn04</t>
+          <t>10.21966/XNH1-TP28</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
@@ -13424,18 +13426,16 @@
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="V120" t="n">
-        <v>5</v>
-      </c>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr"/>
       <c r="W120" t="n">
         <v>1</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 1}]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -13995,12 +13995,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ca-cioos_25674e9b-1d49-4270-b917-cfe6cdc30f95</t>
+          <t>ca-cioos_26443ab2-964f-4031-a53b-f132434573e8</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Watersheds of the northern Pacific coastal temperate rainforest margin</t>
+          <t>Ecosystem Comparison Plots - Calvert Island</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -14028,7 +14028,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Geospatial, Watersheds</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -14052,52 +14052,52 @@
         </is>
       </c>
       <c r="N126" t="n">
+        <v>1</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13903808593744, 51.626542529786036], [-127.97355651855466, 51.626542529786036], [-127.97355651855466, 51.67766477883444], [-128.13903808593744, 51.67766477883444], [-128.13903808593744, 51.626542529786036]]]}</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>10.21966/1.56481</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWc4TU94c2lwT0tYa2U</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>2022-03-29</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="V126" t="n">
         <v>2</v>
       </c>
-      <c r="O126" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-143.16578297, 37.67883738], [-104.45881201, 37.67883738], [-104.45881201, 60.91786918], [-143.16578297, 60.91786918], [-143.16578297, 37.67883738]]]}</t>
-        </is>
-      </c>
-      <c r="P126" t="inlineStr">
-        <is>
-          <t>[{'max': '6000.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q126" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R126" t="inlineStr">
-        <is>
-          <t>10.21966/1.715755</t>
-        </is>
-      </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWJSa2xESlBIbk1rSXA</t>
-        </is>
-      </c>
-      <c r="T126" t="inlineStr">
-        <is>
-          <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="V126" t="n">
-        <v>9</v>
-      </c>
       <c r="W126" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 2}, {'year': '2023', 'total': 1}]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -14107,12 +14107,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
+          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ca-cioos_26443ab2-964f-4031-a53b-f132434573e8</t>
+          <t>ca-cioos_25674e9b-1d49-4270-b917-cfe6cdc30f95</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Ecosystem Comparison Plots - Calvert Island</t>
+          <t>Watersheds of the northern Pacific coastal temperate rainforest margin</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -14140,7 +14140,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Geospatial, Watersheds</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -14164,16 +14164,16 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13903808593744, 51.626542529786036], [-127.97355651855466, 51.626542529786036], [-127.97355651855466, 51.67766477883444], [-128.13903808593744, 51.67766477883444], [-128.13903808593744, 51.626542529786036]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-143.16578297, 37.67883738], [-104.45881201, 37.67883738], [-104.45881201, 60.91786918], [-143.16578297, 60.91786918], [-143.16578297, 37.67883738]]]}</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '6000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
@@ -14183,12 +14183,12 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>10.21966/1.56481</t>
+          <t>10.21966/1.715755</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWc4TU94c2lwT0tYa2U</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWJSa2xESlBIbk1rSXA</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
@@ -14202,14 +14202,14 @@
         </is>
       </c>
       <c r="V127" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="W127" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[{'year': '2022', 'total': 2}, {'year': '2023', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -20859,9 +20859,7 @@
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="V187" t="n">
-        <v>1</v>
-      </c>
+      <c r="V187" t="inlineStr"/>
       <c r="W187" t="n">
         <v>0</v>
       </c>

--- a/main/catalog_summary.xlsx
+++ b/main/catalog_summary.xlsx
@@ -1847,12 +1847,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ca-cioos_af65bf72-27af-4747-8911-ab05591762ac</t>
+          <t>ca-cioos_ab901b46-43f6-4044-b0c3-b5fd825622f4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kelp forest communities along an otter gradient</t>
+          <t>World View 2 Imagery - Coverage of three regions of the BC Central Coast - Summer 2014, 2015, &amp; 2016</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>underDevelopment</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Simon Fraser University</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1908,23 +1908,27 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.770751953125, 51.33404377878941], [-127.74902343749999, 51.33404377878941], [-127.74902343749999, 52.19077237113535], [-128.770751953125, 52.19077237113535], [-128.770751953125, 51.33404377878941]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.61145019531247, 51.61801654877371], [-127.91931152343746, 51.61801654877371], [-127.91931152343746, 52.11325243469631], [-128.61145019531247, 52.11325243469631], [-128.61145019531247, 51.61801654877371]]]}</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>[{'max': '50.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>other, invertebrateAbundanceAndDistribution, fishAbundanceAndDistribution</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr"/>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>10.21966/nmds-rx42</t>
+        </is>
+      </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXlMbjJYUlpvZFpITks</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXp1R01BNWFYV0RkUEY</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -1934,14 +1938,18 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="V14" t="n">
-        <v>3</v>
-      </c>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1949,12 +1957,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ca-cioos_ab901b46-43f6-4044-b0c3-b5fd825622f4</t>
+          <t>ca-cioos_af65bf72-27af-4747-8911-ab05591762ac</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1964,7 +1972,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>World View 2 Imagery - Coverage of three regions of the BC Central Coast - Summer 2014, 2015, &amp; 2016</t>
+          <t>Kelp forest communities along an otter gradient</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1982,12 +1990,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>underDevelopment</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2002,7 +2010,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Simon Fraser University</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -2010,27 +2018,23 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.61145019531247, 51.61801654877371], [-127.91931152343746, 51.61801654877371], [-127.91931152343746, 52.11325243469631], [-128.61145019531247, 52.11325243469631], [-128.61145019531247, 51.61801654877371]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.770751953125, 51.33404377878941], [-127.74902343749999, 51.33404377878941], [-127.74902343749999, 52.19077237113535], [-128.770751953125, 52.19077237113535], [-128.770751953125, 51.33404377878941]]]}</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '50.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>10.21966/nmds-rx42</t>
-        </is>
-      </c>
+          <t>other, invertebrateAbundanceAndDistribution, fishAbundanceAndDistribution</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXp1R01BNWFYV0RkUEY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXlMbjJYUlpvZFpITks</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -2040,18 +2044,14 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>3</v>
+      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
+          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
+          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -8756,11 +8756,7 @@
       <c r="H77" t="b">
         <v>0</v>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Airborne Coastal Observatory</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>completed</t>
@@ -8786,12 +8782,12 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -8802,7 +8798,7 @@
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -8816,7 +8812,7 @@
         </is>
       </c>
       <c r="V77" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
@@ -8827,12 +8823,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
+          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -8842,7 +8838,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
+          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8858,7 +8854,11 @@
       <c r="H78" t="b">
         <v>0</v>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Airborne Coastal Observatory</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr">
         <is>
           <t>completed</t>
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -8900,7 +8900,7 @@
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -8914,7 +8914,7 @@
         </is>
       </c>
       <c r="V78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
@@ -13883,12 +13883,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ca-cioos_23bc8c35-2e4e-4382-9296-a52d5ea49889</t>
+          <t>ca-cioos_26443ab2-964f-4031-a53b-f132434573e8</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -13898,7 +13898,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Discharge Time Series (2013-2017) – Calvert Island - Archived Version 3.0</t>
+          <t>Ecosystem Comparison Plots - Calvert Island</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Geospatial, Watersheds</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13903808593744, 51.626542529786036], [-127.97355651855466, 51.626542529786036], [-127.97355651855466, 51.67766477883444], [-128.13903808593744, 51.67766477883444], [-128.13903808593744, 51.626542529786036]]]}</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -13959,12 +13959,12 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>10.21966/sbyc-d030</t>
+          <t>10.21966/1.56481</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUdGRGRjUW9LRnBVNVI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWc4TU94c2lwT0tYa2U</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
@@ -13974,18 +13974,18 @@
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V125" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="W125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -13995,12 +13995,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ca-cioos_26443ab2-964f-4031-a53b-f132434573e8</t>
+          <t>ca-cioos_23bc8c35-2e4e-4382-9296-a52d5ea49889</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Ecosystem Comparison Plots - Calvert Island</t>
+          <t>Discharge Time Series (2013-2017) – Calvert Island - Archived Version 3.0</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -14028,7 +14028,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Geospatial, Watersheds</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13903808593744, 51.626542529786036], [-127.97355651855466, 51.626542529786036], [-127.97355651855466, 51.67766477883444], [-128.13903808593744, 51.67766477883444], [-128.13903808593744, 51.626542529786036]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -14071,12 +14071,12 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>10.21966/1.56481</t>
+          <t>10.21966/sbyc-d030</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWc4TU94c2lwT0tYa2U</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUdGRGRjUW9LRnBVNVI</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
@@ -14086,18 +14086,18 @@
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="V126" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="W126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -14655,12 +14655,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>ca-cioos_765d00bb-beec-486c-bd00-e27f972b7324</t>
+          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -14670,7 +14670,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Microbial activity and carbon fluxes in rainforest soil – Tsunami Hill, Calvert Island – June 2015 - April 2016</t>
+          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -14688,7 +14688,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Genomics, Watersheds</t>
+          <t>Watersheds, Oceanography</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -14706,37 +14706,33 @@
           <t>dataset</t>
         </is>
       </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>University of British Columbia</t>
-        </is>
-      </c>
+      <c r="M132" t="inlineStr"/>
       <c r="N132" t="n">
         <v>1</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13650264, 51.64966999], [-128.12495841, 51.64966999], [-128.12495841, 51.65523482], [-128.13650264, 51.65523482], [-128.13650264, 51.64966999]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>10.21966/1.715630</t>
+          <t>10.21966/66x5-a210</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUE0SHdBOUNiWjU5bFY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
         </is>
       </c>
       <c r="T132" t="inlineStr">
@@ -14746,11 +14742,11 @@
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="V132" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W132" t="n">
         <v>0</v>
@@ -14767,12 +14763,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
+          <t>ca-cioos_765d00bb-beec-486c-bd00-e27f972b7324</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -14782,7 +14778,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada</t>
+          <t>Microbial activity and carbon fluxes in rainforest soil – Tsunami Hill, Calvert Island – June 2015 - April 2016</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -14800,7 +14796,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Watersheds, Oceanography</t>
+          <t>Genomics, Watersheds</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -14818,33 +14814,37 @@
           <t>dataset</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>University of British Columbia</t>
+        </is>
+      </c>
       <c r="N133" t="n">
         <v>1</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13650264, 51.64966999], [-128.12495841, 51.64966999], [-128.12495841, 51.65523482], [-128.13650264, 51.65523482], [-128.13650264, 51.64966999]]]}</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>10.21966/66x5-a210</t>
+          <t>10.21966/1.715630</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUE0SHdBOUNiWjU5bFY</t>
         </is>
       </c>
       <c r="T133" t="inlineStr">
@@ -14854,11 +14854,11 @@
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="V133" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W133" t="n">
         <v>0</v>

--- a/main/catalog_summary.xlsx
+++ b/main/catalog_summary.xlsx
@@ -1847,12 +1847,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ca-cioos_ab901b46-43f6-4044-b0c3-b5fd825622f4</t>
+          <t>ca-cioos_af65bf72-27af-4747-8911-ab05591762ac</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>World View 2 Imagery - Coverage of three regions of the BC Central Coast - Summer 2014, 2015, &amp; 2016</t>
+          <t>Kelp forest communities along an otter gradient</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>underDevelopment</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Simon Fraser University</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1908,27 +1908,23 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.61145019531247, 51.61801654877371], [-127.91931152343746, 51.61801654877371], [-127.91931152343746, 52.11325243469631], [-128.61145019531247, 52.11325243469631], [-128.61145019531247, 51.61801654877371]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.770751953125, 51.33404377878941], [-127.74902343749999, 51.33404377878941], [-127.74902343749999, 52.19077237113535], [-128.770751953125, 52.19077237113535], [-128.770751953125, 51.33404377878941]]]}</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '50.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>10.21966/nmds-rx42</t>
-        </is>
-      </c>
+          <t>other, invertebrateAbundanceAndDistribution, fishAbundanceAndDistribution</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXp1R01BNWFYV0RkUEY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXlMbjJYUlpvZFpITks</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -1938,18 +1934,14 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>3</v>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1957,12 +1949,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ca-cioos_af65bf72-27af-4747-8911-ab05591762ac</t>
+          <t>ca-cioos_ab901b46-43f6-4044-b0c3-b5fd825622f4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1972,7 +1964,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kelp forest communities along an otter gradient</t>
+          <t>World View 2 Imagery - Coverage of three regions of the BC Central Coast - Summer 2014, 2015, &amp; 2016</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1990,12 +1982,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>underDevelopment</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2010,7 +2002,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Simon Fraser University</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -2018,23 +2010,27 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.770751953125, 51.33404377878941], [-127.74902343749999, 51.33404377878941], [-127.74902343749999, 52.19077237113535], [-128.770751953125, 52.19077237113535], [-128.770751953125, 51.33404377878941]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.61145019531247, 51.61801654877371], [-127.91931152343746, 51.61801654877371], [-127.91931152343746, 52.11325243469631], [-128.61145019531247, 52.11325243469631], [-128.61145019531247, 51.61801654877371]]]}</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>[{'max': '50.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>other, invertebrateAbundanceAndDistribution, fishAbundanceAndDistribution</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>10.21966/nmds-rx42</t>
+        </is>
+      </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXlMbjJYUlpvZFpITks</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXp1R01BNWFYV0RkUEY</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -2044,14 +2040,18 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="V15" t="n">
-        <v>3</v>
-      </c>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -4338,7 +4338,7 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W36" t="n">
         <v>0</v>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
+          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
+          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -8756,7 +8756,11 @@
       <c r="H77" t="b">
         <v>0</v>
       </c>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Airborne Coastal Observatory</t>
+        </is>
+      </c>
       <c r="J77" t="inlineStr">
         <is>
           <t>completed</t>
@@ -8782,12 +8786,12 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -8798,7 +8802,7 @@
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -8812,7 +8816,7 @@
         </is>
       </c>
       <c r="V77" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
@@ -8823,12 +8827,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
+          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -8838,7 +8842,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
+          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8854,11 +8858,7 @@
       <c r="H78" t="b">
         <v>0</v>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Airborne Coastal Observatory</t>
-        </is>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>completed</t>
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -8900,7 +8900,7 @@
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -8914,7 +8914,7 @@
         </is>
       </c>
       <c r="V78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
@@ -11623,12 +11623,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ca-cioos_51171738-7556-48f1-8757-658d99fa25dd</t>
+          <t>ca-cioos_4fac74c8-f58c-46b0-87dc-ab70ce756880</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -11638,7 +11638,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Eelgrass Extent 2014 - Central Coast</t>
+          <t>Discovery Islands LiDAR Dataset  - 2014 - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -11654,7 +11654,11 @@
       <c r="H104" t="b">
         <v>0</v>
       </c>
-      <c r="I104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Geospatial</t>
+        </is>
+      </c>
       <c r="J104" t="inlineStr">
         <is>
           <t>completed</t>
@@ -11676,16 +11680,16 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4878540039062, 51.653814904471545], [-128.0978393554687, 51.653814904471545], [-128.0978393554687, 52.07950600379698], [-128.4878540039062, 52.07950600379698], [-128.4878540039062, 51.653814904471545]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.3704833984375, 49.9229354544957], [-124.75524902343749, 49.9229354544957], [-124.75524902343749, 50.291094042311386], [-125.3704833984375, 50.291094042311386], [-125.3704833984375, 49.9229354544957]]]}</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>[{'max': '50.0', 'min': '0.0'}]</t>
+          <t>[{'max': '500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -11696,7 +11700,7 @@
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUZuOThkU2QzakpPNEQ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXR6SWM4aTRoYk9MeU0</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
@@ -11706,11 +11710,11 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="V104" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W104" t="inlineStr"/>
       <c r="X104" t="inlineStr"/>
@@ -11721,12 +11725,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ca-cioos_4fac74c8-f58c-46b0-87dc-ab70ce756880</t>
+          <t>ca-cioos_51171738-7556-48f1-8757-658d99fa25dd</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -11736,7 +11740,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Discovery Islands LiDAR Dataset  - 2014 - British Columbia - Canada</t>
+          <t>Eelgrass Extent 2014 - Central Coast</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -11752,11 +11756,7 @@
       <c r="H105" t="b">
         <v>0</v>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>Geospatial</t>
-        </is>
-      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
           <t>completed</t>
@@ -11778,16 +11778,16 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.3704833984375, 49.9229354544957], [-124.75524902343749, 49.9229354544957], [-124.75524902343749, 50.291094042311386], [-125.3704833984375, 50.291094042311386], [-125.3704833984375, 49.9229354544957]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4878540039062, 51.653814904471545], [-128.0978393554687, 51.653814904471545], [-128.0978393554687, 52.07950600379698], [-128.4878540039062, 52.07950600379698], [-128.4878540039062, 51.653814904471545]]]}</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>[{'max': '500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '50.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -11798,7 +11798,7 @@
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXR6SWM4aTRoYk9MeU0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUZuOThkU2QzakpPNEQ</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
@@ -11808,11 +11808,11 @@
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V105" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W105" t="inlineStr"/>
       <c r="X105" t="inlineStr"/>
@@ -13223,12 +13223,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
+          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -13238,7 +13238,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019 Version 4.1</t>
+          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -13261,7 +13261,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -13280,11 +13280,11 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>10.21966/zvwf-qn04</t>
+          <t>10.21966/XNH1-TP28</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
         </is>
       </c>
       <c r="T119" t="inlineStr">
@@ -13314,18 +13314,16 @@
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="V119" t="n">
-        <v>5</v>
-      </c>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr"/>
       <c r="W119" t="n">
         <v>1</v>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 1}]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -13335,12 +13333,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
+          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -13350,7 +13348,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
+          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019 Version 4.1</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -13373,7 +13371,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -13392,11 +13390,11 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -13411,12 +13409,12 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>10.21966/XNH1-TP28</t>
+          <t>10.21966/zvwf-qn04</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
@@ -13426,16 +13424,18 @@
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="V120" t="inlineStr"/>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="V120" t="n">
+        <v>5</v>
+      </c>
       <c r="W120" t="n">
         <v>1</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[{'year': '2025', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -13883,12 +13883,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
+          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ca-cioos_26443ab2-964f-4031-a53b-f132434573e8</t>
+          <t>ca-cioos_23bc8c35-2e4e-4382-9296-a52d5ea49889</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -13898,7 +13898,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Ecosystem Comparison Plots - Calvert Island</t>
+          <t>Discharge Time Series (2013-2017) – Calvert Island - Archived Version 3.0</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Geospatial, Watersheds</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13903808593744, 51.626542529786036], [-127.97355651855466, 51.626542529786036], [-127.97355651855466, 51.67766477883444], [-128.13903808593744, 51.67766477883444], [-128.13903808593744, 51.626542529786036]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -13959,12 +13959,12 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>10.21966/1.56481</t>
+          <t>10.21966/sbyc-d030</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWc4TU94c2lwT0tYa2U</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUdGRGRjUW9LRnBVNVI</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
@@ -13974,18 +13974,18 @@
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="V125" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="W125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -13995,12 +13995,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>38fabad7-d7d2-405f-aa4c-592ef064895f</t>
+          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ca-cioos_23bc8c35-2e4e-4382-9296-a52d5ea49889</t>
+          <t>ca-cioos_26443ab2-964f-4031-a53b-f132434573e8</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Discharge Time Series (2013-2017) – Calvert Island - Archived Version 3.0</t>
+          <t>Ecosystem Comparison Plots - Calvert Island</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -14028,7 +14028,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Geospatial, Watersheds</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13903808593744, 51.626542529786036], [-127.97355651855466, 51.626542529786036], [-127.97355651855466, 51.67766477883444], [-128.13903808593744, 51.67766477883444], [-128.13903808593744, 51.626542529786036]]]}</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -14071,12 +14071,12 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>10.21966/sbyc-d030</t>
+          <t>10.21966/1.56481</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUdGRGRjUW9LRnBVNVI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWc4TU94c2lwT0tYa2U</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
@@ -14086,18 +14086,18 @@
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V126" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="W126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
         </is>
       </c>
       <c r="V176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W176" t="n">
         <v>0</v>

--- a/main/catalog_summary.xlsx
+++ b/main/catalog_summary.xlsx
@@ -1847,12 +1847,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ca-cioos_af65bf72-27af-4747-8911-ab05591762ac</t>
+          <t>ca-cioos_ab901b46-43f6-4044-b0c3-b5fd825622f4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kelp forest communities along an otter gradient</t>
+          <t>World View 2 Imagery - Coverage of three regions of the BC Central Coast - Summer 2014, 2015, &amp; 2016</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>underDevelopment</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Simon Fraser University</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1908,23 +1908,27 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.770751953125, 51.33404377878941], [-127.74902343749999, 51.33404377878941], [-127.74902343749999, 52.19077237113535], [-128.770751953125, 52.19077237113535], [-128.770751953125, 51.33404377878941]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.61145019531247, 51.61801654877371], [-127.91931152343746, 51.61801654877371], [-127.91931152343746, 52.11325243469631], [-128.61145019531247, 52.11325243469631], [-128.61145019531247, 51.61801654877371]]]}</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>[{'max': '50.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>other, invertebrateAbundanceAndDistribution, fishAbundanceAndDistribution</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr"/>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>10.21966/nmds-rx42</t>
+        </is>
+      </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXlMbjJYUlpvZFpITks</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXp1R01BNWFYV0RkUEY</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -1934,14 +1938,18 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="V14" t="n">
-        <v>3</v>
-      </c>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1949,12 +1957,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ca-cioos_ab901b46-43f6-4044-b0c3-b5fd825622f4</t>
+          <t>ca-cioos_af65bf72-27af-4747-8911-ab05591762ac</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1964,7 +1972,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>World View 2 Imagery - Coverage of three regions of the BC Central Coast - Summer 2014, 2015, &amp; 2016</t>
+          <t>Kelp forest communities along an otter gradient</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1982,12 +1990,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>underDevelopment</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2002,7 +2010,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Simon Fraser University</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -2010,27 +2018,23 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.61145019531247, 51.61801654877371], [-127.91931152343746, 51.61801654877371], [-127.91931152343746, 52.11325243469631], [-128.61145019531247, 52.11325243469631], [-128.61145019531247, 51.61801654877371]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.770751953125, 51.33404377878941], [-127.74902343749999, 51.33404377878941], [-127.74902343749999, 52.19077237113535], [-128.770751953125, 52.19077237113535], [-128.770751953125, 51.33404377878941]]]}</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '50.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>10.21966/nmds-rx42</t>
-        </is>
-      </c>
+          <t>other, invertebrateAbundanceAndDistribution, fishAbundanceAndDistribution</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXp1R01BNWFYV0RkUEY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXlMbjJYUlpvZFpITks</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -2040,18 +2044,14 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>3</v>
+      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -4300,45 +4300,45 @@
         </is>
       </c>
       <c r="N36" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.34725189558227, 50.23307863302776], [-125.21060943952757, 50.23307863302776], [-125.21060943952757, 50.28641446558299], [-125.34725189558227, 50.28641446558299], [-125.34725189558227, 50.23307863302776]]]}</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>[{'max': '10.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>10.21966/1.346775</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWU1ek9Mc1IwTVhWcEo</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>2022-01-19</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="V36" t="n">
         <v>2</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.34725189558227, 50.23307863302776], [-125.21060943952757, 50.23307863302776], [-125.21060943952757, 50.28641446558299], [-125.34725189558227, 50.28641446558299], [-125.34725189558227, 50.23307863302776]]]}</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>[{'max': '10.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>10.21966/1.346775</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWU1ek9Mc1IwTVhWcEo</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>2022-01-19</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="V36" t="n">
-        <v>7</v>
       </c>
       <c r="W36" t="n">
         <v>0</v>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>High-resolution record of surface seawater CO2 content from December 2014 to April 2016 collected in Hyacinthe Bay, British Columbia, Canada. Version 1.0.</t>
+          <t>High-resolution record of surface seawater CO2 content from December 2014 to April 2016 collected in Hyacinthe Bay, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7246,7 +7246,7 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="V63" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
+          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
+          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -8756,11 +8756,7 @@
       <c r="H77" t="b">
         <v>0</v>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Airborne Coastal Observatory</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>completed</t>
@@ -8786,12 +8782,12 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -8802,7 +8798,7 @@
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -8816,7 +8812,7 @@
         </is>
       </c>
       <c r="V77" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
@@ -8827,12 +8823,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
+          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -8842,7 +8838,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
+          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8858,7 +8854,11 @@
       <c r="H78" t="b">
         <v>0</v>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Airborne Coastal Observatory</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr">
         <is>
           <t>completed</t>
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -8900,7 +8900,7 @@
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -8914,7 +8914,7 @@
         </is>
       </c>
       <c r="V78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
@@ -9835,7 +9835,9 @@
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="V87" t="inlineStr"/>
+      <c r="V87" t="n">
+        <v>1</v>
+      </c>
       <c r="W87" t="n">
         <v>0</v>
       </c>
@@ -11623,12 +11625,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ca-cioos_4fac74c8-f58c-46b0-87dc-ab70ce756880</t>
+          <t>ca-cioos_51171738-7556-48f1-8757-658d99fa25dd</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -11638,7 +11640,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Discovery Islands LiDAR Dataset  - 2014 - British Columbia - Canada</t>
+          <t>Eelgrass Extent 2014 - Central Coast</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -11654,11 +11656,7 @@
       <c r="H104" t="b">
         <v>0</v>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>Geospatial</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>completed</t>
@@ -11680,16 +11678,16 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.3704833984375, 49.9229354544957], [-124.75524902343749, 49.9229354544957], [-124.75524902343749, 50.291094042311386], [-125.3704833984375, 50.291094042311386], [-125.3704833984375, 49.9229354544957]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4878540039062, 51.653814904471545], [-128.0978393554687, 51.653814904471545], [-128.0978393554687, 52.07950600379698], [-128.4878540039062, 52.07950600379698], [-128.4878540039062, 51.653814904471545]]]}</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>[{'max': '500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '50.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -11700,7 +11698,7 @@
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXR6SWM4aTRoYk9MeU0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUZuOThkU2QzakpPNEQ</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
@@ -11710,11 +11708,11 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V104" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W104" t="inlineStr"/>
       <c r="X104" t="inlineStr"/>
@@ -11725,12 +11723,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ca-cioos_51171738-7556-48f1-8757-658d99fa25dd</t>
+          <t>ca-cioos_4fac74c8-f58c-46b0-87dc-ab70ce756880</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -11740,7 +11738,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Eelgrass Extent 2014 - Central Coast</t>
+          <t>Discovery Islands LiDAR Dataset  - 2014 - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -11756,7 +11754,11 @@
       <c r="H105" t="b">
         <v>0</v>
       </c>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Geospatial</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr">
         <is>
           <t>completed</t>
@@ -11778,16 +11780,16 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4878540039062, 51.653814904471545], [-128.0978393554687, 51.653814904471545], [-128.0978393554687, 52.07950600379698], [-128.4878540039062, 52.07950600379698], [-128.4878540039062, 51.653814904471545]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.3704833984375, 49.9229354544957], [-124.75524902343749, 49.9229354544957], [-124.75524902343749, 50.291094042311386], [-125.3704833984375, 50.291094042311386], [-125.3704833984375, 49.9229354544957]]]}</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>[{'max': '50.0', 'min': '0.0'}]</t>
+          <t>[{'max': '500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -11798,7 +11800,7 @@
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUZuOThkU2QzakpPNEQ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXR6SWM4aTRoYk9MeU0</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
@@ -11808,11 +11810,11 @@
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="V105" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W105" t="inlineStr"/>
       <c r="X105" t="inlineStr"/>
@@ -19410,7 +19412,7 @@
         </is>
       </c>
       <c r="V174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W174" t="n">
         <v>0</v>
@@ -19630,11 +19632,11 @@
       </c>
       <c r="U176" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="V176" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W176" t="n">
         <v>0</v>
@@ -25747,7 +25749,9 @@
           <t>2026-03-19</t>
         </is>
       </c>
-      <c r="V231" t="inlineStr"/>
+      <c r="V231" t="n">
+        <v>1</v>
+      </c>
       <c r="W231" t="n">
         <v>0</v>
       </c>
@@ -25970,7 +25974,7 @@
         </is>
       </c>
       <c r="V233" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W233" t="n">
         <v>0</v>

--- a/main/catalog_summary.xlsx
+++ b/main/catalog_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X264"/>
+  <dimension ref="A1:X266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="V58" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W58" t="n">
         <v>0</v>
@@ -7932,7 +7932,7 @@
         </is>
       </c>
       <c r="V69" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="W69" t="n">
         <v>0</v>
@@ -9741,12 +9741,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2fe3bd2a-973e-48db-a599-6d44ca1ef0ad</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ca-cioos_27ba6c11-2421-4e85-bc11-1c1083514ed9</t>
+          <t>ca-cioos_2a92ca16-f5c6-4362-acea-6bb5117b8d65</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Owikeno Lake Bathymetric Survey</t>
+          <t>Google Earth Engine Kelp Tool - Central Coast Output</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>software</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Hakai Geospatial</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N87" t="n">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.22312137, 51.63113942], [-126.67792484, 51.63113942], [-126.67792484, 51.7324654], [-127.22312137, 51.7324654], [-127.22312137, 51.63113942]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-130.35642493, 50.22213452], [-126.18162025, 50.22213452], [-126.18162025, 52.9911972], [-130.35642493, 52.9911972], [-130.35642493, 50.22213452]]]}</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -9817,12 +9817,12 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>10.21966/31db-5090</t>
+          <t>10.21966/yff8-2w22</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFqOFB5dmFHWXM5am0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFUcWNIVGxwZEVLNTE</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
@@ -9835,9 +9835,7 @@
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="V87" t="n">
-        <v>1</v>
-      </c>
+      <c r="V87" t="inlineStr"/>
       <c r="W87" t="n">
         <v>0</v>
       </c>
@@ -9853,12 +9851,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>2fe3bd2a-973e-48db-a599-6d44ca1ef0ad</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ca-cioos_2a92ca16-f5c6-4362-acea-6bb5117b8d65</t>
+          <t>ca-cioos_27ba6c11-2421-4e85-bc11-1c1083514ed9</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -9868,12 +9866,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Google Earth Engine Kelp Tool - Central Coast Output</t>
+          <t>Owikeno Lake Bathymetric Survey</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>dataset</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -9906,7 +9904,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Hakai Geospatial</t>
         </is>
       </c>
       <c r="N88" t="n">
@@ -9914,7 +9912,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-130.35642493, 50.22213452], [-126.18162025, 50.22213452], [-126.18162025, 52.9911972], [-130.35642493, 52.9911972], [-130.35642493, 50.22213452]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.22312137, 51.63113942], [-126.67792484, 51.63113942], [-126.67792484, 51.7324654], [-127.22312137, 51.7324654], [-127.22312137, 51.63113942]]]}</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -9929,12 +9927,12 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>10.21966/yff8-2w22</t>
+          <t>10.21966/31db-5090</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFUcWNIVGxwZEVLNTE</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFqOFB5dmFHWXM5am0</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
@@ -9947,7 +9945,9 @@
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="V88" t="inlineStr"/>
+      <c r="V88" t="n">
+        <v>1</v>
+      </c>
       <c r="W88" t="n">
         <v>0</v>
       </c>
@@ -10942,7 +10942,7 @@
         </is>
       </c>
       <c r="V97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W97" t="n">
         <v>0</v>
@@ -13208,7 +13208,7 @@
         </is>
       </c>
       <c r="V118" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W118" t="n">
         <v>0</v>
@@ -13225,12 +13225,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
+          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -13240,7 +13240,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
+          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019 Version 4.1</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -13263,7 +13263,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -13282,11 +13282,11 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>10.21966/XNH1-TP28</t>
+          <t>10.21966/zvwf-qn04</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
         </is>
       </c>
       <c r="T119" t="inlineStr">
@@ -13316,16 +13316,18 @@
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="V119" t="inlineStr"/>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="V119" t="n">
+        <v>5</v>
+      </c>
       <c r="W119" t="n">
         <v>1</v>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[{'year': '2025', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -13335,12 +13337,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
+          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -13350,7 +13352,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019 Version 4.1</t>
+          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -13373,7 +13375,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -13392,11 +13394,11 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -13411,12 +13413,12 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>10.21966/zvwf-qn04</t>
+          <t>10.21966/XNH1-TP28</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
@@ -13426,18 +13428,16 @@
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="V120" t="n">
-        <v>5</v>
-      </c>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr"/>
       <c r="W120" t="n">
         <v>1</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 1}]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -13980,7 +13980,7 @@
         </is>
       </c>
       <c r="V125" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W125" t="n">
         <v>0</v>
@@ -14204,7 +14204,7 @@
         </is>
       </c>
       <c r="V127" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W127" t="n">
         <v>3</v>
@@ -17074,7 +17074,7 @@
         </is>
       </c>
       <c r="V153" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="W153" t="n">
         <v>0</v>
@@ -17186,7 +17186,7 @@
         </is>
       </c>
       <c r="V154" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W154" t="n">
         <v>0</v>
@@ -19412,7 +19412,7 @@
         </is>
       </c>
       <c r="V174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W174" t="n">
         <v>0</v>
@@ -25749,9 +25749,7 @@
           <t>2026-03-19</t>
         </is>
       </c>
-      <c r="V231" t="n">
-        <v>1</v>
-      </c>
+      <c r="V231" t="inlineStr"/>
       <c r="W231" t="n">
         <v>0</v>
       </c>
@@ -25974,7 +25972,7 @@
         </is>
       </c>
       <c r="V233" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W233" t="n">
         <v>0</v>
@@ -29315,12 +29313,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>0cef18ab-cea6-4522-baba-1bcd73a30646</t>
+          <t>e1247209-cc26-4788-82a2-dd8a5c971e22</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>ca-cioos_66fbb7f5-3644-471a-95ee-f8d3758e888b</t>
+          <t>ca-cioos_2e5ddbaa-4f0c-4339-8595-1ddbd35c3df4</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -29330,7 +29328,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Mount Robson Aerial Photo and LiDAR Survey</t>
+          <t>Glacier and Icefield Aerial Surveys in British Columbia, Washington, and Alberta - 2025 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -29368,7 +29366,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Tula Foundation</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N264" t="n">
@@ -29376,12 +29374,12 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-119.3, 53.03], [-118.8, 53.03], [-118.8, 53.26], [-119.3, 53.26], [-119.3, 53.03]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.9263, 48.0077], [-112.7224, 48.0077], [-112.7224, 54.6673], [-127.9263, 54.6673], [-127.9263, 48.0077]]]}</t>
         </is>
       </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>[{'max': '3954.0', 'min': '800.0'}]</t>
+          <t>[{'max': '4019.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q264" t="inlineStr">
@@ -29391,18 +29389,22 @@
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>10.21966/w9n0-kn30</t>
+          <t>10.21966/n6ga-nc24</t>
         </is>
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICbtZXkj6anGvgB3Qi</t>
-        </is>
-      </c>
-      <c r="T264" t="inlineStr"/>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Ou3t_K6rGOHTMO67Xbq</t>
+        </is>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
       <c r="U264" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="V264" t="inlineStr"/>
@@ -29410,6 +29412,222 @@
         <v>0</v>
       </c>
       <c r="X264" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>263</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>5ac3ac5f-702e-43d8-bcb7-79f30c4d9e08</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>ca-cioos_656ea307-fed0-48ca-b5d8-1bc017dc52d2</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Botanical Beach - Juan de Fuca Provincial Park - Drone Mapping</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="H265" t="b">
+        <v>0</v>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>Geospatial</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="N265" t="n">
+        <v>1</v>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.45265489, 48.52152402], [-124.43377214, 48.52152402], [-124.43377214, 48.53061904], [-124.45265489, 48.53061904], [-124.45265489, 48.52152402]]]}</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>[{'max': '20.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R265" t="inlineStr">
+        <is>
+          <t>10.21966/kn3e-fn08</t>
+        </is>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUdvcmtQME1NZmdWcDY</t>
+        </is>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr"/>
+      <c r="W265" t="n">
+        <v>0</v>
+      </c>
+      <c r="X265" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>264</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>0cef18ab-cea6-4522-baba-1bcd73a30646</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>ca-cioos_66fbb7f5-3644-471a-95ee-f8d3758e888b</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Mount Robson Aerial Photo and LiDAR Survey</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="H266" t="b">
+        <v>0</v>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Airborne Coastal Observatory, Geospatial</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>Tula Foundation</t>
+        </is>
+      </c>
+      <c r="N266" t="n">
+        <v>1</v>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-119.3, 53.03], [-118.8, 53.03], [-118.8, 53.26], [-119.3, 53.26], [-119.3, 53.03]]]}</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>[{'max': '3954.0', 'min': '800.0'}]</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R266" t="inlineStr">
+        <is>
+          <t>10.21966/w9n0-kn30</t>
+        </is>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICbtZXkj6anGvgB3Qi</t>
+        </is>
+      </c>
+      <c r="T266" t="inlineStr"/>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="V266" t="inlineStr"/>
+      <c r="W266" t="n">
+        <v>0</v>
+      </c>
+      <c r="X266" t="inlineStr">
         <is>
           <t>[]</t>
         </is>

--- a/main/catalog_summary.xlsx
+++ b/main/catalog_summary.xlsx
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -732,11 +732,11 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
@@ -912,45 +912,45 @@
         </is>
       </c>
       <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>{'type': 'Point', 'coordinates': [-125.222, 50.116]}</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>[{'max': '2.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>seaSurfaceTemperature, inorganicCarbon, seaSurfaceSalinity</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>10.21966/ea8w-bf35</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MVOSTlh_rgekISRw3Q8</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2021-03-31</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
         <v>2</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>{'type': 'Point', 'coordinates': [-125.222, 50.116]}</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>[{'max': '2.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>seaSurfaceTemperature, inorganicCarbon, seaSurfaceSalinity</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>10.25921/v5j2-x847</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MVOSTlh_rgekISRw3Q8</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2021-03-31</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>6</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.25921/jq11-2268</t>
+          <t>10.21966/bn33-w557</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1058,18 +1058,16 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="V6" t="n">
-        <v>2</v>
-      </c>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1612,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V11" t="inlineStr"/>
@@ -1847,12 +1845,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
+          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ca-cioos_ab901b46-43f6-4044-b0c3-b5fd825622f4</t>
+          <t>ca-cioos_af65bf72-27af-4747-8911-ab05591762ac</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1862,7 +1860,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>World View 2 Imagery - Coverage of three regions of the BC Central Coast - Summer 2014, 2015, &amp; 2016</t>
+          <t>Kelp forest communities along an otter gradient</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1880,12 +1878,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>underDevelopment</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1900,7 +1898,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Simon Fraser University</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1908,27 +1906,23 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.61145019531247, 51.61801654877371], [-127.91931152343746, 51.61801654877371], [-127.91931152343746, 52.11325243469631], [-128.61145019531247, 52.11325243469631], [-128.61145019531247, 51.61801654877371]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.770751953125, 51.33404377878941], [-127.74902343749999, 51.33404377878941], [-127.74902343749999, 52.19077237113535], [-128.770751953125, 52.19077237113535], [-128.770751953125, 51.33404377878941]]]}</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '50.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>10.21966/nmds-rx42</t>
-        </is>
-      </c>
+          <t>other, invertebrateAbundanceAndDistribution, fishAbundanceAndDistribution</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXp1R01BNWFYV0RkUEY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXlMbjJYUlpvZFpITks</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -1938,18 +1932,14 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>3</v>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1957,12 +1947,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>f5d51d99-ce24-4713-a317-7927dd283f1a</t>
+          <t>0d9ca9c8-95b0-48db-87b9-7db8af77363e</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ca-cioos_af65bf72-27af-4747-8911-ab05591762ac</t>
+          <t>ca-cioos_ab901b46-43f6-4044-b0c3-b5fd825622f4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1972,7 +1962,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kelp forest communities along an otter gradient</t>
+          <t>World View 2 Imagery - Coverage of three regions of the BC Central Coast - Summer 2014, 2015, &amp; 2016</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1990,12 +1980,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>underDevelopment</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2010,7 +2000,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Simon Fraser University</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -2018,23 +2008,27 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.770751953125, 51.33404377878941], [-127.74902343749999, 51.33404377878941], [-127.74902343749999, 52.19077237113535], [-128.770751953125, 52.19077237113535], [-128.770751953125, 51.33404377878941]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.61145019531247, 51.61801654877371], [-127.91931152343746, 51.61801654877371], [-127.91931152343746, 52.11325243469631], [-128.61145019531247, 52.11325243469631], [-128.61145019531247, 51.61801654877371]]]}</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>[{'max': '50.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>other, invertebrateAbundanceAndDistribution, fishAbundanceAndDistribution</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>10.21966/nmds-rx42</t>
+        </is>
+      </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXlMbjJYUlpvZFpITks</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXp1R01BNWFYV0RkUEY</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -2044,14 +2038,18 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="V15" t="n">
-        <v>3</v>
-      </c>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2150,7 +2148,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V16" t="n">
@@ -6648,7 +6646,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>High-resolution record of surface seawater CO2 content from August 2016 to August 2017 collected in at the OceansAlaska shellfish hatchery in Ketchikan, Alaska, USA</t>
+          <t>High-resolution record of surface seawater CO2 content from August 2016 to August 2017 collected at the OceansAlaska shellfish hatchery in Ketchikan, Alaska, USA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6724,12 +6722,10 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="V58" t="n">
-        <v>7</v>
-      </c>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr"/>
       <c r="W58" t="n">
         <v>0</v>
       </c>
@@ -7928,11 +7924,11 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V69" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W69" t="n">
         <v>0</v>
@@ -8484,7 +8480,7 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V74" t="inlineStr"/>
@@ -9741,12 +9737,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
+          <t>2fe3bd2a-973e-48db-a599-6d44ca1ef0ad</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ca-cioos_2a92ca16-f5c6-4362-acea-6bb5117b8d65</t>
+          <t>ca-cioos_27ba6c11-2421-4e85-bc11-1c1083514ed9</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -9756,12 +9752,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Google Earth Engine Kelp Tool - Central Coast Output</t>
+          <t>Owikeno Lake Bathymetric Survey</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>dataset</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -9802,7 +9798,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-130.35642493, 50.22213452], [-126.18162025, 50.22213452], [-126.18162025, 52.9911972], [-130.35642493, 52.9911972], [-130.35642493, 50.22213452]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.22312137, 51.63113942], [-126.67792484, 51.63113942], [-126.67792484, 51.7324654], [-127.22312137, 51.7324654], [-127.22312137, 51.63113942]]]}</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -9817,12 +9813,12 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>10.21966/yff8-2w22</t>
+          <t>10.21966/31db-5090</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFUcWNIVGxwZEVLNTE</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFqOFB5dmFHWXM5am0</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
@@ -9832,10 +9828,12 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr"/>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="V87" t="n">
+        <v>1</v>
+      </c>
       <c r="W87" t="n">
         <v>0</v>
       </c>
@@ -9851,12 +9849,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2fe3bd2a-973e-48db-a599-6d44ca1ef0ad</t>
+          <t>571ef4fa-eda3-4e67-baae-2e9b5e598f56</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ca-cioos_27ba6c11-2421-4e85-bc11-1c1083514ed9</t>
+          <t>ca-cioos_2a92ca16-f5c6-4362-acea-6bb5117b8d65</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -9866,12 +9864,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Owikeno Lake Bathymetric Survey</t>
+          <t>Google Earth Engine Kelp Tool - Central Coast Output</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>software</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -9904,7 +9902,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Hakai Geospatial</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N88" t="n">
@@ -9912,7 +9910,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.22312137, 51.63113942], [-126.67792484, 51.63113942], [-126.67792484, 51.7324654], [-127.22312137, 51.7324654], [-127.22312137, 51.63113942]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-130.35642493, 50.22213452], [-126.18162025, 50.22213452], [-126.18162025, 52.9911972], [-130.35642493, 52.9911972], [-130.35642493, 50.22213452]]]}</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -9927,12 +9925,12 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>10.21966/31db-5090</t>
+          <t>10.21966/yff8-2w22</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFqOFB5dmFHWXM5am0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MTFUcWNIVGxwZEVLNTE</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
@@ -9945,9 +9943,7 @@
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="V88" t="n">
-        <v>1</v>
-      </c>
+      <c r="V88" t="inlineStr"/>
       <c r="W88" t="n">
         <v>0</v>
       </c>
@@ -10054,7 +10050,7 @@
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V89" t="n">
@@ -10166,7 +10162,7 @@
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V90" t="inlineStr"/>
@@ -10276,7 +10272,7 @@
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V91" t="n">
@@ -10388,7 +10384,7 @@
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V92" t="n">
@@ -10942,7 +10938,7 @@
         </is>
       </c>
       <c r="V97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W97" t="n">
         <v>0</v>
@@ -11050,7 +11046,7 @@
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V98" t="n">
@@ -13128,7 +13124,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 - Sept 2019 Version 5</t>
+          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 - Sept 2019</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -13204,12 +13200,10 @@
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="V118" t="n">
-        <v>7</v>
-      </c>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr"/>
       <c r="W118" t="n">
         <v>0</v>
       </c>
@@ -13538,7 +13532,7 @@
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V121" t="n">
@@ -13756,7 +13750,7 @@
         </is>
       </c>
       <c r="V123" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="W123" t="n">
         <v>0</v>
@@ -13868,7 +13862,7 @@
         </is>
       </c>
       <c r="V124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W124" t="n">
         <v>1</v>
@@ -13900,7 +13894,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Discharge Time Series (2013-2017) – Calvert Island - Archived Version 3.0</t>
+          <t>Discharge Time Series (2013-2017) – Calvert Island</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -13938,7 +13932,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>McGill University</t>
         </is>
       </c>
       <c r="N125" t="n">
@@ -13976,11 +13970,11 @@
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V125" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W125" t="n">
         <v>0</v>
@@ -14200,12 +14194,10 @@
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="V127" t="n">
-        <v>8</v>
-      </c>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr"/>
       <c r="W127" t="n">
         <v>3</v>
       </c>
@@ -14529,7 +14521,9 @@
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="V130" t="inlineStr"/>
+      <c r="V130" t="n">
+        <v>1</v>
+      </c>
       <c r="W130" t="n">
         <v>1</v>
       </c>
@@ -14640,7 +14634,7 @@
         </is>
       </c>
       <c r="V131" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W131" t="n">
         <v>1</v>
@@ -14708,7 +14702,11 @@
           <t>dataset</t>
         </is>
       </c>
-      <c r="M132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>Skeena Fisheries Commission</t>
+        </is>
+      </c>
       <c r="N132" t="n">
         <v>1</v>
       </c>
@@ -14744,11 +14742,11 @@
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V132" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="W132" t="n">
         <v>0</v>
@@ -14860,7 +14858,7 @@
         </is>
       </c>
       <c r="V133" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="W133" t="n">
         <v>0</v>
@@ -14968,7 +14966,7 @@
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V134" t="inlineStr"/>
@@ -15654,7 +15652,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Groundwater sampling in the Kwakshua Watersheds of Calvert and Hecate Islands, BC (2016-2019) - Version 1.0</t>
+          <t>Groundwater sampling in the Kwakshua Watersheds of Calvert and Hecate Islands, BC (2016-2019)</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -15730,11 +15728,11 @@
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V141" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W141" t="n">
         <v>1</v>
@@ -16066,11 +16064,11 @@
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V144" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W144" t="n">
         <v>0</v>
@@ -17070,12 +17068,10 @@
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
-        </is>
-      </c>
-      <c r="V153" t="n">
-        <v>9</v>
-      </c>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr"/>
       <c r="W153" t="n">
         <v>0</v>
       </c>
@@ -17182,12 +17178,10 @@
       </c>
       <c r="U154" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
-        </is>
-      </c>
-      <c r="V154" t="n">
-        <v>7</v>
-      </c>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr"/>
       <c r="W154" t="n">
         <v>0</v>
       </c>
@@ -17696,7 +17690,7 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
@@ -17730,7 +17724,7 @@
       </c>
       <c r="U159" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V159" t="n">
@@ -18848,11 +18842,11 @@
       </c>
       <c r="U169" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V169" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W169" t="n">
         <v>0</v>
@@ -19169,7 +19163,7 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>10.5281/zenodo.4005400</t>
+          <t>10.21966/54tw-kh93</t>
         </is>
       </c>
       <c r="S172" t="inlineStr">
@@ -19184,18 +19178,18 @@
       </c>
       <c r="U172" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V172" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="W172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X172" t="inlineStr">
         <is>
-          <t>[{'year': '2024', 'total': 2}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -19970,7 +19964,7 @@
         </is>
       </c>
       <c r="V179" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W179" t="n">
         <v>1</v>
@@ -22306,7 +22300,7 @@
       </c>
       <c r="U200" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V200" t="inlineStr"/>
@@ -23628,7 +23622,7 @@
       </c>
       <c r="U212" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V212" t="inlineStr"/>

--- a/main/catalog_summary.xlsx
+++ b/main/catalog_summary.xlsx
@@ -13219,12 +13219,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
+          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -13234,7 +13234,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019 Version 4.1</t>
+          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -13276,11 +13276,11 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -13295,12 +13295,12 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>10.21966/zvwf-qn04</t>
+          <t>10.21966/XNH1-TP28</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
         </is>
       </c>
       <c r="T119" t="inlineStr">
@@ -13310,18 +13310,16 @@
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="V119" t="n">
-        <v>5</v>
-      </c>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr"/>
       <c r="W119" t="n">
         <v>1</v>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 1}]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -13331,12 +13329,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
+          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -13346,7 +13344,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
+          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019 Version 4.1</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -13369,7 +13367,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -13388,11 +13386,11 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -13407,12 +13405,12 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>10.21966/XNH1-TP28</t>
+          <t>10.21966/zvwf-qn04</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
@@ -13422,16 +13420,18 @@
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="V120" t="inlineStr"/>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="V120" t="n">
+        <v>5</v>
+      </c>
       <c r="W120" t="n">
         <v>1</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[{'year': '2025', 'total': 1}]</t>
         </is>
       </c>
     </row>

--- a/main/catalog_summary.xlsx
+++ b/main/catalog_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X265"/>
+  <dimension ref="A1:X266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1061,7 +1061,9 @@
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
@@ -2590,7 +2592,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
@@ -3136,7 +3138,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
@@ -7494,7 +7496,7 @@
         </is>
       </c>
       <c r="V65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W65" t="inlineStr"/>
       <c r="X65" t="inlineStr"/>
@@ -7596,7 +7598,7 @@
         </is>
       </c>
       <c r="V66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W66" t="inlineStr"/>
       <c r="X66" t="inlineStr"/>
@@ -8719,12 +8721,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
+          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
+          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -8734,7 +8736,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
+          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -8750,7 +8752,11 @@
       <c r="H77" t="b">
         <v>0</v>
       </c>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Airborne Coastal Observatory</t>
+        </is>
+      </c>
       <c r="J77" t="inlineStr">
         <is>
           <t>completed</t>
@@ -8776,12 +8782,12 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -8792,7 +8798,7 @@
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -8806,7 +8812,7 @@
         </is>
       </c>
       <c r="V77" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
@@ -8817,12 +8823,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>92e1c9df-0419-4d91-93c2-b9c85f4ce74e</t>
+          <t>8a71bb9f-e419-42aa-9ed7-f891631314a5</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ca-cioos_0f524f76-a88b-4e0a-9c3c-ee83114c3679</t>
+          <t>ca-cioos_0ebfdd89-61d6-453c-870a-83167617b26a</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -8832,7 +8838,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Gitanyow Archaeology, Cranberry Junction - 2020 - Airborne Coastal Observatory</t>
+          <t>Glacier and Icefield Mapping - British Columbia - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8848,11 +8854,7 @@
       <c r="H78" t="b">
         <v>0</v>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Airborne Coastal Observatory</t>
-        </is>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>completed</t>
@@ -8878,12 +8880,12 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.0, 55.96], [-127.2, 55.96], [-127.2, 56.36], [-128.0, 56.36], [-128.0, 55.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.4, 48.85], [-114.4, 48.85], [-114.4, 55.75], [-127.4, 55.75], [-127.4, 48.85]]]}</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -8894,7 +8896,7 @@
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MiNpB5mjvTnWKqOFiq-</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -8908,7 +8910,7 @@
         </is>
       </c>
       <c r="V78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
@@ -9217,12 +9219,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
+          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ca-cioos_c3958106-fc49-44bd-8227-bfc3e8bcb58c</t>
+          <t>ca-cioos_bb59cb9e-887a-40a3-b41a-f4a5b2263ce6</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -9232,7 +9234,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Moore Island Archaeology Survey - 2019 - Airborne Coastal Observatory</t>
+          <t>Fountain Valley LiDAR Data - 2019 &amp; 2020 - Hakai Airborne Coastal Observatory - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -9248,11 +9250,7 @@
       <c r="H82" t="b">
         <v>0</v>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>Airborne Coastal Observatory</t>
-        </is>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>completed</t>
@@ -9278,12 +9276,12 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.5, 52.65], [-129.4, 52.65], [-129.4, 52.7], [-129.5, 52.7], [-129.5, 52.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.0, 50.56], [-121.7, 50.56], [-121.7, 50.8], [-122.0, 50.8], [-122.0, 50.56]]]}</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>[{'max': '150.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
@@ -9291,14 +9289,10 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>10.21966/wfcv-n753</t>
-        </is>
-      </c>
+      <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6MBp3WwVTVbFK-0kv</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MmUnbGWVNvtiQAsYVPj</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
@@ -9312,16 +9306,10 @@
         </is>
       </c>
       <c r="V82" t="n">
-        <v>3</v>
-      </c>
-      <c r="W82" t="n">
-        <v>0</v>
-      </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9329,12 +9317,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5b78f1a7-6adb-4610-9ebe-019c3da65ae8</t>
+          <t>281d7444-efa6-4b18-ac0a-55c8f8b484be</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ca-cioos_bb59cb9e-887a-40a3-b41a-f4a5b2263ce6</t>
+          <t>ca-cioos_c3958106-fc49-44bd-8227-bfc3e8bcb58c</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -9344,7 +9332,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Fountain Valley LiDAR Data - 2019 &amp; 2020 - Hakai Airborne Coastal Observatory - British Columbia - Canada</t>
+          <t>Moore Island Archaeology Survey - 2019 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -9360,7 +9348,11 @@
       <c r="H83" t="b">
         <v>0</v>
       </c>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Airborne Coastal Observatory</t>
+        </is>
+      </c>
       <c r="J83" t="inlineStr">
         <is>
           <t>completed</t>
@@ -9386,12 +9378,12 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.0, 50.56], [-121.7, 50.56], [-121.7, 50.8], [-122.0, 50.8], [-122.0, 50.56]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.5, 52.65], [-129.4, 52.65], [-129.4, 52.7], [-129.5, 52.7], [-129.5, 52.65]]]}</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>[{'max': '1500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '150.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -9399,10 +9391,14 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr"/>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>10.21966/wfcv-n753</t>
+        </is>
+      </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MmUnbGWVNvtiQAsYVPj</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Mj6MBp3WwVTVbFK-0kv</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
@@ -9416,10 +9412,16 @@
         </is>
       </c>
       <c r="V83" t="n">
-        <v>4</v>
-      </c>
-      <c r="W83" t="inlineStr"/>
-      <c r="X83" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="W83" t="n">
+        <v>0</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -11619,12 +11621,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ca-cioos_51171738-7556-48f1-8757-658d99fa25dd</t>
+          <t>ca-cioos_4fac74c8-f58c-46b0-87dc-ab70ce756880</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -11634,7 +11636,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Eelgrass Extent 2014 - Central Coast</t>
+          <t>Discovery Islands LiDAR Dataset  - 2014 - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -11650,7 +11652,11 @@
       <c r="H104" t="b">
         <v>0</v>
       </c>
-      <c r="I104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Geospatial</t>
+        </is>
+      </c>
       <c r="J104" t="inlineStr">
         <is>
           <t>completed</t>
@@ -11672,16 +11678,16 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4878540039062, 51.653814904471545], [-128.0978393554687, 51.653814904471545], [-128.0978393554687, 52.07950600379698], [-128.4878540039062, 52.07950600379698], [-128.4878540039062, 51.653814904471545]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.3704833984375, 49.9229354544957], [-124.75524902343749, 49.9229354544957], [-124.75524902343749, 50.291094042311386], [-125.3704833984375, 50.291094042311386], [-125.3704833984375, 49.9229354544957]]]}</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>[{'max': '50.0', 'min': '0.0'}]</t>
+          <t>[{'max': '500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -11692,7 +11698,7 @@
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUZuOThkU2QzakpPNEQ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXR6SWM4aTRoYk9MeU0</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
@@ -11702,11 +11708,11 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="V104" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W104" t="inlineStr"/>
       <c r="X104" t="inlineStr"/>
@@ -11717,12 +11723,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ca-cioos_4fac74c8-f58c-46b0-87dc-ab70ce756880</t>
+          <t>ca-cioos_51171738-7556-48f1-8757-658d99fa25dd</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -11732,7 +11738,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Discovery Islands LiDAR Dataset  - 2014 - British Columbia - Canada</t>
+          <t>Eelgrass Extent 2014 - Central Coast</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -11748,11 +11754,7 @@
       <c r="H105" t="b">
         <v>0</v>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>Geospatial</t>
-        </is>
-      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
           <t>completed</t>
@@ -11774,16 +11776,16 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.3704833984375, 49.9229354544957], [-124.75524902343749, 49.9229354544957], [-124.75524902343749, 50.291094042311386], [-125.3704833984375, 50.291094042311386], [-125.3704833984375, 49.9229354544957]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4878540039062, 51.653814904471545], [-128.0978393554687, 51.653814904471545], [-128.0978393554687, 52.07950600379698], [-128.4878540039062, 52.07950600379698], [-128.4878540039062, 51.653814904471545]]]}</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>[{'max': '500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '50.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -11794,7 +11796,7 @@
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXR6SWM4aTRoYk9MeU0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUZuOThkU2QzakpPNEQ</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
@@ -11804,11 +11806,11 @@
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V105" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W105" t="inlineStr"/>
       <c r="X105" t="inlineStr"/>
@@ -13217,12 +13219,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
+          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
+          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -13232,7 +13234,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
+          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019 Version 4.1</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -13255,7 +13257,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -13274,11 +13276,11 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -13293,12 +13295,12 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>10.21966/XNH1-TP28</t>
+          <t>10.21966/zvwf-qn04</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
         </is>
       </c>
       <c r="T119" t="inlineStr">
@@ -13308,16 +13310,18 @@
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="V119" t="inlineStr"/>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="V119" t="n">
+        <v>5</v>
+      </c>
       <c r="W119" t="n">
         <v>1</v>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[{'year': '2025', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -13327,12 +13331,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>67871f51-9f69-44f6-9206-747e4d2a1553</t>
+          <t>55826c6b-772a-45b4-a869-b97a4774e232</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ca-cioos_ed3c5cb4-e6b0-4c8a-808e-3583a9a6cfde</t>
+          <t>ca-cioos_ef59cc12-5031-4c65-b379-7ca03ad76d34</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -13342,7 +13346,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Observed stream flow from seven small coastal watersheds in British Columbia, Canada, Sept 2013 – April 2019 Version 4.1</t>
+          <t>Precipitation time-series – Central Coast and Quadra Island – 2013 - 2019 Version 1.0</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -13365,7 +13369,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -13384,11 +13388,11 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13265424, 51.60936247], [-127.95907025, 51.60936247], [-127.95907025, 51.69558793], [-128.13265424, 51.69558793], [-128.13265424, 51.60936247]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.35114344, 51.37506462], [-127.65170145, 51.37506462], [-127.65170145, 51.8069493], [-128.35114344, 51.8069493], [-128.35114344, 51.37506462]]]}</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -13403,12 +13407,12 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>10.21966/zvwf-qn04</t>
+          <t>10.21966/XNH1-TP28</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MU1zSkI4S24ySE1rMGI</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUh2UDc1YkRVdUxzOVc</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
@@ -13418,18 +13422,16 @@
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="V120" t="n">
-        <v>5</v>
-      </c>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr"/>
       <c r="W120" t="n">
         <v>1</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 1}]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -14649,12 +14651,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
+          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>ca-cioos_765d00bb-beec-486c-bd00-e27f972b7324</t>
+          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -14664,7 +14666,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Microbial activity and carbon fluxes in rainforest soil – Tsunami Hill, Calvert Island – June 2015 - April 2016</t>
+          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -14682,7 +14684,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Genomics, Watersheds</t>
+          <t>Watersheds, Oceanography</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -14702,7 +14704,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>University of British Columbia</t>
+          <t>Skeena Fisheries Commission</t>
         </is>
       </c>
       <c r="N132" t="n">
@@ -14710,27 +14712,27 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.13650264, 51.64966999], [-128.12495841, 51.64966999], [-128.12495841, 51.65523482], [-128.13650264, 51.65523482], [-128.13650264, 51.64966999]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, dissolvedOrganicCarbon</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>10.21966/1.715630</t>
+          <t>10.21966/66x5-a210</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUE0SHdBOUNiWjU5bFY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
         </is>
       </c>
       <c r="T132" t="inlineStr">
@@ -14740,10 +14742,12 @@
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="V132" t="inlineStr"/>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="V132" t="n">
+        <v>1</v>
+      </c>
       <c r="W132" t="n">
         <v>0</v>
       </c>
@@ -14759,12 +14763,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>41e0fbeb-9e27-429c-84ea-7bb1be3f2a0d</t>
+          <t>9a930f50-82e2-4d7c-9686-6b551b9a458e</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ca-cioos_74f47ab6-a1ca-4aef-9115-cf2baaf87bef</t>
+          <t>ca-cioos_765d00bb-beec-486c-bd00-e27f972b7324</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -14774,7 +14778,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Dissolved and particulate organic carbon chemistry for freshwater and marine stations from 2014 through 2016 on Calvert and Hecate Islands, British Columbia, Canada</t>
+          <t>Microbial activity and carbon fluxes in rainforest soil – Tsunami Hill, Calvert Island – June 2015 - April 2016</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -14792,7 +14796,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Watersheds, Oceanography</t>
+          <t>Genomics, Watersheds</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -14812,7 +14816,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Skeena Fisheries Commission</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="N133" t="n">
@@ -14820,27 +14824,27 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.23772561, 51.55090182], [-127.87151456, 51.55090182], [-127.87151456, 51.75810598], [-128.23772561, 51.75810598], [-128.23772561, 51.55090182]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13650264, 51.64966999], [-128.12495841, 51.64966999], [-128.12495841, 51.65523482], [-128.13650264, 51.65523482], [-128.13650264, 51.64966999]]]}</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>other, dissolvedOrganicCarbon</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>10.21966/66x5-a210</t>
+          <t>10.21966/1.715630</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWFXb1lySHV6ZnY5ck0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUE0SHdBOUNiWjU5bFY</t>
         </is>
       </c>
       <c r="T133" t="inlineStr">
@@ -14850,12 +14854,10 @@
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="V133" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr"/>
       <c r="W133" t="n">
         <v>0</v>
       </c>
@@ -16296,7 +16298,7 @@
         </is>
       </c>
       <c r="V146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W146" t="n">
         <v>0</v>
@@ -17732,7 +17734,7 @@
         </is>
       </c>
       <c r="V159" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W159" t="n">
         <v>0</v>
@@ -18755,12 +18757,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
+          <t>96b5a7f2-5f23-413a-b060-d268bcff83ba</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>ca-cioos_12f951d4-4155-4c05-969d-a7158412f579</t>
+          <t>ca-cioos_4a09d56b-b120-46c8-9263-ae3c42a02e9b</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -18770,7 +18772,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Avian and paired Vegetation data from 100 Islands Project (BC Central Coast) Hakai Institute - 2015-2017</t>
+          <t>High-resolution time series of surface seawater CO2 content from the OceansAlaska Shellfish Hatchery in Ketchikan, Alaska, USA</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -18788,12 +18790,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Geospatial, 100 Islands</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -18812,45 +18814,45 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.60227432, 51.39074678], [-127.47434441, 51.39074678], [-127.47434441, 52.07117353], [-128.60227432, 52.07117353], [-128.60227432, 51.39074678]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-131.5954, 55.315]}</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '4.3', 'min': '4.3'}]</t>
         </is>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>other, marineTurtlesBirdsMammalsAbundanceAndDistribution</t>
+          <t>inorganicCarbon, seaSurfaceTemperature, seaSurfaceSalinity</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>10.21966/10tk-4956</t>
+          <t>10.25921/kmam-ct93</t>
         </is>
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUNJMG8wUVlZa1NiNUM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-NHZti4Qjk0UuD4Ocz77</t>
         </is>
       </c>
       <c r="T169" t="inlineStr">
         <is>
-          <t>2023-03-03</t>
+          <t>2023-01-24</t>
         </is>
       </c>
       <c r="U169" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V169" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W169" t="n">
         <v>0</v>
@@ -18867,12 +18869,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>3a8b11a2-5deb-469e-824b-32ab0eb5c2ca</t>
+          <t>79ace68f-f5a9-4224-8615-20fa255cb6d4</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>ca-cioos_251aef08-4017-4493-b9d8-c4583913b511</t>
+          <t>ca-cioos_12f951d4-4155-4c05-969d-a7158412f579</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -18882,7 +18884,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Remotely-Piloted Aerial Systems Imagery, Terrain Data, and Derivates - 100 Islands Project, Central Coast, BC, Canada</t>
+          <t>Avian and paired Vegetation data from 100 Islands Project (BC Central Coast) Hakai Institute - 2015-2017</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -18900,7 +18902,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Geospatial, 100 Islands</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -18924,31 +18926,31 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.7, 51.38], [-127.5, 51.38], [-127.5, 52.23], [-128.7, 52.23], [-128.7, 51.38]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.60227432, 51.39074678], [-127.47434441, 51.39074678], [-127.47434441, 52.07117353], [-128.60227432, 52.07117353], [-128.60227432, 51.39074678]]]}</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>[{'max': '200.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, marineTurtlesBirdsMammalsAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>10.21966/25ng-ar52</t>
+          <t>10.21966/10tk-4956</t>
         </is>
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DCH8GzsQKSM8xwJ8WdQFIZrtCaq2/-MnacSB0YNeFCB0Qmn2r</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUNJMG8wUVlZa1NiNUM</t>
         </is>
       </c>
       <c r="T170" t="inlineStr">
@@ -18958,7 +18960,7 @@
       </c>
       <c r="U170" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="V170" t="n">
@@ -18979,12 +18981,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
+          <t>3a8b11a2-5deb-469e-824b-32ab0eb5c2ca</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>ca-cioos_476204a7-0714-4755-953d-61fa3c5df497</t>
+          <t>ca-cioos_251aef08-4017-4493-b9d8-c4583913b511</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -18994,7 +18996,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Hakai Institute Nutrients (Dosser et al., 2021)</t>
+          <t>Remotely-Piloted Aerial Systems Imagery, Terrain Data, and Derivates - 100 Islands Project, Central Coast, BC, Canada</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -19012,7 +19014,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -19040,40 +19042,42 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.6, 50.69], [-126.3, 50.8], [-124.8, 50.44], [-123.9, 49.65], [-125.1, 49.65], [-127.6, 50.69]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.7, 51.38], [-127.5, 51.38], [-127.5, 52.23], [-128.7, 52.23], [-128.7, 51.38]]]}</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>[{'max': '500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '200.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>nutrients</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>10.21966/j3j5-wt70</t>
+          <t>10.21966/25ng-ar52</t>
         </is>
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/oOseiEWez6TzqPUIisEXczg6G8y2/-MoZtzH-n9LBy9Bn29Hl</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DCH8GzsQKSM8xwJ8WdQFIZrtCaq2/-MnacSB0YNeFCB0Qmn2r</t>
         </is>
       </c>
       <c r="T171" t="inlineStr">
         <is>
-          <t>2023-03-13</t>
+          <t>2023-03-03</t>
         </is>
       </c>
       <c r="U171" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="V171" t="inlineStr"/>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="V171" t="n">
+        <v>2</v>
+      </c>
       <c r="W171" t="n">
         <v>0</v>
       </c>
@@ -19201,12 +19205,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>5c2aac2c-0dd8-49d8-87b2-5c52b3d42946</t>
+          <t>75b60436-da51-4ccf-b14a-27f45f782b2b</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>ca-cioos_60f653ae-a3fd-484d-807c-3d7e4a0712cb</t>
+          <t>ca-cioos_476204a7-0714-4755-953d-61fa3c5df497</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -19216,7 +19220,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Biodiversity Surveys of the Gwaxdlala/Nalaxdlala Indigenous Protected and Conserved Area (IPCA) in Knight Inlet, British Columbia</t>
+          <t>Hakai Institute Nutrients (Dosser et al., 2021)</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -19234,12 +19238,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Nearshore, Genomics</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -19258,46 +19262,44 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.1, 50.65], [-125.7, 50.65], [-125.7, 50.71], [-126.1, 50.71], [-126.1, 50.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.6, 50.69], [-126.3, 50.8], [-124.8, 50.44], [-123.9, 49.65], [-125.1, 49.65], [-127.6, 50.69]]]}</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, macroalgalCanopyCoverAndComposition, invertebrateAbundanceAndDistribution, other</t>
+          <t>nutrients</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>10.21966/wabn-bq33</t>
+          <t>10.21966/j3j5-wt70</t>
         </is>
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/4TvAwNKXC7PkAi0TEZsZbbAzXfi1/-NOHQei0clSbCzMMFHdq</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/oOseiEWez6TzqPUIisEXczg6G8y2/-MoZtzH-n9LBy9Bn29Hl</t>
         </is>
       </c>
       <c r="T173" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2023-03-13</t>
         </is>
       </c>
       <c r="U173" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="V173" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr"/>
       <c r="W173" t="n">
         <v>0</v>
       </c>
@@ -19313,12 +19315,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
+          <t>5c2aac2c-0dd8-49d8-87b2-5c52b3d42946</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>ca-cioos_16ae186b-9d99-42cf-b18d-09f9bb0501d7</t>
+          <t>ca-cioos_60f653ae-a3fd-484d-807c-3d7e4a0712cb</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -19328,7 +19330,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Dataset for article: 'Migration timing affects the foraging ecology of Fraser River sockeye salmon stocks in coastal waters of British Columbia, Canada'</t>
+          <t>Biodiversity Surveys of the Gwaxdlala/Nalaxdlala Indigenous Protected and Conserved Area (IPCA) in Knight Inlet, British Columbia</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -19346,12 +19348,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Juvenile Salmon Program</t>
+          <t>Nearshore, Genomics</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -19366,45 +19368,45 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>University of British Columbia</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.2, 49.96], [-124.8, 50.0], [-125.2, 50.49], [-126.9, 50.72], [-127.0, 50.62], [-127.0, 50.58], [-126.8, 50.51], [-126.0, 50.39], [-125.5, 50.33], [-125.3, 50.06], [-125.2, 49.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.1, 50.65], [-125.7, 50.65], [-125.7, 50.71], [-126.1, 50.71], [-126.1, 50.65]]]}</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>[{'max': '9.0', 'min': '0.0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>zooplanktonBiomassAndDiversity, fishAbundanceAndDistribution, seaSurfaceTemperature, seaSurfaceSalinity</t>
+          <t>fishAbundanceAndDistribution, macroalgalCanopyCoverAndComposition, invertebrateAbundanceAndDistribution, other</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>10.21966/tmch-5606</t>
+          <t>10.21966/wabn-bq33</t>
         </is>
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/UTb9hNU3GJRK302QyaKNIvj2OiJ2/-NVeebS1ZbFsXi_w6LXR</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/4TvAwNKXC7PkAi0TEZsZbbAzXfi1/-NOHQei0clSbCzMMFHdq</t>
         </is>
       </c>
       <c r="T174" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="U174" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="V174" t="n">
@@ -19425,12 +19427,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
+          <t>b1c4c93b-6324-4b84-b341-76be046cbf28</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>ca-cioos_86343dd1-28d0-4d02-8eaf-402d51a7fef7</t>
+          <t>ca-cioos_16ae186b-9d99-42cf-b18d-09f9bb0501d7</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -19440,7 +19442,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Vertical Water Properties Profiles (CTD) from the Hakai Institute Juvenile Salmon Program, Provisional</t>
+          <t>Dataset for article: 'Migration timing affects the foraging ecology of Fraser River sockeye salmon stocks in coastal waters of British Columbia, Canada'</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -19478,45 +19480,45 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="N175" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.2, 49.92], [-124.6, 49.92], [-124.6, 50.8], [-127.2, 50.8], [-127.2, 49.92]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.2, 49.96], [-124.8, 50.0], [-125.2, 50.49], [-126.9, 50.72], [-127.0, 50.62], [-127.0, 50.58], [-126.8, 50.51], [-126.0, 50.39], [-125.5, 50.33], [-125.3, 50.06], [-125.2, 49.96]]]}</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>[{'max': '418.0', 'min': '0.0'}]</t>
+          <t>[{'max': '9.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>oxygen, particulateMatter, subSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, seaSurfaceTemperature</t>
+          <t>zooplanktonBiomassAndDiversity, fishAbundanceAndDistribution, seaSurfaceTemperature, seaSurfaceSalinity</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>10.21966/82q4-y443</t>
+          <t>10.21966/tmch-5606</t>
         </is>
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/UTb9hNU3GJRK302QyaKNIvj2OiJ2/-NcYL5JndZWMdXmXuFqB</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/UTb9hNU3GJRK302QyaKNIvj2OiJ2/-NVeebS1ZbFsXi_w6LXR</t>
         </is>
       </c>
       <c r="T175" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="U175" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="V175" t="n">
@@ -19537,12 +19539,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>e40c42ef-cabf-4969-aeb3-263407a91a68</t>
+          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>ca-cioos_b63374a9-2288-4512-9820-5d1b44d2b502</t>
+          <t>ca-cioos_86343dd1-28d0-4d02-8eaf-402d51a7fef7</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -19552,7 +19554,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Spatial extent of eelgrass (Zostera marina) meadows from monitoring sites within Gwaii Haanas (2016, 2017, 2018) mapped using remote piloted aerial systems</t>
+          <t>Vertical Water Properties Profiles (CTD) from the Hakai Institute Juvenile Salmon Program, Provisional</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -19562,7 +19564,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>CC-BY-NC-ND-4.0</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="H176" t="b">
@@ -19570,7 +19572,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Juvenile Salmon Program</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -19594,45 +19596,45 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-131.4, 52.75], [-131.7, 52.74], [-131.9, 52.58], [-131.6, 52.25], [-131.0, 51.89], [-130.9, 52.1], [-131.2, 52.52], [-131.4, 52.75]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.2, 49.92], [-124.6, 49.92], [-124.6, 50.8], [-127.2, 50.8], [-127.2, 49.92]]]}</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '418.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>seagrassCoverAndComposition</t>
+          <t>oxygen, particulateMatter, subSurfaceTemperature, subSurfaceSalinity, seaSurfaceSalinity, seaSurfaceTemperature</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>10.21966/gv88-hv41</t>
+          <t>10.21966/82q4-y443</t>
         </is>
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-NeEpZEr5wOQ_rWGa5CN</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/UTb9hNU3GJRK302QyaKNIvj2OiJ2/-NcYL5JndZWMdXmXuFqB</t>
         </is>
       </c>
       <c r="T176" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="U176" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="V176" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W176" t="n">
         <v>0</v>
@@ -19649,12 +19651,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>3f7bca49-27cf-4f39-9366-35808e82f2a8</t>
+          <t>e40c42ef-cabf-4969-aeb3-263407a91a68</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>ca-cioos_c074bff6-408b-443a-bdaf-4713f0eadb95</t>
+          <t>ca-cioos_b63374a9-2288-4512-9820-5d1b44d2b502</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -19664,7 +19666,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Mapping Canopy-Forming Kelps in the Northeast Pacific: A Guidebook for Decision-Makers and Practitioners</t>
+          <t>Spatial extent of eelgrass (Zostera marina) meadows from monitoring sites within Gwaii Haanas (2016, 2017, 2018) mapped using remote piloted aerial systems</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -19674,7 +19676,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>CC-BY-NC-4.0</t>
+          <t>CC-BY-NC-ND-4.0</t>
         </is>
       </c>
       <c r="H177" t="b">
@@ -19706,11 +19708,11 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-171.2, 55.45], [-151.0, 62.33], [-132.6, 61.34], [-133.0, 61.22], [-120.5, 47.26], [-106.4, 23.65], [-112.0, 21.38], [-138.4, 51.91], [-166.3, 50.7], [-182.6, 51.91], [-182.6, 51.91], [-171.2, 55.45]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-131.4, 52.75], [-131.7, 52.74], [-131.9, 52.58], [-131.6, 52.25], [-131.0, 51.89], [-130.9, 52.1], [-131.2, 52.52], [-131.4, 52.75]]]}</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
@@ -19720,22 +19722,22 @@
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>10.21966/7ze4-x883</t>
+          <t>10.21966/gv88-hv41</t>
         </is>
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-NaOChPRrsxKnkqLfBG8</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-NeEpZEr5wOQ_rWGa5CN</t>
         </is>
       </c>
       <c r="T177" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="U177" t="inlineStr">
@@ -19743,7 +19745,9 @@
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="V177" t="inlineStr"/>
+      <c r="V177" t="n">
+        <v>1</v>
+      </c>
       <c r="W177" t="n">
         <v>0</v>
       </c>
@@ -19759,12 +19763,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
+          <t>3f7bca49-27cf-4f39-9366-35808e82f2a8</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>ca-cioos_6c449900-c726-4e9a-b241-707711e253a7</t>
+          <t>ca-cioos_c074bff6-408b-443a-bdaf-4713f0eadb95</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -19774,7 +19778,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Hakai Institute Juvenile Salmon Program Time Series</t>
+          <t>Mapping Canopy-Forming Kelps in the Northeast Pacific: A Guidebook for Decision-Makers and Practitioners</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -19784,7 +19788,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>CC-BY-4.0</t>
+          <t>CC-BY-NC-4.0</t>
         </is>
       </c>
       <c r="H178" t="b">
@@ -19792,7 +19796,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Juvenile Salmon Program</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -19816,52 +19820,50 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.8232006, 49.89790212], [-124.67574133, 49.89790212], [-124.67574133, 50.73488305], [-126.8232006, 50.73488305], [-126.8232006, 49.89790212]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-171.2, 55.45], [-151.0, 62.33], [-132.6, 61.34], [-133.0, 61.22], [-120.5, 47.26], [-106.4, 23.65], [-112.0, 21.38], [-138.4, 51.91], [-166.3, 50.7], [-182.6, 51.91], [-182.6, 51.91], [-171.2, 55.45]]]}</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>[{'max': '9.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>10.21966/1.566666</t>
+          <t>10.21966/7ze4-x883</t>
         </is>
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXNUQUNpb1hBa0pYWVg</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-NaOChPRrsxKnkqLfBG8</t>
         </is>
       </c>
       <c r="T178" t="inlineStr">
         <is>
-          <t>2023-11-03</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="U178" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
-        </is>
-      </c>
-      <c r="V178" t="n">
-        <v>4</v>
-      </c>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr"/>
       <c r="W178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X178" t="inlineStr">
         <is>
-          <t>[{'year': '2024', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -19871,12 +19873,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>432b05ce-8904-4094-94bf-b97fb6636e41</t>
+          <t>16e0a0d9-b817-4d83-b9e0-e2c8cd016e74</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>ca-cioos_3e90a567-cdd7-41f3-8157-0e7be76eefb8</t>
+          <t>ca-cioos_6c449900-c726-4e9a-b241-707711e253a7</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -19886,7 +19888,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Nuchatlaht Survey - Hakai Airborne Coastal Observatory Imagery and Topography Data - Nootka Island British Columbia - 2023</t>
+          <t>Hakai Institute Juvenile Salmon Program Time Series</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -19904,7 +19906,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Juvenile Salmon Program</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -19932,46 +19934,48 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.1, 49.71], [-126.7, 49.71], [-126.7, 50.01], [-127.1, 50.01], [-127.1, 49.71]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.8232006, 49.89790212], [-124.67574133, 49.89790212], [-124.67574133, 50.73488305], [-126.8232006, 50.73488305], [-126.8232006, 49.89790212]]]}</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>[{'max': '500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '9.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>10.21966/kp87-sf64</t>
+          <t>10.21966/1.566666</t>
         </is>
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Nlir_Hi8PQBF_etobGR</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXNUQUNpb1hBa0pYWVg</t>
         </is>
       </c>
       <c r="T179" t="inlineStr">
         <is>
-          <t>2024-01-08</t>
+          <t>2023-11-03</t>
         </is>
       </c>
       <c r="U179" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="V179" t="inlineStr"/>
+          <t>2025-01-18</t>
+        </is>
+      </c>
+      <c r="V179" t="n">
+        <v>4</v>
+      </c>
       <c r="W179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X179" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2024', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -19981,12 +19985,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>582c6ff0-029e-44ba-8ba1-d3f2f39f2005</t>
+          <t>432b05ce-8904-4094-94bf-b97fb6636e41</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>ca-cioos_6f6560e7-7497-4685-9df2-51c66080b7c9</t>
+          <t>ca-cioos_3e90a567-cdd7-41f3-8157-0e7be76eefb8</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -19996,7 +20000,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Genetic Stock Identification of Juvenile Sockeye Salmon Captured in the Discovery Islands and Johnstone Strait BC, Canada</t>
+          <t>Nuchatlaht Survey - Hakai Airborne Coastal Observatory Imagery and Topography Data - Nootka Island British Columbia - 2023</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -20014,7 +20018,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Juvenile Salmon Program</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -20042,48 +20046,46 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.0, 49.88], [-124.4, 49.88], [-124.4, 50.84], [-127.0, 50.84], [-127.0, 49.88]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.1, 49.71], [-126.7, 49.71], [-126.7, 50.01], [-127.1, 50.01], [-127.1, 49.71]]]}</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>[{'max': '9.0', 'min': '0.0'}]</t>
+          <t>[{'max': '500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>10.21966/9ktc-qm09</t>
+          <t>10.21966/kp87-sf64</t>
         </is>
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/UTb9hNU3GJRK302QyaKNIvj2OiJ2/-NM0DF83_HSOwpbGBM8m</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Nlir_Hi8PQBF_etobGR</t>
         </is>
       </c>
       <c r="T180" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-08</t>
         </is>
       </c>
       <c r="U180" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="V180" t="n">
-        <v>1</v>
-      </c>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr"/>
       <c r="W180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X180" t="inlineStr">
         <is>
-          <t>[{'year': '2024', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -20093,12 +20095,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>11051c56-8d67-43fc-a13c-b706e851a5a4</t>
+          <t>582c6ff0-029e-44ba-8ba1-d3f2f39f2005</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>ca-cioos_2d693456-7e65-46be-95d7-6bb697320017</t>
+          <t>ca-cioos_6f6560e7-7497-4685-9df2-51c66080b7c9</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -20108,7 +20110,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Water Level and Weather Station Time Series, Pruth Bay, Kwakshua Channel, Central Coast, BC, Canada (Provisional)</t>
+          <t>Genetic Stock Identification of Juvenile Sockeye Salmon Captured in the Discovery Islands and Johnstone Strait BC, Canada</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -20126,12 +20128,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Oceanography, Watersheds</t>
+          <t>Juvenile Salmon Program</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -20154,46 +20156,48 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-128.1302805556, 51.6544888889]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.0, 49.88], [-124.4, 49.88], [-124.4, 50.84], [-127.0, 50.84], [-127.0, 49.88]]]}</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '9.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>seaSurfaceHeight, other, seaSurfaceTemperature</t>
+          <t>fishAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>10.21966/8d4w-sr07</t>
+          <t>10.21966/9ktc-qm09</t>
         </is>
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MkxD-S6TxIvv2e6_OGH</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/UTb9hNU3GJRK302QyaKNIvj2OiJ2/-NM0DF83_HSOwpbGBM8m</t>
         </is>
       </c>
       <c r="T181" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="U181" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="V181" t="inlineStr"/>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="V181" t="n">
+        <v>1</v>
+      </c>
       <c r="W181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X181" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2024', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -20203,12 +20207,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>b0e815da-1b17-404d-8bf6-0bdb4a22d170</t>
+          <t>11051c56-8d67-43fc-a13c-b706e851a5a4</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>ca-cioos_c24f23f0-8d16-4bfd-835a-5475f1ecd8e8</t>
+          <t>ca-cioos_2d693456-7e65-46be-95d7-6bb697320017</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -20218,7 +20222,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Extent of Canopy-Forming Kelps, Derived from World View-2, Central Coast, Central Coast, British Columbia</t>
+          <t>Water Level and Weather Station Time Series, Pruth Bay, Kwakshua Channel, Central Coast, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -20236,12 +20240,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Oceanography, Watersheds</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -20260,31 +20264,31 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6993408203125, 51.31001339554933], [-127.65014648437497, 51.31001339554933], [-127.65014648437497, 52.221069523572794], [-128.6993408203125, 52.221069523572794], [-128.6993408203125, 51.31001339554933]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-128.1302805556, 51.6544888889]}</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>seaSurfaceHeight, other, seaSurfaceTemperature</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>10.21966/5fs0-nn02</t>
+          <t>10.21966/8d4w-sr07</t>
         </is>
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVE2ZkIxMnhEdmF6Rkw</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MkxD-S6TxIvv2e6_OGH</t>
         </is>
       </c>
       <c r="T182" t="inlineStr">
@@ -20294,7 +20298,7 @@
       </c>
       <c r="U182" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="V182" t="n">
@@ -20315,12 +20319,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>abb0b617-3a3e-43ec-b62e-e2918bfc10aa</t>
+          <t>b0e815da-1b17-404d-8bf6-0bdb4a22d170</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>ca-cioos_b8483c9e-81e6-4e1a-b09f-2d66f8fee9a2</t>
+          <t>ca-cioos_c24f23f0-8d16-4bfd-835a-5475f1ecd8e8</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -20330,7 +20334,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp (Nereocystis luetkeana) derived from fixed-wing surveys (2023), Denman Island to south Quadra Island, British Columbia, Canada</t>
+          <t>Extent of Canopy-Forming Kelps, Derived from World View-2, Central Coast, Central Coast, British Columbia</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -20348,7 +20352,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Nearshore, Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -20372,41 +20376,41 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.3, 50.02], [-125.1, 50.05], [-125.1, 49.9], [-124.8, 49.71], [-124.7, 49.56], [-124.8, 49.55], [-124.9, 49.64], [-125.2, 49.9], [-125.2, 49.9], [-125.3, 50.02]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6993408203125, 51.31001339554933], [-127.65014648437497, 51.31001339554933], [-127.65014648437497, 52.221069523572794], [-128.6993408203125, 52.221069523572794], [-128.6993408203125, 51.31001339554933]]]}</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>10.21966/fmw1-8w35</t>
+          <t>10.21966/5fs0-nn02</t>
         </is>
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-NpNoCv2XWdhBoo5RBKV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MVE2ZkIxMnhEdmF6Rkw</t>
         </is>
       </c>
       <c r="T183" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="U183" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="V183" t="n">
@@ -20427,12 +20431,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>9df42f88-b8d8-4e2d-97bb-ad5ba49f6f1f</t>
+          <t>abb0b617-3a3e-43ec-b62e-e2918bfc10aa</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>ca-cioos_59b33373-ae4a-4719-a3df-0e36a08187d8</t>
+          <t>ca-cioos_b8483c9e-81e6-4e1a-b09f-2d66f8fee9a2</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -20442,7 +20446,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Seagrass Site-Level Production on BC Central Coast</t>
+          <t>Spatial extent of surface canopy kelp (Nereocystis luetkeana) derived from fixed-wing surveys (2023), Denman Island to south Quadra Island, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -20460,12 +20464,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Airborne Coastal Observatory, Nearshore, Geospatial</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -20488,37 +20492,37 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.98931373, 50.8340959], [-127.03580726, 50.8340959], [-127.03580726, 52.33530479], [-128.98931373, 52.33530479], [-128.98931373, 50.8340959]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.3, 50.02], [-125.1, 50.05], [-125.1, 49.9], [-124.8, 49.71], [-124.7, 49.56], [-124.8, 49.55], [-124.9, 49.64], [-125.2, 49.9], [-125.2, 49.9], [-125.3, 50.02]]]}</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>[{'max': '10.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>other, seagrassCoverAndComposition</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>10.21966/ezev-0v96</t>
+          <t>10.21966/fmw1-8w35</t>
         </is>
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/lJHlH9nm20QQOPuk217xLlxWbNv1/-NPt7-mgrZEUzma8l5W_</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-NpNoCv2XWdhBoo5RBKV</t>
         </is>
       </c>
       <c r="T184" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="U184" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="V184" t="n">
@@ -20539,12 +20543,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>bf7c05e8-510d-4449-9e81-4c358ff3f440</t>
+          <t>9df42f88-b8d8-4e2d-97bb-ad5ba49f6f1f</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>ca-cioos_1755dc37-8d33-4158-8041-c22536fd5771</t>
+          <t>ca-cioos_59b33373-ae4a-4719-a3df-0e36a08187d8</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -20554,7 +20558,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Bulk and Size-Fractionated Chlorophyll and Phaeopigment Concentrations Collected by Niskin Bottle, BC, Canada (Provisional)</t>
+          <t>Seagrass Site-Level Production on BC Central Coast</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -20572,7 +20576,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -20600,37 +20604,37 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.98931373, 50.8340959], [-127.03580726, 50.8340959], [-127.03580726, 52.33530479], [-128.98931373, 52.33530479], [-128.98931373, 50.8340959]]]}</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>[{'max': '650.0', 'min': '0.0'}]</t>
+          <t>[{'max': '10.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>particulateMatter</t>
+          <t>other, seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>10.21966/90h6-b497</t>
+          <t>10.21966/ezev-0v96</t>
         </is>
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-McQFPAf457LB4-SWmyL</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/lJHlH9nm20QQOPuk217xLlxWbNv1/-NPt7-mgrZEUzma8l5W_</t>
         </is>
       </c>
       <c r="T185" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="U185" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="V185" t="n">
@@ -20651,12 +20655,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>8882a149-fabd-4ecd-98d3-68a2a88aee38</t>
+          <t>bf7c05e8-510d-4449-9e81-4c358ff3f440</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>ca-cioos_d55021c3-a142-4e14-8208-36c9826c1893</t>
+          <t>ca-cioos_1755dc37-8d33-4158-8041-c22536fd5771</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -20666,7 +20670,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Bulk and Size-Fractionated Chlorophyll and Phaeopigment Concentrations Collected by Niskin Bottle, BC, Canada (Research)</t>
+          <t>Bulk and Size-Fractionated Chlorophyll and Phaeopigment Concentrations Collected by Niskin Bottle, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -20708,45 +20712,45 @@
         </is>
       </c>
       <c r="N186" t="n">
+        <v>1</v>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>[{'max': '650.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>particulateMatter</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>10.21966/90h6-b497</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-McQFPAf457LB4-SWmyL</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="V186" t="n">
         <v>2</v>
-      </c>
-      <c r="O186" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
-        </is>
-      </c>
-      <c r="P186" t="inlineStr">
-        <is>
-          <t>[{'max': '650.0', 'min': '0.0'}]</t>
-        </is>
-      </c>
-      <c r="Q186" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R186" t="inlineStr">
-        <is>
-          <t>10.21966/q5vm-8797</t>
-        </is>
-      </c>
-      <c r="S186" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-MadZvZJ4ZeikpCgRcV8</t>
-        </is>
-      </c>
-      <c r="T186" t="inlineStr">
-        <is>
-          <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="U186" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="V186" t="n">
-        <v>1</v>
       </c>
       <c r="W186" t="n">
         <v>0</v>
@@ -20763,12 +20767,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
+          <t>8882a149-fabd-4ecd-98d3-68a2a88aee38</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>ca-cioos_6143028b-028d-46c7-a67d-f3a513435e63</t>
+          <t>ca-cioos_d55021c3-a142-4e14-8208-36c9826c1893</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -20778,7 +20782,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Water Property Measurements from Conductivity-Temperature-Depth Profiles, BC, Canada (Provisional)</t>
+          <t>Bulk and Size-Fractionated Chlorophyll and Phaeopigment Concentrations Collected by Niskin Bottle, BC, Canada (Research)</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -20796,7 +20800,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Juvenile Salmon Program, Oceanography, Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -20820,45 +20824,45 @@
         </is>
       </c>
       <c r="N187" t="n">
+        <v>2</v>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>[{'max': '650.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>10.21966/q5vm-8797</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-MadZvZJ4ZeikpCgRcV8</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="V187" t="n">
         <v>1</v>
-      </c>
-      <c r="O187" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
-        </is>
-      </c>
-      <c r="P187" t="inlineStr">
-        <is>
-          <t>[{'max': '700.0', 'min': '1.0'}]</t>
-        </is>
-      </c>
-      <c r="Q187" t="inlineStr">
-        <is>
-          <t>oxygen, subSurfaceSalinity, subSurfaceTemperature</t>
-        </is>
-      </c>
-      <c r="R187" t="inlineStr">
-        <is>
-          <t>10.21966/rj8w-aa62</t>
-        </is>
-      </c>
-      <c r="S187" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MMHJ4k2EEwxkbXkrjxa</t>
-        </is>
-      </c>
-      <c r="T187" t="inlineStr">
-        <is>
-          <t>2024-07-17</t>
-        </is>
-      </c>
-      <c r="U187" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="V187" t="n">
-        <v>2</v>
       </c>
       <c r="W187" t="n">
         <v>0</v>
@@ -20875,12 +20879,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
+          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>ca-cioos_6652a7a9-d27f-4cbe-ac04-435c238e991d</t>
+          <t>ca-cioos_6143028b-028d-46c7-a67d-f3a513435e63</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -20890,7 +20894,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Water Level Time Series, Choke Pass, Central Coast, BC, Canada (Provisional)</t>
+          <t>Water Property Measurements from Conductivity-Temperature-Depth Profiles, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -20908,12 +20912,12 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Juvenile Salmon Program, Oceanography, Nearshore</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -20936,41 +20940,41 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-128.12103, 51.670666]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>[{'max': '6.0', 'min': '0.0'}]</t>
+          <t>[{'max': '700.0', 'min': '1.0'}]</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>seaSurfaceHeight</t>
+          <t>oxygen, subSurfaceSalinity, subSurfaceTemperature</t>
         </is>
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>10.21966/kqd6-1j57</t>
+          <t>10.21966/rj8w-aa62</t>
         </is>
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-Mknr8pYvIQKw4r-WTFd</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MMHJ4k2EEwxkbXkrjxa</t>
         </is>
       </c>
       <c r="T188" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="U188" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="V188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W188" t="n">
         <v>0</v>
@@ -20987,12 +20991,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2081eb2e-67c5-44b7-b048-aeb2c646f238</t>
+          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>ca-cioos_f67c0c58-3225-4dac-9264-1e76f07c9374</t>
+          <t>ca-cioos_6652a7a9-d27f-4cbe-ac04-435c238e991d</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -21002,7 +21006,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Data for the paper "Phylogenomic position of eupelagonemids, abundant, and diverse deep-ocean heterotrophs"</t>
+          <t>Water Level Time Series, Choke Pass, Central Coast, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -21020,7 +21024,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Genomics</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -21040,7 +21044,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>University of British Columbia</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N189" t="n">
@@ -21048,40 +21052,42 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.9661, 51.65001], [-127.966, 51.65001], [-127.966, 51.65], [-127.9661, 51.65], [-127.9661, 51.65001]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-128.12103, 51.670666]}</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>[{'max': '300.0', 'min': '300.0'}]</t>
+          <t>[{'max': '6.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>seaSurfaceHeight</t>
         </is>
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>10.21966/7t4p-s714</t>
+          <t>10.21966/kqd6-1j57</t>
         </is>
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/NSo1FkJnvIbQDOlYlwNfWGnAxx33/-O1xBAkNi0P8igzOb4rg</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-Mknr8pYvIQKw4r-WTFd</t>
         </is>
       </c>
       <c r="T189" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="U189" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
-        </is>
-      </c>
-      <c r="V189" t="inlineStr"/>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="V189" t="n">
+        <v>3</v>
+      </c>
       <c r="W189" t="n">
         <v>0</v>
       </c>
@@ -21097,12 +21103,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>1dfdbadf-6314-4411-8d18-752f6dd920e9</t>
+          <t>2081eb2e-67c5-44b7-b048-aeb2c646f238</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>ca-cioos_67e89414-a93f-496d-9766-9311f0d3954e</t>
+          <t>ca-cioos_f67c0c58-3225-4dac-9264-1e76f07c9374</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -21112,7 +21118,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Motile Invertebrate Surveys - BC Central Coast</t>
+          <t>Data for the paper "Phylogenomic position of eupelagonemids, abundant, and diverse deep-ocean heterotrophs"</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -21130,12 +21136,12 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Genomics</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -21150,7 +21156,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="N190" t="n">
@@ -21158,48 +21164,46 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.2, 51.63], [-128.1, 51.63], [-128.1, 51.67], [-128.2, 51.67], [-128.2, 51.63]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.9661, 51.65001], [-127.966, 51.65001], [-127.966, 51.65], [-127.9661, 51.65], [-127.9661, 51.65001]]]}</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '-5.0'}]</t>
+          <t>[{'max': '300.0', 'min': '300.0'}]</t>
         </is>
       </c>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>10.21966/0052-wk15</t>
+          <t>10.21966/7t4p-s714</t>
         </is>
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-MotWzhmBvoGPE8QZ0sf</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/NSo1FkJnvIbQDOlYlwNfWGnAxx33/-O1xBAkNi0P8igzOb4rg</t>
         </is>
       </c>
       <c r="T190" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="U190" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="V190" t="n">
-        <v>1</v>
-      </c>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr"/>
       <c r="W190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X190" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -21209,12 +21213,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>a8f61379-14f9-4ccc-bc9b-4408ba8340d7</t>
+          <t>1dfdbadf-6314-4411-8d18-752f6dd920e9</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>ca-cioos_52797e17-c0ed-46a4-9dcd-e34f801c6205</t>
+          <t>ca-cioos_67e89414-a93f-496d-9766-9311f0d3954e</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -21224,7 +21228,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Fucus Dynamics - Point Intercept Surveys - BC Central Coast</t>
+          <t>Motile Invertebrate Surveys - BC Central Coast</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -21280,27 +21284,27 @@
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>10.21966/v57r-g944</t>
+          <t>10.21966/0052-wk15</t>
         </is>
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-MopPnOL2o_bshK-cKxr</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-MotWzhmBvoGPE8QZ0sf</t>
         </is>
       </c>
       <c r="T191" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="U191" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="V191" t="n">
@@ -21311,7 +21315,7 @@
       </c>
       <c r="X191" t="inlineStr">
         <is>
-          <t>[{'year': '2024', 'total': 1}]</t>
+          <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -21321,12 +21325,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>c4d3a53a-faa2-4c3e-bcd3-cfdb0aef0078</t>
+          <t>a8f61379-14f9-4ccc-bc9b-4408ba8340d7</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>ca-cioos_355467ad-104d-40a6-b06e-52a67bfe247e</t>
+          <t>ca-cioos_52797e17-c0ed-46a4-9dcd-e34f801c6205</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -21336,7 +21340,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Water column CO2 system measurements from January 2016 to December 2023 from Hakai Institute oceanographic station QU39 in northern Strait of Georgia, British Columbia, Canada</t>
+          <t>Fucus Dynamics - Point Intercept Surveys - BC Central Coast</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -21354,12 +21358,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -21382,48 +21386,48 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.1, 50.03]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.2, 51.63], [-128.1, 51.63], [-128.1, 51.67], [-128.2, 51.67], [-128.2, 51.63]]]}</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>[{'max': '262.0', 'min': '1.0'}]</t>
+          <t>[{'max': '5.0', 'min': '-5.0'}]</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>inorganicCarbon, oxygen, subSurfaceSalinity, seaSurfaceTemperature, seaSurfaceSalinity, subSurfaceTemperature</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>10.21966/k1xg-6920</t>
+          <t>10.21966/v57r-g944</t>
         </is>
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-O6XpUwSfsllQlTBMz53</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/Q7WjoEJM1Sc9HrFLJCRgKAtMzTH2/-MopPnOL2o_bshK-cKxr</t>
         </is>
       </c>
       <c r="T192" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="U192" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="V192" t="n">
         <v>1</v>
       </c>
       <c r="W192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X192" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2024', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -21433,12 +21437,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>52d607c9-46cd-4be9-a752-1b5446272f32</t>
+          <t>c4d3a53a-faa2-4c3e-bcd3-cfdb0aef0078</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>ca-cioos_0507a738-cd65-4ba4-943e-42b9d022b637</t>
+          <t>ca-cioos_355467ad-104d-40a6-b06e-52a67bfe247e</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -21448,7 +21452,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Fraser River Airborne Surveys - 2021 - Hakai Airborne Coastal Observatory</t>
+          <t>Water column CO2 system measurements from January 2016 to December 2023 from Hakai Institute oceanographic station QU39 in northern Strait of Georgia, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -21466,7 +21470,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -21494,40 +21498,42 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.1, 50.5], [-121.7, 50.5], [-121.7, 51.12], [-122.1, 51.12], [-122.1, 50.5]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.1, 50.03]}</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>[{'max': '1500.0', 'min': '185.0'}]</t>
+          <t>[{'max': '262.0', 'min': '1.0'}]</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>inorganicCarbon, oxygen, subSurfaceSalinity, seaSurfaceTemperature, seaSurfaceSalinity, subSurfaceTemperature</t>
         </is>
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>10.21966/ytgc-6g46</t>
+          <t>10.21966/k1xg-6920</t>
         </is>
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NHfqx-d8tuAroY8BWc7</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-O6XpUwSfsllQlTBMz53</t>
         </is>
       </c>
       <c r="T193" t="inlineStr">
         <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
           <t>2024-10-09</t>
         </is>
       </c>
-      <c r="U193" t="inlineStr">
-        <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="V193" t="inlineStr"/>
+      <c r="V193" t="n">
+        <v>1</v>
+      </c>
       <c r="W193" t="n">
         <v>0</v>
       </c>
@@ -21543,12 +21549,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>551bbe09-f182-478b-8d50-2f9a4dbd93ae</t>
+          <t>52d607c9-46cd-4be9-a752-1b5446272f32</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>ca-cioos_189dd319-d5ef-4f2a-a060-df8d47628b86</t>
+          <t>ca-cioos_0507a738-cd65-4ba4-943e-42b9d022b637</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -21558,7 +21564,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Elliot Creek Landslide LiDAR Mapping - 2023 - Airborne Coastal Observatory</t>
+          <t>Fraser River Airborne Surveys - 2021 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -21576,7 +21582,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -21600,16 +21606,16 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.8, 50.84], [-124.5, 50.84], [-124.5, 51.0], [-124.8, 51.0], [-124.8, 50.84]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.1, 50.5], [-121.7, 50.5], [-121.7, 51.12], [-122.1, 51.12], [-122.1, 50.5]]]}</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>[{'max': '2300.0', 'min': '0.0'}]</t>
+          <t>[{'max': '1500.0', 'min': '185.0'}]</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
@@ -21619,12 +21625,12 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>10.21966/szqj-b355</t>
+          <t>10.21966/ytgc-6g46</t>
         </is>
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRZqJivYfce75NOoBD</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NHfqx-d8tuAroY8BWc7</t>
         </is>
       </c>
       <c r="T194" t="inlineStr">
@@ -21634,7 +21640,7 @@
       </c>
       <c r="U194" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="V194" t="inlineStr"/>
@@ -21653,12 +21659,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
+          <t>551bbe09-f182-478b-8d50-2f9a4dbd93ae</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>ca-cioos_33a367c1-2706-4301-af99-4455fbe189a0</t>
+          <t>ca-cioos_189dd319-d5ef-4f2a-a060-df8d47628b86</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -21668,7 +21674,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Cryosphere Snow Surveys Southwest British Columbia - Airborne Coastal Observatory</t>
+          <t>Elliot Creek Landslide LiDAR Mapping - 2023 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -21686,7 +21692,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -21714,7 +21720,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.9, 48.62], [-122.1, 48.62], [-122.1, 50.82], [-126.9, 50.82], [-126.9, 48.62]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.8, 50.84], [-124.5, 50.84], [-124.5, 51.0], [-124.8, 51.0], [-124.8, 50.84]]]}</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
@@ -21729,12 +21735,12 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>10.21966/thq7-0g08</t>
+          <t>10.21966/szqj-b355</t>
         </is>
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRfMcU9I8mMcBH6qiv</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRZqJivYfce75NOoBD</t>
         </is>
       </c>
       <c r="T195" t="inlineStr">
@@ -21747,9 +21753,7 @@
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="V195" t="n">
-        <v>3</v>
-      </c>
+      <c r="V195" t="inlineStr"/>
       <c r="W195" t="n">
         <v>0</v>
       </c>
@@ -21765,12 +21769,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
+          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a</t>
+          <t>ca-cioos_33a367c1-2706-4301-af99-4455fbe189a0</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -21780,7 +21784,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Bute Inlet Geohazard - Topography Surveys - 2023 - Hakai Airborne Coastal Observatory</t>
+          <t>Cryosphere Snow Surveys Southwest British Columbia - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -21822,16 +21826,16 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.9, 50.53], [-124.2, 50.53], [-124.2, 50.99], [-124.9, 50.99], [-124.9, 50.53]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.9, 48.62], [-122.1, 48.62], [-122.1, 50.82], [-126.9, 50.82], [-126.9, 48.62]]]}</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>[{'max': '2600.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2300.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
@@ -21841,12 +21845,12 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>10.21966/e4b8-vp48</t>
+          <t>10.21966/thq7-0g08</t>
         </is>
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRG7xQ84LQrgS4jhie</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRfMcU9I8mMcBH6qiv</t>
         </is>
       </c>
       <c r="T196" t="inlineStr">
@@ -21856,18 +21860,18 @@
       </c>
       <c r="U196" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="V196" t="n">
         <v>3</v>
       </c>
       <c r="W196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X196" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -21877,12 +21881,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>78efda1b-9688-4bcf-b16e-7167c17c0bcb</t>
+          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>ca-cioos_43422dc8-2573-4f60-bf87-df447d57ab7a</t>
+          <t>ca-cioos_3efdccb0-08ef-4e90-ac91-72969f94a99a</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -21892,7 +21896,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>USGS Glacier Mapping - 2023 - Hakai Airborne Coastal Observatory</t>
+          <t>Bute Inlet Geohazard - Topography Surveys - 2023 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -21934,16 +21938,16 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-121.4, 47.68], [-113.0, 47.68], [-113.0, 49.08], [-121.4, 49.08], [-121.4, 47.68]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.9, 50.53], [-124.2, 50.53], [-124.2, 50.99], [-124.9, 50.99], [-124.9, 50.53]]]}</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>[{'max': '2800.0', 'min': '100.0'}]</t>
+          <t>[{'max': '2600.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr">
@@ -21953,12 +21957,12 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>10.21966/bzr6-er66</t>
+          <t>10.21966/e4b8-vp48</t>
         </is>
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRKhzLRiCcp6ENuX2r</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRG7xQ84LQrgS4jhie</t>
         </is>
       </c>
       <c r="T197" t="inlineStr">
@@ -21968,18 +21972,18 @@
       </c>
       <c r="U197" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="V197" t="n">
+        <v>3</v>
+      </c>
+      <c r="W197" t="n">
         <v>1</v>
       </c>
-      <c r="W197" t="n">
-        <v>0</v>
-      </c>
       <c r="X197" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -21989,12 +21993,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
+          <t>78efda1b-9688-4bcf-b16e-7167c17c0bcb</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>ca-cioos_6756b221-28a0-4848-9761-905cbd558cd7</t>
+          <t>ca-cioos_43422dc8-2573-4f60-bf87-df447d57ab7a</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -22004,7 +22008,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Protistan plankton time series from the northern Salish Sea and Central Coast, British Columbia, Canada</t>
+          <t>USGS Glacier Mapping - 2023 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -22022,12 +22026,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -22046,45 +22050,45 @@
         </is>
       </c>
       <c r="N198" t="n">
+        <v>2</v>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-121.4, 47.68], [-113.0, 47.68], [-113.0, 49.08], [-121.4, 49.08], [-121.4, 47.68]]]}</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>[{'max': '2800.0', 'min': '100.0'}]</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>10.21966/bzr6-er66</t>
+        </is>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpRKhzLRiCcp6ENuX2r</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="V198" t="n">
         <v>1</v>
-      </c>
-      <c r="O198" t="inlineStr">
-        <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
-        </is>
-      </c>
-      <c r="P198" t="inlineStr">
-        <is>
-          <t>[{'max': '6.0', 'min': '1.0'}]</t>
-        </is>
-      </c>
-      <c r="Q198" t="inlineStr">
-        <is>
-          <t>phytoplanktonBiomassAndDiversity</t>
-        </is>
-      </c>
-      <c r="R198" t="inlineStr">
-        <is>
-          <t>10.21966/jv5k-3k59</t>
-        </is>
-      </c>
-      <c r="S198" t="inlineStr">
-        <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-Nh8VlPQ_m681tso87Gd</t>
-        </is>
-      </c>
-      <c r="T198" t="inlineStr">
-        <is>
-          <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="U198" t="inlineStr">
-        <is>
-          <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="V198" t="n">
-        <v>4</v>
       </c>
       <c r="W198" t="n">
         <v>0</v>
@@ -22101,12 +22105,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>9d1749f8-9be2-468c-946e-965f92fcdc67</t>
+          <t>5042c858-d375-42f5-82e0-ee1e4da962b6</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>ca-cioos_6e947d50-8392-42ce-bff9-24b126c7cab7</t>
+          <t>ca-cioos_6756b221-28a0-4848-9761-905cbd558cd7</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -22116,7 +22120,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Spatial extent of eelgrass (Zostera marina) beds from monitoring sites within the greater park ecosystem of Pacific Rim National Park Reserve (2017, 2018)</t>
+          <t>Protistan plankton time series from the northern Salish Sea and Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -22134,12 +22138,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Nearshore, Geospatial</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -22158,44 +22162,46 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.0511576, 48.72717181], [-124.94565833, 48.72717181], [-124.94565833, 49.24536019], [-126.0511576, 49.24536019], [-126.0511576, 48.72717181]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+          <t>[{'max': '6.0', 'min': '1.0'}]</t>
         </is>
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>other, seagrassCoverAndComposition</t>
+          <t>phytoplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>10.21966/8mpe-h081</t>
+          <t>10.21966/jv5k-3k59</t>
         </is>
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUR4a1V0N1UxYTc2U3Q</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-Nh8VlPQ_m681tso87Gd</t>
         </is>
       </c>
       <c r="T199" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="U199" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="V199" t="inlineStr"/>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="V199" t="n">
+        <v>4</v>
+      </c>
       <c r="W199" t="n">
         <v>0</v>
       </c>
@@ -22211,12 +22217,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
+          <t>9d1749f8-9be2-468c-946e-965f92fcdc67</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>ca-cioos_f25b00ba-ad63-42b3-8021-3fb6aa99baff</t>
+          <t>ca-cioos_6e947d50-8392-42ce-bff9-24b126c7cab7</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -22226,12 +22232,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Fraser River Landslide Project - Sites of Concern 2024</t>
+          <t>Spatial extent of eelgrass (Zostera marina) beds from monitoring sites within the greater park ecosystem of Pacific Rim National Park Reserve (2017, 2018)</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>document</t>
+          <t>dataset</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -22244,7 +22250,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Nearshore, Geospatial</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -22264,50 +22270,48 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Hakai Geospatial</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N200" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.0, 49.0], [-119.5, 49.0], [-119.5, 54.34], [-124.0, 54.34], [-124.0, 49.0]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.0511576, 48.72717181], [-124.94565833, 48.72717181], [-124.94565833, 49.24536019], [-126.0511576, 49.24536019], [-126.0511576, 48.72717181]]]}</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>[{'max': '2500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>10.21966/xp9x-m243</t>
+          <t>10.21966/8mpe-h081</t>
         </is>
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NTLT7n49Ox3SnVoy6nW</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUR4a1V0N1UxYTc2U3Q</t>
         </is>
       </c>
       <c r="T200" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="U200" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
-        </is>
-      </c>
-      <c r="V200" t="n">
-        <v>4</v>
-      </c>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr"/>
       <c r="W200" t="n">
         <v>0</v>
       </c>
@@ -22323,12 +22327,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
+          <t>5c162406-4886-4a66-9d9c-12c3d0316e2e</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>ca-cioos_c513de71-ac9d-43fa-b693-8f865de4b137</t>
+          <t>ca-cioos_f25b00ba-ad63-42b3-8021-3fb6aa99baff</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -22338,12 +22342,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Fraser River Landslide Project - 2022-2024 - Drone Data</t>
+          <t>Fraser River Landslide Project - Sites of Concern 2024</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>document</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -22356,7 +22360,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -22376,7 +22380,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Hakai Geospatial</t>
         </is>
       </c>
       <c r="N201" t="n">
@@ -22384,12 +22388,12 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.8, 49.29], [-121.2, 49.29], [-121.2, 52.28], [-122.8, 52.28], [-122.8, 49.29]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.0, 49.0], [-119.5, 49.0], [-119.5, 54.34], [-124.0, 54.34], [-124.0, 49.0]]]}</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>[{'max': '1500.0', 'min': '50.0'}]</t>
+          <t>[{'max': '2500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q201" t="inlineStr">
@@ -22399,26 +22403,26 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>10.21966/qpe8-ay93</t>
+          <t>10.21966/xp9x-m243</t>
         </is>
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpurN_vwkhOgSJmgBh9</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NTLT7n49Ox3SnVoy6nW</t>
         </is>
       </c>
       <c r="T201" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="U201" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="V201" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W201" t="n">
         <v>0</v>
@@ -22435,12 +22439,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>e8414189-54c9-4311-874e-b97f9b7916ae</t>
+          <t>45a45b5d-e45c-453c-9d36-036f69d533ae</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>ca-cioos_48acba27-5e01-4b41-9a0e-f3fc8d809a13</t>
+          <t>ca-cioos_c513de71-ac9d-43fa-b693-8f865de4b137</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -22450,7 +22454,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>MusselSeg: Semantic Segmentation for Rocky Intertidal Mussel Habitat</t>
+          <t>Fraser River Landslide Project - 2022-2024 - Drone Data</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -22468,12 +22472,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -22496,40 +22500,42 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-130.1, 51.59], [-120.4, 31.75], [-118.4, 33.38], [-124.3, 44.43], [-122.0, 49.35], [-126.2, 51.59], [-130.1, 51.59]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.8, 49.29], [-121.2, 49.29], [-121.2, 52.28], [-122.8, 52.28], [-122.8, 49.29]]]}</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>[{'max': '75.0', 'min': '15.0'}]</t>
+          <t>[{'max': '1500.0', 'min': '50.0'}]</t>
         </is>
       </c>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>other, invertebrateAbundanceAndDistribution</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>10.21966/fbv4-th96</t>
+          <t>10.21966/qpe8-ay93</t>
         </is>
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DCH8GzsQKSM8xwJ8WdQFIZrtCaq2/-O26fyGiVXoF__M22UrP</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NpurN_vwkhOgSJmgBh9</t>
         </is>
       </c>
       <c r="T202" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="U202" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="V202" t="inlineStr"/>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="V202" t="n">
+        <v>2</v>
+      </c>
       <c r="W202" t="n">
         <v>0</v>
       </c>
@@ -22545,12 +22551,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
+          <t>e8414189-54c9-4311-874e-b97f9b7916ae</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>ca-cioos_d4942b86-d362-40a3-9399-c124c4c263bd</t>
+          <t>ca-cioos_48acba27-5e01-4b41-9a0e-f3fc8d809a13</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -22560,7 +22566,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Larval Dungeness crab abundance and size time series along the coast of British Columbia</t>
+          <t>MusselSeg: Semantic Segmentation for Rocky Intertidal Mussel Habitat</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -22578,7 +22584,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Sentinels of Change</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -22606,42 +22612,40 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.8, 48.3], [-123.2, 48.37], [-123.2, 48.65], [-123.0, 48.77], [-123.3, 49.01], [-122.9, 49.25], [-122.6, 49.4], [-123.2, 49.45], [-123.7, 49.54], [-124.5, 49.89], [-124.8, 50.09], [-126.5, 50.79], [-128.3, 52.31], [-130.4, 54.75], [-133.8, 54.36], [-132.9, 52.85], [-130.3, 51.48], [-128.1, 50.15], [-125.2, 48.62], [-123.8, 48.3]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-130.1, 51.59], [-120.4, 31.75], [-118.4, 33.38], [-124.3, 44.43], [-122.0, 49.35], [-126.2, 51.59], [-130.1, 51.59]]]}</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>[{'max': '2.0', 'min': '0.0'}]</t>
+          <t>[{'max': '75.0', 'min': '15.0'}]</t>
         </is>
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution</t>
+          <t>other, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>10.21966/36hp-7f40</t>
+          <t>10.21966/fbv4-th96</t>
         </is>
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/57FPdLIBPcb9BOLfIOW44RJVywN2/-N1KAki3SSBEw0aHCoSv</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DCH8GzsQKSM8xwJ8WdQFIZrtCaq2/-O26fyGiVXoF__M22UrP</t>
         </is>
       </c>
       <c r="T203" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="U203" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="V203" t="n">
-        <v>2</v>
-      </c>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr"/>
       <c r="W203" t="n">
         <v>0</v>
       </c>
@@ -22657,12 +22661,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>265e0ec8-1d85-4e73-b85d-371845dbd08f</t>
+          <t>357b017c-6add-4bde-95d0-386bdbab92b3</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>ca-cioos_f762a307-6dfb-41a8-a56c-ecacfb075a0a</t>
+          <t>ca-cioos_d4942b86-d362-40a3-9399-c124c4c263bd</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -22672,7 +22676,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Denali Fault - 2024 - Airborne LiDAR Survey</t>
+          <t>Larval Dungeness crab abundance and size time series along the coast of British Columbia</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -22690,12 +22694,12 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Sentinels of Change</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -22718,40 +22722,42 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-141.3, 62.08], [-139.8, 61.49], [-137.7, 60.61], [-136.8, 60.1], [-136.4, 60.29], [-138.3, 61.12], [-140.1, 61.86], [-141.2, 62.19], [-141.3, 62.08]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.8, 48.3], [-123.2, 48.37], [-123.2, 48.65], [-123.0, 48.77], [-123.3, 49.01], [-122.9, 49.25], [-122.6, 49.4], [-123.2, 49.45], [-123.7, 49.54], [-124.5, 49.89], [-124.8, 50.09], [-126.5, 50.79], [-128.3, 52.31], [-130.4, 54.75], [-133.8, 54.36], [-132.9, 52.85], [-130.3, 51.48], [-128.1, 50.15], [-125.2, 48.62], [-123.8, 48.3]]]}</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>[{'max': '5000.0', 'min': '100.0'}]</t>
+          <t>[{'max': '2.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>10.21966/wxph-tz51</t>
+          <t>10.21966/36hp-7f40</t>
         </is>
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCKOQlOxJdTg_BFOoXb</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/57FPdLIBPcb9BOLfIOW44RJVywN2/-N1KAki3SSBEw0aHCoSv</t>
         </is>
       </c>
       <c r="T204" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="U204" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="V204" t="inlineStr"/>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="V204" t="n">
+        <v>2</v>
+      </c>
       <c r="W204" t="n">
         <v>0</v>
       </c>
@@ -22767,12 +22773,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
+          <t>265e0ec8-1d85-4e73-b85d-371845dbd08f</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>ca-cioos_5185ac00-8148-4472-adfd-21741d8a10ce</t>
+          <t>ca-cioos_f762a307-6dfb-41a8-a56c-ecacfb075a0a</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -22782,7 +22788,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Sentinels of Change Sea Surface Temperature Time Series Data Along the British Columbia Coast</t>
+          <t>Denali Fault - 2024 - Airborne LiDAR Survey</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -22800,12 +22806,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Sentinels of Change</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -22828,48 +22834,46 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.6, 48.25], [-123.2, 48.37], [-123.3, 48.71], [-123.0, 48.8], [-123.3, 49.09], [-123.0, 49.1], [-122.4, 49.39], [-122.6, 49.56], [-123.6, 49.55], [-124.8, 50.1], [-125.8, 50.51], [-127.5, 51.15], [-128.6, 52.64], [-130.4, 54.77], [-133.4, 54.37], [-132.8, 52.99], [-130.8, 51.58], [-128.3, 50.21], [-126.5, 49.17], [-125.2, 48.63], [-124.3, 48.43], [-123.6, 48.25]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-141.3, 62.08], [-139.8, 61.49], [-137.7, 60.61], [-136.8, 60.1], [-136.4, 60.29], [-138.3, 61.12], [-140.1, 61.86], [-141.2, 62.19], [-141.3, 62.08]]]}</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>[{'max': '0.5', 'min': '0.5'}]</t>
+          <t>[{'max': '5000.0', 'min': '100.0'}]</t>
         </is>
       </c>
       <c r="Q205" t="inlineStr">
         <is>
-          <t>seaSurfaceTemperature</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>10.21966/4kr2-jc55</t>
+          <t>10.21966/wxph-tz51</t>
         </is>
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/57FPdLIBPcb9BOLfIOW44RJVywN2/-NH0r8ddHNhVJ5bXkyqR</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCKOQlOxJdTg_BFOoXb</t>
         </is>
       </c>
       <c r="T205" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="U205" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="V205" t="n">
-        <v>2</v>
-      </c>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr"/>
       <c r="W205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X205" t="inlineStr">
         <is>
-          <t>[{'year': '2024', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -22879,12 +22883,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
+          <t>0049e274-f23e-448c-b307-14aa3b4e0b4a</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>ca-cioos_7fd3ec6c-083a-4942-84b4-215e69492072</t>
+          <t>ca-cioos_5185ac00-8148-4472-adfd-21741d8a10ce</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -22894,7 +22898,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Phytoplankton Pigment Timeseries from High-Performance Liquid Chromatography for the Northern Salish Sea and Central Coast, BC, Canada (Research)</t>
+          <t>Sentinels of Change Sea Surface Temperature Time Series Data Along the British Columbia Coast</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -22912,7 +22916,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Sentinels of Change</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -22940,32 +22944,32 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.6, 48.25], [-123.2, 48.37], [-123.3, 48.71], [-123.0, 48.8], [-123.3, 49.09], [-123.0, 49.1], [-122.4, 49.39], [-122.6, 49.56], [-123.6, 49.55], [-124.8, 50.1], [-125.8, 50.51], [-127.5, 51.15], [-128.6, 52.64], [-130.4, 54.77], [-133.4, 54.37], [-132.8, 52.99], [-130.8, 51.58], [-128.3, 50.21], [-126.5, 49.17], [-125.2, 48.63], [-124.3, 48.43], [-123.6, 48.25]]]}</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0.5', 'min': '0.5'}]</t>
         </is>
       </c>
       <c r="Q206" t="inlineStr">
         <is>
-          <t>phytoplanktonBiomassAndDiversity</t>
+          <t>seaSurfaceTemperature</t>
         </is>
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>10.21966/bw2d-tg65</t>
+          <t>10.21966/4kr2-jc55</t>
         </is>
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-O25qzW3OpioeACGpRHl</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/57FPdLIBPcb9BOLfIOW44RJVywN2/-NH0r8ddHNhVJ5bXkyqR</t>
         </is>
       </c>
       <c r="T206" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="U206" t="inlineStr">
@@ -22974,14 +22978,14 @@
         </is>
       </c>
       <c r="V206" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X206" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2024', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -22991,12 +22995,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>0781c19a-7efb-4680-92fd-8cd5faf0cfe4</t>
+          <t>cb0f4710-d78a-4073-959c-95f874f88711</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>ca-cioos_af344fb9-4901-470c-a441-41f11ee2ccd7</t>
+          <t>ca-cioos_7fd3ec6c-083a-4942-84b4-215e69492072</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -23006,7 +23010,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>iTrack Oysters February 2023 Experiment - Environmental and Oyster Health Data</t>
+          <t>Phytoplankton Pigment Timeseries from High-Performance Liquid Chromatography for the Northern Salish Sea and Central Coast, BC, Canada (Research)</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -23024,12 +23028,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Wet Lab</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -23044,7 +23048,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N207" t="n">
@@ -23052,40 +23056,42 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>phytoplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>10.21966/pvy6-nw38</t>
+          <t>10.21966/bw2d-tg65</t>
         </is>
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-O0G3gSlISPfB-f0u3Zz</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-O25qzW3OpioeACGpRHl</t>
         </is>
       </c>
       <c r="T207" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="U207" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
-        </is>
-      </c>
-      <c r="V207" t="inlineStr"/>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="V207" t="n">
+        <v>3</v>
+      </c>
       <c r="W207" t="n">
         <v>0</v>
       </c>
@@ -23101,12 +23107,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>0781c19a-7efb-4680-92fd-8cd5faf0cfe4</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>ca-cioos_9fafb4c8-e61f-4372-ac71-c1ddbe57d80c</t>
+          <t>ca-cioos_af344fb9-4901-470c-a441-41f11ee2ccd7</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -23116,7 +23122,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Data record does not exist anymore: Geomorphology - Calvert Island</t>
+          <t>iTrack Oysters February 2023 Experiment - Environmental and Oyster Health Data</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -23132,7 +23138,11 @@
       <c r="H208" t="b">
         <v>0</v>
       </c>
-      <c r="I208" t="inlineStr"/>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Wet Lab</t>
+        </is>
+      </c>
       <c r="J208" t="inlineStr">
         <is>
           <t>completed</t>
@@ -23150,7 +23160,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N208" t="n">
@@ -23158,40 +23168,48 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.2489013671875, 51.40605940499276], [-127.83142089843751, 51.40605940499276], [-127.83142089843751, 51.75934048406748], [-128.2489013671875, 51.75934048406748], [-128.2489013671875, 51.40605940499276]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q208" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="R208" t="inlineStr"/>
+          <t>other, inorganicCarbon</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>10.21966/pvy6-nw38</t>
+        </is>
+      </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OFhFpUJDNDF0hlFiGUV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-O0G3gSlISPfB-f0u3Zz</t>
         </is>
       </c>
       <c r="T208" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="U208" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
-        </is>
-      </c>
-      <c r="V208" t="n">
-        <v>4</v>
-      </c>
-      <c r="W208" t="inlineStr"/>
-      <c r="X208" t="inlineStr"/>
+          <t>2024-12-19</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr"/>
+      <c r="W208" t="n">
+        <v>0</v>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -23199,12 +23217,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>ca-cioos_d7ffd737-5725-4a56-9134-a9ad91c2734d</t>
+          <t>ca-cioos_9fafb4c8-e61f-4372-ac71-c1ddbe57d80c</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -23214,7 +23232,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Seton and Anderson Lake Multibeam Survey - 2024 - British Columbia</t>
+          <t>Data record does not exist anymore: Geomorphology - Calvert Island</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -23230,11 +23248,7 @@
       <c r="H209" t="b">
         <v>0</v>
       </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>Geospatial</t>
-        </is>
-      </c>
+      <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr">
         <is>
           <t>completed</t>
@@ -23260,12 +23274,12 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.4, 50.62], [-122.0, 50.62], [-122.0, 50.75], [-122.4, 50.75], [-122.4, 50.62]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.2489013671875, 51.40605940499276], [-127.83142089843751, 51.40605940499276], [-127.83142089843751, 51.75934048406748], [-128.2489013671875, 51.75934048406748], [-128.2489013671875, 51.40605940499276]]]}</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>[{'max': '254.0', 'min': '61.0'}]</t>
+          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q209" t="inlineStr">
@@ -23273,37 +23287,27 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R209" t="inlineStr">
-        <is>
-          <t>10.21966/zfxe-rd73</t>
-        </is>
-      </c>
+      <c r="R209" t="inlineStr"/>
       <c r="S209" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCe-GBA4i93dk_I9uOR</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OFhFpUJDNDF0hlFiGUV</t>
         </is>
       </c>
       <c r="T209" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="U209" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="V209" t="n">
-        <v>1</v>
-      </c>
-      <c r="W209" t="n">
-        <v>0</v>
-      </c>
-      <c r="X209" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="W209" t="inlineStr"/>
+      <c r="X209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -23311,12 +23315,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>4a949e26-fe94-4f63-a3c6-a62e19301102</t>
+          <t>8dc6dfd7-cda8-4fbf-af6a-dcae7d92ed0e</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>ca-cioos_35beb32e-8dc9-42ab-9630-2ae23e414026</t>
+          <t>ca-cioos_d7ffd737-5725-4a56-9134-a9ad91c2734d</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -23326,7 +23330,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Rocky Subtidal Fish and Invertebrate Community Surveys from the Central Coast of BC</t>
+          <t>Seton and Anderson Lake Multibeam Survey - 2024 - British Columbia</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -23344,12 +23348,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -23372,37 +23376,37 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.7, 51.35], [-127.3, 51.35], [-127.3, 52.27], [-128.7, 52.27], [-128.7, 51.35]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.4, 50.62], [-122.0, 50.62], [-122.0, 50.75], [-122.4, 50.75], [-122.4, 50.62]]]}</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>[{'max': '15.0', 'min': '0.0'}]</t>
+          <t>[{'max': '254.0', 'min': '61.0'}]</t>
         </is>
       </c>
       <c r="Q210" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>10.21966/jj9p-d309</t>
+          <t>10.21966/zfxe-rd73</t>
         </is>
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtF5vh1GUMdwtJdYjoJ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCe-GBA4i93dk_I9uOR</t>
         </is>
       </c>
       <c r="T210" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="U210" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="V210" t="n">
@@ -23423,12 +23427,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>7fa8cfec-e2e3-4459-9b9d-836335b9fcfa</t>
+          <t>4a949e26-fe94-4f63-a3c6-a62e19301102</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>ca-cioos_00f42725-0a88-4d4f-87a9-4e359d2abff4</t>
+          <t>ca-cioos_35beb32e-8dc9-42ab-9630-2ae23e414026</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -23438,7 +23442,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Knight Inlet Remotely Operated Vehicle Marine Habitat Survey</t>
+          <t>Rocky Subtidal Fish and Invertebrate Community Surveys from the Central Coast of BC</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -23456,12 +23460,12 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -23484,46 +23488,48 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.0, 50.65], [-125.9, 50.65], [-125.9, 50.71], [-126.0, 50.71], [-126.0, 50.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.7, 51.35], [-127.3, 51.35], [-127.3, 52.27], [-128.7, 52.27], [-128.7, 51.35]]]}</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>[{'max': '105.0', 'min': '0.0'}]</t>
+          <t>[{'max': '15.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q211" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>10.21966/529y-sh57</t>
+          <t>10.21966/jj9p-d309</t>
         </is>
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OG736nDr1-1b51V4ZIc</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtF5vh1GUMdwtJdYjoJ</t>
         </is>
       </c>
       <c r="T211" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="U211" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="V211" t="inlineStr"/>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="V211" t="n">
+        <v>1</v>
+      </c>
       <c r="W211" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X211" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -23533,12 +23539,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>5576c279-6d3a-4323-8104-0e1040d9906c</t>
+          <t>7fa8cfec-e2e3-4459-9b9d-836335b9fcfa</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>ca-cioos_314a0846-0fe9-4c2e-81e2-d2b24ac98b6e</t>
+          <t>ca-cioos_00f42725-0a88-4d4f-87a9-4e359d2abff4</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -23548,7 +23554,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Understory kelp biomass data from BC Central Coast</t>
+          <t>Knight Inlet Remotely Operated Vehicle Marine Habitat Survey</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -23566,12 +23572,12 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -23594,46 +23600,46 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.7, 51.33], [-127.4, 51.33], [-127.4, 52.26], [-128.7, 52.26], [-128.7, 51.33]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.0, 50.65], [-125.9, 50.65], [-125.9, 50.71], [-126.0, 50.71], [-126.0, 50.65]]]}</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '105.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q212" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>10.21966/wmsy-5g39</t>
+          <t>10.21966/529y-sh57</t>
         </is>
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtGQFN6AV5bNminNtYH</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OG736nDr1-1b51V4ZIc</t>
         </is>
       </c>
       <c r="T212" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="U212" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="V212" t="inlineStr"/>
       <c r="W212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X212" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -23643,12 +23649,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>cc016896-78d9-46e8-887d-6c1dd106c0e8</t>
+          <t>5576c279-6d3a-4323-8104-0e1040d9906c</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>ca-cioos_52d4f546-dfdf-4bf1-b1ad-f6ec6f2663c0</t>
+          <t>ca-cioos_314a0846-0fe9-4c2e-81e2-d2b24ac98b6e</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -23658,7 +23664,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Bute Inlet Geo-Hazards &amp; Ramsay West - 2024 - Airborne Coastal Observatory</t>
+          <t>Understory kelp biomass data from BC Central Coast</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -23676,12 +23682,12 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -23704,42 +23710,40 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.5, 50.23], [-124.1, 50.23], [-124.1, 51.73], [-125.5, 51.73], [-125.5, 50.23]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.7, 51.33], [-127.4, 51.33], [-127.4, 52.26], [-128.7, 52.26], [-128.7, 51.33]]]}</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>[{'max': '2500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q213" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>10.21966/8yp1-7m94</t>
+          <t>10.21966/wmsy-5g39</t>
         </is>
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCKR1jead4rZb1ooVa6</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/df5J7W5Hk4e0p4yvlOAI0qcU9Gs2/-MtGQFN6AV5bNminNtYH</t>
         </is>
       </c>
       <c r="T213" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="U213" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="V213" t="n">
-        <v>1</v>
-      </c>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr"/>
       <c r="W213" t="n">
         <v>0</v>
       </c>
@@ -23755,12 +23759,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>046e5ef5-1480-4868-a65f-23171088bdb8</t>
+          <t>cc016896-78d9-46e8-887d-6c1dd106c0e8</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>ca-cioos_31e15496-e906-43f4-9120-2446ab6125b2</t>
+          <t>ca-cioos_52d4f546-dfdf-4bf1-b1ad-f6ec6f2663c0</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -23770,7 +23774,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Elliot Creek Aerial Photo and LiDAR Survey</t>
+          <t>Bute Inlet Geo-Hazards &amp; Ramsay West - 2024 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -23788,7 +23792,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -23816,12 +23820,12 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.8, 50.84], [-124.5, 50.84], [-124.5, 50.99], [-124.8, 50.99], [-124.8, 50.84]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.5, 50.23], [-124.1, 50.23], [-124.1, 51.73], [-125.5, 51.73], [-125.5, 50.23]]]}</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>[{'max': '2650.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q214" t="inlineStr">
@@ -23831,25 +23835,27 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>10.21966/g64t-ec45</t>
+          <t>10.21966/8yp1-7m94</t>
         </is>
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICfZ5e-2vhf5NUtDZS</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCKR1jead4rZb1ooVa6</t>
         </is>
       </c>
       <c r="T214" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="U214" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="V214" t="inlineStr"/>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="V214" t="n">
+        <v>1</v>
+      </c>
       <c r="W214" t="n">
         <v>0</v>
       </c>
@@ -23865,12 +23871,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>8ce79018-75da-42f8-b7cd-195a412ab532</t>
+          <t>046e5ef5-1480-4868-a65f-23171088bdb8</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>ca-cioos_98807d0a-ba68-41e3-a2f5-e3248b459904</t>
+          <t>ca-cioos_31e15496-e906-43f4-9120-2446ab6125b2</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -23880,7 +23886,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Place Glacier Aerial Photo and LiDAR Survey</t>
+          <t>Elliot Creek Aerial Photo and LiDAR Survey</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -23918,7 +23924,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Tula Foundation</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N215" t="n">
@@ -23926,12 +23932,12 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.7, 50.39], [-122.6, 50.39], [-122.6, 50.48], [-122.7, 50.48], [-122.7, 50.39]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.8, 50.84], [-124.5, 50.84], [-124.5, 50.99], [-124.8, 50.99], [-124.8, 50.84]]]}</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>[{'max': '2587.0', 'min': '500.0'}]</t>
+          <t>[{'max': '2650.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q215" t="inlineStr">
@@ -23941,12 +23947,12 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>10.21966/0ydj-0t79</t>
+          <t>10.21966/g64t-ec45</t>
         </is>
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICMGpnoARQcIltW087</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICfZ5e-2vhf5NUtDZS</t>
         </is>
       </c>
       <c r="T215" t="inlineStr">
@@ -23975,12 +23981,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>83f387d2-f77e-4921-af15-e064d87ad01a</t>
+          <t>8ce79018-75da-42f8-b7cd-195a412ab532</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>ca-cioos_53730b70-be6f-4e24-8b9d-4a5e2c491121</t>
+          <t>ca-cioos_98807d0a-ba68-41e3-a2f5-e3248b459904</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -23990,12 +23996,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Cloud-Based LiDAR Application - ELVIZ - Place Glacier, Mt. Robson, and Elliot Creek, BC</t>
+          <t>Place Glacier Aerial Photo and LiDAR Survey</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>dataset</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -24028,7 +24034,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Tula Foundation</t>
         </is>
       </c>
       <c r="N216" t="n">
@@ -24036,12 +24042,12 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.5, 50.34], [-118.7, 50.34], [-118.7, 53.28], [-124.5, 53.28], [-124.5, 50.34]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.7, 50.39], [-122.6, 50.39], [-122.6, 50.48], [-122.7, 50.48], [-122.7, 50.39]]]}</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>[{'max': '3954.0', 'min': '0.0'}]</t>
+          <t>[{'max': '2587.0', 'min': '500.0'}]</t>
         </is>
       </c>
       <c r="Q216" t="inlineStr">
@@ -24051,27 +24057,25 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>10.21966/6x1v-1v62</t>
+          <t>10.21966/0ydj-0t79</t>
         </is>
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OIMCEnEEW63IyHyYZOM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICMGpnoARQcIltW087</t>
         </is>
       </c>
       <c r="T216" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="U216" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="V216" t="n">
-        <v>1</v>
-      </c>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr"/>
       <c r="W216" t="n">
         <v>0</v>
       </c>
@@ -24087,12 +24091,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
+          <t>83f387d2-f77e-4921-af15-e064d87ad01a</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>ca-cioos_78818ed7-ec26-4004-afa1-137741ddda1e</t>
+          <t>ca-cioos_53730b70-be6f-4e24-8b9d-4a5e2c491121</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -24102,12 +24106,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Calliarthron 2023 Experiment - Environmental Data</t>
+          <t>Cloud-Based LiDAR Application - ELVIZ - Place Glacier, Mt. Robson, and Elliot Creek, BC</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>service</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -24120,7 +24124,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>Wet Lab</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -24140,7 +24144,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>University of British Columbia</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N217" t="n">
@@ -24148,37 +24152,37 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.5, 50.34], [-118.7, 50.34], [-118.7, 53.28], [-124.5, 53.28], [-124.5, 50.34]]]}</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '3954.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q217" t="inlineStr">
         <is>
-          <t>other, inorganicCarbon</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>10.21966/7nwn-bj60</t>
+          <t>10.21966/6x1v-1v62</t>
         </is>
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-O6XAwxhj0r9Xs-V2QSA</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-OIMCEnEEW63IyHyYZOM</t>
         </is>
       </c>
       <c r="T217" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="U217" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="V217" t="n">
@@ -24199,12 +24203,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
+          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>ca-cioos_87341cb3-f906-4fa5-973c-b6742aa0fbb5</t>
+          <t>ca-cioos_78818ed7-ec26-4004-afa1-137741ddda1e</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -24214,7 +24218,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Glacier and Ice Aerial Surveys in British Columbia - 2023-2024 - Hakai Airborne Coastal Observatory</t>
+          <t>Calliarthron 2023 Experiment - Environmental Data</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -24232,7 +24236,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Wet Lab</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -24252,7 +24256,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="N218" t="n">
@@ -24260,27 +24264,27 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.9, 48.81], [-115.2, 48.81], [-115.2, 54.38], [-128.9, 54.38], [-128.9, 48.81]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>[{'max': '3954.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q218" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>other, inorganicCarbon</t>
         </is>
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>10.21966/ks82-th39</t>
+          <t>10.21966/7nwn-bj60</t>
         </is>
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OP2QaXeKeZ30lz51gEE</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-O6XAwxhj0r9Xs-V2QSA</t>
         </is>
       </c>
       <c r="T218" t="inlineStr">
@@ -24290,11 +24294,11 @@
       </c>
       <c r="U218" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="V218" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W218" t="n">
         <v>0</v>
@@ -24311,12 +24315,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>6c99bd67-3be1-4818-bf01-dfa56e910db3</t>
+          <t>2916abf5-419e-4cd7-8e25-f45f07a21313</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>ca-cioos_96e3dd9c-7863-44d5-95cd-a3d0a8653d83</t>
+          <t>ca-cioos_87341cb3-f906-4fa5-973c-b6742aa0fbb5</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -24326,7 +24330,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Glacier and Ice Aerial Surveys in British Columbia - 2022 - Hakai Airborne Coastal Observatory</t>
+          <t>Glacier and Ice Aerial Surveys in British Columbia - 2023-2024 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -24344,7 +24348,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -24372,12 +24376,12 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.8, 48.1], [-113.1, 48.1], [-113.1, 56.61], [-127.8, 56.61], [-127.8, 48.1]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.9, 48.81], [-115.2, 48.81], [-115.2, 54.38], [-128.9, 54.38], [-128.9, 48.81]]]}</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>[{'max': '4000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '3954.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q219" t="inlineStr">
@@ -24387,12 +24391,12 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>10.21966/n3b4-d226</t>
+          <t>10.21966/ks82-th39</t>
         </is>
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NM0zdQjdjAMBZ4cN8ou</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OP2QaXeKeZ30lz51gEE</t>
         </is>
       </c>
       <c r="T219" t="inlineStr">
@@ -24402,18 +24406,18 @@
       </c>
       <c r="U219" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="V219" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W219" t="n">
         <v>0</v>
       </c>
       <c r="X219" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -24423,12 +24427,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
+          <t>6c99bd67-3be1-4818-bf01-dfa56e910db3</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>ca-cioos_47d8bdd4-c815-4e8d-8d75-53a9db4ae46a</t>
+          <t>ca-cioos_96e3dd9c-7863-44d5-95cd-a3d0a8653d83</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -24438,7 +24442,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Glaciers in Western North America Mass Loss Geospatial Data (2021-2024)</t>
+          <t>Glacier and Ice Aerial Surveys in British Columbia - 2022 - Hakai Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -24484,12 +24488,12 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.3, 54.17], [-119.5, 55.38], [-112.5, 52.06], [-115.3, 47.05], [-125.9, 48.0], [-128.3, 51.41], [-127.3, 54.17]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.8, 48.1], [-113.1, 48.1], [-113.1, 56.61], [-127.8, 56.61], [-127.8, 48.1]]]}</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>[{'max': '2822.0', 'min': '0.0'}]</t>
+          <t>[{'max': '4000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q220" t="inlineStr">
@@ -24499,33 +24503,33 @@
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>10.21966/p6jv-pe95</t>
+          <t>10.21966/n3b4-d226</t>
         </is>
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OP86akjVj471Wit4O2y</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-NM0zdQjdjAMBZ4cN8ou</t>
         </is>
       </c>
       <c r="T220" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="U220" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="V220" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W220" t="n">
         <v>0</v>
       </c>
       <c r="X220" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2025', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -24535,12 +24539,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
+          <t>d70bcd3d-dc07-479f-856f-ad70d11c51f1</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>ca-cioos_1d142201-cbbe-4c58-b2c2-1feeac112c51</t>
+          <t>ca-cioos_47d8bdd4-c815-4e8d-8d75-53a9db4ae46a</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -24550,7 +24554,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>iTrack Oysters September 2023 Experiment - Environmental and Oyster Health Data</t>
+          <t>Glaciers in Western North America Mass Loss Geospatial Data (2021-2024)</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -24568,7 +24572,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Wet Lab</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -24588,7 +24592,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>University of Victoria</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N221" t="n">
@@ -24596,41 +24600,41 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.3, 54.17], [-119.5, 55.38], [-112.5, 52.06], [-115.3, 47.05], [-125.9, 48.0], [-128.3, 51.41], [-127.3, 54.17]]]}</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '2822.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q221" t="inlineStr">
         <is>
-          <t>inorganicCarbon, other</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>10.21966/q1m4-pz94</t>
+          <t>10.21966/p6jv-pe95</t>
         </is>
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-OMsFWHXIwEWiFjwQeEo</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OP86akjVj471Wit4O2y</t>
         </is>
       </c>
       <c r="T221" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="U221" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="V221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W221" t="n">
         <v>0</v>
@@ -24647,12 +24651,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>da040f55-984d-490d-b917-a67856de4bac</t>
+          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>ca-cioos_31ac855d-bf15-42d8-b20d-754638202c66</t>
+          <t>ca-cioos_1d142201-cbbe-4c58-b2c2-1feeac112c51</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -24662,7 +24666,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Sea Stars 2024 Experiment - Environmental Data</t>
+          <t>iTrack Oysters September 2023 Experiment - Environmental and Oyster Health Data</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -24700,7 +24704,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>University of Victoria</t>
         </is>
       </c>
       <c r="N222" t="n">
@@ -24723,12 +24727,12 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>10.21966/jkf5-ss08</t>
+          <t>10.21966/q1m4-pz94</t>
         </is>
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-OIMW8OO0buhOm_kHuIz</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-OMsFWHXIwEWiFjwQeEo</t>
         </is>
       </c>
       <c r="T222" t="inlineStr">
@@ -24759,12 +24763,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
+          <t>da040f55-984d-490d-b917-a67856de4bac</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>ca-cioos_d959f8f3-6d20-42fe-94da-be49bcd3aeca</t>
+          <t>ca-cioos_31ac855d-bf15-42d8-b20d-754638202c66</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -24774,7 +24778,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Eelgrass (Z. marina) extent at Gulf Islands National Park Reserve eelgrass monitoring sites (2024)</t>
+          <t>Sea Stars 2024 Experiment - Environmental Data</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -24792,7 +24796,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Wet Lab</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -24812,15 +24816,15 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Gulf Islands National Park Reserve</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N223" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.4, 48.61], [-123.0, 48.61], [-123.0, 48.87], [-123.4, 48.87], [-123.4, 48.61]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.2, 50.12]}</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
@@ -24830,31 +24834,31 @@
       </c>
       <c r="Q223" t="inlineStr">
         <is>
-          <t>other, seagrassCoverAndComposition</t>
+          <t>inorganicCarbon, other</t>
         </is>
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>10.21966/x3jm-p494</t>
+          <t>10.21966/jkf5-ss08</t>
         </is>
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OUG8anVj4yBJDEHy6Wj</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/KstJ1LGR2ZbovZiE2SeSKVz4y4E2/-OIMW8OO0buhOm_kHuIz</t>
         </is>
       </c>
       <c r="T223" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="U223" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="V223" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W223" t="n">
         <v>0</v>
@@ -24871,12 +24875,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>262f25ca-ca11-4b10-bb6c-9aec117319a9</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>ca-cioos_39a83551-ab8e-45be-a564-cece4b229371</t>
+          <t>ca-cioos_d959f8f3-6d20-42fe-94da-be49bcd3aeca</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -24886,7 +24890,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Zooplankton taxonomic abundance and biomass along the BC Coast</t>
+          <t>Eelgrass (Z. marina) extent at Gulf Islands National Park Reserve eelgrass monitoring sites (2024)</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -24904,12 +24908,12 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -24924,7 +24928,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Gulf Islands National Park Reserve</t>
         </is>
       </c>
       <c r="N224" t="n">
@@ -24932,48 +24936,48 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.4, 48.61], [-123.0, 48.61], [-123.0, 48.87], [-123.4, 48.87], [-123.4, 48.61]]]}</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>[{'max': '350.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q224" t="inlineStr">
         <is>
-          <t>zooplanktonBiomassAndDiversity</t>
+          <t>other, seagrassCoverAndComposition</t>
         </is>
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>10.21966/g7zf-1v08</t>
+          <t>10.21966/x3jm-p494</t>
         </is>
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-ODO1YbIGbR3Rd8hvLxT</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OUG8anVj4yBJDEHy6Wj</t>
         </is>
       </c>
       <c r="T224" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="U224" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="V224" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W224" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X224" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 2}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -24983,12 +24987,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>ca-cioos_dbb33efe-c207-4d9c-abef-2350595bf47a</t>
+          <t>ca-cioos_39a83551-ab8e-45be-a564-cece4b229371</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -24998,7 +25002,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Size-fractionated zooplankton biomass and isotopes along the BC coast</t>
+          <t>Zooplankton taxonomic abundance and biomass along the BC Coast</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -25040,7 +25044,7 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O225" t="inlineStr">
         <is>
@@ -25059,12 +25063,12 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>10.21966/tcp2-mm86</t>
+          <t>10.21966/g7zf-1v08</t>
         </is>
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/NZb1YZT9Xtbc9Cp9Jc3OtSLRffT2/-OQtxgedRzyaVsL4bWUx</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/jnK2pbrIzbMBHpSiUOi8XDUeev93/-ODO1YbIGbR3Rd8hvLxT</t>
         </is>
       </c>
       <c r="T225" t="inlineStr">
@@ -25078,7 +25082,7 @@
         </is>
       </c>
       <c r="V225" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W225" t="n">
         <v>2</v>
@@ -25095,12 +25099,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>328b062b-3af6-4149-b90f-a85b99dc40eb</t>
+          <t>186d3139-66a1-43f9-9ac7-c5607252146e</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>ca-cioos_34a20547-cb60-4ecf-901b-f4ca52eae451</t>
+          <t>ca-cioos_dbb33efe-c207-4d9c-abef-2350595bf47a</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -25110,7 +25114,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), Central Coast, British Columbia, Canada</t>
+          <t>Size-fractionated zooplankton biomass and isotopes along the BC coast</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -25128,12 +25132,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -25156,48 +25160,48 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.4], [-127.9, 51.4], [-127.9, 52.09], [-128.5, 52.09], [-128.5, 51.4]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '350.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q226" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>zooplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>10.21966/w08z-zk15</t>
+          <t>10.21966/tcp2-mm86</t>
         </is>
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8sPFZem68YnizN7L7l</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/NZb1YZT9Xtbc9Cp9Jc3OtSLRffT2/-OQtxgedRzyaVsL4bWUx</t>
         </is>
       </c>
       <c r="T226" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="U226" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="V226" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W226" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X226" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2025', 'total': 2}]</t>
         </is>
       </c>
     </row>
@@ -25207,12 +25211,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>439d703a-2132-4dbd-8d39-a4cacdb8f81d</t>
+          <t>328b062b-3af6-4149-b90f-a85b99dc40eb</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>ca-cioos_e8343aa0-dbea-4267-9f78-662bec08d4bc</t>
+          <t>ca-cioos_34a20547-cb60-4ecf-901b-f4ca52eae451</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -25222,7 +25226,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020-2022), Central Coast, British Columbia, Canada</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -25240,7 +25244,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -25268,7 +25272,7 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 52.15], [-128.5, 52.23], [-128.2, 52.05], [-128.0, 51.71], [-128.0, 51.63], [-128.2, 51.62], [-128.4, 51.8], [-128.6, 51.89], [-128.6, 51.89], [-128.6, 52.15]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.4], [-127.9, 51.4], [-127.9, 52.09], [-128.5, 52.09], [-128.5, 51.4]]]}</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -25283,12 +25287,12 @@
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>10.21966/kqzp-f639</t>
+          <t>10.21966/w08z-zk15</t>
         </is>
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-NbzgAmVWcvz-_SOMA0E</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8sPFZem68YnizN7L7l</t>
         </is>
       </c>
       <c r="T227" t="inlineStr">
@@ -25298,10 +25302,12 @@
       </c>
       <c r="U227" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="V227" t="inlineStr"/>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="V227" t="n">
+        <v>1</v>
+      </c>
       <c r="W227" t="n">
         <v>0</v>
       </c>
@@ -25317,12 +25323,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
+          <t>439d703a-2132-4dbd-8d39-a4cacdb8f81d</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>ca-cioos_f7a867ce-0f18-43f6-8148-775235d800b6</t>
+          <t>ca-cioos_e8343aa0-dbea-4267-9f78-662bec08d4bc</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -25332,7 +25338,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2023), Central Coast, British Columbia, Canada</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020-2022), Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -25350,7 +25356,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
+          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -25378,7 +25384,7 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.64], [-128.1, 51.64], [-128.1, 52.19], [-128.6, 52.19], [-128.6, 51.64]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 52.15], [-128.5, 52.23], [-128.2, 52.05], [-128.0, 51.71], [-128.0, 51.63], [-128.2, 51.62], [-128.4, 51.8], [-128.6, 51.89], [-128.6, 51.89], [-128.6, 52.15]]]}</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -25393,12 +25399,12 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>10.21966/qs1b-g693</t>
+          <t>10.21966/kqzp-f639</t>
         </is>
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-O8Dvx_fnz1WMY_Wetch</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-NbzgAmVWcvz-_SOMA0E</t>
         </is>
       </c>
       <c r="T228" t="inlineStr">
@@ -25408,12 +25414,10 @@
       </c>
       <c r="U228" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="V228" t="n">
-        <v>3</v>
-      </c>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr"/>
       <c r="W228" t="n">
         <v>0</v>
       </c>
@@ -25429,12 +25433,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
+          <t>e67a81ba-0ac5-49bd-a1fe-02b98f79d8a7</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>ca-cioos_291b98a4-d868-462c-852a-d6cf79ecf6ce</t>
+          <t>ca-cioos_f7a867ce-0f18-43f6-8148-775235d800b6</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -25444,7 +25448,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Time series of surface kelp canopy area derived from remotely piloted aerial systems (RPAS, or drone) surveys, Central Coast, British Columbia</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2023), Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -25462,12 +25466,12 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Nearshore, Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -25482,7 +25486,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Tula Foundation</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N229" t="n">
@@ -25490,7 +25494,7 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.65], [-128.1, 51.65], [-128.1, 52.09], [-128.4, 52.09], [-128.4, 51.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.64], [-128.1, 51.64], [-128.1, 52.19], [-128.6, 52.19], [-128.6, 51.64]]]}</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -25505,26 +25509,26 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>10.21966/9cbv-ra30</t>
+          <t>10.21966/qs1b-g693</t>
         </is>
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OVIwXhdGT9n7FV0wmyz</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-O8Dvx_fnz1WMY_Wetch</t>
         </is>
       </c>
       <c r="T229" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="U229" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="V229" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W229" t="n">
         <v>0</v>
@@ -25541,12 +25545,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>44bdc298-1329-400a-bc02-4d35d251865d</t>
+          <t>39cc31fc-aa41-43f5-bfe7-48ea173b1f1e</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>ca-cioos_012164c6-28dd-4078-b702-f0c2ce63d548</t>
+          <t>ca-cioos_291b98a4-d868-462c-852a-d6cf79ecf6ce</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -25556,7 +25560,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Biodiversity and Oceanographic data from the False Creek Bioblitz, 2022</t>
+          <t>Time series of surface kelp canopy area derived from remotely piloted aerial systems (RPAS, or drone) surveys, Central Coast, British Columbia</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -25574,12 +25578,12 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Genomics, Nearshore, Oceanography</t>
+          <t>Nearshore, Geospatial</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
@@ -25594,48 +25598,50 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Hakai Institute</t>
+          <t>Tula Foundation</t>
         </is>
       </c>
       <c r="N230" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-123.2, 49.27], [-123.1, 49.27], [-123.1, 49.28], [-123.2, 49.28], [-123.2, 49.27]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.65], [-128.1, 51.65], [-128.1, 52.09], [-128.4, 52.09], [-128.4, 51.65]]]}</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q230" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution, marineTurtlesBirdsMammalsAbundanceAndDistribution, fishAbundanceAndDistribution, seaSurfaceTemperature, subSurfaceTemperature, other, microbeBiomassAndDiversity</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>10.21966/8sgn-jg38</t>
+          <t>10.21966/9cbv-ra30</t>
         </is>
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-Nd0YqVrleM4mMLlJDSU</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OVIwXhdGT9n7FV0wmyz</t>
         </is>
       </c>
       <c r="T230" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="U230" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="V230" t="inlineStr"/>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="V230" t="n">
+        <v>2</v>
+      </c>
       <c r="W230" t="n">
         <v>0</v>
       </c>
@@ -25651,12 +25657,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
+          <t>44bdc298-1329-400a-bc02-4d35d251865d</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>ca-cioos_7e9c97a3-4bf1-4852-81b6-d74cedf2c94c</t>
+          <t>ca-cioos_012164c6-28dd-4078-b702-f0c2ce63d548</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -25666,7 +25672,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Environmental DNA survey of Calvert Island, British Columbia, 2021</t>
+          <t>Biodiversity and Oceanographic data from the False Creek Bioblitz, 2022</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -25684,7 +25690,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Genomics</t>
+          <t>Genomics, Nearshore, Oceanography</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -25708,46 +25714,44 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.31], [-127.3, 51.31], [-127.3, 52.05], [-128.6, 52.05], [-128.6, 51.31]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-123.2, 49.27], [-123.1, 49.27], [-123.1, 49.28], [-123.2, 49.28], [-123.2, 49.27]]]}</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>[{'max': '60.0', 'min': '0.0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q231" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
+          <t>invertebrateAbundanceAndDistribution, marineTurtlesBirdsMammalsAbundanceAndDistribution, fishAbundanceAndDistribution, seaSurfaceTemperature, subSurfaceTemperature, other, microbeBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>10.21966/vdyq-r660</t>
+          <t>10.21966/8sgn-jg38</t>
         </is>
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-ORCQx4QHUuJ1NV1SEig</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-Nd0YqVrleM4mMLlJDSU</t>
         </is>
       </c>
       <c r="T231" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="U231" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="V231" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr"/>
       <c r="W231" t="n">
         <v>0</v>
       </c>
@@ -25763,12 +25767,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
+          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>ca-cioos_9a018fe0-8bd1-41d1-af8d-079960b71473</t>
+          <t>ca-cioos_7e9c97a3-4bf1-4852-81b6-d74cedf2c94c</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -25778,7 +25782,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Data from: Prentice et al. 2025. Vibrio pectenicida strain FHCF-3 is a causative agent of sea star wasting disease</t>
+          <t>Environmental DNA survey of Calvert Island, British Columbia, 2021</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -25796,7 +25800,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Genomics, Nearshore</t>
+          <t>Genomics</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -25820,41 +25824,41 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 47.91], [-122.3, 47.91], [-122.3, 51.82], [-128.5, 51.82], [-128.5, 47.91]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.6, 51.31], [-127.3, 51.31], [-127.3, 52.05], [-128.6, 52.05], [-128.6, 51.31]]]}</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '60.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q232" t="inlineStr">
         <is>
-          <t>microbeBiomassAndDiversity</t>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>10.21966/4dvn-5y90</t>
+          <t>10.21966/vdyq-r660</t>
         </is>
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/24mf0TP0vkh6bmNOOA3ynoTFPNJ2/-OX0Xm6VoYH22oc68Jfp</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-ORCQx4QHUuJ1NV1SEig</t>
         </is>
       </c>
       <c r="T232" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="U232" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="V232" t="n">
@@ -25875,12 +25879,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>0272fd06-6ac8-48cd-80c9-b6e05f15be0f</t>
+          <t>6be4c552-469a-4558-b63d-7a2c52566fe2</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>ca-cioos_132cecdf-de8a-4b17-b610-0e2b3a343812</t>
+          <t>ca-cioos_9a018fe0-8bd1-41d1-af8d-079960b71473</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -25890,7 +25894,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), North Coast, British Columbia, Canada</t>
+          <t>Data from: Prentice et al. 2025. Vibrio pectenicida strain FHCF-3 is a causative agent of sea star wasting disease</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -25908,7 +25912,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
+          <t>Genomics, Nearshore</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -25932,11 +25936,11 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-131.0, 53.74], [-130.4, 53.74], [-130.4, 54.46], [-131.0, 54.46], [-131.0, 53.74]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 47.91], [-122.3, 47.91], [-122.3, 51.82], [-128.5, 51.82], [-128.5, 47.91]]]}</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
@@ -25946,27 +25950,27 @@
       </c>
       <c r="Q233" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>microbeBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>10.21966/m93t-4181</t>
+          <t>10.21966/4dvn-5y90</t>
         </is>
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8sPEiAvbPxw16A-L6I</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/24mf0TP0vkh6bmNOOA3ynoTFPNJ2/-OX0Xm6VoYH22oc68Jfp</t>
         </is>
       </c>
       <c r="T233" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="U233" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="V233" t="n">
@@ -25987,12 +25991,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>b01f58f7-1518-4829-aff6-ac4a8f2c0616</t>
+          <t>0272fd06-6ac8-48cd-80c9-b6e05f15be0f</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>ca-cioos_f815a700-c943-4d6f-afeb-a4854ad10cfc</t>
+          <t>ca-cioos_132cecdf-de8a-4b17-b610-0e2b3a343812</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -26002,7 +26006,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), North Vancouver Island, British Columbia, Canada</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), North Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -26048,7 +26052,7 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.6, 50.35], [-124.8, 50.35], [-124.8, 50.7], [-126.6, 50.7], [-126.6, 50.35]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-131.0, 53.74], [-130.4, 53.74], [-130.4, 54.46], [-131.0, 54.46], [-131.0, 53.74]]]}</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
@@ -26063,12 +26067,12 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>10.21966/ntdg-e790</t>
+          <t>10.21966/m93t-4181</t>
         </is>
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8raBb8T2xZJ-oRzesS</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8sPEiAvbPxw16A-L6I</t>
         </is>
       </c>
       <c r="T234" t="inlineStr">
@@ -26099,12 +26103,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
+          <t>b01f58f7-1518-4829-aff6-ac4a8f2c0616</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>ca-cioos_5b4cbe9f-8f2e-414c-80ff-741372891fe9</t>
+          <t>ca-cioos_f815a700-c943-4d6f-afeb-a4854ad10cfc</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -26114,7 +26118,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Gitga'at Territory Coastal Monitoring and Mapping - Airborne Coastal Observatory</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2024), North Vancouver Island, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -26124,7 +26128,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="H235" t="b">
@@ -26132,7 +26136,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -26160,48 +26164,48 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.8, 52.92], [-129.1, 52.92], [-129.1, 53.67], [-129.8, 53.67], [-129.8, 52.92]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.6, 50.35], [-124.8, 50.35], [-124.8, 50.7], [-126.6, 50.7], [-126.6, 50.35]]]}</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>[{'max': '475.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q235" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>10.21966/0xex-r023</t>
+          <t>10.21966/ntdg-e790</t>
         </is>
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OdPFhWCkXwvqjCqum30</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-O8raBb8T2xZJ-oRzesS</t>
         </is>
       </c>
       <c r="T235" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="U235" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="V235" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X235" t="inlineStr">
         <is>
-          <t>[{'year': '2025', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -26211,12 +26215,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>0074861a-39f2-42c1-ae71-abef4f78fd78</t>
+          <t>b9671efe-5980-452b-90f8-f30e4f1bc194</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>ca-cioos_b5f0f854-efe1-4132-808d-074244d813e1</t>
+          <t>ca-cioos_5b4cbe9f-8f2e-414c-80ff-741372891fe9</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -26226,7 +26230,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Gitga'at Territory Coastal Mapping Project</t>
+          <t>Gitga'at Territory Coastal Monitoring and Mapping - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -26244,12 +26248,12 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -26272,12 +26276,12 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.6, 53.18], [-129.0, 53.18], [-129.0, 53.68], [-129.6, 53.68], [-129.6, 53.18]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.8, 52.92], [-129.1, 52.92], [-129.1, 53.67], [-129.8, 53.67], [-129.8, 52.92]]]}</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>[{'max': '150.0', 'min': '0.0'}]</t>
+          <t>[{'max': '475.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q236" t="inlineStr">
@@ -26287,12 +26291,12 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>10.21966/2aap-hn61</t>
+          <t>10.21966/0xex-r023</t>
         </is>
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Oa5tvTh2mXFQbI3SkzK</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OdPFhWCkXwvqjCqum30</t>
         </is>
       </c>
       <c r="T236" t="inlineStr">
@@ -26302,18 +26306,18 @@
       </c>
       <c r="U236" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="V236" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W236" t="n">
         <v>1</v>
       </c>
       <c r="X236" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
+          <t>[{'year': '2025', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -26323,12 +26327,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>5fc21b4d-2dfa-4908-8aaf-90a82509324a</t>
+          <t>0074861a-39f2-42c1-ae71-abef4f78fd78</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>ca-cioos_35900174-c64a-493e-9a7e-390ac7e997e4</t>
+          <t>ca-cioos_b5f0f854-efe1-4132-808d-074244d813e1</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -26338,7 +26342,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Bowhead Whale Drone Data Collection - Cumberland Sound - Nunavut</t>
+          <t>Gitga'at Territory Coastal Mapping Project</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -26348,7 +26352,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>CC-BY-4.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H237" t="b">
@@ -26361,7 +26365,7 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -26384,12 +26388,12 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-68.21, 64.72], [-64.14, 64.72], [-64.14, 66.48], [-68.21, 66.48], [-68.21, 64.72]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.6, 53.18], [-129.0, 53.18], [-129.0, 53.68], [-129.6, 53.68], [-129.6, 53.18]]]}</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '150.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q237" t="inlineStr">
@@ -26399,22 +26403,22 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>10.21966/fv0q-q364</t>
+          <t>10.21966/2aap-hn61</t>
         </is>
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OeY_smu3pJj8TBE9ivK</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Oa5tvTh2mXFQbI3SkzK</t>
         </is>
       </c>
       <c r="T237" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="U237" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="V237" t="n">
@@ -26435,12 +26439,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>dbfc5189-f657-4034-af7f-cc358042047d</t>
+          <t>5fc21b4d-2dfa-4908-8aaf-90a82509324a</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>ca-cioos_78686602-1aa9-4246-8a24-915471fe4255</t>
+          <t>ca-cioos_35900174-c64a-493e-9a7e-390ac7e997e4</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -26450,7 +26454,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2025), North Coast, British Columbia, Canada</t>
+          <t>Bowhead Whale Drone Data Collection - Cumberland Sound - Nunavut</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -26468,7 +26472,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -26496,7 +26500,7 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-129.8, 52.69], [-129.0, 52.69], [-129.0, 53.14], [-129.8, 53.14], [-129.8, 52.69]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-68.21, 64.72], [-64.14, 64.72], [-64.14, 66.48], [-68.21, 66.48], [-68.21, 64.72]]]}</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
@@ -26506,17 +26510,17 @@
       </c>
       <c r="Q238" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>10.21966/nwg7-fe05</t>
+          <t>10.21966/fv0q-q364</t>
         </is>
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OeItznXpvEFI_t-jsCl</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OeY_smu3pJj8TBE9ivK</t>
         </is>
       </c>
       <c r="T238" t="inlineStr">
@@ -26526,16 +26530,18 @@
       </c>
       <c r="U238" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="V238" t="inlineStr"/>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="V238" t="n">
+        <v>1</v>
+      </c>
       <c r="W238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X238" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -26545,12 +26551,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>9eda1bfc-0d13-4e1d-9542-b9a7cce16991</t>
+          <t>dbfc5189-f657-4034-af7f-cc358042047d</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>ca-cioos_c544ef5b-967d-46b2-bbcf-395116b50e7d</t>
+          <t>ca-cioos_78686602-1aa9-4246-8a24-915471fe4255</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -26560,7 +26566,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Mystery Creek Aerial Photo and LiDAR Survey - 2025 - Airborne Coastal Observatory</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2025), North Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -26578,7 +26584,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -26606,32 +26612,32 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.9, 50.21], [-122.8, 50.21], [-122.8, 50.25], [-122.9, 50.25], [-122.9, 50.21]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-129.8, 52.69], [-129.0, 52.69], [-129.0, 53.14], [-129.8, 53.14], [-129.8, 52.69]]]}</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>[{'max': '1690.0', 'min': '378.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q239" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>10.21966/02qp-4945</t>
+          <t>10.21966/nwg7-fe05</t>
         </is>
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/FfIFMI0sx4beFpYCFD9liFIEiMt1/-OeTbb0MbfTCH-YFCNGG</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OeItznXpvEFI_t-jsCl</t>
         </is>
       </c>
       <c r="T239" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="U239" t="inlineStr">
@@ -26655,12 +26661,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>37440dfd-53f8-462b-a544-b6c8d39c44cd</t>
+          <t>9eda1bfc-0d13-4e1d-9542-b9a7cce16991</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>ca-cioos_43bad5e5-0484-4c11-80a5-c844245f940e</t>
+          <t>ca-cioos_c544ef5b-967d-46b2-bbcf-395116b50e7d</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -26670,7 +26676,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Farwell Canyon Airborne Surveys - 2024 - Airborne Coastal Observatory</t>
+          <t>Mystery Creek Aerial Photo and LiDAR Survey - 2025 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -26716,12 +26722,12 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.6, 51.86], [-122.5, 51.81], [-122.4, 51.74], [-122.4, 51.73], [-122.5, 51.8], [-122.7, 51.83], [-122.6, 51.86]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.9, 50.21], [-122.8, 50.21], [-122.8, 50.25], [-122.9, 50.25], [-122.9, 50.21]]]}</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>[{'max': '1347.62', 'min': '345.9'}]</t>
+          <t>[{'max': '1690.0', 'min': '378.0'}]</t>
         </is>
       </c>
       <c r="Q240" t="inlineStr">
@@ -26731,22 +26737,22 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>10.21966/dtt0-s264</t>
+          <t>10.21966/02qp-4945</t>
         </is>
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/FfIFMI0sx4beFpYCFD9liFIEiMt1/-OgDkxI9LmB0KWXvOsZe</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/FfIFMI0sx4beFpYCFD9liFIEiMt1/-OeTbb0MbfTCH-YFCNGG</t>
         </is>
       </c>
       <c r="T240" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="U240" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="V240" t="inlineStr"/>
@@ -26765,12 +26771,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
+          <t>37440dfd-53f8-462b-a544-b6c8d39c44cd</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>ca-cioos_7cafde4f-bdd5-4b95-a41d-7939ddcf08c6</t>
+          <t>ca-cioos_43bad5e5-0484-4c11-80a5-c844245f940e</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -26780,7 +26786,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Time series of quarterly kelp canopy extent from Landsat 5, 7, 8, and 9 since 1985</t>
+          <t>Farwell Canyon Airborne Surveys - 2024 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -26798,12 +26804,12 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>Geospatial, Nearshore</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -26826,42 +26832,40 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-130.5, 54.75], [-133.5, 54.36], [-133.0, 53.09], [-126.0, 48.92], [-123.6, 48.28], [-123.2, 48.8], [-123.8, 49.61], [-127.6, 51.04], [-128.4, 52.4], [-130.4, 54.24], [-130.5, 54.75]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.6, 51.86], [-122.5, 51.81], [-122.4, 51.74], [-122.4, 51.73], [-122.5, 51.8], [-122.7, 51.83], [-122.6, 51.86]]]}</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '1347.62', 'min': '345.9'}]</t>
         </is>
       </c>
       <c r="Q241" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>10.21966/xc7x-9207</t>
+          <t>10.21966/dtt0-s264</t>
         </is>
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OZGbDlZ5dgF0dD-ceZ7</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/FfIFMI0sx4beFpYCFD9liFIEiMt1/-OgDkxI9LmB0KWXvOsZe</t>
         </is>
       </c>
       <c r="T241" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="U241" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="V241" t="n">
-        <v>2</v>
-      </c>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="V241" t="inlineStr"/>
       <c r="W241" t="n">
         <v>0</v>
       </c>
@@ -26877,12 +26881,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>3d082072-1ee8-4005-8bba-f9ec795ad5ab</t>
+          <t>a48161da-c603-43d6-9dc6-44b861984b49</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>ca-cioos_cfa4ad65-ee12-47c0-9527-206a0f8d92ae</t>
+          <t>ca-cioos_7cafde4f-bdd5-4b95-a41d-7939ddcf08c6</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -26892,7 +26896,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Hakai Institute Drone Data Index</t>
+          <t>Time series of quarterly kelp canopy extent from Landsat 5, 7, 8, and 9 since 1985</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -26910,7 +26914,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -26938,40 +26942,42 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-134.1, 42.65], [-59.42, 42.65], [-59.42, 67.53], [-134.1, 67.53], [-134.1, 42.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-130.5, 54.75], [-133.5, 54.36], [-133.0, 53.09], [-126.0, 48.92], [-123.6, 48.28], [-123.2, 48.8], [-123.8, 49.61], [-127.6, 51.04], [-128.4, 52.4], [-130.4, 54.24], [-130.5, 54.75]]]}</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q242" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>macroalgalCanopyCoverAndComposition</t>
         </is>
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>10.21966/0r8b-t282</t>
+          <t>10.21966/xc7x-9207</t>
         </is>
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCdraToZivfj6ZZ8TqZ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/owhqxLMKaJdQBPGxgc2FH82HfLp1/-OZGbDlZ5dgF0dD-ceZ7</t>
         </is>
       </c>
       <c r="T242" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="U242" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="V242" t="inlineStr"/>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="V242" t="n">
+        <v>2</v>
+      </c>
       <c r="W242" t="n">
         <v>0</v>
       </c>
@@ -26987,12 +26993,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
+          <t>3d082072-1ee8-4005-8bba-f9ec795ad5ab</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>ca-cioos_a924b31b-9882-4abe-8d8e-e875dbbbec82</t>
+          <t>ca-cioos_cfa4ad65-ee12-47c0-9527-206a0f8d92ae</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -27002,7 +27008,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Surface Seawater and Marine Boundary Layer CO2 Time Series from the Bute Inlet Ocean Observing Station (BIOOS) Buoy, Bute Inlet, BC, Canada (Provisional)</t>
+          <t>Hakai Institute Drone Data Index</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -27020,7 +27026,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -27048,40 +27054,48 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-134.1, 42.65], [-59.42, 42.65], [-59.42, 67.53], [-134.1, 67.53], [-134.1, 42.65]]]}</t>
         </is>
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '2000.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q243" t="inlineStr">
         <is>
-          <t>inorganicCarbon, oxygen, seaSurfaceSalinity, seaSurfaceTemperature</t>
-        </is>
-      </c>
-      <c r="R243" t="inlineStr"/>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R243" t="inlineStr">
+        <is>
+          <t>10.21966/0r8b-t282</t>
+        </is>
+      </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-OlwZ9MM8a9VqCYIJo4W</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OCdraToZivfj6ZZ8TqZ</t>
         </is>
       </c>
       <c r="T243" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="U243" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="V243" t="n">
-        <v>2</v>
-      </c>
-      <c r="W243" t="inlineStr"/>
-      <c r="X243" t="inlineStr"/>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="V243" t="inlineStr"/>
+      <c r="W243" t="n">
+        <v>0</v>
+      </c>
+      <c r="X243" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -27089,12 +27103,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>0894f661-f9cb-48cb-a0b4-8a001eb69420</t>
+          <t>5dea887f-9b1d-4b20-a59a-3d4a2877a52c</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>ca-cioos_bfefcdf9-c922-4e4f-a958-aa6da739d3cd</t>
+          <t>ca-cioos_a924b31b-9882-4abe-8d8e-e875dbbbec82</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -27104,7 +27118,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Surface Seawater and Marine Boundary Layer CO2 Time Series from the Bute Inlet Ocean Observing Station (BIOOS) Buoy, Bute Inlet, BC, Canada (Research)</t>
+          <t>Surface Seawater and Marine Boundary Layer CO2 Time Series from the Bute Inlet Ocean Observing Station (BIOOS) Buoy, Bute Inlet, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -27160,17 +27174,13 @@
       </c>
       <c r="Q244" t="inlineStr">
         <is>
-          <t>oxygen, inorganicCarbon, particulateMatter, phytoplanktonBiomassAndDiversity, seaSurfaceSalinity, seaSurfaceTemperature</t>
-        </is>
-      </c>
-      <c r="R244" t="inlineStr">
-        <is>
-          <t>10.21966/4jvz-bv44</t>
-        </is>
-      </c>
+          <t>inorganicCarbon, oxygen, seaSurfaceSalinity, seaSurfaceTemperature</t>
+        </is>
+      </c>
+      <c r="R244" t="inlineStr"/>
       <c r="S244" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-OOYvTmfsWUPdHkDTTFS</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-OlwZ9MM8a9VqCYIJo4W</t>
         </is>
       </c>
       <c r="T244" t="inlineStr">
@@ -27180,18 +27190,14 @@
       </c>
       <c r="U244" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="V244" t="inlineStr"/>
-      <c r="W244" t="n">
-        <v>0</v>
-      </c>
-      <c r="X244" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="V244" t="n">
+        <v>3</v>
+      </c>
+      <c r="W244" t="inlineStr"/>
+      <c r="X244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -27199,12 +27205,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>e788c2f6-c842-4240-bab4-54a323d62174</t>
+          <t>0894f661-f9cb-48cb-a0b4-8a001eb69420</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>ca-cioos_984e6b72-15d0-4742-bb2d-9ac13b14383a</t>
+          <t>ca-cioos_bfefcdf9-c922-4e4f-a958-aa6da739d3cd</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -27214,7 +27220,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Stream Temperature Observations for Three Streams Near Gold River</t>
+          <t>Surface Seawater and Marine Boundary Layer CO2 Time Series from the Bute Inlet Ocean Observing Station (BIOOS) Buoy, Bute Inlet, BC, Canada (Research)</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -27232,12 +27238,12 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -27260,7 +27266,7 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.7, 49.96], [-125.9, 49.93], [-126.0, 49.56], [-126.7, 49.73], [-126.7, 49.96]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976], [-124.899883, 50.5976]]]}</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
@@ -27270,30 +27276,32 @@
       </c>
       <c r="Q245" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>oxygen, inorganicCarbon, particulateMatter, phytoplanktonBiomassAndDiversity, seaSurfaceSalinity, seaSurfaceTemperature</t>
         </is>
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>10.21966/cqrt-sk09</t>
+          <t>10.21966/4jvz-bv44</t>
         </is>
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DvuBcQQuVHdxmYEF4yDNBDj30lu1/-Oj8Fegu6V858hz57O8z</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-OOYvTmfsWUPdHkDTTFS</t>
         </is>
       </c>
       <c r="T245" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="U245" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="V245" t="inlineStr"/>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="V245" t="n">
+        <v>1</v>
+      </c>
       <c r="W245" t="n">
         <v>0</v>
       </c>
@@ -27309,12 +27317,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
+          <t>e788c2f6-c842-4240-bab4-54a323d62174</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>ca-cioos_84820f31-b6db-479c-a47e-f22f2899b4d2</t>
+          <t>ca-cioos_984e6b72-15d0-4742-bb2d-9ac13b14383a</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -27324,7 +27332,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Biogeochemical Sampling of 28 Streams on Vancouver Island</t>
+          <t>Stream Temperature Observations for Three Streams Near Gold River</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -27370,7 +27378,7 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 50.65], [-127.9, 50.71], [-123.6, 48.43], [-124.0, 48.36], [-127.3, 49.77], [-128.4, 50.65]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.7, 49.96], [-125.9, 49.93], [-126.0, 49.56], [-126.7, 49.73], [-126.7, 49.96]]]}</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
@@ -27385,33 +27393,31 @@
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>10.21966/chc3-rj93</t>
+          <t>10.21966/cqrt-sk09</t>
         </is>
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DvuBcQQuVHdxmYEF4yDNBDj30lu1/-OnCm7wniBlFr2gSXQhf</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DvuBcQQuVHdxmYEF4yDNBDj30lu1/-Oj8Fegu6V858hz57O8z</t>
         </is>
       </c>
       <c r="T246" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="U246" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="V246" t="n">
-        <v>3</v>
-      </c>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr"/>
       <c r="W246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X246" t="inlineStr">
         <is>
-          <t>[{'year': '2026', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -27421,12 +27427,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>63f6c693-7c22-49cc-ad7d-9aa1774a5972</t>
+          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>ca-cioos_d7b34963-67bc-404b-bdd1-b41cc750bdaa</t>
+          <t>ca-cioos_84820f31-b6db-479c-a47e-f22f2899b4d2</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -27436,7 +27442,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Fraser River Airborne Surveys - 2020 - Airborne Coastal Observatory</t>
+          <t>Biogeochemical Sampling of 28 Streams on Vancouver Island</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -27454,7 +27460,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Watersheds</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -27482,12 +27488,12 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-121.5, 49.51], [-121.3, 49.53], [-121.4, 49.95], [-121.5, 50.28], [-121.7, 50.52], [-121.8, 50.66], [-121.8, 50.76], [-121.8, 51.01], [-122.1, 51.32], [-122.3, 51.79], [-122.1, 52.11], [-122.3, 52.37], [-122.3, 52.51], [-122.6, 52.49], [-122.4, 51.96], [-122.5, 51.83], [-122.4, 51.49], [-122.3, 51.18], [-121.9, 50.95], [-121.9, 50.62], [-121.8, 50.53], [-121.7, 50.17], [-121.6, 49.89], [-121.5, 49.63], [-121.5, 49.51]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 50.65], [-127.9, 50.71], [-123.6, 48.43], [-124.0, 48.36], [-127.3, 49.77], [-128.4, 50.65]]]}</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>[{'max': '850.0', 'min': '400.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q247" t="inlineStr">
@@ -27497,31 +27503,33 @@
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>10.21966/f9m6-qg12</t>
+          <t>10.21966/chc3-rj93</t>
         </is>
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MibW0TZpoaJ4Ih_2ev7</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/DvuBcQQuVHdxmYEF4yDNBDj30lu1/-OnCm7wniBlFr2gSXQhf</t>
         </is>
       </c>
       <c r="T247" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="V247" t="inlineStr"/>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="V247" t="n">
+        <v>3</v>
+      </c>
       <c r="W247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X247" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2026', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -27531,12 +27539,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
+          <t>63f6c693-7c22-49cc-ad7d-9aa1774a5972</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>ca-cioos_1efbadd2-e735-48cc-9498-e3a5a88e48a6</t>
+          <t>ca-cioos_d7b34963-67bc-404b-bdd1-b41cc750bdaa</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -27546,7 +27554,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Seawater Carbon Dioxide (CO2) Content from the SuperCO2 System in the Pacific Ecosystem Autonomous Research Laboratory, Bamfield Marine Sciences Centre, BC, Canada (Provisional)</t>
+          <t>Fraser River Airborne Surveys - 2020 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -27564,12 +27572,12 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -27588,46 +27596,44 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-121.5, 49.51], [-121.3, 49.53], [-121.4, 49.95], [-121.5, 50.28], [-121.7, 50.52], [-121.8, 50.66], [-121.8, 50.76], [-121.8, 51.01], [-122.1, 51.32], [-122.3, 51.79], [-122.1, 52.11], [-122.3, 52.37], [-122.3, 52.51], [-122.6, 52.49], [-122.4, 51.96], [-122.5, 51.83], [-122.4, 51.49], [-122.3, 51.18], [-121.9, 50.95], [-121.9, 50.62], [-121.8, 50.53], [-121.7, 50.17], [-121.6, 49.89], [-121.5, 49.63], [-121.5, 49.51]]]}</t>
         </is>
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '850.0', 'min': '400.0'}]</t>
         </is>
       </c>
       <c r="Q248" t="inlineStr">
         <is>
-          <t>inorganicCarbon, seaSurfaceSalinity, seaSurfaceTemperature</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>10.21966/a0v4-x512</t>
+          <t>10.21966/f9m6-qg12</t>
         </is>
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-Olwvch3kCplJcz3CCeR</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MibW0TZpoaJ4Ih_2ev7</t>
         </is>
       </c>
       <c r="T248" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="V248" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr"/>
       <c r="W248" t="n">
         <v>0</v>
       </c>
@@ -27643,12 +27649,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>7b1120bc-4a2c-432c-9e54-879d66751a59</t>
+          <t>c5dafa6e-f2df-4f02-a94e-8f82b29dfb66</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>ca-cioos_b2b18171-35b6-4345-b81b-497a90c2e7c5</t>
+          <t>ca-cioos_1efbadd2-e735-48cc-9498-e3a5a88e48a6</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -27658,7 +27664,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Seagrass fish and macroinvertebrate swaths BC Central Coast</t>
+          <t>Seawater Carbon Dioxide (CO2) Content from the SuperCO2 System in the Pacific Ecosystem Autonomous Research Laboratory, Bamfield Marine Sciences Centre, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -27676,7 +27682,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Nearshore</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -27700,31 +27706,31 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 52.09], [-128.5, 52.04], [-128.5, 51.97], [-128.5, 51.93], [-128.5, 51.9], [-128.4, 51.88], [-128.3, 51.86], [-128.3, 51.83], [-128.2, 51.63], [-127.9, 51.62], [-127.8, 51.77], [-127.8, 51.83], [-127.9, 51.99], [-128.4, 52.09]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359], [-125.1361, 48.8359]]]}</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>[{'max': '10.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
-          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
+          <t>inorganicCarbon, seaSurfaceSalinity, seaSurfaceTemperature</t>
         </is>
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>10.21966/NMNG-SF35</t>
+          <t>10.21966/a0v4-x512</t>
         </is>
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/lJHlH9nm20QQOPuk217xLlxWbNv1/-NPt7327bul36pby-Odi</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RLSJmX44tkZoh8ncSpZECUoikBt1/-Olwvch3kCplJcz3CCeR</t>
         </is>
       </c>
       <c r="T249" t="inlineStr">
@@ -27734,10 +27740,12 @@
       </c>
       <c r="U249" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="V249" t="inlineStr"/>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="V249" t="n">
+        <v>2</v>
+      </c>
       <c r="W249" t="n">
         <v>0</v>
       </c>
@@ -27753,12 +27761,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>49374495-400f-4acc-aac6-d7d0b7cae297</t>
+          <t>7b1120bc-4a2c-432c-9e54-879d66751a59</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>ca-cioos_bafcd0eb-8249-471b-b93b-0797cfeea287</t>
+          <t>ca-cioos_b2b18171-35b6-4345-b81b-497a90c2e7c5</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -27768,7 +27776,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020), Central Coast, British Columbia, Canada</t>
+          <t>Seagrass fish and macroinvertebrate swaths BC Central Coast</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -27786,12 +27794,12 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
+          <t>Nearshore</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -27814,37 +27822,37 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.64], [-128.1, 51.64], [-128.1, 52.01], [-128.5, 52.01], [-128.5, 51.64]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 52.09], [-128.5, 52.04], [-128.5, 51.97], [-128.5, 51.93], [-128.5, 51.9], [-128.4, 51.88], [-128.3, 51.86], [-128.3, 51.83], [-128.2, 51.63], [-127.9, 51.62], [-127.8, 51.77], [-127.8, 51.83], [-127.9, 51.99], [-128.4, 52.09]]]}</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '10.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q250" t="inlineStr">
         <is>
-          <t>macroalgalCanopyCoverAndComposition, other</t>
+          <t>fishAbundanceAndDistribution, invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>10.21966/20ym-8826</t>
+          <t>10.21966/NMNG-SF35</t>
         </is>
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Miha19AtLQ2u1uo0b_q</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/lJHlH9nm20QQOPuk217xLlxWbNv1/-NPt7327bul36pby-Odi</t>
         </is>
       </c>
       <c r="T250" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="U250" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="V250" t="inlineStr"/>
@@ -27863,12 +27871,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>613ba2f9-b21d-445f-8eaa-f42950c9350b</t>
+          <t>49374495-400f-4acc-aac6-d7d0b7cae297</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>ca-cioos_ba41d935-f293-447f-be3d-7098e569b431</t>
+          <t>ca-cioos_bafcd0eb-8249-471b-b93b-0797cfeea287</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -27878,7 +27886,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Water Property Measurements from Conductivity-Temperature-Depth Profiles, BC, Canada (Research)</t>
+          <t>Spatial extent of surface canopy kelp derived from fixed-wing surveys (2020), Central Coast, British Columbia, Canada</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -27896,12 +27904,12 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>Oceanography, Nearshore, Watersheds, Juvenile Salmon Program</t>
+          <t>Nearshore, Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -27920,46 +27928,44 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 51.64], [-128.1, 51.64], [-128.1, 52.01], [-128.5, 52.01], [-128.5, 51.64]]]}</t>
         </is>
       </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>[{'max': '700.0', 'min': '1.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q251" t="inlineStr">
         <is>
-          <t>oxygen, subSurfaceSalinity, subSurfaceTemperature</t>
+          <t>macroalgalCanopyCoverAndComposition, other</t>
         </is>
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>10.21966/kace-2d24</t>
+          <t>10.21966/20ym-8826</t>
         </is>
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MX35qgX-BrwJDdeJKe1</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Miha19AtLQ2u1uo0b_q</t>
         </is>
       </c>
       <c r="T251" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="U251" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="V251" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr"/>
       <c r="W251" t="n">
         <v>0</v>
       </c>
@@ -27975,12 +27981,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
+          <t>613ba2f9-b21d-445f-8eaa-f42950c9350b</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>ca-cioos_fb5c9e1e-a911-46b7-8c1d-e34215a105ed</t>
+          <t>ca-cioos_ba41d935-f293-447f-be3d-7098e569b431</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -27990,7 +27996,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 Analyzer located at Bamfield Marine Sciences Centre, Bamfield, BC, Canada (Provisional)</t>
+          <t>Water Property Measurements from Conductivity-Temperature-Depth Profiles, BC, Canada (Research)</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -28008,7 +28014,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Oceanography, Nearshore, Watersheds, Juvenile Salmon Program</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -28032,31 +28038,31 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-125.13535, 48.83515]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.5, 52.27], [-127.4, 52.21], [-127.2, 51.66], [-125.6, 51.13], [-124.8, 50.96], [-124.1, 50.43], [-124.7, 49.98], [-124.9, 49.8], [-126.7, 50.45], [-128.1, 51.37], [-128.4, 51.69], [-128.5, 52.27]]]}</t>
         </is>
       </c>
       <c r="P252" t="inlineStr">
         <is>
-          <t>[{'max': '20.0', 'min': '20.0'}]</t>
+          <t>[{'max': '700.0', 'min': '1.0'}]</t>
         </is>
       </c>
       <c r="Q252" t="inlineStr">
         <is>
-          <t>seaSurfaceTemperature, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
+          <t>oxygen, subSurfaceSalinity, subSurfaceTemperature</t>
         </is>
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>10.21966/65d8-k051</t>
+          <t>10.21966/kace-2d24</t>
         </is>
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-NdH-jgHZQzKrYdb2nw_</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-MX35qgX-BrwJDdeJKe1</t>
         </is>
       </c>
       <c r="T252" t="inlineStr">
@@ -28066,11 +28072,11 @@
       </c>
       <c r="U252" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="V252" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W252" t="n">
         <v>0</v>
@@ -28087,12 +28093,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>c657dfa1-5970-4794-9c46-7c352df393d7</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>ca-cioos_91107fce-93a4-4bc9-bce4-e7d9e1cf02a0</t>
+          <t>ca-cioos_fb5c9e1e-a911-46b7-8c1d-e34215a105ed</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -28102,7 +28108,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Sentinel 3A and 3B Chlorophyll and Suspended Matter Concentrations for Coastal British Columbia and Southeast Alaska, 8-Day Average (Research)</t>
+          <t>Seawater Carbon Dioxide (CO2) Content from the Burke-o-Lator pCO2/TCO2 Analyzer located at Bamfield Marine Sciences Centre, Bamfield, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -28148,41 +28154,41 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-139.0, 47.0], [-121.5, 47.0], [-121.5, 59.5], [-139.0, 59.5], [-139.0, 47.0]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-125.13535, 48.83515]}</t>
         </is>
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>[{'max': '5.0', 'min': '0.0'}]</t>
+          <t>[{'max': '20.0', 'min': '20.0'}]</t>
         </is>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
-          <t>phytoplanktonBiomassAndDiversity, particulateMatter, other</t>
+          <t>seaSurfaceTemperature, inorganicCarbon, subSurfaceSalinity, subSurfaceTemperature</t>
         </is>
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>10.21966/175j-8k96</t>
+          <t>10.21966/65d8-k051</t>
         </is>
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-Nueis-TZEnz_78f8PYf</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/tV5qE0aUgaOjSVmgPgiZ6MyHuSy1/-NdH-jgHZQzKrYdb2nw_</t>
         </is>
       </c>
       <c r="T253" t="inlineStr">
         <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="U253" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
       <c r="V253" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W253" t="n">
         <v>0</v>
@@ -28199,12 +28205,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>ca-cioos_d1bef0b7-4d15-4bc1-bf34-faca6352891f</t>
+          <t>ca-cioos_91107fce-93a4-4bc9-bce4-e7d9e1cf02a0</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -28214,7 +28220,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Daily satellite (Sentinel 3A and 3B) chlorophyll and suspended matter concentrations for coastal British Columbia and southeast Alaska</t>
+          <t>Sentinel 3A and 3B Chlorophyll and Suspended Matter Concentrations for Coastal British Columbia and Southeast Alaska, 8-Day Average (Research)</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -28275,12 +28281,12 @@
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>10.21966/dveq-bt48</t>
+          <t>10.21966/175j-8k96</t>
         </is>
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-NTteirxDjvnABVz_7Dh</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-Nueis-TZEnz_78f8PYf</t>
         </is>
       </c>
       <c r="T254" t="inlineStr">
@@ -28290,11 +28296,11 @@
       </c>
       <c r="U254" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="V254" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W254" t="n">
         <v>0</v>
@@ -28311,12 +28317,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>b7b923ed-b3fa-48b3-878d-40a3797046bc</t>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>ca-cioos_f7538807-4d49-4ed8-ad36-836c0e71428a</t>
+          <t>ca-cioos_d1bef0b7-4d15-4bc1-bf34-faca6352891f</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -28326,7 +28332,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>3m Digital Elevation Model - Calvert Island - British Columbia - Canada</t>
+          <t>Daily satellite (Sentinel 3A and 3B) chlorophyll and suspended matter concentrations for coastal British Columbia and southeast Alaska</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -28344,12 +28350,12 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>Geospatial, Airborne Coastal Observatory</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -28368,50 +28374,52 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.16482, 51.408116], [-127.868831, 51.408116], [-127.868831, 51.734994], [-128.16482, 51.734994], [-128.16482, 51.408116]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-139.0, 47.0], [-121.5, 47.0], [-121.5, 59.5], [-139.0, 59.5], [-139.0, 47.0]]]}</t>
         </is>
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
+          <t>[{'max': '5.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q255" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>phytoplanktonBiomassAndDiversity, particulateMatter, other</t>
         </is>
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>10.21966/RZVW-4A72</t>
+          <t>10.21966/dveq-bt48</t>
         </is>
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW13R3BBSGRER2ZkYnM</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/7U7b8oPpeTN6gjvXlUCTGJr5pga2/-NTteirxDjvnABVz_7Dh</t>
         </is>
       </c>
       <c r="T255" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="U255" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="V255" t="inlineStr"/>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="V255" t="n">
+        <v>5</v>
+      </c>
       <c r="W255" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X255" t="inlineStr">
         <is>
-          <t>[{'year': '2022', 'total': 1}]</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -28421,12 +28429,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
+          <t>b7b923ed-b3fa-48b3-878d-40a3797046bc</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>ca-cioos_33c8ce77-0674-4933-a305-01a25d253f70</t>
+          <t>ca-cioos_f7538807-4d49-4ed8-ad36-836c0e71428a</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -28436,7 +28444,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Sea star microbiome data from 16S amplicon sequencing associated with rocky intertidal sites on Calvert and Quadra Islands</t>
+          <t>3m Digital Elevation Model - Calvert Island - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -28454,7 +28462,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Nearshore, Genomics</t>
+          <t>Geospatial, Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -28482,48 +28490,46 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.3, 49.87], [-124.8, 49.87], [-124.8, 51.75], [-128.3, 51.75], [-128.3, 49.87]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.16482, 51.408116], [-127.868831, 51.408116], [-127.868831, 51.734994], [-128.16482, 51.734994], [-128.16482, 51.408116]]]}</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>[{'max': '0', 'min': '0'}]</t>
+          <t>[{'max': '1013.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution, microbeBiomassAndDiversity</t>
+          <t>other</t>
         </is>
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>10.21966/0xvh-1318</t>
+          <t>10.21966/RZVW-4A72</t>
         </is>
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/4TvAwNKXC7PkAi0TEZsZbbAzXfi1/-Oo1MBmr8fW1fputdBh6</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MW13R3BBSGRER2ZkYnM</t>
         </is>
       </c>
       <c r="T256" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="U256" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="V256" t="n">
-        <v>2</v>
-      </c>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr"/>
       <c r="W256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X256" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'year': '2022', 'total': 1}]</t>
         </is>
       </c>
     </row>
@@ -28533,12 +28539,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
+          <t>e14d0456-297e-4636-8e7c-c615791b165e</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>ca-cioos_a8671db6-81cc-4c92-b681-58595fe66182</t>
+          <t>ca-cioos_33c8ce77-0674-4933-a305-01a25d253f70</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -28548,7 +28554,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Water Property Measurements from the Bute Inlet Ocean Observing Station (BIOOS) Wirewalker, Bute Inlet, BC, Canada (Provisional)</t>
+          <t>Sea star microbiome data from 16S amplicon sequencing associated with rocky intertidal sites on Calvert and Quadra Islands</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -28566,12 +28572,12 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Oceanography</t>
+          <t>Nearshore, Genomics</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>onGoing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -28590,45 +28596,45 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>{'type': 'Point', 'coordinates': [-124.9009, 50.5744]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.3, 49.87], [-124.8, 49.87], [-124.8, 51.75], [-128.3, 51.75], [-128.3, 49.87]]]}</t>
         </is>
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>[{'max': '250.0', 'min': '0.0'}]</t>
+          <t>[{'max': '0', 'min': '0'}]</t>
         </is>
       </c>
       <c r="Q257" t="inlineStr">
         <is>
-          <t>subSurfaceTemperature, subSurfaceSalinity, oxygen, phytoplanktonBiomassAndDiversity</t>
+          <t>invertebrateAbundanceAndDistribution, microbeBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>10.21966/3q5j-n957</t>
+          <t>10.21966/0xvh-1318</t>
         </is>
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-OqDQ7wqqJtwSgUoAN1g</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/4TvAwNKXC7PkAi0TEZsZbbAzXfi1/-Oo1MBmr8fW1fputdBh6</t>
         </is>
       </c>
       <c r="T257" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="U257" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="V257" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W257" t="n">
         <v>0</v>
@@ -28645,12 +28651,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>227eb965-1892-4bad-8ded-dd2e1d68fdf6</t>
+          <t>2510cc69-bd46-4534-a62f-dae1903b388d</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>ca-cioos_08d3e779-2f44-4ce3-82cb-c7b763f72175</t>
+          <t>ca-cioos_a8671db6-81cc-4c92-b681-58595fe66182</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -28660,7 +28666,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>DNA metabarcoding data from Autonomous Reef Monitoring Structures (ARMS) deployed around Calvert Island British Columbia</t>
+          <t>Water Property Measurements from the Bute Inlet Ocean Observing Station (BIOOS) Wirewalker, Bute Inlet, BC, Canada (Provisional)</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -28678,12 +28684,12 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Nearshore, Genomics</t>
+          <t>Oceanography</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>onGoing</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -28702,44 +28708,46 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.61], [-127.8, 51.61], [-127.8, 51.9], [-128.4, 51.9], [-128.4, 51.61]]]}</t>
+          <t>{'type': 'Point', 'coordinates': [-124.9009, 50.5744]}</t>
         </is>
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>[{'max': '30.0', 'min': '0.0'}]</t>
+          <t>[{'max': '250.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q258" t="inlineStr">
         <is>
-          <t>invertebrateAbundanceAndDistribution</t>
+          <t>subSurfaceTemperature, subSurfaceSalinity, oxygen, phytoplanktonBiomassAndDiversity</t>
         </is>
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>10.21966/kmc2-5r12</t>
+          <t>10.21966/3q5j-n957</t>
         </is>
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-ORSLLie2O-FFN8cPV1e</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/3LY8ezYsI9hglwZSsfkAdSBcoEG3/-OqDQ7wqqJtwSgUoAN1g</t>
         </is>
       </c>
       <c r="T258" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="U258" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="V258" t="inlineStr"/>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="V258" t="n">
+        <v>2</v>
+      </c>
       <c r="W258" t="n">
         <v>0</v>
       </c>
@@ -28755,12 +28763,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>ed22dc0f-f2cc-41e5-ac1c-893e1b65c6d0</t>
+          <t>227eb965-1892-4bad-8ded-dd2e1d68fdf6</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>ca-cioos_7e49967a-b5ab-443d-860b-e3c0eb0f709c</t>
+          <t>ca-cioos_08d3e779-2f44-4ce3-82cb-c7b763f72175</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -28770,7 +28778,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Horne Lake Bathymetry Mapping</t>
+          <t>DNA metabarcoding data from Autonomous Reef Monitoring Structures (ARMS) deployed around Calvert Island British Columbia</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -28780,7 +28788,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>CC-BY-NC-4.0</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="H259" t="b">
@@ -28788,7 +28796,7 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Nearshore, Genomics</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -28812,46 +28820,44 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.7872, 49.3105], [-124.6447, 49.3105], [-124.6447, 49.3644], [-124.7872, 49.3644], [-124.7872, 49.3105]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4, 51.61], [-127.8, 51.61], [-127.8, 51.9], [-128.4, 51.9], [-128.4, 51.61]]]}</t>
         </is>
       </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>[{'max': '50.0', 'min': '0.0'}]</t>
+          <t>[{'max': '30.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q259" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>invertebrateAbundanceAndDistribution</t>
         </is>
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>10.21966/vwee-e004</t>
+          <t>10.21966/kmc2-5r12</t>
         </is>
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/G8LjsjnnPxb5TxWL730BxDTQu532/-Njn-0LeJ-Uwj4L8EmOV</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/pX9Euv7m4yaHRKPuMtylMexACtt2/-ORSLLie2O-FFN8cPV1e</t>
         </is>
       </c>
       <c r="T259" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="U259" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="V259" t="n">
-        <v>3</v>
-      </c>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr"/>
       <c r="W259" t="n">
         <v>0</v>
       </c>
@@ -28867,12 +28873,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>18f56a52-11af-446a-aea9-07feca8d197e</t>
+          <t>ed22dc0f-f2cc-41e5-ac1c-893e1b65c6d0</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>ca-cioos_e897c9d0-3fca-4c89-b37f-e571413ffd12</t>
+          <t>ca-cioos_7e49967a-b5ab-443d-860b-e3c0eb0f709c</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -28882,7 +28888,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Joffre Provincial Park Aerial Surveys - 2025 - Airborne Coastal Observatory</t>
+          <t>Horne Lake Bathymetry Mapping</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -28892,7 +28898,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>CC-BY-4.0</t>
+          <t>CC-BY-NC-4.0</t>
         </is>
       </c>
       <c r="H260" t="b">
@@ -28900,7 +28906,7 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
@@ -28928,12 +28934,12 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.5281, 50.3147], [-122.4303, 50.3147], [-122.4303, 50.3796], [-122.5281, 50.3796], [-122.5281, 50.3147]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.7872, 49.3105], [-124.6447, 49.3105], [-124.6447, 49.3644], [-124.7872, 49.3644], [-124.7872, 49.3105]]]}</t>
         </is>
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>[{'max': '475.0', 'min': '0.0'}]</t>
+          <t>[{'max': '50.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q260" t="inlineStr">
@@ -28943,12 +28949,12 @@
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>10.21966/k0z0-3z50</t>
+          <t>10.21966/vwee-e004</t>
         </is>
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Ot_OaAHxjund0-w5rXq</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/G8LjsjnnPxb5TxWL730BxDTQu532/-Njn-0LeJ-Uwj4L8EmOV</t>
         </is>
       </c>
       <c r="T260" t="inlineStr">
@@ -28958,10 +28964,12 @@
       </c>
       <c r="U260" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="V260" t="inlineStr"/>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="V260" t="n">
+        <v>3</v>
+      </c>
       <c r="W260" t="n">
         <v>0</v>
       </c>
@@ -28977,12 +28985,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>6c4803cc-d1c6-4327-806a-7f6796606175</t>
+          <t>18f56a52-11af-446a-aea9-07feca8d197e</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>ca-cioos_6c34ed6e-5a17-41f2-b83a-cd59d1ce07bd</t>
+          <t>ca-cioos_e897c9d0-3fca-4c89-b37f-e571413ffd12</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -28992,7 +29000,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Knight Inlet Multibeam Bathymetry Survey</t>
+          <t>Joffre Provincial Park Aerial Surveys - 2025 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -29010,7 +29018,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -29038,12 +29046,12 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-126.0537, 50.6529], [-125.9229, 50.6529], [-125.9229, 50.7077], [-126.0537, 50.7077], [-126.0537, 50.6529]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.5281, 50.3147], [-122.4303, 50.3147], [-122.4303, 50.3796], [-122.5281, 50.3796], [-122.5281, 50.3147]]]}</t>
         </is>
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>[{'max': '288.0', 'min': '0.0'}]</t>
+          <t>[{'max': '475.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q261" t="inlineStr">
@@ -29053,27 +29061,25 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>10.21966/8dgz-1z27</t>
+          <t>10.21966/k0z0-3z50</t>
         </is>
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OG7EOynnzSIOU7LPWgs</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Ot_OaAHxjund0-w5rXq</t>
         </is>
       </c>
       <c r="T261" t="inlineStr">
         <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="U261" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="V261" t="n">
-        <v>1</v>
-      </c>
+      <c r="V261" t="inlineStr"/>
       <c r="W261" t="n">
         <v>0</v>
       </c>
@@ -29089,12 +29095,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>ce6f3f8c-6b57-4f18-be46-8c0b5a4baeb9</t>
+          <t>6c4803cc-d1c6-4327-806a-7f6796606175</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>ca-cioos_8755f475-2133-4205-baff-5e2937824f45</t>
+          <t>ca-cioos_6c34ed6e-5a17-41f2-b83a-cd59d1ce07bd</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -29104,7 +29110,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Poole Creek Aerial Surveys - Airborne Coastal Observatory</t>
+          <t>Knight Inlet Multibeam Bathymetry Survey</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -29122,7 +29128,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -29150,12 +29156,12 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-122.9075, 50.2436], [-122.8124, 50.2436], [-122.8124, 50.3016], [-122.9075, 50.3016], [-122.9075, 50.2436]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-126.0537, 50.6529], [-125.9229, 50.6529], [-125.9229, 50.7077], [-126.0537, 50.7077], [-126.0537, 50.6529]]]}</t>
         </is>
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>[{'max': '450.0', 'min': '200.0'}]</t>
+          <t>[{'max': '288.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q262" t="inlineStr">
@@ -29165,12 +29171,12 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>10.21966/g8f2-jw82</t>
+          <t>10.21966/8dgz-1z27</t>
         </is>
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OtfdtO43um_1J_LdCpn</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OG7EOynnzSIOU7LPWgs</t>
         </is>
       </c>
       <c r="T262" t="inlineStr">
@@ -29183,7 +29189,9 @@
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="V262" t="inlineStr"/>
+      <c r="V262" t="n">
+        <v>1</v>
+      </c>
       <c r="W262" t="n">
         <v>0</v>
       </c>
@@ -29199,12 +29207,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>e1247209-cc26-4788-82a2-dd8a5c971e22</t>
+          <t>ce6f3f8c-6b57-4f18-be46-8c0b5a4baeb9</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>ca-cioos_2e5ddbaa-4f0c-4339-8595-1ddbd35c3df4</t>
+          <t>ca-cioos_8755f475-2133-4205-baff-5e2937824f45</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -29214,7 +29222,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Glacier and Icefield Aerial Surveys in British Columbia, Washington, and Alberta - 2025 - Airborne Coastal Observatory</t>
+          <t>Poole Creek Aerial Surveys - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -29260,12 +29268,12 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-127.9263, 48.0077], [-112.7224, 48.0077], [-112.7224, 54.6673], [-127.9263, 54.6673], [-127.9263, 48.0077]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-122.9075, 50.2436], [-122.8124, 50.2436], [-122.8124, 50.3016], [-122.9075, 50.3016], [-122.9075, 50.2436]]]}</t>
         </is>
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>[{'max': '4019.0', 'min': '0.0'}]</t>
+          <t>[{'max': '450.0', 'min': '200.0'}]</t>
         </is>
       </c>
       <c r="Q263" t="inlineStr">
@@ -29275,22 +29283,22 @@
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>10.21966/n6ga-nc24</t>
+          <t>10.21966/g8f2-jw82</t>
         </is>
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Ou3t_K6rGOHTMO67Xbq</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OtfdtO43um_1J_LdCpn</t>
         </is>
       </c>
       <c r="T263" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="U263" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="V263" t="inlineStr"/>
@@ -29309,12 +29317,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>5ac3ac5f-702e-43d8-bcb7-79f30c4d9e08</t>
+          <t>e1247209-cc26-4788-82a2-dd8a5c971e22</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>ca-cioos_656ea307-fed0-48ca-b5d8-1bc017dc52d2</t>
+          <t>ca-cioos_2e5ddbaa-4f0c-4339-8595-1ddbd35c3df4</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -29324,7 +29332,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Botanical Beach - Juan de Fuca Provincial Park - Drone Mapping</t>
+          <t>Glacier and Icefield Aerial Surveys in British Columbia, Washington, and Alberta - 2025 - Airborne Coastal Observatory</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -29342,7 +29350,7 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Airborne Coastal Observatory, Geospatial</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -29370,12 +29378,12 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-124.45265489, 48.52152402], [-124.43377214, 48.52152402], [-124.43377214, 48.53061904], [-124.45265489, 48.53061904], [-124.45265489, 48.52152402]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-127.9263, 48.0077], [-112.7224, 48.0077], [-112.7224, 54.6673], [-127.9263, 54.6673], [-127.9263, 48.0077]]]}</t>
         </is>
       </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>[{'max': '20.0', 'min': '0.0'}]</t>
+          <t>[{'max': '4019.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q264" t="inlineStr">
@@ -29385,12 +29393,12 @@
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>10.21966/kn3e-fn08</t>
+          <t>10.21966/n6ga-nc24</t>
         </is>
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUdvcmtQME1NZmdWcDY</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-Ou3t_K6rGOHTMO67Xbq</t>
         </is>
       </c>
       <c r="T264" t="inlineStr">
@@ -29419,12 +29427,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>0cef18ab-cea6-4522-baba-1bcd73a30646</t>
+          <t>5ac3ac5f-702e-43d8-bcb7-79f30c4d9e08</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>ca-cioos_66fbb7f5-3644-471a-95ee-f8d3758e888b</t>
+          <t>ca-cioos_656ea307-fed0-48ca-b5d8-1bc017dc52d2</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -29434,7 +29442,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Mount Robson Aerial Photo and LiDAR Survey</t>
+          <t>Botanical Beach - Juan de Fuca Provincial Park - Drone Mapping</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -29452,7 +29460,7 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>Airborne Coastal Observatory, Geospatial</t>
+          <t>Geospatial</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -29472,7 +29480,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Tula Foundation</t>
+          <t>Hakai Institute</t>
         </is>
       </c>
       <c r="N265" t="n">
@@ -29480,12 +29488,12 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-119.3, 53.03], [-118.8, 53.03], [-118.8, 53.26], [-119.3, 53.26], [-119.3, 53.03]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-124.45265489, 48.52152402], [-124.43377214, 48.52152402], [-124.43377214, 48.53061904], [-124.45265489, 48.53061904], [-124.45265489, 48.52152402]]]}</t>
         </is>
       </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>[{'max': '3954.0', 'min': '800.0'}]</t>
+          <t>[{'max': '20.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q265" t="inlineStr">
@@ -29495,18 +29503,22 @@
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>10.21966/w9n0-kn30</t>
+          <t>10.21966/kn3e-fn08</t>
         </is>
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICbtZXkj6anGvgB3Qi</t>
-        </is>
-      </c>
-      <c r="T265" t="inlineStr"/>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUdvcmtQME1NZmdWcDY</t>
+        </is>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
       <c r="U265" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="V265" t="inlineStr"/>
@@ -29514,6 +29526,112 @@
         <v>0</v>
       </c>
       <c r="X265" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>264</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>0cef18ab-cea6-4522-baba-1bcd73a30646</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>ca-cioos_66fbb7f5-3644-471a-95ee-f8d3758e888b</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Hakai Institute</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Mount Robson Aerial Photo and LiDAR Survey</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="H266" t="b">
+        <v>0</v>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Airborne Coastal Observatory, Geospatial</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>Tula Foundation</t>
+        </is>
+      </c>
+      <c r="N266" t="n">
+        <v>1</v>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-119.3, 53.03], [-118.8, 53.03], [-118.8, 53.26], [-119.3, 53.26], [-119.3, 53.03]]]}</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>[{'max': '3954.0', 'min': '800.0'}]</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R266" t="inlineStr">
+        <is>
+          <t>10.21966/w9n0-kn30</t>
+        </is>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-OICbtZXkj6anGvgB3Qi</t>
+        </is>
+      </c>
+      <c r="T266" t="inlineStr"/>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="V266" t="inlineStr"/>
+      <c r="W266" t="n">
+        <v>0</v>
+      </c>
+      <c r="X266" t="inlineStr">
         <is>
           <t>[]</t>
         </is>

--- a/main/catalog_summary.xlsx
+++ b/main/catalog_summary.xlsx
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="V63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W63" t="n">
         <v>0</v>
@@ -7326,7 +7326,11 @@
       <c r="H64" t="b">
         <v>0</v>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Nearshore</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
           <t>completed</t>
@@ -7382,12 +7386,10 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="V64" t="n">
-        <v>5</v>
-      </c>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr"/>
       <c r="W64" t="n">
         <v>0</v>
       </c>
@@ -8852,7 +8854,11 @@
       <c r="H78" t="b">
         <v>0</v>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Airborne Coastal Observatory</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr">
         <is>
           <t>completed</t>
@@ -8891,7 +8897,11 @@
           <t>other</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr"/>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>10.21966/awsk-my87</t>
+        </is>
+      </c>
       <c r="S78" t="inlineStr">
         <is>
           <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/RvRPlFMSsIaBwoGdQIq5BVYfBBa2/-MkE_rRkw9irKz8XxrLV</t>
@@ -8904,14 +8914,18 @@
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="V78" t="n">
-        <v>4</v>
-      </c>
-      <c r="W78" t="inlineStr"/>
-      <c r="X78" t="inlineStr"/>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="n">
+        <v>0</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9052,7 +9066,11 @@
       <c r="H80" t="b">
         <v>0</v>
       </c>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Airborne Coastal Observatory</t>
+        </is>
+      </c>
       <c r="J80" t="inlineStr">
         <is>
           <t>completed</t>
@@ -9104,11 +9122,11 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="V80" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W80" t="inlineStr"/>
       <c r="X80" t="inlineStr"/>
@@ -9150,7 +9168,11 @@
       <c r="H81" t="b">
         <v>0</v>
       </c>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Airborne Coastal Observatory</t>
+        </is>
+      </c>
       <c r="J81" t="inlineStr">
         <is>
           <t>completed</t>
@@ -9202,11 +9224,11 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="V81" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr"/>
@@ -9248,7 +9270,11 @@
       <c r="H82" t="b">
         <v>0</v>
       </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Airborne Coastal Observatory</t>
+        </is>
+      </c>
       <c r="J82" t="inlineStr">
         <is>
           <t>completed</t>
@@ -9300,11 +9326,11 @@
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="V82" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr"/>
@@ -9630,7 +9656,7 @@
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="V85" t="inlineStr"/>
@@ -10568,7 +10594,11 @@
       <c r="H94" t="b">
         <v>0</v>
       </c>
-      <c r="I94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Nearshore</t>
+        </is>
+      </c>
       <c r="J94" t="inlineStr">
         <is>
           <t>completed</t>
@@ -10624,12 +10654,10 @@
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="V94" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr"/>
       <c r="W94" t="n">
         <v>0</v>
       </c>
@@ -11120,7 +11148,11 @@
       <c r="H99" t="b">
         <v>0</v>
       </c>
-      <c r="I99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Geospatial</t>
+        </is>
+      </c>
       <c r="J99" t="inlineStr">
         <is>
           <t>completed</t>
@@ -11176,12 +11208,10 @@
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="V99" t="n">
-        <v>1</v>
-      </c>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr"/>
       <c r="W99" t="n">
         <v>0</v>
       </c>
@@ -11643,12 +11673,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
+          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ca-cioos_4fac74c8-f58c-46b0-87dc-ab70ce756880</t>
+          <t>ca-cioos_51171738-7556-48f1-8757-658d99fa25dd</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -11658,7 +11688,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Discovery Islands LiDAR Dataset  - 2014 - British Columbia - Canada</t>
+          <t>Eelgrass Extent 2014 - Central Coast</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -11676,7 +11706,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Geospatial</t>
+          <t>Geospatial, Nearshore</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -11700,16 +11730,16 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-125.3704833984375, 49.9229354544957], [-124.75524902343749, 49.9229354544957], [-124.75524902343749, 50.291094042311386], [-125.3704833984375, 50.291094042311386], [-125.3704833984375, 49.9229354544957]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.4878540039062, 51.653814904471545], [-128.0978393554687, 51.653814904471545], [-128.0978393554687, 52.07950600379698], [-128.4878540039062, 52.07950600379698], [-128.4878540039062, 51.653814904471545]]]}</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>[{'max': '500.0', 'min': '0.0'}]</t>
+          <t>[{'max': '50.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -11720,7 +11750,7 @@
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXR6SWM4aTRoYk9MeU0</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUZuOThkU2QzakpPNEQ</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
@@ -11730,7 +11760,7 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="V104" t="n">
@@ -11745,12 +11775,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>017ab2c4-70ea-484a-ae6c-7d441d2ba19d</t>
+          <t>57770468-42a9-4654-bf7d-7672939ed002</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ca-cioos_51171738-7556-48f1-8757-658d99fa25dd</t>
+          <t>ca-cioos_4fac74c8-f58c-46b0-87dc-ab70ce756880</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -11760,7 +11790,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Eelgrass Extent 2014 - Central Coast</t>
+          <t>Discovery Islands LiDAR Dataset  - 2014 - British Columbia - Canada</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -11776,7 +11806,11 @@
       <c r="H105" t="b">
         <v>0</v>
       </c>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Geospatial</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr">
         <is>
           <t>completed</t>
@@ -11798,16 +11832,16 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>{'type': 'Polygon', 'coordinates': [[[-128.4878540039062, 51.653814904471545], [-128.0978393554687, 51.653814904471545], [-128.0978393554687, 52.07950600379698], [-128.4878540039062, 52.07950600379698], [-128.4878540039062, 51.653814904471545]]]}</t>
+          <t>{'type': 'Polygon', 'coordinates': [[[-125.3704833984375, 49.9229354544957], [-124.75524902343749, 49.9229354544957], [-124.75524902343749, 50.291094042311386], [-125.3704833984375, 50.291094042311386], [-125.3704833984375, 49.9229354544957]]]}</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>[{'max': '50.0', 'min': '0.0'}]</t>
+          <t>[{'max': '500.0', 'min': '0.0'}]</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -11818,7 +11852,7 @@
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
-          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MUZuOThkU2QzakpPNEQ</t>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MXR6SWM4aTRoYk9MeU0</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
@@ -11828,11 +11862,11 @@
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="V105" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W105" t="inlineStr"/>
       <c r="X105" t="inlineStr"/>
@@ -14011,12 +14045,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>30560220-bc44-4020-b424-0abf617d1c00</t>
+          <t>d8754c99-a540-4085-8c66-d9447da5f6e9</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ca-cioos_25674e9b-1d49-4270-b917-cfe6cdc30f95</t>
+          <t>ca-cioos_26443ab2-964f-4031-a53b-f132434573e8</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -14026,7 +14060,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Watersheds of the northern Pacific coastal temperate rainforest margin</t>
+          <t>Ecosystem Comparison Plots - Calvert Island</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -14044,7 +14078,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Watersheds</t>
+          <t>Geospatial, Watersheds</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -14068,50 +14102,52 @@
         </is>
       </c>
       <c r="N126" t="n">
+        <v>1</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>{'type': 'Polygon', 'coordinates': [[[-128.13903808593744, 51.626542529786036], [-127.97355651855466, 51.626542529786036], [-127.97355651855466, 51.67766477883444], [-128.13903808593744, 51.67766477883444], [-128.13903808593744, 51.626542529786036]]]}</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>[{'max': '0.0', 'min': '0.0'}]</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>10.21966/1.56481</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>https://hakaiinstitute.github.io/hakai-metadata-entry-form#/en/hakai/qbqh6DF00XZq8MOpQ3kKkI9GUv43/-MWc4TU94c2lwT0tYa2U</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>2022-03-29</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      